--- a/data/ahlsell_led_panel_inventory.xlsx
+++ b/data/ahlsell_led_panel_inventory.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y70"/>
+  <dimension ref="A1:Y71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -503,14 +503,14 @@
       </c>
       <c r="D1" s="3" t="inlineStr">
         <is>
+          <t>Tupex</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
           <t>SG Armaturen</t>
         </is>
       </c>
-      <c r="E1" s="3" t="inlineStr">
-        <is>
-          <t>Tupex</t>
-        </is>
-      </c>
       <c r="F1" s="3" t="inlineStr">
         <is>
           <t>Hide-a-lite</t>
@@ -548,67 +548,67 @@
       </c>
       <c r="M1" s="3" t="inlineStr">
         <is>
+          <t>ANETA LIGHTING</t>
+        </is>
+      </c>
+      <c r="N1" s="3" t="inlineStr">
+        <is>
+          <t>Airam</t>
+        </is>
+      </c>
+      <c r="O1" s="3" t="inlineStr">
+        <is>
+          <t>Black Box</t>
+        </is>
+      </c>
+      <c r="P1" s="3" t="inlineStr">
+        <is>
+          <t>Westal</t>
+        </is>
+      </c>
+      <c r="Q1" s="3" t="inlineStr">
+        <is>
+          <t>Legrand</t>
+        </is>
+      </c>
+      <c r="R1" s="3" t="inlineStr">
+        <is>
+          <t>Nokalux</t>
+        </is>
+      </c>
+      <c r="S1" s="3" t="inlineStr">
+        <is>
           <t>ZG Lighting</t>
         </is>
       </c>
-      <c r="N1" s="3" t="inlineStr">
-        <is>
-          <t>Nokalux</t>
-        </is>
-      </c>
-      <c r="O1" s="3" t="inlineStr">
+      <c r="T1" s="3" t="inlineStr">
+        <is>
+          <t>Ensto</t>
+        </is>
+      </c>
+      <c r="U1" s="3" t="inlineStr">
         <is>
           <t>Philips</t>
         </is>
       </c>
-      <c r="P1" s="3" t="inlineStr">
-        <is>
-          <t>Airam</t>
-        </is>
-      </c>
-      <c r="Q1" s="3" t="inlineStr">
+      <c r="V1" s="3" t="inlineStr">
+        <is>
+          <t>THORN</t>
+        </is>
+      </c>
+      <c r="W1" s="3" t="inlineStr">
+        <is>
+          <t>Siteco</t>
+        </is>
+      </c>
+      <c r="X1" s="3" t="inlineStr">
+        <is>
+          <t>Easyform</t>
+        </is>
+      </c>
+      <c r="Y1" s="3" t="inlineStr">
         <is>
           <t>Bergdahls</t>
-        </is>
-      </c>
-      <c r="R1" s="3" t="inlineStr">
-        <is>
-          <t>Legrand</t>
-        </is>
-      </c>
-      <c r="S1" s="3" t="inlineStr">
-        <is>
-          <t>Ensto</t>
-        </is>
-      </c>
-      <c r="T1" s="3" t="inlineStr">
-        <is>
-          <t>Westal</t>
-        </is>
-      </c>
-      <c r="U1" s="3" t="inlineStr">
-        <is>
-          <t>Easyform</t>
-        </is>
-      </c>
-      <c r="V1" s="3" t="inlineStr">
-        <is>
-          <t>Black Box</t>
-        </is>
-      </c>
-      <c r="W1" s="3" t="inlineStr">
-        <is>
-          <t>THORN</t>
-        </is>
-      </c>
-      <c r="X1" s="3" t="inlineStr">
-        <is>
-          <t>ANETA LIGHTING</t>
-        </is>
-      </c>
-      <c r="Y1" s="3" t="inlineStr">
-        <is>
-          <t>Siteco</t>
         </is>
       </c>
     </row>
@@ -625,10 +625,10 @@
         <v>527</v>
       </c>
       <c r="D2" s="5" t="n">
+        <v>233</v>
+      </c>
+      <c r="E2" s="5" t="n">
         <v>1402</v>
-      </c>
-      <c r="E2" s="5" t="n">
-        <v>233</v>
       </c>
       <c r="F2" s="5" t="n">
         <v>223</v>
@@ -704,10 +704,10 @@
         <v>527</v>
       </c>
       <c r="D3" t="n">
+        <v>233</v>
+      </c>
+      <c r="E3" t="n">
         <v>1402</v>
-      </c>
-      <c r="E3" t="n">
-        <v>233</v>
       </c>
       <c r="F3" t="n">
         <v>223</v>
@@ -783,10 +783,10 @@
         <v>523</v>
       </c>
       <c r="D4" s="5" t="n">
+        <v>233</v>
+      </c>
+      <c r="E4" s="5" t="n">
         <v>1391</v>
-      </c>
-      <c r="E4" s="5" t="n">
-        <v>233</v>
       </c>
       <c r="F4" s="5" t="n">
         <v>217</v>
@@ -862,10 +862,10 @@
         <v>522</v>
       </c>
       <c r="D5" t="n">
+        <v>233</v>
+      </c>
+      <c r="E5" t="n">
         <v>1384</v>
-      </c>
-      <c r="E5" t="n">
-        <v>233</v>
       </c>
       <c r="F5" t="n">
         <v>221</v>
@@ -941,10 +941,10 @@
         <v>528</v>
       </c>
       <c r="D6" s="5" t="n">
+        <v>232</v>
+      </c>
+      <c r="E6" s="5" t="n">
         <v>1377</v>
-      </c>
-      <c r="E6" s="5" t="n">
-        <v>232</v>
       </c>
       <c r="F6" s="5" t="n">
         <v>215</v>
@@ -1017,10 +1017,10 @@
         <v>920</v>
       </c>
       <c r="D7" t="n">
+        <v>232</v>
+      </c>
+      <c r="E7" t="n">
         <v>1348</v>
-      </c>
-      <c r="E7" t="n">
-        <v>232</v>
       </c>
       <c r="F7" t="n">
         <v>215</v>
@@ -1096,10 +1096,10 @@
         <v>528</v>
       </c>
       <c r="D8" s="5" t="n">
+        <v>232</v>
+      </c>
+      <c r="E8" s="5" t="n">
         <v>1377</v>
-      </c>
-      <c r="E8" s="5" t="n">
-        <v>232</v>
       </c>
       <c r="F8" s="5" t="n">
         <v>215</v>
@@ -1175,10 +1175,10 @@
         <v>532</v>
       </c>
       <c r="D9" t="n">
+        <v>232</v>
+      </c>
+      <c r="E9" t="n">
         <v>1385</v>
-      </c>
-      <c r="E9" t="n">
-        <v>232</v>
       </c>
       <c r="F9" t="n">
         <v>214</v>
@@ -1254,10 +1254,10 @@
         <v>544</v>
       </c>
       <c r="D10" s="5" t="n">
+        <v>231</v>
+      </c>
+      <c r="E10" s="5" t="n">
         <v>1381</v>
-      </c>
-      <c r="E10" s="5" t="n">
-        <v>231</v>
       </c>
       <c r="F10" s="5" t="n">
         <v>218</v>
@@ -1333,10 +1333,10 @@
         <v>544</v>
       </c>
       <c r="D11" t="n">
+        <v>231</v>
+      </c>
+      <c r="E11" t="n">
         <v>1385</v>
-      </c>
-      <c r="E11" t="n">
-        <v>231</v>
       </c>
       <c r="F11" t="n">
         <v>225</v>
@@ -1412,10 +1412,10 @@
         <v>544</v>
       </c>
       <c r="D12" s="5" t="n">
+        <v>224</v>
+      </c>
+      <c r="E12" s="5" t="n">
         <v>1372</v>
-      </c>
-      <c r="E12" s="5" t="n">
-        <v>224</v>
       </c>
       <c r="F12" s="5" t="n">
         <v>228</v>
@@ -1491,10 +1491,10 @@
         <v>545</v>
       </c>
       <c r="D13" t="n">
+        <v>224</v>
+      </c>
+      <c r="E13" t="n">
         <v>1360</v>
-      </c>
-      <c r="E13" t="n">
-        <v>224</v>
       </c>
       <c r="F13" t="n">
         <v>228</v>
@@ -1570,10 +1570,10 @@
         <v>545</v>
       </c>
       <c r="D14" s="5" t="n">
+        <v>224</v>
+      </c>
+      <c r="E14" s="5" t="n">
         <v>1331</v>
-      </c>
-      <c r="E14" s="5" t="n">
-        <v>224</v>
       </c>
       <c r="F14" s="5" t="n">
         <v>228</v>
@@ -1649,10 +1649,10 @@
         <v>545</v>
       </c>
       <c r="D15" t="n">
+        <v>224</v>
+      </c>
+      <c r="E15" t="n">
         <v>1360</v>
-      </c>
-      <c r="E15" t="n">
-        <v>224</v>
       </c>
       <c r="F15" t="n">
         <v>228</v>
@@ -1728,10 +1728,10 @@
         <v>545</v>
       </c>
       <c r="D16" s="5" t="n">
+        <v>224</v>
+      </c>
+      <c r="E16" s="5" t="n">
         <v>1348</v>
-      </c>
-      <c r="E16" s="5" t="n">
-        <v>224</v>
       </c>
       <c r="F16" s="5" t="n">
         <v>226</v>
@@ -1807,10 +1807,10 @@
         <v>572</v>
       </c>
       <c r="D17" t="n">
+        <v>224</v>
+      </c>
+      <c r="E17" t="n">
         <v>1347</v>
-      </c>
-      <c r="E17" t="n">
-        <v>224</v>
       </c>
       <c r="F17" t="n">
         <v>228</v>
@@ -1886,10 +1886,10 @@
         <v>571</v>
       </c>
       <c r="D18" s="5" t="n">
+        <v>224</v>
+      </c>
+      <c r="E18" s="5" t="n">
         <v>1343</v>
-      </c>
-      <c r="E18" s="5" t="n">
-        <v>224</v>
       </c>
       <c r="F18" s="5" t="n">
         <v>233</v>
@@ -1965,10 +1965,10 @@
         <v>565</v>
       </c>
       <c r="D19" t="n">
+        <v>224</v>
+      </c>
+      <c r="E19" t="n">
         <v>1341</v>
-      </c>
-      <c r="E19" t="n">
-        <v>224</v>
       </c>
       <c r="F19" t="n">
         <v>233</v>
@@ -2044,10 +2044,10 @@
         <v>565</v>
       </c>
       <c r="D20" s="5" t="n">
+        <v>224</v>
+      </c>
+      <c r="E20" s="5" t="n">
         <v>1340</v>
-      </c>
-      <c r="E20" s="5" t="n">
-        <v>224</v>
       </c>
       <c r="F20" s="5" t="n">
         <v>232</v>
@@ -2123,10 +2123,10 @@
         <v>565</v>
       </c>
       <c r="D21" t="n">
+        <v>224</v>
+      </c>
+      <c r="E21" t="n">
         <v>1340</v>
-      </c>
-      <c r="E21" t="n">
-        <v>224</v>
       </c>
       <c r="F21" t="n">
         <v>232</v>
@@ -2202,10 +2202,10 @@
         <v>565</v>
       </c>
       <c r="D22" s="5" t="n">
+        <v>224</v>
+      </c>
+      <c r="E22" s="5" t="n">
         <v>1340</v>
-      </c>
-      <c r="E22" s="5" t="n">
-        <v>224</v>
       </c>
       <c r="F22" s="5" t="n">
         <v>232</v>
@@ -2281,10 +2281,10 @@
         <v>565</v>
       </c>
       <c r="D23" t="n">
+        <v>221</v>
+      </c>
+      <c r="E23" t="n">
         <v>1344</v>
-      </c>
-      <c r="E23" t="n">
-        <v>221</v>
       </c>
       <c r="F23" t="n">
         <v>229</v>
@@ -2360,10 +2360,10 @@
         <v>565</v>
       </c>
       <c r="D24" s="5" t="n">
+        <v>220</v>
+      </c>
+      <c r="E24" s="5" t="n">
         <v>1328</v>
-      </c>
-      <c r="E24" s="5" t="n">
-        <v>220</v>
       </c>
       <c r="F24" s="5" t="n">
         <v>228</v>
@@ -2439,10 +2439,10 @@
         <v>565</v>
       </c>
       <c r="D25" t="n">
+        <v>219</v>
+      </c>
+      <c r="E25" t="n">
         <v>1316</v>
-      </c>
-      <c r="E25" t="n">
-        <v>219</v>
       </c>
       <c r="F25" t="n">
         <v>228</v>
@@ -2518,10 +2518,10 @@
         <v>565</v>
       </c>
       <c r="D26" s="5" t="n">
+        <v>217</v>
+      </c>
+      <c r="E26" s="5" t="n">
         <v>1322</v>
-      </c>
-      <c r="E26" s="5" t="n">
-        <v>217</v>
       </c>
       <c r="F26" s="5" t="n">
         <v>230</v>
@@ -2597,10 +2597,10 @@
         <v>565</v>
       </c>
       <c r="D27" t="n">
+        <v>217</v>
+      </c>
+      <c r="E27" t="n">
         <v>1322</v>
-      </c>
-      <c r="E27" t="n">
-        <v>217</v>
       </c>
       <c r="F27" t="n">
         <v>233</v>
@@ -2676,10 +2676,10 @@
         <v>565</v>
       </c>
       <c r="D28" s="5" t="n">
+        <v>217</v>
+      </c>
+      <c r="E28" s="5" t="n">
         <v>1291</v>
-      </c>
-      <c r="E28" s="5" t="n">
-        <v>217</v>
       </c>
       <c r="F28" s="5" t="n">
         <v>233</v>
@@ -2755,10 +2755,10 @@
         <v>565</v>
       </c>
       <c r="D29" t="n">
+        <v>217</v>
+      </c>
+      <c r="E29" t="n">
         <v>1322</v>
-      </c>
-      <c r="E29" t="n">
-        <v>217</v>
       </c>
       <c r="F29" t="n">
         <v>233</v>
@@ -2834,10 +2834,10 @@
         <v>541</v>
       </c>
       <c r="D30" s="5" t="n">
+        <v>215</v>
+      </c>
+      <c r="E30" s="5" t="n">
         <v>1284</v>
-      </c>
-      <c r="E30" s="5" t="n">
-        <v>215</v>
       </c>
       <c r="F30" s="5" t="n">
         <v>208</v>
@@ -2913,10 +2913,10 @@
         <v>544</v>
       </c>
       <c r="D31" t="n">
+        <v>217</v>
+      </c>
+      <c r="E31" t="n">
         <v>1284</v>
-      </c>
-      <c r="E31" t="n">
-        <v>217</v>
       </c>
       <c r="F31" t="n">
         <v>208</v>
@@ -2992,10 +2992,10 @@
         <v>556</v>
       </c>
       <c r="D32" s="5" t="n">
+        <v>217</v>
+      </c>
+      <c r="E32" s="5" t="n">
         <v>1286</v>
-      </c>
-      <c r="E32" s="5" t="n">
-        <v>217</v>
       </c>
       <c r="F32" s="5" t="n">
         <v>218</v>
@@ -3071,10 +3071,10 @@
         <v>564</v>
       </c>
       <c r="D33" t="n">
+        <v>216</v>
+      </c>
+      <c r="E33" t="n">
         <v>1286</v>
-      </c>
-      <c r="E33" t="n">
-        <v>216</v>
       </c>
       <c r="F33" t="n">
         <v>218</v>
@@ -3150,10 +3150,10 @@
         <v>563</v>
       </c>
       <c r="D34" s="5" t="n">
+        <v>216</v>
+      </c>
+      <c r="E34" s="5" t="n">
         <v>1324</v>
-      </c>
-      <c r="E34" s="5" t="n">
-        <v>216</v>
       </c>
       <c r="F34" s="5" t="n">
         <v>218</v>
@@ -3229,10 +3229,10 @@
         <v>563</v>
       </c>
       <c r="D35" t="n">
+        <v>216</v>
+      </c>
+      <c r="E35" t="n">
         <v>1324</v>
-      </c>
-      <c r="E35" t="n">
-        <v>216</v>
       </c>
       <c r="F35" t="n">
         <v>218</v>
@@ -3308,10 +3308,10 @@
         <v>563</v>
       </c>
       <c r="D36" s="5" t="n">
+        <v>216</v>
+      </c>
+      <c r="E36" s="5" t="n">
         <v>1324</v>
-      </c>
-      <c r="E36" s="5" t="n">
-        <v>216</v>
       </c>
       <c r="F36" s="5" t="n">
         <v>218</v>
@@ -3387,10 +3387,10 @@
         <v>563</v>
       </c>
       <c r="D37" t="n">
+        <v>212</v>
+      </c>
+      <c r="E37" t="n">
         <v>1306</v>
-      </c>
-      <c r="E37" t="n">
-        <v>212</v>
       </c>
       <c r="F37" t="n">
         <v>216</v>
@@ -3466,10 +3466,10 @@
         <v>556</v>
       </c>
       <c r="D38" s="5" t="n">
+        <v>212</v>
+      </c>
+      <c r="E38" s="5" t="n">
         <v>1310</v>
-      </c>
-      <c r="E38" s="5" t="n">
-        <v>212</v>
       </c>
       <c r="F38" s="5" t="n">
         <v>207</v>
@@ -3545,10 +3545,10 @@
         <v>562</v>
       </c>
       <c r="D39" t="n">
+        <v>214</v>
+      </c>
+      <c r="E39" t="n">
         <v>1305</v>
-      </c>
-      <c r="E39" t="n">
-        <v>214</v>
       </c>
       <c r="F39" t="n">
         <v>207</v>
@@ -3624,10 +3624,10 @@
         <v>519</v>
       </c>
       <c r="D40" s="5" t="n">
+        <v>210</v>
+      </c>
+      <c r="E40" s="5" t="n">
         <v>1295</v>
-      </c>
-      <c r="E40" s="5" t="n">
-        <v>210</v>
       </c>
       <c r="F40" s="5" t="n">
         <v>226</v>
@@ -3703,10 +3703,10 @@
         <v>517</v>
       </c>
       <c r="D41" t="n">
+        <v>210</v>
+      </c>
+      <c r="E41" t="n">
         <v>1285</v>
-      </c>
-      <c r="E41" t="n">
-        <v>210</v>
       </c>
       <c r="F41" t="n">
         <v>219</v>
@@ -3782,10 +3782,10 @@
         <v>517</v>
       </c>
       <c r="D42" s="5" t="n">
+        <v>210</v>
+      </c>
+      <c r="E42" s="5" t="n">
         <v>1239</v>
-      </c>
-      <c r="E42" s="5" t="n">
-        <v>210</v>
       </c>
       <c r="F42" s="5" t="n">
         <v>219</v>
@@ -3861,10 +3861,10 @@
         <v>517</v>
       </c>
       <c r="D43" t="n">
+        <v>210</v>
+      </c>
+      <c r="E43" t="n">
         <v>1270</v>
-      </c>
-      <c r="E43" t="n">
-        <v>210</v>
       </c>
       <c r="F43" t="n">
         <v>219</v>
@@ -3940,10 +3940,10 @@
         <v>531</v>
       </c>
       <c r="D44" s="5" t="n">
+        <v>208</v>
+      </c>
+      <c r="E44" s="5" t="n">
         <v>1255</v>
-      </c>
-      <c r="E44" s="5" t="n">
-        <v>208</v>
       </c>
       <c r="F44" s="5" t="n">
         <v>214</v>
@@ -4019,10 +4019,10 @@
         <v>548</v>
       </c>
       <c r="D45" t="n">
+        <v>208</v>
+      </c>
+      <c r="E45" t="n">
         <v>1254</v>
-      </c>
-      <c r="E45" t="n">
-        <v>208</v>
       </c>
       <c r="F45" t="n">
         <v>214</v>
@@ -4098,10 +4098,10 @@
         <v>548</v>
       </c>
       <c r="D46" s="5" t="n">
+        <v>203</v>
+      </c>
+      <c r="E46" s="5" t="n">
         <v>1244</v>
-      </c>
-      <c r="E46" s="5" t="n">
-        <v>203</v>
       </c>
       <c r="F46" s="5" t="n">
         <v>218</v>
@@ -4177,10 +4177,10 @@
         <v>554</v>
       </c>
       <c r="D47" t="n">
+        <v>233</v>
+      </c>
+      <c r="E47" t="n">
         <v>1235</v>
-      </c>
-      <c r="E47" t="n">
-        <v>233</v>
       </c>
       <c r="F47" t="n">
         <v>214</v>
@@ -4256,10 +4256,10 @@
         <v>550</v>
       </c>
       <c r="D48" s="5" t="n">
+        <v>232</v>
+      </c>
+      <c r="E48" s="5" t="n">
         <v>1253</v>
-      </c>
-      <c r="E48" s="5" t="n">
-        <v>232</v>
       </c>
       <c r="F48" s="5" t="n">
         <v>211</v>
@@ -4335,10 +4335,10 @@
         <v>550</v>
       </c>
       <c r="D49" t="n">
+        <v>232</v>
+      </c>
+      <c r="E49" t="n">
         <v>1221</v>
-      </c>
-      <c r="E49" t="n">
-        <v>232</v>
       </c>
       <c r="F49" t="n">
         <v>211</v>
@@ -4414,10 +4414,10 @@
         <v>550</v>
       </c>
       <c r="D50" s="5" t="n">
+        <v>232</v>
+      </c>
+      <c r="E50" s="5" t="n">
         <v>1253</v>
-      </c>
-      <c r="E50" s="5" t="n">
-        <v>232</v>
       </c>
       <c r="F50" s="5" t="n">
         <v>211</v>
@@ -4493,10 +4493,10 @@
         <v>550</v>
       </c>
       <c r="D51" t="n">
+        <v>227</v>
+      </c>
+      <c r="E51" t="n">
         <v>1155</v>
-      </c>
-      <c r="E51" t="n">
-        <v>227</v>
       </c>
       <c r="F51" t="n">
         <v>226</v>
@@ -4572,10 +4572,10 @@
         <v>541</v>
       </c>
       <c r="D52" s="5" t="n">
+        <v>225</v>
+      </c>
+      <c r="E52" s="5" t="n">
         <v>1062</v>
-      </c>
-      <c r="E52" s="5" t="n">
-        <v>225</v>
       </c>
       <c r="F52" s="5" t="n">
         <v>224</v>
@@ -4651,10 +4651,10 @@
         <v>539</v>
       </c>
       <c r="D53" t="n">
+        <v>224</v>
+      </c>
+      <c r="E53" t="n">
         <v>993</v>
-      </c>
-      <c r="E53" t="n">
-        <v>224</v>
       </c>
       <c r="F53" t="n">
         <v>232</v>
@@ -4730,10 +4730,10 @@
         <v>533</v>
       </c>
       <c r="D54" s="5" t="n">
+        <v>224</v>
+      </c>
+      <c r="E54" s="5" t="n">
         <v>988</v>
-      </c>
-      <c r="E54" s="5" t="n">
-        <v>224</v>
       </c>
       <c r="F54" s="5" t="n">
         <v>232</v>
@@ -4809,10 +4809,10 @@
         <v>533</v>
       </c>
       <c r="D55" t="n">
+        <v>224</v>
+      </c>
+      <c r="E55" t="n">
         <v>956</v>
-      </c>
-      <c r="E55" t="n">
-        <v>224</v>
       </c>
       <c r="F55" t="n">
         <v>232</v>
@@ -4888,10 +4888,10 @@
         <v>532</v>
       </c>
       <c r="D56" s="5" t="n">
+        <v>223</v>
+      </c>
+      <c r="E56" s="5" t="n">
         <v>985</v>
-      </c>
-      <c r="E56" s="5" t="n">
-        <v>223</v>
       </c>
       <c r="F56" s="5" t="n">
         <v>232</v>
@@ -4967,10 +4967,10 @@
         <v>527</v>
       </c>
       <c r="D57" t="n">
+        <v>0</v>
+      </c>
+      <c r="E57" t="n">
         <v>72</v>
-      </c>
-      <c r="E57" t="n">
-        <v>0</v>
       </c>
       <c r="F57" t="n">
         <v>0</v>
@@ -5046,10 +5046,10 @@
         <v>525</v>
       </c>
       <c r="D58" s="5" t="n">
+        <v>216</v>
+      </c>
+      <c r="E58" s="5" t="n">
         <v>72</v>
-      </c>
-      <c r="E58" s="5" t="n">
-        <v>216</v>
       </c>
       <c r="F58" s="5" t="n">
         <v>0</v>
@@ -5125,10 +5125,10 @@
         <v>528</v>
       </c>
       <c r="D59" t="n">
+        <v>205</v>
+      </c>
+      <c r="E59" t="n">
         <v>549</v>
-      </c>
-      <c r="E59" t="n">
-        <v>205</v>
       </c>
       <c r="F59" t="n">
         <v>207</v>
@@ -5204,10 +5204,10 @@
         <v>536</v>
       </c>
       <c r="D60" s="5" t="n">
+        <v>270</v>
+      </c>
+      <c r="E60" s="5" t="n">
         <v>504</v>
-      </c>
-      <c r="E60" s="5" t="n">
-        <v>270</v>
       </c>
       <c r="F60" s="5" t="n">
         <v>218</v>
@@ -5283,10 +5283,10 @@
         <v>533</v>
       </c>
       <c r="D61" t="n">
+        <v>282</v>
+      </c>
+      <c r="E61" t="n">
         <v>495</v>
-      </c>
-      <c r="E61" t="n">
-        <v>282</v>
       </c>
       <c r="F61" t="n">
         <v>218</v>
@@ -5362,10 +5362,10 @@
         <v>533</v>
       </c>
       <c r="D62" s="5" t="n">
+        <v>282</v>
+      </c>
+      <c r="E62" s="5" t="n">
         <v>495</v>
-      </c>
-      <c r="E62" s="5" t="n">
-        <v>282</v>
       </c>
       <c r="F62" s="5" t="n">
         <v>218</v>
@@ -5441,10 +5441,10 @@
         <v>533</v>
       </c>
       <c r="D63" t="n">
+        <v>282</v>
+      </c>
+      <c r="E63" t="n">
         <v>495</v>
-      </c>
-      <c r="E63" t="n">
-        <v>282</v>
       </c>
       <c r="F63" t="n">
         <v>218</v>
@@ -5520,10 +5520,10 @@
         <v>541</v>
       </c>
       <c r="D64" s="5" t="n">
+        <v>366</v>
+      </c>
+      <c r="E64" s="5" t="n">
         <v>469</v>
-      </c>
-      <c r="E64" s="5" t="n">
-        <v>366</v>
       </c>
       <c r="F64" s="5" t="n">
         <v>215</v>
@@ -5599,10 +5599,10 @@
         <v>534</v>
       </c>
       <c r="D65" t="n">
+        <v>356</v>
+      </c>
+      <c r="E65" t="n">
         <v>471</v>
-      </c>
-      <c r="E65" t="n">
-        <v>356</v>
       </c>
       <c r="F65" t="n">
         <v>211</v>
@@ -5678,10 +5678,10 @@
         <v>521</v>
       </c>
       <c r="D66" s="5" t="n">
+        <v>381</v>
+      </c>
+      <c r="E66" s="5" t="n">
         <v>470</v>
-      </c>
-      <c r="E66" s="5" t="n">
-        <v>381</v>
       </c>
       <c r="F66" s="5" t="n">
         <v>201</v>
@@ -5757,10 +5757,10 @@
         <v>525</v>
       </c>
       <c r="D67" t="n">
+        <v>380</v>
+      </c>
+      <c r="E67" t="n">
         <v>446</v>
-      </c>
-      <c r="E67" t="n">
-        <v>380</v>
       </c>
       <c r="F67" t="n">
         <v>200</v>
@@ -5833,10 +5833,10 @@
         <v>518</v>
       </c>
       <c r="D68" s="5" t="n">
+        <v>370</v>
+      </c>
+      <c r="E68" s="5" t="n">
         <v>416</v>
-      </c>
-      <c r="E68" s="5" t="n">
-        <v>370</v>
       </c>
       <c r="F68" s="5" t="n">
         <v>206</v>
@@ -5909,10 +5909,10 @@
         <v>850</v>
       </c>
       <c r="D69" t="n">
+        <v>370</v>
+      </c>
+      <c r="E69" t="n">
         <v>416</v>
-      </c>
-      <c r="E69" t="n">
-        <v>370</v>
       </c>
       <c r="F69" t="n">
         <v>206</v>
@@ -5985,10 +5985,10 @@
         <v>518</v>
       </c>
       <c r="D70" s="5" t="n">
+        <v>370</v>
+      </c>
+      <c r="E70" s="5" t="n">
         <v>416</v>
-      </c>
-      <c r="E70" s="5" t="n">
-        <v>370</v>
       </c>
       <c r="F70" s="5" t="n">
         <v>206</v>
@@ -6048,6 +6048,85 @@
         <v>0</v>
       </c>
       <c r="Y70" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B71" t="n">
+        <v>861</v>
+      </c>
+      <c r="C71" t="n">
+        <v>516</v>
+      </c>
+      <c r="D71" t="n">
+        <v>397</v>
+      </c>
+      <c r="E71" t="n">
+        <v>395</v>
+      </c>
+      <c r="F71" t="n">
+        <v>190</v>
+      </c>
+      <c r="G71" t="n">
+        <v>100</v>
+      </c>
+      <c r="H71" t="n">
+        <v>42</v>
+      </c>
+      <c r="I71" t="n">
+        <v>26</v>
+      </c>
+      <c r="J71" t="n">
+        <v>24</v>
+      </c>
+      <c r="K71" t="n">
+        <v>21</v>
+      </c>
+      <c r="L71" t="n">
+        <v>0</v>
+      </c>
+      <c r="M71" t="n">
+        <v>0</v>
+      </c>
+      <c r="N71" t="n">
+        <v>0</v>
+      </c>
+      <c r="O71" t="n">
+        <v>0</v>
+      </c>
+      <c r="P71" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q71" t="n">
+        <v>0</v>
+      </c>
+      <c r="R71" t="n">
+        <v>0</v>
+      </c>
+      <c r="S71" t="n">
+        <v>0</v>
+      </c>
+      <c r="T71" t="n">
+        <v>0</v>
+      </c>
+      <c r="U71" t="n">
+        <v>0</v>
+      </c>
+      <c r="V71" t="n">
+        <v>0</v>
+      </c>
+      <c r="W71" t="n">
+        <v>0</v>
+      </c>
+      <c r="X71" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y71" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6089,7 +6168,7 @@
       </c>
       <c r="D1" s="3" t="inlineStr">
         <is>
-          <t>Lager (2026-09-14)</t>
+          <t>Lager (2026-09-15)</t>
         </is>
       </c>
     </row>
@@ -6110,7 +6189,7 @@
         </is>
       </c>
       <c r="D2" s="4" t="n">
-        <v>518</v>
+        <v>516</v>
       </c>
     </row>
     <row r="3">
@@ -6836,7 +6915,7 @@
     <row r="39">
       <c r="A39" s="6" t="inlineStr">
         <is>
-          <t>7018180</t>
+          <t>7018181</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -6856,7 +6935,7 @@
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>7018182</t>
+          <t>7018183</t>
         </is>
       </c>
       <c r="B40" s="5" t="inlineStr">
@@ -6876,7 +6955,7 @@
     <row r="41">
       <c r="A41" s="6" t="inlineStr">
         <is>
-          <t>7018184</t>
+          <t>7018185</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -6896,7 +6975,7 @@
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>7018186</t>
+          <t>7018187</t>
         </is>
       </c>
       <c r="B42" s="5" t="inlineStr">
@@ -6916,7 +6995,7 @@
     <row r="43">
       <c r="A43" s="6" t="inlineStr">
         <is>
-          <t>7018188</t>
+          <t>7018189</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -6936,7 +7015,7 @@
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t>7018190</t>
+          <t>7018191</t>
         </is>
       </c>
       <c r="B44" s="5" t="inlineStr">
@@ -6956,7 +7035,7 @@
     <row r="45">
       <c r="A45" s="6" t="inlineStr">
         <is>
-          <t>7018192</t>
+          <t>7018180</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -6976,7 +7055,7 @@
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
         <is>
-          <t>7018194</t>
+          <t>7018182</t>
         </is>
       </c>
       <c r="B46" s="5" t="inlineStr">
@@ -6996,7 +7075,7 @@
     <row r="47">
       <c r="A47" s="6" t="inlineStr">
         <is>
-          <t>7018181</t>
+          <t>7018184</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -7016,7 +7095,7 @@
     <row r="48">
       <c r="A48" s="4" t="inlineStr">
         <is>
-          <t>7018183</t>
+          <t>7018186</t>
         </is>
       </c>
       <c r="B48" s="5" t="inlineStr">
@@ -7036,7 +7115,7 @@
     <row r="49">
       <c r="A49" s="6" t="inlineStr">
         <is>
-          <t>7018185</t>
+          <t>7018188</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -7056,7 +7135,7 @@
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t>7018187</t>
+          <t>7018190</t>
         </is>
       </c>
       <c r="B50" s="5" t="inlineStr">
@@ -7076,7 +7155,7 @@
     <row r="51">
       <c r="A51" s="6" t="inlineStr">
         <is>
-          <t>7018189</t>
+          <t>7018192</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -7096,7 +7175,7 @@
     <row r="52">
       <c r="A52" s="4" t="inlineStr">
         <is>
-          <t>7018191</t>
+          <t>7018194</t>
         </is>
       </c>
       <c r="B52" s="5" t="inlineStr">
@@ -10110,7 +10189,7 @@
         </is>
       </c>
       <c r="D202" s="4" t="n">
-        <v>21</v>
+        <v>10</v>
       </c>
     </row>
     <row r="203">
@@ -14750,7 +14829,7 @@
         </is>
       </c>
       <c r="D434" s="4" t="n">
-        <v>160</v>
+        <v>143</v>
       </c>
     </row>
     <row r="435">
@@ -14770,7 +14849,7 @@
         </is>
       </c>
       <c r="D435" s="6" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="436">
@@ -14830,7 +14909,7 @@
         </is>
       </c>
       <c r="D438" s="4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="439">
@@ -14850,7 +14929,7 @@
         </is>
       </c>
       <c r="D439" s="6" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="440">
@@ -23830,7 +23909,7 @@
         </is>
       </c>
       <c r="D888" s="4" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="889">
@@ -23970,7 +24049,7 @@
         </is>
       </c>
       <c r="D895" s="6" t="n">
-        <v>307</v>
+        <v>290</v>
       </c>
     </row>
     <row r="896">
@@ -24010,7 +24089,7 @@
         </is>
       </c>
       <c r="D897" s="6" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
     </row>
     <row r="898">
@@ -25650,7 +25729,7 @@
         </is>
       </c>
       <c r="D979" s="6" t="n">
-        <v>174</v>
+        <v>177</v>
       </c>
     </row>
     <row r="980">
@@ -25690,7 +25769,7 @@
         </is>
       </c>
       <c r="D981" s="6" t="n">
-        <v>110</v>
+        <v>134</v>
       </c>
     </row>
     <row r="982">
@@ -28770,7 +28849,7 @@
         </is>
       </c>
       <c r="D1135" s="6" t="n">
-        <v>420</v>
+        <v>418</v>
       </c>
     </row>
     <row r="1136">
@@ -28790,7 +28869,7 @@
         </is>
       </c>
       <c r="D1136" s="4" t="n">
-        <v>343</v>
+        <v>356</v>
       </c>
     </row>
   </sheetData>

--- a/data/ahlsell_led_panel_inventory.xlsx
+++ b/data/ahlsell_led_panel_inventory.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y71"/>
+  <dimension ref="A1:Y72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -543,72 +543,72 @@
       </c>
       <c r="L1" s="3" t="inlineStr">
         <is>
+          <t>THORN</t>
+        </is>
+      </c>
+      <c r="M1" s="3" t="inlineStr">
+        <is>
+          <t>Nokalux</t>
+        </is>
+      </c>
+      <c r="N1" s="3" t="inlineStr">
+        <is>
+          <t>Philips</t>
+        </is>
+      </c>
+      <c r="O1" s="3" t="inlineStr">
+        <is>
+          <t>Legrand</t>
+        </is>
+      </c>
+      <c r="P1" s="3" t="inlineStr">
+        <is>
+          <t>Siteco</t>
+        </is>
+      </c>
+      <c r="Q1" s="3" t="inlineStr">
+        <is>
+          <t>Bergdahls</t>
+        </is>
+      </c>
+      <c r="R1" s="3" t="inlineStr">
+        <is>
+          <t>Easyform</t>
+        </is>
+      </c>
+      <c r="S1" s="3" t="inlineStr">
+        <is>
+          <t>Airam</t>
+        </is>
+      </c>
+      <c r="T1" s="3" t="inlineStr">
+        <is>
+          <t>ANETA LIGHTING</t>
+        </is>
+      </c>
+      <c r="U1" s="3" t="inlineStr">
+        <is>
           <t>Norwesco</t>
         </is>
       </c>
-      <c r="M1" s="3" t="inlineStr">
-        <is>
-          <t>ANETA LIGHTING</t>
-        </is>
-      </c>
-      <c r="N1" s="3" t="inlineStr">
-        <is>
-          <t>Airam</t>
-        </is>
-      </c>
-      <c r="O1" s="3" t="inlineStr">
+      <c r="V1" s="3" t="inlineStr">
         <is>
           <t>Black Box</t>
         </is>
       </c>
-      <c r="P1" s="3" t="inlineStr">
+      <c r="W1" s="3" t="inlineStr">
         <is>
           <t>Westal</t>
         </is>
       </c>
-      <c r="Q1" s="3" t="inlineStr">
-        <is>
-          <t>Legrand</t>
-        </is>
-      </c>
-      <c r="R1" s="3" t="inlineStr">
-        <is>
-          <t>Nokalux</t>
-        </is>
-      </c>
-      <c r="S1" s="3" t="inlineStr">
+      <c r="X1" s="3" t="inlineStr">
         <is>
           <t>ZG Lighting</t>
         </is>
       </c>
-      <c r="T1" s="3" t="inlineStr">
+      <c r="Y1" s="3" t="inlineStr">
         <is>
           <t>Ensto</t>
-        </is>
-      </c>
-      <c r="U1" s="3" t="inlineStr">
-        <is>
-          <t>Philips</t>
-        </is>
-      </c>
-      <c r="V1" s="3" t="inlineStr">
-        <is>
-          <t>THORN</t>
-        </is>
-      </c>
-      <c r="W1" s="3" t="inlineStr">
-        <is>
-          <t>Siteco</t>
-        </is>
-      </c>
-      <c r="X1" s="3" t="inlineStr">
-        <is>
-          <t>Easyform</t>
-        </is>
-      </c>
-      <c r="Y1" s="3" t="inlineStr">
-        <is>
-          <t>Bergdahls</t>
         </is>
       </c>
     </row>
@@ -6127,6 +6127,85 @@
         <v>0</v>
       </c>
       <c r="Y71" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B72" s="5" t="n">
+        <v>859</v>
+      </c>
+      <c r="C72" s="5" t="n">
+        <v>531</v>
+      </c>
+      <c r="D72" s="5" t="n">
+        <v>398</v>
+      </c>
+      <c r="E72" s="5" t="n">
+        <v>394</v>
+      </c>
+      <c r="F72" s="5" t="n">
+        <v>196</v>
+      </c>
+      <c r="G72" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="H72" s="5" t="n">
+        <v>42</v>
+      </c>
+      <c r="I72" s="5" t="n">
+        <v>26</v>
+      </c>
+      <c r="J72" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="K72" s="5" t="n">
+        <v>21</v>
+      </c>
+      <c r="L72" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M72" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N72" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O72" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P72" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q72" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R72" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S72" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T72" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U72" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V72" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W72" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X72" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y72" s="5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6168,7 +6247,7 @@
       </c>
       <c r="D1" s="3" t="inlineStr">
         <is>
-          <t>Lager (2026-09-15)</t>
+          <t>Lager (2026-09-16)</t>
         </is>
       </c>
     </row>
@@ -6189,7 +6268,7 @@
         </is>
       </c>
       <c r="D2" s="4" t="n">
-        <v>516</v>
+        <v>531</v>
       </c>
     </row>
     <row r="3">
@@ -6915,7 +6994,7 @@
     <row r="39">
       <c r="A39" s="6" t="inlineStr">
         <is>
-          <t>7018181</t>
+          <t>7018180</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -6935,7 +7014,7 @@
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>7018183</t>
+          <t>7018182</t>
         </is>
       </c>
       <c r="B40" s="5" t="inlineStr">
@@ -6955,7 +7034,7 @@
     <row r="41">
       <c r="A41" s="6" t="inlineStr">
         <is>
-          <t>7018185</t>
+          <t>7018184</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -6975,7 +7054,7 @@
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>7018187</t>
+          <t>7018186</t>
         </is>
       </c>
       <c r="B42" s="5" t="inlineStr">
@@ -6995,7 +7074,7 @@
     <row r="43">
       <c r="A43" s="6" t="inlineStr">
         <is>
-          <t>7018189</t>
+          <t>7018188</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -7015,7 +7094,7 @@
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t>7018191</t>
+          <t>7018190</t>
         </is>
       </c>
       <c r="B44" s="5" t="inlineStr">
@@ -7035,7 +7114,7 @@
     <row r="45">
       <c r="A45" s="6" t="inlineStr">
         <is>
-          <t>7018180</t>
+          <t>7018192</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -7055,7 +7134,7 @@
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
         <is>
-          <t>7018182</t>
+          <t>7018194</t>
         </is>
       </c>
       <c r="B46" s="5" t="inlineStr">
@@ -7075,7 +7154,7 @@
     <row r="47">
       <c r="A47" s="6" t="inlineStr">
         <is>
-          <t>7018184</t>
+          <t>7018181</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -7095,7 +7174,7 @@
     <row r="48">
       <c r="A48" s="4" t="inlineStr">
         <is>
-          <t>7018186</t>
+          <t>7018183</t>
         </is>
       </c>
       <c r="B48" s="5" t="inlineStr">
@@ -7115,7 +7194,7 @@
     <row r="49">
       <c r="A49" s="6" t="inlineStr">
         <is>
-          <t>7018188</t>
+          <t>7018185</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -7135,7 +7214,7 @@
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t>7018190</t>
+          <t>7018187</t>
         </is>
       </c>
       <c r="B50" s="5" t="inlineStr">
@@ -7155,7 +7234,7 @@
     <row r="51">
       <c r="A51" s="6" t="inlineStr">
         <is>
-          <t>7018192</t>
+          <t>7018189</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -7175,7 +7254,7 @@
     <row r="52">
       <c r="A52" s="4" t="inlineStr">
         <is>
-          <t>7018194</t>
+          <t>7018191</t>
         </is>
       </c>
       <c r="B52" s="5" t="inlineStr">
@@ -14829,7 +14908,7 @@
         </is>
       </c>
       <c r="D434" s="4" t="n">
-        <v>143</v>
+        <v>150</v>
       </c>
     </row>
     <row r="435">
@@ -14929,7 +15008,7 @@
         </is>
       </c>
       <c r="D439" s="6" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="440">
@@ -23909,7 +23988,7 @@
         </is>
       </c>
       <c r="D888" s="4" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="889">
@@ -25729,7 +25808,7 @@
         </is>
       </c>
       <c r="D979" s="6" t="n">
-        <v>177</v>
+        <v>158</v>
       </c>
     </row>
     <row r="980">
@@ -25749,7 +25828,7 @@
         </is>
       </c>
       <c r="D980" s="4" t="n">
-        <v>74</v>
+        <v>94</v>
       </c>
     </row>
     <row r="981">
@@ -28849,7 +28928,7 @@
         </is>
       </c>
       <c r="D1135" s="6" t="n">
-        <v>418</v>
+        <v>412</v>
       </c>
     </row>
     <row r="1136">
@@ -28869,7 +28948,7 @@
         </is>
       </c>
       <c r="D1136" s="4" t="n">
-        <v>356</v>
+        <v>360</v>
       </c>
     </row>
   </sheetData>

--- a/data/ahlsell_led_panel_inventory.xlsx
+++ b/data/ahlsell_led_panel_inventory.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y72"/>
+  <dimension ref="A1:Y73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -503,14 +503,14 @@
       </c>
       <c r="D1" s="3" t="inlineStr">
         <is>
+          <t>SG Armaturen</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
           <t>Tupex</t>
         </is>
       </c>
-      <c r="E1" s="3" t="inlineStr">
-        <is>
-          <t>SG Armaturen</t>
-        </is>
-      </c>
       <c r="F1" s="3" t="inlineStr">
         <is>
           <t>Hide-a-lite</t>
@@ -543,72 +543,72 @@
       </c>
       <c r="L1" s="3" t="inlineStr">
         <is>
+          <t>Ensto</t>
+        </is>
+      </c>
+      <c r="M1" s="3" t="inlineStr">
+        <is>
+          <t>ANETA LIGHTING</t>
+        </is>
+      </c>
+      <c r="N1" s="3" t="inlineStr">
+        <is>
+          <t>ZG Lighting</t>
+        </is>
+      </c>
+      <c r="O1" s="3" t="inlineStr">
+        <is>
+          <t>Nokalux</t>
+        </is>
+      </c>
+      <c r="P1" s="3" t="inlineStr">
+        <is>
+          <t>Easyform</t>
+        </is>
+      </c>
+      <c r="Q1" s="3" t="inlineStr">
+        <is>
+          <t>Black Box</t>
+        </is>
+      </c>
+      <c r="R1" s="3" t="inlineStr">
+        <is>
+          <t>Westal</t>
+        </is>
+      </c>
+      <c r="S1" s="3" t="inlineStr">
+        <is>
+          <t>Airam</t>
+        </is>
+      </c>
+      <c r="T1" s="3" t="inlineStr">
+        <is>
+          <t>Legrand</t>
+        </is>
+      </c>
+      <c r="U1" s="3" t="inlineStr">
+        <is>
+          <t>Philips</t>
+        </is>
+      </c>
+      <c r="V1" s="3" t="inlineStr">
+        <is>
+          <t>Siteco</t>
+        </is>
+      </c>
+      <c r="W1" s="3" t="inlineStr">
+        <is>
           <t>THORN</t>
         </is>
       </c>
-      <c r="M1" s="3" t="inlineStr">
-        <is>
-          <t>Nokalux</t>
-        </is>
-      </c>
-      <c r="N1" s="3" t="inlineStr">
-        <is>
-          <t>Philips</t>
-        </is>
-      </c>
-      <c r="O1" s="3" t="inlineStr">
-        <is>
-          <t>Legrand</t>
-        </is>
-      </c>
-      <c r="P1" s="3" t="inlineStr">
-        <is>
-          <t>Siteco</t>
-        </is>
-      </c>
-      <c r="Q1" s="3" t="inlineStr">
+      <c r="X1" s="3" t="inlineStr">
         <is>
           <t>Bergdahls</t>
         </is>
       </c>
-      <c r="R1" s="3" t="inlineStr">
-        <is>
-          <t>Easyform</t>
-        </is>
-      </c>
-      <c r="S1" s="3" t="inlineStr">
-        <is>
-          <t>Airam</t>
-        </is>
-      </c>
-      <c r="T1" s="3" t="inlineStr">
-        <is>
-          <t>ANETA LIGHTING</t>
-        </is>
-      </c>
-      <c r="U1" s="3" t="inlineStr">
+      <c r="Y1" s="3" t="inlineStr">
         <is>
           <t>Norwesco</t>
-        </is>
-      </c>
-      <c r="V1" s="3" t="inlineStr">
-        <is>
-          <t>Black Box</t>
-        </is>
-      </c>
-      <c r="W1" s="3" t="inlineStr">
-        <is>
-          <t>Westal</t>
-        </is>
-      </c>
-      <c r="X1" s="3" t="inlineStr">
-        <is>
-          <t>ZG Lighting</t>
-        </is>
-      </c>
-      <c r="Y1" s="3" t="inlineStr">
-        <is>
-          <t>Ensto</t>
         </is>
       </c>
     </row>
@@ -625,10 +625,10 @@
         <v>527</v>
       </c>
       <c r="D2" s="5" t="n">
+        <v>1402</v>
+      </c>
+      <c r="E2" s="5" t="n">
         <v>233</v>
-      </c>
-      <c r="E2" s="5" t="n">
-        <v>1402</v>
       </c>
       <c r="F2" s="5" t="n">
         <v>223</v>
@@ -704,10 +704,10 @@
         <v>527</v>
       </c>
       <c r="D3" t="n">
+        <v>1402</v>
+      </c>
+      <c r="E3" t="n">
         <v>233</v>
-      </c>
-      <c r="E3" t="n">
-        <v>1402</v>
       </c>
       <c r="F3" t="n">
         <v>223</v>
@@ -783,10 +783,10 @@
         <v>523</v>
       </c>
       <c r="D4" s="5" t="n">
+        <v>1391</v>
+      </c>
+      <c r="E4" s="5" t="n">
         <v>233</v>
-      </c>
-      <c r="E4" s="5" t="n">
-        <v>1391</v>
       </c>
       <c r="F4" s="5" t="n">
         <v>217</v>
@@ -862,10 +862,10 @@
         <v>522</v>
       </c>
       <c r="D5" t="n">
+        <v>1384</v>
+      </c>
+      <c r="E5" t="n">
         <v>233</v>
-      </c>
-      <c r="E5" t="n">
-        <v>1384</v>
       </c>
       <c r="F5" t="n">
         <v>221</v>
@@ -941,10 +941,10 @@
         <v>528</v>
       </c>
       <c r="D6" s="5" t="n">
+        <v>1377</v>
+      </c>
+      <c r="E6" s="5" t="n">
         <v>232</v>
-      </c>
-      <c r="E6" s="5" t="n">
-        <v>1377</v>
       </c>
       <c r="F6" s="5" t="n">
         <v>215</v>
@@ -1017,10 +1017,10 @@
         <v>920</v>
       </c>
       <c r="D7" t="n">
+        <v>1348</v>
+      </c>
+      <c r="E7" t="n">
         <v>232</v>
-      </c>
-      <c r="E7" t="n">
-        <v>1348</v>
       </c>
       <c r="F7" t="n">
         <v>215</v>
@@ -1096,10 +1096,10 @@
         <v>528</v>
       </c>
       <c r="D8" s="5" t="n">
+        <v>1377</v>
+      </c>
+      <c r="E8" s="5" t="n">
         <v>232</v>
-      </c>
-      <c r="E8" s="5" t="n">
-        <v>1377</v>
       </c>
       <c r="F8" s="5" t="n">
         <v>215</v>
@@ -1175,10 +1175,10 @@
         <v>532</v>
       </c>
       <c r="D9" t="n">
+        <v>1385</v>
+      </c>
+      <c r="E9" t="n">
         <v>232</v>
-      </c>
-      <c r="E9" t="n">
-        <v>1385</v>
       </c>
       <c r="F9" t="n">
         <v>214</v>
@@ -1254,10 +1254,10 @@
         <v>544</v>
       </c>
       <c r="D10" s="5" t="n">
+        <v>1381</v>
+      </c>
+      <c r="E10" s="5" t="n">
         <v>231</v>
-      </c>
-      <c r="E10" s="5" t="n">
-        <v>1381</v>
       </c>
       <c r="F10" s="5" t="n">
         <v>218</v>
@@ -1333,10 +1333,10 @@
         <v>544</v>
       </c>
       <c r="D11" t="n">
+        <v>1385</v>
+      </c>
+      <c r="E11" t="n">
         <v>231</v>
-      </c>
-      <c r="E11" t="n">
-        <v>1385</v>
       </c>
       <c r="F11" t="n">
         <v>225</v>
@@ -1412,10 +1412,10 @@
         <v>544</v>
       </c>
       <c r="D12" s="5" t="n">
+        <v>1372</v>
+      </c>
+      <c r="E12" s="5" t="n">
         <v>224</v>
-      </c>
-      <c r="E12" s="5" t="n">
-        <v>1372</v>
       </c>
       <c r="F12" s="5" t="n">
         <v>228</v>
@@ -1491,10 +1491,10 @@
         <v>545</v>
       </c>
       <c r="D13" t="n">
+        <v>1360</v>
+      </c>
+      <c r="E13" t="n">
         <v>224</v>
-      </c>
-      <c r="E13" t="n">
-        <v>1360</v>
       </c>
       <c r="F13" t="n">
         <v>228</v>
@@ -1570,10 +1570,10 @@
         <v>545</v>
       </c>
       <c r="D14" s="5" t="n">
+        <v>1331</v>
+      </c>
+      <c r="E14" s="5" t="n">
         <v>224</v>
-      </c>
-      <c r="E14" s="5" t="n">
-        <v>1331</v>
       </c>
       <c r="F14" s="5" t="n">
         <v>228</v>
@@ -1649,10 +1649,10 @@
         <v>545</v>
       </c>
       <c r="D15" t="n">
+        <v>1360</v>
+      </c>
+      <c r="E15" t="n">
         <v>224</v>
-      </c>
-      <c r="E15" t="n">
-        <v>1360</v>
       </c>
       <c r="F15" t="n">
         <v>228</v>
@@ -1728,10 +1728,10 @@
         <v>545</v>
       </c>
       <c r="D16" s="5" t="n">
+        <v>1348</v>
+      </c>
+      <c r="E16" s="5" t="n">
         <v>224</v>
-      </c>
-      <c r="E16" s="5" t="n">
-        <v>1348</v>
       </c>
       <c r="F16" s="5" t="n">
         <v>226</v>
@@ -1807,10 +1807,10 @@
         <v>572</v>
       </c>
       <c r="D17" t="n">
+        <v>1347</v>
+      </c>
+      <c r="E17" t="n">
         <v>224</v>
-      </c>
-      <c r="E17" t="n">
-        <v>1347</v>
       </c>
       <c r="F17" t="n">
         <v>228</v>
@@ -1886,10 +1886,10 @@
         <v>571</v>
       </c>
       <c r="D18" s="5" t="n">
+        <v>1343</v>
+      </c>
+      <c r="E18" s="5" t="n">
         <v>224</v>
-      </c>
-      <c r="E18" s="5" t="n">
-        <v>1343</v>
       </c>
       <c r="F18" s="5" t="n">
         <v>233</v>
@@ -1965,10 +1965,10 @@
         <v>565</v>
       </c>
       <c r="D19" t="n">
+        <v>1341</v>
+      </c>
+      <c r="E19" t="n">
         <v>224</v>
-      </c>
-      <c r="E19" t="n">
-        <v>1341</v>
       </c>
       <c r="F19" t="n">
         <v>233</v>
@@ -2044,10 +2044,10 @@
         <v>565</v>
       </c>
       <c r="D20" s="5" t="n">
+        <v>1340</v>
+      </c>
+      <c r="E20" s="5" t="n">
         <v>224</v>
-      </c>
-      <c r="E20" s="5" t="n">
-        <v>1340</v>
       </c>
       <c r="F20" s="5" t="n">
         <v>232</v>
@@ -2123,10 +2123,10 @@
         <v>565</v>
       </c>
       <c r="D21" t="n">
+        <v>1340</v>
+      </c>
+      <c r="E21" t="n">
         <v>224</v>
-      </c>
-      <c r="E21" t="n">
-        <v>1340</v>
       </c>
       <c r="F21" t="n">
         <v>232</v>
@@ -2202,10 +2202,10 @@
         <v>565</v>
       </c>
       <c r="D22" s="5" t="n">
+        <v>1340</v>
+      </c>
+      <c r="E22" s="5" t="n">
         <v>224</v>
-      </c>
-      <c r="E22" s="5" t="n">
-        <v>1340</v>
       </c>
       <c r="F22" s="5" t="n">
         <v>232</v>
@@ -2281,10 +2281,10 @@
         <v>565</v>
       </c>
       <c r="D23" t="n">
+        <v>1344</v>
+      </c>
+      <c r="E23" t="n">
         <v>221</v>
-      </c>
-      <c r="E23" t="n">
-        <v>1344</v>
       </c>
       <c r="F23" t="n">
         <v>229</v>
@@ -2360,10 +2360,10 @@
         <v>565</v>
       </c>
       <c r="D24" s="5" t="n">
+        <v>1328</v>
+      </c>
+      <c r="E24" s="5" t="n">
         <v>220</v>
-      </c>
-      <c r="E24" s="5" t="n">
-        <v>1328</v>
       </c>
       <c r="F24" s="5" t="n">
         <v>228</v>
@@ -2439,10 +2439,10 @@
         <v>565</v>
       </c>
       <c r="D25" t="n">
+        <v>1316</v>
+      </c>
+      <c r="E25" t="n">
         <v>219</v>
-      </c>
-      <c r="E25" t="n">
-        <v>1316</v>
       </c>
       <c r="F25" t="n">
         <v>228</v>
@@ -2518,10 +2518,10 @@
         <v>565</v>
       </c>
       <c r="D26" s="5" t="n">
+        <v>1322</v>
+      </c>
+      <c r="E26" s="5" t="n">
         <v>217</v>
-      </c>
-      <c r="E26" s="5" t="n">
-        <v>1322</v>
       </c>
       <c r="F26" s="5" t="n">
         <v>230</v>
@@ -2597,10 +2597,10 @@
         <v>565</v>
       </c>
       <c r="D27" t="n">
+        <v>1322</v>
+      </c>
+      <c r="E27" t="n">
         <v>217</v>
-      </c>
-      <c r="E27" t="n">
-        <v>1322</v>
       </c>
       <c r="F27" t="n">
         <v>233</v>
@@ -2676,10 +2676,10 @@
         <v>565</v>
       </c>
       <c r="D28" s="5" t="n">
+        <v>1291</v>
+      </c>
+      <c r="E28" s="5" t="n">
         <v>217</v>
-      </c>
-      <c r="E28" s="5" t="n">
-        <v>1291</v>
       </c>
       <c r="F28" s="5" t="n">
         <v>233</v>
@@ -2755,10 +2755,10 @@
         <v>565</v>
       </c>
       <c r="D29" t="n">
+        <v>1322</v>
+      </c>
+      <c r="E29" t="n">
         <v>217</v>
-      </c>
-      <c r="E29" t="n">
-        <v>1322</v>
       </c>
       <c r="F29" t="n">
         <v>233</v>
@@ -2834,10 +2834,10 @@
         <v>541</v>
       </c>
       <c r="D30" s="5" t="n">
+        <v>1284</v>
+      </c>
+      <c r="E30" s="5" t="n">
         <v>215</v>
-      </c>
-      <c r="E30" s="5" t="n">
-        <v>1284</v>
       </c>
       <c r="F30" s="5" t="n">
         <v>208</v>
@@ -2913,10 +2913,10 @@
         <v>544</v>
       </c>
       <c r="D31" t="n">
+        <v>1284</v>
+      </c>
+      <c r="E31" t="n">
         <v>217</v>
-      </c>
-      <c r="E31" t="n">
-        <v>1284</v>
       </c>
       <c r="F31" t="n">
         <v>208</v>
@@ -2992,10 +2992,10 @@
         <v>556</v>
       </c>
       <c r="D32" s="5" t="n">
+        <v>1286</v>
+      </c>
+      <c r="E32" s="5" t="n">
         <v>217</v>
-      </c>
-      <c r="E32" s="5" t="n">
-        <v>1286</v>
       </c>
       <c r="F32" s="5" t="n">
         <v>218</v>
@@ -3071,10 +3071,10 @@
         <v>564</v>
       </c>
       <c r="D33" t="n">
+        <v>1286</v>
+      </c>
+      <c r="E33" t="n">
         <v>216</v>
-      </c>
-      <c r="E33" t="n">
-        <v>1286</v>
       </c>
       <c r="F33" t="n">
         <v>218</v>
@@ -3150,10 +3150,10 @@
         <v>563</v>
       </c>
       <c r="D34" s="5" t="n">
+        <v>1324</v>
+      </c>
+      <c r="E34" s="5" t="n">
         <v>216</v>
-      </c>
-      <c r="E34" s="5" t="n">
-        <v>1324</v>
       </c>
       <c r="F34" s="5" t="n">
         <v>218</v>
@@ -3229,10 +3229,10 @@
         <v>563</v>
       </c>
       <c r="D35" t="n">
+        <v>1324</v>
+      </c>
+      <c r="E35" t="n">
         <v>216</v>
-      </c>
-      <c r="E35" t="n">
-        <v>1324</v>
       </c>
       <c r="F35" t="n">
         <v>218</v>
@@ -3308,10 +3308,10 @@
         <v>563</v>
       </c>
       <c r="D36" s="5" t="n">
+        <v>1324</v>
+      </c>
+      <c r="E36" s="5" t="n">
         <v>216</v>
-      </c>
-      <c r="E36" s="5" t="n">
-        <v>1324</v>
       </c>
       <c r="F36" s="5" t="n">
         <v>218</v>
@@ -3387,10 +3387,10 @@
         <v>563</v>
       </c>
       <c r="D37" t="n">
+        <v>1306</v>
+      </c>
+      <c r="E37" t="n">
         <v>212</v>
-      </c>
-      <c r="E37" t="n">
-        <v>1306</v>
       </c>
       <c r="F37" t="n">
         <v>216</v>
@@ -3466,10 +3466,10 @@
         <v>556</v>
       </c>
       <c r="D38" s="5" t="n">
+        <v>1310</v>
+      </c>
+      <c r="E38" s="5" t="n">
         <v>212</v>
-      </c>
-      <c r="E38" s="5" t="n">
-        <v>1310</v>
       </c>
       <c r="F38" s="5" t="n">
         <v>207</v>
@@ -3545,10 +3545,10 @@
         <v>562</v>
       </c>
       <c r="D39" t="n">
+        <v>1305</v>
+      </c>
+      <c r="E39" t="n">
         <v>214</v>
-      </c>
-      <c r="E39" t="n">
-        <v>1305</v>
       </c>
       <c r="F39" t="n">
         <v>207</v>
@@ -3624,10 +3624,10 @@
         <v>519</v>
       </c>
       <c r="D40" s="5" t="n">
+        <v>1295</v>
+      </c>
+      <c r="E40" s="5" t="n">
         <v>210</v>
-      </c>
-      <c r="E40" s="5" t="n">
-        <v>1295</v>
       </c>
       <c r="F40" s="5" t="n">
         <v>226</v>
@@ -3703,10 +3703,10 @@
         <v>517</v>
       </c>
       <c r="D41" t="n">
+        <v>1285</v>
+      </c>
+      <c r="E41" t="n">
         <v>210</v>
-      </c>
-      <c r="E41" t="n">
-        <v>1285</v>
       </c>
       <c r="F41" t="n">
         <v>219</v>
@@ -3782,10 +3782,10 @@
         <v>517</v>
       </c>
       <c r="D42" s="5" t="n">
+        <v>1239</v>
+      </c>
+      <c r="E42" s="5" t="n">
         <v>210</v>
-      </c>
-      <c r="E42" s="5" t="n">
-        <v>1239</v>
       </c>
       <c r="F42" s="5" t="n">
         <v>219</v>
@@ -3861,10 +3861,10 @@
         <v>517</v>
       </c>
       <c r="D43" t="n">
+        <v>1270</v>
+      </c>
+      <c r="E43" t="n">
         <v>210</v>
-      </c>
-      <c r="E43" t="n">
-        <v>1270</v>
       </c>
       <c r="F43" t="n">
         <v>219</v>
@@ -3940,10 +3940,10 @@
         <v>531</v>
       </c>
       <c r="D44" s="5" t="n">
+        <v>1255</v>
+      </c>
+      <c r="E44" s="5" t="n">
         <v>208</v>
-      </c>
-      <c r="E44" s="5" t="n">
-        <v>1255</v>
       </c>
       <c r="F44" s="5" t="n">
         <v>214</v>
@@ -4019,10 +4019,10 @@
         <v>548</v>
       </c>
       <c r="D45" t="n">
+        <v>1254</v>
+      </c>
+      <c r="E45" t="n">
         <v>208</v>
-      </c>
-      <c r="E45" t="n">
-        <v>1254</v>
       </c>
       <c r="F45" t="n">
         <v>214</v>
@@ -4098,10 +4098,10 @@
         <v>548</v>
       </c>
       <c r="D46" s="5" t="n">
+        <v>1244</v>
+      </c>
+      <c r="E46" s="5" t="n">
         <v>203</v>
-      </c>
-      <c r="E46" s="5" t="n">
-        <v>1244</v>
       </c>
       <c r="F46" s="5" t="n">
         <v>218</v>
@@ -4177,10 +4177,10 @@
         <v>554</v>
       </c>
       <c r="D47" t="n">
+        <v>1235</v>
+      </c>
+      <c r="E47" t="n">
         <v>233</v>
-      </c>
-      <c r="E47" t="n">
-        <v>1235</v>
       </c>
       <c r="F47" t="n">
         <v>214</v>
@@ -4256,10 +4256,10 @@
         <v>550</v>
       </c>
       <c r="D48" s="5" t="n">
+        <v>1253</v>
+      </c>
+      <c r="E48" s="5" t="n">
         <v>232</v>
-      </c>
-      <c r="E48" s="5" t="n">
-        <v>1253</v>
       </c>
       <c r="F48" s="5" t="n">
         <v>211</v>
@@ -4335,10 +4335,10 @@
         <v>550</v>
       </c>
       <c r="D49" t="n">
+        <v>1221</v>
+      </c>
+      <c r="E49" t="n">
         <v>232</v>
-      </c>
-      <c r="E49" t="n">
-        <v>1221</v>
       </c>
       <c r="F49" t="n">
         <v>211</v>
@@ -4414,10 +4414,10 @@
         <v>550</v>
       </c>
       <c r="D50" s="5" t="n">
+        <v>1253</v>
+      </c>
+      <c r="E50" s="5" t="n">
         <v>232</v>
-      </c>
-      <c r="E50" s="5" t="n">
-        <v>1253</v>
       </c>
       <c r="F50" s="5" t="n">
         <v>211</v>
@@ -4493,10 +4493,10 @@
         <v>550</v>
       </c>
       <c r="D51" t="n">
+        <v>1155</v>
+      </c>
+      <c r="E51" t="n">
         <v>227</v>
-      </c>
-      <c r="E51" t="n">
-        <v>1155</v>
       </c>
       <c r="F51" t="n">
         <v>226</v>
@@ -4572,10 +4572,10 @@
         <v>541</v>
       </c>
       <c r="D52" s="5" t="n">
+        <v>1062</v>
+      </c>
+      <c r="E52" s="5" t="n">
         <v>225</v>
-      </c>
-      <c r="E52" s="5" t="n">
-        <v>1062</v>
       </c>
       <c r="F52" s="5" t="n">
         <v>224</v>
@@ -4651,10 +4651,10 @@
         <v>539</v>
       </c>
       <c r="D53" t="n">
+        <v>993</v>
+      </c>
+      <c r="E53" t="n">
         <v>224</v>
-      </c>
-      <c r="E53" t="n">
-        <v>993</v>
       </c>
       <c r="F53" t="n">
         <v>232</v>
@@ -4730,10 +4730,10 @@
         <v>533</v>
       </c>
       <c r="D54" s="5" t="n">
+        <v>988</v>
+      </c>
+      <c r="E54" s="5" t="n">
         <v>224</v>
-      </c>
-      <c r="E54" s="5" t="n">
-        <v>988</v>
       </c>
       <c r="F54" s="5" t="n">
         <v>232</v>
@@ -4809,10 +4809,10 @@
         <v>533</v>
       </c>
       <c r="D55" t="n">
+        <v>956</v>
+      </c>
+      <c r="E55" t="n">
         <v>224</v>
-      </c>
-      <c r="E55" t="n">
-        <v>956</v>
       </c>
       <c r="F55" t="n">
         <v>232</v>
@@ -4888,10 +4888,10 @@
         <v>532</v>
       </c>
       <c r="D56" s="5" t="n">
+        <v>985</v>
+      </c>
+      <c r="E56" s="5" t="n">
         <v>223</v>
-      </c>
-      <c r="E56" s="5" t="n">
-        <v>985</v>
       </c>
       <c r="F56" s="5" t="n">
         <v>232</v>
@@ -4967,10 +4967,10 @@
         <v>527</v>
       </c>
       <c r="D57" t="n">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="E57" t="n">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="F57" t="n">
         <v>0</v>
@@ -5046,10 +5046,10 @@
         <v>525</v>
       </c>
       <c r="D58" s="5" t="n">
+        <v>72</v>
+      </c>
+      <c r="E58" s="5" t="n">
         <v>216</v>
-      </c>
-      <c r="E58" s="5" t="n">
-        <v>72</v>
       </c>
       <c r="F58" s="5" t="n">
         <v>0</v>
@@ -5125,10 +5125,10 @@
         <v>528</v>
       </c>
       <c r="D59" t="n">
+        <v>549</v>
+      </c>
+      <c r="E59" t="n">
         <v>205</v>
-      </c>
-      <c r="E59" t="n">
-        <v>549</v>
       </c>
       <c r="F59" t="n">
         <v>207</v>
@@ -5204,10 +5204,10 @@
         <v>536</v>
       </c>
       <c r="D60" s="5" t="n">
+        <v>504</v>
+      </c>
+      <c r="E60" s="5" t="n">
         <v>270</v>
-      </c>
-      <c r="E60" s="5" t="n">
-        <v>504</v>
       </c>
       <c r="F60" s="5" t="n">
         <v>218</v>
@@ -5283,10 +5283,10 @@
         <v>533</v>
       </c>
       <c r="D61" t="n">
+        <v>495</v>
+      </c>
+      <c r="E61" t="n">
         <v>282</v>
-      </c>
-      <c r="E61" t="n">
-        <v>495</v>
       </c>
       <c r="F61" t="n">
         <v>218</v>
@@ -5362,10 +5362,10 @@
         <v>533</v>
       </c>
       <c r="D62" s="5" t="n">
+        <v>495</v>
+      </c>
+      <c r="E62" s="5" t="n">
         <v>282</v>
-      </c>
-      <c r="E62" s="5" t="n">
-        <v>495</v>
       </c>
       <c r="F62" s="5" t="n">
         <v>218</v>
@@ -5441,10 +5441,10 @@
         <v>533</v>
       </c>
       <c r="D63" t="n">
+        <v>495</v>
+      </c>
+      <c r="E63" t="n">
         <v>282</v>
-      </c>
-      <c r="E63" t="n">
-        <v>495</v>
       </c>
       <c r="F63" t="n">
         <v>218</v>
@@ -5520,10 +5520,10 @@
         <v>541</v>
       </c>
       <c r="D64" s="5" t="n">
+        <v>469</v>
+      </c>
+      <c r="E64" s="5" t="n">
         <v>366</v>
-      </c>
-      <c r="E64" s="5" t="n">
-        <v>469</v>
       </c>
       <c r="F64" s="5" t="n">
         <v>215</v>
@@ -5599,10 +5599,10 @@
         <v>534</v>
       </c>
       <c r="D65" t="n">
+        <v>471</v>
+      </c>
+      <c r="E65" t="n">
         <v>356</v>
-      </c>
-      <c r="E65" t="n">
-        <v>471</v>
       </c>
       <c r="F65" t="n">
         <v>211</v>
@@ -5678,10 +5678,10 @@
         <v>521</v>
       </c>
       <c r="D66" s="5" t="n">
+        <v>470</v>
+      </c>
+      <c r="E66" s="5" t="n">
         <v>381</v>
-      </c>
-      <c r="E66" s="5" t="n">
-        <v>470</v>
       </c>
       <c r="F66" s="5" t="n">
         <v>201</v>
@@ -5757,10 +5757,10 @@
         <v>525</v>
       </c>
       <c r="D67" t="n">
+        <v>446</v>
+      </c>
+      <c r="E67" t="n">
         <v>380</v>
-      </c>
-      <c r="E67" t="n">
-        <v>446</v>
       </c>
       <c r="F67" t="n">
         <v>200</v>
@@ -5833,10 +5833,10 @@
         <v>518</v>
       </c>
       <c r="D68" s="5" t="n">
+        <v>416</v>
+      </c>
+      <c r="E68" s="5" t="n">
         <v>370</v>
-      </c>
-      <c r="E68" s="5" t="n">
-        <v>416</v>
       </c>
       <c r="F68" s="5" t="n">
         <v>206</v>
@@ -5909,10 +5909,10 @@
         <v>850</v>
       </c>
       <c r="D69" t="n">
+        <v>416</v>
+      </c>
+      <c r="E69" t="n">
         <v>370</v>
-      </c>
-      <c r="E69" t="n">
-        <v>416</v>
       </c>
       <c r="F69" t="n">
         <v>206</v>
@@ -5985,10 +5985,10 @@
         <v>518</v>
       </c>
       <c r="D70" s="5" t="n">
+        <v>416</v>
+      </c>
+      <c r="E70" s="5" t="n">
         <v>370</v>
-      </c>
-      <c r="E70" s="5" t="n">
-        <v>416</v>
       </c>
       <c r="F70" s="5" t="n">
         <v>206</v>
@@ -6064,10 +6064,10 @@
         <v>516</v>
       </c>
       <c r="D71" t="n">
+        <v>395</v>
+      </c>
+      <c r="E71" t="n">
         <v>397</v>
-      </c>
-      <c r="E71" t="n">
-        <v>395</v>
       </c>
       <c r="F71" t="n">
         <v>190</v>
@@ -6143,10 +6143,10 @@
         <v>531</v>
       </c>
       <c r="D72" s="5" t="n">
+        <v>394</v>
+      </c>
+      <c r="E72" s="5" t="n">
         <v>398</v>
-      </c>
-      <c r="E72" s="5" t="n">
-        <v>394</v>
       </c>
       <c r="F72" s="5" t="n">
         <v>196</v>
@@ -6206,6 +6206,85 @@
         <v>0</v>
       </c>
       <c r="Y72" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B73" t="n">
+        <v>858</v>
+      </c>
+      <c r="C73" t="n">
+        <v>529</v>
+      </c>
+      <c r="D73" t="n">
+        <v>395</v>
+      </c>
+      <c r="E73" t="n">
+        <v>390</v>
+      </c>
+      <c r="F73" t="n">
+        <v>201</v>
+      </c>
+      <c r="G73" t="n">
+        <v>100</v>
+      </c>
+      <c r="H73" t="n">
+        <v>42</v>
+      </c>
+      <c r="I73" t="n">
+        <v>26</v>
+      </c>
+      <c r="J73" t="n">
+        <v>24</v>
+      </c>
+      <c r="K73" t="n">
+        <v>19</v>
+      </c>
+      <c r="L73" t="n">
+        <v>0</v>
+      </c>
+      <c r="M73" t="n">
+        <v>0</v>
+      </c>
+      <c r="N73" t="n">
+        <v>0</v>
+      </c>
+      <c r="O73" t="n">
+        <v>0</v>
+      </c>
+      <c r="P73" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q73" t="n">
+        <v>0</v>
+      </c>
+      <c r="R73" t="n">
+        <v>0</v>
+      </c>
+      <c r="S73" t="n">
+        <v>0</v>
+      </c>
+      <c r="T73" t="n">
+        <v>0</v>
+      </c>
+      <c r="U73" t="n">
+        <v>0</v>
+      </c>
+      <c r="V73" t="n">
+        <v>0</v>
+      </c>
+      <c r="W73" t="n">
+        <v>0</v>
+      </c>
+      <c r="X73" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y73" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6220,7 +6299,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D1136"/>
+  <dimension ref="A1:D1134"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -6247,7 +6326,7 @@
       </c>
       <c r="D1" s="3" t="inlineStr">
         <is>
-          <t>Lager (2026-09-16)</t>
+          <t>Lager (2026-09-17)</t>
         </is>
       </c>
     </row>
@@ -6268,7 +6347,7 @@
         </is>
       </c>
       <c r="D2" s="4" t="n">
-        <v>531</v>
+        <v>529</v>
       </c>
     </row>
     <row r="3">
@@ -14908,7 +14987,7 @@
         </is>
       </c>
       <c r="D434" s="4" t="n">
-        <v>150</v>
+        <v>156</v>
       </c>
     </row>
     <row r="435">
@@ -14988,7 +15067,7 @@
         </is>
       </c>
       <c r="D438" s="4" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="439">
@@ -15568,7 +15647,7 @@
         </is>
       </c>
       <c r="D467" s="6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="468">
@@ -20934,12 +21013,12 @@
     <row r="736">
       <c r="A736" s="4" t="inlineStr">
         <is>
-          <t>7015170</t>
+          <t>7029050</t>
         </is>
       </c>
       <c r="B736" s="5" t="inlineStr">
         <is>
-          <t>Infälld armatur Invoid "Hörn"</t>
+          <t>Interiörarmatur IR 92</t>
         </is>
       </c>
       <c r="C736" s="5" t="inlineStr">
@@ -20954,12 +21033,12 @@
     <row r="737">
       <c r="A737" s="6" t="inlineStr">
         <is>
-          <t>7015171</t>
+          <t>7029051</t>
         </is>
       </c>
       <c r="B737" t="inlineStr">
         <is>
-          <t>Infälld armatur Invoid "Hörn"</t>
+          <t>Interiörarmatur IR 92</t>
         </is>
       </c>
       <c r="C737" t="inlineStr">
@@ -20974,12 +21053,12 @@
     <row r="738">
       <c r="A738" s="4" t="inlineStr">
         <is>
-          <t>7015172</t>
+          <t>7029052</t>
         </is>
       </c>
       <c r="B738" s="5" t="inlineStr">
         <is>
-          <t>Infälld armatur Invoid "Hörn"</t>
+          <t>Interiörarmatur IR 92</t>
         </is>
       </c>
       <c r="C738" s="5" t="inlineStr">
@@ -20994,12 +21073,12 @@
     <row r="739">
       <c r="A739" s="6" t="inlineStr">
         <is>
-          <t>7015173</t>
+          <t>7029053</t>
         </is>
       </c>
       <c r="B739" t="inlineStr">
         <is>
-          <t>Infälld armatur Invoid "Hörn"</t>
+          <t>Interiörarmatur IR 92</t>
         </is>
       </c>
       <c r="C739" t="inlineStr">
@@ -21014,7 +21093,7 @@
     <row r="740">
       <c r="A740" s="4" t="inlineStr">
         <is>
-          <t>7029050</t>
+          <t>7029054</t>
         </is>
       </c>
       <c r="B740" s="5" t="inlineStr">
@@ -21034,7 +21113,7 @@
     <row r="741">
       <c r="A741" s="6" t="inlineStr">
         <is>
-          <t>7029051</t>
+          <t>7029055</t>
         </is>
       </c>
       <c r="B741" t="inlineStr">
@@ -21054,12 +21133,12 @@
     <row r="742">
       <c r="A742" s="4" t="inlineStr">
         <is>
-          <t>7029052</t>
+          <t>7019046</t>
         </is>
       </c>
       <c r="B742" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur IR 92</t>
+          <t>Interiörarmatur InLED infälld</t>
         </is>
       </c>
       <c r="C742" s="5" t="inlineStr">
@@ -21074,12 +21153,12 @@
     <row r="743">
       <c r="A743" s="6" t="inlineStr">
         <is>
-          <t>7029053</t>
+          <t>7019047</t>
         </is>
       </c>
       <c r="B743" t="inlineStr">
         <is>
-          <t>Interiörarmatur IR 92</t>
+          <t>Interiörarmatur InLED infälld</t>
         </is>
       </c>
       <c r="C743" t="inlineStr">
@@ -21094,12 +21173,12 @@
     <row r="744">
       <c r="A744" s="4" t="inlineStr">
         <is>
-          <t>7029054</t>
+          <t>7019053</t>
         </is>
       </c>
       <c r="B744" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur IR 92</t>
+          <t>Interiörarmatur InLED infälld</t>
         </is>
       </c>
       <c r="C744" s="5" t="inlineStr">
@@ -21114,12 +21193,12 @@
     <row r="745">
       <c r="A745" s="6" t="inlineStr">
         <is>
-          <t>7029055</t>
+          <t>7019058</t>
         </is>
       </c>
       <c r="B745" t="inlineStr">
         <is>
-          <t>Interiörarmatur IR 92</t>
+          <t>Interiörarmatur InLED infälld</t>
         </is>
       </c>
       <c r="C745" t="inlineStr">
@@ -21134,7 +21213,7 @@
     <row r="746">
       <c r="A746" s="4" t="inlineStr">
         <is>
-          <t>7019046</t>
+          <t>7019059</t>
         </is>
       </c>
       <c r="B746" s="5" t="inlineStr">
@@ -21154,7 +21233,7 @@
     <row r="747">
       <c r="A747" s="6" t="inlineStr">
         <is>
-          <t>7019047</t>
+          <t>7019060</t>
         </is>
       </c>
       <c r="B747" t="inlineStr">
@@ -21174,7 +21253,7 @@
     <row r="748">
       <c r="A748" s="4" t="inlineStr">
         <is>
-          <t>7019053</t>
+          <t>7019073</t>
         </is>
       </c>
       <c r="B748" s="5" t="inlineStr">
@@ -21194,7 +21273,7 @@
     <row r="749">
       <c r="A749" s="6" t="inlineStr">
         <is>
-          <t>7019058</t>
+          <t>7019074</t>
         </is>
       </c>
       <c r="B749" t="inlineStr">
@@ -21214,12 +21293,12 @@
     <row r="750">
       <c r="A750" s="4" t="inlineStr">
         <is>
-          <t>7019059</t>
+          <t>7019315</t>
         </is>
       </c>
       <c r="B750" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur InLED infälld</t>
+          <t>Interiörarmatur InMY infälld</t>
         </is>
       </c>
       <c r="C750" s="5" t="inlineStr">
@@ -21234,12 +21313,12 @@
     <row r="751">
       <c r="A751" s="6" t="inlineStr">
         <is>
-          <t>7019060</t>
+          <t>7019344</t>
         </is>
       </c>
       <c r="B751" t="inlineStr">
         <is>
-          <t>Interiörarmatur InLED infälld</t>
+          <t>Interiörarmatur InMY infälld</t>
         </is>
       </c>
       <c r="C751" t="inlineStr">
@@ -21254,12 +21333,12 @@
     <row r="752">
       <c r="A752" s="4" t="inlineStr">
         <is>
-          <t>7019073</t>
+          <t>7019345</t>
         </is>
       </c>
       <c r="B752" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur InLED infälld</t>
+          <t>Interiörarmatur InMY infälld</t>
         </is>
       </c>
       <c r="C752" s="5" t="inlineStr">
@@ -21274,12 +21353,12 @@
     <row r="753">
       <c r="A753" s="6" t="inlineStr">
         <is>
-          <t>7019074</t>
+          <t>7019346</t>
         </is>
       </c>
       <c r="B753" t="inlineStr">
         <is>
-          <t>Interiörarmatur InLED infälld</t>
+          <t>Interiörarmatur InMY infälld</t>
         </is>
       </c>
       <c r="C753" t="inlineStr">
@@ -21294,7 +21373,7 @@
     <row r="754">
       <c r="A754" s="4" t="inlineStr">
         <is>
-          <t>7019315</t>
+          <t>7019347</t>
         </is>
       </c>
       <c r="B754" s="5" t="inlineStr">
@@ -21314,7 +21393,7 @@
     <row r="755">
       <c r="A755" s="6" t="inlineStr">
         <is>
-          <t>7019344</t>
+          <t>7019358</t>
         </is>
       </c>
       <c r="B755" t="inlineStr">
@@ -21334,7 +21413,7 @@
     <row r="756">
       <c r="A756" s="4" t="inlineStr">
         <is>
-          <t>7019345</t>
+          <t>7019359</t>
         </is>
       </c>
       <c r="B756" s="5" t="inlineStr">
@@ -21354,7 +21433,7 @@
     <row r="757">
       <c r="A757" s="6" t="inlineStr">
         <is>
-          <t>7019346</t>
+          <t>7019360</t>
         </is>
       </c>
       <c r="B757" t="inlineStr">
@@ -21374,7 +21453,7 @@
     <row r="758">
       <c r="A758" s="4" t="inlineStr">
         <is>
-          <t>7019347</t>
+          <t>7019361</t>
         </is>
       </c>
       <c r="B758" s="5" t="inlineStr">
@@ -21394,7 +21473,7 @@
     <row r="759">
       <c r="A759" s="6" t="inlineStr">
         <is>
-          <t>7019358</t>
+          <t>7019348</t>
         </is>
       </c>
       <c r="B759" t="inlineStr">
@@ -21414,7 +21493,7 @@
     <row r="760">
       <c r="A760" s="4" t="inlineStr">
         <is>
-          <t>7019359</t>
+          <t>7019349</t>
         </is>
       </c>
       <c r="B760" s="5" t="inlineStr">
@@ -21434,7 +21513,7 @@
     <row r="761">
       <c r="A761" s="6" t="inlineStr">
         <is>
-          <t>7019360</t>
+          <t>7019350</t>
         </is>
       </c>
       <c r="B761" t="inlineStr">
@@ -21454,7 +21533,7 @@
     <row r="762">
       <c r="A762" s="4" t="inlineStr">
         <is>
-          <t>7019361</t>
+          <t>7019351</t>
         </is>
       </c>
       <c r="B762" s="5" t="inlineStr">
@@ -21474,7 +21553,7 @@
     <row r="763">
       <c r="A763" s="6" t="inlineStr">
         <is>
-          <t>7019348</t>
+          <t>7019352</t>
         </is>
       </c>
       <c r="B763" t="inlineStr">
@@ -21494,7 +21573,7 @@
     <row r="764">
       <c r="A764" s="4" t="inlineStr">
         <is>
-          <t>7019349</t>
+          <t>7019353</t>
         </is>
       </c>
       <c r="B764" s="5" t="inlineStr">
@@ -21514,7 +21593,7 @@
     <row r="765">
       <c r="A765" s="6" t="inlineStr">
         <is>
-          <t>7019350</t>
+          <t>7019354</t>
         </is>
       </c>
       <c r="B765" t="inlineStr">
@@ -21534,7 +21613,7 @@
     <row r="766">
       <c r="A766" s="4" t="inlineStr">
         <is>
-          <t>7019351</t>
+          <t>7019355</t>
         </is>
       </c>
       <c r="B766" s="5" t="inlineStr">
@@ -21554,7 +21633,7 @@
     <row r="767">
       <c r="A767" s="6" t="inlineStr">
         <is>
-          <t>7019352</t>
+          <t>7019356</t>
         </is>
       </c>
       <c r="B767" t="inlineStr">
@@ -21574,7 +21653,7 @@
     <row r="768">
       <c r="A768" s="4" t="inlineStr">
         <is>
-          <t>7019353</t>
+          <t>7019357</t>
         </is>
       </c>
       <c r="B768" s="5" t="inlineStr">
@@ -21594,12 +21673,12 @@
     <row r="769">
       <c r="A769" s="6" t="inlineStr">
         <is>
-          <t>7019354</t>
+          <t>7021449</t>
         </is>
       </c>
       <c r="B769" t="inlineStr">
         <is>
-          <t>Interiörarmatur InMY infälld</t>
+          <t>Interiörarmatur Inlens</t>
         </is>
       </c>
       <c r="C769" t="inlineStr">
@@ -21614,12 +21693,12 @@
     <row r="770">
       <c r="A770" s="4" t="inlineStr">
         <is>
-          <t>7019355</t>
+          <t>7021450</t>
         </is>
       </c>
       <c r="B770" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur InMY infälld</t>
+          <t>Interiörarmatur Inlens</t>
         </is>
       </c>
       <c r="C770" s="5" t="inlineStr">
@@ -21634,12 +21713,12 @@
     <row r="771">
       <c r="A771" s="6" t="inlineStr">
         <is>
-          <t>7019356</t>
+          <t>7021451</t>
         </is>
       </c>
       <c r="B771" t="inlineStr">
         <is>
-          <t>Interiörarmatur InMY infälld</t>
+          <t>Interiörarmatur Inlens</t>
         </is>
       </c>
       <c r="C771" t="inlineStr">
@@ -21654,12 +21733,12 @@
     <row r="772">
       <c r="A772" s="4" t="inlineStr">
         <is>
-          <t>7019357</t>
+          <t>7021452</t>
         </is>
       </c>
       <c r="B772" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur InMY infälld</t>
+          <t>Interiörarmatur Inlens</t>
         </is>
       </c>
       <c r="C772" s="5" t="inlineStr">
@@ -21674,7 +21753,7 @@
     <row r="773">
       <c r="A773" s="6" t="inlineStr">
         <is>
-          <t>7021449</t>
+          <t>7021453</t>
         </is>
       </c>
       <c r="B773" t="inlineStr">
@@ -21694,7 +21773,7 @@
     <row r="774">
       <c r="A774" s="4" t="inlineStr">
         <is>
-          <t>7021450</t>
+          <t>7021454</t>
         </is>
       </c>
       <c r="B774" s="5" t="inlineStr">
@@ -21714,7 +21793,7 @@
     <row r="775">
       <c r="A775" s="6" t="inlineStr">
         <is>
-          <t>7021451</t>
+          <t>7021443</t>
         </is>
       </c>
       <c r="B775" t="inlineStr">
@@ -21734,7 +21813,7 @@
     <row r="776">
       <c r="A776" s="4" t="inlineStr">
         <is>
-          <t>7021452</t>
+          <t>7021444</t>
         </is>
       </c>
       <c r="B776" s="5" t="inlineStr">
@@ -21754,7 +21833,7 @@
     <row r="777">
       <c r="A777" s="6" t="inlineStr">
         <is>
-          <t>7021453</t>
+          <t>7021445</t>
         </is>
       </c>
       <c r="B777" t="inlineStr">
@@ -21774,7 +21853,7 @@
     <row r="778">
       <c r="A778" s="4" t="inlineStr">
         <is>
-          <t>7021454</t>
+          <t>7021446</t>
         </is>
       </c>
       <c r="B778" s="5" t="inlineStr">
@@ -21794,7 +21873,7 @@
     <row r="779">
       <c r="A779" s="6" t="inlineStr">
         <is>
-          <t>7021443</t>
+          <t>7021447</t>
         </is>
       </c>
       <c r="B779" t="inlineStr">
@@ -21814,7 +21893,7 @@
     <row r="780">
       <c r="A780" s="4" t="inlineStr">
         <is>
-          <t>7021444</t>
+          <t>7021448</t>
         </is>
       </c>
       <c r="B780" s="5" t="inlineStr">
@@ -21834,12 +21913,12 @@
     <row r="781">
       <c r="A781" s="6" t="inlineStr">
         <is>
-          <t>7021445</t>
+          <t>7018887</t>
         </is>
       </c>
       <c r="B781" t="inlineStr">
         <is>
-          <t>Interiörarmatur Inlens</t>
+          <t>Interiörarmatur Pi infälld</t>
         </is>
       </c>
       <c r="C781" t="inlineStr">
@@ -21854,12 +21933,12 @@
     <row r="782">
       <c r="A782" s="4" t="inlineStr">
         <is>
-          <t>7021446</t>
+          <t>7018888</t>
         </is>
       </c>
       <c r="B782" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Inlens</t>
+          <t>Interiörarmatur Pi infälld</t>
         </is>
       </c>
       <c r="C782" s="5" t="inlineStr">
@@ -21874,12 +21953,12 @@
     <row r="783">
       <c r="A783" s="6" t="inlineStr">
         <is>
-          <t>7021447</t>
+          <t>7028566</t>
         </is>
       </c>
       <c r="B783" t="inlineStr">
         <is>
-          <t>Interiörarmatur Inlens</t>
+          <t>Interiörarmatur Safe</t>
         </is>
       </c>
       <c r="C783" t="inlineStr">
@@ -21894,12 +21973,12 @@
     <row r="784">
       <c r="A784" s="4" t="inlineStr">
         <is>
-          <t>7021448</t>
+          <t>7028567</t>
         </is>
       </c>
       <c r="B784" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Inlens</t>
+          <t>Interiörarmatur Safe</t>
         </is>
       </c>
       <c r="C784" s="5" t="inlineStr">
@@ -21914,12 +21993,12 @@
     <row r="785">
       <c r="A785" s="6" t="inlineStr">
         <is>
-          <t>7018887</t>
+          <t>7028568</t>
         </is>
       </c>
       <c r="B785" t="inlineStr">
         <is>
-          <t>Interiörarmatur Pi infälld</t>
+          <t>Interiörarmatur Safe</t>
         </is>
       </c>
       <c r="C785" t="inlineStr">
@@ -21934,12 +22013,12 @@
     <row r="786">
       <c r="A786" s="4" t="inlineStr">
         <is>
-          <t>7018888</t>
+          <t>7028569</t>
         </is>
       </c>
       <c r="B786" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Pi infälld</t>
+          <t>Interiörarmatur Safe</t>
         </is>
       </c>
       <c r="C786" s="5" t="inlineStr">
@@ -21954,7 +22033,7 @@
     <row r="787">
       <c r="A787" s="6" t="inlineStr">
         <is>
-          <t>7028566</t>
+          <t>7028570</t>
         </is>
       </c>
       <c r="B787" t="inlineStr">
@@ -21974,7 +22053,7 @@
     <row r="788">
       <c r="A788" s="4" t="inlineStr">
         <is>
-          <t>7028567</t>
+          <t>7028571</t>
         </is>
       </c>
       <c r="B788" s="5" t="inlineStr">
@@ -21994,7 +22073,7 @@
     <row r="789">
       <c r="A789" s="6" t="inlineStr">
         <is>
-          <t>7028568</t>
+          <t>7028572</t>
         </is>
       </c>
       <c r="B789" t="inlineStr">
@@ -22014,7 +22093,7 @@
     <row r="790">
       <c r="A790" s="4" t="inlineStr">
         <is>
-          <t>7028569</t>
+          <t>7028573</t>
         </is>
       </c>
       <c r="B790" s="5" t="inlineStr">
@@ -22034,7 +22113,7 @@
     <row r="791">
       <c r="A791" s="6" t="inlineStr">
         <is>
-          <t>7028570</t>
+          <t>7028574</t>
         </is>
       </c>
       <c r="B791" t="inlineStr">
@@ -22054,7 +22133,7 @@
     <row r="792">
       <c r="A792" s="4" t="inlineStr">
         <is>
-          <t>7028571</t>
+          <t>7028575</t>
         </is>
       </c>
       <c r="B792" s="5" t="inlineStr">
@@ -22074,7 +22153,7 @@
     <row r="793">
       <c r="A793" s="6" t="inlineStr">
         <is>
-          <t>7028572</t>
+          <t>7028576</t>
         </is>
       </c>
       <c r="B793" t="inlineStr">
@@ -22094,7 +22173,7 @@
     <row r="794">
       <c r="A794" s="4" t="inlineStr">
         <is>
-          <t>7028573</t>
+          <t>7028577</t>
         </is>
       </c>
       <c r="B794" s="5" t="inlineStr">
@@ -22114,7 +22193,7 @@
     <row r="795">
       <c r="A795" s="6" t="inlineStr">
         <is>
-          <t>7028574</t>
+          <t>7028578</t>
         </is>
       </c>
       <c r="B795" t="inlineStr">
@@ -22134,7 +22213,7 @@
     <row r="796">
       <c r="A796" s="4" t="inlineStr">
         <is>
-          <t>7028575</t>
+          <t>7028579</t>
         </is>
       </c>
       <c r="B796" s="5" t="inlineStr">
@@ -22154,7 +22233,7 @@
     <row r="797">
       <c r="A797" s="6" t="inlineStr">
         <is>
-          <t>7028576</t>
+          <t>7028580</t>
         </is>
       </c>
       <c r="B797" t="inlineStr">
@@ -22174,7 +22253,7 @@
     <row r="798">
       <c r="A798" s="4" t="inlineStr">
         <is>
-          <t>7028577</t>
+          <t>7028581</t>
         </is>
       </c>
       <c r="B798" s="5" t="inlineStr">
@@ -22194,17 +22273,17 @@
     <row r="799">
       <c r="A799" s="6" t="inlineStr">
         <is>
-          <t>7028578</t>
+          <t>7029244</t>
         </is>
       </c>
       <c r="B799" t="inlineStr">
         <is>
-          <t>Interiörarmatur Safe</t>
+          <t>LED-panel Easyfit</t>
         </is>
       </c>
       <c r="C799" t="inlineStr">
         <is>
-          <t>Nokalux</t>
+          <t>Norwesco</t>
         </is>
       </c>
       <c r="D799" s="6" t="n">
@@ -22214,17 +22293,17 @@
     <row r="800">
       <c r="A800" s="4" t="inlineStr">
         <is>
-          <t>7028579</t>
+          <t>7029245</t>
         </is>
       </c>
       <c r="B800" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Safe</t>
+          <t>LED-panel Easyfit</t>
         </is>
       </c>
       <c r="C800" s="5" t="inlineStr">
         <is>
-          <t>Nokalux</t>
+          <t>Norwesco</t>
         </is>
       </c>
       <c r="D800" s="4" t="n">
@@ -22234,17 +22313,17 @@
     <row r="801">
       <c r="A801" s="6" t="inlineStr">
         <is>
-          <t>7028580</t>
+          <t>7029246</t>
         </is>
       </c>
       <c r="B801" t="inlineStr">
         <is>
-          <t>Interiörarmatur Safe</t>
+          <t>LED-panel Easyfit</t>
         </is>
       </c>
       <c r="C801" t="inlineStr">
         <is>
-          <t>Nokalux</t>
+          <t>Norwesco</t>
         </is>
       </c>
       <c r="D801" s="6" t="n">
@@ -22254,17 +22333,17 @@
     <row r="802">
       <c r="A802" s="4" t="inlineStr">
         <is>
-          <t>7028581</t>
+          <t>7029247</t>
         </is>
       </c>
       <c r="B802" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Safe</t>
+          <t>LED-panel Easyfit</t>
         </is>
       </c>
       <c r="C802" s="5" t="inlineStr">
         <is>
-          <t>Nokalux</t>
+          <t>Norwesco</t>
         </is>
       </c>
       <c r="D802" s="4" t="n">
@@ -22274,12 +22353,12 @@
     <row r="803">
       <c r="A803" s="6" t="inlineStr">
         <is>
-          <t>7029244</t>
+          <t>7029248</t>
         </is>
       </c>
       <c r="B803" t="inlineStr">
         <is>
-          <t>LED-panel Easyfit</t>
+          <t>LED-panel Orion</t>
         </is>
       </c>
       <c r="C803" t="inlineStr">
@@ -22294,12 +22373,12 @@
     <row r="804">
       <c r="A804" s="4" t="inlineStr">
         <is>
-          <t>7029245</t>
+          <t>7029249</t>
         </is>
       </c>
       <c r="B804" s="5" t="inlineStr">
         <is>
-          <t>LED-panel Easyfit</t>
+          <t>LED-panel Orion</t>
         </is>
       </c>
       <c r="C804" s="5" t="inlineStr">
@@ -22314,12 +22393,12 @@
     <row r="805">
       <c r="A805" s="6" t="inlineStr">
         <is>
-          <t>7029246</t>
+          <t>7029250</t>
         </is>
       </c>
       <c r="B805" t="inlineStr">
         <is>
-          <t>LED-panel Easyfit</t>
+          <t>LED-panel Orion</t>
         </is>
       </c>
       <c r="C805" t="inlineStr">
@@ -22334,12 +22413,12 @@
     <row r="806">
       <c r="A806" s="4" t="inlineStr">
         <is>
-          <t>7029247</t>
+          <t>7029251</t>
         </is>
       </c>
       <c r="B806" s="5" t="inlineStr">
         <is>
-          <t>LED-panel Easyfit</t>
+          <t>LED-panel Orion</t>
         </is>
       </c>
       <c r="C806" s="5" t="inlineStr">
@@ -22354,17 +22433,17 @@
     <row r="807">
       <c r="A807" s="6" t="inlineStr">
         <is>
-          <t>7029248</t>
+          <t>7028893</t>
         </is>
       </c>
       <c r="B807" t="inlineStr">
         <is>
-          <t>LED-panel Orion</t>
+          <t>Infälld Interiörarmatur Coreline Panel</t>
         </is>
       </c>
       <c r="C807" t="inlineStr">
         <is>
-          <t>Norwesco</t>
+          <t>Philips</t>
         </is>
       </c>
       <c r="D807" s="6" t="n">
@@ -22374,17 +22453,17 @@
     <row r="808">
       <c r="A808" s="4" t="inlineStr">
         <is>
-          <t>7029249</t>
+          <t>7023008</t>
         </is>
       </c>
       <c r="B808" s="5" t="inlineStr">
         <is>
-          <t>LED-panel Orion</t>
+          <t>Infälld interiörarmatur CoreLine Panel, 600x600</t>
         </is>
       </c>
       <c r="C808" s="5" t="inlineStr">
         <is>
-          <t>Norwesco</t>
+          <t>Philips</t>
         </is>
       </c>
       <c r="D808" s="4" t="n">
@@ -22394,17 +22473,17 @@
     <row r="809">
       <c r="A809" s="6" t="inlineStr">
         <is>
-          <t>7029250</t>
+          <t>7028892</t>
         </is>
       </c>
       <c r="B809" t="inlineStr">
         <is>
-          <t>LED-panel Orion</t>
+          <t>Infälld interiörarmatur Coreline Panel Interact</t>
         </is>
       </c>
       <c r="C809" t="inlineStr">
         <is>
-          <t>Norwesco</t>
+          <t>Philips</t>
         </is>
       </c>
       <c r="D809" s="6" t="n">
@@ -22414,17 +22493,17 @@
     <row r="810">
       <c r="A810" s="4" t="inlineStr">
         <is>
-          <t>7029251</t>
+          <t>7042301</t>
         </is>
       </c>
       <c r="B810" s="5" t="inlineStr">
         <is>
-          <t>LED-panel Orion</t>
+          <t>Interiörarmatur Coreline RC132V infälld, 30x120</t>
         </is>
       </c>
       <c r="C810" s="5" t="inlineStr">
         <is>
-          <t>Norwesco</t>
+          <t>Philips</t>
         </is>
       </c>
       <c r="D810" s="4" t="n">
@@ -22434,12 +22513,12 @@
     <row r="811">
       <c r="A811" s="6" t="inlineStr">
         <is>
-          <t>7028893</t>
+          <t>7042305</t>
         </is>
       </c>
       <c r="B811" t="inlineStr">
         <is>
-          <t>Infälld Interiörarmatur Coreline Panel</t>
+          <t>Interiörarmatur Coreline RC132V infälld, 30x120</t>
         </is>
       </c>
       <c r="C811" t="inlineStr">
@@ -22454,12 +22533,12 @@
     <row r="812">
       <c r="A812" s="4" t="inlineStr">
         <is>
-          <t>7023008</t>
+          <t>7042306</t>
         </is>
       </c>
       <c r="B812" s="5" t="inlineStr">
         <is>
-          <t>Infälld interiörarmatur CoreLine Panel, 600x600</t>
+          <t>Interiörarmatur Coreline RC132V infälld, 30x120</t>
         </is>
       </c>
       <c r="C812" s="5" t="inlineStr">
@@ -22474,12 +22553,12 @@
     <row r="813">
       <c r="A813" s="6" t="inlineStr">
         <is>
-          <t>7028892</t>
+          <t>7042310</t>
         </is>
       </c>
       <c r="B813" t="inlineStr">
         <is>
-          <t>Infälld interiörarmatur Coreline Panel Interact</t>
+          <t>Interiörarmatur Coreline RC132V infälld, 30x120</t>
         </is>
       </c>
       <c r="C813" t="inlineStr">
@@ -22494,7 +22573,7 @@
     <row r="814">
       <c r="A814" s="4" t="inlineStr">
         <is>
-          <t>7042301</t>
+          <t>7042311</t>
         </is>
       </c>
       <c r="B814" s="5" t="inlineStr">
@@ -22514,7 +22593,7 @@
     <row r="815">
       <c r="A815" s="6" t="inlineStr">
         <is>
-          <t>7042305</t>
+          <t>7042315</t>
         </is>
       </c>
       <c r="B815" t="inlineStr">
@@ -22534,7 +22613,7 @@
     <row r="816">
       <c r="A816" s="4" t="inlineStr">
         <is>
-          <t>7042306</t>
+          <t>7042318</t>
         </is>
       </c>
       <c r="B816" s="5" t="inlineStr">
@@ -22554,12 +22633,12 @@
     <row r="817">
       <c r="A817" s="6" t="inlineStr">
         <is>
-          <t>7042310</t>
+          <t>7042302</t>
         </is>
       </c>
       <c r="B817" t="inlineStr">
         <is>
-          <t>Interiörarmatur Coreline RC132V infälld, 30x120</t>
+          <t>Interiörarmatur Coreline RC132V infälld, 60x60</t>
         </is>
       </c>
       <c r="C817" t="inlineStr">
@@ -22574,12 +22653,12 @@
     <row r="818">
       <c r="A818" s="4" t="inlineStr">
         <is>
-          <t>7042311</t>
+          <t>7042303</t>
         </is>
       </c>
       <c r="B818" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Coreline RC132V infälld, 30x120</t>
+          <t>Interiörarmatur Coreline RC132V infälld, 60x60</t>
         </is>
       </c>
       <c r="C818" s="5" t="inlineStr">
@@ -22594,12 +22673,12 @@
     <row r="819">
       <c r="A819" s="6" t="inlineStr">
         <is>
-          <t>7042315</t>
+          <t>7042304</t>
         </is>
       </c>
       <c r="B819" t="inlineStr">
         <is>
-          <t>Interiörarmatur Coreline RC132V infälld, 30x120</t>
+          <t>Interiörarmatur Coreline RC132V infälld, 60x60</t>
         </is>
       </c>
       <c r="C819" t="inlineStr">
@@ -22614,12 +22693,12 @@
     <row r="820">
       <c r="A820" s="4" t="inlineStr">
         <is>
-          <t>7042318</t>
+          <t>7042307</t>
         </is>
       </c>
       <c r="B820" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Coreline RC132V infälld, 30x120</t>
+          <t>Interiörarmatur Coreline RC132V infälld, 60x60</t>
         </is>
       </c>
       <c r="C820" s="5" t="inlineStr">
@@ -22634,7 +22713,7 @@
     <row r="821">
       <c r="A821" s="6" t="inlineStr">
         <is>
-          <t>7042302</t>
+          <t>7042308</t>
         </is>
       </c>
       <c r="B821" t="inlineStr">
@@ -22654,7 +22733,7 @@
     <row r="822">
       <c r="A822" s="4" t="inlineStr">
         <is>
-          <t>7042303</t>
+          <t>7042309</t>
         </is>
       </c>
       <c r="B822" s="5" t="inlineStr">
@@ -22674,7 +22753,7 @@
     <row r="823">
       <c r="A823" s="6" t="inlineStr">
         <is>
-          <t>7042304</t>
+          <t>7042312</t>
         </is>
       </c>
       <c r="B823" t="inlineStr">
@@ -22694,7 +22773,7 @@
     <row r="824">
       <c r="A824" s="4" t="inlineStr">
         <is>
-          <t>7042307</t>
+          <t>7042313</t>
         </is>
       </c>
       <c r="B824" s="5" t="inlineStr">
@@ -22714,7 +22793,7 @@
     <row r="825">
       <c r="A825" s="6" t="inlineStr">
         <is>
-          <t>7042308</t>
+          <t>7042314</t>
         </is>
       </c>
       <c r="B825" t="inlineStr">
@@ -22734,7 +22813,7 @@
     <row r="826">
       <c r="A826" s="4" t="inlineStr">
         <is>
-          <t>7042309</t>
+          <t>7042316</t>
         </is>
       </c>
       <c r="B826" s="5" t="inlineStr">
@@ -22754,7 +22833,7 @@
     <row r="827">
       <c r="A827" s="6" t="inlineStr">
         <is>
-          <t>7042312</t>
+          <t>7042317</t>
         </is>
       </c>
       <c r="B827" t="inlineStr">
@@ -22774,7 +22853,7 @@
     <row r="828">
       <c r="A828" s="4" t="inlineStr">
         <is>
-          <t>7042313</t>
+          <t>7042319</t>
         </is>
       </c>
       <c r="B828" s="5" t="inlineStr">
@@ -22794,7 +22873,7 @@
     <row r="829">
       <c r="A829" s="6" t="inlineStr">
         <is>
-          <t>7042314</t>
+          <t>7042321</t>
         </is>
       </c>
       <c r="B829" t="inlineStr">
@@ -22814,7 +22893,7 @@
     <row r="830">
       <c r="A830" s="4" t="inlineStr">
         <is>
-          <t>7042316</t>
+          <t>7042322</t>
         </is>
       </c>
       <c r="B830" s="5" t="inlineStr">
@@ -22834,12 +22913,12 @@
     <row r="831">
       <c r="A831" s="6" t="inlineStr">
         <is>
-          <t>7042317</t>
+          <t>7027241</t>
         </is>
       </c>
       <c r="B831" t="inlineStr">
         <is>
-          <t>Interiörarmatur Coreline RC132V infälld, 60x60</t>
+          <t>Interiörarmatur Ledinaire All-in, 3K/4K</t>
         </is>
       </c>
       <c r="C831" t="inlineStr">
@@ -22854,12 +22933,12 @@
     <row r="832">
       <c r="A832" s="4" t="inlineStr">
         <is>
-          <t>7042319</t>
+          <t>7027242</t>
         </is>
       </c>
       <c r="B832" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Coreline RC132V infälld, 60x60</t>
+          <t>Interiörarmatur Ledinaire All-in, 3K/4K</t>
         </is>
       </c>
       <c r="C832" s="5" t="inlineStr">
@@ -22874,12 +22953,12 @@
     <row r="833">
       <c r="A833" s="6" t="inlineStr">
         <is>
-          <t>7042321</t>
+          <t>7027245</t>
         </is>
       </c>
       <c r="B833" t="inlineStr">
         <is>
-          <t>Interiörarmatur Coreline RC132V infälld, 60x60</t>
+          <t>Interiörarmatur Ledinaire All-in, 3K/4K</t>
         </is>
       </c>
       <c r="C833" t="inlineStr">
@@ -22894,12 +22973,12 @@
     <row r="834">
       <c r="A834" s="4" t="inlineStr">
         <is>
-          <t>7042322</t>
+          <t>7024515</t>
         </is>
       </c>
       <c r="B834" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Coreline RC132V infälld, 60x60</t>
+          <t>Interiörarmatur SlimBlend infälld</t>
         </is>
       </c>
       <c r="C834" s="5" t="inlineStr">
@@ -22914,12 +22993,12 @@
     <row r="835">
       <c r="A835" s="6" t="inlineStr">
         <is>
-          <t>7027241</t>
+          <t>7024516</t>
         </is>
       </c>
       <c r="B835" t="inlineStr">
         <is>
-          <t>Interiörarmatur Ledinaire All-in, 3K/4K</t>
+          <t>Interiörarmatur SlimBlend infälld</t>
         </is>
       </c>
       <c r="C835" t="inlineStr">
@@ -22934,12 +23013,12 @@
     <row r="836">
       <c r="A836" s="4" t="inlineStr">
         <is>
-          <t>7027242</t>
+          <t>7024517</t>
         </is>
       </c>
       <c r="B836" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Ledinaire All-in, 3K/4K</t>
+          <t>Interiörarmatur SlimBlend infälld</t>
         </is>
       </c>
       <c r="C836" s="5" t="inlineStr">
@@ -22954,12 +23033,12 @@
     <row r="837">
       <c r="A837" s="6" t="inlineStr">
         <is>
-          <t>7027245</t>
+          <t>7024518</t>
         </is>
       </c>
       <c r="B837" t="inlineStr">
         <is>
-          <t>Interiörarmatur Ledinaire All-in, 3K/4K</t>
+          <t>Interiörarmatur SlimBlend infälld</t>
         </is>
       </c>
       <c r="C837" t="inlineStr">
@@ -22974,7 +23053,7 @@
     <row r="838">
       <c r="A838" s="4" t="inlineStr">
         <is>
-          <t>7024515</t>
+          <t>7024519</t>
         </is>
       </c>
       <c r="B838" s="5" t="inlineStr">
@@ -22994,7 +23073,7 @@
     <row r="839">
       <c r="A839" s="6" t="inlineStr">
         <is>
-          <t>7024516</t>
+          <t>7024520</t>
         </is>
       </c>
       <c r="B839" t="inlineStr">
@@ -23014,7 +23093,7 @@
     <row r="840">
       <c r="A840" s="4" t="inlineStr">
         <is>
-          <t>7024517</t>
+          <t>7024521</t>
         </is>
       </c>
       <c r="B840" s="5" t="inlineStr">
@@ -23034,7 +23113,7 @@
     <row r="841">
       <c r="A841" s="6" t="inlineStr">
         <is>
-          <t>7024518</t>
+          <t>7024522</t>
         </is>
       </c>
       <c r="B841" t="inlineStr">
@@ -23054,7 +23133,7 @@
     <row r="842">
       <c r="A842" s="4" t="inlineStr">
         <is>
-          <t>7024519</t>
+          <t>7024523</t>
         </is>
       </c>
       <c r="B842" s="5" t="inlineStr">
@@ -23074,7 +23153,7 @@
     <row r="843">
       <c r="A843" s="6" t="inlineStr">
         <is>
-          <t>7024520</t>
+          <t>7024524</t>
         </is>
       </c>
       <c r="B843" t="inlineStr">
@@ -23094,7 +23173,7 @@
     <row r="844">
       <c r="A844" s="4" t="inlineStr">
         <is>
-          <t>7024521</t>
+          <t>7024525</t>
         </is>
       </c>
       <c r="B844" s="5" t="inlineStr">
@@ -23114,12 +23193,12 @@
     <row r="845">
       <c r="A845" s="6" t="inlineStr">
         <is>
-          <t>7024522</t>
+          <t>7024527</t>
         </is>
       </c>
       <c r="B845" t="inlineStr">
         <is>
-          <t>Interiörarmatur SlimBlend infälld</t>
+          <t>Interiörarmatur TrueLine infälld</t>
         </is>
       </c>
       <c r="C845" t="inlineStr">
@@ -23134,12 +23213,12 @@
     <row r="846">
       <c r="A846" s="4" t="inlineStr">
         <is>
-          <t>7024523</t>
+          <t>7024528</t>
         </is>
       </c>
       <c r="B846" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur SlimBlend infälld</t>
+          <t>Interiörarmatur TrueLine infälld</t>
         </is>
       </c>
       <c r="C846" s="5" t="inlineStr">
@@ -23154,12 +23233,12 @@
     <row r="847">
       <c r="A847" s="6" t="inlineStr">
         <is>
-          <t>7024524</t>
+          <t>7024529</t>
         </is>
       </c>
       <c r="B847" t="inlineStr">
         <is>
-          <t>Interiörarmatur SlimBlend infälld</t>
+          <t>Interiörarmatur TrueLine infälld</t>
         </is>
       </c>
       <c r="C847" t="inlineStr">
@@ -23174,12 +23253,12 @@
     <row r="848">
       <c r="A848" s="4" t="inlineStr">
         <is>
-          <t>7024525</t>
+          <t>7024530</t>
         </is>
       </c>
       <c r="B848" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur SlimBlend infälld</t>
+          <t>Interiörarmatur TrueLine infälld</t>
         </is>
       </c>
       <c r="C848" s="5" t="inlineStr">
@@ -23194,7 +23273,7 @@
     <row r="849">
       <c r="A849" s="6" t="inlineStr">
         <is>
-          <t>7024527</t>
+          <t>7024531</t>
         </is>
       </c>
       <c r="B849" t="inlineStr">
@@ -23214,7 +23293,7 @@
     <row r="850">
       <c r="A850" s="4" t="inlineStr">
         <is>
-          <t>7024528</t>
+          <t>7024532</t>
         </is>
       </c>
       <c r="B850" s="5" t="inlineStr">
@@ -23234,7 +23313,7 @@
     <row r="851">
       <c r="A851" s="6" t="inlineStr">
         <is>
-          <t>7024529</t>
+          <t>7024533</t>
         </is>
       </c>
       <c r="B851" t="inlineStr">
@@ -23254,7 +23333,7 @@
     <row r="852">
       <c r="A852" s="4" t="inlineStr">
         <is>
-          <t>7024530</t>
+          <t>7024534</t>
         </is>
       </c>
       <c r="B852" s="5" t="inlineStr">
@@ -23274,17 +23353,17 @@
     <row r="853">
       <c r="A853" s="6" t="inlineStr">
         <is>
-          <t>7024531</t>
+          <t>7015063</t>
         </is>
       </c>
       <c r="B853" t="inlineStr">
         <is>
-          <t>Interiörarmatur TrueLine infälld</t>
+          <t>Infälld interörarmatur LED Sence Round</t>
         </is>
       </c>
       <c r="C853" t="inlineStr">
         <is>
-          <t>Philips</t>
+          <t>SG Armaturen</t>
         </is>
       </c>
       <c r="D853" s="6" t="n">
@@ -23294,17 +23373,17 @@
     <row r="854">
       <c r="A854" s="4" t="inlineStr">
         <is>
-          <t>7024532</t>
+          <t>7015064</t>
         </is>
       </c>
       <c r="B854" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur TrueLine infälld</t>
+          <t>Infälld interörarmatur LED Sence Round</t>
         </is>
       </c>
       <c r="C854" s="5" t="inlineStr">
         <is>
-          <t>Philips</t>
+          <t>SG Armaturen</t>
         </is>
       </c>
       <c r="D854" s="4" t="n">
@@ -23314,17 +23393,17 @@
     <row r="855">
       <c r="A855" s="6" t="inlineStr">
         <is>
-          <t>7024533</t>
+          <t>7016290</t>
         </is>
       </c>
       <c r="B855" t="inlineStr">
         <is>
-          <t>Interiörarmatur TrueLine infälld</t>
+          <t>Infälld interörarmatur LED Sence Round</t>
         </is>
       </c>
       <c r="C855" t="inlineStr">
         <is>
-          <t>Philips</t>
+          <t>SG Armaturen</t>
         </is>
       </c>
       <c r="D855" s="6" t="n">
@@ -23334,17 +23413,17 @@
     <row r="856">
       <c r="A856" s="4" t="inlineStr">
         <is>
-          <t>7024534</t>
+          <t>7015271</t>
         </is>
       </c>
       <c r="B856" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur TrueLine infälld</t>
+          <t>Infälld interörarmatur LED Sence Round</t>
         </is>
       </c>
       <c r="C856" s="5" t="inlineStr">
         <is>
-          <t>Philips</t>
+          <t>SG Armaturen</t>
         </is>
       </c>
       <c r="D856" s="4" t="n">
@@ -23354,7 +23433,7 @@
     <row r="857">
       <c r="A857" s="6" t="inlineStr">
         <is>
-          <t>7015063</t>
+          <t>7015272</t>
         </is>
       </c>
       <c r="B857" t="inlineStr">
@@ -23374,7 +23453,7 @@
     <row r="858">
       <c r="A858" s="4" t="inlineStr">
         <is>
-          <t>7015064</t>
+          <t>7016291E</t>
         </is>
       </c>
       <c r="B858" s="5" t="inlineStr">
@@ -23394,7 +23473,7 @@
     <row r="859">
       <c r="A859" s="6" t="inlineStr">
         <is>
-          <t>7016290</t>
+          <t>7015065</t>
         </is>
       </c>
       <c r="B859" t="inlineStr">
@@ -23414,7 +23493,7 @@
     <row r="860">
       <c r="A860" s="4" t="inlineStr">
         <is>
-          <t>7015271</t>
+          <t>7015066</t>
         </is>
       </c>
       <c r="B860" s="5" t="inlineStr">
@@ -23434,7 +23513,7 @@
     <row r="861">
       <c r="A861" s="6" t="inlineStr">
         <is>
-          <t>7015272</t>
+          <t>7016292</t>
         </is>
       </c>
       <c r="B861" t="inlineStr">
@@ -23454,7 +23533,7 @@
     <row r="862">
       <c r="A862" s="4" t="inlineStr">
         <is>
-          <t>7016291E</t>
+          <t>7015273</t>
         </is>
       </c>
       <c r="B862" s="5" t="inlineStr">
@@ -23474,7 +23553,7 @@
     <row r="863">
       <c r="A863" s="6" t="inlineStr">
         <is>
-          <t>7015065</t>
+          <t>7015274</t>
         </is>
       </c>
       <c r="B863" t="inlineStr">
@@ -23494,7 +23573,7 @@
     <row r="864">
       <c r="A864" s="4" t="inlineStr">
         <is>
-          <t>7015066</t>
+          <t>7016293</t>
         </is>
       </c>
       <c r="B864" s="5" t="inlineStr">
@@ -23514,7 +23593,7 @@
     <row r="865">
       <c r="A865" s="6" t="inlineStr">
         <is>
-          <t>7016292</t>
+          <t>7015067</t>
         </is>
       </c>
       <c r="B865" t="inlineStr">
@@ -23534,7 +23613,7 @@
     <row r="866">
       <c r="A866" s="4" t="inlineStr">
         <is>
-          <t>7015273</t>
+          <t>7015068</t>
         </is>
       </c>
       <c r="B866" s="5" t="inlineStr">
@@ -23554,7 +23633,7 @@
     <row r="867">
       <c r="A867" s="6" t="inlineStr">
         <is>
-          <t>7015274</t>
+          <t>7015069</t>
         </is>
       </c>
       <c r="B867" t="inlineStr">
@@ -23574,7 +23653,7 @@
     <row r="868">
       <c r="A868" s="4" t="inlineStr">
         <is>
-          <t>7016293</t>
+          <t>7015275</t>
         </is>
       </c>
       <c r="B868" s="5" t="inlineStr">
@@ -23594,7 +23673,7 @@
     <row r="869">
       <c r="A869" s="6" t="inlineStr">
         <is>
-          <t>7015067</t>
+          <t>7015276</t>
         </is>
       </c>
       <c r="B869" t="inlineStr">
@@ -23614,7 +23693,7 @@
     <row r="870">
       <c r="A870" s="4" t="inlineStr">
         <is>
-          <t>7015068</t>
+          <t>7015277</t>
         </is>
       </c>
       <c r="B870" s="5" t="inlineStr">
@@ -23634,7 +23713,7 @@
     <row r="871">
       <c r="A871" s="6" t="inlineStr">
         <is>
-          <t>7015069</t>
+          <t>7015070</t>
         </is>
       </c>
       <c r="B871" t="inlineStr">
@@ -23654,7 +23733,7 @@
     <row r="872">
       <c r="A872" s="4" t="inlineStr">
         <is>
-          <t>7015275</t>
+          <t>7015071</t>
         </is>
       </c>
       <c r="B872" s="5" t="inlineStr">
@@ -23674,7 +23753,7 @@
     <row r="873">
       <c r="A873" s="6" t="inlineStr">
         <is>
-          <t>7015276</t>
+          <t>7015278</t>
         </is>
       </c>
       <c r="B873" t="inlineStr">
@@ -23694,7 +23773,7 @@
     <row r="874">
       <c r="A874" s="4" t="inlineStr">
         <is>
-          <t>7015277</t>
+          <t>7015279</t>
         </is>
       </c>
       <c r="B874" s="5" t="inlineStr">
@@ -23714,7 +23793,7 @@
     <row r="875">
       <c r="A875" s="6" t="inlineStr">
         <is>
-          <t>7015070</t>
+          <t>7028329</t>
         </is>
       </c>
       <c r="B875" t="inlineStr">
@@ -23734,7 +23813,7 @@
     <row r="876">
       <c r="A876" s="4" t="inlineStr">
         <is>
-          <t>7015071</t>
+          <t>7028330</t>
         </is>
       </c>
       <c r="B876" s="5" t="inlineStr">
@@ -23754,7 +23833,7 @@
     <row r="877">
       <c r="A877" s="6" t="inlineStr">
         <is>
-          <t>7015278</t>
+          <t>7028331</t>
         </is>
       </c>
       <c r="B877" t="inlineStr">
@@ -23774,7 +23853,7 @@
     <row r="878">
       <c r="A878" s="4" t="inlineStr">
         <is>
-          <t>7015279</t>
+          <t>7028332</t>
         </is>
       </c>
       <c r="B878" s="5" t="inlineStr">
@@ -23794,12 +23873,12 @@
     <row r="879">
       <c r="A879" s="6" t="inlineStr">
         <is>
-          <t>7028329</t>
+          <t>7018001</t>
         </is>
       </c>
       <c r="B879" t="inlineStr">
         <is>
-          <t>Infälld interörarmatur LED Sence Round</t>
+          <t>Interiörarmatur LED Sense 300x1200</t>
         </is>
       </c>
       <c r="C879" t="inlineStr">
@@ -23814,12 +23893,12 @@
     <row r="880">
       <c r="A880" s="4" t="inlineStr">
         <is>
-          <t>7028330</t>
+          <t>7018002</t>
         </is>
       </c>
       <c r="B880" s="5" t="inlineStr">
         <is>
-          <t>Infälld interörarmatur LED Sence Round</t>
+          <t>Interiörarmatur LED Sense 300x1200</t>
         </is>
       </c>
       <c r="C880" s="5" t="inlineStr">
@@ -23834,12 +23913,12 @@
     <row r="881">
       <c r="A881" s="6" t="inlineStr">
         <is>
-          <t>7028331</t>
+          <t>7015072</t>
         </is>
       </c>
       <c r="B881" t="inlineStr">
         <is>
-          <t>Infälld interörarmatur LED Sence Round</t>
+          <t>Interiörarmatur LED Sense 300x300</t>
         </is>
       </c>
       <c r="C881" t="inlineStr">
@@ -23854,12 +23933,12 @@
     <row r="882">
       <c r="A882" s="4" t="inlineStr">
         <is>
-          <t>7028332</t>
+          <t>7015280</t>
         </is>
       </c>
       <c r="B882" s="5" t="inlineStr">
         <is>
-          <t>Infälld interörarmatur LED Sence Round</t>
+          <t>Interiörarmatur LED Sense 300x300</t>
         </is>
       </c>
       <c r="C882" s="5" t="inlineStr">
@@ -23874,12 +23953,12 @@
     <row r="883">
       <c r="A883" s="6" t="inlineStr">
         <is>
-          <t>7018001</t>
+          <t>7016295</t>
         </is>
       </c>
       <c r="B883" t="inlineStr">
         <is>
-          <t>Interiörarmatur LED Sense 300x1200</t>
+          <t>Interiörarmatur LED Sense 300x300</t>
         </is>
       </c>
       <c r="C883" t="inlineStr">
@@ -23894,12 +23973,12 @@
     <row r="884">
       <c r="A884" s="4" t="inlineStr">
         <is>
-          <t>7018002</t>
+          <t>7017938</t>
         </is>
       </c>
       <c r="B884" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur LED Sense 300x1200</t>
+          <t>Interiörarmatur LED Sense 600x600</t>
         </is>
       </c>
       <c r="C884" s="5" t="inlineStr">
@@ -23908,18 +23987,18 @@
         </is>
       </c>
       <c r="D884" s="4" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
     </row>
     <row r="885">
       <c r="A885" s="6" t="inlineStr">
         <is>
-          <t>7015072</t>
+          <t>7017939</t>
         </is>
       </c>
       <c r="B885" t="inlineStr">
         <is>
-          <t>Interiörarmatur LED Sense 300x300</t>
+          <t>Interiörarmatur LED Sense 600x600</t>
         </is>
       </c>
       <c r="C885" t="inlineStr">
@@ -23928,18 +24007,18 @@
         </is>
       </c>
       <c r="D885" s="6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="886">
       <c r="A886" s="4" t="inlineStr">
         <is>
-          <t>7015280</t>
+          <t>7019572</t>
         </is>
       </c>
       <c r="B886" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur LED Sense 300x300</t>
+          <t>Interiörarmatur Sense Basic</t>
         </is>
       </c>
       <c r="C886" s="5" t="inlineStr">
@@ -23954,12 +24033,12 @@
     <row r="887">
       <c r="A887" s="6" t="inlineStr">
         <is>
-          <t>7016295</t>
+          <t>7019573</t>
         </is>
       </c>
       <c r="B887" t="inlineStr">
         <is>
-          <t>Interiörarmatur LED Sense 300x300</t>
+          <t>Interiörarmatur Sense Basic</t>
         </is>
       </c>
       <c r="C887" t="inlineStr">
@@ -23974,12 +24053,12 @@
     <row r="888">
       <c r="A888" s="4" t="inlineStr">
         <is>
-          <t>7017938</t>
+          <t>7028217</t>
         </is>
       </c>
       <c r="B888" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur LED Sense 600x600</t>
+          <t>Interiörarmatur Sense Basic Connect</t>
         </is>
       </c>
       <c r="C888" s="5" t="inlineStr">
@@ -23988,18 +24067,18 @@
         </is>
       </c>
       <c r="D888" s="4" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
     </row>
     <row r="889">
       <c r="A889" s="6" t="inlineStr">
         <is>
-          <t>7017939</t>
+          <t>7028218</t>
         </is>
       </c>
       <c r="B889" t="inlineStr">
         <is>
-          <t>Interiörarmatur LED Sense 600x600</t>
+          <t>Interiörarmatur Sense Basic Connect</t>
         </is>
       </c>
       <c r="C889" t="inlineStr">
@@ -24008,18 +24087,18 @@
         </is>
       </c>
       <c r="D889" s="6" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="890">
       <c r="A890" s="4" t="inlineStr">
         <is>
-          <t>7019572</t>
+          <t>7028197</t>
         </is>
       </c>
       <c r="B890" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Basic</t>
+          <t>Interiörarmatur Sense Basic gen2</t>
         </is>
       </c>
       <c r="C890" s="5" t="inlineStr">
@@ -24034,12 +24113,12 @@
     <row r="891">
       <c r="A891" s="6" t="inlineStr">
         <is>
-          <t>7019573</t>
+          <t>7028033</t>
         </is>
       </c>
       <c r="B891" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Basic</t>
+          <t>Interiörarmatur Sense Basic gen2</t>
         </is>
       </c>
       <c r="C891" t="inlineStr">
@@ -24048,18 +24127,18 @@
         </is>
       </c>
       <c r="D891" s="6" t="n">
-        <v>0</v>
+        <v>296</v>
       </c>
     </row>
     <row r="892">
       <c r="A892" s="4" t="inlineStr">
         <is>
-          <t>7028217</t>
+          <t>7028035</t>
         </is>
       </c>
       <c r="B892" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Basic Connect</t>
+          <t>Interiörarmatur Sense Basic gen2</t>
         </is>
       </c>
       <c r="C892" s="5" t="inlineStr">
@@ -24068,18 +24147,18 @@
         </is>
       </c>
       <c r="D892" s="4" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="893">
       <c r="A893" s="6" t="inlineStr">
         <is>
-          <t>7028218</t>
+          <t>7028034</t>
         </is>
       </c>
       <c r="B893" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Basic Connect</t>
+          <t>Interiörarmatur Sense Basic gen2</t>
         </is>
       </c>
       <c r="C893" t="inlineStr">
@@ -24088,13 +24167,13 @@
         </is>
       </c>
       <c r="D893" s="6" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
     </row>
     <row r="894">
       <c r="A894" s="4" t="inlineStr">
         <is>
-          <t>7028197</t>
+          <t>7028044</t>
         </is>
       </c>
       <c r="B894" s="5" t="inlineStr">
@@ -24114,12 +24193,12 @@
     <row r="895">
       <c r="A895" s="6" t="inlineStr">
         <is>
-          <t>7028033</t>
+          <t>7019665</t>
         </is>
       </c>
       <c r="B895" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Basic gen2</t>
+          <t>Interiörarmatur Sense IP65</t>
         </is>
       </c>
       <c r="C895" t="inlineStr">
@@ -24128,18 +24207,18 @@
         </is>
       </c>
       <c r="D895" s="6" t="n">
-        <v>290</v>
+        <v>0</v>
       </c>
     </row>
     <row r="896">
       <c r="A896" s="4" t="inlineStr">
         <is>
-          <t>7028035</t>
+          <t>7019659</t>
         </is>
       </c>
       <c r="B896" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Basic gen2</t>
+          <t>Interiörarmatur Sense IP65</t>
         </is>
       </c>
       <c r="C896" s="5" t="inlineStr">
@@ -24148,18 +24227,18 @@
         </is>
       </c>
       <c r="D896" s="4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="897">
       <c r="A897" s="6" t="inlineStr">
         <is>
-          <t>7028034</t>
+          <t>7021278</t>
         </is>
       </c>
       <c r="B897" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Basic gen2</t>
+          <t>Interiörarmatur Sense IP65 Eco</t>
         </is>
       </c>
       <c r="C897" t="inlineStr">
@@ -24168,18 +24247,18 @@
         </is>
       </c>
       <c r="D897" s="6" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
     </row>
     <row r="898">
       <c r="A898" s="4" t="inlineStr">
         <is>
-          <t>7028044</t>
+          <t>7021279</t>
         </is>
       </c>
       <c r="B898" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Basic gen2</t>
+          <t>Interiörarmatur Sense IP65 Eco</t>
         </is>
       </c>
       <c r="C898" s="5" t="inlineStr">
@@ -24194,12 +24273,12 @@
     <row r="899">
       <c r="A899" s="6" t="inlineStr">
         <is>
-          <t>7019665</t>
+          <t>7028952</t>
         </is>
       </c>
       <c r="B899" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense IP65</t>
+          <t>Interiörarmatur Sense IP65 Eco</t>
         </is>
       </c>
       <c r="C899" t="inlineStr">
@@ -24214,12 +24293,12 @@
     <row r="900">
       <c r="A900" s="4" t="inlineStr">
         <is>
-          <t>7019659</t>
+          <t>7028953</t>
         </is>
       </c>
       <c r="B900" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense IP65</t>
+          <t>Interiörarmatur Sense IP65 Eco</t>
         </is>
       </c>
       <c r="C900" s="5" t="inlineStr">
@@ -24234,12 +24313,12 @@
     <row r="901">
       <c r="A901" s="6" t="inlineStr">
         <is>
-          <t>7021278</t>
+          <t>7024921</t>
         </is>
       </c>
       <c r="B901" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense IP65 Eco</t>
+          <t>Interiörarmatur Sense Line</t>
         </is>
       </c>
       <c r="C901" t="inlineStr">
@@ -24254,12 +24333,12 @@
     <row r="902">
       <c r="A902" s="4" t="inlineStr">
         <is>
-          <t>7021279</t>
+          <t>7024922</t>
         </is>
       </c>
       <c r="B902" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense IP65 Eco</t>
+          <t>Interiörarmatur Sense Line</t>
         </is>
       </c>
       <c r="C902" s="5" t="inlineStr">
@@ -24274,12 +24353,12 @@
     <row r="903">
       <c r="A903" s="6" t="inlineStr">
         <is>
-          <t>7028952</t>
+          <t>7024923</t>
         </is>
       </c>
       <c r="B903" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense IP65 Eco</t>
+          <t>Interiörarmatur Sense Line</t>
         </is>
       </c>
       <c r="C903" t="inlineStr">
@@ -24294,12 +24373,12 @@
     <row r="904">
       <c r="A904" s="4" t="inlineStr">
         <is>
-          <t>7028953</t>
+          <t>7024924</t>
         </is>
       </c>
       <c r="B904" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense IP65 Eco</t>
+          <t>Interiörarmatur Sense Line</t>
         </is>
       </c>
       <c r="C904" s="5" t="inlineStr">
@@ -24314,7 +24393,7 @@
     <row r="905">
       <c r="A905" s="6" t="inlineStr">
         <is>
-          <t>7024921</t>
+          <t>7024925</t>
         </is>
       </c>
       <c r="B905" t="inlineStr">
@@ -24334,7 +24413,7 @@
     <row r="906">
       <c r="A906" s="4" t="inlineStr">
         <is>
-          <t>7024922</t>
+          <t>7024926</t>
         </is>
       </c>
       <c r="B906" s="5" t="inlineStr">
@@ -24354,7 +24433,7 @@
     <row r="907">
       <c r="A907" s="6" t="inlineStr">
         <is>
-          <t>7024923</t>
+          <t>7024927</t>
         </is>
       </c>
       <c r="B907" t="inlineStr">
@@ -24374,7 +24453,7 @@
     <row r="908">
       <c r="A908" s="4" t="inlineStr">
         <is>
-          <t>7024924</t>
+          <t>7024928</t>
         </is>
       </c>
       <c r="B908" s="5" t="inlineStr">
@@ -24394,12 +24473,12 @@
     <row r="909">
       <c r="A909" s="6" t="inlineStr">
         <is>
-          <t>7024925</t>
+          <t>7017941</t>
         </is>
       </c>
       <c r="B909" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Line</t>
+          <t>Interiörarmatur Sense Opalprismatisk</t>
         </is>
       </c>
       <c r="C909" t="inlineStr">
@@ -24414,12 +24493,12 @@
     <row r="910">
       <c r="A910" s="4" t="inlineStr">
         <is>
-          <t>7024926</t>
+          <t>7017942</t>
         </is>
       </c>
       <c r="B910" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Line</t>
+          <t>Interiörarmatur Sense Opalprismatisk</t>
         </is>
       </c>
       <c r="C910" s="5" t="inlineStr">
@@ -24434,12 +24513,12 @@
     <row r="911">
       <c r="A911" s="6" t="inlineStr">
         <is>
-          <t>7024927</t>
+          <t>7024625</t>
         </is>
       </c>
       <c r="B911" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Line</t>
+          <t>Interiörarmatur Sense Opalprismatisk</t>
         </is>
       </c>
       <c r="C911" t="inlineStr">
@@ -24454,12 +24533,12 @@
     <row r="912">
       <c r="A912" s="4" t="inlineStr">
         <is>
-          <t>7024928</t>
+          <t>7024626</t>
         </is>
       </c>
       <c r="B912" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Line</t>
+          <t>Interiörarmatur Sense Opalprismatisk</t>
         </is>
       </c>
       <c r="C912" s="5" t="inlineStr">
@@ -24474,7 +24553,7 @@
     <row r="913">
       <c r="A913" s="6" t="inlineStr">
         <is>
-          <t>7017941</t>
+          <t>7024627</t>
         </is>
       </c>
       <c r="B913" t="inlineStr">
@@ -24488,13 +24567,13 @@
         </is>
       </c>
       <c r="D913" s="6" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
     </row>
     <row r="914">
       <c r="A914" s="4" t="inlineStr">
         <is>
-          <t>7017942</t>
+          <t>7024628</t>
         </is>
       </c>
       <c r="B914" s="5" t="inlineStr">
@@ -24514,7 +24593,7 @@
     <row r="915">
       <c r="A915" s="6" t="inlineStr">
         <is>
-          <t>7024625</t>
+          <t>7024633</t>
         </is>
       </c>
       <c r="B915" t="inlineStr">
@@ -24534,7 +24613,7 @@
     <row r="916">
       <c r="A916" s="4" t="inlineStr">
         <is>
-          <t>7024626</t>
+          <t>7024634</t>
         </is>
       </c>
       <c r="B916" s="5" t="inlineStr">
@@ -24554,12 +24633,12 @@
     <row r="917">
       <c r="A917" s="6" t="inlineStr">
         <is>
-          <t>7024627</t>
+          <t>7019797</t>
         </is>
       </c>
       <c r="B917" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Opalprismatisk</t>
+          <t>Interiörarmatur Sense Pir</t>
         </is>
       </c>
       <c r="C917" t="inlineStr">
@@ -24568,18 +24647,18 @@
         </is>
       </c>
       <c r="D917" s="6" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
     </row>
     <row r="918">
       <c r="A918" s="4" t="inlineStr">
         <is>
-          <t>7024628</t>
+          <t>7019798</t>
         </is>
       </c>
       <c r="B918" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Opalprismatisk</t>
+          <t>Interiörarmatur Sense Pir</t>
         </is>
       </c>
       <c r="C918" s="5" t="inlineStr">
@@ -24594,12 +24673,12 @@
     <row r="919">
       <c r="A919" s="6" t="inlineStr">
         <is>
-          <t>7024633</t>
+          <t>7024635</t>
         </is>
       </c>
       <c r="B919" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Opalprismatisk</t>
+          <t>Interiörarmatur Sense Pir</t>
         </is>
       </c>
       <c r="C919" t="inlineStr">
@@ -24608,18 +24687,18 @@
         </is>
       </c>
       <c r="D919" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="920">
       <c r="A920" s="4" t="inlineStr">
         <is>
-          <t>7024634</t>
+          <t>7024636</t>
         </is>
       </c>
       <c r="B920" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Opalprismatisk</t>
+          <t>Interiörarmatur Sense Pir</t>
         </is>
       </c>
       <c r="C920" s="5" t="inlineStr">
@@ -24634,12 +24713,12 @@
     <row r="921">
       <c r="A921" s="6" t="inlineStr">
         <is>
-          <t>7019797</t>
+          <t>7024631</t>
         </is>
       </c>
       <c r="B921" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Pir</t>
+          <t>Interiörarmatur Sense Pro</t>
         </is>
       </c>
       <c r="C921" t="inlineStr">
@@ -24654,12 +24733,12 @@
     <row r="922">
       <c r="A922" s="4" t="inlineStr">
         <is>
-          <t>7019798</t>
+          <t>7024632</t>
         </is>
       </c>
       <c r="B922" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Pir</t>
+          <t>Interiörarmatur Sense Pro</t>
         </is>
       </c>
       <c r="C922" s="5" t="inlineStr">
@@ -24674,12 +24753,12 @@
     <row r="923">
       <c r="A923" s="6" t="inlineStr">
         <is>
-          <t>7024635</t>
+          <t>7028741</t>
         </is>
       </c>
       <c r="B923" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Pir</t>
+          <t>Interiörarmatur Sense Pro</t>
         </is>
       </c>
       <c r="C923" t="inlineStr">
@@ -24688,18 +24767,18 @@
         </is>
       </c>
       <c r="D923" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="924">
       <c r="A924" s="4" t="inlineStr">
         <is>
-          <t>7024636</t>
+          <t>7026638</t>
         </is>
       </c>
       <c r="B924" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Pir</t>
+          <t>Interiörarmatur Sense Pro Connect</t>
         </is>
       </c>
       <c r="C924" s="5" t="inlineStr">
@@ -24714,12 +24793,12 @@
     <row r="925">
       <c r="A925" s="6" t="inlineStr">
         <is>
-          <t>7024631</t>
+          <t>7026639</t>
         </is>
       </c>
       <c r="B925" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Pro</t>
+          <t>Interiörarmatur Sense Pro Connect</t>
         </is>
       </c>
       <c r="C925" t="inlineStr">
@@ -24734,12 +24813,12 @@
     <row r="926">
       <c r="A926" s="4" t="inlineStr">
         <is>
-          <t>7024632</t>
+          <t>7026640</t>
         </is>
       </c>
       <c r="B926" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Pro</t>
+          <t>Interiörarmatur Sense Pro Connect</t>
         </is>
       </c>
       <c r="C926" s="5" t="inlineStr">
@@ -24754,12 +24833,12 @@
     <row r="927">
       <c r="A927" s="6" t="inlineStr">
         <is>
-          <t>7028741</t>
+          <t>7026641</t>
         </is>
       </c>
       <c r="B927" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Pro</t>
+          <t>Interiörarmatur Sense Pro Connect</t>
         </is>
       </c>
       <c r="C927" t="inlineStr">
@@ -24774,7 +24853,7 @@
     <row r="928">
       <c r="A928" s="4" t="inlineStr">
         <is>
-          <t>7026638</t>
+          <t>7028954</t>
         </is>
       </c>
       <c r="B928" s="5" t="inlineStr">
@@ -24794,7 +24873,7 @@
     <row r="929">
       <c r="A929" s="6" t="inlineStr">
         <is>
-          <t>7026639</t>
+          <t>7028955</t>
         </is>
       </c>
       <c r="B929" t="inlineStr">
@@ -24814,12 +24893,12 @@
     <row r="930">
       <c r="A930" s="4" t="inlineStr">
         <is>
-          <t>7026640</t>
+          <t>7024629</t>
         </is>
       </c>
       <c r="B930" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Pro Connect</t>
+          <t>Interiörarmatur Sense Pro Round</t>
         </is>
       </c>
       <c r="C930" s="5" t="inlineStr">
@@ -24834,12 +24913,12 @@
     <row r="931">
       <c r="A931" s="6" t="inlineStr">
         <is>
-          <t>7026641</t>
+          <t>7024630</t>
         </is>
       </c>
       <c r="B931" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Pro Connect</t>
+          <t>Interiörarmatur Sense Pro Round</t>
         </is>
       </c>
       <c r="C931" t="inlineStr">
@@ -24854,12 +24933,12 @@
     <row r="932">
       <c r="A932" s="4" t="inlineStr">
         <is>
-          <t>7028954</t>
+          <t>7026783</t>
         </is>
       </c>
       <c r="B932" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Pro Connect</t>
+          <t>Interiörarmatur Sense Pro X</t>
         </is>
       </c>
       <c r="C932" s="5" t="inlineStr">
@@ -24874,12 +24953,12 @@
     <row r="933">
       <c r="A933" s="6" t="inlineStr">
         <is>
-          <t>7028955</t>
+          <t>7026784</t>
         </is>
       </c>
       <c r="B933" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Pro Connect</t>
+          <t>Interiörarmatur Sense Pro X</t>
         </is>
       </c>
       <c r="C933" t="inlineStr">
@@ -24894,12 +24973,12 @@
     <row r="934">
       <c r="A934" s="4" t="inlineStr">
         <is>
-          <t>7024629</t>
+          <t>7028122</t>
         </is>
       </c>
       <c r="B934" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Pro Round</t>
+          <t>Interiörarmatur Sense Pro X</t>
         </is>
       </c>
       <c r="C934" s="5" t="inlineStr">
@@ -24914,12 +24993,12 @@
     <row r="935">
       <c r="A935" s="6" t="inlineStr">
         <is>
-          <t>7024630</t>
+          <t>7028123</t>
         </is>
       </c>
       <c r="B935" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Pro Round</t>
+          <t>Interiörarmatur Sense Pro X</t>
         </is>
       </c>
       <c r="C935" t="inlineStr">
@@ -24934,12 +25013,12 @@
     <row r="936">
       <c r="A936" s="4" t="inlineStr">
         <is>
-          <t>7026783</t>
+          <t>7018057</t>
         </is>
       </c>
       <c r="B936" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Pro X</t>
+          <t>Interiörarmatur Sense TW</t>
         </is>
       </c>
       <c r="C936" s="5" t="inlineStr">
@@ -24954,12 +25033,12 @@
     <row r="937">
       <c r="A937" s="6" t="inlineStr">
         <is>
-          <t>7026784</t>
+          <t>7018056</t>
         </is>
       </c>
       <c r="B937" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Pro X</t>
+          <t>Interiörarmatur Sense TW</t>
         </is>
       </c>
       <c r="C937" t="inlineStr">
@@ -24974,12 +25053,12 @@
     <row r="938">
       <c r="A938" s="4" t="inlineStr">
         <is>
-          <t>7028122</t>
+          <t>7016803</t>
         </is>
       </c>
       <c r="B938" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Pro X</t>
+          <t>Interiörarmatur Sense TW rund</t>
         </is>
       </c>
       <c r="C938" s="5" t="inlineStr">
@@ -24994,12 +25073,12 @@
     <row r="939">
       <c r="A939" s="6" t="inlineStr">
         <is>
-          <t>7028123</t>
+          <t>7016818</t>
         </is>
       </c>
       <c r="B939" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Pro X</t>
+          <t>Interiörarmatur Sense TW rund</t>
         </is>
       </c>
       <c r="C939" t="inlineStr">
@@ -25014,12 +25093,12 @@
     <row r="940">
       <c r="A940" s="4" t="inlineStr">
         <is>
-          <t>7018057</t>
+          <t>7016819</t>
         </is>
       </c>
       <c r="B940" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense TW</t>
+          <t>Interiörarmatur Sense TW rund</t>
         </is>
       </c>
       <c r="C940" s="5" t="inlineStr">
@@ -25034,12 +25113,12 @@
     <row r="941">
       <c r="A941" s="6" t="inlineStr">
         <is>
-          <t>7018056</t>
+          <t>7016820</t>
         </is>
       </c>
       <c r="B941" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense TW</t>
+          <t>Interiörarmatur Sense TW rund</t>
         </is>
       </c>
       <c r="C941" t="inlineStr">
@@ -25054,7 +25133,7 @@
     <row r="942">
       <c r="A942" s="4" t="inlineStr">
         <is>
-          <t>7016803</t>
+          <t>7016822</t>
         </is>
       </c>
       <c r="B942" s="5" t="inlineStr">
@@ -25074,7 +25153,7 @@
     <row r="943">
       <c r="A943" s="6" t="inlineStr">
         <is>
-          <t>7016818</t>
+          <t>7016821</t>
         </is>
       </c>
       <c r="B943" t="inlineStr">
@@ -25094,12 +25173,12 @@
     <row r="944">
       <c r="A944" s="4" t="inlineStr">
         <is>
-          <t>7016819</t>
+          <t>7028408</t>
         </is>
       </c>
       <c r="B944" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense TW rund</t>
+          <t>Interiörarmatur Sense Velios</t>
         </is>
       </c>
       <c r="C944" s="5" t="inlineStr">
@@ -25114,12 +25193,12 @@
     <row r="945">
       <c r="A945" s="6" t="inlineStr">
         <is>
-          <t>7016820</t>
+          <t>7028409</t>
         </is>
       </c>
       <c r="B945" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense TW rund</t>
+          <t>Interiörarmatur Sense Velios</t>
         </is>
       </c>
       <c r="C945" t="inlineStr">
@@ -25134,12 +25213,12 @@
     <row r="946">
       <c r="A946" s="4" t="inlineStr">
         <is>
-          <t>7016822</t>
+          <t>7028410</t>
         </is>
       </c>
       <c r="B946" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense TW rund</t>
+          <t>Interiörarmatur Sense Velios</t>
         </is>
       </c>
       <c r="C946" s="5" t="inlineStr">
@@ -25154,12 +25233,12 @@
     <row r="947">
       <c r="A947" s="6" t="inlineStr">
         <is>
-          <t>7016821</t>
+          <t>7028411</t>
         </is>
       </c>
       <c r="B947" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense TW rund</t>
+          <t>Interiörarmatur Sense Velios</t>
         </is>
       </c>
       <c r="C947" t="inlineStr">
@@ -25174,7 +25253,7 @@
     <row r="948">
       <c r="A948" s="4" t="inlineStr">
         <is>
-          <t>7028408</t>
+          <t>7028412</t>
         </is>
       </c>
       <c r="B948" s="5" t="inlineStr">
@@ -25194,7 +25273,7 @@
     <row r="949">
       <c r="A949" s="6" t="inlineStr">
         <is>
-          <t>7028409</t>
+          <t>7028413</t>
         </is>
       </c>
       <c r="B949" t="inlineStr">
@@ -25214,7 +25293,7 @@
     <row r="950">
       <c r="A950" s="4" t="inlineStr">
         <is>
-          <t>7028410</t>
+          <t>7028414</t>
         </is>
       </c>
       <c r="B950" s="5" t="inlineStr">
@@ -25234,7 +25313,7 @@
     <row r="951">
       <c r="A951" s="6" t="inlineStr">
         <is>
-          <t>7028411</t>
+          <t>7028415</t>
         </is>
       </c>
       <c r="B951" t="inlineStr">
@@ -25254,17 +25333,17 @@
     <row r="952">
       <c r="A952" s="4" t="inlineStr">
         <is>
-          <t>7028412</t>
+          <t>7026760</t>
         </is>
       </c>
       <c r="B952" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Velios</t>
+          <t>Interiörarmatur Apollon 21</t>
         </is>
       </c>
       <c r="C952" s="5" t="inlineStr">
         <is>
-          <t>SG Armaturen</t>
+          <t>Siteco</t>
         </is>
       </c>
       <c r="D952" s="4" t="n">
@@ -25274,17 +25353,17 @@
     <row r="953">
       <c r="A953" s="6" t="inlineStr">
         <is>
-          <t>7028413</t>
+          <t>7027137</t>
         </is>
       </c>
       <c r="B953" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Velios</t>
+          <t>Interiörarmatur Apollon 21</t>
         </is>
       </c>
       <c r="C953" t="inlineStr">
         <is>
-          <t>SG Armaturen</t>
+          <t>Siteco</t>
         </is>
       </c>
       <c r="D953" s="6" t="n">
@@ -25294,17 +25373,17 @@
     <row r="954">
       <c r="A954" s="4" t="inlineStr">
         <is>
-          <t>7028414</t>
+          <t>7027138</t>
         </is>
       </c>
       <c r="B954" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Velios</t>
+          <t>Interiörarmatur Apollon 21</t>
         </is>
       </c>
       <c r="C954" s="5" t="inlineStr">
         <is>
-          <t>SG Armaturen</t>
+          <t>Siteco</t>
         </is>
       </c>
       <c r="D954" s="4" t="n">
@@ -25314,17 +25393,17 @@
     <row r="955">
       <c r="A955" s="6" t="inlineStr">
         <is>
-          <t>7028415</t>
+          <t>7027139</t>
         </is>
       </c>
       <c r="B955" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Velios</t>
+          <t>Interiörarmatur Apollon 21</t>
         </is>
       </c>
       <c r="C955" t="inlineStr">
         <is>
-          <t>SG Armaturen</t>
+          <t>Siteco</t>
         </is>
       </c>
       <c r="D955" s="6" t="n">
@@ -25334,7 +25413,7 @@
     <row r="956">
       <c r="A956" s="4" t="inlineStr">
         <is>
-          <t>7026760</t>
+          <t>7027140</t>
         </is>
       </c>
       <c r="B956" s="5" t="inlineStr">
@@ -25354,7 +25433,7 @@
     <row r="957">
       <c r="A957" s="6" t="inlineStr">
         <is>
-          <t>7027137</t>
+          <t>7027141</t>
         </is>
       </c>
       <c r="B957" t="inlineStr">
@@ -25374,7 +25453,7 @@
     <row r="958">
       <c r="A958" s="4" t="inlineStr">
         <is>
-          <t>7027138</t>
+          <t>7027142</t>
         </is>
       </c>
       <c r="B958" s="5" t="inlineStr">
@@ -25394,7 +25473,7 @@
     <row r="959">
       <c r="A959" s="6" t="inlineStr">
         <is>
-          <t>7027139</t>
+          <t>7027143</t>
         </is>
       </c>
       <c r="B959" t="inlineStr">
@@ -25414,7 +25493,7 @@
     <row r="960">
       <c r="A960" s="4" t="inlineStr">
         <is>
-          <t>7027140</t>
+          <t>7027144</t>
         </is>
       </c>
       <c r="B960" s="5" t="inlineStr">
@@ -25434,17 +25513,17 @@
     <row r="961">
       <c r="A961" s="6" t="inlineStr">
         <is>
-          <t>7027141</t>
+          <t>7077510</t>
         </is>
       </c>
       <c r="B961" t="inlineStr">
         <is>
-          <t>Interiörarmatur Apollon 21</t>
+          <t>Infälld interiörarmatur IQ Wave</t>
         </is>
       </c>
       <c r="C961" t="inlineStr">
         <is>
-          <t>Siteco</t>
+          <t>THORN</t>
         </is>
       </c>
       <c r="D961" s="6" t="n">
@@ -25454,17 +25533,17 @@
     <row r="962">
       <c r="A962" s="4" t="inlineStr">
         <is>
-          <t>7027142</t>
+          <t>7077516</t>
         </is>
       </c>
       <c r="B962" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Apollon 21</t>
+          <t>Infälld interiörarmatur IQ Wave</t>
         </is>
       </c>
       <c r="C962" s="5" t="inlineStr">
         <is>
-          <t>Siteco</t>
+          <t>THORN</t>
         </is>
       </c>
       <c r="D962" s="4" t="n">
@@ -25474,17 +25553,17 @@
     <row r="963">
       <c r="A963" s="6" t="inlineStr">
         <is>
-          <t>7027143</t>
+          <t>7077513</t>
         </is>
       </c>
       <c r="B963" t="inlineStr">
         <is>
-          <t>Interiörarmatur Apollon 21</t>
+          <t>Infälld interiörarmatur IQ Wave</t>
         </is>
       </c>
       <c r="C963" t="inlineStr">
         <is>
-          <t>Siteco</t>
+          <t>THORN</t>
         </is>
       </c>
       <c r="D963" s="6" t="n">
@@ -25494,17 +25573,17 @@
     <row r="964">
       <c r="A964" s="4" t="inlineStr">
         <is>
-          <t>7027144</t>
+          <t>7077517</t>
         </is>
       </c>
       <c r="B964" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Apollon 21</t>
+          <t>Infälld interiörarmatur IQ Wave</t>
         </is>
       </c>
       <c r="C964" s="5" t="inlineStr">
         <is>
-          <t>Siteco</t>
+          <t>THORN</t>
         </is>
       </c>
       <c r="D964" s="4" t="n">
@@ -25514,7 +25593,7 @@
     <row r="965">
       <c r="A965" s="6" t="inlineStr">
         <is>
-          <t>7077510</t>
+          <t>7077577</t>
         </is>
       </c>
       <c r="B965" t="inlineStr">
@@ -25534,12 +25613,12 @@
     <row r="966">
       <c r="A966" s="4" t="inlineStr">
         <is>
-          <t>7077516</t>
+          <t>7018153</t>
         </is>
       </c>
       <c r="B966" s="5" t="inlineStr">
         <is>
-          <t>Infälld interiörarmatur IQ Wave</t>
+          <t>Infälld interiörarmatur Omega Pro 2</t>
         </is>
       </c>
       <c r="C966" s="5" t="inlineStr">
@@ -25554,12 +25633,12 @@
     <row r="967">
       <c r="A967" s="6" t="inlineStr">
         <is>
-          <t>7077513</t>
+          <t>7018765</t>
         </is>
       </c>
       <c r="B967" t="inlineStr">
         <is>
-          <t>Infälld interiörarmatur IQ Wave</t>
+          <t>Infälld interiörarmatur Omega Pro 2</t>
         </is>
       </c>
       <c r="C967" t="inlineStr">
@@ -25574,17 +25653,17 @@
     <row r="968">
       <c r="A968" s="4" t="inlineStr">
         <is>
-          <t>7077517</t>
+          <t>7022037</t>
         </is>
       </c>
       <c r="B968" s="5" t="inlineStr">
         <is>
-          <t>Infälld interiörarmatur IQ Wave</t>
+          <t>Interiörarmatur US Circle infälld</t>
         </is>
       </c>
       <c r="C968" s="5" t="inlineStr">
         <is>
-          <t>THORN</t>
+          <t>Tupex</t>
         </is>
       </c>
       <c r="D968" s="4" t="n">
@@ -25594,17 +25673,17 @@
     <row r="969">
       <c r="A969" s="6" t="inlineStr">
         <is>
-          <t>7077577</t>
+          <t>7022038</t>
         </is>
       </c>
       <c r="B969" t="inlineStr">
         <is>
-          <t>Infälld interiörarmatur IQ Wave</t>
+          <t>Interiörarmatur US Circle infälld</t>
         </is>
       </c>
       <c r="C969" t="inlineStr">
         <is>
-          <t>THORN</t>
+          <t>Tupex</t>
         </is>
       </c>
       <c r="D969" s="6" t="n">
@@ -25614,17 +25693,17 @@
     <row r="970">
       <c r="A970" s="4" t="inlineStr">
         <is>
-          <t>7018153</t>
+          <t>7021686</t>
         </is>
       </c>
       <c r="B970" s="5" t="inlineStr">
         <is>
-          <t>Infälld interiörarmatur Omega Pro 2</t>
+          <t>Interiörarmatur US Circle infälld</t>
         </is>
       </c>
       <c r="C970" s="5" t="inlineStr">
         <is>
-          <t>THORN</t>
+          <t>Tupex</t>
         </is>
       </c>
       <c r="D970" s="4" t="n">
@@ -25634,17 +25713,17 @@
     <row r="971">
       <c r="A971" s="6" t="inlineStr">
         <is>
-          <t>7018765</t>
+          <t>7021687</t>
         </is>
       </c>
       <c r="B971" t="inlineStr">
         <is>
-          <t>Infälld interiörarmatur Omega Pro 2</t>
+          <t>Interiörarmatur US Circle infälld</t>
         </is>
       </c>
       <c r="C971" t="inlineStr">
         <is>
-          <t>THORN</t>
+          <t>Tupex</t>
         </is>
       </c>
       <c r="D971" s="6" t="n">
@@ -25654,7 +25733,7 @@
     <row r="972">
       <c r="A972" s="4" t="inlineStr">
         <is>
-          <t>7022037</t>
+          <t>7022043</t>
         </is>
       </c>
       <c r="B972" s="5" t="inlineStr">
@@ -25674,7 +25753,7 @@
     <row r="973">
       <c r="A973" s="6" t="inlineStr">
         <is>
-          <t>7022038</t>
+          <t>7022045</t>
         </is>
       </c>
       <c r="B973" t="inlineStr">
@@ -25694,12 +25773,12 @@
     <row r="974">
       <c r="A974" s="4" t="inlineStr">
         <is>
-          <t>7021686</t>
+          <t>7026483</t>
         </is>
       </c>
       <c r="B974" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur US Circle infälld</t>
+          <t>Interiörarmatur US Eco Infälld</t>
         </is>
       </c>
       <c r="C974" s="5" t="inlineStr">
@@ -25714,12 +25793,12 @@
     <row r="975">
       <c r="A975" s="6" t="inlineStr">
         <is>
-          <t>7021687</t>
+          <t>7021611</t>
         </is>
       </c>
       <c r="B975" t="inlineStr">
         <is>
-          <t>Interiörarmatur US Circle infälld</t>
+          <t>Interiörarmatur US Eco Infälld</t>
         </is>
       </c>
       <c r="C975" t="inlineStr">
@@ -25728,18 +25807,18 @@
         </is>
       </c>
       <c r="D975" s="6" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
     </row>
     <row r="976">
       <c r="A976" s="4" t="inlineStr">
         <is>
-          <t>7022043</t>
+          <t>7029355</t>
         </is>
       </c>
       <c r="B976" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur US Circle infälld</t>
+          <t>Interiörarmatur US Eco Infälld</t>
         </is>
       </c>
       <c r="C976" s="5" t="inlineStr">
@@ -25748,18 +25827,18 @@
         </is>
       </c>
       <c r="D976" s="4" t="n">
-        <v>0</v>
+        <v>94</v>
       </c>
     </row>
     <row r="977">
       <c r="A977" s="6" t="inlineStr">
         <is>
-          <t>7022045</t>
+          <t>7029356</t>
         </is>
       </c>
       <c r="B977" t="inlineStr">
         <is>
-          <t>Interiörarmatur US Circle infälld</t>
+          <t>Interiörarmatur US Eco Infälld</t>
         </is>
       </c>
       <c r="C977" t="inlineStr">
@@ -25768,13 +25847,13 @@
         </is>
       </c>
       <c r="D977" s="6" t="n">
-        <v>0</v>
+        <v>134</v>
       </c>
     </row>
     <row r="978">
       <c r="A978" s="4" t="inlineStr">
         <is>
-          <t>7026483</t>
+          <t>7029357</t>
         </is>
       </c>
       <c r="B978" s="5" t="inlineStr">
@@ -25788,18 +25867,18 @@
         </is>
       </c>
       <c r="D978" s="4" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
     </row>
     <row r="979">
       <c r="A979" s="6" t="inlineStr">
         <is>
-          <t>7021611</t>
+          <t>7021628</t>
         </is>
       </c>
       <c r="B979" t="inlineStr">
         <is>
-          <t>Interiörarmatur US Eco Infälld</t>
+          <t>Interiörarmatur US Sens infälld med grundljus</t>
         </is>
       </c>
       <c r="C979" t="inlineStr">
@@ -25808,18 +25887,18 @@
         </is>
       </c>
       <c r="D979" s="6" t="n">
-        <v>158</v>
+        <v>0</v>
       </c>
     </row>
     <row r="980">
       <c r="A980" s="4" t="inlineStr">
         <is>
-          <t>7029355</t>
+          <t>7021629</t>
         </is>
       </c>
       <c r="B980" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur US Eco Infälld</t>
+          <t>Interiörarmatur US Sens infälld med grundljus</t>
         </is>
       </c>
       <c r="C980" s="5" t="inlineStr">
@@ -25828,18 +25907,18 @@
         </is>
       </c>
       <c r="D980" s="4" t="n">
-        <v>94</v>
+        <v>0</v>
       </c>
     </row>
     <row r="981">
       <c r="A981" s="6" t="inlineStr">
         <is>
-          <t>7029356</t>
+          <t>7021996</t>
         </is>
       </c>
       <c r="B981" t="inlineStr">
         <is>
-          <t>Interiörarmatur US Eco Infälld</t>
+          <t>Interiörarmatur US infälld</t>
         </is>
       </c>
       <c r="C981" t="inlineStr">
@@ -25848,18 +25927,18 @@
         </is>
       </c>
       <c r="D981" s="6" t="n">
-        <v>134</v>
+        <v>0</v>
       </c>
     </row>
     <row r="982">
       <c r="A982" s="4" t="inlineStr">
         <is>
-          <t>7029357</t>
+          <t>7021997</t>
         </is>
       </c>
       <c r="B982" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur US Eco Infälld</t>
+          <t>Interiörarmatur US infälld</t>
         </is>
       </c>
       <c r="C982" s="5" t="inlineStr">
@@ -25868,13 +25947,13 @@
         </is>
       </c>
       <c r="D982" s="4" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="983">
       <c r="A983" s="6" t="inlineStr">
         <is>
-          <t>7021996</t>
+          <t>7021617</t>
         </is>
       </c>
       <c r="B983" t="inlineStr">
@@ -25894,7 +25973,7 @@
     <row r="984">
       <c r="A984" s="4" t="inlineStr">
         <is>
-          <t>7021997</t>
+          <t>7021618</t>
         </is>
       </c>
       <c r="B984" s="5" t="inlineStr">
@@ -25914,7 +25993,7 @@
     <row r="985">
       <c r="A985" s="6" t="inlineStr">
         <is>
-          <t>7021617</t>
+          <t>7022019</t>
         </is>
       </c>
       <c r="B985" t="inlineStr">
@@ -25934,7 +26013,7 @@
     <row r="986">
       <c r="A986" s="4" t="inlineStr">
         <is>
-          <t>7021618</t>
+          <t>7022021</t>
         </is>
       </c>
       <c r="B986" s="5" t="inlineStr">
@@ -25954,17 +26033,17 @@
     <row r="987">
       <c r="A987" s="6" t="inlineStr">
         <is>
-          <t>7022019</t>
+          <t>7015332</t>
         </is>
       </c>
       <c r="B987" t="inlineStr">
         <is>
-          <t>Interiörarmatur US infälld</t>
+          <t>Infälld interiörarmatur WLP</t>
         </is>
       </c>
       <c r="C987" t="inlineStr">
         <is>
-          <t>Tupex</t>
+          <t>Westal</t>
         </is>
       </c>
       <c r="D987" s="6" t="n">
@@ -25974,17 +26053,17 @@
     <row r="988">
       <c r="A988" s="4" t="inlineStr">
         <is>
-          <t>7022021</t>
+          <t>7018758</t>
         </is>
       </c>
       <c r="B988" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur US infälld</t>
+          <t>Infälld interiörarmatur WLP</t>
         </is>
       </c>
       <c r="C988" s="5" t="inlineStr">
         <is>
-          <t>Tupex</t>
+          <t>Westal</t>
         </is>
       </c>
       <c r="D988" s="4" t="n">
@@ -25994,7 +26073,7 @@
     <row r="989">
       <c r="A989" s="6" t="inlineStr">
         <is>
-          <t>7015332</t>
+          <t>7015333</t>
         </is>
       </c>
       <c r="B989" t="inlineStr">
@@ -26014,7 +26093,7 @@
     <row r="990">
       <c r="A990" s="4" t="inlineStr">
         <is>
-          <t>7018758</t>
+          <t>7016779</t>
         </is>
       </c>
       <c r="B990" s="5" t="inlineStr">
@@ -26034,12 +26113,12 @@
     <row r="991">
       <c r="A991" s="6" t="inlineStr">
         <is>
-          <t>7015333</t>
+          <t>7018294</t>
         </is>
       </c>
       <c r="B991" t="inlineStr">
         <is>
-          <t>Infälld interiörarmatur WLP</t>
+          <t>Infälld interiörarmatur WLP tunable</t>
         </is>
       </c>
       <c r="C991" t="inlineStr">
@@ -26054,12 +26133,12 @@
     <row r="992">
       <c r="A992" s="4" t="inlineStr">
         <is>
-          <t>7016779</t>
+          <t>7021000</t>
         </is>
       </c>
       <c r="B992" s="5" t="inlineStr">
         <is>
-          <t>Infälld interiörarmatur WLP</t>
+          <t>Infälld interiörarmatur WLP tunable</t>
         </is>
       </c>
       <c r="C992" s="5" t="inlineStr">
@@ -26074,12 +26153,12 @@
     <row r="993">
       <c r="A993" s="6" t="inlineStr">
         <is>
-          <t>7018294</t>
+          <t>7020998</t>
         </is>
       </c>
       <c r="B993" t="inlineStr">
         <is>
-          <t>Infälld interiörarmatur WLP tunable</t>
+          <t>Infälld interiörarmatur WLP, ActiveAhead</t>
         </is>
       </c>
       <c r="C993" t="inlineStr">
@@ -26094,12 +26173,12 @@
     <row r="994">
       <c r="A994" s="4" t="inlineStr">
         <is>
-          <t>7021000</t>
+          <t>7020999</t>
         </is>
       </c>
       <c r="B994" s="5" t="inlineStr">
         <is>
-          <t>Infälld interiörarmatur WLP tunable</t>
+          <t>Infälld interiörarmatur WLP, ActiveAhead</t>
         </is>
       </c>
       <c r="C994" s="5" t="inlineStr">
@@ -26114,7 +26193,7 @@
     <row r="995">
       <c r="A995" s="6" t="inlineStr">
         <is>
-          <t>7020998</t>
+          <t>7024828</t>
         </is>
       </c>
       <c r="B995" t="inlineStr">
@@ -26134,7 +26213,7 @@
     <row r="996">
       <c r="A996" s="4" t="inlineStr">
         <is>
-          <t>7020999</t>
+          <t>7024829</t>
         </is>
       </c>
       <c r="B996" s="5" t="inlineStr">
@@ -26154,12 +26233,12 @@
     <row r="997">
       <c r="A997" s="6" t="inlineStr">
         <is>
-          <t>7024828</t>
+          <t>7018759</t>
         </is>
       </c>
       <c r="B997" t="inlineStr">
         <is>
-          <t>Infälld interiörarmatur WLP, ActiveAhead</t>
+          <t>Infälld interiörarmatur WLP-D IP65</t>
         </is>
       </c>
       <c r="C997" t="inlineStr">
@@ -26174,12 +26253,12 @@
     <row r="998">
       <c r="A998" s="4" t="inlineStr">
         <is>
-          <t>7024829</t>
+          <t>7018764</t>
         </is>
       </c>
       <c r="B998" s="5" t="inlineStr">
         <is>
-          <t>Infälld interiörarmatur WLP, ActiveAhead</t>
+          <t>Infälld interiörarmatur WLP-D IP65</t>
         </is>
       </c>
       <c r="C998" s="5" t="inlineStr">
@@ -26194,12 +26273,12 @@
     <row r="999">
       <c r="A999" s="6" t="inlineStr">
         <is>
-          <t>7018759</t>
+          <t>7025805</t>
         </is>
       </c>
       <c r="B999" t="inlineStr">
         <is>
-          <t>Infälld interiörarmatur WLP-D IP65</t>
+          <t>Interiörarmatur Lino infälld L-stycke</t>
         </is>
       </c>
       <c r="C999" t="inlineStr">
@@ -26214,12 +26293,12 @@
     <row r="1000">
       <c r="A1000" s="4" t="inlineStr">
         <is>
-          <t>7018764</t>
+          <t>7025806</t>
         </is>
       </c>
       <c r="B1000" s="5" t="inlineStr">
         <is>
-          <t>Infälld interiörarmatur WLP-D IP65</t>
+          <t>Interiörarmatur Lino infälld L-stycke</t>
         </is>
       </c>
       <c r="C1000" s="5" t="inlineStr">
@@ -26234,7 +26313,7 @@
     <row r="1001">
       <c r="A1001" s="6" t="inlineStr">
         <is>
-          <t>7025805</t>
+          <t>7025817</t>
         </is>
       </c>
       <c r="B1001" t="inlineStr">
@@ -26254,7 +26333,7 @@
     <row r="1002">
       <c r="A1002" s="4" t="inlineStr">
         <is>
-          <t>7025806</t>
+          <t>7025818</t>
         </is>
       </c>
       <c r="B1002" s="5" t="inlineStr">
@@ -26274,12 +26353,12 @@
     <row r="1003">
       <c r="A1003" s="6" t="inlineStr">
         <is>
-          <t>7025817</t>
+          <t>7025809</t>
         </is>
       </c>
       <c r="B1003" t="inlineStr">
         <is>
-          <t>Interiörarmatur Lino infälld L-stycke</t>
+          <t>Interiörarmatur Lino infälld X-stycke</t>
         </is>
       </c>
       <c r="C1003" t="inlineStr">
@@ -26294,12 +26373,12 @@
     <row r="1004">
       <c r="A1004" s="4" t="inlineStr">
         <is>
-          <t>7025818</t>
+          <t>7025810</t>
         </is>
       </c>
       <c r="B1004" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Lino infälld L-stycke</t>
+          <t>Interiörarmatur Lino infälld X-stycke</t>
         </is>
       </c>
       <c r="C1004" s="5" t="inlineStr">
@@ -26314,7 +26393,7 @@
     <row r="1005">
       <c r="A1005" s="6" t="inlineStr">
         <is>
-          <t>7025809</t>
+          <t>7025821</t>
         </is>
       </c>
       <c r="B1005" t="inlineStr">
@@ -26334,7 +26413,7 @@
     <row r="1006">
       <c r="A1006" s="4" t="inlineStr">
         <is>
-          <t>7025810</t>
+          <t>7025822</t>
         </is>
       </c>
       <c r="B1006" s="5" t="inlineStr">
@@ -26354,12 +26433,12 @@
     <row r="1007">
       <c r="A1007" s="6" t="inlineStr">
         <is>
-          <t>7025821</t>
+          <t>7025757E</t>
         </is>
       </c>
       <c r="B1007" t="inlineStr">
         <is>
-          <t>Interiörarmatur Lino infälld X-stycke</t>
+          <t>Interiörarmatur Lino infälld mittsektion</t>
         </is>
       </c>
       <c r="C1007" t="inlineStr">
@@ -26374,12 +26453,12 @@
     <row r="1008">
       <c r="A1008" s="4" t="inlineStr">
         <is>
-          <t>7025822</t>
+          <t>7025758</t>
         </is>
       </c>
       <c r="B1008" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Lino infälld X-stycke</t>
+          <t>Interiörarmatur Lino infälld mittsektion</t>
         </is>
       </c>
       <c r="C1008" s="5" t="inlineStr">
@@ -26394,7 +26473,7 @@
     <row r="1009">
       <c r="A1009" s="6" t="inlineStr">
         <is>
-          <t>7025757E</t>
+          <t>7025759</t>
         </is>
       </c>
       <c r="B1009" t="inlineStr">
@@ -26414,7 +26493,7 @@
     <row r="1010">
       <c r="A1010" s="4" t="inlineStr">
         <is>
-          <t>7025758</t>
+          <t>7025760</t>
         </is>
       </c>
       <c r="B1010" s="5" t="inlineStr">
@@ -26434,7 +26513,7 @@
     <row r="1011">
       <c r="A1011" s="6" t="inlineStr">
         <is>
-          <t>7025759</t>
+          <t>7025761</t>
         </is>
       </c>
       <c r="B1011" t="inlineStr">
@@ -26454,7 +26533,7 @@
     <row r="1012">
       <c r="A1012" s="4" t="inlineStr">
         <is>
-          <t>7025760</t>
+          <t>7025762E</t>
         </is>
       </c>
       <c r="B1012" s="5" t="inlineStr">
@@ -26474,7 +26553,7 @@
     <row r="1013">
       <c r="A1013" s="6" t="inlineStr">
         <is>
-          <t>7025761</t>
+          <t>7025763E</t>
         </is>
       </c>
       <c r="B1013" t="inlineStr">
@@ -26494,7 +26573,7 @@
     <row r="1014">
       <c r="A1014" s="4" t="inlineStr">
         <is>
-          <t>7025762E</t>
+          <t>7025764</t>
         </is>
       </c>
       <c r="B1014" s="5" t="inlineStr">
@@ -26514,7 +26593,7 @@
     <row r="1015">
       <c r="A1015" s="6" t="inlineStr">
         <is>
-          <t>7025763E</t>
+          <t>7025765</t>
         </is>
       </c>
       <c r="B1015" t="inlineStr">
@@ -26534,7 +26613,7 @@
     <row r="1016">
       <c r="A1016" s="4" t="inlineStr">
         <is>
-          <t>7025764</t>
+          <t>7025766</t>
         </is>
       </c>
       <c r="B1016" s="5" t="inlineStr">
@@ -26554,7 +26633,7 @@
     <row r="1017">
       <c r="A1017" s="6" t="inlineStr">
         <is>
-          <t>7025765</t>
+          <t>7025767</t>
         </is>
       </c>
       <c r="B1017" t="inlineStr">
@@ -26574,7 +26653,7 @@
     <row r="1018">
       <c r="A1018" s="4" t="inlineStr">
         <is>
-          <t>7025766</t>
+          <t>7025768</t>
         </is>
       </c>
       <c r="B1018" s="5" t="inlineStr">
@@ -26594,7 +26673,7 @@
     <row r="1019">
       <c r="A1019" s="6" t="inlineStr">
         <is>
-          <t>7025767</t>
+          <t>7025769</t>
         </is>
       </c>
       <c r="B1019" t="inlineStr">
@@ -26614,7 +26693,7 @@
     <row r="1020">
       <c r="A1020" s="4" t="inlineStr">
         <is>
-          <t>7025768</t>
+          <t>7025770</t>
         </is>
       </c>
       <c r="B1020" s="5" t="inlineStr">
@@ -26634,7 +26713,7 @@
     <row r="1021">
       <c r="A1021" s="6" t="inlineStr">
         <is>
-          <t>7025769</t>
+          <t>7025785</t>
         </is>
       </c>
       <c r="B1021" t="inlineStr">
@@ -26654,7 +26733,7 @@
     <row r="1022">
       <c r="A1022" s="4" t="inlineStr">
         <is>
-          <t>7025770</t>
+          <t>7025786</t>
         </is>
       </c>
       <c r="B1022" s="5" t="inlineStr">
@@ -26674,7 +26753,7 @@
     <row r="1023">
       <c r="A1023" s="6" t="inlineStr">
         <is>
-          <t>7025785</t>
+          <t>7025787</t>
         </is>
       </c>
       <c r="B1023" t="inlineStr">
@@ -26694,7 +26773,7 @@
     <row r="1024">
       <c r="A1024" s="4" t="inlineStr">
         <is>
-          <t>7025786</t>
+          <t>7025788</t>
         </is>
       </c>
       <c r="B1024" s="5" t="inlineStr">
@@ -26714,7 +26793,7 @@
     <row r="1025">
       <c r="A1025" s="6" t="inlineStr">
         <is>
-          <t>7025787</t>
+          <t>7025789</t>
         </is>
       </c>
       <c r="B1025" t="inlineStr">
@@ -26734,7 +26813,7 @@
     <row r="1026">
       <c r="A1026" s="4" t="inlineStr">
         <is>
-          <t>7025788</t>
+          <t>7025790</t>
         </is>
       </c>
       <c r="B1026" s="5" t="inlineStr">
@@ -26754,7 +26833,7 @@
     <row r="1027">
       <c r="A1027" s="6" t="inlineStr">
         <is>
-          <t>7025789</t>
+          <t>7025791</t>
         </is>
       </c>
       <c r="B1027" t="inlineStr">
@@ -26774,7 +26853,7 @@
     <row r="1028">
       <c r="A1028" s="4" t="inlineStr">
         <is>
-          <t>7025790</t>
+          <t>7025792</t>
         </is>
       </c>
       <c r="B1028" s="5" t="inlineStr">
@@ -26794,7 +26873,7 @@
     <row r="1029">
       <c r="A1029" s="6" t="inlineStr">
         <is>
-          <t>7025791</t>
+          <t>7025793</t>
         </is>
       </c>
       <c r="B1029" t="inlineStr">
@@ -26814,7 +26893,7 @@
     <row r="1030">
       <c r="A1030" s="4" t="inlineStr">
         <is>
-          <t>7025792</t>
+          <t>7025794</t>
         </is>
       </c>
       <c r="B1030" s="5" t="inlineStr">
@@ -26834,7 +26913,7 @@
     <row r="1031">
       <c r="A1031" s="6" t="inlineStr">
         <is>
-          <t>7025793</t>
+          <t>7025795</t>
         </is>
       </c>
       <c r="B1031" t="inlineStr">
@@ -26854,7 +26933,7 @@
     <row r="1032">
       <c r="A1032" s="4" t="inlineStr">
         <is>
-          <t>7025794</t>
+          <t>7025796</t>
         </is>
       </c>
       <c r="B1032" s="5" t="inlineStr">
@@ -26874,7 +26953,7 @@
     <row r="1033">
       <c r="A1033" s="6" t="inlineStr">
         <is>
-          <t>7025795</t>
+          <t>7025797</t>
         </is>
       </c>
       <c r="B1033" t="inlineStr">
@@ -26894,7 +26973,7 @@
     <row r="1034">
       <c r="A1034" s="4" t="inlineStr">
         <is>
-          <t>7025796</t>
+          <t>7025798</t>
         </is>
       </c>
       <c r="B1034" s="5" t="inlineStr">
@@ -26914,12 +26993,12 @@
     <row r="1035">
       <c r="A1035" s="6" t="inlineStr">
         <is>
-          <t>7025797</t>
+          <t>7025689</t>
         </is>
       </c>
       <c r="B1035" t="inlineStr">
         <is>
-          <t>Interiörarmatur Lino infälld mittsektion</t>
+          <t>Interiörarmatur Lino infälld start/slut sektion</t>
         </is>
       </c>
       <c r="C1035" t="inlineStr">
@@ -26934,12 +27013,12 @@
     <row r="1036">
       <c r="A1036" s="4" t="inlineStr">
         <is>
-          <t>7025798</t>
+          <t>7025690</t>
         </is>
       </c>
       <c r="B1036" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Lino infälld mittsektion</t>
+          <t>Interiörarmatur Lino infälld start/slut sektion</t>
         </is>
       </c>
       <c r="C1036" s="5" t="inlineStr">
@@ -26954,7 +27033,7 @@
     <row r="1037">
       <c r="A1037" s="6" t="inlineStr">
         <is>
-          <t>7025689</t>
+          <t>7025691</t>
         </is>
       </c>
       <c r="B1037" t="inlineStr">
@@ -26974,7 +27053,7 @@
     <row r="1038">
       <c r="A1038" s="4" t="inlineStr">
         <is>
-          <t>7025690</t>
+          <t>7025692</t>
         </is>
       </c>
       <c r="B1038" s="5" t="inlineStr">
@@ -26994,7 +27073,7 @@
     <row r="1039">
       <c r="A1039" s="6" t="inlineStr">
         <is>
-          <t>7025691</t>
+          <t>7025693</t>
         </is>
       </c>
       <c r="B1039" t="inlineStr">
@@ -27014,7 +27093,7 @@
     <row r="1040">
       <c r="A1040" s="4" t="inlineStr">
         <is>
-          <t>7025692</t>
+          <t>7025694</t>
         </is>
       </c>
       <c r="B1040" s="5" t="inlineStr">
@@ -27034,7 +27113,7 @@
     <row r="1041">
       <c r="A1041" s="6" t="inlineStr">
         <is>
-          <t>7025693</t>
+          <t>7025695</t>
         </is>
       </c>
       <c r="B1041" t="inlineStr">
@@ -27054,7 +27133,7 @@
     <row r="1042">
       <c r="A1042" s="4" t="inlineStr">
         <is>
-          <t>7025694</t>
+          <t>7025696</t>
         </is>
       </c>
       <c r="B1042" s="5" t="inlineStr">
@@ -27074,7 +27153,7 @@
     <row r="1043">
       <c r="A1043" s="6" t="inlineStr">
         <is>
-          <t>7025695</t>
+          <t>7025697</t>
         </is>
       </c>
       <c r="B1043" t="inlineStr">
@@ -27094,7 +27173,7 @@
     <row r="1044">
       <c r="A1044" s="4" t="inlineStr">
         <is>
-          <t>7025696</t>
+          <t>7025698</t>
         </is>
       </c>
       <c r="B1044" s="5" t="inlineStr">
@@ -27114,7 +27193,7 @@
     <row r="1045">
       <c r="A1045" s="6" t="inlineStr">
         <is>
-          <t>7025697</t>
+          <t>7025699</t>
         </is>
       </c>
       <c r="B1045" t="inlineStr">
@@ -27134,7 +27213,7 @@
     <row r="1046">
       <c r="A1046" s="4" t="inlineStr">
         <is>
-          <t>7025698</t>
+          <t>7025700</t>
         </is>
       </c>
       <c r="B1046" s="5" t="inlineStr">
@@ -27154,7 +27233,7 @@
     <row r="1047">
       <c r="A1047" s="6" t="inlineStr">
         <is>
-          <t>7025699</t>
+          <t>7025701</t>
         </is>
       </c>
       <c r="B1047" t="inlineStr">
@@ -27174,7 +27253,7 @@
     <row r="1048">
       <c r="A1048" s="4" t="inlineStr">
         <is>
-          <t>7025700</t>
+          <t>7025702</t>
         </is>
       </c>
       <c r="B1048" s="5" t="inlineStr">
@@ -27194,7 +27273,7 @@
     <row r="1049">
       <c r="A1049" s="6" t="inlineStr">
         <is>
-          <t>7025701</t>
+          <t>7025703</t>
         </is>
       </c>
       <c r="B1049" t="inlineStr">
@@ -27214,7 +27293,7 @@
     <row r="1050">
       <c r="A1050" s="4" t="inlineStr">
         <is>
-          <t>7025702</t>
+          <t>7025704</t>
         </is>
       </c>
       <c r="B1050" s="5" t="inlineStr">
@@ -27234,7 +27313,7 @@
     <row r="1051">
       <c r="A1051" s="6" t="inlineStr">
         <is>
-          <t>7025703</t>
+          <t>7025705</t>
         </is>
       </c>
       <c r="B1051" t="inlineStr">
@@ -27254,7 +27333,7 @@
     <row r="1052">
       <c r="A1052" s="4" t="inlineStr">
         <is>
-          <t>7025704</t>
+          <t>7025706</t>
         </is>
       </c>
       <c r="B1052" s="5" t="inlineStr">
@@ -27274,7 +27353,7 @@
     <row r="1053">
       <c r="A1053" s="6" t="inlineStr">
         <is>
-          <t>7025705</t>
+          <t>7025725</t>
         </is>
       </c>
       <c r="B1053" t="inlineStr">
@@ -27294,7 +27373,7 @@
     <row r="1054">
       <c r="A1054" s="4" t="inlineStr">
         <is>
-          <t>7025706</t>
+          <t>7025726</t>
         </is>
       </c>
       <c r="B1054" s="5" t="inlineStr">
@@ -27314,7 +27393,7 @@
     <row r="1055">
       <c r="A1055" s="6" t="inlineStr">
         <is>
-          <t>7025725</t>
+          <t>7025727</t>
         </is>
       </c>
       <c r="B1055" t="inlineStr">
@@ -27334,7 +27413,7 @@
     <row r="1056">
       <c r="A1056" s="4" t="inlineStr">
         <is>
-          <t>7025726</t>
+          <t>7025728</t>
         </is>
       </c>
       <c r="B1056" s="5" t="inlineStr">
@@ -27354,7 +27433,7 @@
     <row r="1057">
       <c r="A1057" s="6" t="inlineStr">
         <is>
-          <t>7025727</t>
+          <t>7025729</t>
         </is>
       </c>
       <c r="B1057" t="inlineStr">
@@ -27374,7 +27453,7 @@
     <row r="1058">
       <c r="A1058" s="4" t="inlineStr">
         <is>
-          <t>7025728</t>
+          <t>7025730</t>
         </is>
       </c>
       <c r="B1058" s="5" t="inlineStr">
@@ -27394,7 +27473,7 @@
     <row r="1059">
       <c r="A1059" s="6" t="inlineStr">
         <is>
-          <t>7025729</t>
+          <t>7025731</t>
         </is>
       </c>
       <c r="B1059" t="inlineStr">
@@ -27414,7 +27493,7 @@
     <row r="1060">
       <c r="A1060" s="4" t="inlineStr">
         <is>
-          <t>7025730</t>
+          <t>7025732</t>
         </is>
       </c>
       <c r="B1060" s="5" t="inlineStr">
@@ -27434,7 +27513,7 @@
     <row r="1061">
       <c r="A1061" s="6" t="inlineStr">
         <is>
-          <t>7025731</t>
+          <t>7025733</t>
         </is>
       </c>
       <c r="B1061" t="inlineStr">
@@ -27454,7 +27533,7 @@
     <row r="1062">
       <c r="A1062" s="4" t="inlineStr">
         <is>
-          <t>7025732</t>
+          <t>7025734</t>
         </is>
       </c>
       <c r="B1062" s="5" t="inlineStr">
@@ -27474,7 +27553,7 @@
     <row r="1063">
       <c r="A1063" s="6" t="inlineStr">
         <is>
-          <t>7025733</t>
+          <t>7025735E</t>
         </is>
       </c>
       <c r="B1063" t="inlineStr">
@@ -27494,7 +27573,7 @@
     <row r="1064">
       <c r="A1064" s="4" t="inlineStr">
         <is>
-          <t>7025734</t>
+          <t>7025736E</t>
         </is>
       </c>
       <c r="B1064" s="5" t="inlineStr">
@@ -27514,7 +27593,7 @@
     <row r="1065">
       <c r="A1065" s="6" t="inlineStr">
         <is>
-          <t>7025735E</t>
+          <t>7025737</t>
         </is>
       </c>
       <c r="B1065" t="inlineStr">
@@ -27534,7 +27613,7 @@
     <row r="1066">
       <c r="A1066" s="4" t="inlineStr">
         <is>
-          <t>7025736E</t>
+          <t>7025738</t>
         </is>
       </c>
       <c r="B1066" s="5" t="inlineStr">
@@ -27554,7 +27633,7 @@
     <row r="1067">
       <c r="A1067" s="6" t="inlineStr">
         <is>
-          <t>7025737</t>
+          <t>7025739</t>
         </is>
       </c>
       <c r="B1067" t="inlineStr">
@@ -27574,7 +27653,7 @@
     <row r="1068">
       <c r="A1068" s="4" t="inlineStr">
         <is>
-          <t>7025738</t>
+          <t>7025740</t>
         </is>
       </c>
       <c r="B1068" s="5" t="inlineStr">
@@ -27594,7 +27673,7 @@
     <row r="1069">
       <c r="A1069" s="6" t="inlineStr">
         <is>
-          <t>7025739</t>
+          <t>7025741</t>
         </is>
       </c>
       <c r="B1069" t="inlineStr">
@@ -27614,7 +27693,7 @@
     <row r="1070">
       <c r="A1070" s="4" t="inlineStr">
         <is>
-          <t>7025740</t>
+          <t>7025742</t>
         </is>
       </c>
       <c r="B1070" s="5" t="inlineStr">
@@ -27634,12 +27713,12 @@
     <row r="1071">
       <c r="A1071" s="6" t="inlineStr">
         <is>
-          <t>7025741</t>
+          <t>7510324</t>
         </is>
       </c>
       <c r="B1071" t="inlineStr">
         <is>
-          <t>Interiörarmatur Lino infälld start/slut sektion</t>
+          <t>Interiörarmatur Mira 1x28 infälld</t>
         </is>
       </c>
       <c r="C1071" t="inlineStr">
@@ -27654,12 +27733,12 @@
     <row r="1072">
       <c r="A1072" s="4" t="inlineStr">
         <is>
-          <t>7025742</t>
+          <t>7510325</t>
         </is>
       </c>
       <c r="B1072" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Lino infälld start/slut sektion</t>
+          <t>Interiörarmatur Mira 1x28 infälld</t>
         </is>
       </c>
       <c r="C1072" s="5" t="inlineStr">
@@ -27674,7 +27753,7 @@
     <row r="1073">
       <c r="A1073" s="6" t="inlineStr">
         <is>
-          <t>7510324</t>
+          <t>7510326</t>
         </is>
       </c>
       <c r="B1073" t="inlineStr">
@@ -27694,7 +27773,7 @@
     <row r="1074">
       <c r="A1074" s="4" t="inlineStr">
         <is>
-          <t>7510325</t>
+          <t>7510327</t>
         </is>
       </c>
       <c r="B1074" s="5" t="inlineStr">
@@ -27714,7 +27793,7 @@
     <row r="1075">
       <c r="A1075" s="6" t="inlineStr">
         <is>
-          <t>7510326</t>
+          <t>7510328</t>
         </is>
       </c>
       <c r="B1075" t="inlineStr">
@@ -27734,7 +27813,7 @@
     <row r="1076">
       <c r="A1076" s="4" t="inlineStr">
         <is>
-          <t>7510327</t>
+          <t>7510329</t>
         </is>
       </c>
       <c r="B1076" s="5" t="inlineStr">
@@ -27754,7 +27833,7 @@
     <row r="1077">
       <c r="A1077" s="6" t="inlineStr">
         <is>
-          <t>7510328</t>
+          <t>7510344</t>
         </is>
       </c>
       <c r="B1077" t="inlineStr">
@@ -27774,7 +27853,7 @@
     <row r="1078">
       <c r="A1078" s="4" t="inlineStr">
         <is>
-          <t>7510329</t>
+          <t>7510345</t>
         </is>
       </c>
       <c r="B1078" s="5" t="inlineStr">
@@ -27794,7 +27873,7 @@
     <row r="1079">
       <c r="A1079" s="6" t="inlineStr">
         <is>
-          <t>7510344</t>
+          <t>7510346</t>
         </is>
       </c>
       <c r="B1079" t="inlineStr">
@@ -27814,7 +27893,7 @@
     <row r="1080">
       <c r="A1080" s="4" t="inlineStr">
         <is>
-          <t>7510345</t>
+          <t>7510347</t>
         </is>
       </c>
       <c r="B1080" s="5" t="inlineStr">
@@ -27834,7 +27913,7 @@
     <row r="1081">
       <c r="A1081" s="6" t="inlineStr">
         <is>
-          <t>7510346</t>
+          <t>7510348</t>
         </is>
       </c>
       <c r="B1081" t="inlineStr">
@@ -27854,7 +27933,7 @@
     <row r="1082">
       <c r="A1082" s="4" t="inlineStr">
         <is>
-          <t>7510347</t>
+          <t>7510349</t>
         </is>
       </c>
       <c r="B1082" s="5" t="inlineStr">
@@ -27874,12 +27953,12 @@
     <row r="1083">
       <c r="A1083" s="6" t="inlineStr">
         <is>
-          <t>7510348</t>
+          <t>7021294</t>
         </is>
       </c>
       <c r="B1083" t="inlineStr">
         <is>
-          <t>Interiörarmatur Mira 1x28 infälld</t>
+          <t>Interiörarmatur WLP Backlit</t>
         </is>
       </c>
       <c r="C1083" t="inlineStr">
@@ -27894,12 +27973,12 @@
     <row r="1084">
       <c r="A1084" s="4" t="inlineStr">
         <is>
-          <t>7510349</t>
+          <t>7021295</t>
         </is>
       </c>
       <c r="B1084" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Mira 1x28 infälld</t>
+          <t>Interiörarmatur WLP Backlit</t>
         </is>
       </c>
       <c r="C1084" s="5" t="inlineStr">
@@ -27914,7 +27993,7 @@
     <row r="1085">
       <c r="A1085" s="6" t="inlineStr">
         <is>
-          <t>7021294</t>
+          <t>7024767</t>
         </is>
       </c>
       <c r="B1085" t="inlineStr">
@@ -27934,7 +28013,7 @@
     <row r="1086">
       <c r="A1086" s="4" t="inlineStr">
         <is>
-          <t>7021295</t>
+          <t>7024768</t>
         </is>
       </c>
       <c r="B1086" s="5" t="inlineStr">
@@ -27954,12 +28033,12 @@
     <row r="1087">
       <c r="A1087" s="6" t="inlineStr">
         <is>
-          <t>7024767</t>
+          <t>7028545</t>
         </is>
       </c>
       <c r="B1087" t="inlineStr">
         <is>
-          <t>Interiörarmatur WLP Backlit</t>
+          <t>Interiörarmatur WLP Backlit PIR</t>
         </is>
       </c>
       <c r="C1087" t="inlineStr">
@@ -27974,12 +28053,12 @@
     <row r="1088">
       <c r="A1088" s="4" t="inlineStr">
         <is>
-          <t>7024768</t>
+          <t>7024616</t>
         </is>
       </c>
       <c r="B1088" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur WLP Backlit</t>
+          <t>Interiörarmatur WLP Backlit, ActiveAhead</t>
         </is>
       </c>
       <c r="C1088" s="5" t="inlineStr">
@@ -27994,12 +28073,12 @@
     <row r="1089">
       <c r="A1089" s="6" t="inlineStr">
         <is>
-          <t>7028545</t>
+          <t>7024617</t>
         </is>
       </c>
       <c r="B1089" t="inlineStr">
         <is>
-          <t>Interiörarmatur WLP Backlit PIR</t>
+          <t>Interiörarmatur WLP Backlit, ActiveAhead</t>
         </is>
       </c>
       <c r="C1089" t="inlineStr">
@@ -28014,7 +28093,7 @@
     <row r="1090">
       <c r="A1090" s="4" t="inlineStr">
         <is>
-          <t>7024616</t>
+          <t>7024816</t>
         </is>
       </c>
       <c r="B1090" s="5" t="inlineStr">
@@ -28034,7 +28113,7 @@
     <row r="1091">
       <c r="A1091" s="6" t="inlineStr">
         <is>
-          <t>7024617</t>
+          <t>7024817</t>
         </is>
       </c>
       <c r="B1091" t="inlineStr">
@@ -28054,12 +28133,12 @@
     <row r="1092">
       <c r="A1092" s="4" t="inlineStr">
         <is>
-          <t>7024816</t>
+          <t>7026165</t>
         </is>
       </c>
       <c r="B1092" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur WLP Backlit, ActiveAhead</t>
+          <t>Interiörarmatur WLP Cleanroom</t>
         </is>
       </c>
       <c r="C1092" s="5" t="inlineStr">
@@ -28074,12 +28153,12 @@
     <row r="1093">
       <c r="A1093" s="6" t="inlineStr">
         <is>
-          <t>7024817</t>
+          <t>7026166</t>
         </is>
       </c>
       <c r="B1093" t="inlineStr">
         <is>
-          <t>Interiörarmatur WLP Backlit, ActiveAhead</t>
+          <t>Interiörarmatur WLP Cleanroom</t>
         </is>
       </c>
       <c r="C1093" t="inlineStr">
@@ -28094,12 +28173,12 @@
     <row r="1094">
       <c r="A1094" s="4" t="inlineStr">
         <is>
-          <t>7026165</t>
+          <t>7027313</t>
         </is>
       </c>
       <c r="B1094" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur WLP Cleanroom</t>
+          <t>Interiörarmatur WLP-B</t>
         </is>
       </c>
       <c r="C1094" s="5" t="inlineStr">
@@ -28114,12 +28193,12 @@
     <row r="1095">
       <c r="A1095" s="6" t="inlineStr">
         <is>
-          <t>7026166</t>
+          <t>7510127</t>
         </is>
       </c>
       <c r="B1095" t="inlineStr">
         <is>
-          <t>Interiörarmatur WLP Cleanroom</t>
+          <t>Takarmatur Mira 1x7 infälld</t>
         </is>
       </c>
       <c r="C1095" t="inlineStr">
@@ -28134,12 +28213,12 @@
     <row r="1096">
       <c r="A1096" s="4" t="inlineStr">
         <is>
-          <t>7027313</t>
+          <t>7510128</t>
         </is>
       </c>
       <c r="B1096" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur WLP-B</t>
+          <t>Takarmatur Mira 1x7 infälld</t>
         </is>
       </c>
       <c r="C1096" s="5" t="inlineStr">
@@ -28154,7 +28233,7 @@
     <row r="1097">
       <c r="A1097" s="6" t="inlineStr">
         <is>
-          <t>7510127</t>
+          <t>7510129</t>
         </is>
       </c>
       <c r="B1097" t="inlineStr">
@@ -28174,7 +28253,7 @@
     <row r="1098">
       <c r="A1098" s="4" t="inlineStr">
         <is>
-          <t>7510128</t>
+          <t>7510130</t>
         </is>
       </c>
       <c r="B1098" s="5" t="inlineStr">
@@ -28194,7 +28273,7 @@
     <row r="1099">
       <c r="A1099" s="6" t="inlineStr">
         <is>
-          <t>7510129</t>
+          <t>7510131</t>
         </is>
       </c>
       <c r="B1099" t="inlineStr">
@@ -28214,7 +28293,7 @@
     <row r="1100">
       <c r="A1100" s="4" t="inlineStr">
         <is>
-          <t>7510130</t>
+          <t>7510132</t>
         </is>
       </c>
       <c r="B1100" s="5" t="inlineStr">
@@ -28234,7 +28313,7 @@
     <row r="1101">
       <c r="A1101" s="6" t="inlineStr">
         <is>
-          <t>7510131</t>
+          <t>7510139</t>
         </is>
       </c>
       <c r="B1101" t="inlineStr">
@@ -28254,7 +28333,7 @@
     <row r="1102">
       <c r="A1102" s="4" t="inlineStr">
         <is>
-          <t>7510132</t>
+          <t>7510140</t>
         </is>
       </c>
       <c r="B1102" s="5" t="inlineStr">
@@ -28274,7 +28353,7 @@
     <row r="1103">
       <c r="A1103" s="6" t="inlineStr">
         <is>
-          <t>7510139</t>
+          <t>7510141</t>
         </is>
       </c>
       <c r="B1103" t="inlineStr">
@@ -28294,7 +28373,7 @@
     <row r="1104">
       <c r="A1104" s="4" t="inlineStr">
         <is>
-          <t>7510140</t>
+          <t>7510142</t>
         </is>
       </c>
       <c r="B1104" s="5" t="inlineStr">
@@ -28314,7 +28393,7 @@
     <row r="1105">
       <c r="A1105" s="6" t="inlineStr">
         <is>
-          <t>7510141</t>
+          <t>7510143</t>
         </is>
       </c>
       <c r="B1105" t="inlineStr">
@@ -28334,7 +28413,7 @@
     <row r="1106">
       <c r="A1106" s="4" t="inlineStr">
         <is>
-          <t>7510142</t>
+          <t>7510144</t>
         </is>
       </c>
       <c r="B1106" s="5" t="inlineStr">
@@ -28354,12 +28433,12 @@
     <row r="1107">
       <c r="A1107" s="6" t="inlineStr">
         <is>
-          <t>7510143</t>
+          <t>7510073</t>
         </is>
       </c>
       <c r="B1107" t="inlineStr">
         <is>
-          <t>Takarmatur Mira 1x7 infälld</t>
+          <t>Takarmatur Mira 2x2 infälld</t>
         </is>
       </c>
       <c r="C1107" t="inlineStr">
@@ -28374,12 +28453,12 @@
     <row r="1108">
       <c r="A1108" s="4" t="inlineStr">
         <is>
-          <t>7510144</t>
+          <t>7510075</t>
         </is>
       </c>
       <c r="B1108" s="5" t="inlineStr">
         <is>
-          <t>Takarmatur Mira 1x7 infälld</t>
+          <t>Takarmatur Mira 2x2 infälld</t>
         </is>
       </c>
       <c r="C1108" s="5" t="inlineStr">
@@ -28394,7 +28473,7 @@
     <row r="1109">
       <c r="A1109" s="6" t="inlineStr">
         <is>
-          <t>7510073</t>
+          <t>7510077</t>
         </is>
       </c>
       <c r="B1109" t="inlineStr">
@@ -28414,7 +28493,7 @@
     <row r="1110">
       <c r="A1110" s="4" t="inlineStr">
         <is>
-          <t>7510075</t>
+          <t>7510079</t>
         </is>
       </c>
       <c r="B1110" s="5" t="inlineStr">
@@ -28434,7 +28513,7 @@
     <row r="1111">
       <c r="A1111" s="6" t="inlineStr">
         <is>
-          <t>7510077</t>
+          <t>7510081</t>
         </is>
       </c>
       <c r="B1111" t="inlineStr">
@@ -28454,7 +28533,7 @@
     <row r="1112">
       <c r="A1112" s="4" t="inlineStr">
         <is>
-          <t>7510079</t>
+          <t>7510083</t>
         </is>
       </c>
       <c r="B1112" s="5" t="inlineStr">
@@ -28474,7 +28553,7 @@
     <row r="1113">
       <c r="A1113" s="6" t="inlineStr">
         <is>
-          <t>7510081</t>
+          <t>7510085</t>
         </is>
       </c>
       <c r="B1113" t="inlineStr">
@@ -28494,7 +28573,7 @@
     <row r="1114">
       <c r="A1114" s="4" t="inlineStr">
         <is>
-          <t>7510083</t>
+          <t>7510087</t>
         </is>
       </c>
       <c r="B1114" s="5" t="inlineStr">
@@ -28514,7 +28593,7 @@
     <row r="1115">
       <c r="A1115" s="6" t="inlineStr">
         <is>
-          <t>7510085</t>
+          <t>7510112</t>
         </is>
       </c>
       <c r="B1115" t="inlineStr">
@@ -28534,7 +28613,7 @@
     <row r="1116">
       <c r="A1116" s="4" t="inlineStr">
         <is>
-          <t>7510087</t>
+          <t>7510114</t>
         </is>
       </c>
       <c r="B1116" s="5" t="inlineStr">
@@ -28554,7 +28633,7 @@
     <row r="1117">
       <c r="A1117" s="6" t="inlineStr">
         <is>
-          <t>7510112</t>
+          <t>7510115</t>
         </is>
       </c>
       <c r="B1117" t="inlineStr">
@@ -28574,7 +28653,7 @@
     <row r="1118">
       <c r="A1118" s="4" t="inlineStr">
         <is>
-          <t>7510114</t>
+          <t>7510116</t>
         </is>
       </c>
       <c r="B1118" s="5" t="inlineStr">
@@ -28594,7 +28673,7 @@
     <row r="1119">
       <c r="A1119" s="6" t="inlineStr">
         <is>
-          <t>7510115</t>
+          <t>7510117</t>
         </is>
       </c>
       <c r="B1119" t="inlineStr">
@@ -28614,7 +28693,7 @@
     <row r="1120">
       <c r="A1120" s="4" t="inlineStr">
         <is>
-          <t>7510116</t>
+          <t>7510118</t>
         </is>
       </c>
       <c r="B1120" s="5" t="inlineStr">
@@ -28634,7 +28713,7 @@
     <row r="1121">
       <c r="A1121" s="6" t="inlineStr">
         <is>
-          <t>7510117</t>
+          <t>7510119</t>
         </is>
       </c>
       <c r="B1121" t="inlineStr">
@@ -28654,7 +28733,7 @@
     <row r="1122">
       <c r="A1122" s="4" t="inlineStr">
         <is>
-          <t>7510118</t>
+          <t>7510120</t>
         </is>
       </c>
       <c r="B1122" s="5" t="inlineStr">
@@ -28674,17 +28753,17 @@
     <row r="1123">
       <c r="A1123" s="6" t="inlineStr">
         <is>
-          <t>7510119</t>
+          <t>7028323</t>
         </is>
       </c>
       <c r="B1123" t="inlineStr">
         <is>
-          <t>Takarmatur Mira 2x2 infälld</t>
+          <t>Interiörarmatur Beta Force</t>
         </is>
       </c>
       <c r="C1123" t="inlineStr">
         <is>
-          <t>Westal</t>
+          <t>ZG Lighting</t>
         </is>
       </c>
       <c r="D1123" s="6" t="n">
@@ -28694,17 +28773,17 @@
     <row r="1124">
       <c r="A1124" s="4" t="inlineStr">
         <is>
-          <t>7510120</t>
+          <t>7028324</t>
         </is>
       </c>
       <c r="B1124" s="5" t="inlineStr">
         <is>
-          <t>Takarmatur Mira 2x2 infälld</t>
+          <t>Interiörarmatur Beta Force</t>
         </is>
       </c>
       <c r="C1124" s="5" t="inlineStr">
         <is>
-          <t>Westal</t>
+          <t>ZG Lighting</t>
         </is>
       </c>
       <c r="D1124" s="4" t="n">
@@ -28714,12 +28793,12 @@
     <row r="1125">
       <c r="A1125" s="6" t="inlineStr">
         <is>
-          <t>7028323</t>
+          <t>7028311</t>
         </is>
       </c>
       <c r="B1125" t="inlineStr">
         <is>
-          <t>Interiörarmatur Beta Force</t>
+          <t>Interiörarmatur Maya</t>
         </is>
       </c>
       <c r="C1125" t="inlineStr">
@@ -28734,52 +28813,52 @@
     <row r="1126">
       <c r="A1126" s="4" t="inlineStr">
         <is>
-          <t>7028324</t>
+          <t>7013475</t>
         </is>
       </c>
       <c r="B1126" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Beta Force</t>
+          <t>Infälld interiörarmatur aLight Office LED</t>
         </is>
       </c>
       <c r="C1126" s="5" t="inlineStr">
         <is>
-          <t>ZG Lighting</t>
+          <t>a-collection</t>
         </is>
       </c>
       <c r="D1126" s="4" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1127">
       <c r="A1127" s="6" t="inlineStr">
         <is>
-          <t>7028311</t>
+          <t>7021097</t>
         </is>
       </c>
       <c r="B1127" t="inlineStr">
         <is>
-          <t>Interiörarmatur Maya</t>
+          <t>Infälld interiörarmatur aLight Office LED Tec rektangulär</t>
         </is>
       </c>
       <c r="C1127" t="inlineStr">
         <is>
-          <t>ZG Lighting</t>
+          <t>a-collection</t>
         </is>
       </c>
       <c r="D1127" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1128">
       <c r="A1128" s="4" t="inlineStr">
         <is>
-          <t>7013475</t>
+          <t>7018286</t>
         </is>
       </c>
       <c r="B1128" s="5" t="inlineStr">
         <is>
-          <t>Infälld interiörarmatur aLight Office LED</t>
+          <t>Infälld interiörarmatur aLight Office aPerture</t>
         </is>
       </c>
       <c r="C1128" s="5" t="inlineStr">
@@ -28788,18 +28867,18 @@
         </is>
       </c>
       <c r="D1128" s="4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1129">
       <c r="A1129" s="6" t="inlineStr">
         <is>
-          <t>7021097</t>
+          <t>7028368</t>
         </is>
       </c>
       <c r="B1129" t="inlineStr">
         <is>
-          <t>Infälld interiörarmatur aLight Office LED Tec rektangulär</t>
+          <t>LED-Panel Flex</t>
         </is>
       </c>
       <c r="C1129" t="inlineStr">
@@ -28808,18 +28887,18 @@
         </is>
       </c>
       <c r="D1129" s="6" t="n">
-        <v>1</v>
+        <v>39</v>
       </c>
     </row>
     <row r="1130">
       <c r="A1130" s="4" t="inlineStr">
         <is>
-          <t>7018286</t>
+          <t>7028369</t>
         </is>
       </c>
       <c r="B1130" s="5" t="inlineStr">
         <is>
-          <t>Infälld interiörarmatur aLight Office aPerture</t>
+          <t>LED-Panel Flex</t>
         </is>
       </c>
       <c r="C1130" s="5" t="inlineStr">
@@ -28828,18 +28907,18 @@
         </is>
       </c>
       <c r="D1130" s="4" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
     </row>
     <row r="1131">
       <c r="A1131" s="6" t="inlineStr">
         <is>
-          <t>7028368</t>
+          <t>7028001</t>
         </is>
       </c>
       <c r="B1131" t="inlineStr">
         <is>
-          <t>LED-Panel Flex</t>
+          <t>LED-Panel aLight Office Rektangulär</t>
         </is>
       </c>
       <c r="C1131" t="inlineStr">
@@ -28848,18 +28927,18 @@
         </is>
       </c>
       <c r="D1131" s="6" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1132">
       <c r="A1132" s="4" t="inlineStr">
         <is>
-          <t>7028369</t>
+          <t>7028002</t>
         </is>
       </c>
       <c r="B1132" s="5" t="inlineStr">
         <is>
-          <t>LED-Panel Flex</t>
+          <t>LED-Panel aLight Office Rektangulär</t>
         </is>
       </c>
       <c r="C1132" s="5" t="inlineStr">
@@ -28868,18 +28947,18 @@
         </is>
       </c>
       <c r="D1132" s="4" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1133">
       <c r="A1133" s="6" t="inlineStr">
         <is>
-          <t>7028001</t>
+          <t>7027999</t>
         </is>
       </c>
       <c r="B1133" t="inlineStr">
         <is>
-          <t>LED-Panel aLight Office Rektangulär</t>
+          <t>LED-panel aLight Office</t>
         </is>
       </c>
       <c r="C1133" t="inlineStr">
@@ -28888,18 +28967,18 @@
         </is>
       </c>
       <c r="D1133" s="6" t="n">
-        <v>0</v>
+        <v>418</v>
       </c>
     </row>
     <row r="1134">
       <c r="A1134" s="4" t="inlineStr">
         <is>
-          <t>7028002</t>
+          <t>7028000</t>
         </is>
       </c>
       <c r="B1134" s="5" t="inlineStr">
         <is>
-          <t>LED-Panel aLight Office Rektangulär</t>
+          <t>LED-panel aLight Office</t>
         </is>
       </c>
       <c r="C1134" s="5" t="inlineStr">
@@ -28908,47 +28987,7 @@
         </is>
       </c>
       <c r="D1134" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1135">
-      <c r="A1135" s="6" t="inlineStr">
-        <is>
-          <t>7027999</t>
-        </is>
-      </c>
-      <c r="B1135" t="inlineStr">
-        <is>
-          <t>LED-panel aLight Office</t>
-        </is>
-      </c>
-      <c r="C1135" t="inlineStr">
-        <is>
-          <t>a-collection</t>
-        </is>
-      </c>
-      <c r="D1135" s="6" t="n">
-        <v>412</v>
-      </c>
-    </row>
-    <row r="1136">
-      <c r="A1136" s="4" t="inlineStr">
-        <is>
-          <t>7028000</t>
-        </is>
-      </c>
-      <c r="B1136" s="5" t="inlineStr">
-        <is>
-          <t>LED-panel aLight Office</t>
-        </is>
-      </c>
-      <c r="C1136" s="5" t="inlineStr">
-        <is>
-          <t>a-collection</t>
-        </is>
-      </c>
-      <c r="D1136" s="4" t="n">
-        <v>360</v>
+        <v>353</v>
       </c>
     </row>
   </sheetData>

--- a/data/ahlsell_led_panel_inventory.xlsx
+++ b/data/ahlsell_led_panel_inventory.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y74"/>
+  <dimension ref="A1:Y75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -543,72 +543,72 @@
       </c>
       <c r="L1" s="3" t="inlineStr">
         <is>
+          <t>Bergdahls</t>
+        </is>
+      </c>
+      <c r="M1" s="3" t="inlineStr">
+        <is>
+          <t>Ensto</t>
+        </is>
+      </c>
+      <c r="N1" s="3" t="inlineStr">
+        <is>
+          <t>Siteco</t>
+        </is>
+      </c>
+      <c r="O1" s="3" t="inlineStr">
+        <is>
+          <t>Westal</t>
+        </is>
+      </c>
+      <c r="P1" s="3" t="inlineStr">
+        <is>
+          <t>ZG Lighting</t>
+        </is>
+      </c>
+      <c r="Q1" s="3" t="inlineStr">
+        <is>
+          <t>THORN</t>
+        </is>
+      </c>
+      <c r="R1" s="3" t="inlineStr">
+        <is>
+          <t>Nokalux</t>
+        </is>
+      </c>
+      <c r="S1" s="3" t="inlineStr">
+        <is>
+          <t>ANETA LIGHTING</t>
+        </is>
+      </c>
+      <c r="T1" s="3" t="inlineStr">
+        <is>
           <t>Legrand</t>
         </is>
       </c>
-      <c r="M1" s="3" t="inlineStr">
-        <is>
-          <t>Ensto</t>
-        </is>
-      </c>
-      <c r="N1" s="3" t="inlineStr">
+      <c r="U1" s="3" t="inlineStr">
+        <is>
+          <t>Easyform</t>
+        </is>
+      </c>
+      <c r="V1" s="3" t="inlineStr">
         <is>
           <t>Airam</t>
         </is>
       </c>
-      <c r="O1" s="3" t="inlineStr">
+      <c r="W1" s="3" t="inlineStr">
         <is>
           <t>Norwesco</t>
         </is>
       </c>
-      <c r="P1" s="3" t="inlineStr">
-        <is>
-          <t>Bergdahls</t>
-        </is>
-      </c>
-      <c r="Q1" s="3" t="inlineStr">
-        <is>
-          <t>Siteco</t>
-        </is>
-      </c>
-      <c r="R1" s="3" t="inlineStr">
-        <is>
-          <t>ANETA LIGHTING</t>
-        </is>
-      </c>
-      <c r="S1" s="3" t="inlineStr">
-        <is>
-          <t>Nokalux</t>
-        </is>
-      </c>
-      <c r="T1" s="3" t="inlineStr">
-        <is>
-          <t>Easyform</t>
-        </is>
-      </c>
-      <c r="U1" s="3" t="inlineStr">
-        <is>
-          <t>ZG Lighting</t>
-        </is>
-      </c>
-      <c r="V1" s="3" t="inlineStr">
+      <c r="X1" s="3" t="inlineStr">
         <is>
           <t>Black Box</t>
         </is>
       </c>
-      <c r="W1" s="3" t="inlineStr">
+      <c r="Y1" s="3" t="inlineStr">
         <is>
           <t>Philips</t>
-        </is>
-      </c>
-      <c r="X1" s="3" t="inlineStr">
-        <is>
-          <t>Westal</t>
-        </is>
-      </c>
-      <c r="Y1" s="3" t="inlineStr">
-        <is>
-          <t>THORN</t>
         </is>
       </c>
     </row>
@@ -6364,6 +6364,85 @@
         <v>0</v>
       </c>
       <c r="Y74" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B75" t="n">
+        <v>867</v>
+      </c>
+      <c r="C75" t="n">
+        <v>529</v>
+      </c>
+      <c r="D75" t="n">
+        <v>396</v>
+      </c>
+      <c r="E75" t="n">
+        <v>392</v>
+      </c>
+      <c r="F75" t="n">
+        <v>181</v>
+      </c>
+      <c r="G75" t="n">
+        <v>100</v>
+      </c>
+      <c r="H75" t="n">
+        <v>42</v>
+      </c>
+      <c r="I75" t="n">
+        <v>26</v>
+      </c>
+      <c r="J75" t="n">
+        <v>24</v>
+      </c>
+      <c r="K75" t="n">
+        <v>23</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0</v>
+      </c>
+      <c r="N75" t="n">
+        <v>0</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>0</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y75" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6405,7 +6484,7 @@
       </c>
       <c r="D1" s="3" t="inlineStr">
         <is>
-          <t>Lager (2026-09-18)</t>
+          <t>Lager (2026-09-19)</t>
         </is>
       </c>
     </row>
@@ -15046,7 +15125,7 @@
         </is>
       </c>
       <c r="D433" s="6" t="n">
-        <v>164</v>
+        <v>143</v>
       </c>
     </row>
     <row r="434">
@@ -15146,7 +15225,7 @@
         </is>
       </c>
       <c r="D438" s="4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="439">
@@ -25986,7 +26065,7 @@
         </is>
       </c>
       <c r="D980" s="4" t="n">
-        <v>149</v>
+        <v>135</v>
       </c>
     </row>
     <row r="981">
@@ -26006,7 +26085,7 @@
         </is>
       </c>
       <c r="D981" s="6" t="n">
-        <v>94</v>
+        <v>91</v>
       </c>
     </row>
     <row r="982">
@@ -26026,7 +26105,7 @@
         </is>
       </c>
       <c r="D982" s="4" t="n">
-        <v>134</v>
+        <v>154</v>
       </c>
     </row>
     <row r="983">
@@ -29146,7 +29225,7 @@
         </is>
       </c>
       <c r="D1138" s="4" t="n">
-        <v>451</v>
+        <v>433</v>
       </c>
     </row>
     <row r="1139">

--- a/data/ahlsell_led_panel_inventory.xlsx
+++ b/data/ahlsell_led_panel_inventory.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y77"/>
+  <dimension ref="A1:Y78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -533,82 +533,82 @@
       </c>
       <c r="J1" s="3" t="inlineStr">
         <is>
+          <t>Esylux</t>
+        </is>
+      </c>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
           <t>Ledvance</t>
         </is>
       </c>
-      <c r="K1" s="3" t="inlineStr">
+      <c r="L1" s="3" t="inlineStr">
+        <is>
+          <t>Airam</t>
+        </is>
+      </c>
+      <c r="M1" s="3" t="inlineStr">
+        <is>
+          <t>ZG Lighting</t>
+        </is>
+      </c>
+      <c r="N1" s="3" t="inlineStr">
+        <is>
+          <t>Philips</t>
+        </is>
+      </c>
+      <c r="O1" s="3" t="inlineStr">
+        <is>
+          <t>Ensto</t>
+        </is>
+      </c>
+      <c r="P1" s="3" t="inlineStr">
+        <is>
+          <t>Black Box</t>
+        </is>
+      </c>
+      <c r="Q1" s="3" t="inlineStr">
+        <is>
+          <t>ANETA LIGHTING</t>
+        </is>
+      </c>
+      <c r="R1" s="3" t="inlineStr">
+        <is>
+          <t>Legrand</t>
+        </is>
+      </c>
+      <c r="S1" s="3" t="inlineStr">
+        <is>
+          <t>Siteco</t>
+        </is>
+      </c>
+      <c r="T1" s="3" t="inlineStr">
         <is>
           <t>THORN</t>
         </is>
       </c>
-      <c r="L1" s="3" t="inlineStr">
-        <is>
-          <t>ZG Lighting</t>
-        </is>
-      </c>
-      <c r="M1" s="3" t="inlineStr">
-        <is>
-          <t>Legrand</t>
-        </is>
-      </c>
-      <c r="N1" s="3" t="inlineStr">
-        <is>
-          <t>Ensto</t>
-        </is>
-      </c>
-      <c r="O1" s="3" t="inlineStr">
+      <c r="U1" s="3" t="inlineStr">
+        <is>
+          <t>Westal</t>
+        </is>
+      </c>
+      <c r="V1" s="3" t="inlineStr">
         <is>
           <t>Easyform</t>
         </is>
       </c>
-      <c r="P1" s="3" t="inlineStr">
-        <is>
-          <t>Philips</t>
-        </is>
-      </c>
-      <c r="Q1" s="3" t="inlineStr">
-        <is>
-          <t>Siteco</t>
-        </is>
-      </c>
-      <c r="R1" s="3" t="inlineStr">
-        <is>
-          <t>Airam</t>
-        </is>
-      </c>
-      <c r="S1" s="3" t="inlineStr">
+      <c r="W1" s="3" t="inlineStr">
         <is>
           <t>Nokalux</t>
         </is>
       </c>
-      <c r="T1" s="3" t="inlineStr">
+      <c r="X1" s="3" t="inlineStr">
         <is>
           <t>Norwesco</t>
         </is>
       </c>
-      <c r="U1" s="3" t="inlineStr">
-        <is>
-          <t>Black Box</t>
-        </is>
-      </c>
-      <c r="V1" s="3" t="inlineStr">
+      <c r="Y1" s="3" t="inlineStr">
         <is>
           <t>Bergdahls</t>
-        </is>
-      </c>
-      <c r="W1" s="3" t="inlineStr">
-        <is>
-          <t>Westal</t>
-        </is>
-      </c>
-      <c r="X1" s="3" t="inlineStr">
-        <is>
-          <t>Esylux</t>
-        </is>
-      </c>
-      <c r="Y1" s="3" t="inlineStr">
-        <is>
-          <t>ANETA LIGHTING</t>
         </is>
       </c>
     </row>
@@ -643,11 +643,11 @@
         <v>33</v>
       </c>
       <c r="J2" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="K2" s="5" t="n">
         <v>17</v>
       </c>
-      <c r="K2" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="L2" s="5" t="n">
         <v>0</v>
       </c>
@@ -685,7 +685,7 @@
         <v>0</v>
       </c>
       <c r="X2" s="5" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="Y2" s="5" t="n">
         <v>0</v>
@@ -722,11 +722,11 @@
         <v>33</v>
       </c>
       <c r="J3" t="n">
+        <v>25</v>
+      </c>
+      <c r="K3" t="n">
         <v>17</v>
       </c>
-      <c r="K3" t="n">
-        <v>0</v>
-      </c>
       <c r="L3" t="n">
         <v>0</v>
       </c>
@@ -764,7 +764,7 @@
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="n">
         <v>0</v>
@@ -801,11 +801,11 @@
         <v>33</v>
       </c>
       <c r="J4" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="K4" s="5" t="n">
         <v>17</v>
       </c>
-      <c r="K4" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="L4" s="5" t="n">
         <v>0</v>
       </c>
@@ -843,7 +843,7 @@
         <v>0</v>
       </c>
       <c r="X4" s="5" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="Y4" s="5" t="n">
         <v>0</v>
@@ -880,11 +880,11 @@
         <v>33</v>
       </c>
       <c r="J5" t="n">
+        <v>24</v>
+      </c>
+      <c r="K5" t="n">
         <v>17</v>
       </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
       <c r="L5" t="n">
         <v>0</v>
       </c>
@@ -922,7 +922,7 @@
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
         <v>0</v>
@@ -959,11 +959,11 @@
         <v>33</v>
       </c>
       <c r="J6" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="K6" s="5" t="n">
         <v>17</v>
       </c>
-      <c r="K6" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="L6" s="5" t="n">
         <v>0</v>
       </c>
@@ -1001,7 +1001,7 @@
         <v>0</v>
       </c>
       <c r="X6" s="5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="Y6" s="5" t="n">
         <v>0</v>
@@ -1035,11 +1035,11 @@
         <v>33</v>
       </c>
       <c r="J7" t="n">
+        <v>24</v>
+      </c>
+      <c r="K7" t="n">
         <v>17</v>
       </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
       <c r="L7" t="n">
         <v>0</v>
       </c>
@@ -1077,7 +1077,7 @@
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
         <v>0</v>
@@ -1114,11 +1114,11 @@
         <v>33</v>
       </c>
       <c r="J8" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="K8" s="5" t="n">
         <v>17</v>
       </c>
-      <c r="K8" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="L8" s="5" t="n">
         <v>0</v>
       </c>
@@ -1156,7 +1156,7 @@
         <v>0</v>
       </c>
       <c r="X8" s="5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="Y8" s="5" t="n">
         <v>0</v>
@@ -1193,11 +1193,11 @@
         <v>33</v>
       </c>
       <c r="J9" t="n">
+        <v>24</v>
+      </c>
+      <c r="K9" t="n">
         <v>17</v>
       </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
       <c r="L9" t="n">
         <v>0</v>
       </c>
@@ -1235,7 +1235,7 @@
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
         <v>0</v>
@@ -1272,11 +1272,11 @@
         <v>33</v>
       </c>
       <c r="J10" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="K10" s="5" t="n">
         <v>17</v>
       </c>
-      <c r="K10" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="L10" s="5" t="n">
         <v>0</v>
       </c>
@@ -1314,7 +1314,7 @@
         <v>0</v>
       </c>
       <c r="X10" s="5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="Y10" s="5" t="n">
         <v>0</v>
@@ -1351,11 +1351,11 @@
         <v>33</v>
       </c>
       <c r="J11" t="n">
+        <v>24</v>
+      </c>
+      <c r="K11" t="n">
         <v>17</v>
       </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
       <c r="L11" t="n">
         <v>0</v>
       </c>
@@ -1393,7 +1393,7 @@
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
         <v>0</v>
@@ -1430,11 +1430,11 @@
         <v>33</v>
       </c>
       <c r="J12" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="K12" s="5" t="n">
         <v>17</v>
       </c>
-      <c r="K12" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="L12" s="5" t="n">
         <v>0</v>
       </c>
@@ -1472,7 +1472,7 @@
         <v>0</v>
       </c>
       <c r="X12" s="5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="Y12" s="5" t="n">
         <v>0</v>
@@ -1509,11 +1509,11 @@
         <v>33</v>
       </c>
       <c r="J13" t="n">
+        <v>24</v>
+      </c>
+      <c r="K13" t="n">
         <v>17</v>
       </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
       <c r="L13" t="n">
         <v>0</v>
       </c>
@@ -1551,7 +1551,7 @@
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
         <v>0</v>
@@ -1588,11 +1588,11 @@
         <v>33</v>
       </c>
       <c r="J14" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="K14" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="K14" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="L14" s="5" t="n">
         <v>0</v>
       </c>
@@ -1630,7 +1630,7 @@
         <v>0</v>
       </c>
       <c r="X14" s="5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="Y14" s="5" t="n">
         <v>0</v>
@@ -1667,11 +1667,11 @@
         <v>33</v>
       </c>
       <c r="J15" t="n">
+        <v>24</v>
+      </c>
+      <c r="K15" t="n">
         <v>17</v>
       </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
       <c r="L15" t="n">
         <v>0</v>
       </c>
@@ -1709,7 +1709,7 @@
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
         <v>0</v>
@@ -1746,11 +1746,11 @@
         <v>33</v>
       </c>
       <c r="J16" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="K16" s="5" t="n">
         <v>17</v>
       </c>
-      <c r="K16" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="L16" s="5" t="n">
         <v>0</v>
       </c>
@@ -1788,7 +1788,7 @@
         <v>0</v>
       </c>
       <c r="X16" s="5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="Y16" s="5" t="n">
         <v>0</v>
@@ -1825,11 +1825,11 @@
         <v>33</v>
       </c>
       <c r="J17" t="n">
+        <v>24</v>
+      </c>
+      <c r="K17" t="n">
         <v>17</v>
       </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
       <c r="L17" t="n">
         <v>0</v>
       </c>
@@ -1867,7 +1867,7 @@
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
         <v>0</v>
@@ -1904,11 +1904,11 @@
         <v>33</v>
       </c>
       <c r="J18" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="K18" s="5" t="n">
         <v>17</v>
       </c>
-      <c r="K18" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="L18" s="5" t="n">
         <v>0</v>
       </c>
@@ -1946,7 +1946,7 @@
         <v>0</v>
       </c>
       <c r="X18" s="5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="Y18" s="5" t="n">
         <v>0</v>
@@ -1983,11 +1983,11 @@
         <v>33</v>
       </c>
       <c r="J19" t="n">
+        <v>24</v>
+      </c>
+      <c r="K19" t="n">
         <v>17</v>
       </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
       <c r="L19" t="n">
         <v>0</v>
       </c>
@@ -2025,7 +2025,7 @@
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
         <v>0</v>
@@ -2062,11 +2062,11 @@
         <v>33</v>
       </c>
       <c r="J20" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="K20" s="5" t="n">
         <v>17</v>
       </c>
-      <c r="K20" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="L20" s="5" t="n">
         <v>0</v>
       </c>
@@ -2104,7 +2104,7 @@
         <v>0</v>
       </c>
       <c r="X20" s="5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="Y20" s="5" t="n">
         <v>0</v>
@@ -2141,11 +2141,11 @@
         <v>33</v>
       </c>
       <c r="J21" t="n">
+        <v>24</v>
+      </c>
+      <c r="K21" t="n">
         <v>17</v>
       </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
       <c r="L21" t="n">
         <v>0</v>
       </c>
@@ -2183,7 +2183,7 @@
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
         <v>0</v>
@@ -2220,11 +2220,11 @@
         <v>33</v>
       </c>
       <c r="J22" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="K22" s="5" t="n">
         <v>17</v>
       </c>
-      <c r="K22" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="L22" s="5" t="n">
         <v>0</v>
       </c>
@@ -2262,7 +2262,7 @@
         <v>0</v>
       </c>
       <c r="X22" s="5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="Y22" s="5" t="n">
         <v>0</v>
@@ -2299,11 +2299,11 @@
         <v>33</v>
       </c>
       <c r="J23" t="n">
+        <v>24</v>
+      </c>
+      <c r="K23" t="n">
         <v>17</v>
       </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
       <c r="L23" t="n">
         <v>0</v>
       </c>
@@ -2341,7 +2341,7 @@
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="Y23" t="n">
         <v>0</v>
@@ -2378,11 +2378,11 @@
         <v>33</v>
       </c>
       <c r="J24" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="K24" s="5" t="n">
         <v>17</v>
       </c>
-      <c r="K24" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="L24" s="5" t="n">
         <v>0</v>
       </c>
@@ -2420,7 +2420,7 @@
         <v>0</v>
       </c>
       <c r="X24" s="5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="Y24" s="5" t="n">
         <v>0</v>
@@ -2457,11 +2457,11 @@
         <v>33</v>
       </c>
       <c r="J25" t="n">
+        <v>24</v>
+      </c>
+      <c r="K25" t="n">
         <v>17</v>
       </c>
-      <c r="K25" t="n">
-        <v>0</v>
-      </c>
       <c r="L25" t="n">
         <v>0</v>
       </c>
@@ -2499,7 +2499,7 @@
         <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="Y25" t="n">
         <v>0</v>
@@ -2536,11 +2536,11 @@
         <v>33</v>
       </c>
       <c r="J26" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="K26" s="5" t="n">
         <v>17</v>
       </c>
-      <c r="K26" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="L26" s="5" t="n">
         <v>0</v>
       </c>
@@ -2578,7 +2578,7 @@
         <v>0</v>
       </c>
       <c r="X26" s="5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="Y26" s="5" t="n">
         <v>0</v>
@@ -2615,11 +2615,11 @@
         <v>33</v>
       </c>
       <c r="J27" t="n">
+        <v>24</v>
+      </c>
+      <c r="K27" t="n">
         <v>17</v>
       </c>
-      <c r="K27" t="n">
-        <v>0</v>
-      </c>
       <c r="L27" t="n">
         <v>0</v>
       </c>
@@ -2657,7 +2657,7 @@
         <v>0</v>
       </c>
       <c r="X27" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="Y27" t="n">
         <v>0</v>
@@ -2694,10 +2694,10 @@
         <v>33</v>
       </c>
       <c r="J28" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" s="5" t="n">
         <v>17</v>
-      </c>
-      <c r="K28" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="L28" s="5" t="n">
         <v>0</v>
@@ -2773,11 +2773,11 @@
         <v>33</v>
       </c>
       <c r="J29" t="n">
+        <v>24</v>
+      </c>
+      <c r="K29" t="n">
         <v>17</v>
       </c>
-      <c r="K29" t="n">
-        <v>0</v>
-      </c>
       <c r="L29" t="n">
         <v>0</v>
       </c>
@@ -2815,7 +2815,7 @@
         <v>0</v>
       </c>
       <c r="X29" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="Y29" t="n">
         <v>0</v>
@@ -2852,11 +2852,11 @@
         <v>33</v>
       </c>
       <c r="J30" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="K30" s="5" t="n">
         <v>17</v>
       </c>
-      <c r="K30" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="L30" s="5" t="n">
         <v>0</v>
       </c>
@@ -2894,7 +2894,7 @@
         <v>0</v>
       </c>
       <c r="X30" s="5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="Y30" s="5" t="n">
         <v>0</v>
@@ -2931,11 +2931,11 @@
         <v>33</v>
       </c>
       <c r="J31" t="n">
+        <v>24</v>
+      </c>
+      <c r="K31" t="n">
         <v>17</v>
       </c>
-      <c r="K31" t="n">
-        <v>0</v>
-      </c>
       <c r="L31" t="n">
         <v>0</v>
       </c>
@@ -2973,7 +2973,7 @@
         <v>0</v>
       </c>
       <c r="X31" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="Y31" t="n">
         <v>0</v>
@@ -3010,11 +3010,11 @@
         <v>33</v>
       </c>
       <c r="J32" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="K32" s="5" t="n">
         <v>17</v>
       </c>
-      <c r="K32" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="L32" s="5" t="n">
         <v>0</v>
       </c>
@@ -3052,7 +3052,7 @@
         <v>0</v>
       </c>
       <c r="X32" s="5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="Y32" s="5" t="n">
         <v>0</v>
@@ -3089,11 +3089,11 @@
         <v>33</v>
       </c>
       <c r="J33" t="n">
+        <v>24</v>
+      </c>
+      <c r="K33" t="n">
         <v>17</v>
       </c>
-      <c r="K33" t="n">
-        <v>0</v>
-      </c>
       <c r="L33" t="n">
         <v>0</v>
       </c>
@@ -3131,7 +3131,7 @@
         <v>0</v>
       </c>
       <c r="X33" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="Y33" t="n">
         <v>0</v>
@@ -3168,11 +3168,11 @@
         <v>33</v>
       </c>
       <c r="J34" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="K34" s="5" t="n">
         <v>17</v>
       </c>
-      <c r="K34" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="L34" s="5" t="n">
         <v>0</v>
       </c>
@@ -3210,7 +3210,7 @@
         <v>0</v>
       </c>
       <c r="X34" s="5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="Y34" s="5" t="n">
         <v>0</v>
@@ -3247,11 +3247,11 @@
         <v>33</v>
       </c>
       <c r="J35" t="n">
+        <v>24</v>
+      </c>
+      <c r="K35" t="n">
         <v>17</v>
       </c>
-      <c r="K35" t="n">
-        <v>0</v>
-      </c>
       <c r="L35" t="n">
         <v>0</v>
       </c>
@@ -3289,7 +3289,7 @@
         <v>0</v>
       </c>
       <c r="X35" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="Y35" t="n">
         <v>0</v>
@@ -3326,11 +3326,11 @@
         <v>33</v>
       </c>
       <c r="J36" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="K36" s="5" t="n">
         <v>17</v>
       </c>
-      <c r="K36" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="L36" s="5" t="n">
         <v>0</v>
       </c>
@@ -3368,7 +3368,7 @@
         <v>0</v>
       </c>
       <c r="X36" s="5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="Y36" s="5" t="n">
         <v>0</v>
@@ -3405,11 +3405,11 @@
         <v>33</v>
       </c>
       <c r="J37" t="n">
+        <v>24</v>
+      </c>
+      <c r="K37" t="n">
         <v>17</v>
       </c>
-      <c r="K37" t="n">
-        <v>0</v>
-      </c>
       <c r="L37" t="n">
         <v>0</v>
       </c>
@@ -3447,7 +3447,7 @@
         <v>0</v>
       </c>
       <c r="X37" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="Y37" t="n">
         <v>0</v>
@@ -3484,11 +3484,11 @@
         <v>33</v>
       </c>
       <c r="J38" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="K38" s="5" t="n">
         <v>17</v>
       </c>
-      <c r="K38" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="L38" s="5" t="n">
         <v>0</v>
       </c>
@@ -3526,7 +3526,7 @@
         <v>0</v>
       </c>
       <c r="X38" s="5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="Y38" s="5" t="n">
         <v>0</v>
@@ -3563,11 +3563,11 @@
         <v>33</v>
       </c>
       <c r="J39" t="n">
+        <v>24</v>
+      </c>
+      <c r="K39" t="n">
         <v>17</v>
       </c>
-      <c r="K39" t="n">
-        <v>0</v>
-      </c>
       <c r="L39" t="n">
         <v>0</v>
       </c>
@@ -3605,7 +3605,7 @@
         <v>0</v>
       </c>
       <c r="X39" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="Y39" t="n">
         <v>0</v>
@@ -3642,11 +3642,11 @@
         <v>33</v>
       </c>
       <c r="J40" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="K40" s="5" t="n">
         <v>17</v>
       </c>
-      <c r="K40" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="L40" s="5" t="n">
         <v>0</v>
       </c>
@@ -3684,7 +3684,7 @@
         <v>0</v>
       </c>
       <c r="X40" s="5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="Y40" s="5" t="n">
         <v>0</v>
@@ -3721,11 +3721,11 @@
         <v>33</v>
       </c>
       <c r="J41" t="n">
+        <v>24</v>
+      </c>
+      <c r="K41" t="n">
         <v>17</v>
       </c>
-      <c r="K41" t="n">
-        <v>0</v>
-      </c>
       <c r="L41" t="n">
         <v>0</v>
       </c>
@@ -3763,7 +3763,7 @@
         <v>0</v>
       </c>
       <c r="X41" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="Y41" t="n">
         <v>0</v>
@@ -3800,11 +3800,11 @@
         <v>33</v>
       </c>
       <c r="J42" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="K42" s="5" t="n">
         <v>17</v>
       </c>
-      <c r="K42" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="L42" s="5" t="n">
         <v>0</v>
       </c>
@@ -3842,7 +3842,7 @@
         <v>0</v>
       </c>
       <c r="X42" s="5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="Y42" s="5" t="n">
         <v>0</v>
@@ -3879,11 +3879,11 @@
         <v>33</v>
       </c>
       <c r="J43" t="n">
+        <v>24</v>
+      </c>
+      <c r="K43" t="n">
         <v>17</v>
       </c>
-      <c r="K43" t="n">
-        <v>0</v>
-      </c>
       <c r="L43" t="n">
         <v>0</v>
       </c>
@@ -3921,7 +3921,7 @@
         <v>0</v>
       </c>
       <c r="X43" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="Y43" t="n">
         <v>0</v>
@@ -3958,11 +3958,11 @@
         <v>33</v>
       </c>
       <c r="J44" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="K44" s="5" t="n">
         <v>17</v>
       </c>
-      <c r="K44" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="L44" s="5" t="n">
         <v>0</v>
       </c>
@@ -4000,7 +4000,7 @@
         <v>0</v>
       </c>
       <c r="X44" s="5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="Y44" s="5" t="n">
         <v>0</v>
@@ -4037,11 +4037,11 @@
         <v>33</v>
       </c>
       <c r="J45" t="n">
+        <v>24</v>
+      </c>
+      <c r="K45" t="n">
         <v>17</v>
       </c>
-      <c r="K45" t="n">
-        <v>0</v>
-      </c>
       <c r="L45" t="n">
         <v>0</v>
       </c>
@@ -4079,7 +4079,7 @@
         <v>0</v>
       </c>
       <c r="X45" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="Y45" t="n">
         <v>0</v>
@@ -4116,11 +4116,11 @@
         <v>33</v>
       </c>
       <c r="J46" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="K46" s="5" t="n">
         <v>17</v>
       </c>
-      <c r="K46" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="L46" s="5" t="n">
         <v>0</v>
       </c>
@@ -4158,7 +4158,7 @@
         <v>0</v>
       </c>
       <c r="X46" s="5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="Y46" s="5" t="n">
         <v>0</v>
@@ -4195,11 +4195,11 @@
         <v>33</v>
       </c>
       <c r="J47" t="n">
+        <v>24</v>
+      </c>
+      <c r="K47" t="n">
         <v>17</v>
       </c>
-      <c r="K47" t="n">
-        <v>0</v>
-      </c>
       <c r="L47" t="n">
         <v>0</v>
       </c>
@@ -4237,7 +4237,7 @@
         <v>0</v>
       </c>
       <c r="X47" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="Y47" t="n">
         <v>0</v>
@@ -4274,11 +4274,11 @@
         <v>33</v>
       </c>
       <c r="J48" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="K48" s="5" t="n">
         <v>17</v>
       </c>
-      <c r="K48" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="L48" s="5" t="n">
         <v>0</v>
       </c>
@@ -4316,7 +4316,7 @@
         <v>0</v>
       </c>
       <c r="X48" s="5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="Y48" s="5" t="n">
         <v>0</v>
@@ -4353,11 +4353,11 @@
         <v>33</v>
       </c>
       <c r="J49" t="n">
+        <v>24</v>
+      </c>
+      <c r="K49" t="n">
         <v>17</v>
       </c>
-      <c r="K49" t="n">
-        <v>0</v>
-      </c>
       <c r="L49" t="n">
         <v>0</v>
       </c>
@@ -4395,7 +4395,7 @@
         <v>0</v>
       </c>
       <c r="X49" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="Y49" t="n">
         <v>0</v>
@@ -4432,11 +4432,11 @@
         <v>33</v>
       </c>
       <c r="J50" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="K50" s="5" t="n">
         <v>17</v>
       </c>
-      <c r="K50" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="L50" s="5" t="n">
         <v>0</v>
       </c>
@@ -4474,7 +4474,7 @@
         <v>0</v>
       </c>
       <c r="X50" s="5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="Y50" s="5" t="n">
         <v>0</v>
@@ -4511,11 +4511,11 @@
         <v>33</v>
       </c>
       <c r="J51" t="n">
+        <v>24</v>
+      </c>
+      <c r="K51" t="n">
         <v>17</v>
       </c>
-      <c r="K51" t="n">
-        <v>0</v>
-      </c>
       <c r="L51" t="n">
         <v>0</v>
       </c>
@@ -4553,7 +4553,7 @@
         <v>0</v>
       </c>
       <c r="X51" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="Y51" t="n">
         <v>0</v>
@@ -4590,11 +4590,11 @@
         <v>30</v>
       </c>
       <c r="J52" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="K52" s="5" t="n">
         <v>17</v>
       </c>
-      <c r="K52" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="L52" s="5" t="n">
         <v>0</v>
       </c>
@@ -4632,7 +4632,7 @@
         <v>0</v>
       </c>
       <c r="X52" s="5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="Y52" s="5" t="n">
         <v>0</v>
@@ -4669,11 +4669,11 @@
         <v>30</v>
       </c>
       <c r="J53" t="n">
+        <v>24</v>
+      </c>
+      <c r="K53" t="n">
         <v>17</v>
       </c>
-      <c r="K53" t="n">
-        <v>0</v>
-      </c>
       <c r="L53" t="n">
         <v>0</v>
       </c>
@@ -4711,7 +4711,7 @@
         <v>0</v>
       </c>
       <c r="X53" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="Y53" t="n">
         <v>0</v>
@@ -4748,11 +4748,11 @@
         <v>30</v>
       </c>
       <c r="J54" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="K54" s="5" t="n">
         <v>17</v>
       </c>
-      <c r="K54" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="L54" s="5" t="n">
         <v>0</v>
       </c>
@@ -4790,7 +4790,7 @@
         <v>0</v>
       </c>
       <c r="X54" s="5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="Y54" s="5" t="n">
         <v>0</v>
@@ -4827,11 +4827,11 @@
         <v>30</v>
       </c>
       <c r="J55" t="n">
+        <v>24</v>
+      </c>
+      <c r="K55" t="n">
         <v>17</v>
       </c>
-      <c r="K55" t="n">
-        <v>0</v>
-      </c>
       <c r="L55" t="n">
         <v>0</v>
       </c>
@@ -4869,7 +4869,7 @@
         <v>0</v>
       </c>
       <c r="X55" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="Y55" t="n">
         <v>0</v>
@@ -4906,11 +4906,11 @@
         <v>30</v>
       </c>
       <c r="J56" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="K56" s="5" t="n">
         <v>17</v>
       </c>
-      <c r="K56" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="L56" s="5" t="n">
         <v>0</v>
       </c>
@@ -4948,7 +4948,7 @@
         <v>0</v>
       </c>
       <c r="X56" s="5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="Y56" s="5" t="n">
         <v>0</v>
@@ -4985,11 +4985,11 @@
         <v>24</v>
       </c>
       <c r="J57" t="n">
+        <v>24</v>
+      </c>
+      <c r="K57" t="n">
         <v>22</v>
       </c>
-      <c r="K57" t="n">
-        <v>0</v>
-      </c>
       <c r="L57" t="n">
         <v>0</v>
       </c>
@@ -5027,7 +5027,7 @@
         <v>0</v>
       </c>
       <c r="X57" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="Y57" t="n">
         <v>0</v>
@@ -5064,11 +5064,11 @@
         <v>26</v>
       </c>
       <c r="J58" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="K58" s="5" t="n">
         <v>22</v>
       </c>
-      <c r="K58" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="L58" s="5" t="n">
         <v>0</v>
       </c>
@@ -5106,7 +5106,7 @@
         <v>0</v>
       </c>
       <c r="X58" s="5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="Y58" s="5" t="n">
         <v>0</v>
@@ -5143,11 +5143,11 @@
         <v>26</v>
       </c>
       <c r="J59" t="n">
+        <v>24</v>
+      </c>
+      <c r="K59" t="n">
         <v>16</v>
       </c>
-      <c r="K59" t="n">
-        <v>0</v>
-      </c>
       <c r="L59" t="n">
         <v>0</v>
       </c>
@@ -5185,7 +5185,7 @@
         <v>0</v>
       </c>
       <c r="X59" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="Y59" t="n">
         <v>0</v>
@@ -5222,11 +5222,11 @@
         <v>23</v>
       </c>
       <c r="J60" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="K60" s="5" t="n">
         <v>16</v>
       </c>
-      <c r="K60" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="L60" s="5" t="n">
         <v>0</v>
       </c>
@@ -5264,7 +5264,7 @@
         <v>0</v>
       </c>
       <c r="X60" s="5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="Y60" s="5" t="n">
         <v>0</v>
@@ -5301,11 +5301,11 @@
         <v>29</v>
       </c>
       <c r="J61" t="n">
+        <v>24</v>
+      </c>
+      <c r="K61" t="n">
         <v>16</v>
       </c>
-      <c r="K61" t="n">
-        <v>0</v>
-      </c>
       <c r="L61" t="n">
         <v>0</v>
       </c>
@@ -5343,7 +5343,7 @@
         <v>0</v>
       </c>
       <c r="X61" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="Y61" t="n">
         <v>0</v>
@@ -5380,11 +5380,11 @@
         <v>29</v>
       </c>
       <c r="J62" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="K62" s="5" t="n">
         <v>16</v>
       </c>
-      <c r="K62" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="L62" s="5" t="n">
         <v>0</v>
       </c>
@@ -5422,7 +5422,7 @@
         <v>0</v>
       </c>
       <c r="X62" s="5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="Y62" s="5" t="n">
         <v>0</v>
@@ -5459,11 +5459,11 @@
         <v>29</v>
       </c>
       <c r="J63" t="n">
+        <v>24</v>
+      </c>
+      <c r="K63" t="n">
         <v>16</v>
       </c>
-      <c r="K63" t="n">
-        <v>0</v>
-      </c>
       <c r="L63" t="n">
         <v>0</v>
       </c>
@@ -5501,7 +5501,7 @@
         <v>0</v>
       </c>
       <c r="X63" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="Y63" t="n">
         <v>0</v>
@@ -5538,11 +5538,11 @@
         <v>20</v>
       </c>
       <c r="J64" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="K64" s="5" t="n">
         <v>16</v>
       </c>
-      <c r="K64" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="L64" s="5" t="n">
         <v>0</v>
       </c>
@@ -5580,7 +5580,7 @@
         <v>0</v>
       </c>
       <c r="X64" s="5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="Y64" s="5" t="n">
         <v>0</v>
@@ -5617,11 +5617,11 @@
         <v>20</v>
       </c>
       <c r="J65" t="n">
+        <v>24</v>
+      </c>
+      <c r="K65" t="n">
         <v>21</v>
       </c>
-      <c r="K65" t="n">
-        <v>0</v>
-      </c>
       <c r="L65" t="n">
         <v>0</v>
       </c>
@@ -5659,7 +5659,7 @@
         <v>0</v>
       </c>
       <c r="X65" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="Y65" t="n">
         <v>0</v>
@@ -5696,11 +5696,11 @@
         <v>26</v>
       </c>
       <c r="J66" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="K66" s="5" t="n">
         <v>21</v>
       </c>
-      <c r="K66" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="L66" s="5" t="n">
         <v>0</v>
       </c>
@@ -5738,7 +5738,7 @@
         <v>0</v>
       </c>
       <c r="X66" s="5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="Y66" s="5" t="n">
         <v>0</v>
@@ -5774,12 +5774,9 @@
       <c r="I67" t="n">
         <v>26</v>
       </c>
-      <c r="J67" t="n">
+      <c r="K67" t="n">
         <v>21</v>
       </c>
-      <c r="K67" t="n">
-        <v>0</v>
-      </c>
       <c r="L67" t="n">
         <v>0</v>
       </c>
@@ -5814,6 +5811,9 @@
         <v>0</v>
       </c>
       <c r="W67" t="n">
+        <v>0</v>
+      </c>
+      <c r="X67" t="n">
         <v>0</v>
       </c>
       <c r="Y67" t="n">
@@ -5851,11 +5851,11 @@
         <v>26</v>
       </c>
       <c r="J68" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="K68" s="5" t="n">
         <v>21</v>
       </c>
-      <c r="K68" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="L68" s="5" t="n">
         <v>0</v>
       </c>
@@ -5893,7 +5893,7 @@
         <v>0</v>
       </c>
       <c r="X68" s="5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="Y68" s="5" t="n">
         <v>0</v>
@@ -5926,12 +5926,9 @@
       <c r="I69" t="n">
         <v>26</v>
       </c>
-      <c r="J69" t="n">
+      <c r="K69" t="n">
         <v>21</v>
       </c>
-      <c r="K69" t="n">
-        <v>0</v>
-      </c>
       <c r="L69" t="n">
         <v>0</v>
       </c>
@@ -5966,6 +5963,9 @@
         <v>0</v>
       </c>
       <c r="W69" t="n">
+        <v>0</v>
+      </c>
+      <c r="X69" t="n">
         <v>0</v>
       </c>
       <c r="Y69" t="n">
@@ -6003,11 +6003,11 @@
         <v>26</v>
       </c>
       <c r="J70" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="K70" s="5" t="n">
         <v>21</v>
       </c>
-      <c r="K70" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="L70" s="5" t="n">
         <v>0</v>
       </c>
@@ -6045,7 +6045,7 @@
         <v>0</v>
       </c>
       <c r="X70" s="5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="Y70" s="5" t="n">
         <v>0</v>
@@ -6082,11 +6082,11 @@
         <v>26</v>
       </c>
       <c r="J71" t="n">
+        <v>24</v>
+      </c>
+      <c r="K71" t="n">
         <v>21</v>
       </c>
-      <c r="K71" t="n">
-        <v>0</v>
-      </c>
       <c r="L71" t="n">
         <v>0</v>
       </c>
@@ -6124,7 +6124,7 @@
         <v>0</v>
       </c>
       <c r="X71" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="Y71" t="n">
         <v>0</v>
@@ -6161,11 +6161,11 @@
         <v>26</v>
       </c>
       <c r="J72" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="K72" s="5" t="n">
         <v>21</v>
       </c>
-      <c r="K72" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="L72" s="5" t="n">
         <v>0</v>
       </c>
@@ -6203,7 +6203,7 @@
         <v>0</v>
       </c>
       <c r="X72" s="5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="Y72" s="5" t="n">
         <v>0</v>
@@ -6240,11 +6240,11 @@
         <v>26</v>
       </c>
       <c r="J73" t="n">
+        <v>24</v>
+      </c>
+      <c r="K73" t="n">
         <v>19</v>
       </c>
-      <c r="K73" t="n">
-        <v>0</v>
-      </c>
       <c r="L73" t="n">
         <v>0</v>
       </c>
@@ -6282,7 +6282,7 @@
         <v>0</v>
       </c>
       <c r="X73" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="Y73" t="n">
         <v>0</v>
@@ -6319,11 +6319,11 @@
         <v>26</v>
       </c>
       <c r="J74" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="K74" s="5" t="n">
         <v>23</v>
       </c>
-      <c r="K74" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="L74" s="5" t="n">
         <v>0</v>
       </c>
@@ -6361,7 +6361,7 @@
         <v>0</v>
       </c>
       <c r="X74" s="5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="Y74" s="5" t="n">
         <v>0</v>
@@ -6398,11 +6398,11 @@
         <v>26</v>
       </c>
       <c r="J75" t="n">
+        <v>24</v>
+      </c>
+      <c r="K75" t="n">
         <v>23</v>
       </c>
-      <c r="K75" t="n">
-        <v>0</v>
-      </c>
       <c r="L75" t="n">
         <v>0</v>
       </c>
@@ -6440,7 +6440,7 @@
         <v>0</v>
       </c>
       <c r="X75" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="Y75" t="n">
         <v>0</v>
@@ -6477,37 +6477,37 @@
         <v>26</v>
       </c>
       <c r="J76" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="K76" s="5" t="n">
         <v>23</v>
       </c>
-      <c r="K76" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="L76" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="M76" s="5" t="n"/>
+      <c r="M76" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="N76" s="5" t="n">
         <v>0</v>
       </c>
       <c r="O76" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="P76" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="P76" s="5" t="n"/>
       <c r="Q76" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="R76" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="R76" s="5" t="n"/>
       <c r="S76" s="5" t="n">
         <v>0</v>
       </c>
       <c r="T76" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="U76" s="5" t="n"/>
+      <c r="U76" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="V76" s="5" t="n">
         <v>0</v>
       </c>
@@ -6515,7 +6515,7 @@
         <v>0</v>
       </c>
       <c r="X76" s="5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="Y76" s="5" t="n">
         <v>0</v>
@@ -6551,12 +6551,9 @@
       <c r="I77" t="n">
         <v>26</v>
       </c>
-      <c r="J77" t="n">
+      <c r="K77" t="n">
         <v>23</v>
       </c>
-      <c r="K77" t="n">
-        <v>0</v>
-      </c>
       <c r="L77" t="n">
         <v>0</v>
       </c>
@@ -6593,7 +6590,89 @@
       <c r="W77" t="n">
         <v>0</v>
       </c>
+      <c r="X77" t="n">
+        <v>0</v>
+      </c>
       <c r="Y77" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B78" s="5" t="n">
+        <v>892</v>
+      </c>
+      <c r="C78" s="5" t="n">
+        <v>526</v>
+      </c>
+      <c r="D78" s="5" t="n">
+        <v>396</v>
+      </c>
+      <c r="E78" s="5" t="n">
+        <v>369</v>
+      </c>
+      <c r="F78" s="5" t="n">
+        <v>184</v>
+      </c>
+      <c r="G78" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="H78" s="5" t="n">
+        <v>42</v>
+      </c>
+      <c r="I78" s="5" t="n">
+        <v>26</v>
+      </c>
+      <c r="J78" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="K78" s="5" t="n">
+        <v>23</v>
+      </c>
+      <c r="L78" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M78" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N78" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O78" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P78" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q78" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R78" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S78" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T78" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U78" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V78" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W78" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X78" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y78" s="5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6635,7 +6714,7 @@
       </c>
       <c r="D1" s="3" t="inlineStr">
         <is>
-          <t>Lager (2026-09-21)</t>
+          <t>Lager (2026-09-22)</t>
         </is>
       </c>
     </row>
@@ -6656,7 +6735,7 @@
         </is>
       </c>
       <c r="D2" s="4" t="n">
-        <v>529</v>
+        <v>526</v>
       </c>
     </row>
     <row r="3">
@@ -11842,12 +11921,12 @@
     <row r="262">
       <c r="A262" s="4" t="inlineStr">
         <is>
-          <t>7013678</t>
+          <t>7011676</t>
         </is>
       </c>
       <c r="B262" s="5" t="inlineStr">
         <is>
-          <t>Infälld Interiörarmatur LED DPML Tunable White</t>
+          <t>Infälld interiörarmatur Diana Flat LED 300x300</t>
         </is>
       </c>
       <c r="C262" s="5" t="inlineStr">
@@ -11862,7 +11941,7 @@
     <row r="263">
       <c r="A263" s="6" t="inlineStr">
         <is>
-          <t>7011676</t>
+          <t>7011677</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -11882,12 +11961,12 @@
     <row r="264">
       <c r="A264" s="4" t="inlineStr">
         <is>
-          <t>7011677</t>
+          <t>7013193</t>
         </is>
       </c>
       <c r="B264" s="5" t="inlineStr">
         <is>
-          <t>Infälld interiörarmatur Diana Flat LED 300x300</t>
+          <t>Infälld interiörarmatur Diana Flat LED 600x600</t>
         </is>
       </c>
       <c r="C264" s="5" t="inlineStr">
@@ -11902,7 +11981,7 @@
     <row r="265">
       <c r="A265" s="6" t="inlineStr">
         <is>
-          <t>7013193</t>
+          <t>7013194</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
@@ -11922,7 +12001,7 @@
     <row r="266">
       <c r="A266" s="4" t="inlineStr">
         <is>
-          <t>7013194</t>
+          <t>7018335</t>
         </is>
       </c>
       <c r="B266" s="5" t="inlineStr">
@@ -11942,7 +12021,7 @@
     <row r="267">
       <c r="A267" s="6" t="inlineStr">
         <is>
-          <t>7018335</t>
+          <t>7018336</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
@@ -11962,7 +12041,7 @@
     <row r="268">
       <c r="A268" s="4" t="inlineStr">
         <is>
-          <t>7018336</t>
+          <t>7018337</t>
         </is>
       </c>
       <c r="B268" s="5" t="inlineStr">
@@ -11982,7 +12061,7 @@
     <row r="269">
       <c r="A269" s="6" t="inlineStr">
         <is>
-          <t>7018337</t>
+          <t>7018338</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
@@ -12002,7 +12081,7 @@
     <row r="270">
       <c r="A270" s="4" t="inlineStr">
         <is>
-          <t>7018338</t>
+          <t>7018339</t>
         </is>
       </c>
       <c r="B270" s="5" t="inlineStr">
@@ -12022,7 +12101,7 @@
     <row r="271">
       <c r="A271" s="6" t="inlineStr">
         <is>
-          <t>7018339</t>
+          <t>7018340</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
@@ -12042,7 +12121,7 @@
     <row r="272">
       <c r="A272" s="4" t="inlineStr">
         <is>
-          <t>7018340</t>
+          <t>7018341</t>
         </is>
       </c>
       <c r="B272" s="5" t="inlineStr">
@@ -12062,7 +12141,7 @@
     <row r="273">
       <c r="A273" s="6" t="inlineStr">
         <is>
-          <t>7018341</t>
+          <t>7018342</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
@@ -12082,12 +12161,12 @@
     <row r="274">
       <c r="A274" s="4" t="inlineStr">
         <is>
-          <t>7018342</t>
+          <t>7017462</t>
         </is>
       </c>
       <c r="B274" s="5" t="inlineStr">
         <is>
-          <t>Infälld interiörarmatur Diana Flat LED 600x600</t>
+          <t>Interiörarmatur LED Velox Deco Fyrkantig</t>
         </is>
       </c>
       <c r="C274" s="5" t="inlineStr">
@@ -12102,7 +12181,7 @@
     <row r="275">
       <c r="A275" s="6" t="inlineStr">
         <is>
-          <t>7017462</t>
+          <t>7018858</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
@@ -12122,7 +12201,7 @@
     <row r="276">
       <c r="A276" s="4" t="inlineStr">
         <is>
-          <t>7018858</t>
+          <t>7018877</t>
         </is>
       </c>
       <c r="B276" s="5" t="inlineStr">
@@ -12142,7 +12221,7 @@
     <row r="277">
       <c r="A277" s="6" t="inlineStr">
         <is>
-          <t>7018877</t>
+          <t>7018878</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
@@ -12162,12 +12241,12 @@
     <row r="278">
       <c r="A278" s="4" t="inlineStr">
         <is>
-          <t>7018878</t>
+          <t>7017460</t>
         </is>
       </c>
       <c r="B278" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur LED Velox Deco Fyrkantig</t>
+          <t>Interiörarmatur LED Velox Deco Rund</t>
         </is>
       </c>
       <c r="C278" s="5" t="inlineStr">
@@ -12182,7 +12261,7 @@
     <row r="279">
       <c r="A279" s="6" t="inlineStr">
         <is>
-          <t>7017460</t>
+          <t>7017464</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
@@ -12202,7 +12281,7 @@
     <row r="280">
       <c r="A280" s="4" t="inlineStr">
         <is>
-          <t>7017464</t>
+          <t>7017466</t>
         </is>
       </c>
       <c r="B280" s="5" t="inlineStr">
@@ -12222,7 +12301,7 @@
     <row r="281">
       <c r="A281" s="6" t="inlineStr">
         <is>
-          <t>7017466</t>
+          <t>7018857</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
@@ -12242,7 +12321,7 @@
     <row r="282">
       <c r="A282" s="4" t="inlineStr">
         <is>
-          <t>7018857</t>
+          <t>7018859</t>
         </is>
       </c>
       <c r="B282" s="5" t="inlineStr">
@@ -12262,7 +12341,7 @@
     <row r="283">
       <c r="A283" s="6" t="inlineStr">
         <is>
-          <t>7018859</t>
+          <t>7018860</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
@@ -12282,7 +12361,7 @@
     <row r="284">
       <c r="A284" s="4" t="inlineStr">
         <is>
-          <t>7018860</t>
+          <t>7018874</t>
         </is>
       </c>
       <c r="B284" s="5" t="inlineStr">
@@ -12302,7 +12381,7 @@
     <row r="285">
       <c r="A285" s="6" t="inlineStr">
         <is>
-          <t>7018874</t>
+          <t>7018875</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
@@ -12322,7 +12401,7 @@
     <row r="286">
       <c r="A286" s="4" t="inlineStr">
         <is>
-          <t>7018875</t>
+          <t>7018876</t>
         </is>
       </c>
       <c r="B286" s="5" t="inlineStr">
@@ -12342,7 +12421,7 @@
     <row r="287">
       <c r="A287" s="6" t="inlineStr">
         <is>
-          <t>7018876</t>
+          <t>7018879</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
@@ -12362,7 +12441,7 @@
     <row r="288">
       <c r="A288" s="4" t="inlineStr">
         <is>
-          <t>7018879</t>
+          <t>7018880</t>
         </is>
       </c>
       <c r="B288" s="5" t="inlineStr">
@@ -12382,7 +12461,7 @@
     <row r="289">
       <c r="A289" s="6" t="inlineStr">
         <is>
-          <t>7018880</t>
+          <t>7018881</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
@@ -12402,7 +12481,7 @@
     <row r="290">
       <c r="A290" s="4" t="inlineStr">
         <is>
-          <t>7018881</t>
+          <t>7018882</t>
         </is>
       </c>
       <c r="B290" s="5" t="inlineStr">
@@ -12422,12 +12501,12 @@
     <row r="291">
       <c r="A291" s="6" t="inlineStr">
         <is>
-          <t>7018882</t>
+          <t>7015430</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>Interiörarmatur LED Velox Deco Rund</t>
+          <t>Interiörarmatur LED Velox Infälld rund</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
@@ -12442,7 +12521,7 @@
     <row r="292">
       <c r="A292" s="4" t="inlineStr">
         <is>
-          <t>7015430</t>
+          <t>7015431</t>
         </is>
       </c>
       <c r="B292" s="5" t="inlineStr">
@@ -12462,7 +12541,7 @@
     <row r="293">
       <c r="A293" s="6" t="inlineStr">
         <is>
-          <t>7015431</t>
+          <t>7015437</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
@@ -12482,7 +12561,7 @@
     <row r="294">
       <c r="A294" s="4" t="inlineStr">
         <is>
-          <t>7015437</t>
+          <t>7015439</t>
         </is>
       </c>
       <c r="B294" s="5" t="inlineStr">
@@ -12502,7 +12581,7 @@
     <row r="295">
       <c r="A295" s="6" t="inlineStr">
         <is>
-          <t>7015439</t>
+          <t>7015441</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
@@ -12522,7 +12601,7 @@
     <row r="296">
       <c r="A296" s="4" t="inlineStr">
         <is>
-          <t>7015441</t>
+          <t>7015443</t>
         </is>
       </c>
       <c r="B296" s="5" t="inlineStr">
@@ -12542,12 +12621,12 @@
     <row r="297">
       <c r="A297" s="6" t="inlineStr">
         <is>
-          <t>7015443</t>
+          <t>7015433</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>Interiörarmatur LED Velox Infälld rund</t>
+          <t>Interiörarmatur LED Velox infälld fyrkantig</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
@@ -12562,7 +12641,7 @@
     <row r="298">
       <c r="A298" s="4" t="inlineStr">
         <is>
-          <t>7015433</t>
+          <t>7015435</t>
         </is>
       </c>
       <c r="B298" s="5" t="inlineStr">
@@ -12582,21 +12661,21 @@
     <row r="299">
       <c r="A299" s="6" t="inlineStr">
         <is>
-          <t>7015435</t>
+          <t>7028947</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>Interiörarmatur LED Velox infälld fyrkantig</t>
+          <t>Interiörarmatur Juna</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>Ensto</t>
+          <t>Esylux</t>
         </is>
       </c>
       <c r="D299" s="6" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
     </row>
     <row r="300">
@@ -15276,7 +15355,7 @@
         </is>
       </c>
       <c r="D433" s="6" t="n">
-        <v>143</v>
+        <v>146</v>
       </c>
     </row>
     <row r="434">
@@ -26216,7 +26295,7 @@
         </is>
       </c>
       <c r="D980" s="4" t="n">
-        <v>135</v>
+        <v>114</v>
       </c>
     </row>
     <row r="981">
@@ -26236,7 +26315,7 @@
         </is>
       </c>
       <c r="D981" s="6" t="n">
-        <v>91</v>
+        <v>94</v>
       </c>
     </row>
     <row r="982">
@@ -26256,7 +26335,7 @@
         </is>
       </c>
       <c r="D982" s="4" t="n">
-        <v>154</v>
+        <v>149</v>
       </c>
     </row>
     <row r="983">
@@ -29376,7 +29455,7 @@
         </is>
       </c>
       <c r="D1138" s="4" t="n">
-        <v>433</v>
+        <v>444</v>
       </c>
     </row>
     <row r="1139">
@@ -29396,7 +29475,7 @@
         </is>
       </c>
       <c r="D1139" s="6" t="n">
-        <v>347</v>
+        <v>361</v>
       </c>
     </row>
   </sheetData>

--- a/data/ahlsell_led_panel_inventory.xlsx
+++ b/data/ahlsell_led_panel_inventory.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y78"/>
+  <dimension ref="A1:Y79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -533,82 +533,82 @@
       </c>
       <c r="J1" s="3" t="inlineStr">
         <is>
+          <t>Ledvance</t>
+        </is>
+      </c>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Airam</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="inlineStr">
+        <is>
+          <t>ANETA LIGHTING</t>
+        </is>
+      </c>
+      <c r="M1" s="3" t="inlineStr">
+        <is>
+          <t>Legrand</t>
+        </is>
+      </c>
+      <c r="N1" s="3" t="inlineStr">
+        <is>
+          <t>Ensto</t>
+        </is>
+      </c>
+      <c r="O1" s="3" t="inlineStr">
+        <is>
+          <t>ZG Lighting</t>
+        </is>
+      </c>
+      <c r="P1" s="3" t="inlineStr">
+        <is>
+          <t>Philips</t>
+        </is>
+      </c>
+      <c r="Q1" s="3" t="inlineStr">
+        <is>
           <t>Esylux</t>
         </is>
       </c>
-      <c r="K1" s="3" t="inlineStr">
-        <is>
-          <t>Ledvance</t>
-        </is>
-      </c>
-      <c r="L1" s="3" t="inlineStr">
-        <is>
-          <t>Airam</t>
-        </is>
-      </c>
-      <c r="M1" s="3" t="inlineStr">
-        <is>
-          <t>ZG Lighting</t>
-        </is>
-      </c>
-      <c r="N1" s="3" t="inlineStr">
-        <is>
-          <t>Philips</t>
-        </is>
-      </c>
-      <c r="O1" s="3" t="inlineStr">
-        <is>
-          <t>Ensto</t>
-        </is>
-      </c>
-      <c r="P1" s="3" t="inlineStr">
+      <c r="R1" s="3" t="inlineStr">
+        <is>
+          <t>Easyform</t>
+        </is>
+      </c>
+      <c r="S1" s="3" t="inlineStr">
         <is>
           <t>Black Box</t>
         </is>
       </c>
-      <c r="Q1" s="3" t="inlineStr">
-        <is>
-          <t>ANETA LIGHTING</t>
-        </is>
-      </c>
-      <c r="R1" s="3" t="inlineStr">
-        <is>
-          <t>Legrand</t>
-        </is>
-      </c>
-      <c r="S1" s="3" t="inlineStr">
+      <c r="T1" s="3" t="inlineStr">
+        <is>
+          <t>Westal</t>
+        </is>
+      </c>
+      <c r="U1" s="3" t="inlineStr">
+        <is>
+          <t>THORN</t>
+        </is>
+      </c>
+      <c r="V1" s="3" t="inlineStr">
+        <is>
+          <t>Bergdahls</t>
+        </is>
+      </c>
+      <c r="W1" s="3" t="inlineStr">
         <is>
           <t>Siteco</t>
         </is>
       </c>
-      <c r="T1" s="3" t="inlineStr">
-        <is>
-          <t>THORN</t>
-        </is>
-      </c>
-      <c r="U1" s="3" t="inlineStr">
-        <is>
-          <t>Westal</t>
-        </is>
-      </c>
-      <c r="V1" s="3" t="inlineStr">
-        <is>
-          <t>Easyform</t>
-        </is>
-      </c>
-      <c r="W1" s="3" t="inlineStr">
+      <c r="X1" s="3" t="inlineStr">
         <is>
           <t>Nokalux</t>
         </is>
       </c>
-      <c r="X1" s="3" t="inlineStr">
+      <c r="Y1" s="3" t="inlineStr">
         <is>
           <t>Norwesco</t>
-        </is>
-      </c>
-      <c r="Y1" s="3" t="inlineStr">
-        <is>
-          <t>Bergdahls</t>
         </is>
       </c>
     </row>
@@ -643,28 +643,28 @@
         <v>33</v>
       </c>
       <c r="J2" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="K2" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q2" s="5" t="n">
         <v>25</v>
-      </c>
-      <c r="K2" s="5" t="n">
-        <v>17</v>
-      </c>
-      <c r="L2" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M2" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N2" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O2" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P2" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q2" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="R2" s="5" t="n">
         <v>0</v>
@@ -722,28 +722,28 @@
         <v>33</v>
       </c>
       <c r="J3" t="n">
+        <v>17</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="n">
         <v>25</v>
-      </c>
-      <c r="K3" t="n">
-        <v>17</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>0</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -801,28 +801,28 @@
         <v>33</v>
       </c>
       <c r="J4" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="K4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="5" t="n">
         <v>25</v>
-      </c>
-      <c r="K4" s="5" t="n">
-        <v>17</v>
-      </c>
-      <c r="L4" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M4" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O4" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q4" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="R4" s="5" t="n">
         <v>0</v>
@@ -880,28 +880,28 @@
         <v>33</v>
       </c>
       <c r="J5" t="n">
+        <v>17</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
         <v>24</v>
-      </c>
-      <c r="K5" t="n">
-        <v>17</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>0</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -959,28 +959,28 @@
         <v>33</v>
       </c>
       <c r="J6" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="K6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="K6" s="5" t="n">
-        <v>17</v>
-      </c>
-      <c r="L6" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="R6" s="5" t="n">
         <v>0</v>
@@ -1035,28 +1035,28 @@
         <v>33</v>
       </c>
       <c r="J7" t="n">
+        <v>17</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
         <v>24</v>
-      </c>
-      <c r="K7" t="n">
-        <v>17</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>0</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -1114,28 +1114,28 @@
         <v>33</v>
       </c>
       <c r="J8" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="K8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="K8" s="5" t="n">
-        <v>17</v>
-      </c>
-      <c r="L8" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="R8" s="5" t="n">
         <v>0</v>
@@ -1193,28 +1193,28 @@
         <v>33</v>
       </c>
       <c r="J9" t="n">
+        <v>17</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
         <v>24</v>
-      </c>
-      <c r="K9" t="n">
-        <v>17</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>0</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
@@ -1272,28 +1272,28 @@
         <v>33</v>
       </c>
       <c r="J10" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="K10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="K10" s="5" t="n">
-        <v>17</v>
-      </c>
-      <c r="L10" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="R10" s="5" t="n">
         <v>0</v>
@@ -1351,28 +1351,28 @@
         <v>33</v>
       </c>
       <c r="J11" t="n">
+        <v>17</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
         <v>24</v>
-      </c>
-      <c r="K11" t="n">
-        <v>17</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>0</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -1430,28 +1430,28 @@
         <v>33</v>
       </c>
       <c r="J12" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="K12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="K12" s="5" t="n">
-        <v>17</v>
-      </c>
-      <c r="L12" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="R12" s="5" t="n">
         <v>0</v>
@@ -1509,28 +1509,28 @@
         <v>33</v>
       </c>
       <c r="J13" t="n">
+        <v>17</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
         <v>24</v>
-      </c>
-      <c r="K13" t="n">
-        <v>17</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>0</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -1588,28 +1588,28 @@
         <v>33</v>
       </c>
       <c r="J14" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="K14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="K14" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="L14" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="R14" s="5" t="n">
         <v>0</v>
@@ -1667,28 +1667,28 @@
         <v>33</v>
       </c>
       <c r="J15" t="n">
+        <v>17</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
         <v>24</v>
-      </c>
-      <c r="K15" t="n">
-        <v>17</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>0</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -1746,28 +1746,28 @@
         <v>33</v>
       </c>
       <c r="J16" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="K16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="K16" s="5" t="n">
-        <v>17</v>
-      </c>
-      <c r="L16" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="R16" s="5" t="n">
         <v>0</v>
@@ -1825,28 +1825,28 @@
         <v>33</v>
       </c>
       <c r="J17" t="n">
+        <v>17</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
         <v>24</v>
-      </c>
-      <c r="K17" t="n">
-        <v>17</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>0</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -1904,28 +1904,28 @@
         <v>33</v>
       </c>
       <c r="J18" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="K18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="K18" s="5" t="n">
-        <v>17</v>
-      </c>
-      <c r="L18" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="R18" s="5" t="n">
         <v>0</v>
@@ -1983,28 +1983,28 @@
         <v>33</v>
       </c>
       <c r="J19" t="n">
+        <v>17</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
         <v>24</v>
-      </c>
-      <c r="K19" t="n">
-        <v>17</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>0</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
@@ -2062,28 +2062,28 @@
         <v>33</v>
       </c>
       <c r="J20" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="K20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="K20" s="5" t="n">
-        <v>17</v>
-      </c>
-      <c r="L20" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M20" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O20" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q20" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="R20" s="5" t="n">
         <v>0</v>
@@ -2141,28 +2141,28 @@
         <v>33</v>
       </c>
       <c r="J21" t="n">
+        <v>17</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="n">
         <v>24</v>
-      </c>
-      <c r="K21" t="n">
-        <v>17</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" t="n">
-        <v>0</v>
-      </c>
-      <c r="O21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>0</v>
       </c>
       <c r="R21" t="n">
         <v>0</v>
@@ -2220,28 +2220,28 @@
         <v>33</v>
       </c>
       <c r="J22" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="K22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="K22" s="5" t="n">
-        <v>17</v>
-      </c>
-      <c r="L22" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M22" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N22" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O22" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q22" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="R22" s="5" t="n">
         <v>0</v>
@@ -2299,28 +2299,28 @@
         <v>33</v>
       </c>
       <c r="J23" t="n">
+        <v>17</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" t="n">
         <v>24</v>
-      </c>
-      <c r="K23" t="n">
-        <v>17</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
-      <c r="M23" t="n">
-        <v>0</v>
-      </c>
-      <c r="N23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>0</v>
       </c>
       <c r="R23" t="n">
         <v>0</v>
@@ -2378,28 +2378,28 @@
         <v>33</v>
       </c>
       <c r="J24" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="K24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q24" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="K24" s="5" t="n">
-        <v>17</v>
-      </c>
-      <c r="L24" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M24" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N24" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O24" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P24" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q24" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="R24" s="5" t="n">
         <v>0</v>
@@ -2457,28 +2457,28 @@
         <v>33</v>
       </c>
       <c r="J25" t="n">
+        <v>17</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q25" t="n">
         <v>24</v>
-      </c>
-      <c r="K25" t="n">
-        <v>17</v>
-      </c>
-      <c r="L25" t="n">
-        <v>0</v>
-      </c>
-      <c r="M25" t="n">
-        <v>0</v>
-      </c>
-      <c r="N25" t="n">
-        <v>0</v>
-      </c>
-      <c r="O25" t="n">
-        <v>0</v>
-      </c>
-      <c r="P25" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>0</v>
       </c>
       <c r="R25" t="n">
         <v>0</v>
@@ -2536,28 +2536,28 @@
         <v>33</v>
       </c>
       <c r="J26" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="K26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q26" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="K26" s="5" t="n">
-        <v>17</v>
-      </c>
-      <c r="L26" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M26" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N26" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O26" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P26" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q26" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="R26" s="5" t="n">
         <v>0</v>
@@ -2615,28 +2615,28 @@
         <v>33</v>
       </c>
       <c r="J27" t="n">
+        <v>17</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q27" t="n">
         <v>24</v>
-      </c>
-      <c r="K27" t="n">
-        <v>17</v>
-      </c>
-      <c r="L27" t="n">
-        <v>0</v>
-      </c>
-      <c r="M27" t="n">
-        <v>0</v>
-      </c>
-      <c r="N27" t="n">
-        <v>0</v>
-      </c>
-      <c r="O27" t="n">
-        <v>0</v>
-      </c>
-      <c r="P27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>0</v>
       </c>
       <c r="R27" t="n">
         <v>0</v>
@@ -2694,10 +2694,10 @@
         <v>33</v>
       </c>
       <c r="J28" s="5" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="K28" s="5" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="L28" s="5" t="n">
         <v>0</v>
@@ -2773,28 +2773,28 @@
         <v>33</v>
       </c>
       <c r="J29" t="n">
+        <v>17</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q29" t="n">
         <v>24</v>
-      </c>
-      <c r="K29" t="n">
-        <v>17</v>
-      </c>
-      <c r="L29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M29" t="n">
-        <v>0</v>
-      </c>
-      <c r="N29" t="n">
-        <v>0</v>
-      </c>
-      <c r="O29" t="n">
-        <v>0</v>
-      </c>
-      <c r="P29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>0</v>
       </c>
       <c r="R29" t="n">
         <v>0</v>
@@ -2852,28 +2852,28 @@
         <v>33</v>
       </c>
       <c r="J30" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="K30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="K30" s="5" t="n">
-        <v>17</v>
-      </c>
-      <c r="L30" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M30" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N30" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O30" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P30" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q30" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="R30" s="5" t="n">
         <v>0</v>
@@ -2931,28 +2931,28 @@
         <v>33</v>
       </c>
       <c r="J31" t="n">
+        <v>17</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" t="n">
+        <v>0</v>
+      </c>
+      <c r="N31" t="n">
+        <v>0</v>
+      </c>
+      <c r="O31" t="n">
+        <v>0</v>
+      </c>
+      <c r="P31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q31" t="n">
         <v>24</v>
-      </c>
-      <c r="K31" t="n">
-        <v>17</v>
-      </c>
-      <c r="L31" t="n">
-        <v>0</v>
-      </c>
-      <c r="M31" t="n">
-        <v>0</v>
-      </c>
-      <c r="N31" t="n">
-        <v>0</v>
-      </c>
-      <c r="O31" t="n">
-        <v>0</v>
-      </c>
-      <c r="P31" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>0</v>
       </c>
       <c r="R31" t="n">
         <v>0</v>
@@ -3010,28 +3010,28 @@
         <v>33</v>
       </c>
       <c r="J32" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="K32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="K32" s="5" t="n">
-        <v>17</v>
-      </c>
-      <c r="L32" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M32" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N32" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O32" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P32" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q32" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="R32" s="5" t="n">
         <v>0</v>
@@ -3089,28 +3089,28 @@
         <v>33</v>
       </c>
       <c r="J33" t="n">
+        <v>17</v>
+      </c>
+      <c r="K33" t="n">
+        <v>0</v>
+      </c>
+      <c r="L33" t="n">
+        <v>0</v>
+      </c>
+      <c r="M33" t="n">
+        <v>0</v>
+      </c>
+      <c r="N33" t="n">
+        <v>0</v>
+      </c>
+      <c r="O33" t="n">
+        <v>0</v>
+      </c>
+      <c r="P33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q33" t="n">
         <v>24</v>
-      </c>
-      <c r="K33" t="n">
-        <v>17</v>
-      </c>
-      <c r="L33" t="n">
-        <v>0</v>
-      </c>
-      <c r="M33" t="n">
-        <v>0</v>
-      </c>
-      <c r="N33" t="n">
-        <v>0</v>
-      </c>
-      <c r="O33" t="n">
-        <v>0</v>
-      </c>
-      <c r="P33" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>0</v>
       </c>
       <c r="R33" t="n">
         <v>0</v>
@@ -3168,28 +3168,28 @@
         <v>33</v>
       </c>
       <c r="J34" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="K34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="K34" s="5" t="n">
-        <v>17</v>
-      </c>
-      <c r="L34" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M34" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N34" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O34" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P34" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q34" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="R34" s="5" t="n">
         <v>0</v>
@@ -3247,28 +3247,28 @@
         <v>33</v>
       </c>
       <c r="J35" t="n">
+        <v>17</v>
+      </c>
+      <c r="K35" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" t="n">
+        <v>0</v>
+      </c>
+      <c r="M35" t="n">
+        <v>0</v>
+      </c>
+      <c r="N35" t="n">
+        <v>0</v>
+      </c>
+      <c r="O35" t="n">
+        <v>0</v>
+      </c>
+      <c r="P35" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q35" t="n">
         <v>24</v>
-      </c>
-      <c r="K35" t="n">
-        <v>17</v>
-      </c>
-      <c r="L35" t="n">
-        <v>0</v>
-      </c>
-      <c r="M35" t="n">
-        <v>0</v>
-      </c>
-      <c r="N35" t="n">
-        <v>0</v>
-      </c>
-      <c r="O35" t="n">
-        <v>0</v>
-      </c>
-      <c r="P35" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q35" t="n">
-        <v>0</v>
       </c>
       <c r="R35" t="n">
         <v>0</v>
@@ -3326,28 +3326,28 @@
         <v>33</v>
       </c>
       <c r="J36" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="K36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q36" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="K36" s="5" t="n">
-        <v>17</v>
-      </c>
-      <c r="L36" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M36" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N36" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O36" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P36" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q36" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="R36" s="5" t="n">
         <v>0</v>
@@ -3405,28 +3405,28 @@
         <v>33</v>
       </c>
       <c r="J37" t="n">
+        <v>17</v>
+      </c>
+      <c r="K37" t="n">
+        <v>0</v>
+      </c>
+      <c r="L37" t="n">
+        <v>0</v>
+      </c>
+      <c r="M37" t="n">
+        <v>0</v>
+      </c>
+      <c r="N37" t="n">
+        <v>0</v>
+      </c>
+      <c r="O37" t="n">
+        <v>0</v>
+      </c>
+      <c r="P37" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q37" t="n">
         <v>24</v>
-      </c>
-      <c r="K37" t="n">
-        <v>17</v>
-      </c>
-      <c r="L37" t="n">
-        <v>0</v>
-      </c>
-      <c r="M37" t="n">
-        <v>0</v>
-      </c>
-      <c r="N37" t="n">
-        <v>0</v>
-      </c>
-      <c r="O37" t="n">
-        <v>0</v>
-      </c>
-      <c r="P37" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q37" t="n">
-        <v>0</v>
       </c>
       <c r="R37" t="n">
         <v>0</v>
@@ -3484,28 +3484,28 @@
         <v>33</v>
       </c>
       <c r="J38" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="K38" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L38" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M38" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N38" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O38" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P38" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q38" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="K38" s="5" t="n">
-        <v>17</v>
-      </c>
-      <c r="L38" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M38" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N38" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O38" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P38" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q38" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="R38" s="5" t="n">
         <v>0</v>
@@ -3563,28 +3563,28 @@
         <v>33</v>
       </c>
       <c r="J39" t="n">
+        <v>17</v>
+      </c>
+      <c r="K39" t="n">
+        <v>0</v>
+      </c>
+      <c r="L39" t="n">
+        <v>0</v>
+      </c>
+      <c r="M39" t="n">
+        <v>0</v>
+      </c>
+      <c r="N39" t="n">
+        <v>0</v>
+      </c>
+      <c r="O39" t="n">
+        <v>0</v>
+      </c>
+      <c r="P39" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q39" t="n">
         <v>24</v>
-      </c>
-      <c r="K39" t="n">
-        <v>17</v>
-      </c>
-      <c r="L39" t="n">
-        <v>0</v>
-      </c>
-      <c r="M39" t="n">
-        <v>0</v>
-      </c>
-      <c r="N39" t="n">
-        <v>0</v>
-      </c>
-      <c r="O39" t="n">
-        <v>0</v>
-      </c>
-      <c r="P39" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q39" t="n">
-        <v>0</v>
       </c>
       <c r="R39" t="n">
         <v>0</v>
@@ -3642,28 +3642,28 @@
         <v>33</v>
       </c>
       <c r="J40" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="K40" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L40" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M40" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N40" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O40" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P40" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q40" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="K40" s="5" t="n">
-        <v>17</v>
-      </c>
-      <c r="L40" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M40" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N40" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O40" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P40" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q40" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="R40" s="5" t="n">
         <v>0</v>
@@ -3721,28 +3721,28 @@
         <v>33</v>
       </c>
       <c r="J41" t="n">
+        <v>17</v>
+      </c>
+      <c r="K41" t="n">
+        <v>0</v>
+      </c>
+      <c r="L41" t="n">
+        <v>0</v>
+      </c>
+      <c r="M41" t="n">
+        <v>0</v>
+      </c>
+      <c r="N41" t="n">
+        <v>0</v>
+      </c>
+      <c r="O41" t="n">
+        <v>0</v>
+      </c>
+      <c r="P41" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q41" t="n">
         <v>24</v>
-      </c>
-      <c r="K41" t="n">
-        <v>17</v>
-      </c>
-      <c r="L41" t="n">
-        <v>0</v>
-      </c>
-      <c r="M41" t="n">
-        <v>0</v>
-      </c>
-      <c r="N41" t="n">
-        <v>0</v>
-      </c>
-      <c r="O41" t="n">
-        <v>0</v>
-      </c>
-      <c r="P41" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q41" t="n">
-        <v>0</v>
       </c>
       <c r="R41" t="n">
         <v>0</v>
@@ -3800,28 +3800,28 @@
         <v>33</v>
       </c>
       <c r="J42" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="K42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q42" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="K42" s="5" t="n">
-        <v>17</v>
-      </c>
-      <c r="L42" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M42" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N42" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O42" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P42" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q42" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="R42" s="5" t="n">
         <v>0</v>
@@ -3879,28 +3879,28 @@
         <v>33</v>
       </c>
       <c r="J43" t="n">
+        <v>17</v>
+      </c>
+      <c r="K43" t="n">
+        <v>0</v>
+      </c>
+      <c r="L43" t="n">
+        <v>0</v>
+      </c>
+      <c r="M43" t="n">
+        <v>0</v>
+      </c>
+      <c r="N43" t="n">
+        <v>0</v>
+      </c>
+      <c r="O43" t="n">
+        <v>0</v>
+      </c>
+      <c r="P43" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q43" t="n">
         <v>24</v>
-      </c>
-      <c r="K43" t="n">
-        <v>17</v>
-      </c>
-      <c r="L43" t="n">
-        <v>0</v>
-      </c>
-      <c r="M43" t="n">
-        <v>0</v>
-      </c>
-      <c r="N43" t="n">
-        <v>0</v>
-      </c>
-      <c r="O43" t="n">
-        <v>0</v>
-      </c>
-      <c r="P43" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q43" t="n">
-        <v>0</v>
       </c>
       <c r="R43" t="n">
         <v>0</v>
@@ -3958,28 +3958,28 @@
         <v>33</v>
       </c>
       <c r="J44" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="K44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q44" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="K44" s="5" t="n">
-        <v>17</v>
-      </c>
-      <c r="L44" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M44" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N44" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O44" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P44" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q44" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="R44" s="5" t="n">
         <v>0</v>
@@ -4037,28 +4037,28 @@
         <v>33</v>
       </c>
       <c r="J45" t="n">
+        <v>17</v>
+      </c>
+      <c r="K45" t="n">
+        <v>0</v>
+      </c>
+      <c r="L45" t="n">
+        <v>0</v>
+      </c>
+      <c r="M45" t="n">
+        <v>0</v>
+      </c>
+      <c r="N45" t="n">
+        <v>0</v>
+      </c>
+      <c r="O45" t="n">
+        <v>0</v>
+      </c>
+      <c r="P45" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q45" t="n">
         <v>24</v>
-      </c>
-      <c r="K45" t="n">
-        <v>17</v>
-      </c>
-      <c r="L45" t="n">
-        <v>0</v>
-      </c>
-      <c r="M45" t="n">
-        <v>0</v>
-      </c>
-      <c r="N45" t="n">
-        <v>0</v>
-      </c>
-      <c r="O45" t="n">
-        <v>0</v>
-      </c>
-      <c r="P45" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q45" t="n">
-        <v>0</v>
       </c>
       <c r="R45" t="n">
         <v>0</v>
@@ -4116,28 +4116,28 @@
         <v>33</v>
       </c>
       <c r="J46" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="K46" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L46" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M46" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N46" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O46" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P46" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q46" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="K46" s="5" t="n">
-        <v>17</v>
-      </c>
-      <c r="L46" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M46" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N46" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O46" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P46" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q46" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="R46" s="5" t="n">
         <v>0</v>
@@ -4195,28 +4195,28 @@
         <v>33</v>
       </c>
       <c r="J47" t="n">
+        <v>17</v>
+      </c>
+      <c r="K47" t="n">
+        <v>0</v>
+      </c>
+      <c r="L47" t="n">
+        <v>0</v>
+      </c>
+      <c r="M47" t="n">
+        <v>0</v>
+      </c>
+      <c r="N47" t="n">
+        <v>0</v>
+      </c>
+      <c r="O47" t="n">
+        <v>0</v>
+      </c>
+      <c r="P47" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q47" t="n">
         <v>24</v>
-      </c>
-      <c r="K47" t="n">
-        <v>17</v>
-      </c>
-      <c r="L47" t="n">
-        <v>0</v>
-      </c>
-      <c r="M47" t="n">
-        <v>0</v>
-      </c>
-      <c r="N47" t="n">
-        <v>0</v>
-      </c>
-      <c r="O47" t="n">
-        <v>0</v>
-      </c>
-      <c r="P47" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q47" t="n">
-        <v>0</v>
       </c>
       <c r="R47" t="n">
         <v>0</v>
@@ -4274,28 +4274,28 @@
         <v>33</v>
       </c>
       <c r="J48" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="K48" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L48" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M48" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N48" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O48" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P48" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q48" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="K48" s="5" t="n">
-        <v>17</v>
-      </c>
-      <c r="L48" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M48" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N48" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O48" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P48" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q48" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="R48" s="5" t="n">
         <v>0</v>
@@ -4353,28 +4353,28 @@
         <v>33</v>
       </c>
       <c r="J49" t="n">
+        <v>17</v>
+      </c>
+      <c r="K49" t="n">
+        <v>0</v>
+      </c>
+      <c r="L49" t="n">
+        <v>0</v>
+      </c>
+      <c r="M49" t="n">
+        <v>0</v>
+      </c>
+      <c r="N49" t="n">
+        <v>0</v>
+      </c>
+      <c r="O49" t="n">
+        <v>0</v>
+      </c>
+      <c r="P49" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q49" t="n">
         <v>24</v>
-      </c>
-      <c r="K49" t="n">
-        <v>17</v>
-      </c>
-      <c r="L49" t="n">
-        <v>0</v>
-      </c>
-      <c r="M49" t="n">
-        <v>0</v>
-      </c>
-      <c r="N49" t="n">
-        <v>0</v>
-      </c>
-      <c r="O49" t="n">
-        <v>0</v>
-      </c>
-      <c r="P49" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q49" t="n">
-        <v>0</v>
       </c>
       <c r="R49" t="n">
         <v>0</v>
@@ -4432,28 +4432,28 @@
         <v>33</v>
       </c>
       <c r="J50" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="K50" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L50" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M50" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N50" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O50" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P50" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q50" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="K50" s="5" t="n">
-        <v>17</v>
-      </c>
-      <c r="L50" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M50" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N50" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O50" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P50" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q50" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="R50" s="5" t="n">
         <v>0</v>
@@ -4511,28 +4511,28 @@
         <v>33</v>
       </c>
       <c r="J51" t="n">
+        <v>17</v>
+      </c>
+      <c r="K51" t="n">
+        <v>0</v>
+      </c>
+      <c r="L51" t="n">
+        <v>0</v>
+      </c>
+      <c r="M51" t="n">
+        <v>0</v>
+      </c>
+      <c r="N51" t="n">
+        <v>0</v>
+      </c>
+      <c r="O51" t="n">
+        <v>0</v>
+      </c>
+      <c r="P51" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q51" t="n">
         <v>24</v>
-      </c>
-      <c r="K51" t="n">
-        <v>17</v>
-      </c>
-      <c r="L51" t="n">
-        <v>0</v>
-      </c>
-      <c r="M51" t="n">
-        <v>0</v>
-      </c>
-      <c r="N51" t="n">
-        <v>0</v>
-      </c>
-      <c r="O51" t="n">
-        <v>0</v>
-      </c>
-      <c r="P51" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q51" t="n">
-        <v>0</v>
       </c>
       <c r="R51" t="n">
         <v>0</v>
@@ -4590,28 +4590,28 @@
         <v>30</v>
       </c>
       <c r="J52" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="K52" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L52" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M52" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N52" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O52" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P52" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q52" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="K52" s="5" t="n">
-        <v>17</v>
-      </c>
-      <c r="L52" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M52" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N52" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O52" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P52" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q52" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="R52" s="5" t="n">
         <v>0</v>
@@ -4669,28 +4669,28 @@
         <v>30</v>
       </c>
       <c r="J53" t="n">
+        <v>17</v>
+      </c>
+      <c r="K53" t="n">
+        <v>0</v>
+      </c>
+      <c r="L53" t="n">
+        <v>0</v>
+      </c>
+      <c r="M53" t="n">
+        <v>0</v>
+      </c>
+      <c r="N53" t="n">
+        <v>0</v>
+      </c>
+      <c r="O53" t="n">
+        <v>0</v>
+      </c>
+      <c r="P53" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q53" t="n">
         <v>24</v>
-      </c>
-      <c r="K53" t="n">
-        <v>17</v>
-      </c>
-      <c r="L53" t="n">
-        <v>0</v>
-      </c>
-      <c r="M53" t="n">
-        <v>0</v>
-      </c>
-      <c r="N53" t="n">
-        <v>0</v>
-      </c>
-      <c r="O53" t="n">
-        <v>0</v>
-      </c>
-      <c r="P53" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q53" t="n">
-        <v>0</v>
       </c>
       <c r="R53" t="n">
         <v>0</v>
@@ -4748,28 +4748,28 @@
         <v>30</v>
       </c>
       <c r="J54" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="K54" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L54" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M54" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N54" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O54" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P54" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q54" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="K54" s="5" t="n">
-        <v>17</v>
-      </c>
-      <c r="L54" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M54" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N54" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O54" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P54" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q54" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="R54" s="5" t="n">
         <v>0</v>
@@ -4827,28 +4827,28 @@
         <v>30</v>
       </c>
       <c r="J55" t="n">
+        <v>17</v>
+      </c>
+      <c r="K55" t="n">
+        <v>0</v>
+      </c>
+      <c r="L55" t="n">
+        <v>0</v>
+      </c>
+      <c r="M55" t="n">
+        <v>0</v>
+      </c>
+      <c r="N55" t="n">
+        <v>0</v>
+      </c>
+      <c r="O55" t="n">
+        <v>0</v>
+      </c>
+      <c r="P55" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q55" t="n">
         <v>24</v>
-      </c>
-      <c r="K55" t="n">
-        <v>17</v>
-      </c>
-      <c r="L55" t="n">
-        <v>0</v>
-      </c>
-      <c r="M55" t="n">
-        <v>0</v>
-      </c>
-      <c r="N55" t="n">
-        <v>0</v>
-      </c>
-      <c r="O55" t="n">
-        <v>0</v>
-      </c>
-      <c r="P55" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q55" t="n">
-        <v>0</v>
       </c>
       <c r="R55" t="n">
         <v>0</v>
@@ -4906,28 +4906,28 @@
         <v>30</v>
       </c>
       <c r="J56" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="K56" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L56" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M56" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N56" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O56" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P56" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q56" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="K56" s="5" t="n">
-        <v>17</v>
-      </c>
-      <c r="L56" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M56" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N56" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O56" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P56" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q56" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="R56" s="5" t="n">
         <v>0</v>
@@ -4985,28 +4985,28 @@
         <v>24</v>
       </c>
       <c r="J57" t="n">
+        <v>22</v>
+      </c>
+      <c r="K57" t="n">
+        <v>0</v>
+      </c>
+      <c r="L57" t="n">
+        <v>0</v>
+      </c>
+      <c r="M57" t="n">
+        <v>0</v>
+      </c>
+      <c r="N57" t="n">
+        <v>0</v>
+      </c>
+      <c r="O57" t="n">
+        <v>0</v>
+      </c>
+      <c r="P57" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q57" t="n">
         <v>24</v>
-      </c>
-      <c r="K57" t="n">
-        <v>22</v>
-      </c>
-      <c r="L57" t="n">
-        <v>0</v>
-      </c>
-      <c r="M57" t="n">
-        <v>0</v>
-      </c>
-      <c r="N57" t="n">
-        <v>0</v>
-      </c>
-      <c r="O57" t="n">
-        <v>0</v>
-      </c>
-      <c r="P57" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q57" t="n">
-        <v>0</v>
       </c>
       <c r="R57" t="n">
         <v>0</v>
@@ -5064,28 +5064,28 @@
         <v>26</v>
       </c>
       <c r="J58" s="5" t="n">
+        <v>22</v>
+      </c>
+      <c r="K58" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L58" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M58" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N58" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O58" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P58" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q58" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="K58" s="5" t="n">
-        <v>22</v>
-      </c>
-      <c r="L58" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M58" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N58" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O58" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P58" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q58" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="R58" s="5" t="n">
         <v>0</v>
@@ -5143,28 +5143,28 @@
         <v>26</v>
       </c>
       <c r="J59" t="n">
+        <v>16</v>
+      </c>
+      <c r="K59" t="n">
+        <v>0</v>
+      </c>
+      <c r="L59" t="n">
+        <v>0</v>
+      </c>
+      <c r="M59" t="n">
+        <v>0</v>
+      </c>
+      <c r="N59" t="n">
+        <v>0</v>
+      </c>
+      <c r="O59" t="n">
+        <v>0</v>
+      </c>
+      <c r="P59" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q59" t="n">
         <v>24</v>
-      </c>
-      <c r="K59" t="n">
-        <v>16</v>
-      </c>
-      <c r="L59" t="n">
-        <v>0</v>
-      </c>
-      <c r="M59" t="n">
-        <v>0</v>
-      </c>
-      <c r="N59" t="n">
-        <v>0</v>
-      </c>
-      <c r="O59" t="n">
-        <v>0</v>
-      </c>
-      <c r="P59" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q59" t="n">
-        <v>0</v>
       </c>
       <c r="R59" t="n">
         <v>0</v>
@@ -5222,28 +5222,28 @@
         <v>23</v>
       </c>
       <c r="J60" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="K60" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L60" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M60" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N60" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O60" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P60" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q60" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="K60" s="5" t="n">
-        <v>16</v>
-      </c>
-      <c r="L60" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M60" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N60" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O60" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P60" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q60" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="R60" s="5" t="n">
         <v>0</v>
@@ -5301,28 +5301,28 @@
         <v>29</v>
       </c>
       <c r="J61" t="n">
+        <v>16</v>
+      </c>
+      <c r="K61" t="n">
+        <v>0</v>
+      </c>
+      <c r="L61" t="n">
+        <v>0</v>
+      </c>
+      <c r="M61" t="n">
+        <v>0</v>
+      </c>
+      <c r="N61" t="n">
+        <v>0</v>
+      </c>
+      <c r="O61" t="n">
+        <v>0</v>
+      </c>
+      <c r="P61" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q61" t="n">
         <v>24</v>
-      </c>
-      <c r="K61" t="n">
-        <v>16</v>
-      </c>
-      <c r="L61" t="n">
-        <v>0</v>
-      </c>
-      <c r="M61" t="n">
-        <v>0</v>
-      </c>
-      <c r="N61" t="n">
-        <v>0</v>
-      </c>
-      <c r="O61" t="n">
-        <v>0</v>
-      </c>
-      <c r="P61" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q61" t="n">
-        <v>0</v>
       </c>
       <c r="R61" t="n">
         <v>0</v>
@@ -5380,28 +5380,28 @@
         <v>29</v>
       </c>
       <c r="J62" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="K62" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L62" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M62" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N62" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O62" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P62" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q62" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="K62" s="5" t="n">
-        <v>16</v>
-      </c>
-      <c r="L62" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M62" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N62" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O62" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P62" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q62" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="R62" s="5" t="n">
         <v>0</v>
@@ -5459,28 +5459,28 @@
         <v>29</v>
       </c>
       <c r="J63" t="n">
+        <v>16</v>
+      </c>
+      <c r="K63" t="n">
+        <v>0</v>
+      </c>
+      <c r="L63" t="n">
+        <v>0</v>
+      </c>
+      <c r="M63" t="n">
+        <v>0</v>
+      </c>
+      <c r="N63" t="n">
+        <v>0</v>
+      </c>
+      <c r="O63" t="n">
+        <v>0</v>
+      </c>
+      <c r="P63" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q63" t="n">
         <v>24</v>
-      </c>
-      <c r="K63" t="n">
-        <v>16</v>
-      </c>
-      <c r="L63" t="n">
-        <v>0</v>
-      </c>
-      <c r="M63" t="n">
-        <v>0</v>
-      </c>
-      <c r="N63" t="n">
-        <v>0</v>
-      </c>
-      <c r="O63" t="n">
-        <v>0</v>
-      </c>
-      <c r="P63" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q63" t="n">
-        <v>0</v>
       </c>
       <c r="R63" t="n">
         <v>0</v>
@@ -5538,28 +5538,28 @@
         <v>20</v>
       </c>
       <c r="J64" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="K64" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L64" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M64" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N64" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O64" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P64" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q64" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="K64" s="5" t="n">
-        <v>16</v>
-      </c>
-      <c r="L64" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M64" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N64" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O64" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P64" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q64" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="R64" s="5" t="n">
         <v>0</v>
@@ -5617,28 +5617,28 @@
         <v>20</v>
       </c>
       <c r="J65" t="n">
+        <v>21</v>
+      </c>
+      <c r="K65" t="n">
+        <v>0</v>
+      </c>
+      <c r="L65" t="n">
+        <v>0</v>
+      </c>
+      <c r="M65" t="n">
+        <v>0</v>
+      </c>
+      <c r="N65" t="n">
+        <v>0</v>
+      </c>
+      <c r="O65" t="n">
+        <v>0</v>
+      </c>
+      <c r="P65" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q65" t="n">
         <v>24</v>
-      </c>
-      <c r="K65" t="n">
-        <v>21</v>
-      </c>
-      <c r="L65" t="n">
-        <v>0</v>
-      </c>
-      <c r="M65" t="n">
-        <v>0</v>
-      </c>
-      <c r="N65" t="n">
-        <v>0</v>
-      </c>
-      <c r="O65" t="n">
-        <v>0</v>
-      </c>
-      <c r="P65" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q65" t="n">
-        <v>0</v>
       </c>
       <c r="R65" t="n">
         <v>0</v>
@@ -5696,28 +5696,28 @@
         <v>26</v>
       </c>
       <c r="J66" s="5" t="n">
+        <v>21</v>
+      </c>
+      <c r="K66" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L66" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M66" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N66" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O66" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P66" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q66" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="K66" s="5" t="n">
-        <v>21</v>
-      </c>
-      <c r="L66" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M66" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N66" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O66" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P66" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q66" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="R66" s="5" t="n">
         <v>0</v>
@@ -5774,8 +5774,11 @@
       <c r="I67" t="n">
         <v>26</v>
       </c>
+      <c r="J67" t="n">
+        <v>21</v>
+      </c>
       <c r="K67" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="L67" t="n">
         <v>0</v>
@@ -5790,9 +5793,6 @@
         <v>0</v>
       </c>
       <c r="P67" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q67" t="n">
         <v>0</v>
       </c>
       <c r="R67" t="n">
@@ -5851,28 +5851,28 @@
         <v>26</v>
       </c>
       <c r="J68" s="5" t="n">
+        <v>21</v>
+      </c>
+      <c r="K68" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L68" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M68" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N68" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O68" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P68" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q68" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="K68" s="5" t="n">
-        <v>21</v>
-      </c>
-      <c r="L68" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M68" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N68" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O68" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P68" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q68" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="R68" s="5" t="n">
         <v>0</v>
@@ -5926,8 +5926,11 @@
       <c r="I69" t="n">
         <v>26</v>
       </c>
+      <c r="J69" t="n">
+        <v>21</v>
+      </c>
       <c r="K69" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="L69" t="n">
         <v>0</v>
@@ -5942,9 +5945,6 @@
         <v>0</v>
       </c>
       <c r="P69" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q69" t="n">
         <v>0</v>
       </c>
       <c r="R69" t="n">
@@ -6003,28 +6003,28 @@
         <v>26</v>
       </c>
       <c r="J70" s="5" t="n">
+        <v>21</v>
+      </c>
+      <c r="K70" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L70" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M70" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N70" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O70" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P70" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q70" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="K70" s="5" t="n">
-        <v>21</v>
-      </c>
-      <c r="L70" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M70" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N70" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O70" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P70" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q70" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="R70" s="5" t="n">
         <v>0</v>
@@ -6082,28 +6082,28 @@
         <v>26</v>
       </c>
       <c r="J71" t="n">
+        <v>21</v>
+      </c>
+      <c r="K71" t="n">
+        <v>0</v>
+      </c>
+      <c r="L71" t="n">
+        <v>0</v>
+      </c>
+      <c r="M71" t="n">
+        <v>0</v>
+      </c>
+      <c r="N71" t="n">
+        <v>0</v>
+      </c>
+      <c r="O71" t="n">
+        <v>0</v>
+      </c>
+      <c r="P71" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q71" t="n">
         <v>24</v>
-      </c>
-      <c r="K71" t="n">
-        <v>21</v>
-      </c>
-      <c r="L71" t="n">
-        <v>0</v>
-      </c>
-      <c r="M71" t="n">
-        <v>0</v>
-      </c>
-      <c r="N71" t="n">
-        <v>0</v>
-      </c>
-      <c r="O71" t="n">
-        <v>0</v>
-      </c>
-      <c r="P71" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q71" t="n">
-        <v>0</v>
       </c>
       <c r="R71" t="n">
         <v>0</v>
@@ -6161,28 +6161,28 @@
         <v>26</v>
       </c>
       <c r="J72" s="5" t="n">
+        <v>21</v>
+      </c>
+      <c r="K72" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L72" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M72" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N72" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O72" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P72" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q72" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="K72" s="5" t="n">
-        <v>21</v>
-      </c>
-      <c r="L72" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M72" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N72" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O72" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P72" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q72" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="R72" s="5" t="n">
         <v>0</v>
@@ -6240,28 +6240,28 @@
         <v>26</v>
       </c>
       <c r="J73" t="n">
+        <v>19</v>
+      </c>
+      <c r="K73" t="n">
+        <v>0</v>
+      </c>
+      <c r="L73" t="n">
+        <v>0</v>
+      </c>
+      <c r="M73" t="n">
+        <v>0</v>
+      </c>
+      <c r="N73" t="n">
+        <v>0</v>
+      </c>
+      <c r="O73" t="n">
+        <v>0</v>
+      </c>
+      <c r="P73" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q73" t="n">
         <v>24</v>
-      </c>
-      <c r="K73" t="n">
-        <v>19</v>
-      </c>
-      <c r="L73" t="n">
-        <v>0</v>
-      </c>
-      <c r="M73" t="n">
-        <v>0</v>
-      </c>
-      <c r="N73" t="n">
-        <v>0</v>
-      </c>
-      <c r="O73" t="n">
-        <v>0</v>
-      </c>
-      <c r="P73" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q73" t="n">
-        <v>0</v>
       </c>
       <c r="R73" t="n">
         <v>0</v>
@@ -6319,28 +6319,28 @@
         <v>26</v>
       </c>
       <c r="J74" s="5" t="n">
+        <v>23</v>
+      </c>
+      <c r="K74" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L74" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M74" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N74" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O74" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P74" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q74" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="K74" s="5" t="n">
-        <v>23</v>
-      </c>
-      <c r="L74" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M74" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N74" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O74" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P74" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q74" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="R74" s="5" t="n">
         <v>0</v>
@@ -6398,28 +6398,28 @@
         <v>26</v>
       </c>
       <c r="J75" t="n">
+        <v>23</v>
+      </c>
+      <c r="K75" t="n">
+        <v>0</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0</v>
+      </c>
+      <c r="N75" t="n">
+        <v>0</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q75" t="n">
         <v>24</v>
-      </c>
-      <c r="K75" t="n">
-        <v>23</v>
-      </c>
-      <c r="L75" t="n">
-        <v>0</v>
-      </c>
-      <c r="M75" t="n">
-        <v>0</v>
-      </c>
-      <c r="N75" t="n">
-        <v>0</v>
-      </c>
-      <c r="O75" t="n">
-        <v>0</v>
-      </c>
-      <c r="P75" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q75" t="n">
-        <v>0</v>
       </c>
       <c r="R75" t="n">
         <v>0</v>
@@ -6477,31 +6477,31 @@
         <v>26</v>
       </c>
       <c r="J76" s="5" t="n">
+        <v>23</v>
+      </c>
+      <c r="K76" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L76" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M76" s="5" t="n"/>
+      <c r="N76" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O76" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P76" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q76" s="5" t="n">
         <v>24</v>
       </c>
-      <c r="K76" s="5" t="n">
-        <v>23</v>
-      </c>
-      <c r="L76" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M76" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N76" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O76" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P76" s="5" t="n"/>
-      <c r="Q76" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R76" s="5" t="n"/>
-      <c r="S76" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="R76" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S76" s="5" t="n"/>
       <c r="T76" s="5" t="n">
         <v>0</v>
       </c>
@@ -6551,8 +6551,11 @@
       <c r="I77" t="n">
         <v>26</v>
       </c>
+      <c r="J77" t="n">
+        <v>23</v>
+      </c>
       <c r="K77" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="L77" t="n">
         <v>0</v>
@@ -6567,9 +6570,6 @@
         <v>0</v>
       </c>
       <c r="P77" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q77" t="n">
         <v>0</v>
       </c>
       <c r="R77" t="n">
@@ -6628,51 +6628,127 @@
         <v>26</v>
       </c>
       <c r="J78" s="5" t="n">
+        <v>23</v>
+      </c>
+      <c r="K78" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L78" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M78" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N78" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O78" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P78" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q78" s="5" t="n">
         <v>24</v>
       </c>
-      <c r="K78" s="5" t="n">
+      <c r="R78" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S78" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T78" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U78" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V78" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W78" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X78" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y78" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B79" t="n">
+        <v>901</v>
+      </c>
+      <c r="C79" t="n">
+        <v>540</v>
+      </c>
+      <c r="D79" t="n">
+        <v>394</v>
+      </c>
+      <c r="E79" t="n">
+        <v>369</v>
+      </c>
+      <c r="F79" t="n">
+        <v>207</v>
+      </c>
+      <c r="G79" t="n">
+        <v>100</v>
+      </c>
+      <c r="H79" t="n">
+        <v>42</v>
+      </c>
+      <c r="I79" t="n">
+        <v>26</v>
+      </c>
+      <c r="J79" t="n">
         <v>23</v>
       </c>
-      <c r="L78" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M78" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N78" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O78" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P78" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q78" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R78" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S78" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T78" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U78" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V78" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W78" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="X78" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y78" s="5" t="n">
+      <c r="K79" t="n">
+        <v>0</v>
+      </c>
+      <c r="L79" t="n">
+        <v>0</v>
+      </c>
+      <c r="M79" t="n">
+        <v>0</v>
+      </c>
+      <c r="N79" t="n">
+        <v>0</v>
+      </c>
+      <c r="O79" t="n">
+        <v>0</v>
+      </c>
+      <c r="P79" t="n">
+        <v>0</v>
+      </c>
+      <c r="R79" t="n">
+        <v>0</v>
+      </c>
+      <c r="S79" t="n">
+        <v>0</v>
+      </c>
+      <c r="T79" t="n">
+        <v>0</v>
+      </c>
+      <c r="U79" t="n">
+        <v>0</v>
+      </c>
+      <c r="V79" t="n">
+        <v>0</v>
+      </c>
+      <c r="W79" t="n">
+        <v>0</v>
+      </c>
+      <c r="X79" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y79" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6714,7 +6790,7 @@
       </c>
       <c r="D1" s="3" t="inlineStr">
         <is>
-          <t>Lager (2026-09-22)</t>
+          <t>Lager (2026-09-23)</t>
         </is>
       </c>
     </row>
@@ -6735,7 +6811,7 @@
         </is>
       </c>
       <c r="D2" s="4" t="n">
-        <v>526</v>
+        <v>540</v>
       </c>
     </row>
     <row r="3">
@@ -11921,12 +11997,12 @@
     <row r="262">
       <c r="A262" s="4" t="inlineStr">
         <is>
-          <t>7011676</t>
+          <t>7013678</t>
         </is>
       </c>
       <c r="B262" s="5" t="inlineStr">
         <is>
-          <t>Infälld interiörarmatur Diana Flat LED 300x300</t>
+          <t>Infälld Interiörarmatur LED DPML Tunable White</t>
         </is>
       </c>
       <c r="C262" s="5" t="inlineStr">
@@ -11941,7 +12017,7 @@
     <row r="263">
       <c r="A263" s="6" t="inlineStr">
         <is>
-          <t>7011677</t>
+          <t>7011676</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -11961,12 +12037,12 @@
     <row r="264">
       <c r="A264" s="4" t="inlineStr">
         <is>
-          <t>7013193</t>
+          <t>7011677</t>
         </is>
       </c>
       <c r="B264" s="5" t="inlineStr">
         <is>
-          <t>Infälld interiörarmatur Diana Flat LED 600x600</t>
+          <t>Infälld interiörarmatur Diana Flat LED 300x300</t>
         </is>
       </c>
       <c r="C264" s="5" t="inlineStr">
@@ -11981,7 +12057,7 @@
     <row r="265">
       <c r="A265" s="6" t="inlineStr">
         <is>
-          <t>7013194</t>
+          <t>7013193</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
@@ -12001,7 +12077,7 @@
     <row r="266">
       <c r="A266" s="4" t="inlineStr">
         <is>
-          <t>7018335</t>
+          <t>7013194</t>
         </is>
       </c>
       <c r="B266" s="5" t="inlineStr">
@@ -12021,7 +12097,7 @@
     <row r="267">
       <c r="A267" s="6" t="inlineStr">
         <is>
-          <t>7018336</t>
+          <t>7018335</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
@@ -12041,7 +12117,7 @@
     <row r="268">
       <c r="A268" s="4" t="inlineStr">
         <is>
-          <t>7018337</t>
+          <t>7018336</t>
         </is>
       </c>
       <c r="B268" s="5" t="inlineStr">
@@ -12061,7 +12137,7 @@
     <row r="269">
       <c r="A269" s="6" t="inlineStr">
         <is>
-          <t>7018338</t>
+          <t>7018337</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
@@ -12081,7 +12157,7 @@
     <row r="270">
       <c r="A270" s="4" t="inlineStr">
         <is>
-          <t>7018339</t>
+          <t>7018338</t>
         </is>
       </c>
       <c r="B270" s="5" t="inlineStr">
@@ -12101,7 +12177,7 @@
     <row r="271">
       <c r="A271" s="6" t="inlineStr">
         <is>
-          <t>7018340</t>
+          <t>7018339</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
@@ -12121,7 +12197,7 @@
     <row r="272">
       <c r="A272" s="4" t="inlineStr">
         <is>
-          <t>7018341</t>
+          <t>7018340</t>
         </is>
       </c>
       <c r="B272" s="5" t="inlineStr">
@@ -12141,7 +12217,7 @@
     <row r="273">
       <c r="A273" s="6" t="inlineStr">
         <is>
-          <t>7018342</t>
+          <t>7018341</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
@@ -12161,12 +12237,12 @@
     <row r="274">
       <c r="A274" s="4" t="inlineStr">
         <is>
-          <t>7017462</t>
+          <t>7018342</t>
         </is>
       </c>
       <c r="B274" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur LED Velox Deco Fyrkantig</t>
+          <t>Infälld interiörarmatur Diana Flat LED 600x600</t>
         </is>
       </c>
       <c r="C274" s="5" t="inlineStr">
@@ -12181,7 +12257,7 @@
     <row r="275">
       <c r="A275" s="6" t="inlineStr">
         <is>
-          <t>7018858</t>
+          <t>7017462</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
@@ -12201,7 +12277,7 @@
     <row r="276">
       <c r="A276" s="4" t="inlineStr">
         <is>
-          <t>7018877</t>
+          <t>7018858</t>
         </is>
       </c>
       <c r="B276" s="5" t="inlineStr">
@@ -12221,7 +12297,7 @@
     <row r="277">
       <c r="A277" s="6" t="inlineStr">
         <is>
-          <t>7018878</t>
+          <t>7018877</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
@@ -12241,12 +12317,12 @@
     <row r="278">
       <c r="A278" s="4" t="inlineStr">
         <is>
-          <t>7017460</t>
+          <t>7018878</t>
         </is>
       </c>
       <c r="B278" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur LED Velox Deco Rund</t>
+          <t>Interiörarmatur LED Velox Deco Fyrkantig</t>
         </is>
       </c>
       <c r="C278" s="5" t="inlineStr">
@@ -12261,7 +12337,7 @@
     <row r="279">
       <c r="A279" s="6" t="inlineStr">
         <is>
-          <t>7017464</t>
+          <t>7017460</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
@@ -12281,7 +12357,7 @@
     <row r="280">
       <c r="A280" s="4" t="inlineStr">
         <is>
-          <t>7017466</t>
+          <t>7017464</t>
         </is>
       </c>
       <c r="B280" s="5" t="inlineStr">
@@ -12301,7 +12377,7 @@
     <row r="281">
       <c r="A281" s="6" t="inlineStr">
         <is>
-          <t>7018857</t>
+          <t>7017466</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
@@ -12321,7 +12397,7 @@
     <row r="282">
       <c r="A282" s="4" t="inlineStr">
         <is>
-          <t>7018859</t>
+          <t>7018857</t>
         </is>
       </c>
       <c r="B282" s="5" t="inlineStr">
@@ -12341,7 +12417,7 @@
     <row r="283">
       <c r="A283" s="6" t="inlineStr">
         <is>
-          <t>7018860</t>
+          <t>7018859</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
@@ -12361,7 +12437,7 @@
     <row r="284">
       <c r="A284" s="4" t="inlineStr">
         <is>
-          <t>7018874</t>
+          <t>7018860</t>
         </is>
       </c>
       <c r="B284" s="5" t="inlineStr">
@@ -12381,7 +12457,7 @@
     <row r="285">
       <c r="A285" s="6" t="inlineStr">
         <is>
-          <t>7018875</t>
+          <t>7018874</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
@@ -12401,7 +12477,7 @@
     <row r="286">
       <c r="A286" s="4" t="inlineStr">
         <is>
-          <t>7018876</t>
+          <t>7018875</t>
         </is>
       </c>
       <c r="B286" s="5" t="inlineStr">
@@ -12421,7 +12497,7 @@
     <row r="287">
       <c r="A287" s="6" t="inlineStr">
         <is>
-          <t>7018879</t>
+          <t>7018876</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
@@ -12441,7 +12517,7 @@
     <row r="288">
       <c r="A288" s="4" t="inlineStr">
         <is>
-          <t>7018880</t>
+          <t>7018879</t>
         </is>
       </c>
       <c r="B288" s="5" t="inlineStr">
@@ -12461,7 +12537,7 @@
     <row r="289">
       <c r="A289" s="6" t="inlineStr">
         <is>
-          <t>7018881</t>
+          <t>7018880</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
@@ -12481,7 +12557,7 @@
     <row r="290">
       <c r="A290" s="4" t="inlineStr">
         <is>
-          <t>7018882</t>
+          <t>7018881</t>
         </is>
       </c>
       <c r="B290" s="5" t="inlineStr">
@@ -12501,12 +12577,12 @@
     <row r="291">
       <c r="A291" s="6" t="inlineStr">
         <is>
-          <t>7015430</t>
+          <t>7018882</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>Interiörarmatur LED Velox Infälld rund</t>
+          <t>Interiörarmatur LED Velox Deco Rund</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
@@ -12521,7 +12597,7 @@
     <row r="292">
       <c r="A292" s="4" t="inlineStr">
         <is>
-          <t>7015431</t>
+          <t>7015430</t>
         </is>
       </c>
       <c r="B292" s="5" t="inlineStr">
@@ -12541,7 +12617,7 @@
     <row r="293">
       <c r="A293" s="6" t="inlineStr">
         <is>
-          <t>7015437</t>
+          <t>7015431</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
@@ -12561,7 +12637,7 @@
     <row r="294">
       <c r="A294" s="4" t="inlineStr">
         <is>
-          <t>7015439</t>
+          <t>7015437</t>
         </is>
       </c>
       <c r="B294" s="5" t="inlineStr">
@@ -12581,7 +12657,7 @@
     <row r="295">
       <c r="A295" s="6" t="inlineStr">
         <is>
-          <t>7015441</t>
+          <t>7015439</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
@@ -12601,7 +12677,7 @@
     <row r="296">
       <c r="A296" s="4" t="inlineStr">
         <is>
-          <t>7015443</t>
+          <t>7015441</t>
         </is>
       </c>
       <c r="B296" s="5" t="inlineStr">
@@ -12621,12 +12697,12 @@
     <row r="297">
       <c r="A297" s="6" t="inlineStr">
         <is>
-          <t>7015433</t>
+          <t>7015443</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>Interiörarmatur LED Velox infälld fyrkantig</t>
+          <t>Interiörarmatur LED Velox Infälld rund</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
@@ -12641,7 +12717,7 @@
     <row r="298">
       <c r="A298" s="4" t="inlineStr">
         <is>
-          <t>7015435</t>
+          <t>7015433</t>
         </is>
       </c>
       <c r="B298" s="5" t="inlineStr">
@@ -12661,21 +12737,21 @@
     <row r="299">
       <c r="A299" s="6" t="inlineStr">
         <is>
-          <t>7028947</t>
+          <t>7015435</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>Interiörarmatur Juna</t>
+          <t>Interiörarmatur LED Velox infälld fyrkantig</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>Esylux</t>
+          <t>Ensto</t>
         </is>
       </c>
       <c r="D299" s="6" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
     </row>
     <row r="300">
@@ -15355,7 +15431,7 @@
         </is>
       </c>
       <c r="D433" s="6" t="n">
-        <v>146</v>
+        <v>170</v>
       </c>
     </row>
     <row r="434">
@@ -15375,7 +15451,7 @@
         </is>
       </c>
       <c r="D434" s="4" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="435">
@@ -24615,7 +24691,7 @@
         </is>
       </c>
       <c r="D896" s="4" t="n">
-        <v>296</v>
+        <v>294</v>
       </c>
     </row>
     <row r="897">
@@ -29455,7 +29531,7 @@
         </is>
       </c>
       <c r="D1138" s="4" t="n">
-        <v>444</v>
+        <v>464</v>
       </c>
     </row>
     <row r="1139">
@@ -29475,7 +29551,7 @@
         </is>
       </c>
       <c r="D1139" s="6" t="n">
-        <v>361</v>
+        <v>350</v>
       </c>
     </row>
   </sheetData>

--- a/data/ahlsell_led_panel_inventory.xlsx
+++ b/data/ahlsell_led_panel_inventory.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y79"/>
+  <dimension ref="A1:Y80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -538,77 +538,77 @@
       </c>
       <c r="K1" s="3" t="inlineStr">
         <is>
+          <t>Nokalux</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="inlineStr">
+        <is>
           <t>Airam</t>
         </is>
       </c>
-      <c r="L1" s="3" t="inlineStr">
+      <c r="M1" s="3" t="inlineStr">
+        <is>
+          <t>Siteco</t>
+        </is>
+      </c>
+      <c r="N1" s="3" t="inlineStr">
+        <is>
+          <t>ZG Lighting</t>
+        </is>
+      </c>
+      <c r="O1" s="3" t="inlineStr">
+        <is>
+          <t>Norwesco</t>
+        </is>
+      </c>
+      <c r="P1" s="3" t="inlineStr">
+        <is>
+          <t>Esylux</t>
+        </is>
+      </c>
+      <c r="Q1" s="3" t="inlineStr">
+        <is>
+          <t>Easyform</t>
+        </is>
+      </c>
+      <c r="R1" s="3" t="inlineStr">
+        <is>
+          <t>Black Box</t>
+        </is>
+      </c>
+      <c r="S1" s="3" t="inlineStr">
+        <is>
+          <t>Ensto</t>
+        </is>
+      </c>
+      <c r="T1" s="3" t="inlineStr">
+        <is>
+          <t>Legrand</t>
+        </is>
+      </c>
+      <c r="U1" s="3" t="inlineStr">
         <is>
           <t>ANETA LIGHTING</t>
         </is>
       </c>
-      <c r="M1" s="3" t="inlineStr">
-        <is>
-          <t>Legrand</t>
-        </is>
-      </c>
-      <c r="N1" s="3" t="inlineStr">
-        <is>
-          <t>Ensto</t>
-        </is>
-      </c>
-      <c r="O1" s="3" t="inlineStr">
-        <is>
-          <t>ZG Lighting</t>
-        </is>
-      </c>
-      <c r="P1" s="3" t="inlineStr">
+      <c r="V1" s="3" t="inlineStr">
+        <is>
+          <t>THORN</t>
+        </is>
+      </c>
+      <c r="W1" s="3" t="inlineStr">
+        <is>
+          <t>Bergdahls</t>
+        </is>
+      </c>
+      <c r="X1" s="3" t="inlineStr">
+        <is>
+          <t>Westal</t>
+        </is>
+      </c>
+      <c r="Y1" s="3" t="inlineStr">
         <is>
           <t>Philips</t>
-        </is>
-      </c>
-      <c r="Q1" s="3" t="inlineStr">
-        <is>
-          <t>Esylux</t>
-        </is>
-      </c>
-      <c r="R1" s="3" t="inlineStr">
-        <is>
-          <t>Easyform</t>
-        </is>
-      </c>
-      <c r="S1" s="3" t="inlineStr">
-        <is>
-          <t>Black Box</t>
-        </is>
-      </c>
-      <c r="T1" s="3" t="inlineStr">
-        <is>
-          <t>Westal</t>
-        </is>
-      </c>
-      <c r="U1" s="3" t="inlineStr">
-        <is>
-          <t>THORN</t>
-        </is>
-      </c>
-      <c r="V1" s="3" t="inlineStr">
-        <is>
-          <t>Bergdahls</t>
-        </is>
-      </c>
-      <c r="W1" s="3" t="inlineStr">
-        <is>
-          <t>Siteco</t>
-        </is>
-      </c>
-      <c r="X1" s="3" t="inlineStr">
-        <is>
-          <t>Nokalux</t>
-        </is>
-      </c>
-      <c r="Y1" s="3" t="inlineStr">
-        <is>
-          <t>Norwesco</t>
         </is>
       </c>
     </row>
@@ -661,10 +661,10 @@
         <v>0</v>
       </c>
       <c r="P2" s="5" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="Q2" s="5" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="R2" s="5" t="n">
         <v>0</v>
@@ -740,10 +740,10 @@
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="Q3" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -819,10 +819,10 @@
         <v>0</v>
       </c>
       <c r="P4" s="5" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="Q4" s="5" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="R4" s="5" t="n">
         <v>0</v>
@@ -898,10 +898,10 @@
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="Q5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -977,10 +977,10 @@
         <v>0</v>
       </c>
       <c r="P6" s="5" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="Q6" s="5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="R6" s="5" t="n">
         <v>0</v>
@@ -1053,10 +1053,10 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="Q7" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -1132,10 +1132,10 @@
         <v>0</v>
       </c>
       <c r="P8" s="5" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="Q8" s="5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="R8" s="5" t="n">
         <v>0</v>
@@ -1211,10 +1211,10 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="Q9" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
@@ -1290,10 +1290,10 @@
         <v>0</v>
       </c>
       <c r="P10" s="5" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="Q10" s="5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="R10" s="5" t="n">
         <v>0</v>
@@ -1369,10 +1369,10 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="Q11" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -1448,10 +1448,10 @@
         <v>0</v>
       </c>
       <c r="P12" s="5" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="Q12" s="5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="R12" s="5" t="n">
         <v>0</v>
@@ -1527,10 +1527,10 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="Q13" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -1606,10 +1606,10 @@
         <v>0</v>
       </c>
       <c r="P14" s="5" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="Q14" s="5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="R14" s="5" t="n">
         <v>0</v>
@@ -1685,10 +1685,10 @@
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="Q15" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -1764,10 +1764,10 @@
         <v>0</v>
       </c>
       <c r="P16" s="5" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="Q16" s="5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="R16" s="5" t="n">
         <v>0</v>
@@ -1843,10 +1843,10 @@
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="Q17" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -1922,10 +1922,10 @@
         <v>0</v>
       </c>
       <c r="P18" s="5" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="Q18" s="5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="R18" s="5" t="n">
         <v>0</v>
@@ -2001,10 +2001,10 @@
         <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="Q19" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
@@ -2080,10 +2080,10 @@
         <v>0</v>
       </c>
       <c r="P20" s="5" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="Q20" s="5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="R20" s="5" t="n">
         <v>0</v>
@@ -2159,10 +2159,10 @@
         <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="Q21" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
         <v>0</v>
@@ -2238,10 +2238,10 @@
         <v>0</v>
       </c>
       <c r="P22" s="5" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="Q22" s="5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="R22" s="5" t="n">
         <v>0</v>
@@ -2317,10 +2317,10 @@
         <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="Q23" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
         <v>0</v>
@@ -2396,10 +2396,10 @@
         <v>0</v>
       </c>
       <c r="P24" s="5" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="Q24" s="5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="R24" s="5" t="n">
         <v>0</v>
@@ -2475,10 +2475,10 @@
         <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="Q25" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
         <v>0</v>
@@ -2554,10 +2554,10 @@
         <v>0</v>
       </c>
       <c r="P26" s="5" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="Q26" s="5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="R26" s="5" t="n">
         <v>0</v>
@@ -2633,10 +2633,10 @@
         <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="Q27" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
         <v>0</v>
@@ -2791,10 +2791,10 @@
         <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="Q29" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
         <v>0</v>
@@ -2870,10 +2870,10 @@
         <v>0</v>
       </c>
       <c r="P30" s="5" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="Q30" s="5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="R30" s="5" t="n">
         <v>0</v>
@@ -2949,10 +2949,10 @@
         <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="Q31" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
         <v>0</v>
@@ -3028,10 +3028,10 @@
         <v>0</v>
       </c>
       <c r="P32" s="5" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="Q32" s="5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="R32" s="5" t="n">
         <v>0</v>
@@ -3107,10 +3107,10 @@
         <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="Q33" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
         <v>0</v>
@@ -3186,10 +3186,10 @@
         <v>0</v>
       </c>
       <c r="P34" s="5" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="Q34" s="5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="R34" s="5" t="n">
         <v>0</v>
@@ -3265,10 +3265,10 @@
         <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="Q35" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
         <v>0</v>
@@ -3344,10 +3344,10 @@
         <v>0</v>
       </c>
       <c r="P36" s="5" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="Q36" s="5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="R36" s="5" t="n">
         <v>0</v>
@@ -3423,10 +3423,10 @@
         <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="Q37" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="R37" t="n">
         <v>0</v>
@@ -3502,10 +3502,10 @@
         <v>0</v>
       </c>
       <c r="P38" s="5" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="Q38" s="5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="R38" s="5" t="n">
         <v>0</v>
@@ -3581,10 +3581,10 @@
         <v>0</v>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="Q39" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="R39" t="n">
         <v>0</v>
@@ -3660,10 +3660,10 @@
         <v>0</v>
       </c>
       <c r="P40" s="5" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="Q40" s="5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="R40" s="5" t="n">
         <v>0</v>
@@ -3739,10 +3739,10 @@
         <v>0</v>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="Q41" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="R41" t="n">
         <v>0</v>
@@ -3818,10 +3818,10 @@
         <v>0</v>
       </c>
       <c r="P42" s="5" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="Q42" s="5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="R42" s="5" t="n">
         <v>0</v>
@@ -3897,10 +3897,10 @@
         <v>0</v>
       </c>
       <c r="P43" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="Q43" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="R43" t="n">
         <v>0</v>
@@ -3976,10 +3976,10 @@
         <v>0</v>
       </c>
       <c r="P44" s="5" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="Q44" s="5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="R44" s="5" t="n">
         <v>0</v>
@@ -4055,10 +4055,10 @@
         <v>0</v>
       </c>
       <c r="P45" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="Q45" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="R45" t="n">
         <v>0</v>
@@ -4134,10 +4134,10 @@
         <v>0</v>
       </c>
       <c r="P46" s="5" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="Q46" s="5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="R46" s="5" t="n">
         <v>0</v>
@@ -4213,10 +4213,10 @@
         <v>0</v>
       </c>
       <c r="P47" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="Q47" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="R47" t="n">
         <v>0</v>
@@ -4292,10 +4292,10 @@
         <v>0</v>
       </c>
       <c r="P48" s="5" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="Q48" s="5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="R48" s="5" t="n">
         <v>0</v>
@@ -4371,10 +4371,10 @@
         <v>0</v>
       </c>
       <c r="P49" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="Q49" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="R49" t="n">
         <v>0</v>
@@ -4450,10 +4450,10 @@
         <v>0</v>
       </c>
       <c r="P50" s="5" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="Q50" s="5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="R50" s="5" t="n">
         <v>0</v>
@@ -4529,10 +4529,10 @@
         <v>0</v>
       </c>
       <c r="P51" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="Q51" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="R51" t="n">
         <v>0</v>
@@ -4608,10 +4608,10 @@
         <v>0</v>
       </c>
       <c r="P52" s="5" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="Q52" s="5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="R52" s="5" t="n">
         <v>0</v>
@@ -4687,10 +4687,10 @@
         <v>0</v>
       </c>
       <c r="P53" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="Q53" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="R53" t="n">
         <v>0</v>
@@ -4766,10 +4766,10 @@
         <v>0</v>
       </c>
       <c r="P54" s="5" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="Q54" s="5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="R54" s="5" t="n">
         <v>0</v>
@@ -4845,10 +4845,10 @@
         <v>0</v>
       </c>
       <c r="P55" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="Q55" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="R55" t="n">
         <v>0</v>
@@ -4924,10 +4924,10 @@
         <v>0</v>
       </c>
       <c r="P56" s="5" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="Q56" s="5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="R56" s="5" t="n">
         <v>0</v>
@@ -5003,10 +5003,10 @@
         <v>0</v>
       </c>
       <c r="P57" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="Q57" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="R57" t="n">
         <v>0</v>
@@ -5082,10 +5082,10 @@
         <v>0</v>
       </c>
       <c r="P58" s="5" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="Q58" s="5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="R58" s="5" t="n">
         <v>0</v>
@@ -5161,10 +5161,10 @@
         <v>0</v>
       </c>
       <c r="P59" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="Q59" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="R59" t="n">
         <v>0</v>
@@ -5240,10 +5240,10 @@
         <v>0</v>
       </c>
       <c r="P60" s="5" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="Q60" s="5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="R60" s="5" t="n">
         <v>0</v>
@@ -5319,10 +5319,10 @@
         <v>0</v>
       </c>
       <c r="P61" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="Q61" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="R61" t="n">
         <v>0</v>
@@ -5398,10 +5398,10 @@
         <v>0</v>
       </c>
       <c r="P62" s="5" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="Q62" s="5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="R62" s="5" t="n">
         <v>0</v>
@@ -5477,10 +5477,10 @@
         <v>0</v>
       </c>
       <c r="P63" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="Q63" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="R63" t="n">
         <v>0</v>
@@ -5556,10 +5556,10 @@
         <v>0</v>
       </c>
       <c r="P64" s="5" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="Q64" s="5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="R64" s="5" t="n">
         <v>0</v>
@@ -5635,10 +5635,10 @@
         <v>0</v>
       </c>
       <c r="P65" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="Q65" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="R65" t="n">
         <v>0</v>
@@ -5714,10 +5714,10 @@
         <v>0</v>
       </c>
       <c r="P66" s="5" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="Q66" s="5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="R66" s="5" t="n">
         <v>0</v>
@@ -5792,7 +5792,7 @@
       <c r="O67" t="n">
         <v>0</v>
       </c>
-      <c r="P67" t="n">
+      <c r="Q67" t="n">
         <v>0</v>
       </c>
       <c r="R67" t="n">
@@ -5869,10 +5869,10 @@
         <v>0</v>
       </c>
       <c r="P68" s="5" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="Q68" s="5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="R68" s="5" t="n">
         <v>0</v>
@@ -5944,7 +5944,7 @@
       <c r="O69" t="n">
         <v>0</v>
       </c>
-      <c r="P69" t="n">
+      <c r="Q69" t="n">
         <v>0</v>
       </c>
       <c r="R69" t="n">
@@ -6021,10 +6021,10 @@
         <v>0</v>
       </c>
       <c r="P70" s="5" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="Q70" s="5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="R70" s="5" t="n">
         <v>0</v>
@@ -6100,10 +6100,10 @@
         <v>0</v>
       </c>
       <c r="P71" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="Q71" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="R71" t="n">
         <v>0</v>
@@ -6179,10 +6179,10 @@
         <v>0</v>
       </c>
       <c r="P72" s="5" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="Q72" s="5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="R72" s="5" t="n">
         <v>0</v>
@@ -6258,10 +6258,10 @@
         <v>0</v>
       </c>
       <c r="P73" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="Q73" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="R73" t="n">
         <v>0</v>
@@ -6337,10 +6337,10 @@
         <v>0</v>
       </c>
       <c r="P74" s="5" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="Q74" s="5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="R74" s="5" t="n">
         <v>0</v>
@@ -6416,10 +6416,10 @@
         <v>0</v>
       </c>
       <c r="P75" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="Q75" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="R75" t="n">
         <v>0</v>
@@ -6485,7 +6485,9 @@
       <c r="L76" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="M76" s="5" t="n"/>
+      <c r="M76" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="N76" s="5" t="n">
         <v>0</v>
       </c>
@@ -6493,18 +6495,16 @@
         <v>0</v>
       </c>
       <c r="P76" s="5" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="Q76" s="5" t="n">
-        <v>24</v>
-      </c>
-      <c r="R76" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S76" s="5" t="n"/>
-      <c r="T76" s="5" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="R76" s="5" t="n"/>
+      <c r="S76" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T76" s="5" t="n"/>
       <c r="U76" s="5" t="n">
         <v>0</v>
       </c>
@@ -6569,7 +6569,7 @@
       <c r="O77" t="n">
         <v>0</v>
       </c>
-      <c r="P77" t="n">
+      <c r="Q77" t="n">
         <v>0</v>
       </c>
       <c r="R77" t="n">
@@ -6646,10 +6646,10 @@
         <v>0</v>
       </c>
       <c r="P78" s="5" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="Q78" s="5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="R78" s="5" t="n">
         <v>0</v>
@@ -6724,7 +6724,7 @@
       <c r="O79" t="n">
         <v>0</v>
       </c>
-      <c r="P79" t="n">
+      <c r="Q79" t="n">
         <v>0</v>
       </c>
       <c r="R79" t="n">
@@ -6749,6 +6749,83 @@
         <v>0</v>
       </c>
       <c r="Y79" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B80" s="5" t="n">
+        <v>879</v>
+      </c>
+      <c r="C80" s="5" t="n">
+        <v>537</v>
+      </c>
+      <c r="D80" s="5" t="n">
+        <v>391</v>
+      </c>
+      <c r="E80" s="5" t="n">
+        <v>372</v>
+      </c>
+      <c r="F80" s="5" t="n">
+        <v>207</v>
+      </c>
+      <c r="G80" s="5" t="n">
+        <v>90</v>
+      </c>
+      <c r="H80" s="5" t="n">
+        <v>42</v>
+      </c>
+      <c r="I80" s="5" t="n">
+        <v>26</v>
+      </c>
+      <c r="J80" s="5" t="n">
+        <v>23</v>
+      </c>
+      <c r="K80" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L80" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M80" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N80" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O80" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P80" s="5" t="n"/>
+      <c r="Q80" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R80" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S80" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T80" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U80" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V80" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W80" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X80" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y80" s="5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6790,7 +6867,7 @@
       </c>
       <c r="D1" s="3" t="inlineStr">
         <is>
-          <t>Lager (2026-09-23)</t>
+          <t>Lager (2026-09-24)</t>
         </is>
       </c>
     </row>
@@ -6811,7 +6888,7 @@
         </is>
       </c>
       <c r="D2" s="4" t="n">
-        <v>540</v>
+        <v>537</v>
       </c>
     </row>
     <row r="3">
@@ -19311,7 +19388,7 @@
         </is>
       </c>
       <c r="D627" s="6" t="n">
-        <v>46</v>
+        <v>36</v>
       </c>
     </row>
     <row r="628">
@@ -24551,7 +24628,7 @@
         </is>
       </c>
       <c r="D889" s="6" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="890">
@@ -25131,7 +25208,7 @@
         </is>
       </c>
       <c r="D918" s="4" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="919">
@@ -26371,7 +26448,7 @@
         </is>
       </c>
       <c r="D980" s="4" t="n">
-        <v>114</v>
+        <v>117</v>
       </c>
     </row>
     <row r="981">
@@ -29451,7 +29528,7 @@
         </is>
       </c>
       <c r="D1134" s="4" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="1135">
@@ -29531,7 +29608,7 @@
         </is>
       </c>
       <c r="D1138" s="4" t="n">
-        <v>464</v>
+        <v>460</v>
       </c>
     </row>
     <row r="1139">
@@ -29551,7 +29628,7 @@
         </is>
       </c>
       <c r="D1139" s="6" t="n">
-        <v>350</v>
+        <v>334</v>
       </c>
     </row>
   </sheetData>

--- a/data/ahlsell_led_panel_inventory.xlsx
+++ b/data/ahlsell_led_panel_inventory.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y80"/>
+  <dimension ref="A1:Y81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -533,82 +533,82 @@
       </c>
       <c r="J1" s="3" t="inlineStr">
         <is>
+          <t>Esylux</t>
+        </is>
+      </c>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
           <t>Ledvance</t>
         </is>
       </c>
-      <c r="K1" s="3" t="inlineStr">
+      <c r="L1" s="3" t="inlineStr">
+        <is>
+          <t>Airam</t>
+        </is>
+      </c>
+      <c r="M1" s="3" t="inlineStr">
         <is>
           <t>Nokalux</t>
         </is>
       </c>
-      <c r="L1" s="3" t="inlineStr">
-        <is>
-          <t>Airam</t>
-        </is>
-      </c>
-      <c r="M1" s="3" t="inlineStr">
+      <c r="N1" s="3" t="inlineStr">
+        <is>
+          <t>Ensto</t>
+        </is>
+      </c>
+      <c r="O1" s="3" t="inlineStr">
         <is>
           <t>Siteco</t>
         </is>
       </c>
-      <c r="N1" s="3" t="inlineStr">
+      <c r="P1" s="3" t="inlineStr">
+        <is>
+          <t>Black Box</t>
+        </is>
+      </c>
+      <c r="Q1" s="3" t="inlineStr">
+        <is>
+          <t>ANETA LIGHTING</t>
+        </is>
+      </c>
+      <c r="R1" s="3" t="inlineStr">
+        <is>
+          <t>Easyform</t>
+        </is>
+      </c>
+      <c r="S1" s="3" t="inlineStr">
+        <is>
+          <t>Bergdahls</t>
+        </is>
+      </c>
+      <c r="T1" s="3" t="inlineStr">
+        <is>
+          <t>Westal</t>
+        </is>
+      </c>
+      <c r="U1" s="3" t="inlineStr">
+        <is>
+          <t>Norwesco</t>
+        </is>
+      </c>
+      <c r="V1" s="3" t="inlineStr">
+        <is>
+          <t>THORN</t>
+        </is>
+      </c>
+      <c r="W1" s="3" t="inlineStr">
+        <is>
+          <t>Philips</t>
+        </is>
+      </c>
+      <c r="X1" s="3" t="inlineStr">
         <is>
           <t>ZG Lighting</t>
         </is>
       </c>
-      <c r="O1" s="3" t="inlineStr">
-        <is>
-          <t>Norwesco</t>
-        </is>
-      </c>
-      <c r="P1" s="3" t="inlineStr">
-        <is>
-          <t>Esylux</t>
-        </is>
-      </c>
-      <c r="Q1" s="3" t="inlineStr">
-        <is>
-          <t>Easyform</t>
-        </is>
-      </c>
-      <c r="R1" s="3" t="inlineStr">
-        <is>
-          <t>Black Box</t>
-        </is>
-      </c>
-      <c r="S1" s="3" t="inlineStr">
-        <is>
-          <t>Ensto</t>
-        </is>
-      </c>
-      <c r="T1" s="3" t="inlineStr">
+      <c r="Y1" s="3" t="inlineStr">
         <is>
           <t>Legrand</t>
-        </is>
-      </c>
-      <c r="U1" s="3" t="inlineStr">
-        <is>
-          <t>ANETA LIGHTING</t>
-        </is>
-      </c>
-      <c r="V1" s="3" t="inlineStr">
-        <is>
-          <t>THORN</t>
-        </is>
-      </c>
-      <c r="W1" s="3" t="inlineStr">
-        <is>
-          <t>Bergdahls</t>
-        </is>
-      </c>
-      <c r="X1" s="3" t="inlineStr">
-        <is>
-          <t>Westal</t>
-        </is>
-      </c>
-      <c r="Y1" s="3" t="inlineStr">
-        <is>
-          <t>Philips</t>
         </is>
       </c>
     </row>
@@ -643,11 +643,11 @@
         <v>33</v>
       </c>
       <c r="J2" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="K2" s="5" t="n">
         <v>17</v>
       </c>
-      <c r="K2" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="L2" s="5" t="n">
         <v>0</v>
       </c>
@@ -661,7 +661,7 @@
         <v>0</v>
       </c>
       <c r="P2" s="5" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="Q2" s="5" t="n">
         <v>0</v>
@@ -722,11 +722,11 @@
         <v>33</v>
       </c>
       <c r="J3" t="n">
+        <v>25</v>
+      </c>
+      <c r="K3" t="n">
         <v>17</v>
       </c>
-      <c r="K3" t="n">
-        <v>0</v>
-      </c>
       <c r="L3" t="n">
         <v>0</v>
       </c>
@@ -740,7 +740,7 @@
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -801,11 +801,11 @@
         <v>33</v>
       </c>
       <c r="J4" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="K4" s="5" t="n">
         <v>17</v>
       </c>
-      <c r="K4" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="L4" s="5" t="n">
         <v>0</v>
       </c>
@@ -819,7 +819,7 @@
         <v>0</v>
       </c>
       <c r="P4" s="5" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="Q4" s="5" t="n">
         <v>0</v>
@@ -880,11 +880,11 @@
         <v>33</v>
       </c>
       <c r="J5" t="n">
+        <v>24</v>
+      </c>
+      <c r="K5" t="n">
         <v>17</v>
       </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
       <c r="L5" t="n">
         <v>0</v>
       </c>
@@ -898,7 +898,7 @@
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -959,11 +959,11 @@
         <v>33</v>
       </c>
       <c r="J6" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="K6" s="5" t="n">
         <v>17</v>
       </c>
-      <c r="K6" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="L6" s="5" t="n">
         <v>0</v>
       </c>
@@ -977,7 +977,7 @@
         <v>0</v>
       </c>
       <c r="P6" s="5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="Q6" s="5" t="n">
         <v>0</v>
@@ -1035,11 +1035,11 @@
         <v>33</v>
       </c>
       <c r="J7" t="n">
+        <v>24</v>
+      </c>
+      <c r="K7" t="n">
         <v>17</v>
       </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
       <c r="L7" t="n">
         <v>0</v>
       </c>
@@ -1053,7 +1053,7 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1114,11 +1114,11 @@
         <v>33</v>
       </c>
       <c r="J8" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="K8" s="5" t="n">
         <v>17</v>
       </c>
-      <c r="K8" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="L8" s="5" t="n">
         <v>0</v>
       </c>
@@ -1132,7 +1132,7 @@
         <v>0</v>
       </c>
       <c r="P8" s="5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="Q8" s="5" t="n">
         <v>0</v>
@@ -1193,11 +1193,11 @@
         <v>33</v>
       </c>
       <c r="J9" t="n">
+        <v>24</v>
+      </c>
+      <c r="K9" t="n">
         <v>17</v>
       </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
       <c r="L9" t="n">
         <v>0</v>
       </c>
@@ -1211,7 +1211,7 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -1272,11 +1272,11 @@
         <v>33</v>
       </c>
       <c r="J10" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="K10" s="5" t="n">
         <v>17</v>
       </c>
-      <c r="K10" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="L10" s="5" t="n">
         <v>0</v>
       </c>
@@ -1290,7 +1290,7 @@
         <v>0</v>
       </c>
       <c r="P10" s="5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="Q10" s="5" t="n">
         <v>0</v>
@@ -1351,11 +1351,11 @@
         <v>33</v>
       </c>
       <c r="J11" t="n">
+        <v>24</v>
+      </c>
+      <c r="K11" t="n">
         <v>17</v>
       </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
       <c r="L11" t="n">
         <v>0</v>
       </c>
@@ -1369,7 +1369,7 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -1430,11 +1430,11 @@
         <v>33</v>
       </c>
       <c r="J12" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="K12" s="5" t="n">
         <v>17</v>
       </c>
-      <c r="K12" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="L12" s="5" t="n">
         <v>0</v>
       </c>
@@ -1448,7 +1448,7 @@
         <v>0</v>
       </c>
       <c r="P12" s="5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="Q12" s="5" t="n">
         <v>0</v>
@@ -1509,11 +1509,11 @@
         <v>33</v>
       </c>
       <c r="J13" t="n">
+        <v>24</v>
+      </c>
+      <c r="K13" t="n">
         <v>17</v>
       </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
       <c r="L13" t="n">
         <v>0</v>
       </c>
@@ -1527,7 +1527,7 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -1588,11 +1588,11 @@
         <v>33</v>
       </c>
       <c r="J14" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="K14" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="K14" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="L14" s="5" t="n">
         <v>0</v>
       </c>
@@ -1606,7 +1606,7 @@
         <v>0</v>
       </c>
       <c r="P14" s="5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="Q14" s="5" t="n">
         <v>0</v>
@@ -1667,11 +1667,11 @@
         <v>33</v>
       </c>
       <c r="J15" t="n">
+        <v>24</v>
+      </c>
+      <c r="K15" t="n">
         <v>17</v>
       </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
       <c r="L15" t="n">
         <v>0</v>
       </c>
@@ -1685,7 +1685,7 @@
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -1746,11 +1746,11 @@
         <v>33</v>
       </c>
       <c r="J16" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="K16" s="5" t="n">
         <v>17</v>
       </c>
-      <c r="K16" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="L16" s="5" t="n">
         <v>0</v>
       </c>
@@ -1764,7 +1764,7 @@
         <v>0</v>
       </c>
       <c r="P16" s="5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="Q16" s="5" t="n">
         <v>0</v>
@@ -1825,11 +1825,11 @@
         <v>33</v>
       </c>
       <c r="J17" t="n">
+        <v>24</v>
+      </c>
+      <c r="K17" t="n">
         <v>17</v>
       </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
       <c r="L17" t="n">
         <v>0</v>
       </c>
@@ -1843,7 +1843,7 @@
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -1904,11 +1904,11 @@
         <v>33</v>
       </c>
       <c r="J18" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="K18" s="5" t="n">
         <v>17</v>
       </c>
-      <c r="K18" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="L18" s="5" t="n">
         <v>0</v>
       </c>
@@ -1922,7 +1922,7 @@
         <v>0</v>
       </c>
       <c r="P18" s="5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="Q18" s="5" t="n">
         <v>0</v>
@@ -1983,11 +1983,11 @@
         <v>33</v>
       </c>
       <c r="J19" t="n">
+        <v>24</v>
+      </c>
+      <c r="K19" t="n">
         <v>17</v>
       </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
       <c r="L19" t="n">
         <v>0</v>
       </c>
@@ -2001,7 +2001,7 @@
         <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -2062,11 +2062,11 @@
         <v>33</v>
       </c>
       <c r="J20" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="K20" s="5" t="n">
         <v>17</v>
       </c>
-      <c r="K20" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="L20" s="5" t="n">
         <v>0</v>
       </c>
@@ -2080,7 +2080,7 @@
         <v>0</v>
       </c>
       <c r="P20" s="5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="Q20" s="5" t="n">
         <v>0</v>
@@ -2141,11 +2141,11 @@
         <v>33</v>
       </c>
       <c r="J21" t="n">
+        <v>24</v>
+      </c>
+      <c r="K21" t="n">
         <v>17</v>
       </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
       <c r="L21" t="n">
         <v>0</v>
       </c>
@@ -2159,7 +2159,7 @@
         <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
@@ -2220,11 +2220,11 @@
         <v>33</v>
       </c>
       <c r="J22" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="K22" s="5" t="n">
         <v>17</v>
       </c>
-      <c r="K22" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="L22" s="5" t="n">
         <v>0</v>
       </c>
@@ -2238,7 +2238,7 @@
         <v>0</v>
       </c>
       <c r="P22" s="5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="Q22" s="5" t="n">
         <v>0</v>
@@ -2299,11 +2299,11 @@
         <v>33</v>
       </c>
       <c r="J23" t="n">
+        <v>24</v>
+      </c>
+      <c r="K23" t="n">
         <v>17</v>
       </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
       <c r="L23" t="n">
         <v>0</v>
       </c>
@@ -2317,7 +2317,7 @@
         <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
@@ -2378,11 +2378,11 @@
         <v>33</v>
       </c>
       <c r="J24" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="K24" s="5" t="n">
         <v>17</v>
       </c>
-      <c r="K24" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="L24" s="5" t="n">
         <v>0</v>
       </c>
@@ -2396,7 +2396,7 @@
         <v>0</v>
       </c>
       <c r="P24" s="5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="Q24" s="5" t="n">
         <v>0</v>
@@ -2457,11 +2457,11 @@
         <v>33</v>
       </c>
       <c r="J25" t="n">
+        <v>24</v>
+      </c>
+      <c r="K25" t="n">
         <v>17</v>
       </c>
-      <c r="K25" t="n">
-        <v>0</v>
-      </c>
       <c r="L25" t="n">
         <v>0</v>
       </c>
@@ -2475,7 +2475,7 @@
         <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -2536,11 +2536,11 @@
         <v>33</v>
       </c>
       <c r="J26" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="K26" s="5" t="n">
         <v>17</v>
       </c>
-      <c r="K26" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="L26" s="5" t="n">
         <v>0</v>
       </c>
@@ -2554,7 +2554,7 @@
         <v>0</v>
       </c>
       <c r="P26" s="5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="Q26" s="5" t="n">
         <v>0</v>
@@ -2615,11 +2615,11 @@
         <v>33</v>
       </c>
       <c r="J27" t="n">
+        <v>24</v>
+      </c>
+      <c r="K27" t="n">
         <v>17</v>
       </c>
-      <c r="K27" t="n">
-        <v>0</v>
-      </c>
       <c r="L27" t="n">
         <v>0</v>
       </c>
@@ -2633,7 +2633,7 @@
         <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
@@ -2694,10 +2694,10 @@
         <v>33</v>
       </c>
       <c r="J28" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" s="5" t="n">
         <v>17</v>
-      </c>
-      <c r="K28" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="L28" s="5" t="n">
         <v>0</v>
@@ -2773,11 +2773,11 @@
         <v>33</v>
       </c>
       <c r="J29" t="n">
+        <v>24</v>
+      </c>
+      <c r="K29" t="n">
         <v>17</v>
       </c>
-      <c r="K29" t="n">
-        <v>0</v>
-      </c>
       <c r="L29" t="n">
         <v>0</v>
       </c>
@@ -2791,7 +2791,7 @@
         <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
         <v>0</v>
@@ -2852,11 +2852,11 @@
         <v>33</v>
       </c>
       <c r="J30" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="K30" s="5" t="n">
         <v>17</v>
       </c>
-      <c r="K30" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="L30" s="5" t="n">
         <v>0</v>
       </c>
@@ -2870,7 +2870,7 @@
         <v>0</v>
       </c>
       <c r="P30" s="5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="Q30" s="5" t="n">
         <v>0</v>
@@ -2931,11 +2931,11 @@
         <v>33</v>
       </c>
       <c r="J31" t="n">
+        <v>24</v>
+      </c>
+      <c r="K31" t="n">
         <v>17</v>
       </c>
-      <c r="K31" t="n">
-        <v>0</v>
-      </c>
       <c r="L31" t="n">
         <v>0</v>
       </c>
@@ -2949,7 +2949,7 @@
         <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
         <v>0</v>
@@ -3010,11 +3010,11 @@
         <v>33</v>
       </c>
       <c r="J32" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="K32" s="5" t="n">
         <v>17</v>
       </c>
-      <c r="K32" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="L32" s="5" t="n">
         <v>0</v>
       </c>
@@ -3028,7 +3028,7 @@
         <v>0</v>
       </c>
       <c r="P32" s="5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="Q32" s="5" t="n">
         <v>0</v>
@@ -3089,11 +3089,11 @@
         <v>33</v>
       </c>
       <c r="J33" t="n">
+        <v>24</v>
+      </c>
+      <c r="K33" t="n">
         <v>17</v>
       </c>
-      <c r="K33" t="n">
-        <v>0</v>
-      </c>
       <c r="L33" t="n">
         <v>0</v>
       </c>
@@ -3107,7 +3107,7 @@
         <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="Q33" t="n">
         <v>0</v>
@@ -3168,11 +3168,11 @@
         <v>33</v>
       </c>
       <c r="J34" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="K34" s="5" t="n">
         <v>17</v>
       </c>
-      <c r="K34" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="L34" s="5" t="n">
         <v>0</v>
       </c>
@@ -3186,7 +3186,7 @@
         <v>0</v>
       </c>
       <c r="P34" s="5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="Q34" s="5" t="n">
         <v>0</v>
@@ -3247,11 +3247,11 @@
         <v>33</v>
       </c>
       <c r="J35" t="n">
+        <v>24</v>
+      </c>
+      <c r="K35" t="n">
         <v>17</v>
       </c>
-      <c r="K35" t="n">
-        <v>0</v>
-      </c>
       <c r="L35" t="n">
         <v>0</v>
       </c>
@@ -3265,7 +3265,7 @@
         <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
         <v>0</v>
@@ -3326,11 +3326,11 @@
         <v>33</v>
       </c>
       <c r="J36" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="K36" s="5" t="n">
         <v>17</v>
       </c>
-      <c r="K36" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="L36" s="5" t="n">
         <v>0</v>
       </c>
@@ -3344,7 +3344,7 @@
         <v>0</v>
       </c>
       <c r="P36" s="5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="Q36" s="5" t="n">
         <v>0</v>
@@ -3405,11 +3405,11 @@
         <v>33</v>
       </c>
       <c r="J37" t="n">
+        <v>24</v>
+      </c>
+      <c r="K37" t="n">
         <v>17</v>
       </c>
-      <c r="K37" t="n">
-        <v>0</v>
-      </c>
       <c r="L37" t="n">
         <v>0</v>
       </c>
@@ -3423,7 +3423,7 @@
         <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="Q37" t="n">
         <v>0</v>
@@ -3484,11 +3484,11 @@
         <v>33</v>
       </c>
       <c r="J38" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="K38" s="5" t="n">
         <v>17</v>
       </c>
-      <c r="K38" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="L38" s="5" t="n">
         <v>0</v>
       </c>
@@ -3502,7 +3502,7 @@
         <v>0</v>
       </c>
       <c r="P38" s="5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="Q38" s="5" t="n">
         <v>0</v>
@@ -3563,11 +3563,11 @@
         <v>33</v>
       </c>
       <c r="J39" t="n">
+        <v>24</v>
+      </c>
+      <c r="K39" t="n">
         <v>17</v>
       </c>
-      <c r="K39" t="n">
-        <v>0</v>
-      </c>
       <c r="L39" t="n">
         <v>0</v>
       </c>
@@ -3581,7 +3581,7 @@
         <v>0</v>
       </c>
       <c r="P39" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="Q39" t="n">
         <v>0</v>
@@ -3642,11 +3642,11 @@
         <v>33</v>
       </c>
       <c r="J40" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="K40" s="5" t="n">
         <v>17</v>
       </c>
-      <c r="K40" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="L40" s="5" t="n">
         <v>0</v>
       </c>
@@ -3660,7 +3660,7 @@
         <v>0</v>
       </c>
       <c r="P40" s="5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="Q40" s="5" t="n">
         <v>0</v>
@@ -3721,11 +3721,11 @@
         <v>33</v>
       </c>
       <c r="J41" t="n">
+        <v>24</v>
+      </c>
+      <c r="K41" t="n">
         <v>17</v>
       </c>
-      <c r="K41" t="n">
-        <v>0</v>
-      </c>
       <c r="L41" t="n">
         <v>0</v>
       </c>
@@ -3739,7 +3739,7 @@
         <v>0</v>
       </c>
       <c r="P41" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="Q41" t="n">
         <v>0</v>
@@ -3800,11 +3800,11 @@
         <v>33</v>
       </c>
       <c r="J42" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="K42" s="5" t="n">
         <v>17</v>
       </c>
-      <c r="K42" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="L42" s="5" t="n">
         <v>0</v>
       </c>
@@ -3818,7 +3818,7 @@
         <v>0</v>
       </c>
       <c r="P42" s="5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="Q42" s="5" t="n">
         <v>0</v>
@@ -3879,11 +3879,11 @@
         <v>33</v>
       </c>
       <c r="J43" t="n">
+        <v>24</v>
+      </c>
+      <c r="K43" t="n">
         <v>17</v>
       </c>
-      <c r="K43" t="n">
-        <v>0</v>
-      </c>
       <c r="L43" t="n">
         <v>0</v>
       </c>
@@ -3897,7 +3897,7 @@
         <v>0</v>
       </c>
       <c r="P43" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="Q43" t="n">
         <v>0</v>
@@ -3958,11 +3958,11 @@
         <v>33</v>
       </c>
       <c r="J44" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="K44" s="5" t="n">
         <v>17</v>
       </c>
-      <c r="K44" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="L44" s="5" t="n">
         <v>0</v>
       </c>
@@ -3976,7 +3976,7 @@
         <v>0</v>
       </c>
       <c r="P44" s="5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="Q44" s="5" t="n">
         <v>0</v>
@@ -4037,11 +4037,11 @@
         <v>33</v>
       </c>
       <c r="J45" t="n">
+        <v>24</v>
+      </c>
+      <c r="K45" t="n">
         <v>17</v>
       </c>
-      <c r="K45" t="n">
-        <v>0</v>
-      </c>
       <c r="L45" t="n">
         <v>0</v>
       </c>
@@ -4055,7 +4055,7 @@
         <v>0</v>
       </c>
       <c r="P45" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="Q45" t="n">
         <v>0</v>
@@ -4116,11 +4116,11 @@
         <v>33</v>
       </c>
       <c r="J46" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="K46" s="5" t="n">
         <v>17</v>
       </c>
-      <c r="K46" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="L46" s="5" t="n">
         <v>0</v>
       </c>
@@ -4134,7 +4134,7 @@
         <v>0</v>
       </c>
       <c r="P46" s="5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="Q46" s="5" t="n">
         <v>0</v>
@@ -4195,11 +4195,11 @@
         <v>33</v>
       </c>
       <c r="J47" t="n">
+        <v>24</v>
+      </c>
+      <c r="K47" t="n">
         <v>17</v>
       </c>
-      <c r="K47" t="n">
-        <v>0</v>
-      </c>
       <c r="L47" t="n">
         <v>0</v>
       </c>
@@ -4213,7 +4213,7 @@
         <v>0</v>
       </c>
       <c r="P47" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="Q47" t="n">
         <v>0</v>
@@ -4274,11 +4274,11 @@
         <v>33</v>
       </c>
       <c r="J48" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="K48" s="5" t="n">
         <v>17</v>
       </c>
-      <c r="K48" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="L48" s="5" t="n">
         <v>0</v>
       </c>
@@ -4292,7 +4292,7 @@
         <v>0</v>
       </c>
       <c r="P48" s="5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="Q48" s="5" t="n">
         <v>0</v>
@@ -4353,11 +4353,11 @@
         <v>33</v>
       </c>
       <c r="J49" t="n">
+        <v>24</v>
+      </c>
+      <c r="K49" t="n">
         <v>17</v>
       </c>
-      <c r="K49" t="n">
-        <v>0</v>
-      </c>
       <c r="L49" t="n">
         <v>0</v>
       </c>
@@ -4371,7 +4371,7 @@
         <v>0</v>
       </c>
       <c r="P49" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="Q49" t="n">
         <v>0</v>
@@ -4432,11 +4432,11 @@
         <v>33</v>
       </c>
       <c r="J50" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="K50" s="5" t="n">
         <v>17</v>
       </c>
-      <c r="K50" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="L50" s="5" t="n">
         <v>0</v>
       </c>
@@ -4450,7 +4450,7 @@
         <v>0</v>
       </c>
       <c r="P50" s="5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="Q50" s="5" t="n">
         <v>0</v>
@@ -4511,11 +4511,11 @@
         <v>33</v>
       </c>
       <c r="J51" t="n">
+        <v>24</v>
+      </c>
+      <c r="K51" t="n">
         <v>17</v>
       </c>
-      <c r="K51" t="n">
-        <v>0</v>
-      </c>
       <c r="L51" t="n">
         <v>0</v>
       </c>
@@ -4529,7 +4529,7 @@
         <v>0</v>
       </c>
       <c r="P51" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="Q51" t="n">
         <v>0</v>
@@ -4590,11 +4590,11 @@
         <v>30</v>
       </c>
       <c r="J52" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="K52" s="5" t="n">
         <v>17</v>
       </c>
-      <c r="K52" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="L52" s="5" t="n">
         <v>0</v>
       </c>
@@ -4608,7 +4608,7 @@
         <v>0</v>
       </c>
       <c r="P52" s="5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="Q52" s="5" t="n">
         <v>0</v>
@@ -4669,11 +4669,11 @@
         <v>30</v>
       </c>
       <c r="J53" t="n">
+        <v>24</v>
+      </c>
+      <c r="K53" t="n">
         <v>17</v>
       </c>
-      <c r="K53" t="n">
-        <v>0</v>
-      </c>
       <c r="L53" t="n">
         <v>0</v>
       </c>
@@ -4687,7 +4687,7 @@
         <v>0</v>
       </c>
       <c r="P53" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="Q53" t="n">
         <v>0</v>
@@ -4748,11 +4748,11 @@
         <v>30</v>
       </c>
       <c r="J54" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="K54" s="5" t="n">
         <v>17</v>
       </c>
-      <c r="K54" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="L54" s="5" t="n">
         <v>0</v>
       </c>
@@ -4766,7 +4766,7 @@
         <v>0</v>
       </c>
       <c r="P54" s="5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="Q54" s="5" t="n">
         <v>0</v>
@@ -4827,11 +4827,11 @@
         <v>30</v>
       </c>
       <c r="J55" t="n">
+        <v>24</v>
+      </c>
+      <c r="K55" t="n">
         <v>17</v>
       </c>
-      <c r="K55" t="n">
-        <v>0</v>
-      </c>
       <c r="L55" t="n">
         <v>0</v>
       </c>
@@ -4845,7 +4845,7 @@
         <v>0</v>
       </c>
       <c r="P55" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="Q55" t="n">
         <v>0</v>
@@ -4906,11 +4906,11 @@
         <v>30</v>
       </c>
       <c r="J56" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="K56" s="5" t="n">
         <v>17</v>
       </c>
-      <c r="K56" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="L56" s="5" t="n">
         <v>0</v>
       </c>
@@ -4924,7 +4924,7 @@
         <v>0</v>
       </c>
       <c r="P56" s="5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="Q56" s="5" t="n">
         <v>0</v>
@@ -4985,11 +4985,11 @@
         <v>24</v>
       </c>
       <c r="J57" t="n">
+        <v>24</v>
+      </c>
+      <c r="K57" t="n">
         <v>22</v>
       </c>
-      <c r="K57" t="n">
-        <v>0</v>
-      </c>
       <c r="L57" t="n">
         <v>0</v>
       </c>
@@ -5003,7 +5003,7 @@
         <v>0</v>
       </c>
       <c r="P57" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="Q57" t="n">
         <v>0</v>
@@ -5064,11 +5064,11 @@
         <v>26</v>
       </c>
       <c r="J58" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="K58" s="5" t="n">
         <v>22</v>
       </c>
-      <c r="K58" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="L58" s="5" t="n">
         <v>0</v>
       </c>
@@ -5082,7 +5082,7 @@
         <v>0</v>
       </c>
       <c r="P58" s="5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="Q58" s="5" t="n">
         <v>0</v>
@@ -5143,11 +5143,11 @@
         <v>26</v>
       </c>
       <c r="J59" t="n">
+        <v>24</v>
+      </c>
+      <c r="K59" t="n">
         <v>16</v>
       </c>
-      <c r="K59" t="n">
-        <v>0</v>
-      </c>
       <c r="L59" t="n">
         <v>0</v>
       </c>
@@ -5161,7 +5161,7 @@
         <v>0</v>
       </c>
       <c r="P59" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="Q59" t="n">
         <v>0</v>
@@ -5222,11 +5222,11 @@
         <v>23</v>
       </c>
       <c r="J60" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="K60" s="5" t="n">
         <v>16</v>
       </c>
-      <c r="K60" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="L60" s="5" t="n">
         <v>0</v>
       </c>
@@ -5240,7 +5240,7 @@
         <v>0</v>
       </c>
       <c r="P60" s="5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="Q60" s="5" t="n">
         <v>0</v>
@@ -5301,11 +5301,11 @@
         <v>29</v>
       </c>
       <c r="J61" t="n">
+        <v>24</v>
+      </c>
+      <c r="K61" t="n">
         <v>16</v>
       </c>
-      <c r="K61" t="n">
-        <v>0</v>
-      </c>
       <c r="L61" t="n">
         <v>0</v>
       </c>
@@ -5319,7 +5319,7 @@
         <v>0</v>
       </c>
       <c r="P61" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="Q61" t="n">
         <v>0</v>
@@ -5380,11 +5380,11 @@
         <v>29</v>
       </c>
       <c r="J62" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="K62" s="5" t="n">
         <v>16</v>
       </c>
-      <c r="K62" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="L62" s="5" t="n">
         <v>0</v>
       </c>
@@ -5398,7 +5398,7 @@
         <v>0</v>
       </c>
       <c r="P62" s="5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="Q62" s="5" t="n">
         <v>0</v>
@@ -5459,11 +5459,11 @@
         <v>29</v>
       </c>
       <c r="J63" t="n">
+        <v>24</v>
+      </c>
+      <c r="K63" t="n">
         <v>16</v>
       </c>
-      <c r="K63" t="n">
-        <v>0</v>
-      </c>
       <c r="L63" t="n">
         <v>0</v>
       </c>
@@ -5477,7 +5477,7 @@
         <v>0</v>
       </c>
       <c r="P63" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="Q63" t="n">
         <v>0</v>
@@ -5538,11 +5538,11 @@
         <v>20</v>
       </c>
       <c r="J64" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="K64" s="5" t="n">
         <v>16</v>
       </c>
-      <c r="K64" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="L64" s="5" t="n">
         <v>0</v>
       </c>
@@ -5556,7 +5556,7 @@
         <v>0</v>
       </c>
       <c r="P64" s="5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="Q64" s="5" t="n">
         <v>0</v>
@@ -5617,11 +5617,11 @@
         <v>20</v>
       </c>
       <c r="J65" t="n">
+        <v>24</v>
+      </c>
+      <c r="K65" t="n">
         <v>21</v>
       </c>
-      <c r="K65" t="n">
-        <v>0</v>
-      </c>
       <c r="L65" t="n">
         <v>0</v>
       </c>
@@ -5635,7 +5635,7 @@
         <v>0</v>
       </c>
       <c r="P65" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="Q65" t="n">
         <v>0</v>
@@ -5696,11 +5696,11 @@
         <v>26</v>
       </c>
       <c r="J66" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="K66" s="5" t="n">
         <v>21</v>
       </c>
-      <c r="K66" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="L66" s="5" t="n">
         <v>0</v>
       </c>
@@ -5714,7 +5714,7 @@
         <v>0</v>
       </c>
       <c r="P66" s="5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="Q66" s="5" t="n">
         <v>0</v>
@@ -5774,12 +5774,9 @@
       <c r="I67" t="n">
         <v>26</v>
       </c>
-      <c r="J67" t="n">
+      <c r="K67" t="n">
         <v>21</v>
       </c>
-      <c r="K67" t="n">
-        <v>0</v>
-      </c>
       <c r="L67" t="n">
         <v>0</v>
       </c>
@@ -5790,6 +5787,9 @@
         <v>0</v>
       </c>
       <c r="O67" t="n">
+        <v>0</v>
+      </c>
+      <c r="P67" t="n">
         <v>0</v>
       </c>
       <c r="Q67" t="n">
@@ -5851,11 +5851,11 @@
         <v>26</v>
       </c>
       <c r="J68" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="K68" s="5" t="n">
         <v>21</v>
       </c>
-      <c r="K68" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="L68" s="5" t="n">
         <v>0</v>
       </c>
@@ -5869,7 +5869,7 @@
         <v>0</v>
       </c>
       <c r="P68" s="5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="Q68" s="5" t="n">
         <v>0</v>
@@ -5926,12 +5926,9 @@
       <c r="I69" t="n">
         <v>26</v>
       </c>
-      <c r="J69" t="n">
+      <c r="K69" t="n">
         <v>21</v>
       </c>
-      <c r="K69" t="n">
-        <v>0</v>
-      </c>
       <c r="L69" t="n">
         <v>0</v>
       </c>
@@ -5942,6 +5939,9 @@
         <v>0</v>
       </c>
       <c r="O69" t="n">
+        <v>0</v>
+      </c>
+      <c r="P69" t="n">
         <v>0</v>
       </c>
       <c r="Q69" t="n">
@@ -6003,11 +6003,11 @@
         <v>26</v>
       </c>
       <c r="J70" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="K70" s="5" t="n">
         <v>21</v>
       </c>
-      <c r="K70" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="L70" s="5" t="n">
         <v>0</v>
       </c>
@@ -6021,7 +6021,7 @@
         <v>0</v>
       </c>
       <c r="P70" s="5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="Q70" s="5" t="n">
         <v>0</v>
@@ -6082,11 +6082,11 @@
         <v>26</v>
       </c>
       <c r="J71" t="n">
+        <v>24</v>
+      </c>
+      <c r="K71" t="n">
         <v>21</v>
       </c>
-      <c r="K71" t="n">
-        <v>0</v>
-      </c>
       <c r="L71" t="n">
         <v>0</v>
       </c>
@@ -6100,7 +6100,7 @@
         <v>0</v>
       </c>
       <c r="P71" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="Q71" t="n">
         <v>0</v>
@@ -6161,11 +6161,11 @@
         <v>26</v>
       </c>
       <c r="J72" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="K72" s="5" t="n">
         <v>21</v>
       </c>
-      <c r="K72" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="L72" s="5" t="n">
         <v>0</v>
       </c>
@@ -6179,7 +6179,7 @@
         <v>0</v>
       </c>
       <c r="P72" s="5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="Q72" s="5" t="n">
         <v>0</v>
@@ -6240,11 +6240,11 @@
         <v>26</v>
       </c>
       <c r="J73" t="n">
+        <v>24</v>
+      </c>
+      <c r="K73" t="n">
         <v>19</v>
       </c>
-      <c r="K73" t="n">
-        <v>0</v>
-      </c>
       <c r="L73" t="n">
         <v>0</v>
       </c>
@@ -6258,7 +6258,7 @@
         <v>0</v>
       </c>
       <c r="P73" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="Q73" t="n">
         <v>0</v>
@@ -6319,11 +6319,11 @@
         <v>26</v>
       </c>
       <c r="J74" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="K74" s="5" t="n">
         <v>23</v>
       </c>
-      <c r="K74" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="L74" s="5" t="n">
         <v>0</v>
       </c>
@@ -6337,7 +6337,7 @@
         <v>0</v>
       </c>
       <c r="P74" s="5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="Q74" s="5" t="n">
         <v>0</v>
@@ -6398,11 +6398,11 @@
         <v>26</v>
       </c>
       <c r="J75" t="n">
+        <v>24</v>
+      </c>
+      <c r="K75" t="n">
         <v>23</v>
       </c>
-      <c r="K75" t="n">
-        <v>0</v>
-      </c>
       <c r="L75" t="n">
         <v>0</v>
       </c>
@@ -6416,7 +6416,7 @@
         <v>0</v>
       </c>
       <c r="P75" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="Q75" t="n">
         <v>0</v>
@@ -6477,11 +6477,11 @@
         <v>26</v>
       </c>
       <c r="J76" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="K76" s="5" t="n">
         <v>23</v>
       </c>
-      <c r="K76" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="L76" s="5" t="n">
         <v>0</v>
       </c>
@@ -6494,17 +6494,19 @@
       <c r="O76" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="P76" s="5" t="n">
-        <v>24</v>
-      </c>
+      <c r="P76" s="5" t="n"/>
       <c r="Q76" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="R76" s="5" t="n"/>
+      <c r="R76" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="S76" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="T76" s="5" t="n"/>
+      <c r="T76" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="U76" s="5" t="n">
         <v>0</v>
       </c>
@@ -6517,9 +6519,7 @@
       <c r="X76" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="Y76" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="Y76" s="5" t="n"/>
     </row>
     <row r="77">
       <c r="A77" s="6" t="inlineStr">
@@ -6551,12 +6551,9 @@
       <c r="I77" t="n">
         <v>26</v>
       </c>
-      <c r="J77" t="n">
+      <c r="K77" t="n">
         <v>23</v>
       </c>
-      <c r="K77" t="n">
-        <v>0</v>
-      </c>
       <c r="L77" t="n">
         <v>0</v>
       </c>
@@ -6567,6 +6564,9 @@
         <v>0</v>
       </c>
       <c r="O77" t="n">
+        <v>0</v>
+      </c>
+      <c r="P77" t="n">
         <v>0</v>
       </c>
       <c r="Q77" t="n">
@@ -6628,11 +6628,11 @@
         <v>26</v>
       </c>
       <c r="J78" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="K78" s="5" t="n">
         <v>23</v>
       </c>
-      <c r="K78" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="L78" s="5" t="n">
         <v>0</v>
       </c>
@@ -6646,7 +6646,7 @@
         <v>0</v>
       </c>
       <c r="P78" s="5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="Q78" s="5" t="n">
         <v>0</v>
@@ -6706,12 +6706,9 @@
       <c r="I79" t="n">
         <v>26</v>
       </c>
-      <c r="J79" t="n">
+      <c r="K79" t="n">
         <v>23</v>
       </c>
-      <c r="K79" t="n">
-        <v>0</v>
-      </c>
       <c r="L79" t="n">
         <v>0</v>
       </c>
@@ -6722,6 +6719,9 @@
         <v>0</v>
       </c>
       <c r="O79" t="n">
+        <v>0</v>
+      </c>
+      <c r="P79" t="n">
         <v>0</v>
       </c>
       <c r="Q79" t="n">
@@ -6782,12 +6782,10 @@
       <c r="I80" s="5" t="n">
         <v>26</v>
       </c>
-      <c r="J80" s="5" t="n">
+      <c r="J80" s="5" t="n"/>
+      <c r="K80" s="5" t="n">
         <v>23</v>
       </c>
-      <c r="K80" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="L80" s="5" t="n">
         <v>0</v>
       </c>
@@ -6800,7 +6798,9 @@
       <c r="O80" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="P80" s="5" t="n"/>
+      <c r="P80" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="Q80" s="5" t="n">
         <v>0</v>
       </c>
@@ -6826,6 +6826,85 @@
         <v>0</v>
       </c>
       <c r="Y80" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B81" t="n">
+        <v>886</v>
+      </c>
+      <c r="C81" t="n">
+        <v>532</v>
+      </c>
+      <c r="D81" t="n">
+        <v>389</v>
+      </c>
+      <c r="E81" t="n">
+        <v>388</v>
+      </c>
+      <c r="F81" t="n">
+        <v>216</v>
+      </c>
+      <c r="G81" t="n">
+        <v>90</v>
+      </c>
+      <c r="H81" t="n">
+        <v>42</v>
+      </c>
+      <c r="I81" t="n">
+        <v>26</v>
+      </c>
+      <c r="J81" t="n">
+        <v>24</v>
+      </c>
+      <c r="K81" t="n">
+        <v>23</v>
+      </c>
+      <c r="L81" t="n">
+        <v>0</v>
+      </c>
+      <c r="M81" t="n">
+        <v>0</v>
+      </c>
+      <c r="N81" t="n">
+        <v>0</v>
+      </c>
+      <c r="O81" t="n">
+        <v>0</v>
+      </c>
+      <c r="P81" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q81" t="n">
+        <v>0</v>
+      </c>
+      <c r="R81" t="n">
+        <v>0</v>
+      </c>
+      <c r="S81" t="n">
+        <v>0</v>
+      </c>
+      <c r="T81" t="n">
+        <v>0</v>
+      </c>
+      <c r="U81" t="n">
+        <v>0</v>
+      </c>
+      <c r="V81" t="n">
+        <v>0</v>
+      </c>
+      <c r="W81" t="n">
+        <v>0</v>
+      </c>
+      <c r="X81" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y81" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6840,7 +6919,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D1139"/>
+  <dimension ref="A1:D1138"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -6867,7 +6946,7 @@
       </c>
       <c r="D1" s="3" t="inlineStr">
         <is>
-          <t>Lager (2026-09-24)</t>
+          <t>Lager (2026-09-25)</t>
         </is>
       </c>
     </row>
@@ -6888,7 +6967,7 @@
         </is>
       </c>
       <c r="D2" s="4" t="n">
-        <v>537</v>
+        <v>532</v>
       </c>
     </row>
     <row r="3">
@@ -12074,12 +12153,12 @@
     <row r="262">
       <c r="A262" s="4" t="inlineStr">
         <is>
-          <t>7013678</t>
+          <t>7011676</t>
         </is>
       </c>
       <c r="B262" s="5" t="inlineStr">
         <is>
-          <t>Infälld Interiörarmatur LED DPML Tunable White</t>
+          <t>Infälld interiörarmatur Diana Flat LED 300x300</t>
         </is>
       </c>
       <c r="C262" s="5" t="inlineStr">
@@ -12094,7 +12173,7 @@
     <row r="263">
       <c r="A263" s="6" t="inlineStr">
         <is>
-          <t>7011676</t>
+          <t>7011677</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -12114,12 +12193,12 @@
     <row r="264">
       <c r="A264" s="4" t="inlineStr">
         <is>
-          <t>7011677</t>
+          <t>7013193</t>
         </is>
       </c>
       <c r="B264" s="5" t="inlineStr">
         <is>
-          <t>Infälld interiörarmatur Diana Flat LED 300x300</t>
+          <t>Infälld interiörarmatur Diana Flat LED 600x600</t>
         </is>
       </c>
       <c r="C264" s="5" t="inlineStr">
@@ -12134,7 +12213,7 @@
     <row r="265">
       <c r="A265" s="6" t="inlineStr">
         <is>
-          <t>7013193</t>
+          <t>7013194</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
@@ -12154,7 +12233,7 @@
     <row r="266">
       <c r="A266" s="4" t="inlineStr">
         <is>
-          <t>7013194</t>
+          <t>7018335</t>
         </is>
       </c>
       <c r="B266" s="5" t="inlineStr">
@@ -12174,7 +12253,7 @@
     <row r="267">
       <c r="A267" s="6" t="inlineStr">
         <is>
-          <t>7018335</t>
+          <t>7018336</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
@@ -12194,7 +12273,7 @@
     <row r="268">
       <c r="A268" s="4" t="inlineStr">
         <is>
-          <t>7018336</t>
+          <t>7018337</t>
         </is>
       </c>
       <c r="B268" s="5" t="inlineStr">
@@ -12214,7 +12293,7 @@
     <row r="269">
       <c r="A269" s="6" t="inlineStr">
         <is>
-          <t>7018337</t>
+          <t>7018338</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
@@ -12234,7 +12313,7 @@
     <row r="270">
       <c r="A270" s="4" t="inlineStr">
         <is>
-          <t>7018338</t>
+          <t>7018339</t>
         </is>
       </c>
       <c r="B270" s="5" t="inlineStr">
@@ -12254,7 +12333,7 @@
     <row r="271">
       <c r="A271" s="6" t="inlineStr">
         <is>
-          <t>7018339</t>
+          <t>7018340</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
@@ -12274,7 +12353,7 @@
     <row r="272">
       <c r="A272" s="4" t="inlineStr">
         <is>
-          <t>7018340</t>
+          <t>7018341</t>
         </is>
       </c>
       <c r="B272" s="5" t="inlineStr">
@@ -12294,7 +12373,7 @@
     <row r="273">
       <c r="A273" s="6" t="inlineStr">
         <is>
-          <t>7018341</t>
+          <t>7018342</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
@@ -12314,12 +12393,12 @@
     <row r="274">
       <c r="A274" s="4" t="inlineStr">
         <is>
-          <t>7018342</t>
+          <t>7017462</t>
         </is>
       </c>
       <c r="B274" s="5" t="inlineStr">
         <is>
-          <t>Infälld interiörarmatur Diana Flat LED 600x600</t>
+          <t>Interiörarmatur LED Velox Deco Fyrkantig</t>
         </is>
       </c>
       <c r="C274" s="5" t="inlineStr">
@@ -12334,7 +12413,7 @@
     <row r="275">
       <c r="A275" s="6" t="inlineStr">
         <is>
-          <t>7017462</t>
+          <t>7018858</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
@@ -12354,7 +12433,7 @@
     <row r="276">
       <c r="A276" s="4" t="inlineStr">
         <is>
-          <t>7018858</t>
+          <t>7018877</t>
         </is>
       </c>
       <c r="B276" s="5" t="inlineStr">
@@ -12374,7 +12453,7 @@
     <row r="277">
       <c r="A277" s="6" t="inlineStr">
         <is>
-          <t>7018877</t>
+          <t>7018878</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
@@ -12394,12 +12473,12 @@
     <row r="278">
       <c r="A278" s="4" t="inlineStr">
         <is>
-          <t>7018878</t>
+          <t>7017460</t>
         </is>
       </c>
       <c r="B278" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur LED Velox Deco Fyrkantig</t>
+          <t>Interiörarmatur LED Velox Deco Rund</t>
         </is>
       </c>
       <c r="C278" s="5" t="inlineStr">
@@ -12414,7 +12493,7 @@
     <row r="279">
       <c r="A279" s="6" t="inlineStr">
         <is>
-          <t>7017460</t>
+          <t>7017464</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
@@ -12434,7 +12513,7 @@
     <row r="280">
       <c r="A280" s="4" t="inlineStr">
         <is>
-          <t>7017464</t>
+          <t>7017466</t>
         </is>
       </c>
       <c r="B280" s="5" t="inlineStr">
@@ -12454,7 +12533,7 @@
     <row r="281">
       <c r="A281" s="6" t="inlineStr">
         <is>
-          <t>7017466</t>
+          <t>7018857</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
@@ -12474,7 +12553,7 @@
     <row r="282">
       <c r="A282" s="4" t="inlineStr">
         <is>
-          <t>7018857</t>
+          <t>7018859</t>
         </is>
       </c>
       <c r="B282" s="5" t="inlineStr">
@@ -12494,7 +12573,7 @@
     <row r="283">
       <c r="A283" s="6" t="inlineStr">
         <is>
-          <t>7018859</t>
+          <t>7018860</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
@@ -12514,7 +12593,7 @@
     <row r="284">
       <c r="A284" s="4" t="inlineStr">
         <is>
-          <t>7018860</t>
+          <t>7018874</t>
         </is>
       </c>
       <c r="B284" s="5" t="inlineStr">
@@ -12534,7 +12613,7 @@
     <row r="285">
       <c r="A285" s="6" t="inlineStr">
         <is>
-          <t>7018874</t>
+          <t>7018875</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
@@ -12554,7 +12633,7 @@
     <row r="286">
       <c r="A286" s="4" t="inlineStr">
         <is>
-          <t>7018875</t>
+          <t>7018876</t>
         </is>
       </c>
       <c r="B286" s="5" t="inlineStr">
@@ -12574,7 +12653,7 @@
     <row r="287">
       <c r="A287" s="6" t="inlineStr">
         <is>
-          <t>7018876</t>
+          <t>7018879</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
@@ -12594,7 +12673,7 @@
     <row r="288">
       <c r="A288" s="4" t="inlineStr">
         <is>
-          <t>7018879</t>
+          <t>7018880</t>
         </is>
       </c>
       <c r="B288" s="5" t="inlineStr">
@@ -12614,7 +12693,7 @@
     <row r="289">
       <c r="A289" s="6" t="inlineStr">
         <is>
-          <t>7018880</t>
+          <t>7018881</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
@@ -12634,7 +12713,7 @@
     <row r="290">
       <c r="A290" s="4" t="inlineStr">
         <is>
-          <t>7018881</t>
+          <t>7018882</t>
         </is>
       </c>
       <c r="B290" s="5" t="inlineStr">
@@ -12654,12 +12733,12 @@
     <row r="291">
       <c r="A291" s="6" t="inlineStr">
         <is>
-          <t>7018882</t>
+          <t>7015430</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>Interiörarmatur LED Velox Deco Rund</t>
+          <t>Interiörarmatur LED Velox Infälld rund</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
@@ -12674,7 +12753,7 @@
     <row r="292">
       <c r="A292" s="4" t="inlineStr">
         <is>
-          <t>7015430</t>
+          <t>7015431</t>
         </is>
       </c>
       <c r="B292" s="5" t="inlineStr">
@@ -12694,7 +12773,7 @@
     <row r="293">
       <c r="A293" s="6" t="inlineStr">
         <is>
-          <t>7015431</t>
+          <t>7015437</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
@@ -12714,7 +12793,7 @@
     <row r="294">
       <c r="A294" s="4" t="inlineStr">
         <is>
-          <t>7015437</t>
+          <t>7015439</t>
         </is>
       </c>
       <c r="B294" s="5" t="inlineStr">
@@ -12734,7 +12813,7 @@
     <row r="295">
       <c r="A295" s="6" t="inlineStr">
         <is>
-          <t>7015439</t>
+          <t>7015441</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
@@ -12754,7 +12833,7 @@
     <row r="296">
       <c r="A296" s="4" t="inlineStr">
         <is>
-          <t>7015441</t>
+          <t>7015443</t>
         </is>
       </c>
       <c r="B296" s="5" t="inlineStr">
@@ -12774,12 +12853,12 @@
     <row r="297">
       <c r="A297" s="6" t="inlineStr">
         <is>
-          <t>7015443</t>
+          <t>7015433</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>Interiörarmatur LED Velox Infälld rund</t>
+          <t>Interiörarmatur LED Velox infälld fyrkantig</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
@@ -12794,7 +12873,7 @@
     <row r="298">
       <c r="A298" s="4" t="inlineStr">
         <is>
-          <t>7015433</t>
+          <t>7015435</t>
         </is>
       </c>
       <c r="B298" s="5" t="inlineStr">
@@ -12814,21 +12893,21 @@
     <row r="299">
       <c r="A299" s="6" t="inlineStr">
         <is>
-          <t>7015435</t>
+          <t>7028947</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>Interiörarmatur LED Velox infälld fyrkantig</t>
+          <t>Interiörarmatur Juna</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>Ensto</t>
+          <t>Esylux</t>
         </is>
       </c>
       <c r="D299" s="6" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
     </row>
     <row r="300">
@@ -15508,7 +15587,7 @@
         </is>
       </c>
       <c r="D433" s="6" t="n">
-        <v>170</v>
+        <v>178</v>
       </c>
     </row>
     <row r="434">
@@ -15588,7 +15667,7 @@
         </is>
       </c>
       <c r="D437" s="6" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="438">
@@ -15608,7 +15687,7 @@
         </is>
       </c>
       <c r="D438" s="4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="439">
@@ -22954,12 +23033,12 @@
     <row r="806">
       <c r="A806" s="4" t="inlineStr">
         <is>
-          <t>7028893</t>
+          <t>7023008</t>
         </is>
       </c>
       <c r="B806" s="5" t="inlineStr">
         <is>
-          <t>Infälld Interiörarmatur Coreline Panel</t>
+          <t>Infälld interiörarmatur CoreLine Panel, 600x600</t>
         </is>
       </c>
       <c r="C806" s="5" t="inlineStr">
@@ -22974,12 +23053,12 @@
     <row r="807">
       <c r="A807" s="6" t="inlineStr">
         <is>
-          <t>7023008</t>
+          <t>7028892</t>
         </is>
       </c>
       <c r="B807" t="inlineStr">
         <is>
-          <t>Infälld interiörarmatur CoreLine Panel, 600x600</t>
+          <t>Infälld interiörarmatur Coreline Panel Interact</t>
         </is>
       </c>
       <c r="C807" t="inlineStr">
@@ -22994,12 +23073,12 @@
     <row r="808">
       <c r="A808" s="4" t="inlineStr">
         <is>
-          <t>7028892</t>
+          <t>7042301</t>
         </is>
       </c>
       <c r="B808" s="5" t="inlineStr">
         <is>
-          <t>Infälld interiörarmatur Coreline Panel Interact</t>
+          <t>Interiörarmatur Coreline RC132V infälld, 30x120</t>
         </is>
       </c>
       <c r="C808" s="5" t="inlineStr">
@@ -23014,7 +23093,7 @@
     <row r="809">
       <c r="A809" s="6" t="inlineStr">
         <is>
-          <t>7042301</t>
+          <t>7042305</t>
         </is>
       </c>
       <c r="B809" t="inlineStr">
@@ -23034,7 +23113,7 @@
     <row r="810">
       <c r="A810" s="4" t="inlineStr">
         <is>
-          <t>7042305</t>
+          <t>7042306</t>
         </is>
       </c>
       <c r="B810" s="5" t="inlineStr">
@@ -23054,7 +23133,7 @@
     <row r="811">
       <c r="A811" s="6" t="inlineStr">
         <is>
-          <t>7042306</t>
+          <t>7042310</t>
         </is>
       </c>
       <c r="B811" t="inlineStr">
@@ -23074,7 +23153,7 @@
     <row r="812">
       <c r="A812" s="4" t="inlineStr">
         <is>
-          <t>7042310</t>
+          <t>7042311</t>
         </is>
       </c>
       <c r="B812" s="5" t="inlineStr">
@@ -23094,7 +23173,7 @@
     <row r="813">
       <c r="A813" s="6" t="inlineStr">
         <is>
-          <t>7042311</t>
+          <t>7042315</t>
         </is>
       </c>
       <c r="B813" t="inlineStr">
@@ -23114,7 +23193,7 @@
     <row r="814">
       <c r="A814" s="4" t="inlineStr">
         <is>
-          <t>7042315</t>
+          <t>7042318</t>
         </is>
       </c>
       <c r="B814" s="5" t="inlineStr">
@@ -23134,12 +23213,12 @@
     <row r="815">
       <c r="A815" s="6" t="inlineStr">
         <is>
-          <t>7042318</t>
+          <t>7042302</t>
         </is>
       </c>
       <c r="B815" t="inlineStr">
         <is>
-          <t>Interiörarmatur Coreline RC132V infälld, 30x120</t>
+          <t>Interiörarmatur Coreline RC132V infälld, 60x60</t>
         </is>
       </c>
       <c r="C815" t="inlineStr">
@@ -23154,7 +23233,7 @@
     <row r="816">
       <c r="A816" s="4" t="inlineStr">
         <is>
-          <t>7042302</t>
+          <t>7042303</t>
         </is>
       </c>
       <c r="B816" s="5" t="inlineStr">
@@ -23174,7 +23253,7 @@
     <row r="817">
       <c r="A817" s="6" t="inlineStr">
         <is>
-          <t>7042303</t>
+          <t>7042304</t>
         </is>
       </c>
       <c r="B817" t="inlineStr">
@@ -23194,7 +23273,7 @@
     <row r="818">
       <c r="A818" s="4" t="inlineStr">
         <is>
-          <t>7042304</t>
+          <t>7042307</t>
         </is>
       </c>
       <c r="B818" s="5" t="inlineStr">
@@ -23214,7 +23293,7 @@
     <row r="819">
       <c r="A819" s="6" t="inlineStr">
         <is>
-          <t>7042307</t>
+          <t>7042308</t>
         </is>
       </c>
       <c r="B819" t="inlineStr">
@@ -23234,7 +23313,7 @@
     <row r="820">
       <c r="A820" s="4" t="inlineStr">
         <is>
-          <t>7042308</t>
+          <t>7042309</t>
         </is>
       </c>
       <c r="B820" s="5" t="inlineStr">
@@ -23254,7 +23333,7 @@
     <row r="821">
       <c r="A821" s="6" t="inlineStr">
         <is>
-          <t>7042309</t>
+          <t>7042312</t>
         </is>
       </c>
       <c r="B821" t="inlineStr">
@@ -23274,7 +23353,7 @@
     <row r="822">
       <c r="A822" s="4" t="inlineStr">
         <is>
-          <t>7042312</t>
+          <t>7042313</t>
         </is>
       </c>
       <c r="B822" s="5" t="inlineStr">
@@ -23294,7 +23373,7 @@
     <row r="823">
       <c r="A823" s="6" t="inlineStr">
         <is>
-          <t>7042313</t>
+          <t>7042314</t>
         </is>
       </c>
       <c r="B823" t="inlineStr">
@@ -23314,7 +23393,7 @@
     <row r="824">
       <c r="A824" s="4" t="inlineStr">
         <is>
-          <t>7042314</t>
+          <t>7042316</t>
         </is>
       </c>
       <c r="B824" s="5" t="inlineStr">
@@ -23334,7 +23413,7 @@
     <row r="825">
       <c r="A825" s="6" t="inlineStr">
         <is>
-          <t>7042316</t>
+          <t>7042317</t>
         </is>
       </c>
       <c r="B825" t="inlineStr">
@@ -23354,7 +23433,7 @@
     <row r="826">
       <c r="A826" s="4" t="inlineStr">
         <is>
-          <t>7042317</t>
+          <t>7042319</t>
         </is>
       </c>
       <c r="B826" s="5" t="inlineStr">
@@ -23374,7 +23453,7 @@
     <row r="827">
       <c r="A827" s="6" t="inlineStr">
         <is>
-          <t>7042319</t>
+          <t>7042321</t>
         </is>
       </c>
       <c r="B827" t="inlineStr">
@@ -23394,7 +23473,7 @@
     <row r="828">
       <c r="A828" s="4" t="inlineStr">
         <is>
-          <t>7042321</t>
+          <t>7042322</t>
         </is>
       </c>
       <c r="B828" s="5" t="inlineStr">
@@ -23414,12 +23493,12 @@
     <row r="829">
       <c r="A829" s="6" t="inlineStr">
         <is>
-          <t>7042322</t>
+          <t>7027241</t>
         </is>
       </c>
       <c r="B829" t="inlineStr">
         <is>
-          <t>Interiörarmatur Coreline RC132V infälld, 60x60</t>
+          <t>Interiörarmatur Ledinaire All-in, 3K/4K</t>
         </is>
       </c>
       <c r="C829" t="inlineStr">
@@ -23434,7 +23513,7 @@
     <row r="830">
       <c r="A830" s="4" t="inlineStr">
         <is>
-          <t>7027241</t>
+          <t>7027242</t>
         </is>
       </c>
       <c r="B830" s="5" t="inlineStr">
@@ -23454,7 +23533,7 @@
     <row r="831">
       <c r="A831" s="6" t="inlineStr">
         <is>
-          <t>7027242</t>
+          <t>7027245</t>
         </is>
       </c>
       <c r="B831" t="inlineStr">
@@ -23474,12 +23553,12 @@
     <row r="832">
       <c r="A832" s="4" t="inlineStr">
         <is>
-          <t>7027245</t>
+          <t>7024515</t>
         </is>
       </c>
       <c r="B832" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Ledinaire All-in, 3K/4K</t>
+          <t>Interiörarmatur SlimBlend infälld</t>
         </is>
       </c>
       <c r="C832" s="5" t="inlineStr">
@@ -23494,7 +23573,7 @@
     <row r="833">
       <c r="A833" s="6" t="inlineStr">
         <is>
-          <t>7024515</t>
+          <t>7024516</t>
         </is>
       </c>
       <c r="B833" t="inlineStr">
@@ -23514,7 +23593,7 @@
     <row r="834">
       <c r="A834" s="4" t="inlineStr">
         <is>
-          <t>7024516</t>
+          <t>7024517</t>
         </is>
       </c>
       <c r="B834" s="5" t="inlineStr">
@@ -23534,7 +23613,7 @@
     <row r="835">
       <c r="A835" s="6" t="inlineStr">
         <is>
-          <t>7024517</t>
+          <t>7024518</t>
         </is>
       </c>
       <c r="B835" t="inlineStr">
@@ -23554,7 +23633,7 @@
     <row r="836">
       <c r="A836" s="4" t="inlineStr">
         <is>
-          <t>7024518</t>
+          <t>7024519</t>
         </is>
       </c>
       <c r="B836" s="5" t="inlineStr">
@@ -23574,7 +23653,7 @@
     <row r="837">
       <c r="A837" s="6" t="inlineStr">
         <is>
-          <t>7024519</t>
+          <t>7024520</t>
         </is>
       </c>
       <c r="B837" t="inlineStr">
@@ -23594,7 +23673,7 @@
     <row r="838">
       <c r="A838" s="4" t="inlineStr">
         <is>
-          <t>7024520</t>
+          <t>7024521</t>
         </is>
       </c>
       <c r="B838" s="5" t="inlineStr">
@@ -23614,7 +23693,7 @@
     <row r="839">
       <c r="A839" s="6" t="inlineStr">
         <is>
-          <t>7024521</t>
+          <t>7024522</t>
         </is>
       </c>
       <c r="B839" t="inlineStr">
@@ -23634,7 +23713,7 @@
     <row r="840">
       <c r="A840" s="4" t="inlineStr">
         <is>
-          <t>7024522</t>
+          <t>7024523</t>
         </is>
       </c>
       <c r="B840" s="5" t="inlineStr">
@@ -23654,7 +23733,7 @@
     <row r="841">
       <c r="A841" s="6" t="inlineStr">
         <is>
-          <t>7024523</t>
+          <t>7024524</t>
         </is>
       </c>
       <c r="B841" t="inlineStr">
@@ -23674,7 +23753,7 @@
     <row r="842">
       <c r="A842" s="4" t="inlineStr">
         <is>
-          <t>7024524</t>
+          <t>7024525</t>
         </is>
       </c>
       <c r="B842" s="5" t="inlineStr">
@@ -23694,12 +23773,12 @@
     <row r="843">
       <c r="A843" s="6" t="inlineStr">
         <is>
-          <t>7024525</t>
+          <t>7026517</t>
         </is>
       </c>
       <c r="B843" t="inlineStr">
         <is>
-          <t>Interiörarmatur SlimBlend infälld</t>
+          <t>Interiörarmatur TrueCircle infälld</t>
         </is>
       </c>
       <c r="C843" t="inlineStr">
@@ -23714,7 +23793,7 @@
     <row r="844">
       <c r="A844" s="4" t="inlineStr">
         <is>
-          <t>7026517</t>
+          <t>7026518</t>
         </is>
       </c>
       <c r="B844" s="5" t="inlineStr">
@@ -23734,7 +23813,7 @@
     <row r="845">
       <c r="A845" s="6" t="inlineStr">
         <is>
-          <t>7026518</t>
+          <t>7026519</t>
         </is>
       </c>
       <c r="B845" t="inlineStr">
@@ -23754,7 +23833,7 @@
     <row r="846">
       <c r="A846" s="4" t="inlineStr">
         <is>
-          <t>7026519</t>
+          <t>7026520</t>
         </is>
       </c>
       <c r="B846" s="5" t="inlineStr">
@@ -23774,7 +23853,7 @@
     <row r="847">
       <c r="A847" s="6" t="inlineStr">
         <is>
-          <t>7026520</t>
+          <t>7026521</t>
         </is>
       </c>
       <c r="B847" t="inlineStr">
@@ -23794,7 +23873,7 @@
     <row r="848">
       <c r="A848" s="4" t="inlineStr">
         <is>
-          <t>7026521</t>
+          <t>7026522</t>
         </is>
       </c>
       <c r="B848" s="5" t="inlineStr">
@@ -23814,12 +23893,12 @@
     <row r="849">
       <c r="A849" s="6" t="inlineStr">
         <is>
-          <t>7026522</t>
+          <t>7024527</t>
         </is>
       </c>
       <c r="B849" t="inlineStr">
         <is>
-          <t>Interiörarmatur TrueCircle infälld</t>
+          <t>Interiörarmatur TrueLine infälld</t>
         </is>
       </c>
       <c r="C849" t="inlineStr">
@@ -23834,7 +23913,7 @@
     <row r="850">
       <c r="A850" s="4" t="inlineStr">
         <is>
-          <t>7024527</t>
+          <t>7024528</t>
         </is>
       </c>
       <c r="B850" s="5" t="inlineStr">
@@ -23854,7 +23933,7 @@
     <row r="851">
       <c r="A851" s="6" t="inlineStr">
         <is>
-          <t>7024528</t>
+          <t>7024529</t>
         </is>
       </c>
       <c r="B851" t="inlineStr">
@@ -23874,7 +23953,7 @@
     <row r="852">
       <c r="A852" s="4" t="inlineStr">
         <is>
-          <t>7024529</t>
+          <t>7024530</t>
         </is>
       </c>
       <c r="B852" s="5" t="inlineStr">
@@ -23894,7 +23973,7 @@
     <row r="853">
       <c r="A853" s="6" t="inlineStr">
         <is>
-          <t>7024530</t>
+          <t>7024531</t>
         </is>
       </c>
       <c r="B853" t="inlineStr">
@@ -23914,7 +23993,7 @@
     <row r="854">
       <c r="A854" s="4" t="inlineStr">
         <is>
-          <t>7024531</t>
+          <t>7024532</t>
         </is>
       </c>
       <c r="B854" s="5" t="inlineStr">
@@ -23934,7 +24013,7 @@
     <row r="855">
       <c r="A855" s="6" t="inlineStr">
         <is>
-          <t>7024532</t>
+          <t>7024533</t>
         </is>
       </c>
       <c r="B855" t="inlineStr">
@@ -23954,7 +24033,7 @@
     <row r="856">
       <c r="A856" s="4" t="inlineStr">
         <is>
-          <t>7024533</t>
+          <t>7024534</t>
         </is>
       </c>
       <c r="B856" s="5" t="inlineStr">
@@ -23974,17 +24053,17 @@
     <row r="857">
       <c r="A857" s="6" t="inlineStr">
         <is>
-          <t>7024534</t>
+          <t>7015063</t>
         </is>
       </c>
       <c r="B857" t="inlineStr">
         <is>
-          <t>Interiörarmatur TrueLine infälld</t>
+          <t>Infälld interörarmatur LED Sence Round</t>
         </is>
       </c>
       <c r="C857" t="inlineStr">
         <is>
-          <t>Philips</t>
+          <t>SG Armaturen</t>
         </is>
       </c>
       <c r="D857" s="6" t="n">
@@ -23994,7 +24073,7 @@
     <row r="858">
       <c r="A858" s="4" t="inlineStr">
         <is>
-          <t>7015063</t>
+          <t>7015064</t>
         </is>
       </c>
       <c r="B858" s="5" t="inlineStr">
@@ -24014,7 +24093,7 @@
     <row r="859">
       <c r="A859" s="6" t="inlineStr">
         <is>
-          <t>7015064</t>
+          <t>7016290</t>
         </is>
       </c>
       <c r="B859" t="inlineStr">
@@ -24034,7 +24113,7 @@
     <row r="860">
       <c r="A860" s="4" t="inlineStr">
         <is>
-          <t>7016290</t>
+          <t>7015271</t>
         </is>
       </c>
       <c r="B860" s="5" t="inlineStr">
@@ -24054,7 +24133,7 @@
     <row r="861">
       <c r="A861" s="6" t="inlineStr">
         <is>
-          <t>7015271</t>
+          <t>7015272</t>
         </is>
       </c>
       <c r="B861" t="inlineStr">
@@ -24074,7 +24153,7 @@
     <row r="862">
       <c r="A862" s="4" t="inlineStr">
         <is>
-          <t>7015272</t>
+          <t>7016291E</t>
         </is>
       </c>
       <c r="B862" s="5" t="inlineStr">
@@ -24094,7 +24173,7 @@
     <row r="863">
       <c r="A863" s="6" t="inlineStr">
         <is>
-          <t>7016291E</t>
+          <t>7015065</t>
         </is>
       </c>
       <c r="B863" t="inlineStr">
@@ -24114,7 +24193,7 @@
     <row r="864">
       <c r="A864" s="4" t="inlineStr">
         <is>
-          <t>7015065</t>
+          <t>7015066</t>
         </is>
       </c>
       <c r="B864" s="5" t="inlineStr">
@@ -24134,7 +24213,7 @@
     <row r="865">
       <c r="A865" s="6" t="inlineStr">
         <is>
-          <t>7015066</t>
+          <t>7016292</t>
         </is>
       </c>
       <c r="B865" t="inlineStr">
@@ -24154,7 +24233,7 @@
     <row r="866">
       <c r="A866" s="4" t="inlineStr">
         <is>
-          <t>7016292</t>
+          <t>7015273</t>
         </is>
       </c>
       <c r="B866" s="5" t="inlineStr">
@@ -24174,7 +24253,7 @@
     <row r="867">
       <c r="A867" s="6" t="inlineStr">
         <is>
-          <t>7015273</t>
+          <t>7015274</t>
         </is>
       </c>
       <c r="B867" t="inlineStr">
@@ -24194,7 +24273,7 @@
     <row r="868">
       <c r="A868" s="4" t="inlineStr">
         <is>
-          <t>7015274</t>
+          <t>7016293</t>
         </is>
       </c>
       <c r="B868" s="5" t="inlineStr">
@@ -24214,7 +24293,7 @@
     <row r="869">
       <c r="A869" s="6" t="inlineStr">
         <is>
-          <t>7016293</t>
+          <t>7015067</t>
         </is>
       </c>
       <c r="B869" t="inlineStr">
@@ -24234,7 +24313,7 @@
     <row r="870">
       <c r="A870" s="4" t="inlineStr">
         <is>
-          <t>7015067</t>
+          <t>7015068</t>
         </is>
       </c>
       <c r="B870" s="5" t="inlineStr">
@@ -24254,7 +24333,7 @@
     <row r="871">
       <c r="A871" s="6" t="inlineStr">
         <is>
-          <t>7015068</t>
+          <t>7015069</t>
         </is>
       </c>
       <c r="B871" t="inlineStr">
@@ -24274,7 +24353,7 @@
     <row r="872">
       <c r="A872" s="4" t="inlineStr">
         <is>
-          <t>7015069</t>
+          <t>7015275</t>
         </is>
       </c>
       <c r="B872" s="5" t="inlineStr">
@@ -24294,7 +24373,7 @@
     <row r="873">
       <c r="A873" s="6" t="inlineStr">
         <is>
-          <t>7015275</t>
+          <t>7015276</t>
         </is>
       </c>
       <c r="B873" t="inlineStr">
@@ -24314,7 +24393,7 @@
     <row r="874">
       <c r="A874" s="4" t="inlineStr">
         <is>
-          <t>7015276</t>
+          <t>7015277</t>
         </is>
       </c>
       <c r="B874" s="5" t="inlineStr">
@@ -24334,7 +24413,7 @@
     <row r="875">
       <c r="A875" s="6" t="inlineStr">
         <is>
-          <t>7015277</t>
+          <t>7015070</t>
         </is>
       </c>
       <c r="B875" t="inlineStr">
@@ -24354,7 +24433,7 @@
     <row r="876">
       <c r="A876" s="4" t="inlineStr">
         <is>
-          <t>7015070</t>
+          <t>7015071</t>
         </is>
       </c>
       <c r="B876" s="5" t="inlineStr">
@@ -24374,7 +24453,7 @@
     <row r="877">
       <c r="A877" s="6" t="inlineStr">
         <is>
-          <t>7015071</t>
+          <t>7015278</t>
         </is>
       </c>
       <c r="B877" t="inlineStr">
@@ -24394,7 +24473,7 @@
     <row r="878">
       <c r="A878" s="4" t="inlineStr">
         <is>
-          <t>7015278</t>
+          <t>7015279</t>
         </is>
       </c>
       <c r="B878" s="5" t="inlineStr">
@@ -24414,7 +24493,7 @@
     <row r="879">
       <c r="A879" s="6" t="inlineStr">
         <is>
-          <t>7015279</t>
+          <t>7028329</t>
         </is>
       </c>
       <c r="B879" t="inlineStr">
@@ -24434,7 +24513,7 @@
     <row r="880">
       <c r="A880" s="4" t="inlineStr">
         <is>
-          <t>7028329</t>
+          <t>7028330</t>
         </is>
       </c>
       <c r="B880" s="5" t="inlineStr">
@@ -24454,7 +24533,7 @@
     <row r="881">
       <c r="A881" s="6" t="inlineStr">
         <is>
-          <t>7028330</t>
+          <t>7028331</t>
         </is>
       </c>
       <c r="B881" t="inlineStr">
@@ -24474,7 +24553,7 @@
     <row r="882">
       <c r="A882" s="4" t="inlineStr">
         <is>
-          <t>7028331</t>
+          <t>7028332</t>
         </is>
       </c>
       <c r="B882" s="5" t="inlineStr">
@@ -24494,12 +24573,12 @@
     <row r="883">
       <c r="A883" s="6" t="inlineStr">
         <is>
-          <t>7028332</t>
+          <t>7018001</t>
         </is>
       </c>
       <c r="B883" t="inlineStr">
         <is>
-          <t>Infälld interörarmatur LED Sence Round</t>
+          <t>Interiörarmatur LED Sense 300x1200</t>
         </is>
       </c>
       <c r="C883" t="inlineStr">
@@ -24514,7 +24593,7 @@
     <row r="884">
       <c r="A884" s="4" t="inlineStr">
         <is>
-          <t>7018001</t>
+          <t>7018002</t>
         </is>
       </c>
       <c r="B884" s="5" t="inlineStr">
@@ -24534,12 +24613,12 @@
     <row r="885">
       <c r="A885" s="6" t="inlineStr">
         <is>
-          <t>7018002</t>
+          <t>7015072</t>
         </is>
       </c>
       <c r="B885" t="inlineStr">
         <is>
-          <t>Interiörarmatur LED Sense 300x1200</t>
+          <t>Interiörarmatur LED Sense 300x300</t>
         </is>
       </c>
       <c r="C885" t="inlineStr">
@@ -24554,7 +24633,7 @@
     <row r="886">
       <c r="A886" s="4" t="inlineStr">
         <is>
-          <t>7015072</t>
+          <t>7015280</t>
         </is>
       </c>
       <c r="B886" s="5" t="inlineStr">
@@ -24574,7 +24653,7 @@
     <row r="887">
       <c r="A887" s="6" t="inlineStr">
         <is>
-          <t>7015280</t>
+          <t>7016295</t>
         </is>
       </c>
       <c r="B887" t="inlineStr">
@@ -24594,12 +24673,12 @@
     <row r="888">
       <c r="A888" s="4" t="inlineStr">
         <is>
-          <t>7016295</t>
+          <t>7017938</t>
         </is>
       </c>
       <c r="B888" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur LED Sense 300x300</t>
+          <t>Interiörarmatur LED Sense 600x600</t>
         </is>
       </c>
       <c r="C888" s="5" t="inlineStr">
@@ -24608,13 +24687,13 @@
         </is>
       </c>
       <c r="D888" s="4" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
     </row>
     <row r="889">
       <c r="A889" s="6" t="inlineStr">
         <is>
-          <t>7017938</t>
+          <t>7017939</t>
         </is>
       </c>
       <c r="B889" t="inlineStr">
@@ -24628,18 +24707,18 @@
         </is>
       </c>
       <c r="D889" s="6" t="n">
-        <v>23</v>
+        <v>3</v>
       </c>
     </row>
     <row r="890">
       <c r="A890" s="4" t="inlineStr">
         <is>
-          <t>7017939</t>
+          <t>7019572</t>
         </is>
       </c>
       <c r="B890" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur LED Sense 600x600</t>
+          <t>Interiörarmatur Sense Basic</t>
         </is>
       </c>
       <c r="C890" s="5" t="inlineStr">
@@ -24648,13 +24727,13 @@
         </is>
       </c>
       <c r="D890" s="4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="891">
       <c r="A891" s="6" t="inlineStr">
         <is>
-          <t>7019572</t>
+          <t>7019573</t>
         </is>
       </c>
       <c r="B891" t="inlineStr">
@@ -24674,12 +24753,12 @@
     <row r="892">
       <c r="A892" s="4" t="inlineStr">
         <is>
-          <t>7019573</t>
+          <t>7028217</t>
         </is>
       </c>
       <c r="B892" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Basic</t>
+          <t>Interiörarmatur Sense Basic Connect</t>
         </is>
       </c>
       <c r="C892" s="5" t="inlineStr">
@@ -24694,7 +24773,7 @@
     <row r="893">
       <c r="A893" s="6" t="inlineStr">
         <is>
-          <t>7028217</t>
+          <t>7028218</t>
         </is>
       </c>
       <c r="B893" t="inlineStr">
@@ -24714,12 +24793,12 @@
     <row r="894">
       <c r="A894" s="4" t="inlineStr">
         <is>
-          <t>7028218</t>
+          <t>7028197</t>
         </is>
       </c>
       <c r="B894" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Basic Connect</t>
+          <t>Interiörarmatur Sense Basic gen2</t>
         </is>
       </c>
       <c r="C894" s="5" t="inlineStr">
@@ -24734,7 +24813,7 @@
     <row r="895">
       <c r="A895" s="6" t="inlineStr">
         <is>
-          <t>7028197</t>
+          <t>7028033</t>
         </is>
       </c>
       <c r="B895" t="inlineStr">
@@ -24748,13 +24827,13 @@
         </is>
       </c>
       <c r="D895" s="6" t="n">
-        <v>0</v>
+        <v>294</v>
       </c>
     </row>
     <row r="896">
       <c r="A896" s="4" t="inlineStr">
         <is>
-          <t>7028033</t>
+          <t>7028035</t>
         </is>
       </c>
       <c r="B896" s="5" t="inlineStr">
@@ -24768,13 +24847,13 @@
         </is>
       </c>
       <c r="D896" s="4" t="n">
-        <v>294</v>
+        <v>5</v>
       </c>
     </row>
     <row r="897">
       <c r="A897" s="6" t="inlineStr">
         <is>
-          <t>7028035</t>
+          <t>7028034</t>
         </is>
       </c>
       <c r="B897" t="inlineStr">
@@ -24788,13 +24867,13 @@
         </is>
       </c>
       <c r="D897" s="6" t="n">
-        <v>5</v>
+        <v>29</v>
       </c>
     </row>
     <row r="898">
       <c r="A898" s="4" t="inlineStr">
         <is>
-          <t>7028034</t>
+          <t>7028044</t>
         </is>
       </c>
       <c r="B898" s="5" t="inlineStr">
@@ -24808,18 +24887,18 @@
         </is>
       </c>
       <c r="D898" s="4" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
     </row>
     <row r="899">
       <c r="A899" s="6" t="inlineStr">
         <is>
-          <t>7028044</t>
+          <t>7019665</t>
         </is>
       </c>
       <c r="B899" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Basic gen2</t>
+          <t>Interiörarmatur Sense IP65</t>
         </is>
       </c>
       <c r="C899" t="inlineStr">
@@ -24834,7 +24913,7 @@
     <row r="900">
       <c r="A900" s="4" t="inlineStr">
         <is>
-          <t>7019665</t>
+          <t>7019659</t>
         </is>
       </c>
       <c r="B900" s="5" t="inlineStr">
@@ -24854,12 +24933,12 @@
     <row r="901">
       <c r="A901" s="6" t="inlineStr">
         <is>
-          <t>7019659</t>
+          <t>7021278</t>
         </is>
       </c>
       <c r="B901" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense IP65</t>
+          <t>Interiörarmatur Sense IP65 Eco</t>
         </is>
       </c>
       <c r="C901" t="inlineStr">
@@ -24874,7 +24953,7 @@
     <row r="902">
       <c r="A902" s="4" t="inlineStr">
         <is>
-          <t>7021278</t>
+          <t>7021279</t>
         </is>
       </c>
       <c r="B902" s="5" t="inlineStr">
@@ -24894,7 +24973,7 @@
     <row r="903">
       <c r="A903" s="6" t="inlineStr">
         <is>
-          <t>7021279</t>
+          <t>7028952</t>
         </is>
       </c>
       <c r="B903" t="inlineStr">
@@ -24914,7 +24993,7 @@
     <row r="904">
       <c r="A904" s="4" t="inlineStr">
         <is>
-          <t>7028952</t>
+          <t>7028953</t>
         </is>
       </c>
       <c r="B904" s="5" t="inlineStr">
@@ -24934,12 +25013,12 @@
     <row r="905">
       <c r="A905" s="6" t="inlineStr">
         <is>
-          <t>7028953</t>
+          <t>7024921</t>
         </is>
       </c>
       <c r="B905" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense IP65 Eco</t>
+          <t>Interiörarmatur Sense Line</t>
         </is>
       </c>
       <c r="C905" t="inlineStr">
@@ -24954,7 +25033,7 @@
     <row r="906">
       <c r="A906" s="4" t="inlineStr">
         <is>
-          <t>7024921</t>
+          <t>7024922</t>
         </is>
       </c>
       <c r="B906" s="5" t="inlineStr">
@@ -24974,7 +25053,7 @@
     <row r="907">
       <c r="A907" s="6" t="inlineStr">
         <is>
-          <t>7024922</t>
+          <t>7024923</t>
         </is>
       </c>
       <c r="B907" t="inlineStr">
@@ -24994,7 +25073,7 @@
     <row r="908">
       <c r="A908" s="4" t="inlineStr">
         <is>
-          <t>7024923</t>
+          <t>7024924</t>
         </is>
       </c>
       <c r="B908" s="5" t="inlineStr">
@@ -25014,7 +25093,7 @@
     <row r="909">
       <c r="A909" s="6" t="inlineStr">
         <is>
-          <t>7024924</t>
+          <t>7024925</t>
         </is>
       </c>
       <c r="B909" t="inlineStr">
@@ -25034,7 +25113,7 @@
     <row r="910">
       <c r="A910" s="4" t="inlineStr">
         <is>
-          <t>7024925</t>
+          <t>7024926</t>
         </is>
       </c>
       <c r="B910" s="5" t="inlineStr">
@@ -25054,7 +25133,7 @@
     <row r="911">
       <c r="A911" s="6" t="inlineStr">
         <is>
-          <t>7024926</t>
+          <t>7024927</t>
         </is>
       </c>
       <c r="B911" t="inlineStr">
@@ -25074,7 +25153,7 @@
     <row r="912">
       <c r="A912" s="4" t="inlineStr">
         <is>
-          <t>7024927</t>
+          <t>7024928</t>
         </is>
       </c>
       <c r="B912" s="5" t="inlineStr">
@@ -25094,12 +25173,12 @@
     <row r="913">
       <c r="A913" s="6" t="inlineStr">
         <is>
-          <t>7024928</t>
+          <t>7017941</t>
         </is>
       </c>
       <c r="B913" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Line</t>
+          <t>Interiörarmatur Sense Opalprismatisk</t>
         </is>
       </c>
       <c r="C913" t="inlineStr">
@@ -25114,7 +25193,7 @@
     <row r="914">
       <c r="A914" s="4" t="inlineStr">
         <is>
-          <t>7017941</t>
+          <t>7017942</t>
         </is>
       </c>
       <c r="B914" s="5" t="inlineStr">
@@ -25134,7 +25213,7 @@
     <row r="915">
       <c r="A915" s="6" t="inlineStr">
         <is>
-          <t>7017942</t>
+          <t>7024625</t>
         </is>
       </c>
       <c r="B915" t="inlineStr">
@@ -25154,7 +25233,7 @@
     <row r="916">
       <c r="A916" s="4" t="inlineStr">
         <is>
-          <t>7024625</t>
+          <t>7024626</t>
         </is>
       </c>
       <c r="B916" s="5" t="inlineStr">
@@ -25174,7 +25253,7 @@
     <row r="917">
       <c r="A917" s="6" t="inlineStr">
         <is>
-          <t>7024626</t>
+          <t>7024627</t>
         </is>
       </c>
       <c r="B917" t="inlineStr">
@@ -25188,13 +25267,13 @@
         </is>
       </c>
       <c r="D917" s="6" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
     </row>
     <row r="918">
       <c r="A918" s="4" t="inlineStr">
         <is>
-          <t>7024627</t>
+          <t>7024628</t>
         </is>
       </c>
       <c r="B918" s="5" t="inlineStr">
@@ -25208,13 +25287,13 @@
         </is>
       </c>
       <c r="D918" s="4" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
     </row>
     <row r="919">
       <c r="A919" s="6" t="inlineStr">
         <is>
-          <t>7024628</t>
+          <t>7024633</t>
         </is>
       </c>
       <c r="B919" t="inlineStr">
@@ -25234,7 +25313,7 @@
     <row r="920">
       <c r="A920" s="4" t="inlineStr">
         <is>
-          <t>7024633</t>
+          <t>7024634</t>
         </is>
       </c>
       <c r="B920" s="5" t="inlineStr">
@@ -25254,12 +25333,12 @@
     <row r="921">
       <c r="A921" s="6" t="inlineStr">
         <is>
-          <t>7024634</t>
+          <t>7019797</t>
         </is>
       </c>
       <c r="B921" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Opalprismatisk</t>
+          <t>Interiörarmatur Sense Pir</t>
         </is>
       </c>
       <c r="C921" t="inlineStr">
@@ -25274,7 +25353,7 @@
     <row r="922">
       <c r="A922" s="4" t="inlineStr">
         <is>
-          <t>7019797</t>
+          <t>7019798</t>
         </is>
       </c>
       <c r="B922" s="5" t="inlineStr">
@@ -25294,7 +25373,7 @@
     <row r="923">
       <c r="A923" s="6" t="inlineStr">
         <is>
-          <t>7019798</t>
+          <t>7024635</t>
         </is>
       </c>
       <c r="B923" t="inlineStr">
@@ -25308,13 +25387,13 @@
         </is>
       </c>
       <c r="D923" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="924">
       <c r="A924" s="4" t="inlineStr">
         <is>
-          <t>7024635</t>
+          <t>7024636</t>
         </is>
       </c>
       <c r="B924" s="5" t="inlineStr">
@@ -25328,18 +25407,18 @@
         </is>
       </c>
       <c r="D924" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="925">
       <c r="A925" s="6" t="inlineStr">
         <is>
-          <t>7024636</t>
+          <t>7024631</t>
         </is>
       </c>
       <c r="B925" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Pir</t>
+          <t>Interiörarmatur Sense Pro</t>
         </is>
       </c>
       <c r="C925" t="inlineStr">
@@ -25354,7 +25433,7 @@
     <row r="926">
       <c r="A926" s="4" t="inlineStr">
         <is>
-          <t>7024631</t>
+          <t>7024632</t>
         </is>
       </c>
       <c r="B926" s="5" t="inlineStr">
@@ -25374,7 +25453,7 @@
     <row r="927">
       <c r="A927" s="6" t="inlineStr">
         <is>
-          <t>7024632</t>
+          <t>7028741</t>
         </is>
       </c>
       <c r="B927" t="inlineStr">
@@ -25394,12 +25473,12 @@
     <row r="928">
       <c r="A928" s="4" t="inlineStr">
         <is>
-          <t>7028741</t>
+          <t>7026638</t>
         </is>
       </c>
       <c r="B928" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Pro</t>
+          <t>Interiörarmatur Sense Pro Connect</t>
         </is>
       </c>
       <c r="C928" s="5" t="inlineStr">
@@ -25414,7 +25493,7 @@
     <row r="929">
       <c r="A929" s="6" t="inlineStr">
         <is>
-          <t>7026638</t>
+          <t>7026639</t>
         </is>
       </c>
       <c r="B929" t="inlineStr">
@@ -25434,7 +25513,7 @@
     <row r="930">
       <c r="A930" s="4" t="inlineStr">
         <is>
-          <t>7026639</t>
+          <t>7026640</t>
         </is>
       </c>
       <c r="B930" s="5" t="inlineStr">
@@ -25454,7 +25533,7 @@
     <row r="931">
       <c r="A931" s="6" t="inlineStr">
         <is>
-          <t>7026640</t>
+          <t>7026641</t>
         </is>
       </c>
       <c r="B931" t="inlineStr">
@@ -25474,7 +25553,7 @@
     <row r="932">
       <c r="A932" s="4" t="inlineStr">
         <is>
-          <t>7026641</t>
+          <t>7028954</t>
         </is>
       </c>
       <c r="B932" s="5" t="inlineStr">
@@ -25494,7 +25573,7 @@
     <row r="933">
       <c r="A933" s="6" t="inlineStr">
         <is>
-          <t>7028954</t>
+          <t>7028955</t>
         </is>
       </c>
       <c r="B933" t="inlineStr">
@@ -25514,12 +25593,12 @@
     <row r="934">
       <c r="A934" s="4" t="inlineStr">
         <is>
-          <t>7028955</t>
+          <t>7024629</t>
         </is>
       </c>
       <c r="B934" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Pro Connect</t>
+          <t>Interiörarmatur Sense Pro Round</t>
         </is>
       </c>
       <c r="C934" s="5" t="inlineStr">
@@ -25534,7 +25613,7 @@
     <row r="935">
       <c r="A935" s="6" t="inlineStr">
         <is>
-          <t>7024629</t>
+          <t>7024630</t>
         </is>
       </c>
       <c r="B935" t="inlineStr">
@@ -25554,12 +25633,12 @@
     <row r="936">
       <c r="A936" s="4" t="inlineStr">
         <is>
-          <t>7024630</t>
+          <t>7026783</t>
         </is>
       </c>
       <c r="B936" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Pro Round</t>
+          <t>Interiörarmatur Sense Pro X</t>
         </is>
       </c>
       <c r="C936" s="5" t="inlineStr">
@@ -25574,7 +25653,7 @@
     <row r="937">
       <c r="A937" s="6" t="inlineStr">
         <is>
-          <t>7026783</t>
+          <t>7026784</t>
         </is>
       </c>
       <c r="B937" t="inlineStr">
@@ -25594,7 +25673,7 @@
     <row r="938">
       <c r="A938" s="4" t="inlineStr">
         <is>
-          <t>7026784</t>
+          <t>7028122</t>
         </is>
       </c>
       <c r="B938" s="5" t="inlineStr">
@@ -25614,7 +25693,7 @@
     <row r="939">
       <c r="A939" s="6" t="inlineStr">
         <is>
-          <t>7028122</t>
+          <t>7028123</t>
         </is>
       </c>
       <c r="B939" t="inlineStr">
@@ -25634,12 +25713,12 @@
     <row r="940">
       <c r="A940" s="4" t="inlineStr">
         <is>
-          <t>7028123</t>
+          <t>7018057</t>
         </is>
       </c>
       <c r="B940" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Pro X</t>
+          <t>Interiörarmatur Sense TW</t>
         </is>
       </c>
       <c r="C940" s="5" t="inlineStr">
@@ -25654,7 +25733,7 @@
     <row r="941">
       <c r="A941" s="6" t="inlineStr">
         <is>
-          <t>7018057</t>
+          <t>7018056</t>
         </is>
       </c>
       <c r="B941" t="inlineStr">
@@ -25674,12 +25753,12 @@
     <row r="942">
       <c r="A942" s="4" t="inlineStr">
         <is>
-          <t>7018056</t>
+          <t>7016803</t>
         </is>
       </c>
       <c r="B942" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense TW</t>
+          <t>Interiörarmatur Sense TW rund</t>
         </is>
       </c>
       <c r="C942" s="5" t="inlineStr">
@@ -25694,7 +25773,7 @@
     <row r="943">
       <c r="A943" s="6" t="inlineStr">
         <is>
-          <t>7016803</t>
+          <t>7016818</t>
         </is>
       </c>
       <c r="B943" t="inlineStr">
@@ -25714,7 +25793,7 @@
     <row r="944">
       <c r="A944" s="4" t="inlineStr">
         <is>
-          <t>7016818</t>
+          <t>7016819</t>
         </is>
       </c>
       <c r="B944" s="5" t="inlineStr">
@@ -25734,7 +25813,7 @@
     <row r="945">
       <c r="A945" s="6" t="inlineStr">
         <is>
-          <t>7016819</t>
+          <t>7016820</t>
         </is>
       </c>
       <c r="B945" t="inlineStr">
@@ -25754,7 +25833,7 @@
     <row r="946">
       <c r="A946" s="4" t="inlineStr">
         <is>
-          <t>7016820</t>
+          <t>7016822</t>
         </is>
       </c>
       <c r="B946" s="5" t="inlineStr">
@@ -25774,7 +25853,7 @@
     <row r="947">
       <c r="A947" s="6" t="inlineStr">
         <is>
-          <t>7016822</t>
+          <t>7016821</t>
         </is>
       </c>
       <c r="B947" t="inlineStr">
@@ -25794,12 +25873,12 @@
     <row r="948">
       <c r="A948" s="4" t="inlineStr">
         <is>
-          <t>7016821</t>
+          <t>7028408</t>
         </is>
       </c>
       <c r="B948" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense TW rund</t>
+          <t>Interiörarmatur Sense Velios</t>
         </is>
       </c>
       <c r="C948" s="5" t="inlineStr">
@@ -25814,7 +25893,7 @@
     <row r="949">
       <c r="A949" s="6" t="inlineStr">
         <is>
-          <t>7028408</t>
+          <t>7028409</t>
         </is>
       </c>
       <c r="B949" t="inlineStr">
@@ -25834,7 +25913,7 @@
     <row r="950">
       <c r="A950" s="4" t="inlineStr">
         <is>
-          <t>7028409</t>
+          <t>7028410</t>
         </is>
       </c>
       <c r="B950" s="5" t="inlineStr">
@@ -25854,7 +25933,7 @@
     <row r="951">
       <c r="A951" s="6" t="inlineStr">
         <is>
-          <t>7028410</t>
+          <t>7028411</t>
         </is>
       </c>
       <c r="B951" t="inlineStr">
@@ -25874,7 +25953,7 @@
     <row r="952">
       <c r="A952" s="4" t="inlineStr">
         <is>
-          <t>7028411</t>
+          <t>7028412</t>
         </is>
       </c>
       <c r="B952" s="5" t="inlineStr">
@@ -25894,7 +25973,7 @@
     <row r="953">
       <c r="A953" s="6" t="inlineStr">
         <is>
-          <t>7028412</t>
+          <t>7028413</t>
         </is>
       </c>
       <c r="B953" t="inlineStr">
@@ -25914,7 +25993,7 @@
     <row r="954">
       <c r="A954" s="4" t="inlineStr">
         <is>
-          <t>7028413</t>
+          <t>7028414</t>
         </is>
       </c>
       <c r="B954" s="5" t="inlineStr">
@@ -25934,7 +26013,7 @@
     <row r="955">
       <c r="A955" s="6" t="inlineStr">
         <is>
-          <t>7028414</t>
+          <t>7028415</t>
         </is>
       </c>
       <c r="B955" t="inlineStr">
@@ -25954,17 +26033,17 @@
     <row r="956">
       <c r="A956" s="4" t="inlineStr">
         <is>
-          <t>7028415</t>
+          <t>7026760</t>
         </is>
       </c>
       <c r="B956" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Velios</t>
+          <t>Interiörarmatur Apollon 21</t>
         </is>
       </c>
       <c r="C956" s="5" t="inlineStr">
         <is>
-          <t>SG Armaturen</t>
+          <t>Siteco</t>
         </is>
       </c>
       <c r="D956" s="4" t="n">
@@ -25974,7 +26053,7 @@
     <row r="957">
       <c r="A957" s="6" t="inlineStr">
         <is>
-          <t>7026760</t>
+          <t>7027137</t>
         </is>
       </c>
       <c r="B957" t="inlineStr">
@@ -25994,7 +26073,7 @@
     <row r="958">
       <c r="A958" s="4" t="inlineStr">
         <is>
-          <t>7027137</t>
+          <t>7027138</t>
         </is>
       </c>
       <c r="B958" s="5" t="inlineStr">
@@ -26014,7 +26093,7 @@
     <row r="959">
       <c r="A959" s="6" t="inlineStr">
         <is>
-          <t>7027138</t>
+          <t>7027139</t>
         </is>
       </c>
       <c r="B959" t="inlineStr">
@@ -26034,7 +26113,7 @@
     <row r="960">
       <c r="A960" s="4" t="inlineStr">
         <is>
-          <t>7027139</t>
+          <t>7027140</t>
         </is>
       </c>
       <c r="B960" s="5" t="inlineStr">
@@ -26054,7 +26133,7 @@
     <row r="961">
       <c r="A961" s="6" t="inlineStr">
         <is>
-          <t>7027140</t>
+          <t>7027141</t>
         </is>
       </c>
       <c r="B961" t="inlineStr">
@@ -26074,7 +26153,7 @@
     <row r="962">
       <c r="A962" s="4" t="inlineStr">
         <is>
-          <t>7027141</t>
+          <t>7027142</t>
         </is>
       </c>
       <c r="B962" s="5" t="inlineStr">
@@ -26094,7 +26173,7 @@
     <row r="963">
       <c r="A963" s="6" t="inlineStr">
         <is>
-          <t>7027142</t>
+          <t>7027143</t>
         </is>
       </c>
       <c r="B963" t="inlineStr">
@@ -26114,7 +26193,7 @@
     <row r="964">
       <c r="A964" s="4" t="inlineStr">
         <is>
-          <t>7027143</t>
+          <t>7027144</t>
         </is>
       </c>
       <c r="B964" s="5" t="inlineStr">
@@ -26134,17 +26213,17 @@
     <row r="965">
       <c r="A965" s="6" t="inlineStr">
         <is>
-          <t>7027144</t>
+          <t>7077510</t>
         </is>
       </c>
       <c r="B965" t="inlineStr">
         <is>
-          <t>Interiörarmatur Apollon 21</t>
+          <t>Infälld interiörarmatur IQ Wave</t>
         </is>
       </c>
       <c r="C965" t="inlineStr">
         <is>
-          <t>Siteco</t>
+          <t>THORN</t>
         </is>
       </c>
       <c r="D965" s="6" t="n">
@@ -26154,7 +26233,7 @@
     <row r="966">
       <c r="A966" s="4" t="inlineStr">
         <is>
-          <t>7077510</t>
+          <t>7077516</t>
         </is>
       </c>
       <c r="B966" s="5" t="inlineStr">
@@ -26174,7 +26253,7 @@
     <row r="967">
       <c r="A967" s="6" t="inlineStr">
         <is>
-          <t>7077516</t>
+          <t>7077513</t>
         </is>
       </c>
       <c r="B967" t="inlineStr">
@@ -26194,7 +26273,7 @@
     <row r="968">
       <c r="A968" s="4" t="inlineStr">
         <is>
-          <t>7077513</t>
+          <t>7077517</t>
         </is>
       </c>
       <c r="B968" s="5" t="inlineStr">
@@ -26214,7 +26293,7 @@
     <row r="969">
       <c r="A969" s="6" t="inlineStr">
         <is>
-          <t>7077517</t>
+          <t>7077577</t>
         </is>
       </c>
       <c r="B969" t="inlineStr">
@@ -26234,12 +26313,12 @@
     <row r="970">
       <c r="A970" s="4" t="inlineStr">
         <is>
-          <t>7077577</t>
+          <t>7018153</t>
         </is>
       </c>
       <c r="B970" s="5" t="inlineStr">
         <is>
-          <t>Infälld interiörarmatur IQ Wave</t>
+          <t>Infälld interiörarmatur Omega Pro 2</t>
         </is>
       </c>
       <c r="C970" s="5" t="inlineStr">
@@ -26254,7 +26333,7 @@
     <row r="971">
       <c r="A971" s="6" t="inlineStr">
         <is>
-          <t>7018153</t>
+          <t>7018765</t>
         </is>
       </c>
       <c r="B971" t="inlineStr">
@@ -26274,17 +26353,17 @@
     <row r="972">
       <c r="A972" s="4" t="inlineStr">
         <is>
-          <t>7018765</t>
+          <t>7022037</t>
         </is>
       </c>
       <c r="B972" s="5" t="inlineStr">
         <is>
-          <t>Infälld interiörarmatur Omega Pro 2</t>
+          <t>Interiörarmatur US Circle infälld</t>
         </is>
       </c>
       <c r="C972" s="5" t="inlineStr">
         <is>
-          <t>THORN</t>
+          <t>Tupex</t>
         </is>
       </c>
       <c r="D972" s="4" t="n">
@@ -26294,7 +26373,7 @@
     <row r="973">
       <c r="A973" s="6" t="inlineStr">
         <is>
-          <t>7022037</t>
+          <t>7022038</t>
         </is>
       </c>
       <c r="B973" t="inlineStr">
@@ -26314,7 +26393,7 @@
     <row r="974">
       <c r="A974" s="4" t="inlineStr">
         <is>
-          <t>7022038</t>
+          <t>7021686</t>
         </is>
       </c>
       <c r="B974" s="5" t="inlineStr">
@@ -26334,7 +26413,7 @@
     <row r="975">
       <c r="A975" s="6" t="inlineStr">
         <is>
-          <t>7021686</t>
+          <t>7021687</t>
         </is>
       </c>
       <c r="B975" t="inlineStr">
@@ -26354,7 +26433,7 @@
     <row r="976">
       <c r="A976" s="4" t="inlineStr">
         <is>
-          <t>7021687</t>
+          <t>7022043</t>
         </is>
       </c>
       <c r="B976" s="5" t="inlineStr">
@@ -26374,7 +26453,7 @@
     <row r="977">
       <c r="A977" s="6" t="inlineStr">
         <is>
-          <t>7022043</t>
+          <t>7022045</t>
         </is>
       </c>
       <c r="B977" t="inlineStr">
@@ -26394,12 +26473,12 @@
     <row r="978">
       <c r="A978" s="4" t="inlineStr">
         <is>
-          <t>7022045</t>
+          <t>7026483</t>
         </is>
       </c>
       <c r="B978" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur US Circle infälld</t>
+          <t>Interiörarmatur US Eco Infälld</t>
         </is>
       </c>
       <c r="C978" s="5" t="inlineStr">
@@ -26414,7 +26493,7 @@
     <row r="979">
       <c r="A979" s="6" t="inlineStr">
         <is>
-          <t>7026483</t>
+          <t>7021611</t>
         </is>
       </c>
       <c r="B979" t="inlineStr">
@@ -26428,13 +26507,13 @@
         </is>
       </c>
       <c r="D979" s="6" t="n">
-        <v>0</v>
+        <v>105</v>
       </c>
     </row>
     <row r="980">
       <c r="A980" s="4" t="inlineStr">
         <is>
-          <t>7021611</t>
+          <t>7029355</t>
         </is>
       </c>
       <c r="B980" s="5" t="inlineStr">
@@ -26448,13 +26527,13 @@
         </is>
       </c>
       <c r="D980" s="4" t="n">
-        <v>117</v>
+        <v>104</v>
       </c>
     </row>
     <row r="981">
       <c r="A981" s="6" t="inlineStr">
         <is>
-          <t>7029355</t>
+          <t>7029356</t>
         </is>
       </c>
       <c r="B981" t="inlineStr">
@@ -26468,13 +26547,13 @@
         </is>
       </c>
       <c r="D981" s="6" t="n">
-        <v>94</v>
+        <v>167</v>
       </c>
     </row>
     <row r="982">
       <c r="A982" s="4" t="inlineStr">
         <is>
-          <t>7029356</t>
+          <t>7029357</t>
         </is>
       </c>
       <c r="B982" s="5" t="inlineStr">
@@ -26488,18 +26567,18 @@
         </is>
       </c>
       <c r="D982" s="4" t="n">
-        <v>149</v>
+        <v>12</v>
       </c>
     </row>
     <row r="983">
       <c r="A983" s="6" t="inlineStr">
         <is>
-          <t>7029357</t>
+          <t>7021628</t>
         </is>
       </c>
       <c r="B983" t="inlineStr">
         <is>
-          <t>Interiörarmatur US Eco Infälld</t>
+          <t>Interiörarmatur US Sens infälld med grundljus</t>
         </is>
       </c>
       <c r="C983" t="inlineStr">
@@ -26508,13 +26587,13 @@
         </is>
       </c>
       <c r="D983" s="6" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="984">
       <c r="A984" s="4" t="inlineStr">
         <is>
-          <t>7021628</t>
+          <t>7021629</t>
         </is>
       </c>
       <c r="B984" s="5" t="inlineStr">
@@ -26534,12 +26613,12 @@
     <row r="985">
       <c r="A985" s="6" t="inlineStr">
         <is>
-          <t>7021629</t>
+          <t>7021996</t>
         </is>
       </c>
       <c r="B985" t="inlineStr">
         <is>
-          <t>Interiörarmatur US Sens infälld med grundljus</t>
+          <t>Interiörarmatur US infälld</t>
         </is>
       </c>
       <c r="C985" t="inlineStr">
@@ -26554,7 +26633,7 @@
     <row r="986">
       <c r="A986" s="4" t="inlineStr">
         <is>
-          <t>7021996</t>
+          <t>7021997</t>
         </is>
       </c>
       <c r="B986" s="5" t="inlineStr">
@@ -26574,7 +26653,7 @@
     <row r="987">
       <c r="A987" s="6" t="inlineStr">
         <is>
-          <t>7021997</t>
+          <t>7021617</t>
         </is>
       </c>
       <c r="B987" t="inlineStr">
@@ -26594,7 +26673,7 @@
     <row r="988">
       <c r="A988" s="4" t="inlineStr">
         <is>
-          <t>7021617</t>
+          <t>7021618</t>
         </is>
       </c>
       <c r="B988" s="5" t="inlineStr">
@@ -26614,7 +26693,7 @@
     <row r="989">
       <c r="A989" s="6" t="inlineStr">
         <is>
-          <t>7021618</t>
+          <t>7022019</t>
         </is>
       </c>
       <c r="B989" t="inlineStr">
@@ -26634,7 +26713,7 @@
     <row r="990">
       <c r="A990" s="4" t="inlineStr">
         <is>
-          <t>7022019</t>
+          <t>7022021</t>
         </is>
       </c>
       <c r="B990" s="5" t="inlineStr">
@@ -26654,17 +26733,17 @@
     <row r="991">
       <c r="A991" s="6" t="inlineStr">
         <is>
-          <t>7022021</t>
+          <t>7015332</t>
         </is>
       </c>
       <c r="B991" t="inlineStr">
         <is>
-          <t>Interiörarmatur US infälld</t>
+          <t>Infälld interiörarmatur WLP</t>
         </is>
       </c>
       <c r="C991" t="inlineStr">
         <is>
-          <t>Tupex</t>
+          <t>Westal</t>
         </is>
       </c>
       <c r="D991" s="6" t="n">
@@ -26674,7 +26753,7 @@
     <row r="992">
       <c r="A992" s="4" t="inlineStr">
         <is>
-          <t>7015332</t>
+          <t>7018758</t>
         </is>
       </c>
       <c r="B992" s="5" t="inlineStr">
@@ -26694,7 +26773,7 @@
     <row r="993">
       <c r="A993" s="6" t="inlineStr">
         <is>
-          <t>7018758</t>
+          <t>7015333</t>
         </is>
       </c>
       <c r="B993" t="inlineStr">
@@ -26714,7 +26793,7 @@
     <row r="994">
       <c r="A994" s="4" t="inlineStr">
         <is>
-          <t>7015333</t>
+          <t>7016779</t>
         </is>
       </c>
       <c r="B994" s="5" t="inlineStr">
@@ -26734,12 +26813,12 @@
     <row r="995">
       <c r="A995" s="6" t="inlineStr">
         <is>
-          <t>7016779</t>
+          <t>7018294</t>
         </is>
       </c>
       <c r="B995" t="inlineStr">
         <is>
-          <t>Infälld interiörarmatur WLP</t>
+          <t>Infälld interiörarmatur WLP tunable</t>
         </is>
       </c>
       <c r="C995" t="inlineStr">
@@ -26754,7 +26833,7 @@
     <row r="996">
       <c r="A996" s="4" t="inlineStr">
         <is>
-          <t>7018294</t>
+          <t>7021000</t>
         </is>
       </c>
       <c r="B996" s="5" t="inlineStr">
@@ -26774,12 +26853,12 @@
     <row r="997">
       <c r="A997" s="6" t="inlineStr">
         <is>
-          <t>7021000</t>
+          <t>7020998</t>
         </is>
       </c>
       <c r="B997" t="inlineStr">
         <is>
-          <t>Infälld interiörarmatur WLP tunable</t>
+          <t>Infälld interiörarmatur WLP, ActiveAhead</t>
         </is>
       </c>
       <c r="C997" t="inlineStr">
@@ -26794,7 +26873,7 @@
     <row r="998">
       <c r="A998" s="4" t="inlineStr">
         <is>
-          <t>7020998</t>
+          <t>7020999</t>
         </is>
       </c>
       <c r="B998" s="5" t="inlineStr">
@@ -26814,7 +26893,7 @@
     <row r="999">
       <c r="A999" s="6" t="inlineStr">
         <is>
-          <t>7020999</t>
+          <t>7024828</t>
         </is>
       </c>
       <c r="B999" t="inlineStr">
@@ -26834,7 +26913,7 @@
     <row r="1000">
       <c r="A1000" s="4" t="inlineStr">
         <is>
-          <t>7024828</t>
+          <t>7024829</t>
         </is>
       </c>
       <c r="B1000" s="5" t="inlineStr">
@@ -26854,12 +26933,12 @@
     <row r="1001">
       <c r="A1001" s="6" t="inlineStr">
         <is>
-          <t>7024829</t>
+          <t>7018759</t>
         </is>
       </c>
       <c r="B1001" t="inlineStr">
         <is>
-          <t>Infälld interiörarmatur WLP, ActiveAhead</t>
+          <t>Infälld interiörarmatur WLP-D IP65</t>
         </is>
       </c>
       <c r="C1001" t="inlineStr">
@@ -26874,7 +26953,7 @@
     <row r="1002">
       <c r="A1002" s="4" t="inlineStr">
         <is>
-          <t>7018759</t>
+          <t>7018764</t>
         </is>
       </c>
       <c r="B1002" s="5" t="inlineStr">
@@ -26894,12 +26973,12 @@
     <row r="1003">
       <c r="A1003" s="6" t="inlineStr">
         <is>
-          <t>7018764</t>
+          <t>7025805</t>
         </is>
       </c>
       <c r="B1003" t="inlineStr">
         <is>
-          <t>Infälld interiörarmatur WLP-D IP65</t>
+          <t>Interiörarmatur Lino infälld L-stycke</t>
         </is>
       </c>
       <c r="C1003" t="inlineStr">
@@ -26914,7 +26993,7 @@
     <row r="1004">
       <c r="A1004" s="4" t="inlineStr">
         <is>
-          <t>7025805</t>
+          <t>7025806</t>
         </is>
       </c>
       <c r="B1004" s="5" t="inlineStr">
@@ -26934,7 +27013,7 @@
     <row r="1005">
       <c r="A1005" s="6" t="inlineStr">
         <is>
-          <t>7025806</t>
+          <t>7025817</t>
         </is>
       </c>
       <c r="B1005" t="inlineStr">
@@ -26954,7 +27033,7 @@
     <row r="1006">
       <c r="A1006" s="4" t="inlineStr">
         <is>
-          <t>7025817</t>
+          <t>7025818</t>
         </is>
       </c>
       <c r="B1006" s="5" t="inlineStr">
@@ -26974,12 +27053,12 @@
     <row r="1007">
       <c r="A1007" s="6" t="inlineStr">
         <is>
-          <t>7025818</t>
+          <t>7025809</t>
         </is>
       </c>
       <c r="B1007" t="inlineStr">
         <is>
-          <t>Interiörarmatur Lino infälld L-stycke</t>
+          <t>Interiörarmatur Lino infälld X-stycke</t>
         </is>
       </c>
       <c r="C1007" t="inlineStr">
@@ -26994,7 +27073,7 @@
     <row r="1008">
       <c r="A1008" s="4" t="inlineStr">
         <is>
-          <t>7025809</t>
+          <t>7025810</t>
         </is>
       </c>
       <c r="B1008" s="5" t="inlineStr">
@@ -27014,7 +27093,7 @@
     <row r="1009">
       <c r="A1009" s="6" t="inlineStr">
         <is>
-          <t>7025810</t>
+          <t>7025821</t>
         </is>
       </c>
       <c r="B1009" t="inlineStr">
@@ -27034,7 +27113,7 @@
     <row r="1010">
       <c r="A1010" s="4" t="inlineStr">
         <is>
-          <t>7025821</t>
+          <t>7025822</t>
         </is>
       </c>
       <c r="B1010" s="5" t="inlineStr">
@@ -27054,12 +27133,12 @@
     <row r="1011">
       <c r="A1011" s="6" t="inlineStr">
         <is>
-          <t>7025822</t>
+          <t>7025757E</t>
         </is>
       </c>
       <c r="B1011" t="inlineStr">
         <is>
-          <t>Interiörarmatur Lino infälld X-stycke</t>
+          <t>Interiörarmatur Lino infälld mittsektion</t>
         </is>
       </c>
       <c r="C1011" t="inlineStr">
@@ -27074,7 +27153,7 @@
     <row r="1012">
       <c r="A1012" s="4" t="inlineStr">
         <is>
-          <t>7025757E</t>
+          <t>7025758</t>
         </is>
       </c>
       <c r="B1012" s="5" t="inlineStr">
@@ -27094,7 +27173,7 @@
     <row r="1013">
       <c r="A1013" s="6" t="inlineStr">
         <is>
-          <t>7025758</t>
+          <t>7025759</t>
         </is>
       </c>
       <c r="B1013" t="inlineStr">
@@ -27114,7 +27193,7 @@
     <row r="1014">
       <c r="A1014" s="4" t="inlineStr">
         <is>
-          <t>7025759</t>
+          <t>7025760</t>
         </is>
       </c>
       <c r="B1014" s="5" t="inlineStr">
@@ -27134,7 +27213,7 @@
     <row r="1015">
       <c r="A1015" s="6" t="inlineStr">
         <is>
-          <t>7025760</t>
+          <t>7025761</t>
         </is>
       </c>
       <c r="B1015" t="inlineStr">
@@ -27154,7 +27233,7 @@
     <row r="1016">
       <c r="A1016" s="4" t="inlineStr">
         <is>
-          <t>7025761</t>
+          <t>7025762E</t>
         </is>
       </c>
       <c r="B1016" s="5" t="inlineStr">
@@ -27174,7 +27253,7 @@
     <row r="1017">
       <c r="A1017" s="6" t="inlineStr">
         <is>
-          <t>7025762E</t>
+          <t>7025763E</t>
         </is>
       </c>
       <c r="B1017" t="inlineStr">
@@ -27194,7 +27273,7 @@
     <row r="1018">
       <c r="A1018" s="4" t="inlineStr">
         <is>
-          <t>7025763E</t>
+          <t>7025764</t>
         </is>
       </c>
       <c r="B1018" s="5" t="inlineStr">
@@ -27214,7 +27293,7 @@
     <row r="1019">
       <c r="A1019" s="6" t="inlineStr">
         <is>
-          <t>7025764</t>
+          <t>7025765</t>
         </is>
       </c>
       <c r="B1019" t="inlineStr">
@@ -27234,7 +27313,7 @@
     <row r="1020">
       <c r="A1020" s="4" t="inlineStr">
         <is>
-          <t>7025765</t>
+          <t>7025766</t>
         </is>
       </c>
       <c r="B1020" s="5" t="inlineStr">
@@ -27254,7 +27333,7 @@
     <row r="1021">
       <c r="A1021" s="6" t="inlineStr">
         <is>
-          <t>7025766</t>
+          <t>7025767</t>
         </is>
       </c>
       <c r="B1021" t="inlineStr">
@@ -27274,7 +27353,7 @@
     <row r="1022">
       <c r="A1022" s="4" t="inlineStr">
         <is>
-          <t>7025767</t>
+          <t>7025768</t>
         </is>
       </c>
       <c r="B1022" s="5" t="inlineStr">
@@ -27294,7 +27373,7 @@
     <row r="1023">
       <c r="A1023" s="6" t="inlineStr">
         <is>
-          <t>7025768</t>
+          <t>7025769</t>
         </is>
       </c>
       <c r="B1023" t="inlineStr">
@@ -27314,7 +27393,7 @@
     <row r="1024">
       <c r="A1024" s="4" t="inlineStr">
         <is>
-          <t>7025769</t>
+          <t>7025770</t>
         </is>
       </c>
       <c r="B1024" s="5" t="inlineStr">
@@ -27334,7 +27413,7 @@
     <row r="1025">
       <c r="A1025" s="6" t="inlineStr">
         <is>
-          <t>7025770</t>
+          <t>7025785</t>
         </is>
       </c>
       <c r="B1025" t="inlineStr">
@@ -27354,7 +27433,7 @@
     <row r="1026">
       <c r="A1026" s="4" t="inlineStr">
         <is>
-          <t>7025785</t>
+          <t>7025786</t>
         </is>
       </c>
       <c r="B1026" s="5" t="inlineStr">
@@ -27374,7 +27453,7 @@
     <row r="1027">
       <c r="A1027" s="6" t="inlineStr">
         <is>
-          <t>7025786</t>
+          <t>7025787</t>
         </is>
       </c>
       <c r="B1027" t="inlineStr">
@@ -27394,7 +27473,7 @@
     <row r="1028">
       <c r="A1028" s="4" t="inlineStr">
         <is>
-          <t>7025787</t>
+          <t>7025788</t>
         </is>
       </c>
       <c r="B1028" s="5" t="inlineStr">
@@ -27414,7 +27493,7 @@
     <row r="1029">
       <c r="A1029" s="6" t="inlineStr">
         <is>
-          <t>7025788</t>
+          <t>7025789</t>
         </is>
       </c>
       <c r="B1029" t="inlineStr">
@@ -27434,7 +27513,7 @@
     <row r="1030">
       <c r="A1030" s="4" t="inlineStr">
         <is>
-          <t>7025789</t>
+          <t>7025790</t>
         </is>
       </c>
       <c r="B1030" s="5" t="inlineStr">
@@ -27454,7 +27533,7 @@
     <row r="1031">
       <c r="A1031" s="6" t="inlineStr">
         <is>
-          <t>7025790</t>
+          <t>7025791</t>
         </is>
       </c>
       <c r="B1031" t="inlineStr">
@@ -27474,7 +27553,7 @@
     <row r="1032">
       <c r="A1032" s="4" t="inlineStr">
         <is>
-          <t>7025791</t>
+          <t>7025792</t>
         </is>
       </c>
       <c r="B1032" s="5" t="inlineStr">
@@ -27494,7 +27573,7 @@
     <row r="1033">
       <c r="A1033" s="6" t="inlineStr">
         <is>
-          <t>7025792</t>
+          <t>7025793</t>
         </is>
       </c>
       <c r="B1033" t="inlineStr">
@@ -27514,7 +27593,7 @@
     <row r="1034">
       <c r="A1034" s="4" t="inlineStr">
         <is>
-          <t>7025793</t>
+          <t>7025794</t>
         </is>
       </c>
       <c r="B1034" s="5" t="inlineStr">
@@ -27534,7 +27613,7 @@
     <row r="1035">
       <c r="A1035" s="6" t="inlineStr">
         <is>
-          <t>7025794</t>
+          <t>7025795</t>
         </is>
       </c>
       <c r="B1035" t="inlineStr">
@@ -27554,7 +27633,7 @@
     <row r="1036">
       <c r="A1036" s="4" t="inlineStr">
         <is>
-          <t>7025795</t>
+          <t>7025796</t>
         </is>
       </c>
       <c r="B1036" s="5" t="inlineStr">
@@ -27574,7 +27653,7 @@
     <row r="1037">
       <c r="A1037" s="6" t="inlineStr">
         <is>
-          <t>7025796</t>
+          <t>7025797</t>
         </is>
       </c>
       <c r="B1037" t="inlineStr">
@@ -27594,7 +27673,7 @@
     <row r="1038">
       <c r="A1038" s="4" t="inlineStr">
         <is>
-          <t>7025797</t>
+          <t>7025798</t>
         </is>
       </c>
       <c r="B1038" s="5" t="inlineStr">
@@ -27614,12 +27693,12 @@
     <row r="1039">
       <c r="A1039" s="6" t="inlineStr">
         <is>
-          <t>7025798</t>
+          <t>7025689</t>
         </is>
       </c>
       <c r="B1039" t="inlineStr">
         <is>
-          <t>Interiörarmatur Lino infälld mittsektion</t>
+          <t>Interiörarmatur Lino infälld start/slut sektion</t>
         </is>
       </c>
       <c r="C1039" t="inlineStr">
@@ -27634,7 +27713,7 @@
     <row r="1040">
       <c r="A1040" s="4" t="inlineStr">
         <is>
-          <t>7025689</t>
+          <t>7025690</t>
         </is>
       </c>
       <c r="B1040" s="5" t="inlineStr">
@@ -27654,7 +27733,7 @@
     <row r="1041">
       <c r="A1041" s="6" t="inlineStr">
         <is>
-          <t>7025690</t>
+          <t>7025691</t>
         </is>
       </c>
       <c r="B1041" t="inlineStr">
@@ -27674,7 +27753,7 @@
     <row r="1042">
       <c r="A1042" s="4" t="inlineStr">
         <is>
-          <t>7025691</t>
+          <t>7025692</t>
         </is>
       </c>
       <c r="B1042" s="5" t="inlineStr">
@@ -27694,7 +27773,7 @@
     <row r="1043">
       <c r="A1043" s="6" t="inlineStr">
         <is>
-          <t>7025692</t>
+          <t>7025693</t>
         </is>
       </c>
       <c r="B1043" t="inlineStr">
@@ -27714,7 +27793,7 @@
     <row r="1044">
       <c r="A1044" s="4" t="inlineStr">
         <is>
-          <t>7025693</t>
+          <t>7025694</t>
         </is>
       </c>
       <c r="B1044" s="5" t="inlineStr">
@@ -27734,7 +27813,7 @@
     <row r="1045">
       <c r="A1045" s="6" t="inlineStr">
         <is>
-          <t>7025694</t>
+          <t>7025695</t>
         </is>
       </c>
       <c r="B1045" t="inlineStr">
@@ -27754,7 +27833,7 @@
     <row r="1046">
       <c r="A1046" s="4" t="inlineStr">
         <is>
-          <t>7025695</t>
+          <t>7025696</t>
         </is>
       </c>
       <c r="B1046" s="5" t="inlineStr">
@@ -27774,7 +27853,7 @@
     <row r="1047">
       <c r="A1047" s="6" t="inlineStr">
         <is>
-          <t>7025696</t>
+          <t>7025697</t>
         </is>
       </c>
       <c r="B1047" t="inlineStr">
@@ -27794,7 +27873,7 @@
     <row r="1048">
       <c r="A1048" s="4" t="inlineStr">
         <is>
-          <t>7025697</t>
+          <t>7025698</t>
         </is>
       </c>
       <c r="B1048" s="5" t="inlineStr">
@@ -27814,7 +27893,7 @@
     <row r="1049">
       <c r="A1049" s="6" t="inlineStr">
         <is>
-          <t>7025698</t>
+          <t>7025699</t>
         </is>
       </c>
       <c r="B1049" t="inlineStr">
@@ -27834,7 +27913,7 @@
     <row r="1050">
       <c r="A1050" s="4" t="inlineStr">
         <is>
-          <t>7025699</t>
+          <t>7025700</t>
         </is>
       </c>
       <c r="B1050" s="5" t="inlineStr">
@@ -27854,7 +27933,7 @@
     <row r="1051">
       <c r="A1051" s="6" t="inlineStr">
         <is>
-          <t>7025700</t>
+          <t>7025701</t>
         </is>
       </c>
       <c r="B1051" t="inlineStr">
@@ -27874,7 +27953,7 @@
     <row r="1052">
       <c r="A1052" s="4" t="inlineStr">
         <is>
-          <t>7025701</t>
+          <t>7025702</t>
         </is>
       </c>
       <c r="B1052" s="5" t="inlineStr">
@@ -27894,7 +27973,7 @@
     <row r="1053">
       <c r="A1053" s="6" t="inlineStr">
         <is>
-          <t>7025702</t>
+          <t>7025703</t>
         </is>
       </c>
       <c r="B1053" t="inlineStr">
@@ -27914,7 +27993,7 @@
     <row r="1054">
       <c r="A1054" s="4" t="inlineStr">
         <is>
-          <t>7025703</t>
+          <t>7025704</t>
         </is>
       </c>
       <c r="B1054" s="5" t="inlineStr">
@@ -27934,7 +28013,7 @@
     <row r="1055">
       <c r="A1055" s="6" t="inlineStr">
         <is>
-          <t>7025704</t>
+          <t>7025705</t>
         </is>
       </c>
       <c r="B1055" t="inlineStr">
@@ -27954,7 +28033,7 @@
     <row r="1056">
       <c r="A1056" s="4" t="inlineStr">
         <is>
-          <t>7025705</t>
+          <t>7025706</t>
         </is>
       </c>
       <c r="B1056" s="5" t="inlineStr">
@@ -27974,7 +28053,7 @@
     <row r="1057">
       <c r="A1057" s="6" t="inlineStr">
         <is>
-          <t>7025706</t>
+          <t>7025725</t>
         </is>
       </c>
       <c r="B1057" t="inlineStr">
@@ -27994,7 +28073,7 @@
     <row r="1058">
       <c r="A1058" s="4" t="inlineStr">
         <is>
-          <t>7025725</t>
+          <t>7025726</t>
         </is>
       </c>
       <c r="B1058" s="5" t="inlineStr">
@@ -28014,7 +28093,7 @@
     <row r="1059">
       <c r="A1059" s="6" t="inlineStr">
         <is>
-          <t>7025726</t>
+          <t>7025727</t>
         </is>
       </c>
       <c r="B1059" t="inlineStr">
@@ -28034,7 +28113,7 @@
     <row r="1060">
       <c r="A1060" s="4" t="inlineStr">
         <is>
-          <t>7025727</t>
+          <t>7025728</t>
         </is>
       </c>
       <c r="B1060" s="5" t="inlineStr">
@@ -28054,7 +28133,7 @@
     <row r="1061">
       <c r="A1061" s="6" t="inlineStr">
         <is>
-          <t>7025728</t>
+          <t>7025729</t>
         </is>
       </c>
       <c r="B1061" t="inlineStr">
@@ -28074,7 +28153,7 @@
     <row r="1062">
       <c r="A1062" s="4" t="inlineStr">
         <is>
-          <t>7025729</t>
+          <t>7025730</t>
         </is>
       </c>
       <c r="B1062" s="5" t="inlineStr">
@@ -28094,7 +28173,7 @@
     <row r="1063">
       <c r="A1063" s="6" t="inlineStr">
         <is>
-          <t>7025730</t>
+          <t>7025731</t>
         </is>
       </c>
       <c r="B1063" t="inlineStr">
@@ -28114,7 +28193,7 @@
     <row r="1064">
       <c r="A1064" s="4" t="inlineStr">
         <is>
-          <t>7025731</t>
+          <t>7025732</t>
         </is>
       </c>
       <c r="B1064" s="5" t="inlineStr">
@@ -28134,7 +28213,7 @@
     <row r="1065">
       <c r="A1065" s="6" t="inlineStr">
         <is>
-          <t>7025732</t>
+          <t>7025733</t>
         </is>
       </c>
       <c r="B1065" t="inlineStr">
@@ -28154,7 +28233,7 @@
     <row r="1066">
       <c r="A1066" s="4" t="inlineStr">
         <is>
-          <t>7025733</t>
+          <t>7025734</t>
         </is>
       </c>
       <c r="B1066" s="5" t="inlineStr">
@@ -28174,7 +28253,7 @@
     <row r="1067">
       <c r="A1067" s="6" t="inlineStr">
         <is>
-          <t>7025734</t>
+          <t>7025735E</t>
         </is>
       </c>
       <c r="B1067" t="inlineStr">
@@ -28194,7 +28273,7 @@
     <row r="1068">
       <c r="A1068" s="4" t="inlineStr">
         <is>
-          <t>7025735E</t>
+          <t>7025736E</t>
         </is>
       </c>
       <c r="B1068" s="5" t="inlineStr">
@@ -28214,7 +28293,7 @@
     <row r="1069">
       <c r="A1069" s="6" t="inlineStr">
         <is>
-          <t>7025736E</t>
+          <t>7025737</t>
         </is>
       </c>
       <c r="B1069" t="inlineStr">
@@ -28234,7 +28313,7 @@
     <row r="1070">
       <c r="A1070" s="4" t="inlineStr">
         <is>
-          <t>7025737</t>
+          <t>7025738</t>
         </is>
       </c>
       <c r="B1070" s="5" t="inlineStr">
@@ -28254,7 +28333,7 @@
     <row r="1071">
       <c r="A1071" s="6" t="inlineStr">
         <is>
-          <t>7025738</t>
+          <t>7025739</t>
         </is>
       </c>
       <c r="B1071" t="inlineStr">
@@ -28274,7 +28353,7 @@
     <row r="1072">
       <c r="A1072" s="4" t="inlineStr">
         <is>
-          <t>7025739</t>
+          <t>7025740</t>
         </is>
       </c>
       <c r="B1072" s="5" t="inlineStr">
@@ -28294,7 +28373,7 @@
     <row r="1073">
       <c r="A1073" s="6" t="inlineStr">
         <is>
-          <t>7025740</t>
+          <t>7025741</t>
         </is>
       </c>
       <c r="B1073" t="inlineStr">
@@ -28314,7 +28393,7 @@
     <row r="1074">
       <c r="A1074" s="4" t="inlineStr">
         <is>
-          <t>7025741</t>
+          <t>7025742</t>
         </is>
       </c>
       <c r="B1074" s="5" t="inlineStr">
@@ -28334,12 +28413,12 @@
     <row r="1075">
       <c r="A1075" s="6" t="inlineStr">
         <is>
-          <t>7025742</t>
+          <t>7510324</t>
         </is>
       </c>
       <c r="B1075" t="inlineStr">
         <is>
-          <t>Interiörarmatur Lino infälld start/slut sektion</t>
+          <t>Interiörarmatur Mira 1x28 infälld</t>
         </is>
       </c>
       <c r="C1075" t="inlineStr">
@@ -28354,7 +28433,7 @@
     <row r="1076">
       <c r="A1076" s="4" t="inlineStr">
         <is>
-          <t>7510324</t>
+          <t>7510325</t>
         </is>
       </c>
       <c r="B1076" s="5" t="inlineStr">
@@ -28374,7 +28453,7 @@
     <row r="1077">
       <c r="A1077" s="6" t="inlineStr">
         <is>
-          <t>7510325</t>
+          <t>7510326</t>
         </is>
       </c>
       <c r="B1077" t="inlineStr">
@@ -28394,7 +28473,7 @@
     <row r="1078">
       <c r="A1078" s="4" t="inlineStr">
         <is>
-          <t>7510326</t>
+          <t>7510327</t>
         </is>
       </c>
       <c r="B1078" s="5" t="inlineStr">
@@ -28414,7 +28493,7 @@
     <row r="1079">
       <c r="A1079" s="6" t="inlineStr">
         <is>
-          <t>7510327</t>
+          <t>7510328</t>
         </is>
       </c>
       <c r="B1079" t="inlineStr">
@@ -28434,7 +28513,7 @@
     <row r="1080">
       <c r="A1080" s="4" t="inlineStr">
         <is>
-          <t>7510328</t>
+          <t>7510329</t>
         </is>
       </c>
       <c r="B1080" s="5" t="inlineStr">
@@ -28454,7 +28533,7 @@
     <row r="1081">
       <c r="A1081" s="6" t="inlineStr">
         <is>
-          <t>7510329</t>
+          <t>7510344</t>
         </is>
       </c>
       <c r="B1081" t="inlineStr">
@@ -28474,7 +28553,7 @@
     <row r="1082">
       <c r="A1082" s="4" t="inlineStr">
         <is>
-          <t>7510344</t>
+          <t>7510345</t>
         </is>
       </c>
       <c r="B1082" s="5" t="inlineStr">
@@ -28494,7 +28573,7 @@
     <row r="1083">
       <c r="A1083" s="6" t="inlineStr">
         <is>
-          <t>7510345</t>
+          <t>7510346</t>
         </is>
       </c>
       <c r="B1083" t="inlineStr">
@@ -28514,7 +28593,7 @@
     <row r="1084">
       <c r="A1084" s="4" t="inlineStr">
         <is>
-          <t>7510346</t>
+          <t>7510347</t>
         </is>
       </c>
       <c r="B1084" s="5" t="inlineStr">
@@ -28534,7 +28613,7 @@
     <row r="1085">
       <c r="A1085" s="6" t="inlineStr">
         <is>
-          <t>7510347</t>
+          <t>7510348</t>
         </is>
       </c>
       <c r="B1085" t="inlineStr">
@@ -28554,7 +28633,7 @@
     <row r="1086">
       <c r="A1086" s="4" t="inlineStr">
         <is>
-          <t>7510348</t>
+          <t>7510349</t>
         </is>
       </c>
       <c r="B1086" s="5" t="inlineStr">
@@ -28574,12 +28653,12 @@
     <row r="1087">
       <c r="A1087" s="6" t="inlineStr">
         <is>
-          <t>7510349</t>
+          <t>7021294</t>
         </is>
       </c>
       <c r="B1087" t="inlineStr">
         <is>
-          <t>Interiörarmatur Mira 1x28 infälld</t>
+          <t>Interiörarmatur WLP Backlit</t>
         </is>
       </c>
       <c r="C1087" t="inlineStr">
@@ -28594,7 +28673,7 @@
     <row r="1088">
       <c r="A1088" s="4" t="inlineStr">
         <is>
-          <t>7021294</t>
+          <t>7021295</t>
         </is>
       </c>
       <c r="B1088" s="5" t="inlineStr">
@@ -28614,7 +28693,7 @@
     <row r="1089">
       <c r="A1089" s="6" t="inlineStr">
         <is>
-          <t>7021295</t>
+          <t>7024767</t>
         </is>
       </c>
       <c r="B1089" t="inlineStr">
@@ -28634,7 +28713,7 @@
     <row r="1090">
       <c r="A1090" s="4" t="inlineStr">
         <is>
-          <t>7024767</t>
+          <t>7024768</t>
         </is>
       </c>
       <c r="B1090" s="5" t="inlineStr">
@@ -28654,12 +28733,12 @@
     <row r="1091">
       <c r="A1091" s="6" t="inlineStr">
         <is>
-          <t>7024768</t>
+          <t>7028545</t>
         </is>
       </c>
       <c r="B1091" t="inlineStr">
         <is>
-          <t>Interiörarmatur WLP Backlit</t>
+          <t>Interiörarmatur WLP Backlit PIR</t>
         </is>
       </c>
       <c r="C1091" t="inlineStr">
@@ -28674,12 +28753,12 @@
     <row r="1092">
       <c r="A1092" s="4" t="inlineStr">
         <is>
-          <t>7028545</t>
+          <t>7024616</t>
         </is>
       </c>
       <c r="B1092" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur WLP Backlit PIR</t>
+          <t>Interiörarmatur WLP Backlit, ActiveAhead</t>
         </is>
       </c>
       <c r="C1092" s="5" t="inlineStr">
@@ -28694,7 +28773,7 @@
     <row r="1093">
       <c r="A1093" s="6" t="inlineStr">
         <is>
-          <t>7024616</t>
+          <t>7024617</t>
         </is>
       </c>
       <c r="B1093" t="inlineStr">
@@ -28714,7 +28793,7 @@
     <row r="1094">
       <c r="A1094" s="4" t="inlineStr">
         <is>
-          <t>7024617</t>
+          <t>7024816</t>
         </is>
       </c>
       <c r="B1094" s="5" t="inlineStr">
@@ -28734,7 +28813,7 @@
     <row r="1095">
       <c r="A1095" s="6" t="inlineStr">
         <is>
-          <t>7024816</t>
+          <t>7024817</t>
         </is>
       </c>
       <c r="B1095" t="inlineStr">
@@ -28754,12 +28833,12 @@
     <row r="1096">
       <c r="A1096" s="4" t="inlineStr">
         <is>
-          <t>7024817</t>
+          <t>7026165</t>
         </is>
       </c>
       <c r="B1096" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur WLP Backlit, ActiveAhead</t>
+          <t>Interiörarmatur WLP Cleanroom</t>
         </is>
       </c>
       <c r="C1096" s="5" t="inlineStr">
@@ -28774,7 +28853,7 @@
     <row r="1097">
       <c r="A1097" s="6" t="inlineStr">
         <is>
-          <t>7026165</t>
+          <t>7026166</t>
         </is>
       </c>
       <c r="B1097" t="inlineStr">
@@ -28794,12 +28873,12 @@
     <row r="1098">
       <c r="A1098" s="4" t="inlineStr">
         <is>
-          <t>7026166</t>
+          <t>7027313</t>
         </is>
       </c>
       <c r="B1098" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur WLP Cleanroom</t>
+          <t>Interiörarmatur WLP-B</t>
         </is>
       </c>
       <c r="C1098" s="5" t="inlineStr">
@@ -28814,12 +28893,12 @@
     <row r="1099">
       <c r="A1099" s="6" t="inlineStr">
         <is>
-          <t>7027313</t>
+          <t>7510127</t>
         </is>
       </c>
       <c r="B1099" t="inlineStr">
         <is>
-          <t>Interiörarmatur WLP-B</t>
+          <t>Takarmatur Mira 1x7 infälld</t>
         </is>
       </c>
       <c r="C1099" t="inlineStr">
@@ -28834,7 +28913,7 @@
     <row r="1100">
       <c r="A1100" s="4" t="inlineStr">
         <is>
-          <t>7510127</t>
+          <t>7510128</t>
         </is>
       </c>
       <c r="B1100" s="5" t="inlineStr">
@@ -28854,7 +28933,7 @@
     <row r="1101">
       <c r="A1101" s="6" t="inlineStr">
         <is>
-          <t>7510128</t>
+          <t>7510129</t>
         </is>
       </c>
       <c r="B1101" t="inlineStr">
@@ -28874,7 +28953,7 @@
     <row r="1102">
       <c r="A1102" s="4" t="inlineStr">
         <is>
-          <t>7510129</t>
+          <t>7510130</t>
         </is>
       </c>
       <c r="B1102" s="5" t="inlineStr">
@@ -28894,7 +28973,7 @@
     <row r="1103">
       <c r="A1103" s="6" t="inlineStr">
         <is>
-          <t>7510130</t>
+          <t>7510131</t>
         </is>
       </c>
       <c r="B1103" t="inlineStr">
@@ -28914,7 +28993,7 @@
     <row r="1104">
       <c r="A1104" s="4" t="inlineStr">
         <is>
-          <t>7510131</t>
+          <t>7510132</t>
         </is>
       </c>
       <c r="B1104" s="5" t="inlineStr">
@@ -28934,7 +29013,7 @@
     <row r="1105">
       <c r="A1105" s="6" t="inlineStr">
         <is>
-          <t>7510132</t>
+          <t>7510139</t>
         </is>
       </c>
       <c r="B1105" t="inlineStr">
@@ -28954,7 +29033,7 @@
     <row r="1106">
       <c r="A1106" s="4" t="inlineStr">
         <is>
-          <t>7510139</t>
+          <t>7510140</t>
         </is>
       </c>
       <c r="B1106" s="5" t="inlineStr">
@@ -28974,7 +29053,7 @@
     <row r="1107">
       <c r="A1107" s="6" t="inlineStr">
         <is>
-          <t>7510140</t>
+          <t>7510141</t>
         </is>
       </c>
       <c r="B1107" t="inlineStr">
@@ -28994,7 +29073,7 @@
     <row r="1108">
       <c r="A1108" s="4" t="inlineStr">
         <is>
-          <t>7510141</t>
+          <t>7510142</t>
         </is>
       </c>
       <c r="B1108" s="5" t="inlineStr">
@@ -29014,7 +29093,7 @@
     <row r="1109">
       <c r="A1109" s="6" t="inlineStr">
         <is>
-          <t>7510142</t>
+          <t>7510143</t>
         </is>
       </c>
       <c r="B1109" t="inlineStr">
@@ -29034,7 +29113,7 @@
     <row r="1110">
       <c r="A1110" s="4" t="inlineStr">
         <is>
-          <t>7510143</t>
+          <t>7510144</t>
         </is>
       </c>
       <c r="B1110" s="5" t="inlineStr">
@@ -29054,12 +29133,12 @@
     <row r="1111">
       <c r="A1111" s="6" t="inlineStr">
         <is>
-          <t>7510144</t>
+          <t>7510073</t>
         </is>
       </c>
       <c r="B1111" t="inlineStr">
         <is>
-          <t>Takarmatur Mira 1x7 infälld</t>
+          <t>Takarmatur Mira 2x2 infälld</t>
         </is>
       </c>
       <c r="C1111" t="inlineStr">
@@ -29074,7 +29153,7 @@
     <row r="1112">
       <c r="A1112" s="4" t="inlineStr">
         <is>
-          <t>7510073</t>
+          <t>7510075</t>
         </is>
       </c>
       <c r="B1112" s="5" t="inlineStr">
@@ -29094,7 +29173,7 @@
     <row r="1113">
       <c r="A1113" s="6" t="inlineStr">
         <is>
-          <t>7510075</t>
+          <t>7510077</t>
         </is>
       </c>
       <c r="B1113" t="inlineStr">
@@ -29114,7 +29193,7 @@
     <row r="1114">
       <c r="A1114" s="4" t="inlineStr">
         <is>
-          <t>7510077</t>
+          <t>7510079</t>
         </is>
       </c>
       <c r="B1114" s="5" t="inlineStr">
@@ -29134,7 +29213,7 @@
     <row r="1115">
       <c r="A1115" s="6" t="inlineStr">
         <is>
-          <t>7510079</t>
+          <t>7510081</t>
         </is>
       </c>
       <c r="B1115" t="inlineStr">
@@ -29154,7 +29233,7 @@
     <row r="1116">
       <c r="A1116" s="4" t="inlineStr">
         <is>
-          <t>7510081</t>
+          <t>7510083</t>
         </is>
       </c>
       <c r="B1116" s="5" t="inlineStr">
@@ -29174,7 +29253,7 @@
     <row r="1117">
       <c r="A1117" s="6" t="inlineStr">
         <is>
-          <t>7510083</t>
+          <t>7510085</t>
         </is>
       </c>
       <c r="B1117" t="inlineStr">
@@ -29194,7 +29273,7 @@
     <row r="1118">
       <c r="A1118" s="4" t="inlineStr">
         <is>
-          <t>7510085</t>
+          <t>7510087</t>
         </is>
       </c>
       <c r="B1118" s="5" t="inlineStr">
@@ -29214,7 +29293,7 @@
     <row r="1119">
       <c r="A1119" s="6" t="inlineStr">
         <is>
-          <t>7510087</t>
+          <t>7510112</t>
         </is>
       </c>
       <c r="B1119" t="inlineStr">
@@ -29234,7 +29313,7 @@
     <row r="1120">
       <c r="A1120" s="4" t="inlineStr">
         <is>
-          <t>7510112</t>
+          <t>7510114</t>
         </is>
       </c>
       <c r="B1120" s="5" t="inlineStr">
@@ -29254,7 +29333,7 @@
     <row r="1121">
       <c r="A1121" s="6" t="inlineStr">
         <is>
-          <t>7510114</t>
+          <t>7510115</t>
         </is>
       </c>
       <c r="B1121" t="inlineStr">
@@ -29274,7 +29353,7 @@
     <row r="1122">
       <c r="A1122" s="4" t="inlineStr">
         <is>
-          <t>7510115</t>
+          <t>7510116</t>
         </is>
       </c>
       <c r="B1122" s="5" t="inlineStr">
@@ -29294,7 +29373,7 @@
     <row r="1123">
       <c r="A1123" s="6" t="inlineStr">
         <is>
-          <t>7510116</t>
+          <t>7510117</t>
         </is>
       </c>
       <c r="B1123" t="inlineStr">
@@ -29314,7 +29393,7 @@
     <row r="1124">
       <c r="A1124" s="4" t="inlineStr">
         <is>
-          <t>7510117</t>
+          <t>7510118</t>
         </is>
       </c>
       <c r="B1124" s="5" t="inlineStr">
@@ -29334,7 +29413,7 @@
     <row r="1125">
       <c r="A1125" s="6" t="inlineStr">
         <is>
-          <t>7510118</t>
+          <t>7510119</t>
         </is>
       </c>
       <c r="B1125" t="inlineStr">
@@ -29354,7 +29433,7 @@
     <row r="1126">
       <c r="A1126" s="4" t="inlineStr">
         <is>
-          <t>7510119</t>
+          <t>7510120</t>
         </is>
       </c>
       <c r="B1126" s="5" t="inlineStr">
@@ -29374,17 +29453,17 @@
     <row r="1127">
       <c r="A1127" s="6" t="inlineStr">
         <is>
-          <t>7510120</t>
+          <t>7028323</t>
         </is>
       </c>
       <c r="B1127" t="inlineStr">
         <is>
-          <t>Takarmatur Mira 2x2 infälld</t>
+          <t>Interiörarmatur Beta Force</t>
         </is>
       </c>
       <c r="C1127" t="inlineStr">
         <is>
-          <t>Westal</t>
+          <t>ZG Lighting</t>
         </is>
       </c>
       <c r="D1127" s="6" t="n">
@@ -29394,7 +29473,7 @@
     <row r="1128">
       <c r="A1128" s="4" t="inlineStr">
         <is>
-          <t>7028323</t>
+          <t>7028324</t>
         </is>
       </c>
       <c r="B1128" s="5" t="inlineStr">
@@ -29414,12 +29493,12 @@
     <row r="1129">
       <c r="A1129" s="6" t="inlineStr">
         <is>
-          <t>7028324</t>
+          <t>7028311</t>
         </is>
       </c>
       <c r="B1129" t="inlineStr">
         <is>
-          <t>Interiörarmatur Beta Force</t>
+          <t>Interiörarmatur Maya</t>
         </is>
       </c>
       <c r="C1129" t="inlineStr">
@@ -29434,32 +29513,32 @@
     <row r="1130">
       <c r="A1130" s="4" t="inlineStr">
         <is>
-          <t>7028311</t>
+          <t>7013475</t>
         </is>
       </c>
       <c r="B1130" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Maya</t>
+          <t>Infälld interiörarmatur aLight Office LED</t>
         </is>
       </c>
       <c r="C1130" s="5" t="inlineStr">
         <is>
-          <t>ZG Lighting</t>
+          <t>a-collection</t>
         </is>
       </c>
       <c r="D1130" s="4" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1131">
       <c r="A1131" s="6" t="inlineStr">
         <is>
-          <t>7013475</t>
+          <t>7021097</t>
         </is>
       </c>
       <c r="B1131" t="inlineStr">
         <is>
-          <t>Infälld interiörarmatur aLight Office LED</t>
+          <t>Infälld interiörarmatur aLight Office LED Tec rektangulär</t>
         </is>
       </c>
       <c r="C1131" t="inlineStr">
@@ -29468,18 +29547,18 @@
         </is>
       </c>
       <c r="D1131" s="6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1132">
       <c r="A1132" s="4" t="inlineStr">
         <is>
-          <t>7021097</t>
+          <t>7018286</t>
         </is>
       </c>
       <c r="B1132" s="5" t="inlineStr">
         <is>
-          <t>Infälld interiörarmatur aLight Office LED Tec rektangulär</t>
+          <t>Infälld interiörarmatur aLight Office aPerture</t>
         </is>
       </c>
       <c r="C1132" s="5" t="inlineStr">
@@ -29488,18 +29567,18 @@
         </is>
       </c>
       <c r="D1132" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1133">
       <c r="A1133" s="6" t="inlineStr">
         <is>
-          <t>7018286</t>
+          <t>7028368</t>
         </is>
       </c>
       <c r="B1133" t="inlineStr">
         <is>
-          <t>Infälld interiörarmatur aLight Office aPerture</t>
+          <t>LED-Panel Flex</t>
         </is>
       </c>
       <c r="C1133" t="inlineStr">
@@ -29508,13 +29587,13 @@
         </is>
       </c>
       <c r="D1133" s="6" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
     </row>
     <row r="1134">
       <c r="A1134" s="4" t="inlineStr">
         <is>
-          <t>7028368</t>
+          <t>7028369</t>
         </is>
       </c>
       <c r="B1134" s="5" t="inlineStr">
@@ -29528,18 +29607,18 @@
         </is>
       </c>
       <c r="D1134" s="4" t="n">
-        <v>37</v>
+        <v>42</v>
       </c>
     </row>
     <row r="1135">
       <c r="A1135" s="6" t="inlineStr">
         <is>
-          <t>7028369</t>
+          <t>7028001</t>
         </is>
       </c>
       <c r="B1135" t="inlineStr">
         <is>
-          <t>LED-Panel Flex</t>
+          <t>LED-Panel aLight Office Rektangulär</t>
         </is>
       </c>
       <c r="C1135" t="inlineStr">
@@ -29548,13 +29627,13 @@
         </is>
       </c>
       <c r="D1135" s="6" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1136">
       <c r="A1136" s="4" t="inlineStr">
         <is>
-          <t>7028001</t>
+          <t>7028002</t>
         </is>
       </c>
       <c r="B1136" s="5" t="inlineStr">
@@ -29574,12 +29653,12 @@
     <row r="1137">
       <c r="A1137" s="6" t="inlineStr">
         <is>
-          <t>7028002</t>
+          <t>7027999</t>
         </is>
       </c>
       <c r="B1137" t="inlineStr">
         <is>
-          <t>LED-Panel aLight Office Rektangulär</t>
+          <t>LED-panel aLight Office</t>
         </is>
       </c>
       <c r="C1137" t="inlineStr">
@@ -29588,13 +29667,13 @@
         </is>
       </c>
       <c r="D1137" s="6" t="n">
-        <v>0</v>
+        <v>468</v>
       </c>
     </row>
     <row r="1138">
       <c r="A1138" s="4" t="inlineStr">
         <is>
-          <t>7027999</t>
+          <t>7028000</t>
         </is>
       </c>
       <c r="B1138" s="5" t="inlineStr">
@@ -29608,27 +29687,7 @@
         </is>
       </c>
       <c r="D1138" s="4" t="n">
-        <v>460</v>
-      </c>
-    </row>
-    <row r="1139">
-      <c r="A1139" s="6" t="inlineStr">
-        <is>
-          <t>7028000</t>
-        </is>
-      </c>
-      <c r="B1139" t="inlineStr">
-        <is>
-          <t>LED-panel aLight Office</t>
-        </is>
-      </c>
-      <c r="C1139" t="inlineStr">
-        <is>
-          <t>a-collection</t>
-        </is>
-      </c>
-      <c r="D1139" s="6" t="n">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
   </sheetData>

--- a/data/ahlsell_led_panel_inventory.xlsx
+++ b/data/ahlsell_led_panel_inventory.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y81"/>
+  <dimension ref="A1:Y82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -503,14 +503,14 @@
       </c>
       <c r="D1" s="3" t="inlineStr">
         <is>
+          <t>Tupex</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
           <t>SG Armaturen</t>
         </is>
       </c>
-      <c r="E1" s="3" t="inlineStr">
-        <is>
-          <t>Tupex</t>
-        </is>
-      </c>
       <c r="F1" s="3" t="inlineStr">
         <is>
           <t>Hide-a-lite</t>
@@ -533,82 +533,82 @@
       </c>
       <c r="J1" s="3" t="inlineStr">
         <is>
+          <t>Ledvance</t>
+        </is>
+      </c>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Ensto</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="inlineStr">
+        <is>
+          <t>ANETA LIGHTING</t>
+        </is>
+      </c>
+      <c r="M1" s="3" t="inlineStr">
+        <is>
           <t>Esylux</t>
         </is>
       </c>
-      <c r="K1" s="3" t="inlineStr">
-        <is>
-          <t>Ledvance</t>
-        </is>
-      </c>
-      <c r="L1" s="3" t="inlineStr">
+      <c r="N1" s="3" t="inlineStr">
+        <is>
+          <t>Bergdahls</t>
+        </is>
+      </c>
+      <c r="O1" s="3" t="inlineStr">
+        <is>
+          <t>Philips</t>
+        </is>
+      </c>
+      <c r="P1" s="3" t="inlineStr">
+        <is>
+          <t>Siteco</t>
+        </is>
+      </c>
+      <c r="Q1" s="3" t="inlineStr">
+        <is>
+          <t>Black Box</t>
+        </is>
+      </c>
+      <c r="R1" s="3" t="inlineStr">
+        <is>
+          <t>Easyform</t>
+        </is>
+      </c>
+      <c r="S1" s="3" t="inlineStr">
+        <is>
+          <t>Norwesco</t>
+        </is>
+      </c>
+      <c r="T1" s="3" t="inlineStr">
+        <is>
+          <t>Legrand</t>
+        </is>
+      </c>
+      <c r="U1" s="3" t="inlineStr">
+        <is>
+          <t>THORN</t>
+        </is>
+      </c>
+      <c r="V1" s="3" t="inlineStr">
         <is>
           <t>Airam</t>
         </is>
       </c>
-      <c r="M1" s="3" t="inlineStr">
+      <c r="W1" s="3" t="inlineStr">
         <is>
           <t>Nokalux</t>
         </is>
       </c>
-      <c r="N1" s="3" t="inlineStr">
-        <is>
-          <t>Ensto</t>
-        </is>
-      </c>
-      <c r="O1" s="3" t="inlineStr">
-        <is>
-          <t>Siteco</t>
-        </is>
-      </c>
-      <c r="P1" s="3" t="inlineStr">
-        <is>
-          <t>Black Box</t>
-        </is>
-      </c>
-      <c r="Q1" s="3" t="inlineStr">
-        <is>
-          <t>ANETA LIGHTING</t>
-        </is>
-      </c>
-      <c r="R1" s="3" t="inlineStr">
-        <is>
-          <t>Easyform</t>
-        </is>
-      </c>
-      <c r="S1" s="3" t="inlineStr">
-        <is>
-          <t>Bergdahls</t>
-        </is>
-      </c>
-      <c r="T1" s="3" t="inlineStr">
+      <c r="X1" s="3" t="inlineStr">
         <is>
           <t>Westal</t>
         </is>
       </c>
-      <c r="U1" s="3" t="inlineStr">
-        <is>
-          <t>Norwesco</t>
-        </is>
-      </c>
-      <c r="V1" s="3" t="inlineStr">
-        <is>
-          <t>THORN</t>
-        </is>
-      </c>
-      <c r="W1" s="3" t="inlineStr">
-        <is>
-          <t>Philips</t>
-        </is>
-      </c>
-      <c r="X1" s="3" t="inlineStr">
+      <c r="Y1" s="3" t="inlineStr">
         <is>
           <t>ZG Lighting</t>
-        </is>
-      </c>
-      <c r="Y1" s="3" t="inlineStr">
-        <is>
-          <t>Legrand</t>
         </is>
       </c>
     </row>
@@ -625,10 +625,10 @@
         <v>527</v>
       </c>
       <c r="D2" s="5" t="n">
+        <v>233</v>
+      </c>
+      <c r="E2" s="5" t="n">
         <v>1402</v>
-      </c>
-      <c r="E2" s="5" t="n">
-        <v>233</v>
       </c>
       <c r="F2" s="5" t="n">
         <v>223</v>
@@ -643,16 +643,16 @@
         <v>33</v>
       </c>
       <c r="J2" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="K2" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" s="5" t="n">
         <v>25</v>
-      </c>
-      <c r="K2" s="5" t="n">
-        <v>17</v>
-      </c>
-      <c r="L2" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M2" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="N2" s="5" t="n">
         <v>0</v>
@@ -704,10 +704,10 @@
         <v>527</v>
       </c>
       <c r="D3" t="n">
+        <v>233</v>
+      </c>
+      <c r="E3" t="n">
         <v>1402</v>
-      </c>
-      <c r="E3" t="n">
-        <v>233</v>
       </c>
       <c r="F3" t="n">
         <v>223</v>
@@ -722,16 +722,16 @@
         <v>33</v>
       </c>
       <c r="J3" t="n">
+        <v>17</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
         <v>25</v>
-      </c>
-      <c r="K3" t="n">
-        <v>17</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0</v>
       </c>
       <c r="N3" t="n">
         <v>0</v>
@@ -783,10 +783,10 @@
         <v>523</v>
       </c>
       <c r="D4" s="5" t="n">
+        <v>233</v>
+      </c>
+      <c r="E4" s="5" t="n">
         <v>1391</v>
-      </c>
-      <c r="E4" s="5" t="n">
-        <v>233</v>
       </c>
       <c r="F4" s="5" t="n">
         <v>217</v>
@@ -801,16 +801,16 @@
         <v>33</v>
       </c>
       <c r="J4" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="K4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" s="5" t="n">
         <v>25</v>
-      </c>
-      <c r="K4" s="5" t="n">
-        <v>17</v>
-      </c>
-      <c r="L4" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M4" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="N4" s="5" t="n">
         <v>0</v>
@@ -862,10 +862,10 @@
         <v>522</v>
       </c>
       <c r="D5" t="n">
+        <v>233</v>
+      </c>
+      <c r="E5" t="n">
         <v>1384</v>
-      </c>
-      <c r="E5" t="n">
-        <v>233</v>
       </c>
       <c r="F5" t="n">
         <v>221</v>
@@ -880,16 +880,16 @@
         <v>33</v>
       </c>
       <c r="J5" t="n">
+        <v>17</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
         <v>24</v>
-      </c>
-      <c r="K5" t="n">
-        <v>17</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
@@ -941,10 +941,10 @@
         <v>528</v>
       </c>
       <c r="D6" s="5" t="n">
+        <v>232</v>
+      </c>
+      <c r="E6" s="5" t="n">
         <v>1377</v>
-      </c>
-      <c r="E6" s="5" t="n">
-        <v>232</v>
       </c>
       <c r="F6" s="5" t="n">
         <v>215</v>
@@ -959,16 +959,16 @@
         <v>33</v>
       </c>
       <c r="J6" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="K6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="K6" s="5" t="n">
-        <v>17</v>
-      </c>
-      <c r="L6" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="N6" s="5" t="n">
         <v>0</v>
@@ -1017,10 +1017,10 @@
         <v>920</v>
       </c>
       <c r="D7" t="n">
+        <v>232</v>
+      </c>
+      <c r="E7" t="n">
         <v>1348</v>
-      </c>
-      <c r="E7" t="n">
-        <v>232</v>
       </c>
       <c r="F7" t="n">
         <v>215</v>
@@ -1035,16 +1035,16 @@
         <v>33</v>
       </c>
       <c r="J7" t="n">
+        <v>17</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
         <v>24</v>
-      </c>
-      <c r="K7" t="n">
-        <v>17</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
@@ -1096,10 +1096,10 @@
         <v>528</v>
       </c>
       <c r="D8" s="5" t="n">
+        <v>232</v>
+      </c>
+      <c r="E8" s="5" t="n">
         <v>1377</v>
-      </c>
-      <c r="E8" s="5" t="n">
-        <v>232</v>
       </c>
       <c r="F8" s="5" t="n">
         <v>215</v>
@@ -1114,16 +1114,16 @@
         <v>33</v>
       </c>
       <c r="J8" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="K8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="K8" s="5" t="n">
-        <v>17</v>
-      </c>
-      <c r="L8" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="N8" s="5" t="n">
         <v>0</v>
@@ -1175,10 +1175,10 @@
         <v>532</v>
       </c>
       <c r="D9" t="n">
+        <v>232</v>
+      </c>
+      <c r="E9" t="n">
         <v>1385</v>
-      </c>
-      <c r="E9" t="n">
-        <v>232</v>
       </c>
       <c r="F9" t="n">
         <v>214</v>
@@ -1193,16 +1193,16 @@
         <v>33</v>
       </c>
       <c r="J9" t="n">
+        <v>17</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
         <v>24</v>
-      </c>
-      <c r="K9" t="n">
-        <v>17</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
@@ -1254,10 +1254,10 @@
         <v>544</v>
       </c>
       <c r="D10" s="5" t="n">
+        <v>231</v>
+      </c>
+      <c r="E10" s="5" t="n">
         <v>1381</v>
-      </c>
-      <c r="E10" s="5" t="n">
-        <v>231</v>
       </c>
       <c r="F10" s="5" t="n">
         <v>218</v>
@@ -1272,16 +1272,16 @@
         <v>33</v>
       </c>
       <c r="J10" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="K10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="K10" s="5" t="n">
-        <v>17</v>
-      </c>
-      <c r="L10" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="N10" s="5" t="n">
         <v>0</v>
@@ -1333,10 +1333,10 @@
         <v>544</v>
       </c>
       <c r="D11" t="n">
+        <v>231</v>
+      </c>
+      <c r="E11" t="n">
         <v>1385</v>
-      </c>
-      <c r="E11" t="n">
-        <v>231</v>
       </c>
       <c r="F11" t="n">
         <v>225</v>
@@ -1351,16 +1351,16 @@
         <v>33</v>
       </c>
       <c r="J11" t="n">
+        <v>17</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
         <v>24</v>
-      </c>
-      <c r="K11" t="n">
-        <v>17</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
@@ -1412,10 +1412,10 @@
         <v>544</v>
       </c>
       <c r="D12" s="5" t="n">
+        <v>224</v>
+      </c>
+      <c r="E12" s="5" t="n">
         <v>1372</v>
-      </c>
-      <c r="E12" s="5" t="n">
-        <v>224</v>
       </c>
       <c r="F12" s="5" t="n">
         <v>228</v>
@@ -1430,16 +1430,16 @@
         <v>33</v>
       </c>
       <c r="J12" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="K12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="K12" s="5" t="n">
-        <v>17</v>
-      </c>
-      <c r="L12" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="N12" s="5" t="n">
         <v>0</v>
@@ -1491,10 +1491,10 @@
         <v>545</v>
       </c>
       <c r="D13" t="n">
+        <v>224</v>
+      </c>
+      <c r="E13" t="n">
         <v>1360</v>
-      </c>
-      <c r="E13" t="n">
-        <v>224</v>
       </c>
       <c r="F13" t="n">
         <v>228</v>
@@ -1509,16 +1509,16 @@
         <v>33</v>
       </c>
       <c r="J13" t="n">
+        <v>17</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
         <v>24</v>
-      </c>
-      <c r="K13" t="n">
-        <v>17</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -1570,10 +1570,10 @@
         <v>545</v>
       </c>
       <c r="D14" s="5" t="n">
+        <v>224</v>
+      </c>
+      <c r="E14" s="5" t="n">
         <v>1331</v>
-      </c>
-      <c r="E14" s="5" t="n">
-        <v>224</v>
       </c>
       <c r="F14" s="5" t="n">
         <v>228</v>
@@ -1588,16 +1588,16 @@
         <v>33</v>
       </c>
       <c r="J14" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="K14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="K14" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="L14" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="N14" s="5" t="n">
         <v>0</v>
@@ -1649,10 +1649,10 @@
         <v>545</v>
       </c>
       <c r="D15" t="n">
+        <v>224</v>
+      </c>
+      <c r="E15" t="n">
         <v>1360</v>
-      </c>
-      <c r="E15" t="n">
-        <v>224</v>
       </c>
       <c r="F15" t="n">
         <v>228</v>
@@ -1667,16 +1667,16 @@
         <v>33</v>
       </c>
       <c r="J15" t="n">
+        <v>17</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
         <v>24</v>
-      </c>
-      <c r="K15" t="n">
-        <v>17</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -1728,10 +1728,10 @@
         <v>545</v>
       </c>
       <c r="D16" s="5" t="n">
+        <v>224</v>
+      </c>
+      <c r="E16" s="5" t="n">
         <v>1348</v>
-      </c>
-      <c r="E16" s="5" t="n">
-        <v>224</v>
       </c>
       <c r="F16" s="5" t="n">
         <v>226</v>
@@ -1746,16 +1746,16 @@
         <v>33</v>
       </c>
       <c r="J16" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="K16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="K16" s="5" t="n">
-        <v>17</v>
-      </c>
-      <c r="L16" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="N16" s="5" t="n">
         <v>0</v>
@@ -1807,10 +1807,10 @@
         <v>572</v>
       </c>
       <c r="D17" t="n">
+        <v>224</v>
+      </c>
+      <c r="E17" t="n">
         <v>1347</v>
-      </c>
-      <c r="E17" t="n">
-        <v>224</v>
       </c>
       <c r="F17" t="n">
         <v>228</v>
@@ -1825,16 +1825,16 @@
         <v>33</v>
       </c>
       <c r="J17" t="n">
+        <v>17</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
         <v>24</v>
-      </c>
-      <c r="K17" t="n">
-        <v>17</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
@@ -1886,10 +1886,10 @@
         <v>571</v>
       </c>
       <c r="D18" s="5" t="n">
+        <v>224</v>
+      </c>
+      <c r="E18" s="5" t="n">
         <v>1343</v>
-      </c>
-      <c r="E18" s="5" t="n">
-        <v>224</v>
       </c>
       <c r="F18" s="5" t="n">
         <v>233</v>
@@ -1904,16 +1904,16 @@
         <v>33</v>
       </c>
       <c r="J18" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="K18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="K18" s="5" t="n">
-        <v>17</v>
-      </c>
-      <c r="L18" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="N18" s="5" t="n">
         <v>0</v>
@@ -1965,10 +1965,10 @@
         <v>565</v>
       </c>
       <c r="D19" t="n">
+        <v>224</v>
+      </c>
+      <c r="E19" t="n">
         <v>1341</v>
-      </c>
-      <c r="E19" t="n">
-        <v>224</v>
       </c>
       <c r="F19" t="n">
         <v>233</v>
@@ -1983,16 +1983,16 @@
         <v>33</v>
       </c>
       <c r="J19" t="n">
+        <v>17</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
         <v>24</v>
-      </c>
-      <c r="K19" t="n">
-        <v>17</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0</v>
       </c>
       <c r="N19" t="n">
         <v>0</v>
@@ -2044,10 +2044,10 @@
         <v>565</v>
       </c>
       <c r="D20" s="5" t="n">
+        <v>224</v>
+      </c>
+      <c r="E20" s="5" t="n">
         <v>1340</v>
-      </c>
-      <c r="E20" s="5" t="n">
-        <v>224</v>
       </c>
       <c r="F20" s="5" t="n">
         <v>232</v>
@@ -2062,16 +2062,16 @@
         <v>33</v>
       </c>
       <c r="J20" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="K20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="K20" s="5" t="n">
-        <v>17</v>
-      </c>
-      <c r="L20" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M20" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="N20" s="5" t="n">
         <v>0</v>
@@ -2123,10 +2123,10 @@
         <v>565</v>
       </c>
       <c r="D21" t="n">
+        <v>224</v>
+      </c>
+      <c r="E21" t="n">
         <v>1340</v>
-      </c>
-      <c r="E21" t="n">
-        <v>224</v>
       </c>
       <c r="F21" t="n">
         <v>232</v>
@@ -2141,16 +2141,16 @@
         <v>33</v>
       </c>
       <c r="J21" t="n">
+        <v>17</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
         <v>24</v>
-      </c>
-      <c r="K21" t="n">
-        <v>17</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0</v>
       </c>
       <c r="N21" t="n">
         <v>0</v>
@@ -2202,10 +2202,10 @@
         <v>565</v>
       </c>
       <c r="D22" s="5" t="n">
+        <v>224</v>
+      </c>
+      <c r="E22" s="5" t="n">
         <v>1340</v>
-      </c>
-      <c r="E22" s="5" t="n">
-        <v>224</v>
       </c>
       <c r="F22" s="5" t="n">
         <v>232</v>
@@ -2220,16 +2220,16 @@
         <v>33</v>
       </c>
       <c r="J22" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="K22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="K22" s="5" t="n">
-        <v>17</v>
-      </c>
-      <c r="L22" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M22" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="N22" s="5" t="n">
         <v>0</v>
@@ -2281,10 +2281,10 @@
         <v>565</v>
       </c>
       <c r="D23" t="n">
+        <v>221</v>
+      </c>
+      <c r="E23" t="n">
         <v>1344</v>
-      </c>
-      <c r="E23" t="n">
-        <v>221</v>
       </c>
       <c r="F23" t="n">
         <v>229</v>
@@ -2299,16 +2299,16 @@
         <v>33</v>
       </c>
       <c r="J23" t="n">
+        <v>17</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
         <v>24</v>
-      </c>
-      <c r="K23" t="n">
-        <v>17</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
-      <c r="M23" t="n">
-        <v>0</v>
       </c>
       <c r="N23" t="n">
         <v>0</v>
@@ -2360,10 +2360,10 @@
         <v>565</v>
       </c>
       <c r="D24" s="5" t="n">
+        <v>220</v>
+      </c>
+      <c r="E24" s="5" t="n">
         <v>1328</v>
-      </c>
-      <c r="E24" s="5" t="n">
-        <v>220</v>
       </c>
       <c r="F24" s="5" t="n">
         <v>228</v>
@@ -2378,16 +2378,16 @@
         <v>33</v>
       </c>
       <c r="J24" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="K24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="K24" s="5" t="n">
-        <v>17</v>
-      </c>
-      <c r="L24" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M24" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="N24" s="5" t="n">
         <v>0</v>
@@ -2439,10 +2439,10 @@
         <v>565</v>
       </c>
       <c r="D25" t="n">
+        <v>219</v>
+      </c>
+      <c r="E25" t="n">
         <v>1316</v>
-      </c>
-      <c r="E25" t="n">
-        <v>219</v>
       </c>
       <c r="F25" t="n">
         <v>228</v>
@@ -2457,16 +2457,16 @@
         <v>33</v>
       </c>
       <c r="J25" t="n">
+        <v>17</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" t="n">
         <v>24</v>
-      </c>
-      <c r="K25" t="n">
-        <v>17</v>
-      </c>
-      <c r="L25" t="n">
-        <v>0</v>
-      </c>
-      <c r="M25" t="n">
-        <v>0</v>
       </c>
       <c r="N25" t="n">
         <v>0</v>
@@ -2518,10 +2518,10 @@
         <v>565</v>
       </c>
       <c r="D26" s="5" t="n">
+        <v>217</v>
+      </c>
+      <c r="E26" s="5" t="n">
         <v>1322</v>
-      </c>
-      <c r="E26" s="5" t="n">
-        <v>217</v>
       </c>
       <c r="F26" s="5" t="n">
         <v>230</v>
@@ -2536,16 +2536,16 @@
         <v>33</v>
       </c>
       <c r="J26" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="K26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="K26" s="5" t="n">
-        <v>17</v>
-      </c>
-      <c r="L26" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M26" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="N26" s="5" t="n">
         <v>0</v>
@@ -2597,10 +2597,10 @@
         <v>565</v>
       </c>
       <c r="D27" t="n">
+        <v>217</v>
+      </c>
+      <c r="E27" t="n">
         <v>1322</v>
-      </c>
-      <c r="E27" t="n">
-        <v>217</v>
       </c>
       <c r="F27" t="n">
         <v>233</v>
@@ -2615,16 +2615,16 @@
         <v>33</v>
       </c>
       <c r="J27" t="n">
+        <v>17</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" t="n">
         <v>24</v>
-      </c>
-      <c r="K27" t="n">
-        <v>17</v>
-      </c>
-      <c r="L27" t="n">
-        <v>0</v>
-      </c>
-      <c r="M27" t="n">
-        <v>0</v>
       </c>
       <c r="N27" t="n">
         <v>0</v>
@@ -2676,10 +2676,10 @@
         <v>565</v>
       </c>
       <c r="D28" s="5" t="n">
+        <v>217</v>
+      </c>
+      <c r="E28" s="5" t="n">
         <v>1291</v>
-      </c>
-      <c r="E28" s="5" t="n">
-        <v>217</v>
       </c>
       <c r="F28" s="5" t="n">
         <v>233</v>
@@ -2694,10 +2694,10 @@
         <v>33</v>
       </c>
       <c r="J28" s="5" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="K28" s="5" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="L28" s="5" t="n">
         <v>0</v>
@@ -2755,10 +2755,10 @@
         <v>565</v>
       </c>
       <c r="D29" t="n">
+        <v>217</v>
+      </c>
+      <c r="E29" t="n">
         <v>1322</v>
-      </c>
-      <c r="E29" t="n">
-        <v>217</v>
       </c>
       <c r="F29" t="n">
         <v>233</v>
@@ -2773,16 +2773,16 @@
         <v>33</v>
       </c>
       <c r="J29" t="n">
+        <v>17</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" t="n">
         <v>24</v>
-      </c>
-      <c r="K29" t="n">
-        <v>17</v>
-      </c>
-      <c r="L29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M29" t="n">
-        <v>0</v>
       </c>
       <c r="N29" t="n">
         <v>0</v>
@@ -2834,10 +2834,10 @@
         <v>541</v>
       </c>
       <c r="D30" s="5" t="n">
+        <v>215</v>
+      </c>
+      <c r="E30" s="5" t="n">
         <v>1284</v>
-      </c>
-      <c r="E30" s="5" t="n">
-        <v>215</v>
       </c>
       <c r="F30" s="5" t="n">
         <v>208</v>
@@ -2852,16 +2852,16 @@
         <v>33</v>
       </c>
       <c r="J30" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="K30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="K30" s="5" t="n">
-        <v>17</v>
-      </c>
-      <c r="L30" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M30" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="N30" s="5" t="n">
         <v>0</v>
@@ -2913,10 +2913,10 @@
         <v>544</v>
       </c>
       <c r="D31" t="n">
+        <v>217</v>
+      </c>
+      <c r="E31" t="n">
         <v>1284</v>
-      </c>
-      <c r="E31" t="n">
-        <v>217</v>
       </c>
       <c r="F31" t="n">
         <v>208</v>
@@ -2931,16 +2931,16 @@
         <v>33</v>
       </c>
       <c r="J31" t="n">
+        <v>17</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" t="n">
         <v>24</v>
-      </c>
-      <c r="K31" t="n">
-        <v>17</v>
-      </c>
-      <c r="L31" t="n">
-        <v>0</v>
-      </c>
-      <c r="M31" t="n">
-        <v>0</v>
       </c>
       <c r="N31" t="n">
         <v>0</v>
@@ -2992,10 +2992,10 @@
         <v>556</v>
       </c>
       <c r="D32" s="5" t="n">
+        <v>217</v>
+      </c>
+      <c r="E32" s="5" t="n">
         <v>1286</v>
-      </c>
-      <c r="E32" s="5" t="n">
-        <v>217</v>
       </c>
       <c r="F32" s="5" t="n">
         <v>218</v>
@@ -3010,16 +3010,16 @@
         <v>33</v>
       </c>
       <c r="J32" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="K32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M32" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="K32" s="5" t="n">
-        <v>17</v>
-      </c>
-      <c r="L32" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M32" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="N32" s="5" t="n">
         <v>0</v>
@@ -3071,10 +3071,10 @@
         <v>564</v>
       </c>
       <c r="D33" t="n">
+        <v>216</v>
+      </c>
+      <c r="E33" t="n">
         <v>1286</v>
-      </c>
-      <c r="E33" t="n">
-        <v>216</v>
       </c>
       <c r="F33" t="n">
         <v>218</v>
@@ -3089,16 +3089,16 @@
         <v>33</v>
       </c>
       <c r="J33" t="n">
+        <v>17</v>
+      </c>
+      <c r="K33" t="n">
+        <v>0</v>
+      </c>
+      <c r="L33" t="n">
+        <v>0</v>
+      </c>
+      <c r="M33" t="n">
         <v>24</v>
-      </c>
-      <c r="K33" t="n">
-        <v>17</v>
-      </c>
-      <c r="L33" t="n">
-        <v>0</v>
-      </c>
-      <c r="M33" t="n">
-        <v>0</v>
       </c>
       <c r="N33" t="n">
         <v>0</v>
@@ -3150,10 +3150,10 @@
         <v>563</v>
       </c>
       <c r="D34" s="5" t="n">
+        <v>216</v>
+      </c>
+      <c r="E34" s="5" t="n">
         <v>1324</v>
-      </c>
-      <c r="E34" s="5" t="n">
-        <v>216</v>
       </c>
       <c r="F34" s="5" t="n">
         <v>218</v>
@@ -3168,16 +3168,16 @@
         <v>33</v>
       </c>
       <c r="J34" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="K34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="K34" s="5" t="n">
-        <v>17</v>
-      </c>
-      <c r="L34" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M34" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="N34" s="5" t="n">
         <v>0</v>
@@ -3229,10 +3229,10 @@
         <v>563</v>
       </c>
       <c r="D35" t="n">
+        <v>216</v>
+      </c>
+      <c r="E35" t="n">
         <v>1324</v>
-      </c>
-      <c r="E35" t="n">
-        <v>216</v>
       </c>
       <c r="F35" t="n">
         <v>218</v>
@@ -3247,16 +3247,16 @@
         <v>33</v>
       </c>
       <c r="J35" t="n">
+        <v>17</v>
+      </c>
+      <c r="K35" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" t="n">
+        <v>0</v>
+      </c>
+      <c r="M35" t="n">
         <v>24</v>
-      </c>
-      <c r="K35" t="n">
-        <v>17</v>
-      </c>
-      <c r="L35" t="n">
-        <v>0</v>
-      </c>
-      <c r="M35" t="n">
-        <v>0</v>
       </c>
       <c r="N35" t="n">
         <v>0</v>
@@ -3308,10 +3308,10 @@
         <v>563</v>
       </c>
       <c r="D36" s="5" t="n">
+        <v>216</v>
+      </c>
+      <c r="E36" s="5" t="n">
         <v>1324</v>
-      </c>
-      <c r="E36" s="5" t="n">
-        <v>216</v>
       </c>
       <c r="F36" s="5" t="n">
         <v>218</v>
@@ -3326,16 +3326,16 @@
         <v>33</v>
       </c>
       <c r="J36" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="K36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M36" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="K36" s="5" t="n">
-        <v>17</v>
-      </c>
-      <c r="L36" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M36" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="N36" s="5" t="n">
         <v>0</v>
@@ -3387,10 +3387,10 @@
         <v>563</v>
       </c>
       <c r="D37" t="n">
+        <v>212</v>
+      </c>
+      <c r="E37" t="n">
         <v>1306</v>
-      </c>
-      <c r="E37" t="n">
-        <v>212</v>
       </c>
       <c r="F37" t="n">
         <v>216</v>
@@ -3405,16 +3405,16 @@
         <v>33</v>
       </c>
       <c r="J37" t="n">
+        <v>17</v>
+      </c>
+      <c r="K37" t="n">
+        <v>0</v>
+      </c>
+      <c r="L37" t="n">
+        <v>0</v>
+      </c>
+      <c r="M37" t="n">
         <v>24</v>
-      </c>
-      <c r="K37" t="n">
-        <v>17</v>
-      </c>
-      <c r="L37" t="n">
-        <v>0</v>
-      </c>
-      <c r="M37" t="n">
-        <v>0</v>
       </c>
       <c r="N37" t="n">
         <v>0</v>
@@ -3466,10 +3466,10 @@
         <v>556</v>
       </c>
       <c r="D38" s="5" t="n">
+        <v>212</v>
+      </c>
+      <c r="E38" s="5" t="n">
         <v>1310</v>
-      </c>
-      <c r="E38" s="5" t="n">
-        <v>212</v>
       </c>
       <c r="F38" s="5" t="n">
         <v>207</v>
@@ -3484,16 +3484,16 @@
         <v>33</v>
       </c>
       <c r="J38" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="K38" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L38" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M38" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="K38" s="5" t="n">
-        <v>17</v>
-      </c>
-      <c r="L38" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M38" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="N38" s="5" t="n">
         <v>0</v>
@@ -3545,10 +3545,10 @@
         <v>562</v>
       </c>
       <c r="D39" t="n">
+        <v>214</v>
+      </c>
+      <c r="E39" t="n">
         <v>1305</v>
-      </c>
-      <c r="E39" t="n">
-        <v>214</v>
       </c>
       <c r="F39" t="n">
         <v>207</v>
@@ -3563,16 +3563,16 @@
         <v>33</v>
       </c>
       <c r="J39" t="n">
+        <v>17</v>
+      </c>
+      <c r="K39" t="n">
+        <v>0</v>
+      </c>
+      <c r="L39" t="n">
+        <v>0</v>
+      </c>
+      <c r="M39" t="n">
         <v>24</v>
-      </c>
-      <c r="K39" t="n">
-        <v>17</v>
-      </c>
-      <c r="L39" t="n">
-        <v>0</v>
-      </c>
-      <c r="M39" t="n">
-        <v>0</v>
       </c>
       <c r="N39" t="n">
         <v>0</v>
@@ -3624,10 +3624,10 @@
         <v>519</v>
       </c>
       <c r="D40" s="5" t="n">
+        <v>210</v>
+      </c>
+      <c r="E40" s="5" t="n">
         <v>1295</v>
-      </c>
-      <c r="E40" s="5" t="n">
-        <v>210</v>
       </c>
       <c r="F40" s="5" t="n">
         <v>226</v>
@@ -3642,16 +3642,16 @@
         <v>33</v>
       </c>
       <c r="J40" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="K40" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L40" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M40" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="K40" s="5" t="n">
-        <v>17</v>
-      </c>
-      <c r="L40" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M40" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="N40" s="5" t="n">
         <v>0</v>
@@ -3703,10 +3703,10 @@
         <v>517</v>
       </c>
       <c r="D41" t="n">
+        <v>210</v>
+      </c>
+      <c r="E41" t="n">
         <v>1285</v>
-      </c>
-      <c r="E41" t="n">
-        <v>210</v>
       </c>
       <c r="F41" t="n">
         <v>219</v>
@@ -3721,16 +3721,16 @@
         <v>33</v>
       </c>
       <c r="J41" t="n">
+        <v>17</v>
+      </c>
+      <c r="K41" t="n">
+        <v>0</v>
+      </c>
+      <c r="L41" t="n">
+        <v>0</v>
+      </c>
+      <c r="M41" t="n">
         <v>24</v>
-      </c>
-      <c r="K41" t="n">
-        <v>17</v>
-      </c>
-      <c r="L41" t="n">
-        <v>0</v>
-      </c>
-      <c r="M41" t="n">
-        <v>0</v>
       </c>
       <c r="N41" t="n">
         <v>0</v>
@@ -3782,10 +3782,10 @@
         <v>517</v>
       </c>
       <c r="D42" s="5" t="n">
+        <v>210</v>
+      </c>
+      <c r="E42" s="5" t="n">
         <v>1239</v>
-      </c>
-      <c r="E42" s="5" t="n">
-        <v>210</v>
       </c>
       <c r="F42" s="5" t="n">
         <v>219</v>
@@ -3800,16 +3800,16 @@
         <v>33</v>
       </c>
       <c r="J42" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="K42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M42" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="K42" s="5" t="n">
-        <v>17</v>
-      </c>
-      <c r="L42" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M42" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="N42" s="5" t="n">
         <v>0</v>
@@ -3861,10 +3861,10 @@
         <v>517</v>
       </c>
       <c r="D43" t="n">
+        <v>210</v>
+      </c>
+      <c r="E43" t="n">
         <v>1270</v>
-      </c>
-      <c r="E43" t="n">
-        <v>210</v>
       </c>
       <c r="F43" t="n">
         <v>219</v>
@@ -3879,16 +3879,16 @@
         <v>33</v>
       </c>
       <c r="J43" t="n">
+        <v>17</v>
+      </c>
+      <c r="K43" t="n">
+        <v>0</v>
+      </c>
+      <c r="L43" t="n">
+        <v>0</v>
+      </c>
+      <c r="M43" t="n">
         <v>24</v>
-      </c>
-      <c r="K43" t="n">
-        <v>17</v>
-      </c>
-      <c r="L43" t="n">
-        <v>0</v>
-      </c>
-      <c r="M43" t="n">
-        <v>0</v>
       </c>
       <c r="N43" t="n">
         <v>0</v>
@@ -3940,10 +3940,10 @@
         <v>531</v>
       </c>
       <c r="D44" s="5" t="n">
+        <v>208</v>
+      </c>
+      <c r="E44" s="5" t="n">
         <v>1255</v>
-      </c>
-      <c r="E44" s="5" t="n">
-        <v>208</v>
       </c>
       <c r="F44" s="5" t="n">
         <v>214</v>
@@ -3958,16 +3958,16 @@
         <v>33</v>
       </c>
       <c r="J44" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="K44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M44" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="K44" s="5" t="n">
-        <v>17</v>
-      </c>
-      <c r="L44" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M44" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="N44" s="5" t="n">
         <v>0</v>
@@ -4019,10 +4019,10 @@
         <v>548</v>
       </c>
       <c r="D45" t="n">
+        <v>208</v>
+      </c>
+      <c r="E45" t="n">
         <v>1254</v>
-      </c>
-      <c r="E45" t="n">
-        <v>208</v>
       </c>
       <c r="F45" t="n">
         <v>214</v>
@@ -4037,16 +4037,16 @@
         <v>33</v>
       </c>
       <c r="J45" t="n">
+        <v>17</v>
+      </c>
+      <c r="K45" t="n">
+        <v>0</v>
+      </c>
+      <c r="L45" t="n">
+        <v>0</v>
+      </c>
+      <c r="M45" t="n">
         <v>24</v>
-      </c>
-      <c r="K45" t="n">
-        <v>17</v>
-      </c>
-      <c r="L45" t="n">
-        <v>0</v>
-      </c>
-      <c r="M45" t="n">
-        <v>0</v>
       </c>
       <c r="N45" t="n">
         <v>0</v>
@@ -4098,10 +4098,10 @@
         <v>548</v>
       </c>
       <c r="D46" s="5" t="n">
+        <v>203</v>
+      </c>
+      <c r="E46" s="5" t="n">
         <v>1244</v>
-      </c>
-      <c r="E46" s="5" t="n">
-        <v>203</v>
       </c>
       <c r="F46" s="5" t="n">
         <v>218</v>
@@ -4116,16 +4116,16 @@
         <v>33</v>
       </c>
       <c r="J46" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="K46" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L46" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M46" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="K46" s="5" t="n">
-        <v>17</v>
-      </c>
-      <c r="L46" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M46" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="N46" s="5" t="n">
         <v>0</v>
@@ -4177,10 +4177,10 @@
         <v>554</v>
       </c>
       <c r="D47" t="n">
+        <v>233</v>
+      </c>
+      <c r="E47" t="n">
         <v>1235</v>
-      </c>
-      <c r="E47" t="n">
-        <v>233</v>
       </c>
       <c r="F47" t="n">
         <v>214</v>
@@ -4195,16 +4195,16 @@
         <v>33</v>
       </c>
       <c r="J47" t="n">
+        <v>17</v>
+      </c>
+      <c r="K47" t="n">
+        <v>0</v>
+      </c>
+      <c r="L47" t="n">
+        <v>0</v>
+      </c>
+      <c r="M47" t="n">
         <v>24</v>
-      </c>
-      <c r="K47" t="n">
-        <v>17</v>
-      </c>
-      <c r="L47" t="n">
-        <v>0</v>
-      </c>
-      <c r="M47" t="n">
-        <v>0</v>
       </c>
       <c r="N47" t="n">
         <v>0</v>
@@ -4256,10 +4256,10 @@
         <v>550</v>
       </c>
       <c r="D48" s="5" t="n">
+        <v>232</v>
+      </c>
+      <c r="E48" s="5" t="n">
         <v>1253</v>
-      </c>
-      <c r="E48" s="5" t="n">
-        <v>232</v>
       </c>
       <c r="F48" s="5" t="n">
         <v>211</v>
@@ -4274,16 +4274,16 @@
         <v>33</v>
       </c>
       <c r="J48" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="K48" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L48" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M48" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="K48" s="5" t="n">
-        <v>17</v>
-      </c>
-      <c r="L48" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M48" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="N48" s="5" t="n">
         <v>0</v>
@@ -4335,10 +4335,10 @@
         <v>550</v>
       </c>
       <c r="D49" t="n">
+        <v>232</v>
+      </c>
+      <c r="E49" t="n">
         <v>1221</v>
-      </c>
-      <c r="E49" t="n">
-        <v>232</v>
       </c>
       <c r="F49" t="n">
         <v>211</v>
@@ -4353,16 +4353,16 @@
         <v>33</v>
       </c>
       <c r="J49" t="n">
+        <v>17</v>
+      </c>
+      <c r="K49" t="n">
+        <v>0</v>
+      </c>
+      <c r="L49" t="n">
+        <v>0</v>
+      </c>
+      <c r="M49" t="n">
         <v>24</v>
-      </c>
-      <c r="K49" t="n">
-        <v>17</v>
-      </c>
-      <c r="L49" t="n">
-        <v>0</v>
-      </c>
-      <c r="M49" t="n">
-        <v>0</v>
       </c>
       <c r="N49" t="n">
         <v>0</v>
@@ -4414,10 +4414,10 @@
         <v>550</v>
       </c>
       <c r="D50" s="5" t="n">
+        <v>232</v>
+      </c>
+      <c r="E50" s="5" t="n">
         <v>1253</v>
-      </c>
-      <c r="E50" s="5" t="n">
-        <v>232</v>
       </c>
       <c r="F50" s="5" t="n">
         <v>211</v>
@@ -4432,16 +4432,16 @@
         <v>33</v>
       </c>
       <c r="J50" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="K50" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L50" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M50" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="K50" s="5" t="n">
-        <v>17</v>
-      </c>
-      <c r="L50" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M50" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="N50" s="5" t="n">
         <v>0</v>
@@ -4493,10 +4493,10 @@
         <v>550</v>
       </c>
       <c r="D51" t="n">
+        <v>227</v>
+      </c>
+      <c r="E51" t="n">
         <v>1155</v>
-      </c>
-      <c r="E51" t="n">
-        <v>227</v>
       </c>
       <c r="F51" t="n">
         <v>226</v>
@@ -4511,16 +4511,16 @@
         <v>33</v>
       </c>
       <c r="J51" t="n">
+        <v>17</v>
+      </c>
+      <c r="K51" t="n">
+        <v>0</v>
+      </c>
+      <c r="L51" t="n">
+        <v>0</v>
+      </c>
+      <c r="M51" t="n">
         <v>24</v>
-      </c>
-      <c r="K51" t="n">
-        <v>17</v>
-      </c>
-      <c r="L51" t="n">
-        <v>0</v>
-      </c>
-      <c r="M51" t="n">
-        <v>0</v>
       </c>
       <c r="N51" t="n">
         <v>0</v>
@@ -4572,10 +4572,10 @@
         <v>541</v>
       </c>
       <c r="D52" s="5" t="n">
+        <v>225</v>
+      </c>
+      <c r="E52" s="5" t="n">
         <v>1062</v>
-      </c>
-      <c r="E52" s="5" t="n">
-        <v>225</v>
       </c>
       <c r="F52" s="5" t="n">
         <v>224</v>
@@ -4590,16 +4590,16 @@
         <v>30</v>
       </c>
       <c r="J52" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="K52" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L52" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M52" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="K52" s="5" t="n">
-        <v>17</v>
-      </c>
-      <c r="L52" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M52" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="N52" s="5" t="n">
         <v>0</v>
@@ -4651,10 +4651,10 @@
         <v>539</v>
       </c>
       <c r="D53" t="n">
+        <v>224</v>
+      </c>
+      <c r="E53" t="n">
         <v>993</v>
-      </c>
-      <c r="E53" t="n">
-        <v>224</v>
       </c>
       <c r="F53" t="n">
         <v>232</v>
@@ -4669,16 +4669,16 @@
         <v>30</v>
       </c>
       <c r="J53" t="n">
+        <v>17</v>
+      </c>
+      <c r="K53" t="n">
+        <v>0</v>
+      </c>
+      <c r="L53" t="n">
+        <v>0</v>
+      </c>
+      <c r="M53" t="n">
         <v>24</v>
-      </c>
-      <c r="K53" t="n">
-        <v>17</v>
-      </c>
-      <c r="L53" t="n">
-        <v>0</v>
-      </c>
-      <c r="M53" t="n">
-        <v>0</v>
       </c>
       <c r="N53" t="n">
         <v>0</v>
@@ -4730,10 +4730,10 @@
         <v>533</v>
       </c>
       <c r="D54" s="5" t="n">
+        <v>224</v>
+      </c>
+      <c r="E54" s="5" t="n">
         <v>988</v>
-      </c>
-      <c r="E54" s="5" t="n">
-        <v>224</v>
       </c>
       <c r="F54" s="5" t="n">
         <v>232</v>
@@ -4748,16 +4748,16 @@
         <v>30</v>
       </c>
       <c r="J54" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="K54" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L54" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M54" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="K54" s="5" t="n">
-        <v>17</v>
-      </c>
-      <c r="L54" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M54" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="N54" s="5" t="n">
         <v>0</v>
@@ -4809,10 +4809,10 @@
         <v>533</v>
       </c>
       <c r="D55" t="n">
+        <v>224</v>
+      </c>
+      <c r="E55" t="n">
         <v>956</v>
-      </c>
-      <c r="E55" t="n">
-        <v>224</v>
       </c>
       <c r="F55" t="n">
         <v>232</v>
@@ -4827,16 +4827,16 @@
         <v>30</v>
       </c>
       <c r="J55" t="n">
+        <v>17</v>
+      </c>
+      <c r="K55" t="n">
+        <v>0</v>
+      </c>
+      <c r="L55" t="n">
+        <v>0</v>
+      </c>
+      <c r="M55" t="n">
         <v>24</v>
-      </c>
-      <c r="K55" t="n">
-        <v>17</v>
-      </c>
-      <c r="L55" t="n">
-        <v>0</v>
-      </c>
-      <c r="M55" t="n">
-        <v>0</v>
       </c>
       <c r="N55" t="n">
         <v>0</v>
@@ -4888,10 +4888,10 @@
         <v>532</v>
       </c>
       <c r="D56" s="5" t="n">
+        <v>223</v>
+      </c>
+      <c r="E56" s="5" t="n">
         <v>985</v>
-      </c>
-      <c r="E56" s="5" t="n">
-        <v>223</v>
       </c>
       <c r="F56" s="5" t="n">
         <v>232</v>
@@ -4906,16 +4906,16 @@
         <v>30</v>
       </c>
       <c r="J56" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="K56" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L56" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M56" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="K56" s="5" t="n">
-        <v>17</v>
-      </c>
-      <c r="L56" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M56" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="N56" s="5" t="n">
         <v>0</v>
@@ -4967,10 +4967,10 @@
         <v>527</v>
       </c>
       <c r="D57" t="n">
+        <v>0</v>
+      </c>
+      <c r="E57" t="n">
         <v>72</v>
-      </c>
-      <c r="E57" t="n">
-        <v>0</v>
       </c>
       <c r="F57" t="n">
         <v>0</v>
@@ -4985,16 +4985,16 @@
         <v>24</v>
       </c>
       <c r="J57" t="n">
+        <v>22</v>
+      </c>
+      <c r="K57" t="n">
+        <v>0</v>
+      </c>
+      <c r="L57" t="n">
+        <v>0</v>
+      </c>
+      <c r="M57" t="n">
         <v>24</v>
-      </c>
-      <c r="K57" t="n">
-        <v>22</v>
-      </c>
-      <c r="L57" t="n">
-        <v>0</v>
-      </c>
-      <c r="M57" t="n">
-        <v>0</v>
       </c>
       <c r="N57" t="n">
         <v>0</v>
@@ -5046,10 +5046,10 @@
         <v>525</v>
       </c>
       <c r="D58" s="5" t="n">
+        <v>216</v>
+      </c>
+      <c r="E58" s="5" t="n">
         <v>72</v>
-      </c>
-      <c r="E58" s="5" t="n">
-        <v>216</v>
       </c>
       <c r="F58" s="5" t="n">
         <v>0</v>
@@ -5064,16 +5064,16 @@
         <v>26</v>
       </c>
       <c r="J58" s="5" t="n">
+        <v>22</v>
+      </c>
+      <c r="K58" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L58" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M58" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="K58" s="5" t="n">
-        <v>22</v>
-      </c>
-      <c r="L58" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M58" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="N58" s="5" t="n">
         <v>0</v>
@@ -5125,10 +5125,10 @@
         <v>528</v>
       </c>
       <c r="D59" t="n">
+        <v>205</v>
+      </c>
+      <c r="E59" t="n">
         <v>549</v>
-      </c>
-      <c r="E59" t="n">
-        <v>205</v>
       </c>
       <c r="F59" t="n">
         <v>207</v>
@@ -5143,16 +5143,16 @@
         <v>26</v>
       </c>
       <c r="J59" t="n">
+        <v>16</v>
+      </c>
+      <c r="K59" t="n">
+        <v>0</v>
+      </c>
+      <c r="L59" t="n">
+        <v>0</v>
+      </c>
+      <c r="M59" t="n">
         <v>24</v>
-      </c>
-      <c r="K59" t="n">
-        <v>16</v>
-      </c>
-      <c r="L59" t="n">
-        <v>0</v>
-      </c>
-      <c r="M59" t="n">
-        <v>0</v>
       </c>
       <c r="N59" t="n">
         <v>0</v>
@@ -5204,10 +5204,10 @@
         <v>536</v>
       </c>
       <c r="D60" s="5" t="n">
+        <v>270</v>
+      </c>
+      <c r="E60" s="5" t="n">
         <v>504</v>
-      </c>
-      <c r="E60" s="5" t="n">
-        <v>270</v>
       </c>
       <c r="F60" s="5" t="n">
         <v>218</v>
@@ -5222,16 +5222,16 @@
         <v>23</v>
       </c>
       <c r="J60" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="K60" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L60" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M60" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="K60" s="5" t="n">
-        <v>16</v>
-      </c>
-      <c r="L60" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M60" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="N60" s="5" t="n">
         <v>0</v>
@@ -5283,10 +5283,10 @@
         <v>533</v>
       </c>
       <c r="D61" t="n">
+        <v>282</v>
+      </c>
+      <c r="E61" t="n">
         <v>495</v>
-      </c>
-      <c r="E61" t="n">
-        <v>282</v>
       </c>
       <c r="F61" t="n">
         <v>218</v>
@@ -5301,16 +5301,16 @@
         <v>29</v>
       </c>
       <c r="J61" t="n">
+        <v>16</v>
+      </c>
+      <c r="K61" t="n">
+        <v>0</v>
+      </c>
+      <c r="L61" t="n">
+        <v>0</v>
+      </c>
+      <c r="M61" t="n">
         <v>24</v>
-      </c>
-      <c r="K61" t="n">
-        <v>16</v>
-      </c>
-      <c r="L61" t="n">
-        <v>0</v>
-      </c>
-      <c r="M61" t="n">
-        <v>0</v>
       </c>
       <c r="N61" t="n">
         <v>0</v>
@@ -5362,10 +5362,10 @@
         <v>533</v>
       </c>
       <c r="D62" s="5" t="n">
+        <v>282</v>
+      </c>
+      <c r="E62" s="5" t="n">
         <v>495</v>
-      </c>
-      <c r="E62" s="5" t="n">
-        <v>282</v>
       </c>
       <c r="F62" s="5" t="n">
         <v>218</v>
@@ -5380,16 +5380,16 @@
         <v>29</v>
       </c>
       <c r="J62" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="K62" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L62" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M62" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="K62" s="5" t="n">
-        <v>16</v>
-      </c>
-      <c r="L62" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M62" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="N62" s="5" t="n">
         <v>0</v>
@@ -5441,10 +5441,10 @@
         <v>533</v>
       </c>
       <c r="D63" t="n">
+        <v>282</v>
+      </c>
+      <c r="E63" t="n">
         <v>495</v>
-      </c>
-      <c r="E63" t="n">
-        <v>282</v>
       </c>
       <c r="F63" t="n">
         <v>218</v>
@@ -5459,16 +5459,16 @@
         <v>29</v>
       </c>
       <c r="J63" t="n">
+        <v>16</v>
+      </c>
+      <c r="K63" t="n">
+        <v>0</v>
+      </c>
+      <c r="L63" t="n">
+        <v>0</v>
+      </c>
+      <c r="M63" t="n">
         <v>24</v>
-      </c>
-      <c r="K63" t="n">
-        <v>16</v>
-      </c>
-      <c r="L63" t="n">
-        <v>0</v>
-      </c>
-      <c r="M63" t="n">
-        <v>0</v>
       </c>
       <c r="N63" t="n">
         <v>0</v>
@@ -5520,10 +5520,10 @@
         <v>541</v>
       </c>
       <c r="D64" s="5" t="n">
+        <v>366</v>
+      </c>
+      <c r="E64" s="5" t="n">
         <v>469</v>
-      </c>
-      <c r="E64" s="5" t="n">
-        <v>366</v>
       </c>
       <c r="F64" s="5" t="n">
         <v>215</v>
@@ -5538,16 +5538,16 @@
         <v>20</v>
       </c>
       <c r="J64" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="K64" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L64" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M64" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="K64" s="5" t="n">
-        <v>16</v>
-      </c>
-      <c r="L64" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M64" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="N64" s="5" t="n">
         <v>0</v>
@@ -5599,10 +5599,10 @@
         <v>534</v>
       </c>
       <c r="D65" t="n">
+        <v>356</v>
+      </c>
+      <c r="E65" t="n">
         <v>471</v>
-      </c>
-      <c r="E65" t="n">
-        <v>356</v>
       </c>
       <c r="F65" t="n">
         <v>211</v>
@@ -5617,16 +5617,16 @@
         <v>20</v>
       </c>
       <c r="J65" t="n">
+        <v>21</v>
+      </c>
+      <c r="K65" t="n">
+        <v>0</v>
+      </c>
+      <c r="L65" t="n">
+        <v>0</v>
+      </c>
+      <c r="M65" t="n">
         <v>24</v>
-      </c>
-      <c r="K65" t="n">
-        <v>21</v>
-      </c>
-      <c r="L65" t="n">
-        <v>0</v>
-      </c>
-      <c r="M65" t="n">
-        <v>0</v>
       </c>
       <c r="N65" t="n">
         <v>0</v>
@@ -5678,10 +5678,10 @@
         <v>521</v>
       </c>
       <c r="D66" s="5" t="n">
+        <v>381</v>
+      </c>
+      <c r="E66" s="5" t="n">
         <v>470</v>
-      </c>
-      <c r="E66" s="5" t="n">
-        <v>381</v>
       </c>
       <c r="F66" s="5" t="n">
         <v>201</v>
@@ -5696,16 +5696,16 @@
         <v>26</v>
       </c>
       <c r="J66" s="5" t="n">
+        <v>21</v>
+      </c>
+      <c r="K66" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L66" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M66" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="K66" s="5" t="n">
-        <v>21</v>
-      </c>
-      <c r="L66" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M66" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="N66" s="5" t="n">
         <v>0</v>
@@ -5757,10 +5757,10 @@
         <v>525</v>
       </c>
       <c r="D67" t="n">
+        <v>380</v>
+      </c>
+      <c r="E67" t="n">
         <v>446</v>
-      </c>
-      <c r="E67" t="n">
-        <v>380</v>
       </c>
       <c r="F67" t="n">
         <v>200</v>
@@ -5774,13 +5774,13 @@
       <c r="I67" t="n">
         <v>26</v>
       </c>
+      <c r="J67" t="n">
+        <v>21</v>
+      </c>
       <c r="K67" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="L67" t="n">
-        <v>0</v>
-      </c>
-      <c r="M67" t="n">
         <v>0</v>
       </c>
       <c r="N67" t="n">
@@ -5833,10 +5833,10 @@
         <v>518</v>
       </c>
       <c r="D68" s="5" t="n">
+        <v>370</v>
+      </c>
+      <c r="E68" s="5" t="n">
         <v>416</v>
-      </c>
-      <c r="E68" s="5" t="n">
-        <v>370</v>
       </c>
       <c r="F68" s="5" t="n">
         <v>206</v>
@@ -5851,16 +5851,16 @@
         <v>26</v>
       </c>
       <c r="J68" s="5" t="n">
+        <v>21</v>
+      </c>
+      <c r="K68" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L68" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M68" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="K68" s="5" t="n">
-        <v>21</v>
-      </c>
-      <c r="L68" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M68" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="N68" s="5" t="n">
         <v>0</v>
@@ -5909,10 +5909,10 @@
         <v>850</v>
       </c>
       <c r="D69" t="n">
+        <v>370</v>
+      </c>
+      <c r="E69" t="n">
         <v>416</v>
-      </c>
-      <c r="E69" t="n">
-        <v>370</v>
       </c>
       <c r="F69" t="n">
         <v>206</v>
@@ -5926,13 +5926,13 @@
       <c r="I69" t="n">
         <v>26</v>
       </c>
+      <c r="J69" t="n">
+        <v>21</v>
+      </c>
       <c r="K69" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="L69" t="n">
-        <v>0</v>
-      </c>
-      <c r="M69" t="n">
         <v>0</v>
       </c>
       <c r="N69" t="n">
@@ -5985,10 +5985,10 @@
         <v>518</v>
       </c>
       <c r="D70" s="5" t="n">
+        <v>370</v>
+      </c>
+      <c r="E70" s="5" t="n">
         <v>416</v>
-      </c>
-      <c r="E70" s="5" t="n">
-        <v>370</v>
       </c>
       <c r="F70" s="5" t="n">
         <v>206</v>
@@ -6003,16 +6003,16 @@
         <v>26</v>
       </c>
       <c r="J70" s="5" t="n">
+        <v>21</v>
+      </c>
+      <c r="K70" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L70" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M70" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="K70" s="5" t="n">
-        <v>21</v>
-      </c>
-      <c r="L70" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M70" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="N70" s="5" t="n">
         <v>0</v>
@@ -6064,10 +6064,10 @@
         <v>516</v>
       </c>
       <c r="D71" t="n">
+        <v>397</v>
+      </c>
+      <c r="E71" t="n">
         <v>395</v>
-      </c>
-      <c r="E71" t="n">
-        <v>397</v>
       </c>
       <c r="F71" t="n">
         <v>190</v>
@@ -6082,16 +6082,16 @@
         <v>26</v>
       </c>
       <c r="J71" t="n">
+        <v>21</v>
+      </c>
+      <c r="K71" t="n">
+        <v>0</v>
+      </c>
+      <c r="L71" t="n">
+        <v>0</v>
+      </c>
+      <c r="M71" t="n">
         <v>24</v>
-      </c>
-      <c r="K71" t="n">
-        <v>21</v>
-      </c>
-      <c r="L71" t="n">
-        <v>0</v>
-      </c>
-      <c r="M71" t="n">
-        <v>0</v>
       </c>
       <c r="N71" t="n">
         <v>0</v>
@@ -6143,10 +6143,10 @@
         <v>531</v>
       </c>
       <c r="D72" s="5" t="n">
+        <v>398</v>
+      </c>
+      <c r="E72" s="5" t="n">
         <v>394</v>
-      </c>
-      <c r="E72" s="5" t="n">
-        <v>398</v>
       </c>
       <c r="F72" s="5" t="n">
         <v>196</v>
@@ -6161,16 +6161,16 @@
         <v>26</v>
       </c>
       <c r="J72" s="5" t="n">
+        <v>21</v>
+      </c>
+      <c r="K72" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L72" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M72" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="K72" s="5" t="n">
-        <v>21</v>
-      </c>
-      <c r="L72" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M72" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="N72" s="5" t="n">
         <v>0</v>
@@ -6222,10 +6222,10 @@
         <v>529</v>
       </c>
       <c r="D73" t="n">
+        <v>390</v>
+      </c>
+      <c r="E73" t="n">
         <v>395</v>
-      </c>
-      <c r="E73" t="n">
-        <v>390</v>
       </c>
       <c r="F73" t="n">
         <v>201</v>
@@ -6240,16 +6240,16 @@
         <v>26</v>
       </c>
       <c r="J73" t="n">
+        <v>19</v>
+      </c>
+      <c r="K73" t="n">
+        <v>0</v>
+      </c>
+      <c r="L73" t="n">
+        <v>0</v>
+      </c>
+      <c r="M73" t="n">
         <v>24</v>
-      </c>
-      <c r="K73" t="n">
-        <v>19</v>
-      </c>
-      <c r="L73" t="n">
-        <v>0</v>
-      </c>
-      <c r="M73" t="n">
-        <v>0</v>
       </c>
       <c r="N73" t="n">
         <v>0</v>
@@ -6301,10 +6301,10 @@
         <v>529</v>
       </c>
       <c r="D74" s="5" t="n">
+        <v>389</v>
+      </c>
+      <c r="E74" s="5" t="n">
         <v>396</v>
-      </c>
-      <c r="E74" s="5" t="n">
-        <v>389</v>
       </c>
       <c r="F74" s="5" t="n">
         <v>203</v>
@@ -6319,16 +6319,16 @@
         <v>26</v>
       </c>
       <c r="J74" s="5" t="n">
+        <v>23</v>
+      </c>
+      <c r="K74" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L74" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M74" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="K74" s="5" t="n">
-        <v>23</v>
-      </c>
-      <c r="L74" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M74" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="N74" s="5" t="n">
         <v>0</v>
@@ -6380,10 +6380,10 @@
         <v>529</v>
       </c>
       <c r="D75" t="n">
+        <v>392</v>
+      </c>
+      <c r="E75" t="n">
         <v>396</v>
-      </c>
-      <c r="E75" t="n">
-        <v>392</v>
       </c>
       <c r="F75" t="n">
         <v>181</v>
@@ -6398,16 +6398,16 @@
         <v>26</v>
       </c>
       <c r="J75" t="n">
+        <v>23</v>
+      </c>
+      <c r="K75" t="n">
+        <v>0</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0</v>
+      </c>
+      <c r="M75" t="n">
         <v>24</v>
-      </c>
-      <c r="K75" t="n">
-        <v>23</v>
-      </c>
-      <c r="L75" t="n">
-        <v>0</v>
-      </c>
-      <c r="M75" t="n">
-        <v>0</v>
       </c>
       <c r="N75" t="n">
         <v>0</v>
@@ -6459,10 +6459,10 @@
         <v>529</v>
       </c>
       <c r="D76" s="5" t="n">
+        <v>392</v>
+      </c>
+      <c r="E76" s="5" t="n">
         <v>368</v>
-      </c>
-      <c r="E76" s="5" t="n">
-        <v>392</v>
       </c>
       <c r="F76" s="5" t="n">
         <v>181</v>
@@ -6477,36 +6477,34 @@
         <v>26</v>
       </c>
       <c r="J76" s="5" t="n">
+        <v>23</v>
+      </c>
+      <c r="K76" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L76" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M76" s="5" t="n">
         <v>24</v>
       </c>
-      <c r="K76" s="5" t="n">
-        <v>23</v>
-      </c>
-      <c r="L76" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M76" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="N76" s="5" t="n">
         <v>0</v>
       </c>
       <c r="O76" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="P76" s="5" t="n"/>
-      <c r="Q76" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="P76" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q76" s="5" t="n"/>
       <c r="R76" s="5" t="n">
         <v>0</v>
       </c>
       <c r="S76" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="T76" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="T76" s="5" t="n"/>
       <c r="U76" s="5" t="n">
         <v>0</v>
       </c>
@@ -6519,7 +6517,9 @@
       <c r="X76" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="Y76" s="5" t="n"/>
+      <c r="Y76" s="5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="6" t="inlineStr">
@@ -6534,10 +6534,10 @@
         <v>529</v>
       </c>
       <c r="D77" t="n">
+        <v>392</v>
+      </c>
+      <c r="E77" t="n">
         <v>396</v>
-      </c>
-      <c r="E77" t="n">
-        <v>392</v>
       </c>
       <c r="F77" t="n">
         <v>181</v>
@@ -6551,13 +6551,13 @@
       <c r="I77" t="n">
         <v>26</v>
       </c>
+      <c r="J77" t="n">
+        <v>23</v>
+      </c>
       <c r="K77" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="L77" t="n">
-        <v>0</v>
-      </c>
-      <c r="M77" t="n">
         <v>0</v>
       </c>
       <c r="N77" t="n">
@@ -6610,10 +6610,10 @@
         <v>526</v>
       </c>
       <c r="D78" s="5" t="n">
+        <v>369</v>
+      </c>
+      <c r="E78" s="5" t="n">
         <v>396</v>
-      </c>
-      <c r="E78" s="5" t="n">
-        <v>369</v>
       </c>
       <c r="F78" s="5" t="n">
         <v>184</v>
@@ -6628,16 +6628,16 @@
         <v>26</v>
       </c>
       <c r="J78" s="5" t="n">
+        <v>23</v>
+      </c>
+      <c r="K78" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L78" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M78" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="K78" s="5" t="n">
-        <v>23</v>
-      </c>
-      <c r="L78" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M78" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="N78" s="5" t="n">
         <v>0</v>
@@ -6689,10 +6689,10 @@
         <v>540</v>
       </c>
       <c r="D79" t="n">
+        <v>369</v>
+      </c>
+      <c r="E79" t="n">
         <v>394</v>
-      </c>
-      <c r="E79" t="n">
-        <v>369</v>
       </c>
       <c r="F79" t="n">
         <v>207</v>
@@ -6706,13 +6706,13 @@
       <c r="I79" t="n">
         <v>26</v>
       </c>
+      <c r="J79" t="n">
+        <v>23</v>
+      </c>
       <c r="K79" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="L79" t="n">
-        <v>0</v>
-      </c>
-      <c r="M79" t="n">
         <v>0</v>
       </c>
       <c r="N79" t="n">
@@ -6765,10 +6765,10 @@
         <v>537</v>
       </c>
       <c r="D80" s="5" t="n">
+        <v>372</v>
+      </c>
+      <c r="E80" s="5" t="n">
         <v>391</v>
-      </c>
-      <c r="E80" s="5" t="n">
-        <v>372</v>
       </c>
       <c r="F80" s="5" t="n">
         <v>207</v>
@@ -6782,16 +6782,16 @@
       <c r="I80" s="5" t="n">
         <v>26</v>
       </c>
-      <c r="J80" s="5" t="n"/>
+      <c r="J80" s="5" t="n">
+        <v>23</v>
+      </c>
       <c r="K80" s="5" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="L80" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="M80" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="M80" s="5" t="n"/>
       <c r="N80" s="5" t="n">
         <v>0</v>
       </c>
@@ -6842,10 +6842,10 @@
         <v>532</v>
       </c>
       <c r="D81" t="n">
+        <v>388</v>
+      </c>
+      <c r="E81" t="n">
         <v>389</v>
-      </c>
-      <c r="E81" t="n">
-        <v>388</v>
       </c>
       <c r="F81" t="n">
         <v>216</v>
@@ -6860,51 +6860,128 @@
         <v>26</v>
       </c>
       <c r="J81" t="n">
+        <v>23</v>
+      </c>
+      <c r="K81" t="n">
+        <v>0</v>
+      </c>
+      <c r="L81" t="n">
+        <v>0</v>
+      </c>
+      <c r="M81" t="n">
         <v>24</v>
       </c>
-      <c r="K81" t="n">
+      <c r="N81" t="n">
+        <v>0</v>
+      </c>
+      <c r="O81" t="n">
+        <v>0</v>
+      </c>
+      <c r="P81" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q81" t="n">
+        <v>0</v>
+      </c>
+      <c r="R81" t="n">
+        <v>0</v>
+      </c>
+      <c r="S81" t="n">
+        <v>0</v>
+      </c>
+      <c r="T81" t="n">
+        <v>0</v>
+      </c>
+      <c r="U81" t="n">
+        <v>0</v>
+      </c>
+      <c r="V81" t="n">
+        <v>0</v>
+      </c>
+      <c r="W81" t="n">
+        <v>0</v>
+      </c>
+      <c r="X81" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y81" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B82" s="5" t="n">
+        <v>881</v>
+      </c>
+      <c r="C82" s="5" t="n">
+        <v>530</v>
+      </c>
+      <c r="D82" s="5" t="n">
+        <v>380</v>
+      </c>
+      <c r="E82" s="5" t="n">
+        <v>366</v>
+      </c>
+      <c r="F82" s="5" t="n">
+        <v>216</v>
+      </c>
+      <c r="G82" s="5" t="n">
+        <v>96</v>
+      </c>
+      <c r="H82" s="5" t="n">
+        <v>42</v>
+      </c>
+      <c r="I82" s="5" t="n">
+        <v>26</v>
+      </c>
+      <c r="J82" s="5" t="n">
         <v>23</v>
       </c>
-      <c r="L81" t="n">
-        <v>0</v>
-      </c>
-      <c r="M81" t="n">
-        <v>0</v>
-      </c>
-      <c r="N81" t="n">
-        <v>0</v>
-      </c>
-      <c r="O81" t="n">
-        <v>0</v>
-      </c>
-      <c r="P81" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q81" t="n">
-        <v>0</v>
-      </c>
-      <c r="R81" t="n">
-        <v>0</v>
-      </c>
-      <c r="S81" t="n">
-        <v>0</v>
-      </c>
-      <c r="T81" t="n">
-        <v>0</v>
-      </c>
-      <c r="U81" t="n">
-        <v>0</v>
-      </c>
-      <c r="V81" t="n">
-        <v>0</v>
-      </c>
-      <c r="W81" t="n">
-        <v>0</v>
-      </c>
-      <c r="X81" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y81" t="n">
+      <c r="K82" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L82" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M82" s="5" t="n"/>
+      <c r="N82" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O82" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P82" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q82" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R82" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S82" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T82" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U82" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V82" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W82" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X82" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y82" s="5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6946,7 +7023,7 @@
       </c>
       <c r="D1" s="3" t="inlineStr">
         <is>
-          <t>Lager (2026-09-25)</t>
+          <t>Lager (2026-09-26)</t>
         </is>
       </c>
     </row>
@@ -6967,7 +7044,7 @@
         </is>
       </c>
       <c r="D2" s="4" t="n">
-        <v>532</v>
+        <v>530</v>
       </c>
     </row>
     <row r="3">
@@ -12153,12 +12230,12 @@
     <row r="262">
       <c r="A262" s="4" t="inlineStr">
         <is>
-          <t>7011676</t>
+          <t>7013678</t>
         </is>
       </c>
       <c r="B262" s="5" t="inlineStr">
         <is>
-          <t>Infälld interiörarmatur Diana Flat LED 300x300</t>
+          <t>Infälld Interiörarmatur LED DPML Tunable White</t>
         </is>
       </c>
       <c r="C262" s="5" t="inlineStr">
@@ -12173,7 +12250,7 @@
     <row r="263">
       <c r="A263" s="6" t="inlineStr">
         <is>
-          <t>7011677</t>
+          <t>7011676</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -12193,12 +12270,12 @@
     <row r="264">
       <c r="A264" s="4" t="inlineStr">
         <is>
-          <t>7013193</t>
+          <t>7011677</t>
         </is>
       </c>
       <c r="B264" s="5" t="inlineStr">
         <is>
-          <t>Infälld interiörarmatur Diana Flat LED 600x600</t>
+          <t>Infälld interiörarmatur Diana Flat LED 300x300</t>
         </is>
       </c>
       <c r="C264" s="5" t="inlineStr">
@@ -12213,7 +12290,7 @@
     <row r="265">
       <c r="A265" s="6" t="inlineStr">
         <is>
-          <t>7013194</t>
+          <t>7013193</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
@@ -12233,7 +12310,7 @@
     <row r="266">
       <c r="A266" s="4" t="inlineStr">
         <is>
-          <t>7018335</t>
+          <t>7013194</t>
         </is>
       </c>
       <c r="B266" s="5" t="inlineStr">
@@ -12253,7 +12330,7 @@
     <row r="267">
       <c r="A267" s="6" t="inlineStr">
         <is>
-          <t>7018336</t>
+          <t>7018335</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
@@ -12273,7 +12350,7 @@
     <row r="268">
       <c r="A268" s="4" t="inlineStr">
         <is>
-          <t>7018337</t>
+          <t>7018336</t>
         </is>
       </c>
       <c r="B268" s="5" t="inlineStr">
@@ -12293,7 +12370,7 @@
     <row r="269">
       <c r="A269" s="6" t="inlineStr">
         <is>
-          <t>7018338</t>
+          <t>7018337</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
@@ -12313,7 +12390,7 @@
     <row r="270">
       <c r="A270" s="4" t="inlineStr">
         <is>
-          <t>7018339</t>
+          <t>7018338</t>
         </is>
       </c>
       <c r="B270" s="5" t="inlineStr">
@@ -12333,7 +12410,7 @@
     <row r="271">
       <c r="A271" s="6" t="inlineStr">
         <is>
-          <t>7018340</t>
+          <t>7018339</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
@@ -12353,7 +12430,7 @@
     <row r="272">
       <c r="A272" s="4" t="inlineStr">
         <is>
-          <t>7018341</t>
+          <t>7018340</t>
         </is>
       </c>
       <c r="B272" s="5" t="inlineStr">
@@ -12373,7 +12450,7 @@
     <row r="273">
       <c r="A273" s="6" t="inlineStr">
         <is>
-          <t>7018342</t>
+          <t>7018341</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
@@ -12393,12 +12470,12 @@
     <row r="274">
       <c r="A274" s="4" t="inlineStr">
         <is>
-          <t>7017462</t>
+          <t>7018342</t>
         </is>
       </c>
       <c r="B274" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur LED Velox Deco Fyrkantig</t>
+          <t>Infälld interiörarmatur Diana Flat LED 600x600</t>
         </is>
       </c>
       <c r="C274" s="5" t="inlineStr">
@@ -12413,7 +12490,7 @@
     <row r="275">
       <c r="A275" s="6" t="inlineStr">
         <is>
-          <t>7018858</t>
+          <t>7017462</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
@@ -12433,7 +12510,7 @@
     <row r="276">
       <c r="A276" s="4" t="inlineStr">
         <is>
-          <t>7018877</t>
+          <t>7018858</t>
         </is>
       </c>
       <c r="B276" s="5" t="inlineStr">
@@ -12453,7 +12530,7 @@
     <row r="277">
       <c r="A277" s="6" t="inlineStr">
         <is>
-          <t>7018878</t>
+          <t>7018877</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
@@ -12473,12 +12550,12 @@
     <row r="278">
       <c r="A278" s="4" t="inlineStr">
         <is>
-          <t>7017460</t>
+          <t>7018878</t>
         </is>
       </c>
       <c r="B278" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur LED Velox Deco Rund</t>
+          <t>Interiörarmatur LED Velox Deco Fyrkantig</t>
         </is>
       </c>
       <c r="C278" s="5" t="inlineStr">
@@ -12493,7 +12570,7 @@
     <row r="279">
       <c r="A279" s="6" t="inlineStr">
         <is>
-          <t>7017464</t>
+          <t>7017460</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
@@ -12513,7 +12590,7 @@
     <row r="280">
       <c r="A280" s="4" t="inlineStr">
         <is>
-          <t>7017466</t>
+          <t>7017464</t>
         </is>
       </c>
       <c r="B280" s="5" t="inlineStr">
@@ -12533,7 +12610,7 @@
     <row r="281">
       <c r="A281" s="6" t="inlineStr">
         <is>
-          <t>7018857</t>
+          <t>7017466</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
@@ -12553,7 +12630,7 @@
     <row r="282">
       <c r="A282" s="4" t="inlineStr">
         <is>
-          <t>7018859</t>
+          <t>7018857</t>
         </is>
       </c>
       <c r="B282" s="5" t="inlineStr">
@@ -12573,7 +12650,7 @@
     <row r="283">
       <c r="A283" s="6" t="inlineStr">
         <is>
-          <t>7018860</t>
+          <t>7018859</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
@@ -12593,7 +12670,7 @@
     <row r="284">
       <c r="A284" s="4" t="inlineStr">
         <is>
-          <t>7018874</t>
+          <t>7018860</t>
         </is>
       </c>
       <c r="B284" s="5" t="inlineStr">
@@ -12613,7 +12690,7 @@
     <row r="285">
       <c r="A285" s="6" t="inlineStr">
         <is>
-          <t>7018875</t>
+          <t>7018874</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
@@ -12633,7 +12710,7 @@
     <row r="286">
       <c r="A286" s="4" t="inlineStr">
         <is>
-          <t>7018876</t>
+          <t>7018875</t>
         </is>
       </c>
       <c r="B286" s="5" t="inlineStr">
@@ -12653,7 +12730,7 @@
     <row r="287">
       <c r="A287" s="6" t="inlineStr">
         <is>
-          <t>7018879</t>
+          <t>7018876</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
@@ -12673,7 +12750,7 @@
     <row r="288">
       <c r="A288" s="4" t="inlineStr">
         <is>
-          <t>7018880</t>
+          <t>7018879</t>
         </is>
       </c>
       <c r="B288" s="5" t="inlineStr">
@@ -12693,7 +12770,7 @@
     <row r="289">
       <c r="A289" s="6" t="inlineStr">
         <is>
-          <t>7018881</t>
+          <t>7018880</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
@@ -12713,7 +12790,7 @@
     <row r="290">
       <c r="A290" s="4" t="inlineStr">
         <is>
-          <t>7018882</t>
+          <t>7018881</t>
         </is>
       </c>
       <c r="B290" s="5" t="inlineStr">
@@ -12733,12 +12810,12 @@
     <row r="291">
       <c r="A291" s="6" t="inlineStr">
         <is>
-          <t>7015430</t>
+          <t>7018882</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>Interiörarmatur LED Velox Infälld rund</t>
+          <t>Interiörarmatur LED Velox Deco Rund</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
@@ -12753,7 +12830,7 @@
     <row r="292">
       <c r="A292" s="4" t="inlineStr">
         <is>
-          <t>7015431</t>
+          <t>7015430</t>
         </is>
       </c>
       <c r="B292" s="5" t="inlineStr">
@@ -12773,7 +12850,7 @@
     <row r="293">
       <c r="A293" s="6" t="inlineStr">
         <is>
-          <t>7015437</t>
+          <t>7015431</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
@@ -12793,7 +12870,7 @@
     <row r="294">
       <c r="A294" s="4" t="inlineStr">
         <is>
-          <t>7015439</t>
+          <t>7015437</t>
         </is>
       </c>
       <c r="B294" s="5" t="inlineStr">
@@ -12813,7 +12890,7 @@
     <row r="295">
       <c r="A295" s="6" t="inlineStr">
         <is>
-          <t>7015441</t>
+          <t>7015439</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
@@ -12833,7 +12910,7 @@
     <row r="296">
       <c r="A296" s="4" t="inlineStr">
         <is>
-          <t>7015443</t>
+          <t>7015441</t>
         </is>
       </c>
       <c r="B296" s="5" t="inlineStr">
@@ -12853,12 +12930,12 @@
     <row r="297">
       <c r="A297" s="6" t="inlineStr">
         <is>
-          <t>7015433</t>
+          <t>7015443</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>Interiörarmatur LED Velox infälld fyrkantig</t>
+          <t>Interiörarmatur LED Velox Infälld rund</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
@@ -12873,7 +12950,7 @@
     <row r="298">
       <c r="A298" s="4" t="inlineStr">
         <is>
-          <t>7015435</t>
+          <t>7015433</t>
         </is>
       </c>
       <c r="B298" s="5" t="inlineStr">
@@ -12893,21 +12970,21 @@
     <row r="299">
       <c r="A299" s="6" t="inlineStr">
         <is>
-          <t>7028947</t>
+          <t>7015435</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>Interiörarmatur Juna</t>
+          <t>Interiörarmatur LED Velox infälld fyrkantig</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>Esylux</t>
+          <t>Ensto</t>
         </is>
       </c>
       <c r="D299" s="6" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
     </row>
     <row r="300">
@@ -15587,7 +15664,7 @@
         </is>
       </c>
       <c r="D433" s="6" t="n">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="434">
@@ -15607,7 +15684,7 @@
         </is>
       </c>
       <c r="D434" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="435">
@@ -19467,7 +19544,7 @@
         </is>
       </c>
       <c r="D627" s="6" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
     </row>
     <row r="628">
@@ -24827,7 +24904,7 @@
         </is>
       </c>
       <c r="D895" s="6" t="n">
-        <v>294</v>
+        <v>276</v>
       </c>
     </row>
     <row r="896">
@@ -25267,7 +25344,7 @@
         </is>
       </c>
       <c r="D917" s="6" t="n">
-        <v>33</v>
+        <v>28</v>
       </c>
     </row>
     <row r="918">
@@ -26507,7 +26584,7 @@
         </is>
       </c>
       <c r="D979" s="6" t="n">
-        <v>105</v>
+        <v>97</v>
       </c>
     </row>
     <row r="980">
@@ -29667,7 +29744,7 @@
         </is>
       </c>
       <c r="D1137" s="6" t="n">
-        <v>468</v>
+        <v>466</v>
       </c>
     </row>
     <row r="1138">
@@ -29687,7 +29764,7 @@
         </is>
       </c>
       <c r="D1138" s="4" t="n">
-        <v>333</v>
+        <v>330</v>
       </c>
     </row>
   </sheetData>

--- a/data/ahlsell_led_panel_inventory.xlsx
+++ b/data/ahlsell_led_panel_inventory.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y84"/>
+  <dimension ref="A1:Y85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -528,87 +528,87 @@
       </c>
       <c r="I1" s="3" t="inlineStr">
         <is>
+          <t>Ledvance</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="inlineStr">
+        <is>
           <t>Exaktor</t>
         </is>
       </c>
-      <c r="J1" s="3" t="inlineStr">
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Bergdahls</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="inlineStr">
+        <is>
+          <t>ANETA LIGHTING</t>
+        </is>
+      </c>
+      <c r="M1" s="3" t="inlineStr">
+        <is>
+          <t>Siteco</t>
+        </is>
+      </c>
+      <c r="N1" s="3" t="inlineStr">
+        <is>
+          <t>ZG Lighting</t>
+        </is>
+      </c>
+      <c r="O1" s="3" t="inlineStr">
+        <is>
+          <t>Legrand</t>
+        </is>
+      </c>
+      <c r="P1" s="3" t="inlineStr">
         <is>
           <t>Esylux</t>
         </is>
       </c>
-      <c r="K1" s="3" t="inlineStr">
-        <is>
-          <t>Ledvance</t>
-        </is>
-      </c>
-      <c r="L1" s="3" t="inlineStr">
+      <c r="Q1" s="3" t="inlineStr">
         <is>
           <t>Nokalux</t>
         </is>
       </c>
-      <c r="M1" s="3" t="inlineStr">
+      <c r="R1" s="3" t="inlineStr">
+        <is>
+          <t>THORN</t>
+        </is>
+      </c>
+      <c r="S1" s="3" t="inlineStr">
+        <is>
+          <t>Black Box</t>
+        </is>
+      </c>
+      <c r="T1" s="3" t="inlineStr">
+        <is>
+          <t>Philips</t>
+        </is>
+      </c>
+      <c r="U1" s="3" t="inlineStr">
+        <is>
+          <t>Easyform</t>
+        </is>
+      </c>
+      <c r="V1" s="3" t="inlineStr">
+        <is>
+          <t>Airam</t>
+        </is>
+      </c>
+      <c r="W1" s="3" t="inlineStr">
+        <is>
+          <t>Ensto</t>
+        </is>
+      </c>
+      <c r="X1" s="3" t="inlineStr">
         <is>
           <t>Norwesco</t>
         </is>
       </c>
-      <c r="N1" s="3" t="inlineStr">
-        <is>
-          <t>THORN</t>
-        </is>
-      </c>
-      <c r="O1" s="3" t="inlineStr">
-        <is>
-          <t>Philips</t>
-        </is>
-      </c>
-      <c r="P1" s="3" t="inlineStr">
+      <c r="Y1" s="3" t="inlineStr">
         <is>
           <t>Westal</t>
-        </is>
-      </c>
-      <c r="Q1" s="3" t="inlineStr">
-        <is>
-          <t>ANETA LIGHTING</t>
-        </is>
-      </c>
-      <c r="R1" s="3" t="inlineStr">
-        <is>
-          <t>ZG Lighting</t>
-        </is>
-      </c>
-      <c r="S1" s="3" t="inlineStr">
-        <is>
-          <t>Ensto</t>
-        </is>
-      </c>
-      <c r="T1" s="3" t="inlineStr">
-        <is>
-          <t>Bergdahls</t>
-        </is>
-      </c>
-      <c r="U1" s="3" t="inlineStr">
-        <is>
-          <t>Black Box</t>
-        </is>
-      </c>
-      <c r="V1" s="3" t="inlineStr">
-        <is>
-          <t>Legrand</t>
-        </is>
-      </c>
-      <c r="W1" s="3" t="inlineStr">
-        <is>
-          <t>Airam</t>
-        </is>
-      </c>
-      <c r="X1" s="3" t="inlineStr">
-        <is>
-          <t>Siteco</t>
-        </is>
-      </c>
-      <c r="Y1" s="3" t="inlineStr">
-        <is>
-          <t>Easyform</t>
         </is>
       </c>
     </row>
@@ -640,28 +640,28 @@
         <v>52</v>
       </c>
       <c r="I2" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="J2" s="5" t="n">
         <v>33</v>
       </c>
-      <c r="J2" s="5" t="n">
+      <c r="K2" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2" s="5" t="n">
         <v>25</v>
-      </c>
-      <c r="K2" s="5" t="n">
-        <v>17</v>
-      </c>
-      <c r="L2" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M2" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N2" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O2" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P2" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="Q2" s="5" t="n">
         <v>0</v>
@@ -719,28 +719,28 @@
         <v>52</v>
       </c>
       <c r="I3" t="n">
+        <v>17</v>
+      </c>
+      <c r="J3" t="n">
         <v>33</v>
       </c>
-      <c r="J3" t="n">
+      <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" t="n">
         <v>25</v>
-      </c>
-      <c r="K3" t="n">
-        <v>17</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P3" t="n">
-        <v>0</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -798,28 +798,28 @@
         <v>52</v>
       </c>
       <c r="I4" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="J4" s="5" t="n">
         <v>33</v>
       </c>
-      <c r="J4" s="5" t="n">
+      <c r="K4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" s="5" t="n">
         <v>25</v>
-      </c>
-      <c r="K4" s="5" t="n">
-        <v>17</v>
-      </c>
-      <c r="L4" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M4" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O4" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="Q4" s="5" t="n">
         <v>0</v>
@@ -877,28 +877,28 @@
         <v>52</v>
       </c>
       <c r="I5" t="n">
+        <v>17</v>
+      </c>
+      <c r="J5" t="n">
         <v>33</v>
       </c>
-      <c r="J5" t="n">
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
         <v>24</v>
-      </c>
-      <c r="K5" t="n">
-        <v>17</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -956,28 +956,28 @@
         <v>52</v>
       </c>
       <c r="I6" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="J6" s="5" t="n">
         <v>33</v>
       </c>
-      <c r="J6" s="5" t="n">
+      <c r="K6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="K6" s="5" t="n">
-        <v>17</v>
-      </c>
-      <c r="L6" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="Q6" s="5" t="n">
         <v>0</v>
@@ -1032,28 +1032,28 @@
         <v>14</v>
       </c>
       <c r="I7" t="n">
+        <v>17</v>
+      </c>
+      <c r="J7" t="n">
         <v>33</v>
       </c>
-      <c r="J7" t="n">
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
         <v>24</v>
-      </c>
-      <c r="K7" t="n">
-        <v>17</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1111,28 +1111,28 @@
         <v>52</v>
       </c>
       <c r="I8" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="J8" s="5" t="n">
         <v>33</v>
       </c>
-      <c r="J8" s="5" t="n">
+      <c r="K8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="K8" s="5" t="n">
-        <v>17</v>
-      </c>
-      <c r="L8" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="Q8" s="5" t="n">
         <v>0</v>
@@ -1190,28 +1190,28 @@
         <v>52</v>
       </c>
       <c r="I9" t="n">
+        <v>17</v>
+      </c>
+      <c r="J9" t="n">
         <v>33</v>
       </c>
-      <c r="J9" t="n">
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
         <v>24</v>
-      </c>
-      <c r="K9" t="n">
-        <v>17</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -1269,28 +1269,28 @@
         <v>52</v>
       </c>
       <c r="I10" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="J10" s="5" t="n">
         <v>33</v>
       </c>
-      <c r="J10" s="5" t="n">
+      <c r="K10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="K10" s="5" t="n">
-        <v>17</v>
-      </c>
-      <c r="L10" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="Q10" s="5" t="n">
         <v>0</v>
@@ -1348,28 +1348,28 @@
         <v>52</v>
       </c>
       <c r="I11" t="n">
+        <v>17</v>
+      </c>
+      <c r="J11" t="n">
         <v>33</v>
       </c>
-      <c r="J11" t="n">
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
         <v>24</v>
-      </c>
-      <c r="K11" t="n">
-        <v>17</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -1427,28 +1427,28 @@
         <v>52</v>
       </c>
       <c r="I12" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="J12" s="5" t="n">
         <v>33</v>
       </c>
-      <c r="J12" s="5" t="n">
+      <c r="K12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="K12" s="5" t="n">
-        <v>17</v>
-      </c>
-      <c r="L12" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="Q12" s="5" t="n">
         <v>0</v>
@@ -1506,28 +1506,28 @@
         <v>52</v>
       </c>
       <c r="I13" t="n">
+        <v>17</v>
+      </c>
+      <c r="J13" t="n">
         <v>33</v>
       </c>
-      <c r="J13" t="n">
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
         <v>24</v>
-      </c>
-      <c r="K13" t="n">
-        <v>17</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -1585,28 +1585,28 @@
         <v>2</v>
       </c>
       <c r="I14" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="J14" s="5" t="n">
         <v>33</v>
       </c>
-      <c r="J14" s="5" t="n">
+      <c r="K14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="K14" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="L14" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="Q14" s="5" t="n">
         <v>0</v>
@@ -1664,28 +1664,28 @@
         <v>52</v>
       </c>
       <c r="I15" t="n">
+        <v>17</v>
+      </c>
+      <c r="J15" t="n">
         <v>33</v>
       </c>
-      <c r="J15" t="n">
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
         <v>24</v>
-      </c>
-      <c r="K15" t="n">
-        <v>17</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -1743,28 +1743,28 @@
         <v>52</v>
       </c>
       <c r="I16" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="J16" s="5" t="n">
         <v>33</v>
       </c>
-      <c r="J16" s="5" t="n">
+      <c r="K16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="K16" s="5" t="n">
-        <v>17</v>
-      </c>
-      <c r="L16" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="Q16" s="5" t="n">
         <v>0</v>
@@ -1822,28 +1822,28 @@
         <v>52</v>
       </c>
       <c r="I17" t="n">
+        <v>17</v>
+      </c>
+      <c r="J17" t="n">
         <v>33</v>
       </c>
-      <c r="J17" t="n">
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
         <v>24</v>
-      </c>
-      <c r="K17" t="n">
-        <v>17</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -1901,28 +1901,28 @@
         <v>52</v>
       </c>
       <c r="I18" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="J18" s="5" t="n">
         <v>33</v>
       </c>
-      <c r="J18" s="5" t="n">
+      <c r="K18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="K18" s="5" t="n">
-        <v>17</v>
-      </c>
-      <c r="L18" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="Q18" s="5" t="n">
         <v>0</v>
@@ -1980,28 +1980,28 @@
         <v>50</v>
       </c>
       <c r="I19" t="n">
+        <v>17</v>
+      </c>
+      <c r="J19" t="n">
         <v>33</v>
       </c>
-      <c r="J19" t="n">
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
         <v>24</v>
-      </c>
-      <c r="K19" t="n">
-        <v>17</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -2059,28 +2059,28 @@
         <v>50</v>
       </c>
       <c r="I20" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="J20" s="5" t="n">
         <v>33</v>
       </c>
-      <c r="J20" s="5" t="n">
+      <c r="K20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="K20" s="5" t="n">
-        <v>17</v>
-      </c>
-      <c r="L20" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M20" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O20" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="Q20" s="5" t="n">
         <v>0</v>
@@ -2138,28 +2138,28 @@
         <v>14</v>
       </c>
       <c r="I21" t="n">
+        <v>17</v>
+      </c>
+      <c r="J21" t="n">
         <v>33</v>
       </c>
-      <c r="J21" t="n">
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
         <v>24</v>
-      </c>
-      <c r="K21" t="n">
-        <v>17</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" t="n">
-        <v>0</v>
-      </c>
-      <c r="O21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" t="n">
-        <v>0</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
@@ -2217,28 +2217,28 @@
         <v>50</v>
       </c>
       <c r="I22" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="J22" s="5" t="n">
         <v>33</v>
       </c>
-      <c r="J22" s="5" t="n">
+      <c r="K22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="K22" s="5" t="n">
-        <v>17</v>
-      </c>
-      <c r="L22" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M22" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N22" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O22" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="Q22" s="5" t="n">
         <v>0</v>
@@ -2296,28 +2296,28 @@
         <v>50</v>
       </c>
       <c r="I23" t="n">
+        <v>17</v>
+      </c>
+      <c r="J23" t="n">
         <v>33</v>
       </c>
-      <c r="J23" t="n">
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="n">
         <v>24</v>
-      </c>
-      <c r="K23" t="n">
-        <v>17</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
-      <c r="M23" t="n">
-        <v>0</v>
-      </c>
-      <c r="N23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P23" t="n">
-        <v>0</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
@@ -2375,28 +2375,28 @@
         <v>48</v>
       </c>
       <c r="I24" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="J24" s="5" t="n">
         <v>33</v>
       </c>
-      <c r="J24" s="5" t="n">
+      <c r="K24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="K24" s="5" t="n">
-        <v>17</v>
-      </c>
-      <c r="L24" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M24" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N24" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O24" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P24" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="Q24" s="5" t="n">
         <v>0</v>
@@ -2454,28 +2454,28 @@
         <v>48</v>
       </c>
       <c r="I25" t="n">
+        <v>17</v>
+      </c>
+      <c r="J25" t="n">
         <v>33</v>
       </c>
-      <c r="J25" t="n">
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" t="n">
         <v>24</v>
-      </c>
-      <c r="K25" t="n">
-        <v>17</v>
-      </c>
-      <c r="L25" t="n">
-        <v>0</v>
-      </c>
-      <c r="M25" t="n">
-        <v>0</v>
-      </c>
-      <c r="N25" t="n">
-        <v>0</v>
-      </c>
-      <c r="O25" t="n">
-        <v>0</v>
-      </c>
-      <c r="P25" t="n">
-        <v>0</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -2533,28 +2533,28 @@
         <v>48</v>
       </c>
       <c r="I26" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="J26" s="5" t="n">
         <v>33</v>
       </c>
-      <c r="J26" s="5" t="n">
+      <c r="K26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="K26" s="5" t="n">
-        <v>17</v>
-      </c>
-      <c r="L26" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M26" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N26" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O26" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P26" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="Q26" s="5" t="n">
         <v>0</v>
@@ -2612,28 +2612,28 @@
         <v>48</v>
       </c>
       <c r="I27" t="n">
+        <v>17</v>
+      </c>
+      <c r="J27" t="n">
         <v>33</v>
       </c>
-      <c r="J27" t="n">
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" t="n">
         <v>24</v>
-      </c>
-      <c r="K27" t="n">
-        <v>17</v>
-      </c>
-      <c r="L27" t="n">
-        <v>0</v>
-      </c>
-      <c r="M27" t="n">
-        <v>0</v>
-      </c>
-      <c r="N27" t="n">
-        <v>0</v>
-      </c>
-      <c r="O27" t="n">
-        <v>0</v>
-      </c>
-      <c r="P27" t="n">
-        <v>0</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
@@ -2691,13 +2691,13 @@
         <v>0</v>
       </c>
       <c r="I28" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="J28" s="5" t="n">
         <v>33</v>
       </c>
-      <c r="J28" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="K28" s="5" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="L28" s="5" t="n">
         <v>0</v>
@@ -2770,28 +2770,28 @@
         <v>48</v>
       </c>
       <c r="I29" t="n">
+        <v>17</v>
+      </c>
+      <c r="J29" t="n">
         <v>33</v>
       </c>
-      <c r="J29" t="n">
+      <c r="K29" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P29" t="n">
         <v>24</v>
-      </c>
-      <c r="K29" t="n">
-        <v>17</v>
-      </c>
-      <c r="L29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M29" t="n">
-        <v>0</v>
-      </c>
-      <c r="N29" t="n">
-        <v>0</v>
-      </c>
-      <c r="O29" t="n">
-        <v>0</v>
-      </c>
-      <c r="P29" t="n">
-        <v>0</v>
       </c>
       <c r="Q29" t="n">
         <v>0</v>
@@ -2849,28 +2849,28 @@
         <v>48</v>
       </c>
       <c r="I30" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="J30" s="5" t="n">
         <v>33</v>
       </c>
-      <c r="J30" s="5" t="n">
+      <c r="K30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P30" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="K30" s="5" t="n">
-        <v>17</v>
-      </c>
-      <c r="L30" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M30" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N30" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O30" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P30" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="Q30" s="5" t="n">
         <v>0</v>
@@ -2928,28 +2928,28 @@
         <v>48</v>
       </c>
       <c r="I31" t="n">
+        <v>17</v>
+      </c>
+      <c r="J31" t="n">
         <v>33</v>
       </c>
-      <c r="J31" t="n">
+      <c r="K31" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" t="n">
+        <v>0</v>
+      </c>
+      <c r="N31" t="n">
+        <v>0</v>
+      </c>
+      <c r="O31" t="n">
+        <v>0</v>
+      </c>
+      <c r="P31" t="n">
         <v>24</v>
-      </c>
-      <c r="K31" t="n">
-        <v>17</v>
-      </c>
-      <c r="L31" t="n">
-        <v>0</v>
-      </c>
-      <c r="M31" t="n">
-        <v>0</v>
-      </c>
-      <c r="N31" t="n">
-        <v>0</v>
-      </c>
-      <c r="O31" t="n">
-        <v>0</v>
-      </c>
-      <c r="P31" t="n">
-        <v>0</v>
       </c>
       <c r="Q31" t="n">
         <v>0</v>
@@ -3007,28 +3007,28 @@
         <v>48</v>
       </c>
       <c r="I32" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="J32" s="5" t="n">
         <v>33</v>
       </c>
-      <c r="J32" s="5" t="n">
+      <c r="K32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P32" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="K32" s="5" t="n">
-        <v>17</v>
-      </c>
-      <c r="L32" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M32" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N32" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O32" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P32" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="Q32" s="5" t="n">
         <v>0</v>
@@ -3086,28 +3086,28 @@
         <v>48</v>
       </c>
       <c r="I33" t="n">
+        <v>17</v>
+      </c>
+      <c r="J33" t="n">
         <v>33</v>
       </c>
-      <c r="J33" t="n">
+      <c r="K33" t="n">
+        <v>0</v>
+      </c>
+      <c r="L33" t="n">
+        <v>0</v>
+      </c>
+      <c r="M33" t="n">
+        <v>0</v>
+      </c>
+      <c r="N33" t="n">
+        <v>0</v>
+      </c>
+      <c r="O33" t="n">
+        <v>0</v>
+      </c>
+      <c r="P33" t="n">
         <v>24</v>
-      </c>
-      <c r="K33" t="n">
-        <v>17</v>
-      </c>
-      <c r="L33" t="n">
-        <v>0</v>
-      </c>
-      <c r="M33" t="n">
-        <v>0</v>
-      </c>
-      <c r="N33" t="n">
-        <v>0</v>
-      </c>
-      <c r="O33" t="n">
-        <v>0</v>
-      </c>
-      <c r="P33" t="n">
-        <v>0</v>
       </c>
       <c r="Q33" t="n">
         <v>0</v>
@@ -3165,28 +3165,28 @@
         <v>48</v>
       </c>
       <c r="I34" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="J34" s="5" t="n">
         <v>33</v>
       </c>
-      <c r="J34" s="5" t="n">
+      <c r="K34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P34" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="K34" s="5" t="n">
-        <v>17</v>
-      </c>
-      <c r="L34" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M34" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N34" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O34" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P34" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="Q34" s="5" t="n">
         <v>0</v>
@@ -3244,28 +3244,28 @@
         <v>48</v>
       </c>
       <c r="I35" t="n">
+        <v>17</v>
+      </c>
+      <c r="J35" t="n">
         <v>33</v>
       </c>
-      <c r="J35" t="n">
+      <c r="K35" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" t="n">
+        <v>0</v>
+      </c>
+      <c r="M35" t="n">
+        <v>0</v>
+      </c>
+      <c r="N35" t="n">
+        <v>0</v>
+      </c>
+      <c r="O35" t="n">
+        <v>0</v>
+      </c>
+      <c r="P35" t="n">
         <v>24</v>
-      </c>
-      <c r="K35" t="n">
-        <v>17</v>
-      </c>
-      <c r="L35" t="n">
-        <v>0</v>
-      </c>
-      <c r="M35" t="n">
-        <v>0</v>
-      </c>
-      <c r="N35" t="n">
-        <v>0</v>
-      </c>
-      <c r="O35" t="n">
-        <v>0</v>
-      </c>
-      <c r="P35" t="n">
-        <v>0</v>
       </c>
       <c r="Q35" t="n">
         <v>0</v>
@@ -3323,28 +3323,28 @@
         <v>48</v>
       </c>
       <c r="I36" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="J36" s="5" t="n">
         <v>33</v>
       </c>
-      <c r="J36" s="5" t="n">
+      <c r="K36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P36" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="K36" s="5" t="n">
-        <v>17</v>
-      </c>
-      <c r="L36" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M36" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N36" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O36" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P36" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="Q36" s="5" t="n">
         <v>0</v>
@@ -3402,28 +3402,28 @@
         <v>48</v>
       </c>
       <c r="I37" t="n">
+        <v>17</v>
+      </c>
+      <c r="J37" t="n">
         <v>33</v>
       </c>
-      <c r="J37" t="n">
+      <c r="K37" t="n">
+        <v>0</v>
+      </c>
+      <c r="L37" t="n">
+        <v>0</v>
+      </c>
+      <c r="M37" t="n">
+        <v>0</v>
+      </c>
+      <c r="N37" t="n">
+        <v>0</v>
+      </c>
+      <c r="O37" t="n">
+        <v>0</v>
+      </c>
+      <c r="P37" t="n">
         <v>24</v>
-      </c>
-      <c r="K37" t="n">
-        <v>17</v>
-      </c>
-      <c r="L37" t="n">
-        <v>0</v>
-      </c>
-      <c r="M37" t="n">
-        <v>0</v>
-      </c>
-      <c r="N37" t="n">
-        <v>0</v>
-      </c>
-      <c r="O37" t="n">
-        <v>0</v>
-      </c>
-      <c r="P37" t="n">
-        <v>0</v>
       </c>
       <c r="Q37" t="n">
         <v>0</v>
@@ -3481,28 +3481,28 @@
         <v>48</v>
       </c>
       <c r="I38" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="J38" s="5" t="n">
         <v>33</v>
       </c>
-      <c r="J38" s="5" t="n">
+      <c r="K38" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L38" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M38" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N38" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O38" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P38" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="K38" s="5" t="n">
-        <v>17</v>
-      </c>
-      <c r="L38" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M38" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N38" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O38" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P38" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="Q38" s="5" t="n">
         <v>0</v>
@@ -3560,28 +3560,28 @@
         <v>48</v>
       </c>
       <c r="I39" t="n">
+        <v>17</v>
+      </c>
+      <c r="J39" t="n">
         <v>33</v>
       </c>
-      <c r="J39" t="n">
+      <c r="K39" t="n">
+        <v>0</v>
+      </c>
+      <c r="L39" t="n">
+        <v>0</v>
+      </c>
+      <c r="M39" t="n">
+        <v>0</v>
+      </c>
+      <c r="N39" t="n">
+        <v>0</v>
+      </c>
+      <c r="O39" t="n">
+        <v>0</v>
+      </c>
+      <c r="P39" t="n">
         <v>24</v>
-      </c>
-      <c r="K39" t="n">
-        <v>17</v>
-      </c>
-      <c r="L39" t="n">
-        <v>0</v>
-      </c>
-      <c r="M39" t="n">
-        <v>0</v>
-      </c>
-      <c r="N39" t="n">
-        <v>0</v>
-      </c>
-      <c r="O39" t="n">
-        <v>0</v>
-      </c>
-      <c r="P39" t="n">
-        <v>0</v>
       </c>
       <c r="Q39" t="n">
         <v>0</v>
@@ -3639,28 +3639,28 @@
         <v>48</v>
       </c>
       <c r="I40" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="J40" s="5" t="n">
         <v>33</v>
       </c>
-      <c r="J40" s="5" t="n">
+      <c r="K40" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L40" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M40" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N40" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O40" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P40" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="K40" s="5" t="n">
-        <v>17</v>
-      </c>
-      <c r="L40" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M40" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N40" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O40" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P40" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="Q40" s="5" t="n">
         <v>0</v>
@@ -3718,28 +3718,28 @@
         <v>48</v>
       </c>
       <c r="I41" t="n">
+        <v>17</v>
+      </c>
+      <c r="J41" t="n">
         <v>33</v>
       </c>
-      <c r="J41" t="n">
+      <c r="K41" t="n">
+        <v>0</v>
+      </c>
+      <c r="L41" t="n">
+        <v>0</v>
+      </c>
+      <c r="M41" t="n">
+        <v>0</v>
+      </c>
+      <c r="N41" t="n">
+        <v>0</v>
+      </c>
+      <c r="O41" t="n">
+        <v>0</v>
+      </c>
+      <c r="P41" t="n">
         <v>24</v>
-      </c>
-      <c r="K41" t="n">
-        <v>17</v>
-      </c>
-      <c r="L41" t="n">
-        <v>0</v>
-      </c>
-      <c r="M41" t="n">
-        <v>0</v>
-      </c>
-      <c r="N41" t="n">
-        <v>0</v>
-      </c>
-      <c r="O41" t="n">
-        <v>0</v>
-      </c>
-      <c r="P41" t="n">
-        <v>0</v>
       </c>
       <c r="Q41" t="n">
         <v>0</v>
@@ -3797,28 +3797,28 @@
         <v>46</v>
       </c>
       <c r="I42" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="J42" s="5" t="n">
         <v>33</v>
       </c>
-      <c r="J42" s="5" t="n">
+      <c r="K42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P42" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="K42" s="5" t="n">
-        <v>17</v>
-      </c>
-      <c r="L42" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M42" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N42" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O42" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P42" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="Q42" s="5" t="n">
         <v>0</v>
@@ -3876,28 +3876,28 @@
         <v>48</v>
       </c>
       <c r="I43" t="n">
+        <v>17</v>
+      </c>
+      <c r="J43" t="n">
         <v>33</v>
       </c>
-      <c r="J43" t="n">
+      <c r="K43" t="n">
+        <v>0</v>
+      </c>
+      <c r="L43" t="n">
+        <v>0</v>
+      </c>
+      <c r="M43" t="n">
+        <v>0</v>
+      </c>
+      <c r="N43" t="n">
+        <v>0</v>
+      </c>
+      <c r="O43" t="n">
+        <v>0</v>
+      </c>
+      <c r="P43" t="n">
         <v>24</v>
-      </c>
-      <c r="K43" t="n">
-        <v>17</v>
-      </c>
-      <c r="L43" t="n">
-        <v>0</v>
-      </c>
-      <c r="M43" t="n">
-        <v>0</v>
-      </c>
-      <c r="N43" t="n">
-        <v>0</v>
-      </c>
-      <c r="O43" t="n">
-        <v>0</v>
-      </c>
-      <c r="P43" t="n">
-        <v>0</v>
       </c>
       <c r="Q43" t="n">
         <v>0</v>
@@ -3955,28 +3955,28 @@
         <v>48</v>
       </c>
       <c r="I44" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="J44" s="5" t="n">
         <v>33</v>
       </c>
-      <c r="J44" s="5" t="n">
+      <c r="K44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P44" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="K44" s="5" t="n">
-        <v>17</v>
-      </c>
-      <c r="L44" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M44" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N44" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O44" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P44" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="Q44" s="5" t="n">
         <v>0</v>
@@ -4034,28 +4034,28 @@
         <v>48</v>
       </c>
       <c r="I45" t="n">
+        <v>17</v>
+      </c>
+      <c r="J45" t="n">
         <v>33</v>
       </c>
-      <c r="J45" t="n">
+      <c r="K45" t="n">
+        <v>0</v>
+      </c>
+      <c r="L45" t="n">
+        <v>0</v>
+      </c>
+      <c r="M45" t="n">
+        <v>0</v>
+      </c>
+      <c r="N45" t="n">
+        <v>0</v>
+      </c>
+      <c r="O45" t="n">
+        <v>0</v>
+      </c>
+      <c r="P45" t="n">
         <v>24</v>
-      </c>
-      <c r="K45" t="n">
-        <v>17</v>
-      </c>
-      <c r="L45" t="n">
-        <v>0</v>
-      </c>
-      <c r="M45" t="n">
-        <v>0</v>
-      </c>
-      <c r="N45" t="n">
-        <v>0</v>
-      </c>
-      <c r="O45" t="n">
-        <v>0</v>
-      </c>
-      <c r="P45" t="n">
-        <v>0</v>
       </c>
       <c r="Q45" t="n">
         <v>0</v>
@@ -4113,28 +4113,28 @@
         <v>48</v>
       </c>
       <c r="I46" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="J46" s="5" t="n">
         <v>33</v>
       </c>
-      <c r="J46" s="5" t="n">
+      <c r="K46" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L46" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M46" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N46" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O46" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P46" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="K46" s="5" t="n">
-        <v>17</v>
-      </c>
-      <c r="L46" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M46" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N46" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O46" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P46" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="Q46" s="5" t="n">
         <v>0</v>
@@ -4192,28 +4192,28 @@
         <v>48</v>
       </c>
       <c r="I47" t="n">
+        <v>17</v>
+      </c>
+      <c r="J47" t="n">
         <v>33</v>
       </c>
-      <c r="J47" t="n">
+      <c r="K47" t="n">
+        <v>0</v>
+      </c>
+      <c r="L47" t="n">
+        <v>0</v>
+      </c>
+      <c r="M47" t="n">
+        <v>0</v>
+      </c>
+      <c r="N47" t="n">
+        <v>0</v>
+      </c>
+      <c r="O47" t="n">
+        <v>0</v>
+      </c>
+      <c r="P47" t="n">
         <v>24</v>
-      </c>
-      <c r="K47" t="n">
-        <v>17</v>
-      </c>
-      <c r="L47" t="n">
-        <v>0</v>
-      </c>
-      <c r="M47" t="n">
-        <v>0</v>
-      </c>
-      <c r="N47" t="n">
-        <v>0</v>
-      </c>
-      <c r="O47" t="n">
-        <v>0</v>
-      </c>
-      <c r="P47" t="n">
-        <v>0</v>
       </c>
       <c r="Q47" t="n">
         <v>0</v>
@@ -4271,28 +4271,28 @@
         <v>48</v>
       </c>
       <c r="I48" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="J48" s="5" t="n">
         <v>33</v>
       </c>
-      <c r="J48" s="5" t="n">
+      <c r="K48" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L48" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M48" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N48" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O48" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P48" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="K48" s="5" t="n">
-        <v>17</v>
-      </c>
-      <c r="L48" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M48" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N48" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O48" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P48" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="Q48" s="5" t="n">
         <v>0</v>
@@ -4350,28 +4350,28 @@
         <v>0</v>
       </c>
       <c r="I49" t="n">
+        <v>17</v>
+      </c>
+      <c r="J49" t="n">
         <v>33</v>
       </c>
-      <c r="J49" t="n">
+      <c r="K49" t="n">
+        <v>0</v>
+      </c>
+      <c r="L49" t="n">
+        <v>0</v>
+      </c>
+      <c r="M49" t="n">
+        <v>0</v>
+      </c>
+      <c r="N49" t="n">
+        <v>0</v>
+      </c>
+      <c r="O49" t="n">
+        <v>0</v>
+      </c>
+      <c r="P49" t="n">
         <v>24</v>
-      </c>
-      <c r="K49" t="n">
-        <v>17</v>
-      </c>
-      <c r="L49" t="n">
-        <v>0</v>
-      </c>
-      <c r="M49" t="n">
-        <v>0</v>
-      </c>
-      <c r="N49" t="n">
-        <v>0</v>
-      </c>
-      <c r="O49" t="n">
-        <v>0</v>
-      </c>
-      <c r="P49" t="n">
-        <v>0</v>
       </c>
       <c r="Q49" t="n">
         <v>0</v>
@@ -4429,28 +4429,28 @@
         <v>48</v>
       </c>
       <c r="I50" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="J50" s="5" t="n">
         <v>33</v>
       </c>
-      <c r="J50" s="5" t="n">
+      <c r="K50" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L50" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M50" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N50" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O50" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P50" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="K50" s="5" t="n">
-        <v>17</v>
-      </c>
-      <c r="L50" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M50" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N50" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O50" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P50" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="Q50" s="5" t="n">
         <v>0</v>
@@ -4508,28 +4508,28 @@
         <v>48</v>
       </c>
       <c r="I51" t="n">
+        <v>17</v>
+      </c>
+      <c r="J51" t="n">
         <v>33</v>
       </c>
-      <c r="J51" t="n">
+      <c r="K51" t="n">
+        <v>0</v>
+      </c>
+      <c r="L51" t="n">
+        <v>0</v>
+      </c>
+      <c r="M51" t="n">
+        <v>0</v>
+      </c>
+      <c r="N51" t="n">
+        <v>0</v>
+      </c>
+      <c r="O51" t="n">
+        <v>0</v>
+      </c>
+      <c r="P51" t="n">
         <v>24</v>
-      </c>
-      <c r="K51" t="n">
-        <v>17</v>
-      </c>
-      <c r="L51" t="n">
-        <v>0</v>
-      </c>
-      <c r="M51" t="n">
-        <v>0</v>
-      </c>
-      <c r="N51" t="n">
-        <v>0</v>
-      </c>
-      <c r="O51" t="n">
-        <v>0</v>
-      </c>
-      <c r="P51" t="n">
-        <v>0</v>
       </c>
       <c r="Q51" t="n">
         <v>0</v>
@@ -4587,28 +4587,28 @@
         <v>48</v>
       </c>
       <c r="I52" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="J52" s="5" t="n">
         <v>30</v>
       </c>
-      <c r="J52" s="5" t="n">
+      <c r="K52" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L52" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M52" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N52" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O52" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P52" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="K52" s="5" t="n">
-        <v>17</v>
-      </c>
-      <c r="L52" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M52" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N52" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O52" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P52" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="Q52" s="5" t="n">
         <v>0</v>
@@ -4666,28 +4666,28 @@
         <v>48</v>
       </c>
       <c r="I53" t="n">
+        <v>17</v>
+      </c>
+      <c r="J53" t="n">
         <v>30</v>
       </c>
-      <c r="J53" t="n">
+      <c r="K53" t="n">
+        <v>0</v>
+      </c>
+      <c r="L53" t="n">
+        <v>0</v>
+      </c>
+      <c r="M53" t="n">
+        <v>0</v>
+      </c>
+      <c r="N53" t="n">
+        <v>0</v>
+      </c>
+      <c r="O53" t="n">
+        <v>0</v>
+      </c>
+      <c r="P53" t="n">
         <v>24</v>
-      </c>
-      <c r="K53" t="n">
-        <v>17</v>
-      </c>
-      <c r="L53" t="n">
-        <v>0</v>
-      </c>
-      <c r="M53" t="n">
-        <v>0</v>
-      </c>
-      <c r="N53" t="n">
-        <v>0</v>
-      </c>
-      <c r="O53" t="n">
-        <v>0</v>
-      </c>
-      <c r="P53" t="n">
-        <v>0</v>
       </c>
       <c r="Q53" t="n">
         <v>0</v>
@@ -4745,28 +4745,28 @@
         <v>48</v>
       </c>
       <c r="I54" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="J54" s="5" t="n">
         <v>30</v>
       </c>
-      <c r="J54" s="5" t="n">
+      <c r="K54" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L54" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M54" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N54" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O54" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P54" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="K54" s="5" t="n">
-        <v>17</v>
-      </c>
-      <c r="L54" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M54" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N54" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O54" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P54" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="Q54" s="5" t="n">
         <v>0</v>
@@ -4824,28 +4824,28 @@
         <v>2</v>
       </c>
       <c r="I55" t="n">
+        <v>17</v>
+      </c>
+      <c r="J55" t="n">
         <v>30</v>
       </c>
-      <c r="J55" t="n">
+      <c r="K55" t="n">
+        <v>0</v>
+      </c>
+      <c r="L55" t="n">
+        <v>0</v>
+      </c>
+      <c r="M55" t="n">
+        <v>0</v>
+      </c>
+      <c r="N55" t="n">
+        <v>0</v>
+      </c>
+      <c r="O55" t="n">
+        <v>0</v>
+      </c>
+      <c r="P55" t="n">
         <v>24</v>
-      </c>
-      <c r="K55" t="n">
-        <v>17</v>
-      </c>
-      <c r="L55" t="n">
-        <v>0</v>
-      </c>
-      <c r="M55" t="n">
-        <v>0</v>
-      </c>
-      <c r="N55" t="n">
-        <v>0</v>
-      </c>
-      <c r="O55" t="n">
-        <v>0</v>
-      </c>
-      <c r="P55" t="n">
-        <v>0</v>
       </c>
       <c r="Q55" t="n">
         <v>0</v>
@@ -4903,28 +4903,28 @@
         <v>48</v>
       </c>
       <c r="I56" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="J56" s="5" t="n">
         <v>30</v>
       </c>
-      <c r="J56" s="5" t="n">
+      <c r="K56" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L56" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M56" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N56" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O56" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P56" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="K56" s="5" t="n">
-        <v>17</v>
-      </c>
-      <c r="L56" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M56" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N56" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O56" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P56" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="Q56" s="5" t="n">
         <v>0</v>
@@ -4982,13 +4982,13 @@
         <v>48</v>
       </c>
       <c r="I57" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J57" t="n">
         <v>24</v>
       </c>
       <c r="K57" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="L57" t="n">
         <v>0</v>
@@ -5003,7 +5003,7 @@
         <v>0</v>
       </c>
       <c r="P57" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="Q57" t="n">
         <v>0</v>
@@ -5061,28 +5061,28 @@
         <v>47</v>
       </c>
       <c r="I58" s="5" t="n">
+        <v>22</v>
+      </c>
+      <c r="J58" s="5" t="n">
         <v>26</v>
       </c>
-      <c r="J58" s="5" t="n">
+      <c r="K58" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L58" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M58" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N58" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O58" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P58" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="K58" s="5" t="n">
-        <v>22</v>
-      </c>
-      <c r="L58" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M58" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N58" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O58" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P58" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="Q58" s="5" t="n">
         <v>0</v>
@@ -5140,28 +5140,28 @@
         <v>47</v>
       </c>
       <c r="I59" t="n">
+        <v>16</v>
+      </c>
+      <c r="J59" t="n">
         <v>26</v>
       </c>
-      <c r="J59" t="n">
+      <c r="K59" t="n">
+        <v>0</v>
+      </c>
+      <c r="L59" t="n">
+        <v>0</v>
+      </c>
+      <c r="M59" t="n">
+        <v>0</v>
+      </c>
+      <c r="N59" t="n">
+        <v>0</v>
+      </c>
+      <c r="O59" t="n">
+        <v>0</v>
+      </c>
+      <c r="P59" t="n">
         <v>24</v>
-      </c>
-      <c r="K59" t="n">
-        <v>16</v>
-      </c>
-      <c r="L59" t="n">
-        <v>0</v>
-      </c>
-      <c r="M59" t="n">
-        <v>0</v>
-      </c>
-      <c r="N59" t="n">
-        <v>0</v>
-      </c>
-      <c r="O59" t="n">
-        <v>0</v>
-      </c>
-      <c r="P59" t="n">
-        <v>0</v>
       </c>
       <c r="Q59" t="n">
         <v>0</v>
@@ -5219,28 +5219,28 @@
         <v>46</v>
       </c>
       <c r="I60" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="J60" s="5" t="n">
         <v>23</v>
       </c>
-      <c r="J60" s="5" t="n">
+      <c r="K60" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L60" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M60" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N60" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O60" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P60" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="K60" s="5" t="n">
-        <v>16</v>
-      </c>
-      <c r="L60" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M60" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N60" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O60" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P60" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="Q60" s="5" t="n">
         <v>0</v>
@@ -5298,28 +5298,28 @@
         <v>43</v>
       </c>
       <c r="I61" t="n">
+        <v>16</v>
+      </c>
+      <c r="J61" t="n">
         <v>29</v>
       </c>
-      <c r="J61" t="n">
+      <c r="K61" t="n">
+        <v>0</v>
+      </c>
+      <c r="L61" t="n">
+        <v>0</v>
+      </c>
+      <c r="M61" t="n">
+        <v>0</v>
+      </c>
+      <c r="N61" t="n">
+        <v>0</v>
+      </c>
+      <c r="O61" t="n">
+        <v>0</v>
+      </c>
+      <c r="P61" t="n">
         <v>24</v>
-      </c>
-      <c r="K61" t="n">
-        <v>16</v>
-      </c>
-      <c r="L61" t="n">
-        <v>0</v>
-      </c>
-      <c r="M61" t="n">
-        <v>0</v>
-      </c>
-      <c r="N61" t="n">
-        <v>0</v>
-      </c>
-      <c r="O61" t="n">
-        <v>0</v>
-      </c>
-      <c r="P61" t="n">
-        <v>0</v>
       </c>
       <c r="Q61" t="n">
         <v>0</v>
@@ -5377,28 +5377,28 @@
         <v>43</v>
       </c>
       <c r="I62" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="J62" s="5" t="n">
         <v>29</v>
       </c>
-      <c r="J62" s="5" t="n">
+      <c r="K62" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L62" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M62" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N62" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O62" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P62" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="K62" s="5" t="n">
-        <v>16</v>
-      </c>
-      <c r="L62" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M62" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N62" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O62" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P62" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="Q62" s="5" t="n">
         <v>0</v>
@@ -5456,28 +5456,28 @@
         <v>43</v>
       </c>
       <c r="I63" t="n">
+        <v>16</v>
+      </c>
+      <c r="J63" t="n">
         <v>29</v>
       </c>
-      <c r="J63" t="n">
+      <c r="K63" t="n">
+        <v>0</v>
+      </c>
+      <c r="L63" t="n">
+        <v>0</v>
+      </c>
+      <c r="M63" t="n">
+        <v>0</v>
+      </c>
+      <c r="N63" t="n">
+        <v>0</v>
+      </c>
+      <c r="O63" t="n">
+        <v>0</v>
+      </c>
+      <c r="P63" t="n">
         <v>24</v>
-      </c>
-      <c r="K63" t="n">
-        <v>16</v>
-      </c>
-      <c r="L63" t="n">
-        <v>0</v>
-      </c>
-      <c r="M63" t="n">
-        <v>0</v>
-      </c>
-      <c r="N63" t="n">
-        <v>0</v>
-      </c>
-      <c r="O63" t="n">
-        <v>0</v>
-      </c>
-      <c r="P63" t="n">
-        <v>0</v>
       </c>
       <c r="Q63" t="n">
         <v>0</v>
@@ -5535,28 +5535,28 @@
         <v>42</v>
       </c>
       <c r="I64" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="J64" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="J64" s="5" t="n">
+      <c r="K64" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L64" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M64" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N64" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O64" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P64" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="K64" s="5" t="n">
-        <v>16</v>
-      </c>
-      <c r="L64" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M64" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N64" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O64" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P64" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="Q64" s="5" t="n">
         <v>0</v>
@@ -5614,28 +5614,28 @@
         <v>46</v>
       </c>
       <c r="I65" t="n">
+        <v>21</v>
+      </c>
+      <c r="J65" t="n">
         <v>20</v>
       </c>
-      <c r="J65" t="n">
+      <c r="K65" t="n">
+        <v>0</v>
+      </c>
+      <c r="L65" t="n">
+        <v>0</v>
+      </c>
+      <c r="M65" t="n">
+        <v>0</v>
+      </c>
+      <c r="N65" t="n">
+        <v>0</v>
+      </c>
+      <c r="O65" t="n">
+        <v>0</v>
+      </c>
+      <c r="P65" t="n">
         <v>24</v>
-      </c>
-      <c r="K65" t="n">
-        <v>21</v>
-      </c>
-      <c r="L65" t="n">
-        <v>0</v>
-      </c>
-      <c r="M65" t="n">
-        <v>0</v>
-      </c>
-      <c r="N65" t="n">
-        <v>0</v>
-      </c>
-      <c r="O65" t="n">
-        <v>0</v>
-      </c>
-      <c r="P65" t="n">
-        <v>0</v>
       </c>
       <c r="Q65" t="n">
         <v>0</v>
@@ -5693,28 +5693,28 @@
         <v>42</v>
       </c>
       <c r="I66" s="5" t="n">
+        <v>21</v>
+      </c>
+      <c r="J66" s="5" t="n">
         <v>26</v>
       </c>
-      <c r="J66" s="5" t="n">
+      <c r="K66" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L66" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M66" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N66" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O66" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P66" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="K66" s="5" t="n">
-        <v>21</v>
-      </c>
-      <c r="L66" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M66" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N66" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O66" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P66" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="Q66" s="5" t="n">
         <v>0</v>
@@ -5772,10 +5772,13 @@
         <v>53</v>
       </c>
       <c r="I67" t="n">
+        <v>21</v>
+      </c>
+      <c r="J67" t="n">
         <v>26</v>
       </c>
       <c r="K67" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="L67" t="n">
         <v>0</v>
@@ -5787,9 +5790,6 @@
         <v>0</v>
       </c>
       <c r="O67" t="n">
-        <v>0</v>
-      </c>
-      <c r="P67" t="n">
         <v>0</v>
       </c>
       <c r="Q67" t="n">
@@ -5848,28 +5848,28 @@
         <v>53</v>
       </c>
       <c r="I68" s="5" t="n">
+        <v>21</v>
+      </c>
+      <c r="J68" s="5" t="n">
         <v>26</v>
       </c>
-      <c r="J68" s="5" t="n">
+      <c r="K68" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L68" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M68" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N68" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O68" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P68" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="K68" s="5" t="n">
-        <v>21</v>
-      </c>
-      <c r="L68" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M68" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N68" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O68" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P68" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="Q68" s="5" t="n">
         <v>0</v>
@@ -5924,10 +5924,13 @@
         <v>0</v>
       </c>
       <c r="I69" t="n">
+        <v>21</v>
+      </c>
+      <c r="J69" t="n">
         <v>26</v>
       </c>
       <c r="K69" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="L69" t="n">
         <v>0</v>
@@ -5939,9 +5942,6 @@
         <v>0</v>
       </c>
       <c r="O69" t="n">
-        <v>0</v>
-      </c>
-      <c r="P69" t="n">
         <v>0</v>
       </c>
       <c r="Q69" t="n">
@@ -6000,28 +6000,28 @@
         <v>53</v>
       </c>
       <c r="I70" s="5" t="n">
+        <v>21</v>
+      </c>
+      <c r="J70" s="5" t="n">
         <v>26</v>
       </c>
-      <c r="J70" s="5" t="n">
+      <c r="K70" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L70" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M70" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N70" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O70" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P70" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="K70" s="5" t="n">
-        <v>21</v>
-      </c>
-      <c r="L70" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M70" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N70" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O70" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P70" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="Q70" s="5" t="n">
         <v>0</v>
@@ -6079,28 +6079,28 @@
         <v>42</v>
       </c>
       <c r="I71" t="n">
+        <v>21</v>
+      </c>
+      <c r="J71" t="n">
         <v>26</v>
       </c>
-      <c r="J71" t="n">
+      <c r="K71" t="n">
+        <v>0</v>
+      </c>
+      <c r="L71" t="n">
+        <v>0</v>
+      </c>
+      <c r="M71" t="n">
+        <v>0</v>
+      </c>
+      <c r="N71" t="n">
+        <v>0</v>
+      </c>
+      <c r="O71" t="n">
+        <v>0</v>
+      </c>
+      <c r="P71" t="n">
         <v>24</v>
-      </c>
-      <c r="K71" t="n">
-        <v>21</v>
-      </c>
-      <c r="L71" t="n">
-        <v>0</v>
-      </c>
-      <c r="M71" t="n">
-        <v>0</v>
-      </c>
-      <c r="N71" t="n">
-        <v>0</v>
-      </c>
-      <c r="O71" t="n">
-        <v>0</v>
-      </c>
-      <c r="P71" t="n">
-        <v>0</v>
       </c>
       <c r="Q71" t="n">
         <v>0</v>
@@ -6158,28 +6158,28 @@
         <v>42</v>
       </c>
       <c r="I72" s="5" t="n">
+        <v>21</v>
+      </c>
+      <c r="J72" s="5" t="n">
         <v>26</v>
       </c>
-      <c r="J72" s="5" t="n">
+      <c r="K72" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L72" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M72" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N72" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O72" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P72" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="K72" s="5" t="n">
-        <v>21</v>
-      </c>
-      <c r="L72" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M72" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N72" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O72" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P72" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="Q72" s="5" t="n">
         <v>0</v>
@@ -6237,28 +6237,28 @@
         <v>42</v>
       </c>
       <c r="I73" t="n">
+        <v>19</v>
+      </c>
+      <c r="J73" t="n">
         <v>26</v>
       </c>
-      <c r="J73" t="n">
+      <c r="K73" t="n">
+        <v>0</v>
+      </c>
+      <c r="L73" t="n">
+        <v>0</v>
+      </c>
+      <c r="M73" t="n">
+        <v>0</v>
+      </c>
+      <c r="N73" t="n">
+        <v>0</v>
+      </c>
+      <c r="O73" t="n">
+        <v>0</v>
+      </c>
+      <c r="P73" t="n">
         <v>24</v>
-      </c>
-      <c r="K73" t="n">
-        <v>19</v>
-      </c>
-      <c r="L73" t="n">
-        <v>0</v>
-      </c>
-      <c r="M73" t="n">
-        <v>0</v>
-      </c>
-      <c r="N73" t="n">
-        <v>0</v>
-      </c>
-      <c r="O73" t="n">
-        <v>0</v>
-      </c>
-      <c r="P73" t="n">
-        <v>0</v>
       </c>
       <c r="Q73" t="n">
         <v>0</v>
@@ -6316,28 +6316,28 @@
         <v>42</v>
       </c>
       <c r="I74" s="5" t="n">
+        <v>23</v>
+      </c>
+      <c r="J74" s="5" t="n">
         <v>26</v>
       </c>
-      <c r="J74" s="5" t="n">
+      <c r="K74" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L74" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M74" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N74" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O74" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P74" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="K74" s="5" t="n">
-        <v>23</v>
-      </c>
-      <c r="L74" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M74" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N74" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O74" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P74" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="Q74" s="5" t="n">
         <v>0</v>
@@ -6395,28 +6395,28 @@
         <v>42</v>
       </c>
       <c r="I75" t="n">
+        <v>23</v>
+      </c>
+      <c r="J75" t="n">
         <v>26</v>
       </c>
-      <c r="J75" t="n">
+      <c r="K75" t="n">
+        <v>0</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0</v>
+      </c>
+      <c r="N75" t="n">
+        <v>0</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
         <v>24</v>
-      </c>
-      <c r="K75" t="n">
-        <v>23</v>
-      </c>
-      <c r="L75" t="n">
-        <v>0</v>
-      </c>
-      <c r="M75" t="n">
-        <v>0</v>
-      </c>
-      <c r="N75" t="n">
-        <v>0</v>
-      </c>
-      <c r="O75" t="n">
-        <v>0</v>
-      </c>
-      <c r="P75" t="n">
-        <v>0</v>
       </c>
       <c r="Q75" t="n">
         <v>0</v>
@@ -6474,43 +6474,43 @@
         <v>42</v>
       </c>
       <c r="I76" s="5" t="n">
+        <v>23</v>
+      </c>
+      <c r="J76" s="5" t="n">
         <v>26</v>
       </c>
-      <c r="J76" s="5" t="n">
+      <c r="K76" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L76" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M76" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N76" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O76" s="5" t="n"/>
+      <c r="P76" s="5" t="n">
         <v>24</v>
       </c>
-      <c r="K76" s="5" t="n">
-        <v>23</v>
-      </c>
-      <c r="L76" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M76" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N76" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O76" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P76" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="Q76" s="5" t="n">
         <v>0</v>
       </c>
       <c r="R76" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="S76" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="S76" s="5" t="n"/>
       <c r="T76" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="U76" s="5" t="n"/>
-      <c r="V76" s="5" t="n"/>
+      <c r="U76" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V76" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="W76" s="5" t="n">
         <v>0</v>
       </c>
@@ -6549,10 +6549,13 @@
         <v>42</v>
       </c>
       <c r="I77" t="n">
+        <v>23</v>
+      </c>
+      <c r="J77" t="n">
         <v>26</v>
       </c>
       <c r="K77" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="L77" t="n">
         <v>0</v>
@@ -6564,9 +6567,6 @@
         <v>0</v>
       </c>
       <c r="O77" t="n">
-        <v>0</v>
-      </c>
-      <c r="P77" t="n">
         <v>0</v>
       </c>
       <c r="Q77" t="n">
@@ -6625,28 +6625,28 @@
         <v>42</v>
       </c>
       <c r="I78" s="5" t="n">
+        <v>23</v>
+      </c>
+      <c r="J78" s="5" t="n">
         <v>26</v>
       </c>
-      <c r="J78" s="5" t="n">
+      <c r="K78" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L78" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M78" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N78" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O78" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P78" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="K78" s="5" t="n">
-        <v>23</v>
-      </c>
-      <c r="L78" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M78" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N78" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O78" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P78" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="Q78" s="5" t="n">
         <v>0</v>
@@ -6704,10 +6704,13 @@
         <v>42</v>
       </c>
       <c r="I79" t="n">
+        <v>23</v>
+      </c>
+      <c r="J79" t="n">
         <v>26</v>
       </c>
       <c r="K79" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="L79" t="n">
         <v>0</v>
@@ -6719,9 +6722,6 @@
         <v>0</v>
       </c>
       <c r="O79" t="n">
-        <v>0</v>
-      </c>
-      <c r="P79" t="n">
         <v>0</v>
       </c>
       <c r="Q79" t="n">
@@ -6780,11 +6780,13 @@
         <v>42</v>
       </c>
       <c r="I80" s="5" t="n">
+        <v>23</v>
+      </c>
+      <c r="J80" s="5" t="n">
         <v>26</v>
       </c>
-      <c r="J80" s="5" t="n"/>
       <c r="K80" s="5" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="L80" s="5" t="n">
         <v>0</v>
@@ -6798,9 +6800,7 @@
       <c r="O80" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="P80" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="P80" s="5" t="n"/>
       <c r="Q80" s="5" t="n">
         <v>0</v>
       </c>
@@ -6857,28 +6857,28 @@
         <v>42</v>
       </c>
       <c r="I81" t="n">
+        <v>23</v>
+      </c>
+      <c r="J81" t="n">
         <v>26</v>
       </c>
-      <c r="J81" t="n">
+      <c r="K81" t="n">
+        <v>0</v>
+      </c>
+      <c r="L81" t="n">
+        <v>0</v>
+      </c>
+      <c r="M81" t="n">
+        <v>0</v>
+      </c>
+      <c r="N81" t="n">
+        <v>0</v>
+      </c>
+      <c r="O81" t="n">
+        <v>0</v>
+      </c>
+      <c r="P81" t="n">
         <v>24</v>
-      </c>
-      <c r="K81" t="n">
-        <v>23</v>
-      </c>
-      <c r="L81" t="n">
-        <v>0</v>
-      </c>
-      <c r="M81" t="n">
-        <v>0</v>
-      </c>
-      <c r="N81" t="n">
-        <v>0</v>
-      </c>
-      <c r="O81" t="n">
-        <v>0</v>
-      </c>
-      <c r="P81" t="n">
-        <v>0</v>
       </c>
       <c r="Q81" t="n">
         <v>0</v>
@@ -6936,11 +6936,13 @@
         <v>42</v>
       </c>
       <c r="I82" s="5" t="n">
+        <v>23</v>
+      </c>
+      <c r="J82" s="5" t="n">
         <v>26</v>
       </c>
-      <c r="J82" s="5" t="n"/>
       <c r="K82" s="5" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="L82" s="5" t="n">
         <v>0</v>
@@ -6954,9 +6956,7 @@
       <c r="O82" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="P82" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="P82" s="5" t="n"/>
       <c r="Q82" s="5" t="n">
         <v>0</v>
       </c>
@@ -7010,28 +7010,28 @@
         <v>0</v>
       </c>
       <c r="I83" t="n">
+        <v>23</v>
+      </c>
+      <c r="J83" t="n">
         <v>26</v>
       </c>
-      <c r="J83" t="n">
+      <c r="K83" t="n">
+        <v>0</v>
+      </c>
+      <c r="L83" t="n">
+        <v>0</v>
+      </c>
+      <c r="M83" t="n">
+        <v>0</v>
+      </c>
+      <c r="N83" t="n">
+        <v>0</v>
+      </c>
+      <c r="O83" t="n">
+        <v>0</v>
+      </c>
+      <c r="P83" t="n">
         <v>24</v>
-      </c>
-      <c r="K83" t="n">
-        <v>23</v>
-      </c>
-      <c r="L83" t="n">
-        <v>0</v>
-      </c>
-      <c r="M83" t="n">
-        <v>0</v>
-      </c>
-      <c r="N83" t="n">
-        <v>0</v>
-      </c>
-      <c r="O83" t="n">
-        <v>0</v>
-      </c>
-      <c r="P83" t="n">
-        <v>0</v>
       </c>
       <c r="Q83" t="n">
         <v>0</v>
@@ -7089,54 +7089,130 @@
         <v>42</v>
       </c>
       <c r="I84" s="5" t="n">
+        <v>23</v>
+      </c>
+      <c r="J84" s="5" t="n">
         <v>26</v>
       </c>
-      <c r="J84" s="5" t="n">
+      <c r="K84" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L84" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M84" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N84" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O84" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P84" s="5" t="n">
         <v>24</v>
       </c>
-      <c r="K84" s="5" t="n">
+      <c r="Q84" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R84" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S84" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T84" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U84" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V84" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W84" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X84" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y84" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B85" t="n">
+        <v>918</v>
+      </c>
+      <c r="C85" t="n">
+        <v>523</v>
+      </c>
+      <c r="D85" t="n">
+        <v>383</v>
+      </c>
+      <c r="E85" t="n">
+        <v>352</v>
+      </c>
+      <c r="F85" t="n">
+        <v>211</v>
+      </c>
+      <c r="G85" t="n">
+        <v>94</v>
+      </c>
+      <c r="H85" t="n">
+        <v>42</v>
+      </c>
+      <c r="I85" t="n">
         <v>23</v>
       </c>
-      <c r="L84" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M84" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N84" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O84" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P84" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q84" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R84" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S84" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T84" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U84" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V84" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W84" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="X84" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y84" s="5" t="n">
+      <c r="J85" t="n">
+        <v>15</v>
+      </c>
+      <c r="K85" t="n">
+        <v>0</v>
+      </c>
+      <c r="L85" t="n">
+        <v>0</v>
+      </c>
+      <c r="M85" t="n">
+        <v>0</v>
+      </c>
+      <c r="N85" t="n">
+        <v>0</v>
+      </c>
+      <c r="O85" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q85" t="n">
+        <v>0</v>
+      </c>
+      <c r="R85" t="n">
+        <v>0</v>
+      </c>
+      <c r="S85" t="n">
+        <v>0</v>
+      </c>
+      <c r="T85" t="n">
+        <v>0</v>
+      </c>
+      <c r="U85" t="n">
+        <v>0</v>
+      </c>
+      <c r="V85" t="n">
+        <v>0</v>
+      </c>
+      <c r="W85" t="n">
+        <v>0</v>
+      </c>
+      <c r="X85" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y85" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7178,7 +7254,7 @@
       </c>
       <c r="D1" s="3" t="inlineStr">
         <is>
-          <t>Lager (2026-09-28)</t>
+          <t>Lager (2026-09-29)</t>
         </is>
       </c>
     </row>
@@ -7199,7 +7275,7 @@
         </is>
       </c>
       <c r="D2" s="4" t="n">
-        <v>526</v>
+        <v>523</v>
       </c>
     </row>
     <row r="3">
@@ -12385,12 +12461,12 @@
     <row r="262">
       <c r="A262" s="4" t="inlineStr">
         <is>
-          <t>7011676</t>
+          <t>7013678</t>
         </is>
       </c>
       <c r="B262" s="5" t="inlineStr">
         <is>
-          <t>Infälld interiörarmatur Diana Flat LED 300x300</t>
+          <t>Infälld Interiörarmatur LED DPML Tunable White</t>
         </is>
       </c>
       <c r="C262" s="5" t="inlineStr">
@@ -12405,7 +12481,7 @@
     <row r="263">
       <c r="A263" s="6" t="inlineStr">
         <is>
-          <t>7011677</t>
+          <t>7011676</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -12425,12 +12501,12 @@
     <row r="264">
       <c r="A264" s="4" t="inlineStr">
         <is>
-          <t>7013193</t>
+          <t>7011677</t>
         </is>
       </c>
       <c r="B264" s="5" t="inlineStr">
         <is>
-          <t>Infälld interiörarmatur Diana Flat LED 600x600</t>
+          <t>Infälld interiörarmatur Diana Flat LED 300x300</t>
         </is>
       </c>
       <c r="C264" s="5" t="inlineStr">
@@ -12445,7 +12521,7 @@
     <row r="265">
       <c r="A265" s="6" t="inlineStr">
         <is>
-          <t>7013194</t>
+          <t>7013193</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
@@ -12465,7 +12541,7 @@
     <row r="266">
       <c r="A266" s="4" t="inlineStr">
         <is>
-          <t>7018335</t>
+          <t>7013194</t>
         </is>
       </c>
       <c r="B266" s="5" t="inlineStr">
@@ -12485,7 +12561,7 @@
     <row r="267">
       <c r="A267" s="6" t="inlineStr">
         <is>
-          <t>7018336</t>
+          <t>7018335</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
@@ -12505,7 +12581,7 @@
     <row r="268">
       <c r="A268" s="4" t="inlineStr">
         <is>
-          <t>7018337</t>
+          <t>7018336</t>
         </is>
       </c>
       <c r="B268" s="5" t="inlineStr">
@@ -12525,7 +12601,7 @@
     <row r="269">
       <c r="A269" s="6" t="inlineStr">
         <is>
-          <t>7018338</t>
+          <t>7018337</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
@@ -12545,7 +12621,7 @@
     <row r="270">
       <c r="A270" s="4" t="inlineStr">
         <is>
-          <t>7018339</t>
+          <t>7018338</t>
         </is>
       </c>
       <c r="B270" s="5" t="inlineStr">
@@ -12565,7 +12641,7 @@
     <row r="271">
       <c r="A271" s="6" t="inlineStr">
         <is>
-          <t>7018340</t>
+          <t>7018339</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
@@ -12585,7 +12661,7 @@
     <row r="272">
       <c r="A272" s="4" t="inlineStr">
         <is>
-          <t>7018341</t>
+          <t>7018340</t>
         </is>
       </c>
       <c r="B272" s="5" t="inlineStr">
@@ -12605,7 +12681,7 @@
     <row r="273">
       <c r="A273" s="6" t="inlineStr">
         <is>
-          <t>7018342</t>
+          <t>7018341</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
@@ -12625,12 +12701,12 @@
     <row r="274">
       <c r="A274" s="4" t="inlineStr">
         <is>
-          <t>7017462</t>
+          <t>7018342</t>
         </is>
       </c>
       <c r="B274" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur LED Velox Deco Fyrkantig</t>
+          <t>Infälld interiörarmatur Diana Flat LED 600x600</t>
         </is>
       </c>
       <c r="C274" s="5" t="inlineStr">
@@ -12645,7 +12721,7 @@
     <row r="275">
       <c r="A275" s="6" t="inlineStr">
         <is>
-          <t>7018858</t>
+          <t>7017462</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
@@ -12665,7 +12741,7 @@
     <row r="276">
       <c r="A276" s="4" t="inlineStr">
         <is>
-          <t>7018877</t>
+          <t>7018858</t>
         </is>
       </c>
       <c r="B276" s="5" t="inlineStr">
@@ -12685,7 +12761,7 @@
     <row r="277">
       <c r="A277" s="6" t="inlineStr">
         <is>
-          <t>7018878</t>
+          <t>7018877</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
@@ -12705,12 +12781,12 @@
     <row r="278">
       <c r="A278" s="4" t="inlineStr">
         <is>
-          <t>7017460</t>
+          <t>7018878</t>
         </is>
       </c>
       <c r="B278" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur LED Velox Deco Rund</t>
+          <t>Interiörarmatur LED Velox Deco Fyrkantig</t>
         </is>
       </c>
       <c r="C278" s="5" t="inlineStr">
@@ -12725,7 +12801,7 @@
     <row r="279">
       <c r="A279" s="6" t="inlineStr">
         <is>
-          <t>7017464</t>
+          <t>7017460</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
@@ -12745,7 +12821,7 @@
     <row r="280">
       <c r="A280" s="4" t="inlineStr">
         <is>
-          <t>7017466</t>
+          <t>7017464</t>
         </is>
       </c>
       <c r="B280" s="5" t="inlineStr">
@@ -12765,7 +12841,7 @@
     <row r="281">
       <c r="A281" s="6" t="inlineStr">
         <is>
-          <t>7018857</t>
+          <t>7017466</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
@@ -12785,7 +12861,7 @@
     <row r="282">
       <c r="A282" s="4" t="inlineStr">
         <is>
-          <t>7018859</t>
+          <t>7018857</t>
         </is>
       </c>
       <c r="B282" s="5" t="inlineStr">
@@ -12805,7 +12881,7 @@
     <row r="283">
       <c r="A283" s="6" t="inlineStr">
         <is>
-          <t>7018860</t>
+          <t>7018859</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
@@ -12825,7 +12901,7 @@
     <row r="284">
       <c r="A284" s="4" t="inlineStr">
         <is>
-          <t>7018874</t>
+          <t>7018860</t>
         </is>
       </c>
       <c r="B284" s="5" t="inlineStr">
@@ -12845,7 +12921,7 @@
     <row r="285">
       <c r="A285" s="6" t="inlineStr">
         <is>
-          <t>7018875</t>
+          <t>7018874</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
@@ -12865,7 +12941,7 @@
     <row r="286">
       <c r="A286" s="4" t="inlineStr">
         <is>
-          <t>7018876</t>
+          <t>7018875</t>
         </is>
       </c>
       <c r="B286" s="5" t="inlineStr">
@@ -12885,7 +12961,7 @@
     <row r="287">
       <c r="A287" s="6" t="inlineStr">
         <is>
-          <t>7018879</t>
+          <t>7018876</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
@@ -12905,7 +12981,7 @@
     <row r="288">
       <c r="A288" s="4" t="inlineStr">
         <is>
-          <t>7018880</t>
+          <t>7018879</t>
         </is>
       </c>
       <c r="B288" s="5" t="inlineStr">
@@ -12925,7 +13001,7 @@
     <row r="289">
       <c r="A289" s="6" t="inlineStr">
         <is>
-          <t>7018881</t>
+          <t>7018880</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
@@ -12945,7 +13021,7 @@
     <row r="290">
       <c r="A290" s="4" t="inlineStr">
         <is>
-          <t>7018882</t>
+          <t>7018881</t>
         </is>
       </c>
       <c r="B290" s="5" t="inlineStr">
@@ -12965,12 +13041,12 @@
     <row r="291">
       <c r="A291" s="6" t="inlineStr">
         <is>
-          <t>7015430</t>
+          <t>7018882</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>Interiörarmatur LED Velox Infälld rund</t>
+          <t>Interiörarmatur LED Velox Deco Rund</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
@@ -12985,7 +13061,7 @@
     <row r="292">
       <c r="A292" s="4" t="inlineStr">
         <is>
-          <t>7015431</t>
+          <t>7015430</t>
         </is>
       </c>
       <c r="B292" s="5" t="inlineStr">
@@ -13005,7 +13081,7 @@
     <row r="293">
       <c r="A293" s="6" t="inlineStr">
         <is>
-          <t>7015437</t>
+          <t>7015431</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
@@ -13025,7 +13101,7 @@
     <row r="294">
       <c r="A294" s="4" t="inlineStr">
         <is>
-          <t>7015439</t>
+          <t>7015437</t>
         </is>
       </c>
       <c r="B294" s="5" t="inlineStr">
@@ -13045,7 +13121,7 @@
     <row r="295">
       <c r="A295" s="6" t="inlineStr">
         <is>
-          <t>7015441</t>
+          <t>7015439</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
@@ -13065,7 +13141,7 @@
     <row r="296">
       <c r="A296" s="4" t="inlineStr">
         <is>
-          <t>7015443</t>
+          <t>7015441</t>
         </is>
       </c>
       <c r="B296" s="5" t="inlineStr">
@@ -13085,12 +13161,12 @@
     <row r="297">
       <c r="A297" s="6" t="inlineStr">
         <is>
-          <t>7015433</t>
+          <t>7015443</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>Interiörarmatur LED Velox infälld fyrkantig</t>
+          <t>Interiörarmatur LED Velox Infälld rund</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
@@ -13105,7 +13181,7 @@
     <row r="298">
       <c r="A298" s="4" t="inlineStr">
         <is>
-          <t>7015435</t>
+          <t>7015433</t>
         </is>
       </c>
       <c r="B298" s="5" t="inlineStr">
@@ -13125,21 +13201,21 @@
     <row r="299">
       <c r="A299" s="6" t="inlineStr">
         <is>
-          <t>7028947</t>
+          <t>7015435</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>Interiörarmatur Juna</t>
+          <t>Interiörarmatur LED Velox infälld fyrkantig</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>Esylux</t>
+          <t>Ensto</t>
         </is>
       </c>
       <c r="D299" s="6" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
     </row>
     <row r="300">
@@ -15319,7 +15395,7 @@
         </is>
       </c>
       <c r="D408" s="4" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="409">
@@ -15819,7 +15895,7 @@
         </is>
       </c>
       <c r="D433" s="6" t="n">
-        <v>177</v>
+        <v>172</v>
       </c>
     </row>
     <row r="434">
@@ -19719,7 +19795,7 @@
         </is>
       </c>
       <c r="D628" s="4" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="629">
@@ -26759,7 +26835,7 @@
         </is>
       </c>
       <c r="D980" s="4" t="n">
-        <v>98</v>
+        <v>83</v>
       </c>
     </row>
     <row r="981">
@@ -26779,7 +26855,7 @@
         </is>
       </c>
       <c r="D981" s="6" t="n">
-        <v>103</v>
+        <v>123</v>
       </c>
     </row>
     <row r="982">
@@ -26799,7 +26875,7 @@
         </is>
       </c>
       <c r="D982" s="4" t="n">
-        <v>167</v>
+        <v>165</v>
       </c>
     </row>
     <row r="983">
@@ -29839,7 +29915,7 @@
         </is>
       </c>
       <c r="D1134" s="4" t="n">
-        <v>37</v>
+        <v>43</v>
       </c>
     </row>
     <row r="1135">
@@ -29919,7 +29995,7 @@
         </is>
       </c>
       <c r="D1138" s="4" t="n">
-        <v>471</v>
+        <v>480</v>
       </c>
     </row>
     <row r="1139">
@@ -29939,7 +30015,7 @@
         </is>
       </c>
       <c r="D1139" s="6" t="n">
-        <v>340</v>
+        <v>347</v>
       </c>
     </row>
   </sheetData>

--- a/data/ahlsell_led_panel_inventory.xlsx
+++ b/data/ahlsell_led_panel_inventory.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y88"/>
+  <dimension ref="A1:Y89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -528,87 +528,87 @@
       </c>
       <c r="I1" s="3" t="inlineStr">
         <is>
+          <t>Exaktor</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="inlineStr">
+        <is>
           <t>Ledvance</t>
         </is>
       </c>
-      <c r="J1" s="3" t="inlineStr">
-        <is>
-          <t>Exaktor</t>
-        </is>
-      </c>
       <c r="K1" s="3" t="inlineStr">
         <is>
+          <t>Esylux</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="inlineStr">
+        <is>
+          <t>Norwesco</t>
+        </is>
+      </c>
+      <c r="M1" s="3" t="inlineStr">
+        <is>
+          <t>Legrand</t>
+        </is>
+      </c>
+      <c r="N1" s="3" t="inlineStr">
+        <is>
+          <t>Siteco</t>
+        </is>
+      </c>
+      <c r="O1" s="3" t="inlineStr">
+        <is>
+          <t>Easyform</t>
+        </is>
+      </c>
+      <c r="P1" s="3" t="inlineStr">
+        <is>
+          <t>Westal</t>
+        </is>
+      </c>
+      <c r="Q1" s="3" t="inlineStr">
+        <is>
+          <t>Philips</t>
+        </is>
+      </c>
+      <c r="R1" s="3" t="inlineStr">
+        <is>
+          <t>Bergdahls</t>
+        </is>
+      </c>
+      <c r="S1" s="3" t="inlineStr">
+        <is>
+          <t>ZG Lighting</t>
+        </is>
+      </c>
+      <c r="T1" s="3" t="inlineStr">
+        <is>
+          <t>THORN</t>
+        </is>
+      </c>
+      <c r="U1" s="3" t="inlineStr">
+        <is>
+          <t>Airam</t>
+        </is>
+      </c>
+      <c r="V1" s="3" t="inlineStr">
+        <is>
           <t>ANETA LIGHTING</t>
         </is>
       </c>
-      <c r="L1" s="3" t="inlineStr">
-        <is>
-          <t>ZG Lighting</t>
-        </is>
-      </c>
-      <c r="M1" s="3" t="inlineStr">
-        <is>
-          <t>Airam</t>
-        </is>
-      </c>
-      <c r="N1" s="3" t="inlineStr">
+      <c r="W1" s="3" t="inlineStr">
+        <is>
+          <t>Nokalux</t>
+        </is>
+      </c>
+      <c r="X1" s="3" t="inlineStr">
         <is>
           <t>Ensto</t>
         </is>
       </c>
-      <c r="O1" s="3" t="inlineStr">
-        <is>
-          <t>Legrand</t>
-        </is>
-      </c>
-      <c r="P1" s="3" t="inlineStr">
-        <is>
-          <t>Easyform</t>
-        </is>
-      </c>
-      <c r="Q1" s="3" t="inlineStr">
+      <c r="Y1" s="3" t="inlineStr">
         <is>
           <t>Black Box</t>
-        </is>
-      </c>
-      <c r="R1" s="3" t="inlineStr">
-        <is>
-          <t>Norwesco</t>
-        </is>
-      </c>
-      <c r="S1" s="3" t="inlineStr">
-        <is>
-          <t>THORN</t>
-        </is>
-      </c>
-      <c r="T1" s="3" t="inlineStr">
-        <is>
-          <t>Esylux</t>
-        </is>
-      </c>
-      <c r="U1" s="3" t="inlineStr">
-        <is>
-          <t>Westal</t>
-        </is>
-      </c>
-      <c r="V1" s="3" t="inlineStr">
-        <is>
-          <t>Nokalux</t>
-        </is>
-      </c>
-      <c r="W1" s="3" t="inlineStr">
-        <is>
-          <t>Siteco</t>
-        </is>
-      </c>
-      <c r="X1" s="3" t="inlineStr">
-        <is>
-          <t>Philips</t>
-        </is>
-      </c>
-      <c r="Y1" s="3" t="inlineStr">
-        <is>
-          <t>Bergdahls</t>
         </is>
       </c>
     </row>
@@ -640,13 +640,13 @@
         <v>52</v>
       </c>
       <c r="I2" s="5" t="n">
+        <v>33</v>
+      </c>
+      <c r="J2" s="5" t="n">
         <v>17</v>
       </c>
-      <c r="J2" s="5" t="n">
-        <v>33</v>
-      </c>
       <c r="K2" s="5" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="L2" s="5" t="n">
         <v>0</v>
@@ -673,7 +673,7 @@
         <v>0</v>
       </c>
       <c r="T2" s="5" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="U2" s="5" t="n">
         <v>0</v>
@@ -719,13 +719,13 @@
         <v>52</v>
       </c>
       <c r="I3" t="n">
+        <v>33</v>
+      </c>
+      <c r="J3" t="n">
         <v>17</v>
       </c>
-      <c r="J3" t="n">
-        <v>33</v>
-      </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -752,7 +752,7 @@
         <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
         <v>0</v>
@@ -798,13 +798,13 @@
         <v>52</v>
       </c>
       <c r="I4" s="5" t="n">
+        <v>33</v>
+      </c>
+      <c r="J4" s="5" t="n">
         <v>17</v>
       </c>
-      <c r="J4" s="5" t="n">
-        <v>33</v>
-      </c>
       <c r="K4" s="5" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="L4" s="5" t="n">
         <v>0</v>
@@ -831,7 +831,7 @@
         <v>0</v>
       </c>
       <c r="T4" s="5" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="U4" s="5" t="n">
         <v>0</v>
@@ -877,13 +877,13 @@
         <v>52</v>
       </c>
       <c r="I5" t="n">
+        <v>33</v>
+      </c>
+      <c r="J5" t="n">
         <v>17</v>
       </c>
-      <c r="J5" t="n">
-        <v>33</v>
-      </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -910,7 +910,7 @@
         <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
         <v>0</v>
@@ -956,13 +956,13 @@
         <v>52</v>
       </c>
       <c r="I6" s="5" t="n">
+        <v>33</v>
+      </c>
+      <c r="J6" s="5" t="n">
         <v>17</v>
       </c>
-      <c r="J6" s="5" t="n">
-        <v>33</v>
-      </c>
       <c r="K6" s="5" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L6" s="5" t="n">
         <v>0</v>
@@ -989,7 +989,7 @@
         <v>0</v>
       </c>
       <c r="T6" s="5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="U6" s="5" t="n">
         <v>0</v>
@@ -1032,13 +1032,13 @@
         <v>14</v>
       </c>
       <c r="I7" t="n">
+        <v>33</v>
+      </c>
+      <c r="J7" t="n">
         <v>17</v>
       </c>
-      <c r="J7" t="n">
-        <v>33</v>
-      </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -1065,7 +1065,7 @@
         <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
         <v>0</v>
@@ -1111,13 +1111,13 @@
         <v>52</v>
       </c>
       <c r="I8" s="5" t="n">
+        <v>33</v>
+      </c>
+      <c r="J8" s="5" t="n">
         <v>17</v>
       </c>
-      <c r="J8" s="5" t="n">
-        <v>33</v>
-      </c>
       <c r="K8" s="5" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L8" s="5" t="n">
         <v>0</v>
@@ -1144,7 +1144,7 @@
         <v>0</v>
       </c>
       <c r="T8" s="5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="U8" s="5" t="n">
         <v>0</v>
@@ -1190,13 +1190,13 @@
         <v>52</v>
       </c>
       <c r="I9" t="n">
+        <v>33</v>
+      </c>
+      <c r="J9" t="n">
         <v>17</v>
       </c>
-      <c r="J9" t="n">
-        <v>33</v>
-      </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -1223,7 +1223,7 @@
         <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
         <v>0</v>
@@ -1269,13 +1269,13 @@
         <v>52</v>
       </c>
       <c r="I10" s="5" t="n">
+        <v>33</v>
+      </c>
+      <c r="J10" s="5" t="n">
         <v>17</v>
       </c>
-      <c r="J10" s="5" t="n">
-        <v>33</v>
-      </c>
       <c r="K10" s="5" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L10" s="5" t="n">
         <v>0</v>
@@ -1302,7 +1302,7 @@
         <v>0</v>
       </c>
       <c r="T10" s="5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="U10" s="5" t="n">
         <v>0</v>
@@ -1348,13 +1348,13 @@
         <v>52</v>
       </c>
       <c r="I11" t="n">
+        <v>33</v>
+      </c>
+      <c r="J11" t="n">
         <v>17</v>
       </c>
-      <c r="J11" t="n">
-        <v>33</v>
-      </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -1381,7 +1381,7 @@
         <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
         <v>0</v>
@@ -1427,13 +1427,13 @@
         <v>52</v>
       </c>
       <c r="I12" s="5" t="n">
+        <v>33</v>
+      </c>
+      <c r="J12" s="5" t="n">
         <v>17</v>
       </c>
-      <c r="J12" s="5" t="n">
-        <v>33</v>
-      </c>
       <c r="K12" s="5" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L12" s="5" t="n">
         <v>0</v>
@@ -1460,7 +1460,7 @@
         <v>0</v>
       </c>
       <c r="T12" s="5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="U12" s="5" t="n">
         <v>0</v>
@@ -1506,13 +1506,13 @@
         <v>52</v>
       </c>
       <c r="I13" t="n">
+        <v>33</v>
+      </c>
+      <c r="J13" t="n">
         <v>17</v>
       </c>
-      <c r="J13" t="n">
-        <v>33</v>
-      </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -1539,7 +1539,7 @@
         <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
         <v>0</v>
@@ -1585,13 +1585,13 @@
         <v>2</v>
       </c>
       <c r="I14" s="5" t="n">
+        <v>33</v>
+      </c>
+      <c r="J14" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="J14" s="5" t="n">
-        <v>33</v>
-      </c>
       <c r="K14" s="5" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L14" s="5" t="n">
         <v>0</v>
@@ -1618,7 +1618,7 @@
         <v>0</v>
       </c>
       <c r="T14" s="5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="U14" s="5" t="n">
         <v>0</v>
@@ -1664,13 +1664,13 @@
         <v>52</v>
       </c>
       <c r="I15" t="n">
+        <v>33</v>
+      </c>
+      <c r="J15" t="n">
         <v>17</v>
       </c>
-      <c r="J15" t="n">
-        <v>33</v>
-      </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -1697,7 +1697,7 @@
         <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
         <v>0</v>
@@ -1743,13 +1743,13 @@
         <v>52</v>
       </c>
       <c r="I16" s="5" t="n">
+        <v>33</v>
+      </c>
+      <c r="J16" s="5" t="n">
         <v>17</v>
       </c>
-      <c r="J16" s="5" t="n">
-        <v>33</v>
-      </c>
       <c r="K16" s="5" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L16" s="5" t="n">
         <v>0</v>
@@ -1776,7 +1776,7 @@
         <v>0</v>
       </c>
       <c r="T16" s="5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="U16" s="5" t="n">
         <v>0</v>
@@ -1822,13 +1822,13 @@
         <v>52</v>
       </c>
       <c r="I17" t="n">
+        <v>33</v>
+      </c>
+      <c r="J17" t="n">
         <v>17</v>
       </c>
-      <c r="J17" t="n">
-        <v>33</v>
-      </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
@@ -1855,7 +1855,7 @@
         <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
         <v>0</v>
@@ -1901,13 +1901,13 @@
         <v>52</v>
       </c>
       <c r="I18" s="5" t="n">
+        <v>33</v>
+      </c>
+      <c r="J18" s="5" t="n">
         <v>17</v>
       </c>
-      <c r="J18" s="5" t="n">
-        <v>33</v>
-      </c>
       <c r="K18" s="5" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L18" s="5" t="n">
         <v>0</v>
@@ -1934,7 +1934,7 @@
         <v>0</v>
       </c>
       <c r="T18" s="5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="U18" s="5" t="n">
         <v>0</v>
@@ -1980,13 +1980,13 @@
         <v>50</v>
       </c>
       <c r="I19" t="n">
+        <v>33</v>
+      </c>
+      <c r="J19" t="n">
         <v>17</v>
       </c>
-      <c r="J19" t="n">
-        <v>33</v>
-      </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
@@ -2013,7 +2013,7 @@
         <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
         <v>0</v>
@@ -2059,13 +2059,13 @@
         <v>50</v>
       </c>
       <c r="I20" s="5" t="n">
+        <v>33</v>
+      </c>
+      <c r="J20" s="5" t="n">
         <v>17</v>
       </c>
-      <c r="J20" s="5" t="n">
-        <v>33</v>
-      </c>
       <c r="K20" s="5" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L20" s="5" t="n">
         <v>0</v>
@@ -2092,7 +2092,7 @@
         <v>0</v>
       </c>
       <c r="T20" s="5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="U20" s="5" t="n">
         <v>0</v>
@@ -2138,13 +2138,13 @@
         <v>14</v>
       </c>
       <c r="I21" t="n">
+        <v>33</v>
+      </c>
+      <c r="J21" t="n">
         <v>17</v>
       </c>
-      <c r="J21" t="n">
-        <v>33</v>
-      </c>
       <c r="K21" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
@@ -2171,7 +2171,7 @@
         <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
         <v>0</v>
@@ -2217,13 +2217,13 @@
         <v>50</v>
       </c>
       <c r="I22" s="5" t="n">
+        <v>33</v>
+      </c>
+      <c r="J22" s="5" t="n">
         <v>17</v>
       </c>
-      <c r="J22" s="5" t="n">
-        <v>33</v>
-      </c>
       <c r="K22" s="5" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L22" s="5" t="n">
         <v>0</v>
@@ -2250,7 +2250,7 @@
         <v>0</v>
       </c>
       <c r="T22" s="5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="U22" s="5" t="n">
         <v>0</v>
@@ -2296,13 +2296,13 @@
         <v>50</v>
       </c>
       <c r="I23" t="n">
+        <v>33</v>
+      </c>
+      <c r="J23" t="n">
         <v>17</v>
       </c>
-      <c r="J23" t="n">
-        <v>33</v>
-      </c>
       <c r="K23" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
@@ -2329,7 +2329,7 @@
         <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="U23" t="n">
         <v>0</v>
@@ -2375,13 +2375,13 @@
         <v>48</v>
       </c>
       <c r="I24" s="5" t="n">
+        <v>33</v>
+      </c>
+      <c r="J24" s="5" t="n">
         <v>17</v>
       </c>
-      <c r="J24" s="5" t="n">
-        <v>33</v>
-      </c>
       <c r="K24" s="5" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L24" s="5" t="n">
         <v>0</v>
@@ -2408,7 +2408,7 @@
         <v>0</v>
       </c>
       <c r="T24" s="5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="U24" s="5" t="n">
         <v>0</v>
@@ -2454,13 +2454,13 @@
         <v>48</v>
       </c>
       <c r="I25" t="n">
+        <v>33</v>
+      </c>
+      <c r="J25" t="n">
         <v>17</v>
       </c>
-      <c r="J25" t="n">
-        <v>33</v>
-      </c>
       <c r="K25" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
@@ -2487,7 +2487,7 @@
         <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="U25" t="n">
         <v>0</v>
@@ -2533,13 +2533,13 @@
         <v>48</v>
       </c>
       <c r="I26" s="5" t="n">
+        <v>33</v>
+      </c>
+      <c r="J26" s="5" t="n">
         <v>17</v>
       </c>
-      <c r="J26" s="5" t="n">
-        <v>33</v>
-      </c>
       <c r="K26" s="5" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L26" s="5" t="n">
         <v>0</v>
@@ -2566,7 +2566,7 @@
         <v>0</v>
       </c>
       <c r="T26" s="5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="U26" s="5" t="n">
         <v>0</v>
@@ -2612,13 +2612,13 @@
         <v>48</v>
       </c>
       <c r="I27" t="n">
+        <v>33</v>
+      </c>
+      <c r="J27" t="n">
         <v>17</v>
       </c>
-      <c r="J27" t="n">
-        <v>33</v>
-      </c>
       <c r="K27" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
@@ -2645,7 +2645,7 @@
         <v>0</v>
       </c>
       <c r="T27" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="U27" t="n">
         <v>0</v>
@@ -2691,10 +2691,10 @@
         <v>0</v>
       </c>
       <c r="I28" s="5" t="n">
+        <v>33</v>
+      </c>
+      <c r="J28" s="5" t="n">
         <v>17</v>
-      </c>
-      <c r="J28" s="5" t="n">
-        <v>33</v>
       </c>
       <c r="K28" s="5" t="n">
         <v>0</v>
@@ -2770,13 +2770,13 @@
         <v>48</v>
       </c>
       <c r="I29" t="n">
+        <v>33</v>
+      </c>
+      <c r="J29" t="n">
         <v>17</v>
       </c>
-      <c r="J29" t="n">
-        <v>33</v>
-      </c>
       <c r="K29" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
@@ -2803,7 +2803,7 @@
         <v>0</v>
       </c>
       <c r="T29" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="U29" t="n">
         <v>0</v>
@@ -2849,13 +2849,13 @@
         <v>48</v>
       </c>
       <c r="I30" s="5" t="n">
+        <v>33</v>
+      </c>
+      <c r="J30" s="5" t="n">
         <v>17</v>
       </c>
-      <c r="J30" s="5" t="n">
-        <v>33</v>
-      </c>
       <c r="K30" s="5" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L30" s="5" t="n">
         <v>0</v>
@@ -2882,7 +2882,7 @@
         <v>0</v>
       </c>
       <c r="T30" s="5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="U30" s="5" t="n">
         <v>0</v>
@@ -2928,13 +2928,13 @@
         <v>48</v>
       </c>
       <c r="I31" t="n">
+        <v>33</v>
+      </c>
+      <c r="J31" t="n">
         <v>17</v>
       </c>
-      <c r="J31" t="n">
-        <v>33</v>
-      </c>
       <c r="K31" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
@@ -2961,7 +2961,7 @@
         <v>0</v>
       </c>
       <c r="T31" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="U31" t="n">
         <v>0</v>
@@ -3007,13 +3007,13 @@
         <v>48</v>
       </c>
       <c r="I32" s="5" t="n">
+        <v>33</v>
+      </c>
+      <c r="J32" s="5" t="n">
         <v>17</v>
       </c>
-      <c r="J32" s="5" t="n">
-        <v>33</v>
-      </c>
       <c r="K32" s="5" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L32" s="5" t="n">
         <v>0</v>
@@ -3040,7 +3040,7 @@
         <v>0</v>
       </c>
       <c r="T32" s="5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="U32" s="5" t="n">
         <v>0</v>
@@ -3086,13 +3086,13 @@
         <v>48</v>
       </c>
       <c r="I33" t="n">
+        <v>33</v>
+      </c>
+      <c r="J33" t="n">
         <v>17</v>
       </c>
-      <c r="J33" t="n">
-        <v>33</v>
-      </c>
       <c r="K33" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
@@ -3119,7 +3119,7 @@
         <v>0</v>
       </c>
       <c r="T33" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="U33" t="n">
         <v>0</v>
@@ -3165,13 +3165,13 @@
         <v>48</v>
       </c>
       <c r="I34" s="5" t="n">
+        <v>33</v>
+      </c>
+      <c r="J34" s="5" t="n">
         <v>17</v>
       </c>
-      <c r="J34" s="5" t="n">
-        <v>33</v>
-      </c>
       <c r="K34" s="5" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L34" s="5" t="n">
         <v>0</v>
@@ -3198,7 +3198,7 @@
         <v>0</v>
       </c>
       <c r="T34" s="5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="U34" s="5" t="n">
         <v>0</v>
@@ -3244,13 +3244,13 @@
         <v>48</v>
       </c>
       <c r="I35" t="n">
+        <v>33</v>
+      </c>
+      <c r="J35" t="n">
         <v>17</v>
       </c>
-      <c r="J35" t="n">
-        <v>33</v>
-      </c>
       <c r="K35" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
@@ -3277,7 +3277,7 @@
         <v>0</v>
       </c>
       <c r="T35" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="U35" t="n">
         <v>0</v>
@@ -3323,13 +3323,13 @@
         <v>48</v>
       </c>
       <c r="I36" s="5" t="n">
+        <v>33</v>
+      </c>
+      <c r="J36" s="5" t="n">
         <v>17</v>
       </c>
-      <c r="J36" s="5" t="n">
-        <v>33</v>
-      </c>
       <c r="K36" s="5" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L36" s="5" t="n">
         <v>0</v>
@@ -3356,7 +3356,7 @@
         <v>0</v>
       </c>
       <c r="T36" s="5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="U36" s="5" t="n">
         <v>0</v>
@@ -3402,13 +3402,13 @@
         <v>48</v>
       </c>
       <c r="I37" t="n">
+        <v>33</v>
+      </c>
+      <c r="J37" t="n">
         <v>17</v>
       </c>
-      <c r="J37" t="n">
-        <v>33</v>
-      </c>
       <c r="K37" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L37" t="n">
         <v>0</v>
@@ -3435,7 +3435,7 @@
         <v>0</v>
       </c>
       <c r="T37" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="U37" t="n">
         <v>0</v>
@@ -3481,13 +3481,13 @@
         <v>48</v>
       </c>
       <c r="I38" s="5" t="n">
+        <v>33</v>
+      </c>
+      <c r="J38" s="5" t="n">
         <v>17</v>
       </c>
-      <c r="J38" s="5" t="n">
-        <v>33</v>
-      </c>
       <c r="K38" s="5" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L38" s="5" t="n">
         <v>0</v>
@@ -3514,7 +3514,7 @@
         <v>0</v>
       </c>
       <c r="T38" s="5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="U38" s="5" t="n">
         <v>0</v>
@@ -3560,13 +3560,13 @@
         <v>48</v>
       </c>
       <c r="I39" t="n">
+        <v>33</v>
+      </c>
+      <c r="J39" t="n">
         <v>17</v>
       </c>
-      <c r="J39" t="n">
-        <v>33</v>
-      </c>
       <c r="K39" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L39" t="n">
         <v>0</v>
@@ -3593,7 +3593,7 @@
         <v>0</v>
       </c>
       <c r="T39" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="U39" t="n">
         <v>0</v>
@@ -3639,13 +3639,13 @@
         <v>48</v>
       </c>
       <c r="I40" s="5" t="n">
+        <v>33</v>
+      </c>
+      <c r="J40" s="5" t="n">
         <v>17</v>
       </c>
-      <c r="J40" s="5" t="n">
-        <v>33</v>
-      </c>
       <c r="K40" s="5" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L40" s="5" t="n">
         <v>0</v>
@@ -3672,7 +3672,7 @@
         <v>0</v>
       </c>
       <c r="T40" s="5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="U40" s="5" t="n">
         <v>0</v>
@@ -3718,13 +3718,13 @@
         <v>48</v>
       </c>
       <c r="I41" t="n">
+        <v>33</v>
+      </c>
+      <c r="J41" t="n">
         <v>17</v>
       </c>
-      <c r="J41" t="n">
-        <v>33</v>
-      </c>
       <c r="K41" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L41" t="n">
         <v>0</v>
@@ -3751,7 +3751,7 @@
         <v>0</v>
       </c>
       <c r="T41" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="U41" t="n">
         <v>0</v>
@@ -3797,13 +3797,13 @@
         <v>46</v>
       </c>
       <c r="I42" s="5" t="n">
+        <v>33</v>
+      </c>
+      <c r="J42" s="5" t="n">
         <v>17</v>
       </c>
-      <c r="J42" s="5" t="n">
-        <v>33</v>
-      </c>
       <c r="K42" s="5" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L42" s="5" t="n">
         <v>0</v>
@@ -3830,7 +3830,7 @@
         <v>0</v>
       </c>
       <c r="T42" s="5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="U42" s="5" t="n">
         <v>0</v>
@@ -3876,13 +3876,13 @@
         <v>48</v>
       </c>
       <c r="I43" t="n">
+        <v>33</v>
+      </c>
+      <c r="J43" t="n">
         <v>17</v>
       </c>
-      <c r="J43" t="n">
-        <v>33</v>
-      </c>
       <c r="K43" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L43" t="n">
         <v>0</v>
@@ -3909,7 +3909,7 @@
         <v>0</v>
       </c>
       <c r="T43" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="U43" t="n">
         <v>0</v>
@@ -3955,13 +3955,13 @@
         <v>48</v>
       </c>
       <c r="I44" s="5" t="n">
+        <v>33</v>
+      </c>
+      <c r="J44" s="5" t="n">
         <v>17</v>
       </c>
-      <c r="J44" s="5" t="n">
-        <v>33</v>
-      </c>
       <c r="K44" s="5" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L44" s="5" t="n">
         <v>0</v>
@@ -3988,7 +3988,7 @@
         <v>0</v>
       </c>
       <c r="T44" s="5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="U44" s="5" t="n">
         <v>0</v>
@@ -4034,13 +4034,13 @@
         <v>48</v>
       </c>
       <c r="I45" t="n">
+        <v>33</v>
+      </c>
+      <c r="J45" t="n">
         <v>17</v>
       </c>
-      <c r="J45" t="n">
-        <v>33</v>
-      </c>
       <c r="K45" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L45" t="n">
         <v>0</v>
@@ -4067,7 +4067,7 @@
         <v>0</v>
       </c>
       <c r="T45" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="U45" t="n">
         <v>0</v>
@@ -4113,13 +4113,13 @@
         <v>48</v>
       </c>
       <c r="I46" s="5" t="n">
+        <v>33</v>
+      </c>
+      <c r="J46" s="5" t="n">
         <v>17</v>
       </c>
-      <c r="J46" s="5" t="n">
-        <v>33</v>
-      </c>
       <c r="K46" s="5" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L46" s="5" t="n">
         <v>0</v>
@@ -4146,7 +4146,7 @@
         <v>0</v>
       </c>
       <c r="T46" s="5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="U46" s="5" t="n">
         <v>0</v>
@@ -4192,13 +4192,13 @@
         <v>48</v>
       </c>
       <c r="I47" t="n">
+        <v>33</v>
+      </c>
+      <c r="J47" t="n">
         <v>17</v>
       </c>
-      <c r="J47" t="n">
-        <v>33</v>
-      </c>
       <c r="K47" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L47" t="n">
         <v>0</v>
@@ -4225,7 +4225,7 @@
         <v>0</v>
       </c>
       <c r="T47" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="U47" t="n">
         <v>0</v>
@@ -4271,13 +4271,13 @@
         <v>48</v>
       </c>
       <c r="I48" s="5" t="n">
+        <v>33</v>
+      </c>
+      <c r="J48" s="5" t="n">
         <v>17</v>
       </c>
-      <c r="J48" s="5" t="n">
-        <v>33</v>
-      </c>
       <c r="K48" s="5" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L48" s="5" t="n">
         <v>0</v>
@@ -4304,7 +4304,7 @@
         <v>0</v>
       </c>
       <c r="T48" s="5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="U48" s="5" t="n">
         <v>0</v>
@@ -4350,13 +4350,13 @@
         <v>0</v>
       </c>
       <c r="I49" t="n">
+        <v>33</v>
+      </c>
+      <c r="J49" t="n">
         <v>17</v>
       </c>
-      <c r="J49" t="n">
-        <v>33</v>
-      </c>
       <c r="K49" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L49" t="n">
         <v>0</v>
@@ -4383,7 +4383,7 @@
         <v>0</v>
       </c>
       <c r="T49" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="U49" t="n">
         <v>0</v>
@@ -4429,13 +4429,13 @@
         <v>48</v>
       </c>
       <c r="I50" s="5" t="n">
+        <v>33</v>
+      </c>
+      <c r="J50" s="5" t="n">
         <v>17</v>
       </c>
-      <c r="J50" s="5" t="n">
-        <v>33</v>
-      </c>
       <c r="K50" s="5" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L50" s="5" t="n">
         <v>0</v>
@@ -4462,7 +4462,7 @@
         <v>0</v>
       </c>
       <c r="T50" s="5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="U50" s="5" t="n">
         <v>0</v>
@@ -4508,13 +4508,13 @@
         <v>48</v>
       </c>
       <c r="I51" t="n">
+        <v>33</v>
+      </c>
+      <c r="J51" t="n">
         <v>17</v>
       </c>
-      <c r="J51" t="n">
-        <v>33</v>
-      </c>
       <c r="K51" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L51" t="n">
         <v>0</v>
@@ -4541,7 +4541,7 @@
         <v>0</v>
       </c>
       <c r="T51" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="U51" t="n">
         <v>0</v>
@@ -4587,13 +4587,13 @@
         <v>48</v>
       </c>
       <c r="I52" s="5" t="n">
+        <v>30</v>
+      </c>
+      <c r="J52" s="5" t="n">
         <v>17</v>
       </c>
-      <c r="J52" s="5" t="n">
-        <v>30</v>
-      </c>
       <c r="K52" s="5" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L52" s="5" t="n">
         <v>0</v>
@@ -4620,7 +4620,7 @@
         <v>0</v>
       </c>
       <c r="T52" s="5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="U52" s="5" t="n">
         <v>0</v>
@@ -4666,13 +4666,13 @@
         <v>48</v>
       </c>
       <c r="I53" t="n">
+        <v>30</v>
+      </c>
+      <c r="J53" t="n">
         <v>17</v>
       </c>
-      <c r="J53" t="n">
-        <v>30</v>
-      </c>
       <c r="K53" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L53" t="n">
         <v>0</v>
@@ -4699,7 +4699,7 @@
         <v>0</v>
       </c>
       <c r="T53" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="U53" t="n">
         <v>0</v>
@@ -4745,13 +4745,13 @@
         <v>48</v>
       </c>
       <c r="I54" s="5" t="n">
+        <v>30</v>
+      </c>
+      <c r="J54" s="5" t="n">
         <v>17</v>
       </c>
-      <c r="J54" s="5" t="n">
-        <v>30</v>
-      </c>
       <c r="K54" s="5" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L54" s="5" t="n">
         <v>0</v>
@@ -4778,7 +4778,7 @@
         <v>0</v>
       </c>
       <c r="T54" s="5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="U54" s="5" t="n">
         <v>0</v>
@@ -4824,13 +4824,13 @@
         <v>2</v>
       </c>
       <c r="I55" t="n">
+        <v>30</v>
+      </c>
+      <c r="J55" t="n">
         <v>17</v>
       </c>
-      <c r="J55" t="n">
-        <v>30</v>
-      </c>
       <c r="K55" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L55" t="n">
         <v>0</v>
@@ -4857,7 +4857,7 @@
         <v>0</v>
       </c>
       <c r="T55" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="U55" t="n">
         <v>0</v>
@@ -4903,13 +4903,13 @@
         <v>48</v>
       </c>
       <c r="I56" s="5" t="n">
+        <v>30</v>
+      </c>
+      <c r="J56" s="5" t="n">
         <v>17</v>
       </c>
-      <c r="J56" s="5" t="n">
-        <v>30</v>
-      </c>
       <c r="K56" s="5" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L56" s="5" t="n">
         <v>0</v>
@@ -4936,7 +4936,7 @@
         <v>0</v>
       </c>
       <c r="T56" s="5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="U56" s="5" t="n">
         <v>0</v>
@@ -4982,14 +4982,14 @@
         <v>48</v>
       </c>
       <c r="I57" t="n">
+        <v>24</v>
+      </c>
+      <c r="J57" t="n">
         <v>22</v>
       </c>
-      <c r="J57" t="n">
+      <c r="K57" t="n">
         <v>24</v>
       </c>
-      <c r="K57" t="n">
-        <v>0</v>
-      </c>
       <c r="L57" t="n">
         <v>0</v>
       </c>
@@ -5015,7 +5015,7 @@
         <v>0</v>
       </c>
       <c r="T57" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="U57" t="n">
         <v>0</v>
@@ -5061,13 +5061,13 @@
         <v>47</v>
       </c>
       <c r="I58" s="5" t="n">
+        <v>26</v>
+      </c>
+      <c r="J58" s="5" t="n">
         <v>22</v>
       </c>
-      <c r="J58" s="5" t="n">
-        <v>26</v>
-      </c>
       <c r="K58" s="5" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L58" s="5" t="n">
         <v>0</v>
@@ -5094,7 +5094,7 @@
         <v>0</v>
       </c>
       <c r="T58" s="5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="U58" s="5" t="n">
         <v>0</v>
@@ -5140,13 +5140,13 @@
         <v>47</v>
       </c>
       <c r="I59" t="n">
+        <v>26</v>
+      </c>
+      <c r="J59" t="n">
         <v>16</v>
       </c>
-      <c r="J59" t="n">
-        <v>26</v>
-      </c>
       <c r="K59" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L59" t="n">
         <v>0</v>
@@ -5173,7 +5173,7 @@
         <v>0</v>
       </c>
       <c r="T59" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="U59" t="n">
         <v>0</v>
@@ -5219,13 +5219,13 @@
         <v>46</v>
       </c>
       <c r="I60" s="5" t="n">
+        <v>23</v>
+      </c>
+      <c r="J60" s="5" t="n">
         <v>16</v>
       </c>
-      <c r="J60" s="5" t="n">
-        <v>23</v>
-      </c>
       <c r="K60" s="5" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L60" s="5" t="n">
         <v>0</v>
@@ -5252,7 +5252,7 @@
         <v>0</v>
       </c>
       <c r="T60" s="5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="U60" s="5" t="n">
         <v>0</v>
@@ -5298,13 +5298,13 @@
         <v>43</v>
       </c>
       <c r="I61" t="n">
+        <v>29</v>
+      </c>
+      <c r="J61" t="n">
         <v>16</v>
       </c>
-      <c r="J61" t="n">
-        <v>29</v>
-      </c>
       <c r="K61" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L61" t="n">
         <v>0</v>
@@ -5331,7 +5331,7 @@
         <v>0</v>
       </c>
       <c r="T61" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="U61" t="n">
         <v>0</v>
@@ -5377,13 +5377,13 @@
         <v>43</v>
       </c>
       <c r="I62" s="5" t="n">
+        <v>29</v>
+      </c>
+      <c r="J62" s="5" t="n">
         <v>16</v>
       </c>
-      <c r="J62" s="5" t="n">
-        <v>29</v>
-      </c>
       <c r="K62" s="5" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L62" s="5" t="n">
         <v>0</v>
@@ -5410,7 +5410,7 @@
         <v>0</v>
       </c>
       <c r="T62" s="5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="U62" s="5" t="n">
         <v>0</v>
@@ -5456,13 +5456,13 @@
         <v>43</v>
       </c>
       <c r="I63" t="n">
+        <v>29</v>
+      </c>
+      <c r="J63" t="n">
         <v>16</v>
       </c>
-      <c r="J63" t="n">
-        <v>29</v>
-      </c>
       <c r="K63" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L63" t="n">
         <v>0</v>
@@ -5489,7 +5489,7 @@
         <v>0</v>
       </c>
       <c r="T63" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="U63" t="n">
         <v>0</v>
@@ -5535,13 +5535,13 @@
         <v>42</v>
       </c>
       <c r="I64" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="J64" s="5" t="n">
         <v>16</v>
       </c>
-      <c r="J64" s="5" t="n">
-        <v>20</v>
-      </c>
       <c r="K64" s="5" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L64" s="5" t="n">
         <v>0</v>
@@ -5568,7 +5568,7 @@
         <v>0</v>
       </c>
       <c r="T64" s="5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="U64" s="5" t="n">
         <v>0</v>
@@ -5614,13 +5614,13 @@
         <v>46</v>
       </c>
       <c r="I65" t="n">
+        <v>20</v>
+      </c>
+      <c r="J65" t="n">
         <v>21</v>
       </c>
-      <c r="J65" t="n">
-        <v>20</v>
-      </c>
       <c r="K65" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L65" t="n">
         <v>0</v>
@@ -5647,7 +5647,7 @@
         <v>0</v>
       </c>
       <c r="T65" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="U65" t="n">
         <v>0</v>
@@ -5693,13 +5693,13 @@
         <v>42</v>
       </c>
       <c r="I66" s="5" t="n">
+        <v>26</v>
+      </c>
+      <c r="J66" s="5" t="n">
         <v>21</v>
       </c>
-      <c r="J66" s="5" t="n">
-        <v>26</v>
-      </c>
       <c r="K66" s="5" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L66" s="5" t="n">
         <v>0</v>
@@ -5726,7 +5726,7 @@
         <v>0</v>
       </c>
       <c r="T66" s="5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="U66" s="5" t="n">
         <v>0</v>
@@ -5772,14 +5772,11 @@
         <v>53</v>
       </c>
       <c r="I67" t="n">
+        <v>26</v>
+      </c>
+      <c r="J67" t="n">
         <v>21</v>
       </c>
-      <c r="J67" t="n">
-        <v>26</v>
-      </c>
-      <c r="K67" t="n">
-        <v>0</v>
-      </c>
       <c r="L67" t="n">
         <v>0</v>
       </c>
@@ -5802,6 +5799,9 @@
         <v>0</v>
       </c>
       <c r="S67" t="n">
+        <v>0</v>
+      </c>
+      <c r="T67" t="n">
         <v>0</v>
       </c>
       <c r="U67" t="n">
@@ -5848,13 +5848,13 @@
         <v>53</v>
       </c>
       <c r="I68" s="5" t="n">
+        <v>26</v>
+      </c>
+      <c r="J68" s="5" t="n">
         <v>21</v>
       </c>
-      <c r="J68" s="5" t="n">
-        <v>26</v>
-      </c>
       <c r="K68" s="5" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L68" s="5" t="n">
         <v>0</v>
@@ -5881,7 +5881,7 @@
         <v>0</v>
       </c>
       <c r="T68" s="5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="U68" s="5" t="n">
         <v>0</v>
@@ -5924,14 +5924,11 @@
         <v>0</v>
       </c>
       <c r="I69" t="n">
+        <v>26</v>
+      </c>
+      <c r="J69" t="n">
         <v>21</v>
       </c>
-      <c r="J69" t="n">
-        <v>26</v>
-      </c>
-      <c r="K69" t="n">
-        <v>0</v>
-      </c>
       <c r="L69" t="n">
         <v>0</v>
       </c>
@@ -5954,6 +5951,9 @@
         <v>0</v>
       </c>
       <c r="S69" t="n">
+        <v>0</v>
+      </c>
+      <c r="T69" t="n">
         <v>0</v>
       </c>
       <c r="U69" t="n">
@@ -6000,13 +6000,13 @@
         <v>53</v>
       </c>
       <c r="I70" s="5" t="n">
+        <v>26</v>
+      </c>
+      <c r="J70" s="5" t="n">
         <v>21</v>
       </c>
-      <c r="J70" s="5" t="n">
-        <v>26</v>
-      </c>
       <c r="K70" s="5" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L70" s="5" t="n">
         <v>0</v>
@@ -6033,7 +6033,7 @@
         <v>0</v>
       </c>
       <c r="T70" s="5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="U70" s="5" t="n">
         <v>0</v>
@@ -6079,13 +6079,13 @@
         <v>42</v>
       </c>
       <c r="I71" t="n">
+        <v>26</v>
+      </c>
+      <c r="J71" t="n">
         <v>21</v>
       </c>
-      <c r="J71" t="n">
-        <v>26</v>
-      </c>
       <c r="K71" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L71" t="n">
         <v>0</v>
@@ -6112,7 +6112,7 @@
         <v>0</v>
       </c>
       <c r="T71" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="U71" t="n">
         <v>0</v>
@@ -6158,13 +6158,13 @@
         <v>42</v>
       </c>
       <c r="I72" s="5" t="n">
+        <v>26</v>
+      </c>
+      <c r="J72" s="5" t="n">
         <v>21</v>
       </c>
-      <c r="J72" s="5" t="n">
-        <v>26</v>
-      </c>
       <c r="K72" s="5" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L72" s="5" t="n">
         <v>0</v>
@@ -6191,7 +6191,7 @@
         <v>0</v>
       </c>
       <c r="T72" s="5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="U72" s="5" t="n">
         <v>0</v>
@@ -6237,13 +6237,13 @@
         <v>42</v>
       </c>
       <c r="I73" t="n">
+        <v>26</v>
+      </c>
+      <c r="J73" t="n">
         <v>19</v>
       </c>
-      <c r="J73" t="n">
-        <v>26</v>
-      </c>
       <c r="K73" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L73" t="n">
         <v>0</v>
@@ -6270,7 +6270,7 @@
         <v>0</v>
       </c>
       <c r="T73" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="U73" t="n">
         <v>0</v>
@@ -6316,13 +6316,13 @@
         <v>42</v>
       </c>
       <c r="I74" s="5" t="n">
+        <v>26</v>
+      </c>
+      <c r="J74" s="5" t="n">
         <v>23</v>
       </c>
-      <c r="J74" s="5" t="n">
-        <v>26</v>
-      </c>
       <c r="K74" s="5" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L74" s="5" t="n">
         <v>0</v>
@@ -6349,7 +6349,7 @@
         <v>0</v>
       </c>
       <c r="T74" s="5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="U74" s="5" t="n">
         <v>0</v>
@@ -6395,13 +6395,13 @@
         <v>42</v>
       </c>
       <c r="I75" t="n">
+        <v>26</v>
+      </c>
+      <c r="J75" t="n">
         <v>23</v>
       </c>
-      <c r="J75" t="n">
-        <v>26</v>
-      </c>
       <c r="K75" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L75" t="n">
         <v>0</v>
@@ -6428,7 +6428,7 @@
         <v>0</v>
       </c>
       <c r="T75" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="U75" t="n">
         <v>0</v>
@@ -6474,28 +6474,30 @@
         <v>42</v>
       </c>
       <c r="I76" s="5" t="n">
+        <v>26</v>
+      </c>
+      <c r="J76" s="5" t="n">
         <v>23</v>
       </c>
-      <c r="J76" s="5" t="n">
-        <v>26</v>
-      </c>
       <c r="K76" s="5" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L76" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="M76" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="M76" s="5" t="n"/>
       <c r="N76" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="O76" s="5" t="n"/>
+      <c r="O76" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="P76" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="Q76" s="5" t="n"/>
+      <c r="Q76" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="R76" s="5" t="n">
         <v>0</v>
       </c>
@@ -6503,7 +6505,7 @@
         <v>0</v>
       </c>
       <c r="T76" s="5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="U76" s="5" t="n">
         <v>0</v>
@@ -6517,9 +6519,7 @@
       <c r="X76" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="Y76" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="Y76" s="5" t="n"/>
     </row>
     <row r="77">
       <c r="A77" s="6" t="inlineStr">
@@ -6549,14 +6549,11 @@
         <v>42</v>
       </c>
       <c r="I77" t="n">
+        <v>26</v>
+      </c>
+      <c r="J77" t="n">
         <v>23</v>
       </c>
-      <c r="J77" t="n">
-        <v>26</v>
-      </c>
-      <c r="K77" t="n">
-        <v>0</v>
-      </c>
       <c r="L77" t="n">
         <v>0</v>
       </c>
@@ -6579,6 +6576,9 @@
         <v>0</v>
       </c>
       <c r="S77" t="n">
+        <v>0</v>
+      </c>
+      <c r="T77" t="n">
         <v>0</v>
       </c>
       <c r="U77" t="n">
@@ -6625,13 +6625,13 @@
         <v>42</v>
       </c>
       <c r="I78" s="5" t="n">
+        <v>26</v>
+      </c>
+      <c r="J78" s="5" t="n">
         <v>23</v>
       </c>
-      <c r="J78" s="5" t="n">
-        <v>26</v>
-      </c>
       <c r="K78" s="5" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L78" s="5" t="n">
         <v>0</v>
@@ -6658,7 +6658,7 @@
         <v>0</v>
       </c>
       <c r="T78" s="5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="U78" s="5" t="n">
         <v>0</v>
@@ -6704,14 +6704,11 @@
         <v>42</v>
       </c>
       <c r="I79" t="n">
+        <v>26</v>
+      </c>
+      <c r="J79" t="n">
         <v>23</v>
       </c>
-      <c r="J79" t="n">
-        <v>26</v>
-      </c>
-      <c r="K79" t="n">
-        <v>0</v>
-      </c>
       <c r="L79" t="n">
         <v>0</v>
       </c>
@@ -6734,6 +6731,9 @@
         <v>0</v>
       </c>
       <c r="S79" t="n">
+        <v>0</v>
+      </c>
+      <c r="T79" t="n">
         <v>0</v>
       </c>
       <c r="U79" t="n">
@@ -6780,14 +6780,12 @@
         <v>42</v>
       </c>
       <c r="I80" s="5" t="n">
+        <v>26</v>
+      </c>
+      <c r="J80" s="5" t="n">
         <v>23</v>
       </c>
-      <c r="J80" s="5" t="n">
-        <v>26</v>
-      </c>
-      <c r="K80" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="K80" s="5" t="n"/>
       <c r="L80" s="5" t="n">
         <v>0</v>
       </c>
@@ -6812,7 +6810,9 @@
       <c r="S80" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="T80" s="5" t="n"/>
+      <c r="T80" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="U80" s="5" t="n">
         <v>0</v>
       </c>
@@ -6857,13 +6857,13 @@
         <v>42</v>
       </c>
       <c r="I81" t="n">
+        <v>26</v>
+      </c>
+      <c r="J81" t="n">
         <v>23</v>
       </c>
-      <c r="J81" t="n">
-        <v>26</v>
-      </c>
       <c r="K81" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L81" t="n">
         <v>0</v>
@@ -6890,7 +6890,7 @@
         <v>0</v>
       </c>
       <c r="T81" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="U81" t="n">
         <v>0</v>
@@ -6936,14 +6936,12 @@
         <v>42</v>
       </c>
       <c r="I82" s="5" t="n">
+        <v>26</v>
+      </c>
+      <c r="J82" s="5" t="n">
         <v>23</v>
       </c>
-      <c r="J82" s="5" t="n">
-        <v>26</v>
-      </c>
-      <c r="K82" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="K82" s="5" t="n"/>
       <c r="L82" s="5" t="n">
         <v>0</v>
       </c>
@@ -6968,7 +6966,9 @@
       <c r="S82" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="T82" s="5" t="n"/>
+      <c r="T82" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="U82" s="5" t="n">
         <v>0</v>
       </c>
@@ -7010,13 +7010,13 @@
         <v>0</v>
       </c>
       <c r="I83" t="n">
+        <v>26</v>
+      </c>
+      <c r="J83" t="n">
         <v>23</v>
       </c>
-      <c r="J83" t="n">
-        <v>26</v>
-      </c>
       <c r="K83" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L83" t="n">
         <v>0</v>
@@ -7043,7 +7043,7 @@
         <v>0</v>
       </c>
       <c r="T83" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="U83" t="n">
         <v>0</v>
@@ -7089,13 +7089,13 @@
         <v>42</v>
       </c>
       <c r="I84" s="5" t="n">
+        <v>26</v>
+      </c>
+      <c r="J84" s="5" t="n">
         <v>23</v>
       </c>
-      <c r="J84" s="5" t="n">
-        <v>26</v>
-      </c>
       <c r="K84" s="5" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L84" s="5" t="n">
         <v>0</v>
@@ -7122,7 +7122,7 @@
         <v>0</v>
       </c>
       <c r="T84" s="5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="U84" s="5" t="n">
         <v>0</v>
@@ -7168,14 +7168,11 @@
         <v>42</v>
       </c>
       <c r="I85" t="n">
+        <v>15</v>
+      </c>
+      <c r="J85" t="n">
         <v>23</v>
       </c>
-      <c r="J85" t="n">
-        <v>15</v>
-      </c>
-      <c r="K85" t="n">
-        <v>0</v>
-      </c>
       <c r="L85" t="n">
         <v>0</v>
       </c>
@@ -7198,6 +7195,9 @@
         <v>0</v>
       </c>
       <c r="S85" t="n">
+        <v>0</v>
+      </c>
+      <c r="T85" t="n">
         <v>0</v>
       </c>
       <c r="U85" t="n">
@@ -7244,14 +7244,12 @@
         <v>42</v>
       </c>
       <c r="I86" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="J86" s="5" t="n">
         <v>23</v>
       </c>
-      <c r="J86" s="5" t="n">
-        <v>12</v>
-      </c>
-      <c r="K86" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="K86" s="5" t="n"/>
       <c r="L86" s="5" t="n">
         <v>0</v>
       </c>
@@ -7276,7 +7274,9 @@
       <c r="S86" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="T86" s="5" t="n"/>
+      <c r="T86" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="U86" s="5" t="n">
         <v>0</v>
       </c>
@@ -7321,14 +7321,11 @@
         <v>42</v>
       </c>
       <c r="I87" t="n">
+        <v>12</v>
+      </c>
+      <c r="J87" t="n">
         <v>23</v>
       </c>
-      <c r="J87" t="n">
-        <v>12</v>
-      </c>
-      <c r="K87" t="n">
-        <v>0</v>
-      </c>
       <c r="L87" t="n">
         <v>0</v>
       </c>
@@ -7351,6 +7348,9 @@
         <v>0</v>
       </c>
       <c r="S87" t="n">
+        <v>0</v>
+      </c>
+      <c r="T87" t="n">
         <v>0</v>
       </c>
       <c r="U87" t="n">
@@ -7397,14 +7397,12 @@
         <v>42</v>
       </c>
       <c r="I88" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="J88" s="5" t="n">
         <v>23</v>
       </c>
-      <c r="J88" s="5" t="n">
-        <v>14</v>
-      </c>
-      <c r="K88" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="K88" s="5" t="n"/>
       <c r="L88" s="5" t="n">
         <v>0</v>
       </c>
@@ -7429,7 +7427,9 @@
       <c r="S88" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="T88" s="5" t="n"/>
+      <c r="T88" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="U88" s="5" t="n">
         <v>0</v>
       </c>
@@ -7443,6 +7443,82 @@
         <v>0</v>
       </c>
       <c r="Y88" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B89" t="n">
+        <v>877</v>
+      </c>
+      <c r="C89" t="n">
+        <v>512</v>
+      </c>
+      <c r="D89" t="n">
+        <v>383</v>
+      </c>
+      <c r="E89" t="n">
+        <v>349</v>
+      </c>
+      <c r="F89" t="n">
+        <v>214</v>
+      </c>
+      <c r="G89" t="n">
+        <v>93</v>
+      </c>
+      <c r="H89" t="n">
+        <v>42</v>
+      </c>
+      <c r="I89" t="n">
+        <v>19</v>
+      </c>
+      <c r="J89" t="n">
+        <v>18</v>
+      </c>
+      <c r="L89" t="n">
+        <v>0</v>
+      </c>
+      <c r="M89" t="n">
+        <v>0</v>
+      </c>
+      <c r="N89" t="n">
+        <v>0</v>
+      </c>
+      <c r="O89" t="n">
+        <v>0</v>
+      </c>
+      <c r="P89" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q89" t="n">
+        <v>0</v>
+      </c>
+      <c r="R89" t="n">
+        <v>0</v>
+      </c>
+      <c r="S89" t="n">
+        <v>0</v>
+      </c>
+      <c r="T89" t="n">
+        <v>0</v>
+      </c>
+      <c r="U89" t="n">
+        <v>0</v>
+      </c>
+      <c r="V89" t="n">
+        <v>0</v>
+      </c>
+      <c r="W89" t="n">
+        <v>0</v>
+      </c>
+      <c r="X89" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y89" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7484,7 +7560,7 @@
       </c>
       <c r="D1" s="3" t="inlineStr">
         <is>
-          <t>Lager (2026-10-02)</t>
+          <t>Lager (2026-10-03)</t>
         </is>
       </c>
     </row>
@@ -7505,7 +7581,7 @@
         </is>
       </c>
       <c r="D2" s="4" t="n">
-        <v>505</v>
+        <v>512</v>
       </c>
     </row>
     <row r="3">
@@ -15545,7 +15621,7 @@
         </is>
       </c>
       <c r="D404" s="4" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
     <row r="405">
@@ -17145,7 +17221,7 @@
         </is>
       </c>
       <c r="D484" s="4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="485">
@@ -26925,7 +27001,7 @@
         </is>
       </c>
       <c r="D973" s="6" t="n">
-        <v>78</v>
+        <v>75</v>
       </c>
     </row>
     <row r="974">
@@ -26965,7 +27041,7 @@
         </is>
       </c>
       <c r="D975" s="6" t="n">
-        <v>191</v>
+        <v>183</v>
       </c>
     </row>
     <row r="976">
@@ -30005,7 +30081,7 @@
         </is>
       </c>
       <c r="D1127" s="6" t="n">
-        <v>426</v>
+        <v>448</v>
       </c>
     </row>
     <row r="1128">

--- a/data/ahlsell_led_panel_inventory.xlsx
+++ b/data/ahlsell_led_panel_inventory.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y93"/>
+  <dimension ref="A1:Y94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -528,87 +528,87 @@
       </c>
       <c r="I1" s="3" t="inlineStr">
         <is>
+          <t>Ledvance</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="inlineStr">
+        <is>
           <t>Exaktor</t>
         </is>
       </c>
-      <c r="J1" s="3" t="inlineStr">
-        <is>
-          <t>Ledvance</t>
-        </is>
-      </c>
       <c r="K1" s="3" t="inlineStr">
         <is>
+          <t>Airam</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="inlineStr">
+        <is>
+          <t>Bergdahls</t>
+        </is>
+      </c>
+      <c r="M1" s="3" t="inlineStr">
+        <is>
+          <t>Esylux</t>
+        </is>
+      </c>
+      <c r="N1" s="3" t="inlineStr">
+        <is>
+          <t>THORN</t>
+        </is>
+      </c>
+      <c r="O1" s="3" t="inlineStr">
+        <is>
+          <t>Philips</t>
+        </is>
+      </c>
+      <c r="P1" s="3" t="inlineStr">
+        <is>
           <t>Ensto</t>
         </is>
       </c>
-      <c r="L1" s="3" t="inlineStr">
+      <c r="Q1" s="3" t="inlineStr">
+        <is>
+          <t>ZG Lighting</t>
+        </is>
+      </c>
+      <c r="R1" s="3" t="inlineStr">
         <is>
           <t>Westal</t>
         </is>
       </c>
-      <c r="M1" s="3" t="inlineStr">
+      <c r="S1" s="3" t="inlineStr">
+        <is>
+          <t>Black Box</t>
+        </is>
+      </c>
+      <c r="T1" s="3" t="inlineStr">
         <is>
           <t>ANETA LIGHTING</t>
         </is>
       </c>
-      <c r="N1" s="3" t="inlineStr">
+      <c r="U1" s="3" t="inlineStr">
+        <is>
+          <t>Legrand</t>
+        </is>
+      </c>
+      <c r="V1" s="3" t="inlineStr">
+        <is>
+          <t>Easyform</t>
+        </is>
+      </c>
+      <c r="W1" s="3" t="inlineStr">
         <is>
           <t>Siteco</t>
         </is>
       </c>
-      <c r="O1" s="3" t="inlineStr">
-        <is>
-          <t>Bergdahls</t>
-        </is>
-      </c>
-      <c r="P1" s="3" t="inlineStr">
-        <is>
-          <t>Esylux</t>
-        </is>
-      </c>
-      <c r="Q1" s="3" t="inlineStr">
-        <is>
-          <t>Legrand</t>
-        </is>
-      </c>
-      <c r="R1" s="3" t="inlineStr">
-        <is>
-          <t>ZG Lighting</t>
-        </is>
-      </c>
-      <c r="S1" s="3" t="inlineStr">
-        <is>
-          <t>Easyform</t>
-        </is>
-      </c>
-      <c r="T1" s="3" t="inlineStr">
-        <is>
-          <t>Black Box</t>
-        </is>
-      </c>
-      <c r="U1" s="3" t="inlineStr">
-        <is>
-          <t>Philips</t>
-        </is>
-      </c>
-      <c r="V1" s="3" t="inlineStr">
+      <c r="X1" s="3" t="inlineStr">
         <is>
           <t>Nokalux</t>
         </is>
       </c>
-      <c r="W1" s="3" t="inlineStr">
+      <c r="Y1" s="3" t="inlineStr">
         <is>
           <t>Norwesco</t>
-        </is>
-      </c>
-      <c r="X1" s="3" t="inlineStr">
-        <is>
-          <t>THORN</t>
-        </is>
-      </c>
-      <c r="Y1" s="3" t="inlineStr">
-        <is>
-          <t>Airam</t>
         </is>
       </c>
     </row>
@@ -640,11 +640,11 @@
         <v>52</v>
       </c>
       <c r="I2" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="J2" s="5" t="n">
         <v>33</v>
       </c>
-      <c r="J2" s="5" t="n">
-        <v>17</v>
-      </c>
       <c r="K2" s="5" t="n">
         <v>0</v>
       </c>
@@ -652,7 +652,7 @@
         <v>0</v>
       </c>
       <c r="M2" s="5" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="N2" s="5" t="n">
         <v>0</v>
@@ -661,7 +661,7 @@
         <v>0</v>
       </c>
       <c r="P2" s="5" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="Q2" s="5" t="n">
         <v>0</v>
@@ -719,11 +719,11 @@
         <v>52</v>
       </c>
       <c r="I3" t="n">
+        <v>17</v>
+      </c>
+      <c r="J3" t="n">
         <v>33</v>
       </c>
-      <c r="J3" t="n">
-        <v>17</v>
-      </c>
       <c r="K3" t="n">
         <v>0</v>
       </c>
@@ -731,7 +731,7 @@
         <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="N3" t="n">
         <v>0</v>
@@ -740,7 +740,7 @@
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -798,11 +798,11 @@
         <v>52</v>
       </c>
       <c r="I4" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="J4" s="5" t="n">
         <v>33</v>
       </c>
-      <c r="J4" s="5" t="n">
-        <v>17</v>
-      </c>
       <c r="K4" s="5" t="n">
         <v>0</v>
       </c>
@@ -810,7 +810,7 @@
         <v>0</v>
       </c>
       <c r="M4" s="5" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="N4" s="5" t="n">
         <v>0</v>
@@ -819,7 +819,7 @@
         <v>0</v>
       </c>
       <c r="P4" s="5" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="Q4" s="5" t="n">
         <v>0</v>
@@ -877,11 +877,11 @@
         <v>52</v>
       </c>
       <c r="I5" t="n">
+        <v>17</v>
+      </c>
+      <c r="J5" t="n">
         <v>33</v>
       </c>
-      <c r="J5" t="n">
-        <v>17</v>
-      </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
@@ -889,7 +889,7 @@
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
@@ -898,7 +898,7 @@
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -956,11 +956,11 @@
         <v>52</v>
       </c>
       <c r="I6" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="J6" s="5" t="n">
         <v>33</v>
       </c>
-      <c r="J6" s="5" t="n">
-        <v>17</v>
-      </c>
       <c r="K6" s="5" t="n">
         <v>0</v>
       </c>
@@ -968,7 +968,7 @@
         <v>0</v>
       </c>
       <c r="M6" s="5" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="N6" s="5" t="n">
         <v>0</v>
@@ -977,7 +977,7 @@
         <v>0</v>
       </c>
       <c r="P6" s="5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="Q6" s="5" t="n">
         <v>0</v>
@@ -1032,11 +1032,11 @@
         <v>14</v>
       </c>
       <c r="I7" t="n">
+        <v>17</v>
+      </c>
+      <c r="J7" t="n">
         <v>33</v>
       </c>
-      <c r="J7" t="n">
-        <v>17</v>
-      </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
@@ -1044,7 +1044,7 @@
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
@@ -1053,7 +1053,7 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1111,11 +1111,11 @@
         <v>52</v>
       </c>
       <c r="I8" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="J8" s="5" t="n">
         <v>33</v>
       </c>
-      <c r="J8" s="5" t="n">
-        <v>17</v>
-      </c>
       <c r="K8" s="5" t="n">
         <v>0</v>
       </c>
@@ -1123,7 +1123,7 @@
         <v>0</v>
       </c>
       <c r="M8" s="5" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="N8" s="5" t="n">
         <v>0</v>
@@ -1132,7 +1132,7 @@
         <v>0</v>
       </c>
       <c r="P8" s="5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="Q8" s="5" t="n">
         <v>0</v>
@@ -1190,11 +1190,11 @@
         <v>52</v>
       </c>
       <c r="I9" t="n">
+        <v>17</v>
+      </c>
+      <c r="J9" t="n">
         <v>33</v>
       </c>
-      <c r="J9" t="n">
-        <v>17</v>
-      </c>
       <c r="K9" t="n">
         <v>0</v>
       </c>
@@ -1202,7 +1202,7 @@
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
@@ -1211,7 +1211,7 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -1269,11 +1269,11 @@
         <v>52</v>
       </c>
       <c r="I10" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="J10" s="5" t="n">
         <v>33</v>
       </c>
-      <c r="J10" s="5" t="n">
-        <v>17</v>
-      </c>
       <c r="K10" s="5" t="n">
         <v>0</v>
       </c>
@@ -1281,7 +1281,7 @@
         <v>0</v>
       </c>
       <c r="M10" s="5" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="N10" s="5" t="n">
         <v>0</v>
@@ -1290,7 +1290,7 @@
         <v>0</v>
       </c>
       <c r="P10" s="5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="Q10" s="5" t="n">
         <v>0</v>
@@ -1348,11 +1348,11 @@
         <v>52</v>
       </c>
       <c r="I11" t="n">
+        <v>17</v>
+      </c>
+      <c r="J11" t="n">
         <v>33</v>
       </c>
-      <c r="J11" t="n">
-        <v>17</v>
-      </c>
       <c r="K11" t="n">
         <v>0</v>
       </c>
@@ -1360,7 +1360,7 @@
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
@@ -1369,7 +1369,7 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -1427,11 +1427,11 @@
         <v>52</v>
       </c>
       <c r="I12" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="J12" s="5" t="n">
         <v>33</v>
       </c>
-      <c r="J12" s="5" t="n">
-        <v>17</v>
-      </c>
       <c r="K12" s="5" t="n">
         <v>0</v>
       </c>
@@ -1439,7 +1439,7 @@
         <v>0</v>
       </c>
       <c r="M12" s="5" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="N12" s="5" t="n">
         <v>0</v>
@@ -1448,7 +1448,7 @@
         <v>0</v>
       </c>
       <c r="P12" s="5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="Q12" s="5" t="n">
         <v>0</v>
@@ -1506,11 +1506,11 @@
         <v>52</v>
       </c>
       <c r="I13" t="n">
+        <v>17</v>
+      </c>
+      <c r="J13" t="n">
         <v>33</v>
       </c>
-      <c r="J13" t="n">
-        <v>17</v>
-      </c>
       <c r="K13" t="n">
         <v>0</v>
       </c>
@@ -1518,7 +1518,7 @@
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -1527,7 +1527,7 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -1585,11 +1585,11 @@
         <v>2</v>
       </c>
       <c r="I14" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="J14" s="5" t="n">
         <v>33</v>
       </c>
-      <c r="J14" s="5" t="n">
-        <v>6</v>
-      </c>
       <c r="K14" s="5" t="n">
         <v>0</v>
       </c>
@@ -1597,7 +1597,7 @@
         <v>0</v>
       </c>
       <c r="M14" s="5" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="N14" s="5" t="n">
         <v>0</v>
@@ -1606,7 +1606,7 @@
         <v>0</v>
       </c>
       <c r="P14" s="5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="Q14" s="5" t="n">
         <v>0</v>
@@ -1664,11 +1664,11 @@
         <v>52</v>
       </c>
       <c r="I15" t="n">
+        <v>17</v>
+      </c>
+      <c r="J15" t="n">
         <v>33</v>
       </c>
-      <c r="J15" t="n">
-        <v>17</v>
-      </c>
       <c r="K15" t="n">
         <v>0</v>
       </c>
@@ -1676,7 +1676,7 @@
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -1685,7 +1685,7 @@
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -1743,11 +1743,11 @@
         <v>52</v>
       </c>
       <c r="I16" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="J16" s="5" t="n">
         <v>33</v>
       </c>
-      <c r="J16" s="5" t="n">
-        <v>17</v>
-      </c>
       <c r="K16" s="5" t="n">
         <v>0</v>
       </c>
@@ -1755,7 +1755,7 @@
         <v>0</v>
       </c>
       <c r="M16" s="5" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="N16" s="5" t="n">
         <v>0</v>
@@ -1764,7 +1764,7 @@
         <v>0</v>
       </c>
       <c r="P16" s="5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="Q16" s="5" t="n">
         <v>0</v>
@@ -1822,11 +1822,11 @@
         <v>52</v>
       </c>
       <c r="I17" t="n">
+        <v>17</v>
+      </c>
+      <c r="J17" t="n">
         <v>33</v>
       </c>
-      <c r="J17" t="n">
-        <v>17</v>
-      </c>
       <c r="K17" t="n">
         <v>0</v>
       </c>
@@ -1834,7 +1834,7 @@
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
@@ -1843,7 +1843,7 @@
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -1901,11 +1901,11 @@
         <v>52</v>
       </c>
       <c r="I18" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="J18" s="5" t="n">
         <v>33</v>
       </c>
-      <c r="J18" s="5" t="n">
-        <v>17</v>
-      </c>
       <c r="K18" s="5" t="n">
         <v>0</v>
       </c>
@@ -1913,7 +1913,7 @@
         <v>0</v>
       </c>
       <c r="M18" s="5" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="N18" s="5" t="n">
         <v>0</v>
@@ -1922,7 +1922,7 @@
         <v>0</v>
       </c>
       <c r="P18" s="5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="Q18" s="5" t="n">
         <v>0</v>
@@ -1980,11 +1980,11 @@
         <v>50</v>
       </c>
       <c r="I19" t="n">
+        <v>17</v>
+      </c>
+      <c r="J19" t="n">
         <v>33</v>
       </c>
-      <c r="J19" t="n">
-        <v>17</v>
-      </c>
       <c r="K19" t="n">
         <v>0</v>
       </c>
@@ -1992,7 +1992,7 @@
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="N19" t="n">
         <v>0</v>
@@ -2001,7 +2001,7 @@
         <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -2059,11 +2059,11 @@
         <v>50</v>
       </c>
       <c r="I20" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="J20" s="5" t="n">
         <v>33</v>
       </c>
-      <c r="J20" s="5" t="n">
-        <v>17</v>
-      </c>
       <c r="K20" s="5" t="n">
         <v>0</v>
       </c>
@@ -2071,7 +2071,7 @@
         <v>0</v>
       </c>
       <c r="M20" s="5" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="N20" s="5" t="n">
         <v>0</v>
@@ -2080,7 +2080,7 @@
         <v>0</v>
       </c>
       <c r="P20" s="5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="Q20" s="5" t="n">
         <v>0</v>
@@ -2138,11 +2138,11 @@
         <v>14</v>
       </c>
       <c r="I21" t="n">
+        <v>17</v>
+      </c>
+      <c r="J21" t="n">
         <v>33</v>
       </c>
-      <c r="J21" t="n">
-        <v>17</v>
-      </c>
       <c r="K21" t="n">
         <v>0</v>
       </c>
@@ -2150,7 +2150,7 @@
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="N21" t="n">
         <v>0</v>
@@ -2159,7 +2159,7 @@
         <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
@@ -2217,11 +2217,11 @@
         <v>50</v>
       </c>
       <c r="I22" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="J22" s="5" t="n">
         <v>33</v>
       </c>
-      <c r="J22" s="5" t="n">
-        <v>17</v>
-      </c>
       <c r="K22" s="5" t="n">
         <v>0</v>
       </c>
@@ -2229,7 +2229,7 @@
         <v>0</v>
       </c>
       <c r="M22" s="5" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="N22" s="5" t="n">
         <v>0</v>
@@ -2238,7 +2238,7 @@
         <v>0</v>
       </c>
       <c r="P22" s="5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="Q22" s="5" t="n">
         <v>0</v>
@@ -2296,11 +2296,11 @@
         <v>50</v>
       </c>
       <c r="I23" t="n">
+        <v>17</v>
+      </c>
+      <c r="J23" t="n">
         <v>33</v>
       </c>
-      <c r="J23" t="n">
-        <v>17</v>
-      </c>
       <c r="K23" t="n">
         <v>0</v>
       </c>
@@ -2308,7 +2308,7 @@
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="N23" t="n">
         <v>0</v>
@@ -2317,7 +2317,7 @@
         <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
@@ -2375,11 +2375,11 @@
         <v>48</v>
       </c>
       <c r="I24" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="J24" s="5" t="n">
         <v>33</v>
       </c>
-      <c r="J24" s="5" t="n">
-        <v>17</v>
-      </c>
       <c r="K24" s="5" t="n">
         <v>0</v>
       </c>
@@ -2387,7 +2387,7 @@
         <v>0</v>
       </c>
       <c r="M24" s="5" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="N24" s="5" t="n">
         <v>0</v>
@@ -2396,7 +2396,7 @@
         <v>0</v>
       </c>
       <c r="P24" s="5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="Q24" s="5" t="n">
         <v>0</v>
@@ -2454,11 +2454,11 @@
         <v>48</v>
       </c>
       <c r="I25" t="n">
+        <v>17</v>
+      </c>
+      <c r="J25" t="n">
         <v>33</v>
       </c>
-      <c r="J25" t="n">
-        <v>17</v>
-      </c>
       <c r="K25" t="n">
         <v>0</v>
       </c>
@@ -2466,7 +2466,7 @@
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="N25" t="n">
         <v>0</v>
@@ -2475,7 +2475,7 @@
         <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -2533,11 +2533,11 @@
         <v>48</v>
       </c>
       <c r="I26" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="J26" s="5" t="n">
         <v>33</v>
       </c>
-      <c r="J26" s="5" t="n">
-        <v>17</v>
-      </c>
       <c r="K26" s="5" t="n">
         <v>0</v>
       </c>
@@ -2545,7 +2545,7 @@
         <v>0</v>
       </c>
       <c r="M26" s="5" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="N26" s="5" t="n">
         <v>0</v>
@@ -2554,7 +2554,7 @@
         <v>0</v>
       </c>
       <c r="P26" s="5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="Q26" s="5" t="n">
         <v>0</v>
@@ -2612,11 +2612,11 @@
         <v>48</v>
       </c>
       <c r="I27" t="n">
+        <v>17</v>
+      </c>
+      <c r="J27" t="n">
         <v>33</v>
       </c>
-      <c r="J27" t="n">
-        <v>17</v>
-      </c>
       <c r="K27" t="n">
         <v>0</v>
       </c>
@@ -2624,7 +2624,7 @@
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="N27" t="n">
         <v>0</v>
@@ -2633,7 +2633,7 @@
         <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
@@ -2691,10 +2691,10 @@
         <v>0</v>
       </c>
       <c r="I28" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="J28" s="5" t="n">
         <v>33</v>
-      </c>
-      <c r="J28" s="5" t="n">
-        <v>17</v>
       </c>
       <c r="K28" s="5" t="n">
         <v>0</v>
@@ -2770,11 +2770,11 @@
         <v>48</v>
       </c>
       <c r="I29" t="n">
+        <v>17</v>
+      </c>
+      <c r="J29" t="n">
         <v>33</v>
       </c>
-      <c r="J29" t="n">
-        <v>17</v>
-      </c>
       <c r="K29" t="n">
         <v>0</v>
       </c>
@@ -2782,7 +2782,7 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="N29" t="n">
         <v>0</v>
@@ -2791,7 +2791,7 @@
         <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
         <v>0</v>
@@ -2849,11 +2849,11 @@
         <v>48</v>
       </c>
       <c r="I30" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="J30" s="5" t="n">
         <v>33</v>
       </c>
-      <c r="J30" s="5" t="n">
-        <v>17</v>
-      </c>
       <c r="K30" s="5" t="n">
         <v>0</v>
       </c>
@@ -2861,7 +2861,7 @@
         <v>0</v>
       </c>
       <c r="M30" s="5" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="N30" s="5" t="n">
         <v>0</v>
@@ -2870,7 +2870,7 @@
         <v>0</v>
       </c>
       <c r="P30" s="5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="Q30" s="5" t="n">
         <v>0</v>
@@ -2928,11 +2928,11 @@
         <v>48</v>
       </c>
       <c r="I31" t="n">
+        <v>17</v>
+      </c>
+      <c r="J31" t="n">
         <v>33</v>
       </c>
-      <c r="J31" t="n">
-        <v>17</v>
-      </c>
       <c r="K31" t="n">
         <v>0</v>
       </c>
@@ -2940,7 +2940,7 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="N31" t="n">
         <v>0</v>
@@ -2949,7 +2949,7 @@
         <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
         <v>0</v>
@@ -3007,11 +3007,11 @@
         <v>48</v>
       </c>
       <c r="I32" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="J32" s="5" t="n">
         <v>33</v>
       </c>
-      <c r="J32" s="5" t="n">
-        <v>17</v>
-      </c>
       <c r="K32" s="5" t="n">
         <v>0</v>
       </c>
@@ -3019,7 +3019,7 @@
         <v>0</v>
       </c>
       <c r="M32" s="5" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="N32" s="5" t="n">
         <v>0</v>
@@ -3028,7 +3028,7 @@
         <v>0</v>
       </c>
       <c r="P32" s="5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="Q32" s="5" t="n">
         <v>0</v>
@@ -3086,11 +3086,11 @@
         <v>48</v>
       </c>
       <c r="I33" t="n">
+        <v>17</v>
+      </c>
+      <c r="J33" t="n">
         <v>33</v>
       </c>
-      <c r="J33" t="n">
-        <v>17</v>
-      </c>
       <c r="K33" t="n">
         <v>0</v>
       </c>
@@ -3098,7 +3098,7 @@
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="N33" t="n">
         <v>0</v>
@@ -3107,7 +3107,7 @@
         <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="Q33" t="n">
         <v>0</v>
@@ -3165,11 +3165,11 @@
         <v>48</v>
       </c>
       <c r="I34" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="J34" s="5" t="n">
         <v>33</v>
       </c>
-      <c r="J34" s="5" t="n">
-        <v>17</v>
-      </c>
       <c r="K34" s="5" t="n">
         <v>0</v>
       </c>
@@ -3177,7 +3177,7 @@
         <v>0</v>
       </c>
       <c r="M34" s="5" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="N34" s="5" t="n">
         <v>0</v>
@@ -3186,7 +3186,7 @@
         <v>0</v>
       </c>
       <c r="P34" s="5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="Q34" s="5" t="n">
         <v>0</v>
@@ -3244,11 +3244,11 @@
         <v>48</v>
       </c>
       <c r="I35" t="n">
+        <v>17</v>
+      </c>
+      <c r="J35" t="n">
         <v>33</v>
       </c>
-      <c r="J35" t="n">
-        <v>17</v>
-      </c>
       <c r="K35" t="n">
         <v>0</v>
       </c>
@@ -3256,7 +3256,7 @@
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="N35" t="n">
         <v>0</v>
@@ -3265,7 +3265,7 @@
         <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
         <v>0</v>
@@ -3323,11 +3323,11 @@
         <v>48</v>
       </c>
       <c r="I36" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="J36" s="5" t="n">
         <v>33</v>
       </c>
-      <c r="J36" s="5" t="n">
-        <v>17</v>
-      </c>
       <c r="K36" s="5" t="n">
         <v>0</v>
       </c>
@@ -3335,7 +3335,7 @@
         <v>0</v>
       </c>
       <c r="M36" s="5" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="N36" s="5" t="n">
         <v>0</v>
@@ -3344,7 +3344,7 @@
         <v>0</v>
       </c>
       <c r="P36" s="5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="Q36" s="5" t="n">
         <v>0</v>
@@ -3402,11 +3402,11 @@
         <v>48</v>
       </c>
       <c r="I37" t="n">
+        <v>17</v>
+      </c>
+      <c r="J37" t="n">
         <v>33</v>
       </c>
-      <c r="J37" t="n">
-        <v>17</v>
-      </c>
       <c r="K37" t="n">
         <v>0</v>
       </c>
@@ -3414,7 +3414,7 @@
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="N37" t="n">
         <v>0</v>
@@ -3423,7 +3423,7 @@
         <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="Q37" t="n">
         <v>0</v>
@@ -3481,11 +3481,11 @@
         <v>48</v>
       </c>
       <c r="I38" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="J38" s="5" t="n">
         <v>33</v>
       </c>
-      <c r="J38" s="5" t="n">
-        <v>17</v>
-      </c>
       <c r="K38" s="5" t="n">
         <v>0</v>
       </c>
@@ -3493,7 +3493,7 @@
         <v>0</v>
       </c>
       <c r="M38" s="5" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="N38" s="5" t="n">
         <v>0</v>
@@ -3502,7 +3502,7 @@
         <v>0</v>
       </c>
       <c r="P38" s="5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="Q38" s="5" t="n">
         <v>0</v>
@@ -3560,11 +3560,11 @@
         <v>48</v>
       </c>
       <c r="I39" t="n">
+        <v>17</v>
+      </c>
+      <c r="J39" t="n">
         <v>33</v>
       </c>
-      <c r="J39" t="n">
-        <v>17</v>
-      </c>
       <c r="K39" t="n">
         <v>0</v>
       </c>
@@ -3572,7 +3572,7 @@
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="N39" t="n">
         <v>0</v>
@@ -3581,7 +3581,7 @@
         <v>0</v>
       </c>
       <c r="P39" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="Q39" t="n">
         <v>0</v>
@@ -3639,11 +3639,11 @@
         <v>48</v>
       </c>
       <c r="I40" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="J40" s="5" t="n">
         <v>33</v>
       </c>
-      <c r="J40" s="5" t="n">
-        <v>17</v>
-      </c>
       <c r="K40" s="5" t="n">
         <v>0</v>
       </c>
@@ -3651,7 +3651,7 @@
         <v>0</v>
       </c>
       <c r="M40" s="5" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="N40" s="5" t="n">
         <v>0</v>
@@ -3660,7 +3660,7 @@
         <v>0</v>
       </c>
       <c r="P40" s="5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="Q40" s="5" t="n">
         <v>0</v>
@@ -3718,11 +3718,11 @@
         <v>48</v>
       </c>
       <c r="I41" t="n">
+        <v>17</v>
+      </c>
+      <c r="J41" t="n">
         <v>33</v>
       </c>
-      <c r="J41" t="n">
-        <v>17</v>
-      </c>
       <c r="K41" t="n">
         <v>0</v>
       </c>
@@ -3730,7 +3730,7 @@
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="N41" t="n">
         <v>0</v>
@@ -3739,7 +3739,7 @@
         <v>0</v>
       </c>
       <c r="P41" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="Q41" t="n">
         <v>0</v>
@@ -3797,11 +3797,11 @@
         <v>46</v>
       </c>
       <c r="I42" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="J42" s="5" t="n">
         <v>33</v>
       </c>
-      <c r="J42" s="5" t="n">
-        <v>17</v>
-      </c>
       <c r="K42" s="5" t="n">
         <v>0</v>
       </c>
@@ -3809,7 +3809,7 @@
         <v>0</v>
       </c>
       <c r="M42" s="5" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="N42" s="5" t="n">
         <v>0</v>
@@ -3818,7 +3818,7 @@
         <v>0</v>
       </c>
       <c r="P42" s="5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="Q42" s="5" t="n">
         <v>0</v>
@@ -3876,11 +3876,11 @@
         <v>48</v>
       </c>
       <c r="I43" t="n">
+        <v>17</v>
+      </c>
+      <c r="J43" t="n">
         <v>33</v>
       </c>
-      <c r="J43" t="n">
-        <v>17</v>
-      </c>
       <c r="K43" t="n">
         <v>0</v>
       </c>
@@ -3888,7 +3888,7 @@
         <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="N43" t="n">
         <v>0</v>
@@ -3897,7 +3897,7 @@
         <v>0</v>
       </c>
       <c r="P43" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="Q43" t="n">
         <v>0</v>
@@ -3955,11 +3955,11 @@
         <v>48</v>
       </c>
       <c r="I44" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="J44" s="5" t="n">
         <v>33</v>
       </c>
-      <c r="J44" s="5" t="n">
-        <v>17</v>
-      </c>
       <c r="K44" s="5" t="n">
         <v>0</v>
       </c>
@@ -3967,7 +3967,7 @@
         <v>0</v>
       </c>
       <c r="M44" s="5" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="N44" s="5" t="n">
         <v>0</v>
@@ -3976,7 +3976,7 @@
         <v>0</v>
       </c>
       <c r="P44" s="5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="Q44" s="5" t="n">
         <v>0</v>
@@ -4034,11 +4034,11 @@
         <v>48</v>
       </c>
       <c r="I45" t="n">
+        <v>17</v>
+      </c>
+      <c r="J45" t="n">
         <v>33</v>
       </c>
-      <c r="J45" t="n">
-        <v>17</v>
-      </c>
       <c r="K45" t="n">
         <v>0</v>
       </c>
@@ -4046,7 +4046,7 @@
         <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="N45" t="n">
         <v>0</v>
@@ -4055,7 +4055,7 @@
         <v>0</v>
       </c>
       <c r="P45" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="Q45" t="n">
         <v>0</v>
@@ -4113,11 +4113,11 @@
         <v>48</v>
       </c>
       <c r="I46" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="J46" s="5" t="n">
         <v>33</v>
       </c>
-      <c r="J46" s="5" t="n">
-        <v>17</v>
-      </c>
       <c r="K46" s="5" t="n">
         <v>0</v>
       </c>
@@ -4125,7 +4125,7 @@
         <v>0</v>
       </c>
       <c r="M46" s="5" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="N46" s="5" t="n">
         <v>0</v>
@@ -4134,7 +4134,7 @@
         <v>0</v>
       </c>
       <c r="P46" s="5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="Q46" s="5" t="n">
         <v>0</v>
@@ -4192,11 +4192,11 @@
         <v>48</v>
       </c>
       <c r="I47" t="n">
+        <v>17</v>
+      </c>
+      <c r="J47" t="n">
         <v>33</v>
       </c>
-      <c r="J47" t="n">
-        <v>17</v>
-      </c>
       <c r="K47" t="n">
         <v>0</v>
       </c>
@@ -4204,7 +4204,7 @@
         <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="N47" t="n">
         <v>0</v>
@@ -4213,7 +4213,7 @@
         <v>0</v>
       </c>
       <c r="P47" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="Q47" t="n">
         <v>0</v>
@@ -4271,11 +4271,11 @@
         <v>48</v>
       </c>
       <c r="I48" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="J48" s="5" t="n">
         <v>33</v>
       </c>
-      <c r="J48" s="5" t="n">
-        <v>17</v>
-      </c>
       <c r="K48" s="5" t="n">
         <v>0</v>
       </c>
@@ -4283,7 +4283,7 @@
         <v>0</v>
       </c>
       <c r="M48" s="5" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="N48" s="5" t="n">
         <v>0</v>
@@ -4292,7 +4292,7 @@
         <v>0</v>
       </c>
       <c r="P48" s="5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="Q48" s="5" t="n">
         <v>0</v>
@@ -4350,11 +4350,11 @@
         <v>0</v>
       </c>
       <c r="I49" t="n">
+        <v>17</v>
+      </c>
+      <c r="J49" t="n">
         <v>33</v>
       </c>
-      <c r="J49" t="n">
-        <v>17</v>
-      </c>
       <c r="K49" t="n">
         <v>0</v>
       </c>
@@ -4362,7 +4362,7 @@
         <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="N49" t="n">
         <v>0</v>
@@ -4371,7 +4371,7 @@
         <v>0</v>
       </c>
       <c r="P49" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="Q49" t="n">
         <v>0</v>
@@ -4429,11 +4429,11 @@
         <v>48</v>
       </c>
       <c r="I50" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="J50" s="5" t="n">
         <v>33</v>
       </c>
-      <c r="J50" s="5" t="n">
-        <v>17</v>
-      </c>
       <c r="K50" s="5" t="n">
         <v>0</v>
       </c>
@@ -4441,7 +4441,7 @@
         <v>0</v>
       </c>
       <c r="M50" s="5" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="N50" s="5" t="n">
         <v>0</v>
@@ -4450,7 +4450,7 @@
         <v>0</v>
       </c>
       <c r="P50" s="5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="Q50" s="5" t="n">
         <v>0</v>
@@ -4508,11 +4508,11 @@
         <v>48</v>
       </c>
       <c r="I51" t="n">
+        <v>17</v>
+      </c>
+      <c r="J51" t="n">
         <v>33</v>
       </c>
-      <c r="J51" t="n">
-        <v>17</v>
-      </c>
       <c r="K51" t="n">
         <v>0</v>
       </c>
@@ -4520,7 +4520,7 @@
         <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="N51" t="n">
         <v>0</v>
@@ -4529,7 +4529,7 @@
         <v>0</v>
       </c>
       <c r="P51" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="Q51" t="n">
         <v>0</v>
@@ -4587,11 +4587,11 @@
         <v>48</v>
       </c>
       <c r="I52" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="J52" s="5" t="n">
         <v>30</v>
       </c>
-      <c r="J52" s="5" t="n">
-        <v>17</v>
-      </c>
       <c r="K52" s="5" t="n">
         <v>0</v>
       </c>
@@ -4599,7 +4599,7 @@
         <v>0</v>
       </c>
       <c r="M52" s="5" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="N52" s="5" t="n">
         <v>0</v>
@@ -4608,7 +4608,7 @@
         <v>0</v>
       </c>
       <c r="P52" s="5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="Q52" s="5" t="n">
         <v>0</v>
@@ -4666,11 +4666,11 @@
         <v>48</v>
       </c>
       <c r="I53" t="n">
+        <v>17</v>
+      </c>
+      <c r="J53" t="n">
         <v>30</v>
       </c>
-      <c r="J53" t="n">
-        <v>17</v>
-      </c>
       <c r="K53" t="n">
         <v>0</v>
       </c>
@@ -4678,7 +4678,7 @@
         <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="N53" t="n">
         <v>0</v>
@@ -4687,7 +4687,7 @@
         <v>0</v>
       </c>
       <c r="P53" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="Q53" t="n">
         <v>0</v>
@@ -4745,11 +4745,11 @@
         <v>48</v>
       </c>
       <c r="I54" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="J54" s="5" t="n">
         <v>30</v>
       </c>
-      <c r="J54" s="5" t="n">
-        <v>17</v>
-      </c>
       <c r="K54" s="5" t="n">
         <v>0</v>
       </c>
@@ -4757,7 +4757,7 @@
         <v>0</v>
       </c>
       <c r="M54" s="5" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="N54" s="5" t="n">
         <v>0</v>
@@ -4766,7 +4766,7 @@
         <v>0</v>
       </c>
       <c r="P54" s="5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="Q54" s="5" t="n">
         <v>0</v>
@@ -4824,11 +4824,11 @@
         <v>2</v>
       </c>
       <c r="I55" t="n">
+        <v>17</v>
+      </c>
+      <c r="J55" t="n">
         <v>30</v>
       </c>
-      <c r="J55" t="n">
-        <v>17</v>
-      </c>
       <c r="K55" t="n">
         <v>0</v>
       </c>
@@ -4836,7 +4836,7 @@
         <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="N55" t="n">
         <v>0</v>
@@ -4845,7 +4845,7 @@
         <v>0</v>
       </c>
       <c r="P55" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="Q55" t="n">
         <v>0</v>
@@ -4903,11 +4903,11 @@
         <v>48</v>
       </c>
       <c r="I56" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="J56" s="5" t="n">
         <v>30</v>
       </c>
-      <c r="J56" s="5" t="n">
-        <v>17</v>
-      </c>
       <c r="K56" s="5" t="n">
         <v>0</v>
       </c>
@@ -4915,7 +4915,7 @@
         <v>0</v>
       </c>
       <c r="M56" s="5" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="N56" s="5" t="n">
         <v>0</v>
@@ -4924,7 +4924,7 @@
         <v>0</v>
       </c>
       <c r="P56" s="5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="Q56" s="5" t="n">
         <v>0</v>
@@ -4982,11 +4982,11 @@
         <v>48</v>
       </c>
       <c r="I57" t="n">
+        <v>22</v>
+      </c>
+      <c r="J57" t="n">
         <v>24</v>
       </c>
-      <c r="J57" t="n">
-        <v>22</v>
-      </c>
       <c r="K57" t="n">
         <v>0</v>
       </c>
@@ -4994,7 +4994,7 @@
         <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="N57" t="n">
         <v>0</v>
@@ -5003,7 +5003,7 @@
         <v>0</v>
       </c>
       <c r="P57" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="Q57" t="n">
         <v>0</v>
@@ -5061,11 +5061,11 @@
         <v>47</v>
       </c>
       <c r="I58" s="5" t="n">
+        <v>22</v>
+      </c>
+      <c r="J58" s="5" t="n">
         <v>26</v>
       </c>
-      <c r="J58" s="5" t="n">
-        <v>22</v>
-      </c>
       <c r="K58" s="5" t="n">
         <v>0</v>
       </c>
@@ -5073,7 +5073,7 @@
         <v>0</v>
       </c>
       <c r="M58" s="5" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="N58" s="5" t="n">
         <v>0</v>
@@ -5082,7 +5082,7 @@
         <v>0</v>
       </c>
       <c r="P58" s="5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="Q58" s="5" t="n">
         <v>0</v>
@@ -5140,11 +5140,11 @@
         <v>47</v>
       </c>
       <c r="I59" t="n">
+        <v>16</v>
+      </c>
+      <c r="J59" t="n">
         <v>26</v>
       </c>
-      <c r="J59" t="n">
-        <v>16</v>
-      </c>
       <c r="K59" t="n">
         <v>0</v>
       </c>
@@ -5152,7 +5152,7 @@
         <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="N59" t="n">
         <v>0</v>
@@ -5161,7 +5161,7 @@
         <v>0</v>
       </c>
       <c r="P59" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="Q59" t="n">
         <v>0</v>
@@ -5219,11 +5219,11 @@
         <v>46</v>
       </c>
       <c r="I60" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="J60" s="5" t="n">
         <v>23</v>
       </c>
-      <c r="J60" s="5" t="n">
-        <v>16</v>
-      </c>
       <c r="K60" s="5" t="n">
         <v>0</v>
       </c>
@@ -5231,7 +5231,7 @@
         <v>0</v>
       </c>
       <c r="M60" s="5" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="N60" s="5" t="n">
         <v>0</v>
@@ -5240,7 +5240,7 @@
         <v>0</v>
       </c>
       <c r="P60" s="5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="Q60" s="5" t="n">
         <v>0</v>
@@ -5298,11 +5298,11 @@
         <v>43</v>
       </c>
       <c r="I61" t="n">
+        <v>16</v>
+      </c>
+      <c r="J61" t="n">
         <v>29</v>
       </c>
-      <c r="J61" t="n">
-        <v>16</v>
-      </c>
       <c r="K61" t="n">
         <v>0</v>
       </c>
@@ -5310,7 +5310,7 @@
         <v>0</v>
       </c>
       <c r="M61" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="N61" t="n">
         <v>0</v>
@@ -5319,7 +5319,7 @@
         <v>0</v>
       </c>
       <c r="P61" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="Q61" t="n">
         <v>0</v>
@@ -5377,11 +5377,11 @@
         <v>43</v>
       </c>
       <c r="I62" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="J62" s="5" t="n">
         <v>29</v>
       </c>
-      <c r="J62" s="5" t="n">
-        <v>16</v>
-      </c>
       <c r="K62" s="5" t="n">
         <v>0</v>
       </c>
@@ -5389,7 +5389,7 @@
         <v>0</v>
       </c>
       <c r="M62" s="5" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="N62" s="5" t="n">
         <v>0</v>
@@ -5398,7 +5398,7 @@
         <v>0</v>
       </c>
       <c r="P62" s="5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="Q62" s="5" t="n">
         <v>0</v>
@@ -5456,11 +5456,11 @@
         <v>43</v>
       </c>
       <c r="I63" t="n">
+        <v>16</v>
+      </c>
+      <c r="J63" t="n">
         <v>29</v>
       </c>
-      <c r="J63" t="n">
-        <v>16</v>
-      </c>
       <c r="K63" t="n">
         <v>0</v>
       </c>
@@ -5468,7 +5468,7 @@
         <v>0</v>
       </c>
       <c r="M63" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="N63" t="n">
         <v>0</v>
@@ -5477,7 +5477,7 @@
         <v>0</v>
       </c>
       <c r="P63" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="Q63" t="n">
         <v>0</v>
@@ -5535,11 +5535,11 @@
         <v>42</v>
       </c>
       <c r="I64" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="J64" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="J64" s="5" t="n">
-        <v>16</v>
-      </c>
       <c r="K64" s="5" t="n">
         <v>0</v>
       </c>
@@ -5547,7 +5547,7 @@
         <v>0</v>
       </c>
       <c r="M64" s="5" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="N64" s="5" t="n">
         <v>0</v>
@@ -5556,7 +5556,7 @@
         <v>0</v>
       </c>
       <c r="P64" s="5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="Q64" s="5" t="n">
         <v>0</v>
@@ -5614,11 +5614,11 @@
         <v>46</v>
       </c>
       <c r="I65" t="n">
+        <v>21</v>
+      </c>
+      <c r="J65" t="n">
         <v>20</v>
       </c>
-      <c r="J65" t="n">
-        <v>21</v>
-      </c>
       <c r="K65" t="n">
         <v>0</v>
       </c>
@@ -5626,7 +5626,7 @@
         <v>0</v>
       </c>
       <c r="M65" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="N65" t="n">
         <v>0</v>
@@ -5635,7 +5635,7 @@
         <v>0</v>
       </c>
       <c r="P65" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="Q65" t="n">
         <v>0</v>
@@ -5693,11 +5693,11 @@
         <v>42</v>
       </c>
       <c r="I66" s="5" t="n">
+        <v>21</v>
+      </c>
+      <c r="J66" s="5" t="n">
         <v>26</v>
       </c>
-      <c r="J66" s="5" t="n">
-        <v>21</v>
-      </c>
       <c r="K66" s="5" t="n">
         <v>0</v>
       </c>
@@ -5705,7 +5705,7 @@
         <v>0</v>
       </c>
       <c r="M66" s="5" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="N66" s="5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>0</v>
       </c>
       <c r="P66" s="5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="Q66" s="5" t="n">
         <v>0</v>
@@ -5772,24 +5772,24 @@
         <v>53</v>
       </c>
       <c r="I67" t="n">
+        <v>21</v>
+      </c>
+      <c r="J67" t="n">
         <v>26</v>
       </c>
-      <c r="J67" t="n">
-        <v>21</v>
-      </c>
       <c r="K67" t="n">
         <v>0</v>
       </c>
       <c r="L67" t="n">
         <v>0</v>
       </c>
-      <c r="M67" t="n">
-        <v>0</v>
-      </c>
       <c r="N67" t="n">
         <v>0</v>
       </c>
       <c r="O67" t="n">
+        <v>0</v>
+      </c>
+      <c r="P67" t="n">
         <v>0</v>
       </c>
       <c r="Q67" t="n">
@@ -5848,11 +5848,11 @@
         <v>53</v>
       </c>
       <c r="I68" s="5" t="n">
+        <v>21</v>
+      </c>
+      <c r="J68" s="5" t="n">
         <v>26</v>
       </c>
-      <c r="J68" s="5" t="n">
-        <v>21</v>
-      </c>
       <c r="K68" s="5" t="n">
         <v>0</v>
       </c>
@@ -5860,7 +5860,7 @@
         <v>0</v>
       </c>
       <c r="M68" s="5" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="N68" s="5" t="n">
         <v>0</v>
@@ -5869,7 +5869,7 @@
         <v>0</v>
       </c>
       <c r="P68" s="5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="Q68" s="5" t="n">
         <v>0</v>
@@ -5924,24 +5924,24 @@
         <v>0</v>
       </c>
       <c r="I69" t="n">
+        <v>21</v>
+      </c>
+      <c r="J69" t="n">
         <v>26</v>
       </c>
-      <c r="J69" t="n">
-        <v>21</v>
-      </c>
       <c r="K69" t="n">
         <v>0</v>
       </c>
       <c r="L69" t="n">
         <v>0</v>
       </c>
-      <c r="M69" t="n">
-        <v>0</v>
-      </c>
       <c r="N69" t="n">
         <v>0</v>
       </c>
       <c r="O69" t="n">
+        <v>0</v>
+      </c>
+      <c r="P69" t="n">
         <v>0</v>
       </c>
       <c r="Q69" t="n">
@@ -6000,11 +6000,11 @@
         <v>53</v>
       </c>
       <c r="I70" s="5" t="n">
+        <v>21</v>
+      </c>
+      <c r="J70" s="5" t="n">
         <v>26</v>
       </c>
-      <c r="J70" s="5" t="n">
-        <v>21</v>
-      </c>
       <c r="K70" s="5" t="n">
         <v>0</v>
       </c>
@@ -6012,7 +6012,7 @@
         <v>0</v>
       </c>
       <c r="M70" s="5" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="N70" s="5" t="n">
         <v>0</v>
@@ -6021,7 +6021,7 @@
         <v>0</v>
       </c>
       <c r="P70" s="5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="Q70" s="5" t="n">
         <v>0</v>
@@ -6079,11 +6079,11 @@
         <v>42</v>
       </c>
       <c r="I71" t="n">
+        <v>21</v>
+      </c>
+      <c r="J71" t="n">
         <v>26</v>
       </c>
-      <c r="J71" t="n">
-        <v>21</v>
-      </c>
       <c r="K71" t="n">
         <v>0</v>
       </c>
@@ -6091,7 +6091,7 @@
         <v>0</v>
       </c>
       <c r="M71" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="N71" t="n">
         <v>0</v>
@@ -6100,7 +6100,7 @@
         <v>0</v>
       </c>
       <c r="P71" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="Q71" t="n">
         <v>0</v>
@@ -6158,11 +6158,11 @@
         <v>42</v>
       </c>
       <c r="I72" s="5" t="n">
+        <v>21</v>
+      </c>
+      <c r="J72" s="5" t="n">
         <v>26</v>
       </c>
-      <c r="J72" s="5" t="n">
-        <v>21</v>
-      </c>
       <c r="K72" s="5" t="n">
         <v>0</v>
       </c>
@@ -6170,7 +6170,7 @@
         <v>0</v>
       </c>
       <c r="M72" s="5" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="N72" s="5" t="n">
         <v>0</v>
@@ -6179,7 +6179,7 @@
         <v>0</v>
       </c>
       <c r="P72" s="5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="Q72" s="5" t="n">
         <v>0</v>
@@ -6237,11 +6237,11 @@
         <v>42</v>
       </c>
       <c r="I73" t="n">
+        <v>19</v>
+      </c>
+      <c r="J73" t="n">
         <v>26</v>
       </c>
-      <c r="J73" t="n">
-        <v>19</v>
-      </c>
       <c r="K73" t="n">
         <v>0</v>
       </c>
@@ -6249,7 +6249,7 @@
         <v>0</v>
       </c>
       <c r="M73" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="N73" t="n">
         <v>0</v>
@@ -6258,7 +6258,7 @@
         <v>0</v>
       </c>
       <c r="P73" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="Q73" t="n">
         <v>0</v>
@@ -6316,11 +6316,11 @@
         <v>42</v>
       </c>
       <c r="I74" s="5" t="n">
+        <v>23</v>
+      </c>
+      <c r="J74" s="5" t="n">
         <v>26</v>
       </c>
-      <c r="J74" s="5" t="n">
-        <v>23</v>
-      </c>
       <c r="K74" s="5" t="n">
         <v>0</v>
       </c>
@@ -6328,7 +6328,7 @@
         <v>0</v>
       </c>
       <c r="M74" s="5" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="N74" s="5" t="n">
         <v>0</v>
@@ -6337,7 +6337,7 @@
         <v>0</v>
       </c>
       <c r="P74" s="5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="Q74" s="5" t="n">
         <v>0</v>
@@ -6395,11 +6395,11 @@
         <v>42</v>
       </c>
       <c r="I75" t="n">
+        <v>23</v>
+      </c>
+      <c r="J75" t="n">
         <v>26</v>
       </c>
-      <c r="J75" t="n">
-        <v>23</v>
-      </c>
       <c r="K75" t="n">
         <v>0</v>
       </c>
@@ -6407,7 +6407,7 @@
         <v>0</v>
       </c>
       <c r="M75" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="N75" t="n">
         <v>0</v>
@@ -6416,7 +6416,7 @@
         <v>0</v>
       </c>
       <c r="P75" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="Q75" t="n">
         <v>0</v>
@@ -6474,11 +6474,11 @@
         <v>42</v>
       </c>
       <c r="I76" s="5" t="n">
+        <v>23</v>
+      </c>
+      <c r="J76" s="5" t="n">
         <v>26</v>
       </c>
-      <c r="J76" s="5" t="n">
-        <v>23</v>
-      </c>
       <c r="K76" s="5" t="n">
         <v>0</v>
       </c>
@@ -6486,7 +6486,7 @@
         <v>0</v>
       </c>
       <c r="M76" s="5" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="N76" s="5" t="n">
         <v>0</v>
@@ -6495,19 +6495,19 @@
         <v>0</v>
       </c>
       <c r="P76" s="5" t="n">
-        <v>24</v>
-      </c>
-      <c r="Q76" s="5" t="n"/>
+        <v>0</v>
+      </c>
+      <c r="Q76" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="R76" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="S76" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T76" s="5" t="n"/>
-      <c r="U76" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="S76" s="5" t="n"/>
+      <c r="T76" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U76" s="5" t="n"/>
       <c r="V76" s="5" t="n">
         <v>0</v>
       </c>
@@ -6549,24 +6549,24 @@
         <v>42</v>
       </c>
       <c r="I77" t="n">
+        <v>23</v>
+      </c>
+      <c r="J77" t="n">
         <v>26</v>
       </c>
-      <c r="J77" t="n">
-        <v>23</v>
-      </c>
       <c r="K77" t="n">
         <v>0</v>
       </c>
       <c r="L77" t="n">
         <v>0</v>
       </c>
-      <c r="M77" t="n">
-        <v>0</v>
-      </c>
       <c r="N77" t="n">
         <v>0</v>
       </c>
       <c r="O77" t="n">
+        <v>0</v>
+      </c>
+      <c r="P77" t="n">
         <v>0</v>
       </c>
       <c r="Q77" t="n">
@@ -6625,11 +6625,11 @@
         <v>42</v>
       </c>
       <c r="I78" s="5" t="n">
+        <v>23</v>
+      </c>
+      <c r="J78" s="5" t="n">
         <v>26</v>
       </c>
-      <c r="J78" s="5" t="n">
-        <v>23</v>
-      </c>
       <c r="K78" s="5" t="n">
         <v>0</v>
       </c>
@@ -6637,7 +6637,7 @@
         <v>0</v>
       </c>
       <c r="M78" s="5" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="N78" s="5" t="n">
         <v>0</v>
@@ -6646,7 +6646,7 @@
         <v>0</v>
       </c>
       <c r="P78" s="5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="Q78" s="5" t="n">
         <v>0</v>
@@ -6704,24 +6704,24 @@
         <v>42</v>
       </c>
       <c r="I79" t="n">
+        <v>23</v>
+      </c>
+      <c r="J79" t="n">
         <v>26</v>
       </c>
-      <c r="J79" t="n">
-        <v>23</v>
-      </c>
       <c r="K79" t="n">
         <v>0</v>
       </c>
       <c r="L79" t="n">
         <v>0</v>
       </c>
-      <c r="M79" t="n">
-        <v>0</v>
-      </c>
       <c r="N79" t="n">
         <v>0</v>
       </c>
       <c r="O79" t="n">
+        <v>0</v>
+      </c>
+      <c r="P79" t="n">
         <v>0</v>
       </c>
       <c r="Q79" t="n">
@@ -6780,27 +6780,27 @@
         <v>42</v>
       </c>
       <c r="I80" s="5" t="n">
+        <v>23</v>
+      </c>
+      <c r="J80" s="5" t="n">
         <v>26</v>
       </c>
-      <c r="J80" s="5" t="n">
-        <v>23</v>
-      </c>
       <c r="K80" s="5" t="n">
         <v>0</v>
       </c>
       <c r="L80" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="M80" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="M80" s="5" t="n"/>
       <c r="N80" s="5" t="n">
         <v>0</v>
       </c>
       <c r="O80" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="P80" s="5" t="n"/>
+      <c r="P80" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="Q80" s="5" t="n">
         <v>0</v>
       </c>
@@ -6857,11 +6857,11 @@
         <v>42</v>
       </c>
       <c r="I81" t="n">
+        <v>23</v>
+      </c>
+      <c r="J81" t="n">
         <v>26</v>
       </c>
-      <c r="J81" t="n">
-        <v>23</v>
-      </c>
       <c r="K81" t="n">
         <v>0</v>
       </c>
@@ -6869,7 +6869,7 @@
         <v>0</v>
       </c>
       <c r="M81" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="N81" t="n">
         <v>0</v>
@@ -6878,7 +6878,7 @@
         <v>0</v>
       </c>
       <c r="P81" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="Q81" t="n">
         <v>0</v>
@@ -6936,27 +6936,27 @@
         <v>42</v>
       </c>
       <c r="I82" s="5" t="n">
+        <v>23</v>
+      </c>
+      <c r="J82" s="5" t="n">
         <v>26</v>
       </c>
-      <c r="J82" s="5" t="n">
-        <v>23</v>
-      </c>
       <c r="K82" s="5" t="n">
         <v>0</v>
       </c>
       <c r="L82" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="M82" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="M82" s="5" t="n"/>
       <c r="N82" s="5" t="n">
         <v>0</v>
       </c>
       <c r="O82" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="P82" s="5" t="n"/>
+      <c r="P82" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="Q82" s="5" t="n">
         <v>0</v>
       </c>
@@ -7010,11 +7010,11 @@
         <v>0</v>
       </c>
       <c r="I83" t="n">
+        <v>23</v>
+      </c>
+      <c r="J83" t="n">
         <v>26</v>
       </c>
-      <c r="J83" t="n">
-        <v>23</v>
-      </c>
       <c r="K83" t="n">
         <v>0</v>
       </c>
@@ -7022,7 +7022,7 @@
         <v>0</v>
       </c>
       <c r="M83" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="N83" t="n">
         <v>0</v>
@@ -7031,7 +7031,7 @@
         <v>0</v>
       </c>
       <c r="P83" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="Q83" t="n">
         <v>0</v>
@@ -7089,11 +7089,11 @@
         <v>42</v>
       </c>
       <c r="I84" s="5" t="n">
+        <v>23</v>
+      </c>
+      <c r="J84" s="5" t="n">
         <v>26</v>
       </c>
-      <c r="J84" s="5" t="n">
-        <v>23</v>
-      </c>
       <c r="K84" s="5" t="n">
         <v>0</v>
       </c>
@@ -7101,7 +7101,7 @@
         <v>0</v>
       </c>
       <c r="M84" s="5" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="N84" s="5" t="n">
         <v>0</v>
@@ -7110,7 +7110,7 @@
         <v>0</v>
       </c>
       <c r="P84" s="5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="Q84" s="5" t="n">
         <v>0</v>
@@ -7168,24 +7168,24 @@
         <v>42</v>
       </c>
       <c r="I85" t="n">
+        <v>23</v>
+      </c>
+      <c r="J85" t="n">
         <v>15</v>
       </c>
-      <c r="J85" t="n">
-        <v>23</v>
-      </c>
       <c r="K85" t="n">
         <v>0</v>
       </c>
       <c r="L85" t="n">
         <v>0</v>
       </c>
-      <c r="M85" t="n">
-        <v>0</v>
-      </c>
       <c r="N85" t="n">
         <v>0</v>
       </c>
       <c r="O85" t="n">
+        <v>0</v>
+      </c>
+      <c r="P85" t="n">
         <v>0</v>
       </c>
       <c r="Q85" t="n">
@@ -7244,27 +7244,27 @@
         <v>42</v>
       </c>
       <c r="I86" s="5" t="n">
+        <v>23</v>
+      </c>
+      <c r="J86" s="5" t="n">
         <v>12</v>
       </c>
-      <c r="J86" s="5" t="n">
-        <v>23</v>
-      </c>
       <c r="K86" s="5" t="n">
         <v>0</v>
       </c>
       <c r="L86" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="M86" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="M86" s="5" t="n"/>
       <c r="N86" s="5" t="n">
         <v>0</v>
       </c>
       <c r="O86" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="P86" s="5" t="n"/>
+      <c r="P86" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="Q86" s="5" t="n">
         <v>0</v>
       </c>
@@ -7321,24 +7321,24 @@
         <v>42</v>
       </c>
       <c r="I87" t="n">
+        <v>23</v>
+      </c>
+      <c r="J87" t="n">
         <v>12</v>
       </c>
-      <c r="J87" t="n">
-        <v>23</v>
-      </c>
       <c r="K87" t="n">
         <v>0</v>
       </c>
       <c r="L87" t="n">
         <v>0</v>
       </c>
-      <c r="M87" t="n">
-        <v>0</v>
-      </c>
       <c r="N87" t="n">
         <v>0</v>
       </c>
       <c r="O87" t="n">
+        <v>0</v>
+      </c>
+      <c r="P87" t="n">
         <v>0</v>
       </c>
       <c r="Q87" t="n">
@@ -7397,27 +7397,27 @@
         <v>42</v>
       </c>
       <c r="I88" s="5" t="n">
+        <v>23</v>
+      </c>
+      <c r="J88" s="5" t="n">
         <v>14</v>
       </c>
-      <c r="J88" s="5" t="n">
-        <v>23</v>
-      </c>
       <c r="K88" s="5" t="n">
         <v>0</v>
       </c>
       <c r="L88" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="M88" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="M88" s="5" t="n"/>
       <c r="N88" s="5" t="n">
         <v>0</v>
       </c>
       <c r="O88" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="P88" s="5" t="n"/>
+      <c r="P88" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="Q88" s="5" t="n">
         <v>0</v>
       </c>
@@ -7474,24 +7474,24 @@
         <v>42</v>
       </c>
       <c r="I89" t="n">
+        <v>18</v>
+      </c>
+      <c r="J89" t="n">
         <v>19</v>
       </c>
-      <c r="J89" t="n">
-        <v>18</v>
-      </c>
       <c r="K89" t="n">
         <v>0</v>
       </c>
       <c r="L89" t="n">
         <v>0</v>
       </c>
-      <c r="M89" t="n">
-        <v>0</v>
-      </c>
       <c r="N89" t="n">
         <v>0</v>
       </c>
       <c r="O89" t="n">
+        <v>0</v>
+      </c>
+      <c r="P89" t="n">
         <v>0</v>
       </c>
       <c r="Q89" t="n">
@@ -7549,10 +7549,10 @@
       <c r="H90" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="I90" s="5" t="n"/>
-      <c r="J90" s="5" t="n">
+      <c r="I90" s="5" t="n">
         <v>18</v>
       </c>
+      <c r="J90" s="5" t="n"/>
       <c r="K90" s="5" t="n">
         <v>0</v>
       </c>
@@ -7560,7 +7560,7 @@
         <v>0</v>
       </c>
       <c r="M90" s="5" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="N90" s="5" t="n">
         <v>0</v>
@@ -7569,7 +7569,7 @@
         <v>0</v>
       </c>
       <c r="P90" s="5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="Q90" s="5" t="n">
         <v>0</v>
@@ -7627,24 +7627,24 @@
         <v>42</v>
       </c>
       <c r="I91" t="n">
+        <v>18</v>
+      </c>
+      <c r="J91" t="n">
         <v>19</v>
       </c>
-      <c r="J91" t="n">
-        <v>18</v>
-      </c>
       <c r="K91" t="n">
         <v>0</v>
       </c>
       <c r="L91" t="n">
         <v>0</v>
       </c>
-      <c r="M91" t="n">
-        <v>0</v>
-      </c>
       <c r="N91" t="n">
         <v>0</v>
       </c>
       <c r="O91" t="n">
+        <v>0</v>
+      </c>
+      <c r="P91" t="n">
         <v>0</v>
       </c>
       <c r="Q91" t="n">
@@ -7703,27 +7703,27 @@
         <v>42</v>
       </c>
       <c r="I92" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="J92" s="5" t="n">
         <v>19</v>
       </c>
-      <c r="J92" s="5" t="n">
-        <v>18</v>
-      </c>
       <c r="K92" s="5" t="n">
         <v>0</v>
       </c>
       <c r="L92" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="M92" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="M92" s="5" t="n"/>
       <c r="N92" s="5" t="n">
         <v>0</v>
       </c>
       <c r="O92" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="P92" s="5" t="n"/>
+      <c r="P92" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="Q92" s="5" t="n">
         <v>0</v>
       </c>
@@ -7780,51 +7780,128 @@
         <v>42</v>
       </c>
       <c r="I93" t="n">
+        <v>18</v>
+      </c>
+      <c r="J93" t="n">
         <v>23</v>
       </c>
-      <c r="J93" t="n">
+      <c r="K93" t="n">
+        <v>0</v>
+      </c>
+      <c r="L93" t="n">
+        <v>0</v>
+      </c>
+      <c r="N93" t="n">
+        <v>0</v>
+      </c>
+      <c r="O93" t="n">
+        <v>0</v>
+      </c>
+      <c r="P93" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q93" t="n">
+        <v>0</v>
+      </c>
+      <c r="R93" t="n">
+        <v>0</v>
+      </c>
+      <c r="S93" t="n">
+        <v>0</v>
+      </c>
+      <c r="T93" t="n">
+        <v>0</v>
+      </c>
+      <c r="U93" t="n">
+        <v>0</v>
+      </c>
+      <c r="V93" t="n">
+        <v>0</v>
+      </c>
+      <c r="W93" t="n">
+        <v>0</v>
+      </c>
+      <c r="X93" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y93" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B94" s="5" t="n">
+        <v>876</v>
+      </c>
+      <c r="C94" s="5" t="n">
+        <v>523</v>
+      </c>
+      <c r="D94" s="5" t="n">
+        <v>382</v>
+      </c>
+      <c r="E94" s="5" t="n">
+        <v>315</v>
+      </c>
+      <c r="F94" s="5" t="n">
+        <v>218</v>
+      </c>
+      <c r="G94" s="5" t="n">
+        <v>101</v>
+      </c>
+      <c r="H94" s="5" t="n">
+        <v>42</v>
+      </c>
+      <c r="I94" s="5" t="n">
         <v>18</v>
       </c>
-      <c r="K93" t="n">
-        <v>0</v>
-      </c>
-      <c r="L93" t="n">
-        <v>0</v>
-      </c>
-      <c r="M93" t="n">
-        <v>0</v>
-      </c>
-      <c r="N93" t="n">
-        <v>0</v>
-      </c>
-      <c r="O93" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q93" t="n">
-        <v>0</v>
-      </c>
-      <c r="R93" t="n">
-        <v>0</v>
-      </c>
-      <c r="S93" t="n">
-        <v>0</v>
-      </c>
-      <c r="T93" t="n">
-        <v>0</v>
-      </c>
-      <c r="U93" t="n">
-        <v>0</v>
-      </c>
-      <c r="V93" t="n">
-        <v>0</v>
-      </c>
-      <c r="W93" t="n">
-        <v>0</v>
-      </c>
-      <c r="X93" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y93" t="n">
+      <c r="J94" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="K94" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L94" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M94" s="5" t="n"/>
+      <c r="N94" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O94" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P94" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q94" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R94" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S94" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T94" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U94" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V94" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W94" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X94" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y94" s="5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7866,7 +7943,7 @@
       </c>
       <c r="D1" s="3" t="inlineStr">
         <is>
-          <t>Lager (2026-10-07)</t>
+          <t>Lager (2026-10-08)</t>
         </is>
       </c>
     </row>
@@ -7887,7 +7964,7 @@
         </is>
       </c>
       <c r="D2" s="4" t="n">
-        <v>515</v>
+        <v>523</v>
       </c>
     </row>
     <row r="3">
@@ -15767,7 +15844,7 @@
         </is>
       </c>
       <c r="D396" s="4" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
     </row>
     <row r="397">
@@ -16227,7 +16304,7 @@
         </is>
       </c>
       <c r="D419" s="6" t="n">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="420">
@@ -16247,7 +16324,7 @@
         </is>
       </c>
       <c r="D420" s="4" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="421">
@@ -25347,7 +25424,7 @@
         </is>
       </c>
       <c r="D875" s="6" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="876">
@@ -27167,7 +27244,7 @@
         </is>
       </c>
       <c r="D966" s="4" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="967">
@@ -30247,7 +30324,7 @@
         </is>
       </c>
       <c r="D1120" s="4" t="n">
-        <v>467</v>
+        <v>473</v>
       </c>
     </row>
     <row r="1121">
@@ -30267,7 +30344,7 @@
         </is>
       </c>
       <c r="D1121" s="6" t="n">
-        <v>316</v>
+        <v>314</v>
       </c>
     </row>
   </sheetData>

--- a/data/ahlsell_led_panel_inventory.xlsx
+++ b/data/ahlsell_led_panel_inventory.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y95"/>
+  <dimension ref="A1:Y96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -523,92 +523,92 @@
       </c>
       <c r="H1" s="3" t="inlineStr">
         <is>
+          <t>Ledvance</t>
+        </is>
+      </c>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
           <t>Designlight</t>
         </is>
       </c>
-      <c r="I1" s="3" t="inlineStr">
+      <c r="J1" s="3" t="inlineStr">
         <is>
           <t>Exaktor</t>
         </is>
       </c>
-      <c r="J1" s="3" t="inlineStr">
-        <is>
-          <t>Ledvance</t>
-        </is>
-      </c>
       <c r="K1" s="3" t="inlineStr">
         <is>
+          <t>THORN</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="inlineStr">
+        <is>
+          <t>Siteco</t>
+        </is>
+      </c>
+      <c r="M1" s="3" t="inlineStr">
+        <is>
+          <t>Westal</t>
+        </is>
+      </c>
+      <c r="N1" s="3" t="inlineStr">
+        <is>
+          <t>Esylux</t>
+        </is>
+      </c>
+      <c r="O1" s="3" t="inlineStr">
+        <is>
+          <t>ZG Lighting</t>
+        </is>
+      </c>
+      <c r="P1" s="3" t="inlineStr">
+        <is>
+          <t>ANETA LIGHTING</t>
+        </is>
+      </c>
+      <c r="Q1" s="3" t="inlineStr">
+        <is>
+          <t>Ensto</t>
+        </is>
+      </c>
+      <c r="R1" s="3" t="inlineStr">
+        <is>
+          <t>Black Box</t>
+        </is>
+      </c>
+      <c r="S1" s="3" t="inlineStr">
+        <is>
+          <t>Norwesco</t>
+        </is>
+      </c>
+      <c r="T1" s="3" t="inlineStr">
+        <is>
+          <t>Airam</t>
+        </is>
+      </c>
+      <c r="U1" s="3" t="inlineStr">
+        <is>
+          <t>Easyform</t>
+        </is>
+      </c>
+      <c r="V1" s="3" t="inlineStr">
+        <is>
+          <t>Bergdahls</t>
+        </is>
+      </c>
+      <c r="W1" s="3" t="inlineStr">
+        <is>
+          <t>Legrand</t>
+        </is>
+      </c>
+      <c r="X1" s="3" t="inlineStr">
+        <is>
           <t>Philips</t>
         </is>
       </c>
-      <c r="L1" s="3" t="inlineStr">
-        <is>
-          <t>Easyform</t>
-        </is>
-      </c>
-      <c r="M1" s="3" t="inlineStr">
-        <is>
-          <t>Westal</t>
-        </is>
-      </c>
-      <c r="N1" s="3" t="inlineStr">
-        <is>
-          <t>Black Box</t>
-        </is>
-      </c>
-      <c r="O1" s="3" t="inlineStr">
-        <is>
-          <t>Siteco</t>
-        </is>
-      </c>
-      <c r="P1" s="3" t="inlineStr">
-        <is>
-          <t>Airam</t>
-        </is>
-      </c>
-      <c r="Q1" s="3" t="inlineStr">
-        <is>
-          <t>Ensto</t>
-        </is>
-      </c>
-      <c r="R1" s="3" t="inlineStr">
-        <is>
-          <t>ZG Lighting</t>
-        </is>
-      </c>
-      <c r="S1" s="3" t="inlineStr">
-        <is>
-          <t>Esylux</t>
-        </is>
-      </c>
-      <c r="T1" s="3" t="inlineStr">
-        <is>
-          <t>THORN</t>
-        </is>
-      </c>
-      <c r="U1" s="3" t="inlineStr">
-        <is>
-          <t>Bergdahls</t>
-        </is>
-      </c>
-      <c r="V1" s="3" t="inlineStr">
-        <is>
-          <t>Norwesco</t>
-        </is>
-      </c>
-      <c r="W1" s="3" t="inlineStr">
-        <is>
-          <t>Legrand</t>
-        </is>
-      </c>
-      <c r="X1" s="3" t="inlineStr">
+      <c r="Y1" s="3" t="inlineStr">
         <is>
           <t>Nokalux</t>
-        </is>
-      </c>
-      <c r="Y1" s="3" t="inlineStr">
-        <is>
-          <t>ANETA LIGHTING</t>
         </is>
       </c>
     </row>
@@ -637,14 +637,14 @@
         <v>93</v>
       </c>
       <c r="H2" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="I2" s="5" t="n">
         <v>52</v>
       </c>
-      <c r="I2" s="5" t="n">
+      <c r="J2" s="5" t="n">
         <v>33</v>
       </c>
-      <c r="J2" s="5" t="n">
-        <v>17</v>
-      </c>
       <c r="K2" s="5" t="n">
         <v>0</v>
       </c>
@@ -655,7 +655,7 @@
         <v>0</v>
       </c>
       <c r="N2" s="5" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="O2" s="5" t="n">
         <v>0</v>
@@ -670,7 +670,7 @@
         <v>0</v>
       </c>
       <c r="S2" s="5" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="T2" s="5" t="n">
         <v>0</v>
@@ -716,14 +716,14 @@
         <v>93</v>
       </c>
       <c r="H3" t="n">
+        <v>17</v>
+      </c>
+      <c r="I3" t="n">
         <v>52</v>
       </c>
-      <c r="I3" t="n">
+      <c r="J3" t="n">
         <v>33</v>
       </c>
-      <c r="J3" t="n">
-        <v>17</v>
-      </c>
       <c r="K3" t="n">
         <v>0</v>
       </c>
@@ -734,7 +734,7 @@
         <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -749,7 +749,7 @@
         <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
         <v>0</v>
@@ -795,14 +795,14 @@
         <v>100</v>
       </c>
       <c r="H4" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="I4" s="5" t="n">
         <v>52</v>
       </c>
-      <c r="I4" s="5" t="n">
+      <c r="J4" s="5" t="n">
         <v>33</v>
       </c>
-      <c r="J4" s="5" t="n">
-        <v>17</v>
-      </c>
       <c r="K4" s="5" t="n">
         <v>0</v>
       </c>
@@ -813,7 +813,7 @@
         <v>0</v>
       </c>
       <c r="N4" s="5" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="O4" s="5" t="n">
         <v>0</v>
@@ -828,7 +828,7 @@
         <v>0</v>
       </c>
       <c r="S4" s="5" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="T4" s="5" t="n">
         <v>0</v>
@@ -874,14 +874,14 @@
         <v>100</v>
       </c>
       <c r="H5" t="n">
+        <v>17</v>
+      </c>
+      <c r="I5" t="n">
         <v>52</v>
       </c>
-      <c r="I5" t="n">
+      <c r="J5" t="n">
         <v>33</v>
       </c>
-      <c r="J5" t="n">
-        <v>17</v>
-      </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
@@ -892,7 +892,7 @@
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -907,7 +907,7 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
         <v>0</v>
@@ -953,14 +953,14 @@
         <v>100</v>
       </c>
       <c r="H6" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="I6" s="5" t="n">
         <v>52</v>
       </c>
-      <c r="I6" s="5" t="n">
+      <c r="J6" s="5" t="n">
         <v>33</v>
       </c>
-      <c r="J6" s="5" t="n">
-        <v>17</v>
-      </c>
       <c r="K6" s="5" t="n">
         <v>0</v>
       </c>
@@ -971,7 +971,7 @@
         <v>0</v>
       </c>
       <c r="N6" s="5" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="O6" s="5" t="n">
         <v>0</v>
@@ -986,7 +986,7 @@
         <v>0</v>
       </c>
       <c r="S6" s="5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="T6" s="5" t="n">
         <v>0</v>
@@ -1029,14 +1029,14 @@
         <v>100</v>
       </c>
       <c r="H7" t="n">
+        <v>17</v>
+      </c>
+      <c r="I7" t="n">
         <v>14</v>
       </c>
-      <c r="I7" t="n">
+      <c r="J7" t="n">
         <v>33</v>
       </c>
-      <c r="J7" t="n">
-        <v>17</v>
-      </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
@@ -1047,7 +1047,7 @@
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1062,7 +1062,7 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
         <v>0</v>
@@ -1108,14 +1108,14 @@
         <v>100</v>
       </c>
       <c r="H8" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="I8" s="5" t="n">
         <v>52</v>
       </c>
-      <c r="I8" s="5" t="n">
+      <c r="J8" s="5" t="n">
         <v>33</v>
       </c>
-      <c r="J8" s="5" t="n">
-        <v>17</v>
-      </c>
       <c r="K8" s="5" t="n">
         <v>0</v>
       </c>
@@ -1126,7 +1126,7 @@
         <v>0</v>
       </c>
       <c r="N8" s="5" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="O8" s="5" t="n">
         <v>0</v>
@@ -1141,7 +1141,7 @@
         <v>0</v>
       </c>
       <c r="S8" s="5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="T8" s="5" t="n">
         <v>0</v>
@@ -1187,14 +1187,14 @@
         <v>100</v>
       </c>
       <c r="H9" t="n">
+        <v>17</v>
+      </c>
+      <c r="I9" t="n">
         <v>52</v>
       </c>
-      <c r="I9" t="n">
+      <c r="J9" t="n">
         <v>33</v>
       </c>
-      <c r="J9" t="n">
-        <v>17</v>
-      </c>
       <c r="K9" t="n">
         <v>0</v>
       </c>
@@ -1205,7 +1205,7 @@
         <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1220,7 +1220,7 @@
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
         <v>0</v>
@@ -1266,14 +1266,14 @@
         <v>100</v>
       </c>
       <c r="H10" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="I10" s="5" t="n">
         <v>52</v>
       </c>
-      <c r="I10" s="5" t="n">
+      <c r="J10" s="5" t="n">
         <v>33</v>
       </c>
-      <c r="J10" s="5" t="n">
-        <v>17</v>
-      </c>
       <c r="K10" s="5" t="n">
         <v>0</v>
       </c>
@@ -1284,7 +1284,7 @@
         <v>0</v>
       </c>
       <c r="N10" s="5" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="O10" s="5" t="n">
         <v>0</v>
@@ -1299,7 +1299,7 @@
         <v>0</v>
       </c>
       <c r="S10" s="5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="T10" s="5" t="n">
         <v>0</v>
@@ -1345,14 +1345,14 @@
         <v>100</v>
       </c>
       <c r="H11" t="n">
+        <v>17</v>
+      </c>
+      <c r="I11" t="n">
         <v>52</v>
       </c>
-      <c r="I11" t="n">
+      <c r="J11" t="n">
         <v>33</v>
       </c>
-      <c r="J11" t="n">
-        <v>17</v>
-      </c>
       <c r="K11" t="n">
         <v>0</v>
       </c>
@@ -1363,7 +1363,7 @@
         <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1378,7 +1378,7 @@
         <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
         <v>0</v>
@@ -1424,14 +1424,14 @@
         <v>94</v>
       </c>
       <c r="H12" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="I12" s="5" t="n">
         <v>52</v>
       </c>
-      <c r="I12" s="5" t="n">
+      <c r="J12" s="5" t="n">
         <v>33</v>
       </c>
-      <c r="J12" s="5" t="n">
-        <v>17</v>
-      </c>
       <c r="K12" s="5" t="n">
         <v>0</v>
       </c>
@@ -1442,7 +1442,7 @@
         <v>0</v>
       </c>
       <c r="N12" s="5" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="O12" s="5" t="n">
         <v>0</v>
@@ -1457,7 +1457,7 @@
         <v>0</v>
       </c>
       <c r="S12" s="5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="T12" s="5" t="n">
         <v>0</v>
@@ -1503,14 +1503,14 @@
         <v>94</v>
       </c>
       <c r="H13" t="n">
+        <v>17</v>
+      </c>
+      <c r="I13" t="n">
         <v>52</v>
       </c>
-      <c r="I13" t="n">
+      <c r="J13" t="n">
         <v>33</v>
       </c>
-      <c r="J13" t="n">
-        <v>17</v>
-      </c>
       <c r="K13" t="n">
         <v>0</v>
       </c>
@@ -1521,7 +1521,7 @@
         <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -1536,7 +1536,7 @@
         <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
         <v>0</v>
@@ -1582,14 +1582,14 @@
         <v>94</v>
       </c>
       <c r="H14" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="I14" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="I14" s="5" t="n">
+      <c r="J14" s="5" t="n">
         <v>33</v>
       </c>
-      <c r="J14" s="5" t="n">
-        <v>6</v>
-      </c>
       <c r="K14" s="5" t="n">
         <v>0</v>
       </c>
@@ -1600,7 +1600,7 @@
         <v>0</v>
       </c>
       <c r="N14" s="5" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="O14" s="5" t="n">
         <v>0</v>
@@ -1615,7 +1615,7 @@
         <v>0</v>
       </c>
       <c r="S14" s="5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="T14" s="5" t="n">
         <v>0</v>
@@ -1661,14 +1661,14 @@
         <v>94</v>
       </c>
       <c r="H15" t="n">
+        <v>17</v>
+      </c>
+      <c r="I15" t="n">
         <v>52</v>
       </c>
-      <c r="I15" t="n">
+      <c r="J15" t="n">
         <v>33</v>
       </c>
-      <c r="J15" t="n">
-        <v>17</v>
-      </c>
       <c r="K15" t="n">
         <v>0</v>
       </c>
@@ -1679,7 +1679,7 @@
         <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -1694,7 +1694,7 @@
         <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
         <v>0</v>
@@ -1740,14 +1740,14 @@
         <v>94</v>
       </c>
       <c r="H16" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="I16" s="5" t="n">
         <v>52</v>
       </c>
-      <c r="I16" s="5" t="n">
+      <c r="J16" s="5" t="n">
         <v>33</v>
       </c>
-      <c r="J16" s="5" t="n">
-        <v>17</v>
-      </c>
       <c r="K16" s="5" t="n">
         <v>0</v>
       </c>
@@ -1758,7 +1758,7 @@
         <v>0</v>
       </c>
       <c r="N16" s="5" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="O16" s="5" t="n">
         <v>0</v>
@@ -1773,7 +1773,7 @@
         <v>0</v>
       </c>
       <c r="S16" s="5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="T16" s="5" t="n">
         <v>0</v>
@@ -1819,14 +1819,14 @@
         <v>94</v>
       </c>
       <c r="H17" t="n">
+        <v>17</v>
+      </c>
+      <c r="I17" t="n">
         <v>52</v>
       </c>
-      <c r="I17" t="n">
+      <c r="J17" t="n">
         <v>33</v>
       </c>
-      <c r="J17" t="n">
-        <v>17</v>
-      </c>
       <c r="K17" t="n">
         <v>0</v>
       </c>
@@ -1837,7 +1837,7 @@
         <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -1852,7 +1852,7 @@
         <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
         <v>0</v>
@@ -1898,14 +1898,14 @@
         <v>102</v>
       </c>
       <c r="H18" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="I18" s="5" t="n">
         <v>52</v>
       </c>
-      <c r="I18" s="5" t="n">
+      <c r="J18" s="5" t="n">
         <v>33</v>
       </c>
-      <c r="J18" s="5" t="n">
-        <v>17</v>
-      </c>
       <c r="K18" s="5" t="n">
         <v>0</v>
       </c>
@@ -1916,7 +1916,7 @@
         <v>0</v>
       </c>
       <c r="N18" s="5" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="O18" s="5" t="n">
         <v>0</v>
@@ -1931,7 +1931,7 @@
         <v>0</v>
       </c>
       <c r="S18" s="5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="T18" s="5" t="n">
         <v>0</v>
@@ -1977,14 +1977,14 @@
         <v>102</v>
       </c>
       <c r="H19" t="n">
+        <v>17</v>
+      </c>
+      <c r="I19" t="n">
         <v>50</v>
       </c>
-      <c r="I19" t="n">
+      <c r="J19" t="n">
         <v>33</v>
       </c>
-      <c r="J19" t="n">
-        <v>17</v>
-      </c>
       <c r="K19" t="n">
         <v>0</v>
       </c>
@@ -1995,7 +1995,7 @@
         <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2010,7 +2010,7 @@
         <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
         <v>0</v>
@@ -2056,14 +2056,14 @@
         <v>102</v>
       </c>
       <c r="H20" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="I20" s="5" t="n">
         <v>50</v>
       </c>
-      <c r="I20" s="5" t="n">
+      <c r="J20" s="5" t="n">
         <v>33</v>
       </c>
-      <c r="J20" s="5" t="n">
-        <v>17</v>
-      </c>
       <c r="K20" s="5" t="n">
         <v>0</v>
       </c>
@@ -2074,7 +2074,7 @@
         <v>0</v>
       </c>
       <c r="N20" s="5" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="O20" s="5" t="n">
         <v>0</v>
@@ -2089,7 +2089,7 @@
         <v>0</v>
       </c>
       <c r="S20" s="5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="T20" s="5" t="n">
         <v>0</v>
@@ -2135,14 +2135,14 @@
         <v>102</v>
       </c>
       <c r="H21" t="n">
+        <v>17</v>
+      </c>
+      <c r="I21" t="n">
         <v>14</v>
       </c>
-      <c r="I21" t="n">
+      <c r="J21" t="n">
         <v>33</v>
       </c>
-      <c r="J21" t="n">
-        <v>17</v>
-      </c>
       <c r="K21" t="n">
         <v>0</v>
       </c>
@@ -2153,7 +2153,7 @@
         <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2168,7 +2168,7 @@
         <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
         <v>0</v>
@@ -2214,14 +2214,14 @@
         <v>102</v>
       </c>
       <c r="H22" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="I22" s="5" t="n">
         <v>50</v>
       </c>
-      <c r="I22" s="5" t="n">
+      <c r="J22" s="5" t="n">
         <v>33</v>
       </c>
-      <c r="J22" s="5" t="n">
-        <v>17</v>
-      </c>
       <c r="K22" s="5" t="n">
         <v>0</v>
       </c>
@@ -2232,7 +2232,7 @@
         <v>0</v>
       </c>
       <c r="N22" s="5" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="O22" s="5" t="n">
         <v>0</v>
@@ -2247,7 +2247,7 @@
         <v>0</v>
       </c>
       <c r="S22" s="5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="T22" s="5" t="n">
         <v>0</v>
@@ -2293,14 +2293,14 @@
         <v>102</v>
       </c>
       <c r="H23" t="n">
+        <v>17</v>
+      </c>
+      <c r="I23" t="n">
         <v>50</v>
       </c>
-      <c r="I23" t="n">
+      <c r="J23" t="n">
         <v>33</v>
       </c>
-      <c r="J23" t="n">
-        <v>17</v>
-      </c>
       <c r="K23" t="n">
         <v>0</v>
       </c>
@@ -2311,7 +2311,7 @@
         <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -2326,7 +2326,7 @@
         <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="T23" t="n">
         <v>0</v>
@@ -2372,14 +2372,14 @@
         <v>102</v>
       </c>
       <c r="H24" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="I24" s="5" t="n">
         <v>48</v>
       </c>
-      <c r="I24" s="5" t="n">
+      <c r="J24" s="5" t="n">
         <v>33</v>
       </c>
-      <c r="J24" s="5" t="n">
-        <v>17</v>
-      </c>
       <c r="K24" s="5" t="n">
         <v>0</v>
       </c>
@@ -2390,7 +2390,7 @@
         <v>0</v>
       </c>
       <c r="N24" s="5" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="O24" s="5" t="n">
         <v>0</v>
@@ -2405,7 +2405,7 @@
         <v>0</v>
       </c>
       <c r="S24" s="5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="T24" s="5" t="n">
         <v>0</v>
@@ -2451,14 +2451,14 @@
         <v>102</v>
       </c>
       <c r="H25" t="n">
+        <v>17</v>
+      </c>
+      <c r="I25" t="n">
         <v>48</v>
       </c>
-      <c r="I25" t="n">
+      <c r="J25" t="n">
         <v>33</v>
       </c>
-      <c r="J25" t="n">
-        <v>17</v>
-      </c>
       <c r="K25" t="n">
         <v>0</v>
       </c>
@@ -2469,7 +2469,7 @@
         <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -2484,7 +2484,7 @@
         <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="T25" t="n">
         <v>0</v>
@@ -2530,14 +2530,14 @@
         <v>102</v>
       </c>
       <c r="H26" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="I26" s="5" t="n">
         <v>48</v>
       </c>
-      <c r="I26" s="5" t="n">
+      <c r="J26" s="5" t="n">
         <v>33</v>
       </c>
-      <c r="J26" s="5" t="n">
-        <v>17</v>
-      </c>
       <c r="K26" s="5" t="n">
         <v>0</v>
       </c>
@@ -2548,7 +2548,7 @@
         <v>0</v>
       </c>
       <c r="N26" s="5" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="O26" s="5" t="n">
         <v>0</v>
@@ -2563,7 +2563,7 @@
         <v>0</v>
       </c>
       <c r="S26" s="5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="T26" s="5" t="n">
         <v>0</v>
@@ -2609,14 +2609,14 @@
         <v>102</v>
       </c>
       <c r="H27" t="n">
+        <v>17</v>
+      </c>
+      <c r="I27" t="n">
         <v>48</v>
       </c>
-      <c r="I27" t="n">
+      <c r="J27" t="n">
         <v>33</v>
       </c>
-      <c r="J27" t="n">
-        <v>17</v>
-      </c>
       <c r="K27" t="n">
         <v>0</v>
       </c>
@@ -2627,7 +2627,7 @@
         <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -2642,7 +2642,7 @@
         <v>0</v>
       </c>
       <c r="S27" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="T27" t="n">
         <v>0</v>
@@ -2688,13 +2688,13 @@
         <v>102</v>
       </c>
       <c r="H28" s="5" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="I28" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" s="5" t="n">
         <v>33</v>
-      </c>
-      <c r="J28" s="5" t="n">
-        <v>17</v>
       </c>
       <c r="K28" s="5" t="n">
         <v>0</v>
@@ -2767,14 +2767,14 @@
         <v>102</v>
       </c>
       <c r="H29" t="n">
+        <v>17</v>
+      </c>
+      <c r="I29" t="n">
         <v>48</v>
       </c>
-      <c r="I29" t="n">
+      <c r="J29" t="n">
         <v>33</v>
       </c>
-      <c r="J29" t="n">
-        <v>17</v>
-      </c>
       <c r="K29" t="n">
         <v>0</v>
       </c>
@@ -2785,7 +2785,7 @@
         <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -2800,7 +2800,7 @@
         <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="T29" t="n">
         <v>0</v>
@@ -2846,14 +2846,14 @@
         <v>102</v>
       </c>
       <c r="H30" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="I30" s="5" t="n">
         <v>48</v>
       </c>
-      <c r="I30" s="5" t="n">
+      <c r="J30" s="5" t="n">
         <v>33</v>
       </c>
-      <c r="J30" s="5" t="n">
-        <v>17</v>
-      </c>
       <c r="K30" s="5" t="n">
         <v>0</v>
       </c>
@@ -2864,7 +2864,7 @@
         <v>0</v>
       </c>
       <c r="N30" s="5" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="O30" s="5" t="n">
         <v>0</v>
@@ -2879,7 +2879,7 @@
         <v>0</v>
       </c>
       <c r="S30" s="5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="T30" s="5" t="n">
         <v>0</v>
@@ -2925,14 +2925,14 @@
         <v>102</v>
       </c>
       <c r="H31" t="n">
+        <v>17</v>
+      </c>
+      <c r="I31" t="n">
         <v>48</v>
       </c>
-      <c r="I31" t="n">
+      <c r="J31" t="n">
         <v>33</v>
       </c>
-      <c r="J31" t="n">
-        <v>17</v>
-      </c>
       <c r="K31" t="n">
         <v>0</v>
       </c>
@@ -2943,7 +2943,7 @@
         <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -2958,7 +2958,7 @@
         <v>0</v>
       </c>
       <c r="S31" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="T31" t="n">
         <v>0</v>
@@ -3004,14 +3004,14 @@
         <v>102</v>
       </c>
       <c r="H32" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="I32" s="5" t="n">
         <v>48</v>
       </c>
-      <c r="I32" s="5" t="n">
+      <c r="J32" s="5" t="n">
         <v>33</v>
       </c>
-      <c r="J32" s="5" t="n">
-        <v>17</v>
-      </c>
       <c r="K32" s="5" t="n">
         <v>0</v>
       </c>
@@ -3022,7 +3022,7 @@
         <v>0</v>
       </c>
       <c r="N32" s="5" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="O32" s="5" t="n">
         <v>0</v>
@@ -3037,7 +3037,7 @@
         <v>0</v>
       </c>
       <c r="S32" s="5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="T32" s="5" t="n">
         <v>0</v>
@@ -3083,14 +3083,14 @@
         <v>102</v>
       </c>
       <c r="H33" t="n">
+        <v>17</v>
+      </c>
+      <c r="I33" t="n">
         <v>48</v>
       </c>
-      <c r="I33" t="n">
+      <c r="J33" t="n">
         <v>33</v>
       </c>
-      <c r="J33" t="n">
-        <v>17</v>
-      </c>
       <c r="K33" t="n">
         <v>0</v>
       </c>
@@ -3101,7 +3101,7 @@
         <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -3116,7 +3116,7 @@
         <v>0</v>
       </c>
       <c r="S33" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="T33" t="n">
         <v>0</v>
@@ -3162,14 +3162,14 @@
         <v>102</v>
       </c>
       <c r="H34" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="I34" s="5" t="n">
         <v>48</v>
       </c>
-      <c r="I34" s="5" t="n">
+      <c r="J34" s="5" t="n">
         <v>33</v>
       </c>
-      <c r="J34" s="5" t="n">
-        <v>17</v>
-      </c>
       <c r="K34" s="5" t="n">
         <v>0</v>
       </c>
@@ -3180,7 +3180,7 @@
         <v>0</v>
       </c>
       <c r="N34" s="5" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="O34" s="5" t="n">
         <v>0</v>
@@ -3195,7 +3195,7 @@
         <v>0</v>
       </c>
       <c r="S34" s="5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="T34" s="5" t="n">
         <v>0</v>
@@ -3241,14 +3241,14 @@
         <v>102</v>
       </c>
       <c r="H35" t="n">
+        <v>17</v>
+      </c>
+      <c r="I35" t="n">
         <v>48</v>
       </c>
-      <c r="I35" t="n">
+      <c r="J35" t="n">
         <v>33</v>
       </c>
-      <c r="J35" t="n">
-        <v>17</v>
-      </c>
       <c r="K35" t="n">
         <v>0</v>
       </c>
@@ -3259,7 +3259,7 @@
         <v>0</v>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -3274,7 +3274,7 @@
         <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="T35" t="n">
         <v>0</v>
@@ -3320,14 +3320,14 @@
         <v>102</v>
       </c>
       <c r="H36" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="I36" s="5" t="n">
         <v>48</v>
       </c>
-      <c r="I36" s="5" t="n">
+      <c r="J36" s="5" t="n">
         <v>33</v>
       </c>
-      <c r="J36" s="5" t="n">
-        <v>17</v>
-      </c>
       <c r="K36" s="5" t="n">
         <v>0</v>
       </c>
@@ -3338,7 +3338,7 @@
         <v>0</v>
       </c>
       <c r="N36" s="5" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="O36" s="5" t="n">
         <v>0</v>
@@ -3353,7 +3353,7 @@
         <v>0</v>
       </c>
       <c r="S36" s="5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="T36" s="5" t="n">
         <v>0</v>
@@ -3399,14 +3399,14 @@
         <v>102</v>
       </c>
       <c r="H37" t="n">
+        <v>17</v>
+      </c>
+      <c r="I37" t="n">
         <v>48</v>
       </c>
-      <c r="I37" t="n">
+      <c r="J37" t="n">
         <v>33</v>
       </c>
-      <c r="J37" t="n">
-        <v>17</v>
-      </c>
       <c r="K37" t="n">
         <v>0</v>
       </c>
@@ -3417,7 +3417,7 @@
         <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -3432,7 +3432,7 @@
         <v>0</v>
       </c>
       <c r="S37" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="T37" t="n">
         <v>0</v>
@@ -3478,14 +3478,14 @@
         <v>101</v>
       </c>
       <c r="H38" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="I38" s="5" t="n">
         <v>48</v>
       </c>
-      <c r="I38" s="5" t="n">
+      <c r="J38" s="5" t="n">
         <v>33</v>
       </c>
-      <c r="J38" s="5" t="n">
-        <v>17</v>
-      </c>
       <c r="K38" s="5" t="n">
         <v>0</v>
       </c>
@@ -3496,7 +3496,7 @@
         <v>0</v>
       </c>
       <c r="N38" s="5" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="O38" s="5" t="n">
         <v>0</v>
@@ -3511,7 +3511,7 @@
         <v>0</v>
       </c>
       <c r="S38" s="5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="T38" s="5" t="n">
         <v>0</v>
@@ -3557,14 +3557,14 @@
         <v>101</v>
       </c>
       <c r="H39" t="n">
+        <v>17</v>
+      </c>
+      <c r="I39" t="n">
         <v>48</v>
       </c>
-      <c r="I39" t="n">
+      <c r="J39" t="n">
         <v>33</v>
       </c>
-      <c r="J39" t="n">
-        <v>17</v>
-      </c>
       <c r="K39" t="n">
         <v>0</v>
       </c>
@@ -3575,7 +3575,7 @@
         <v>0</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -3590,7 +3590,7 @@
         <v>0</v>
       </c>
       <c r="S39" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="T39" t="n">
         <v>0</v>
@@ -3636,14 +3636,14 @@
         <v>101</v>
       </c>
       <c r="H40" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="I40" s="5" t="n">
         <v>48</v>
       </c>
-      <c r="I40" s="5" t="n">
+      <c r="J40" s="5" t="n">
         <v>33</v>
       </c>
-      <c r="J40" s="5" t="n">
-        <v>17</v>
-      </c>
       <c r="K40" s="5" t="n">
         <v>0</v>
       </c>
@@ -3654,7 +3654,7 @@
         <v>0</v>
       </c>
       <c r="N40" s="5" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="O40" s="5" t="n">
         <v>0</v>
@@ -3669,7 +3669,7 @@
         <v>0</v>
       </c>
       <c r="S40" s="5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="T40" s="5" t="n">
         <v>0</v>
@@ -3715,14 +3715,14 @@
         <v>101</v>
       </c>
       <c r="H41" t="n">
+        <v>17</v>
+      </c>
+      <c r="I41" t="n">
         <v>48</v>
       </c>
-      <c r="I41" t="n">
+      <c r="J41" t="n">
         <v>33</v>
       </c>
-      <c r="J41" t="n">
-        <v>17</v>
-      </c>
       <c r="K41" t="n">
         <v>0</v>
       </c>
@@ -3733,7 +3733,7 @@
         <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -3748,7 +3748,7 @@
         <v>0</v>
       </c>
       <c r="S41" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="T41" t="n">
         <v>0</v>
@@ -3794,14 +3794,14 @@
         <v>101</v>
       </c>
       <c r="H42" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="I42" s="5" t="n">
         <v>46</v>
       </c>
-      <c r="I42" s="5" t="n">
+      <c r="J42" s="5" t="n">
         <v>33</v>
       </c>
-      <c r="J42" s="5" t="n">
-        <v>17</v>
-      </c>
       <c r="K42" s="5" t="n">
         <v>0</v>
       </c>
@@ -3812,7 +3812,7 @@
         <v>0</v>
       </c>
       <c r="N42" s="5" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="O42" s="5" t="n">
         <v>0</v>
@@ -3827,7 +3827,7 @@
         <v>0</v>
       </c>
       <c r="S42" s="5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="T42" s="5" t="n">
         <v>0</v>
@@ -3873,14 +3873,14 @@
         <v>101</v>
       </c>
       <c r="H43" t="n">
+        <v>17</v>
+      </c>
+      <c r="I43" t="n">
         <v>48</v>
       </c>
-      <c r="I43" t="n">
+      <c r="J43" t="n">
         <v>33</v>
       </c>
-      <c r="J43" t="n">
-        <v>17</v>
-      </c>
       <c r="K43" t="n">
         <v>0</v>
       </c>
@@ -3891,7 +3891,7 @@
         <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -3906,7 +3906,7 @@
         <v>0</v>
       </c>
       <c r="S43" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="T43" t="n">
         <v>0</v>
@@ -3952,14 +3952,14 @@
         <v>101</v>
       </c>
       <c r="H44" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="I44" s="5" t="n">
         <v>48</v>
       </c>
-      <c r="I44" s="5" t="n">
+      <c r="J44" s="5" t="n">
         <v>33</v>
       </c>
-      <c r="J44" s="5" t="n">
-        <v>17</v>
-      </c>
       <c r="K44" s="5" t="n">
         <v>0</v>
       </c>
@@ -3970,7 +3970,7 @@
         <v>0</v>
       </c>
       <c r="N44" s="5" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="O44" s="5" t="n">
         <v>0</v>
@@ -3985,7 +3985,7 @@
         <v>0</v>
       </c>
       <c r="S44" s="5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="T44" s="5" t="n">
         <v>0</v>
@@ -4031,14 +4031,14 @@
         <v>101</v>
       </c>
       <c r="H45" t="n">
+        <v>17</v>
+      </c>
+      <c r="I45" t="n">
         <v>48</v>
       </c>
-      <c r="I45" t="n">
+      <c r="J45" t="n">
         <v>33</v>
       </c>
-      <c r="J45" t="n">
-        <v>17</v>
-      </c>
       <c r="K45" t="n">
         <v>0</v>
       </c>
@@ -4049,7 +4049,7 @@
         <v>0</v>
       </c>
       <c r="N45" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -4064,7 +4064,7 @@
         <v>0</v>
       </c>
       <c r="S45" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="T45" t="n">
         <v>0</v>
@@ -4110,14 +4110,14 @@
         <v>101</v>
       </c>
       <c r="H46" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="I46" s="5" t="n">
         <v>48</v>
       </c>
-      <c r="I46" s="5" t="n">
+      <c r="J46" s="5" t="n">
         <v>33</v>
       </c>
-      <c r="J46" s="5" t="n">
-        <v>17</v>
-      </c>
       <c r="K46" s="5" t="n">
         <v>0</v>
       </c>
@@ -4128,7 +4128,7 @@
         <v>0</v>
       </c>
       <c r="N46" s="5" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="O46" s="5" t="n">
         <v>0</v>
@@ -4143,7 +4143,7 @@
         <v>0</v>
       </c>
       <c r="S46" s="5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="T46" s="5" t="n">
         <v>0</v>
@@ -4189,14 +4189,14 @@
         <v>101</v>
       </c>
       <c r="H47" t="n">
+        <v>17</v>
+      </c>
+      <c r="I47" t="n">
         <v>48</v>
       </c>
-      <c r="I47" t="n">
+      <c r="J47" t="n">
         <v>33</v>
       </c>
-      <c r="J47" t="n">
-        <v>17</v>
-      </c>
       <c r="K47" t="n">
         <v>0</v>
       </c>
@@ -4207,7 +4207,7 @@
         <v>0</v>
       </c>
       <c r="N47" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -4222,7 +4222,7 @@
         <v>0</v>
       </c>
       <c r="S47" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="T47" t="n">
         <v>0</v>
@@ -4268,14 +4268,14 @@
         <v>101</v>
       </c>
       <c r="H48" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="I48" s="5" t="n">
         <v>48</v>
       </c>
-      <c r="I48" s="5" t="n">
+      <c r="J48" s="5" t="n">
         <v>33</v>
       </c>
-      <c r="J48" s="5" t="n">
-        <v>17</v>
-      </c>
       <c r="K48" s="5" t="n">
         <v>0</v>
       </c>
@@ -4286,7 +4286,7 @@
         <v>0</v>
       </c>
       <c r="N48" s="5" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="O48" s="5" t="n">
         <v>0</v>
@@ -4301,7 +4301,7 @@
         <v>0</v>
       </c>
       <c r="S48" s="5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="T48" s="5" t="n">
         <v>0</v>
@@ -4347,14 +4347,14 @@
         <v>101</v>
       </c>
       <c r="H49" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="I49" t="n">
+        <v>0</v>
+      </c>
+      <c r="J49" t="n">
         <v>33</v>
       </c>
-      <c r="J49" t="n">
-        <v>17</v>
-      </c>
       <c r="K49" t="n">
         <v>0</v>
       </c>
@@ -4365,7 +4365,7 @@
         <v>0</v>
       </c>
       <c r="N49" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -4380,7 +4380,7 @@
         <v>0</v>
       </c>
       <c r="S49" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="T49" t="n">
         <v>0</v>
@@ -4426,14 +4426,14 @@
         <v>101</v>
       </c>
       <c r="H50" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="I50" s="5" t="n">
         <v>48</v>
       </c>
-      <c r="I50" s="5" t="n">
+      <c r="J50" s="5" t="n">
         <v>33</v>
       </c>
-      <c r="J50" s="5" t="n">
-        <v>17</v>
-      </c>
       <c r="K50" s="5" t="n">
         <v>0</v>
       </c>
@@ -4444,7 +4444,7 @@
         <v>0</v>
       </c>
       <c r="N50" s="5" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="O50" s="5" t="n">
         <v>0</v>
@@ -4459,7 +4459,7 @@
         <v>0</v>
       </c>
       <c r="S50" s="5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="T50" s="5" t="n">
         <v>0</v>
@@ -4505,14 +4505,14 @@
         <v>101</v>
       </c>
       <c r="H51" t="n">
+        <v>17</v>
+      </c>
+      <c r="I51" t="n">
         <v>48</v>
       </c>
-      <c r="I51" t="n">
+      <c r="J51" t="n">
         <v>33</v>
       </c>
-      <c r="J51" t="n">
-        <v>17</v>
-      </c>
       <c r="K51" t="n">
         <v>0</v>
       </c>
@@ -4523,7 +4523,7 @@
         <v>0</v>
       </c>
       <c r="N51" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -4538,7 +4538,7 @@
         <v>0</v>
       </c>
       <c r="S51" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="T51" t="n">
         <v>0</v>
@@ -4584,14 +4584,14 @@
         <v>101</v>
       </c>
       <c r="H52" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="I52" s="5" t="n">
         <v>48</v>
       </c>
-      <c r="I52" s="5" t="n">
+      <c r="J52" s="5" t="n">
         <v>30</v>
       </c>
-      <c r="J52" s="5" t="n">
-        <v>17</v>
-      </c>
       <c r="K52" s="5" t="n">
         <v>0</v>
       </c>
@@ -4602,7 +4602,7 @@
         <v>0</v>
       </c>
       <c r="N52" s="5" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="O52" s="5" t="n">
         <v>0</v>
@@ -4617,7 +4617,7 @@
         <v>0</v>
       </c>
       <c r="S52" s="5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="T52" s="5" t="n">
         <v>0</v>
@@ -4663,14 +4663,14 @@
         <v>101</v>
       </c>
       <c r="H53" t="n">
+        <v>17</v>
+      </c>
+      <c r="I53" t="n">
         <v>48</v>
       </c>
-      <c r="I53" t="n">
+      <c r="J53" t="n">
         <v>30</v>
       </c>
-      <c r="J53" t="n">
-        <v>17</v>
-      </c>
       <c r="K53" t="n">
         <v>0</v>
       </c>
@@ -4681,7 +4681,7 @@
         <v>0</v>
       </c>
       <c r="N53" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -4696,7 +4696,7 @@
         <v>0</v>
       </c>
       <c r="S53" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="T53" t="n">
         <v>0</v>
@@ -4742,14 +4742,14 @@
         <v>101</v>
       </c>
       <c r="H54" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="I54" s="5" t="n">
         <v>48</v>
       </c>
-      <c r="I54" s="5" t="n">
+      <c r="J54" s="5" t="n">
         <v>30</v>
       </c>
-      <c r="J54" s="5" t="n">
-        <v>17</v>
-      </c>
       <c r="K54" s="5" t="n">
         <v>0</v>
       </c>
@@ -4760,7 +4760,7 @@
         <v>0</v>
       </c>
       <c r="N54" s="5" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="O54" s="5" t="n">
         <v>0</v>
@@ -4775,7 +4775,7 @@
         <v>0</v>
       </c>
       <c r="S54" s="5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="T54" s="5" t="n">
         <v>0</v>
@@ -4821,14 +4821,14 @@
         <v>101</v>
       </c>
       <c r="H55" t="n">
+        <v>17</v>
+      </c>
+      <c r="I55" t="n">
         <v>2</v>
       </c>
-      <c r="I55" t="n">
+      <c r="J55" t="n">
         <v>30</v>
       </c>
-      <c r="J55" t="n">
-        <v>17</v>
-      </c>
       <c r="K55" t="n">
         <v>0</v>
       </c>
@@ -4839,7 +4839,7 @@
         <v>0</v>
       </c>
       <c r="N55" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
@@ -4854,7 +4854,7 @@
         <v>0</v>
       </c>
       <c r="S55" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="T55" t="n">
         <v>0</v>
@@ -4900,14 +4900,14 @@
         <v>101</v>
       </c>
       <c r="H56" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="I56" s="5" t="n">
         <v>48</v>
       </c>
-      <c r="I56" s="5" t="n">
+      <c r="J56" s="5" t="n">
         <v>30</v>
       </c>
-      <c r="J56" s="5" t="n">
-        <v>17</v>
-      </c>
       <c r="K56" s="5" t="n">
         <v>0</v>
       </c>
@@ -4918,7 +4918,7 @@
         <v>0</v>
       </c>
       <c r="N56" s="5" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="O56" s="5" t="n">
         <v>0</v>
@@ -4933,7 +4933,7 @@
         <v>0</v>
       </c>
       <c r="S56" s="5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="T56" s="5" t="n">
         <v>0</v>
@@ -4979,14 +4979,14 @@
         <v>101</v>
       </c>
       <c r="H57" t="n">
+        <v>22</v>
+      </c>
+      <c r="I57" t="n">
         <v>48</v>
       </c>
-      <c r="I57" t="n">
+      <c r="J57" t="n">
         <v>24</v>
       </c>
-      <c r="J57" t="n">
-        <v>22</v>
-      </c>
       <c r="K57" t="n">
         <v>0</v>
       </c>
@@ -4997,7 +4997,7 @@
         <v>0</v>
       </c>
       <c r="N57" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -5012,7 +5012,7 @@
         <v>0</v>
       </c>
       <c r="S57" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="T57" t="n">
         <v>0</v>
@@ -5058,14 +5058,14 @@
         <v>101</v>
       </c>
       <c r="H58" s="5" t="n">
+        <v>22</v>
+      </c>
+      <c r="I58" s="5" t="n">
         <v>47</v>
       </c>
-      <c r="I58" s="5" t="n">
+      <c r="J58" s="5" t="n">
         <v>26</v>
       </c>
-      <c r="J58" s="5" t="n">
-        <v>22</v>
-      </c>
       <c r="K58" s="5" t="n">
         <v>0</v>
       </c>
@@ -5076,7 +5076,7 @@
         <v>0</v>
       </c>
       <c r="N58" s="5" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="O58" s="5" t="n">
         <v>0</v>
@@ -5091,7 +5091,7 @@
         <v>0</v>
       </c>
       <c r="S58" s="5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="T58" s="5" t="n">
         <v>0</v>
@@ -5137,14 +5137,14 @@
         <v>101</v>
       </c>
       <c r="H59" t="n">
+        <v>16</v>
+      </c>
+      <c r="I59" t="n">
         <v>47</v>
       </c>
-      <c r="I59" t="n">
+      <c r="J59" t="n">
         <v>26</v>
       </c>
-      <c r="J59" t="n">
-        <v>16</v>
-      </c>
       <c r="K59" t="n">
         <v>0</v>
       </c>
@@ -5155,7 +5155,7 @@
         <v>0</v>
       </c>
       <c r="N59" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -5170,7 +5170,7 @@
         <v>0</v>
       </c>
       <c r="S59" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="T59" t="n">
         <v>0</v>
@@ -5216,14 +5216,14 @@
         <v>101</v>
       </c>
       <c r="H60" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="I60" s="5" t="n">
         <v>46</v>
       </c>
-      <c r="I60" s="5" t="n">
+      <c r="J60" s="5" t="n">
         <v>23</v>
       </c>
-      <c r="J60" s="5" t="n">
-        <v>16</v>
-      </c>
       <c r="K60" s="5" t="n">
         <v>0</v>
       </c>
@@ -5234,7 +5234,7 @@
         <v>0</v>
       </c>
       <c r="N60" s="5" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="O60" s="5" t="n">
         <v>0</v>
@@ -5249,7 +5249,7 @@
         <v>0</v>
       </c>
       <c r="S60" s="5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="T60" s="5" t="n">
         <v>0</v>
@@ -5295,14 +5295,14 @@
         <v>101</v>
       </c>
       <c r="H61" t="n">
+        <v>16</v>
+      </c>
+      <c r="I61" t="n">
         <v>43</v>
       </c>
-      <c r="I61" t="n">
+      <c r="J61" t="n">
         <v>29</v>
       </c>
-      <c r="J61" t="n">
-        <v>16</v>
-      </c>
       <c r="K61" t="n">
         <v>0</v>
       </c>
@@ -5313,7 +5313,7 @@
         <v>0</v>
       </c>
       <c r="N61" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -5328,7 +5328,7 @@
         <v>0</v>
       </c>
       <c r="S61" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="T61" t="n">
         <v>0</v>
@@ -5374,14 +5374,14 @@
         <v>101</v>
       </c>
       <c r="H62" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="I62" s="5" t="n">
         <v>43</v>
       </c>
-      <c r="I62" s="5" t="n">
+      <c r="J62" s="5" t="n">
         <v>29</v>
       </c>
-      <c r="J62" s="5" t="n">
-        <v>16</v>
-      </c>
       <c r="K62" s="5" t="n">
         <v>0</v>
       </c>
@@ -5392,7 +5392,7 @@
         <v>0</v>
       </c>
       <c r="N62" s="5" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="O62" s="5" t="n">
         <v>0</v>
@@ -5407,7 +5407,7 @@
         <v>0</v>
       </c>
       <c r="S62" s="5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="T62" s="5" t="n">
         <v>0</v>
@@ -5453,14 +5453,14 @@
         <v>101</v>
       </c>
       <c r="H63" t="n">
+        <v>16</v>
+      </c>
+      <c r="I63" t="n">
         <v>43</v>
       </c>
-      <c r="I63" t="n">
+      <c r="J63" t="n">
         <v>29</v>
       </c>
-      <c r="J63" t="n">
-        <v>16</v>
-      </c>
       <c r="K63" t="n">
         <v>0</v>
       </c>
@@ -5471,7 +5471,7 @@
         <v>0</v>
       </c>
       <c r="N63" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -5486,7 +5486,7 @@
         <v>0</v>
       </c>
       <c r="S63" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="T63" t="n">
         <v>0</v>
@@ -5532,14 +5532,14 @@
         <v>101</v>
       </c>
       <c r="H64" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="I64" s="5" t="n">
         <v>42</v>
       </c>
-      <c r="I64" s="5" t="n">
+      <c r="J64" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="J64" s="5" t="n">
-        <v>16</v>
-      </c>
       <c r="K64" s="5" t="n">
         <v>0</v>
       </c>
@@ -5550,7 +5550,7 @@
         <v>0</v>
       </c>
       <c r="N64" s="5" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="O64" s="5" t="n">
         <v>0</v>
@@ -5565,7 +5565,7 @@
         <v>0</v>
       </c>
       <c r="S64" s="5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="T64" s="5" t="n">
         <v>0</v>
@@ -5611,14 +5611,14 @@
         <v>101</v>
       </c>
       <c r="H65" t="n">
+        <v>21</v>
+      </c>
+      <c r="I65" t="n">
         <v>46</v>
       </c>
-      <c r="I65" t="n">
+      <c r="J65" t="n">
         <v>20</v>
       </c>
-      <c r="J65" t="n">
-        <v>21</v>
-      </c>
       <c r="K65" t="n">
         <v>0</v>
       </c>
@@ -5629,7 +5629,7 @@
         <v>0</v>
       </c>
       <c r="N65" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -5644,7 +5644,7 @@
         <v>0</v>
       </c>
       <c r="S65" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="T65" t="n">
         <v>0</v>
@@ -5690,14 +5690,14 @@
         <v>100</v>
       </c>
       <c r="H66" s="5" t="n">
+        <v>21</v>
+      </c>
+      <c r="I66" s="5" t="n">
         <v>42</v>
       </c>
-      <c r="I66" s="5" t="n">
+      <c r="J66" s="5" t="n">
         <v>26</v>
       </c>
-      <c r="J66" s="5" t="n">
-        <v>21</v>
-      </c>
       <c r="K66" s="5" t="n">
         <v>0</v>
       </c>
@@ -5708,7 +5708,7 @@
         <v>0</v>
       </c>
       <c r="N66" s="5" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="O66" s="5" t="n">
         <v>0</v>
@@ -5723,7 +5723,7 @@
         <v>0</v>
       </c>
       <c r="S66" s="5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="T66" s="5" t="n">
         <v>0</v>
@@ -5769,14 +5769,14 @@
         <v>100</v>
       </c>
       <c r="H67" t="n">
+        <v>21</v>
+      </c>
+      <c r="I67" t="n">
         <v>53</v>
       </c>
-      <c r="I67" t="n">
+      <c r="J67" t="n">
         <v>26</v>
       </c>
-      <c r="J67" t="n">
-        <v>21</v>
-      </c>
       <c r="K67" t="n">
         <v>0</v>
       </c>
@@ -5786,9 +5786,6 @@
       <c r="M67" t="n">
         <v>0</v>
       </c>
-      <c r="N67" t="n">
-        <v>0</v>
-      </c>
       <c r="O67" t="n">
         <v>0</v>
       </c>
@@ -5799,6 +5796,9 @@
         <v>0</v>
       </c>
       <c r="R67" t="n">
+        <v>0</v>
+      </c>
+      <c r="S67" t="n">
         <v>0</v>
       </c>
       <c r="T67" t="n">
@@ -5845,14 +5845,14 @@
         <v>100</v>
       </c>
       <c r="H68" s="5" t="n">
+        <v>21</v>
+      </c>
+      <c r="I68" s="5" t="n">
         <v>53</v>
       </c>
-      <c r="I68" s="5" t="n">
+      <c r="J68" s="5" t="n">
         <v>26</v>
       </c>
-      <c r="J68" s="5" t="n">
-        <v>21</v>
-      </c>
       <c r="K68" s="5" t="n">
         <v>0</v>
       </c>
@@ -5863,7 +5863,7 @@
         <v>0</v>
       </c>
       <c r="N68" s="5" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="O68" s="5" t="n">
         <v>0</v>
@@ -5878,7 +5878,7 @@
         <v>0</v>
       </c>
       <c r="S68" s="5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="T68" s="5" t="n">
         <v>0</v>
@@ -5921,14 +5921,14 @@
         <v>100</v>
       </c>
       <c r="H69" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="I69" t="n">
+        <v>0</v>
+      </c>
+      <c r="J69" t="n">
         <v>26</v>
       </c>
-      <c r="J69" t="n">
-        <v>21</v>
-      </c>
       <c r="K69" t="n">
         <v>0</v>
       </c>
@@ -5938,9 +5938,6 @@
       <c r="M69" t="n">
         <v>0</v>
       </c>
-      <c r="N69" t="n">
-        <v>0</v>
-      </c>
       <c r="O69" t="n">
         <v>0</v>
       </c>
@@ -5951,6 +5948,9 @@
         <v>0</v>
       </c>
       <c r="R69" t="n">
+        <v>0</v>
+      </c>
+      <c r="S69" t="n">
         <v>0</v>
       </c>
       <c r="T69" t="n">
@@ -5997,14 +5997,14 @@
         <v>100</v>
       </c>
       <c r="H70" s="5" t="n">
+        <v>21</v>
+      </c>
+      <c r="I70" s="5" t="n">
         <v>53</v>
       </c>
-      <c r="I70" s="5" t="n">
+      <c r="J70" s="5" t="n">
         <v>26</v>
       </c>
-      <c r="J70" s="5" t="n">
-        <v>21</v>
-      </c>
       <c r="K70" s="5" t="n">
         <v>0</v>
       </c>
@@ -6015,7 +6015,7 @@
         <v>0</v>
       </c>
       <c r="N70" s="5" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="O70" s="5" t="n">
         <v>0</v>
@@ -6030,7 +6030,7 @@
         <v>0</v>
       </c>
       <c r="S70" s="5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="T70" s="5" t="n">
         <v>0</v>
@@ -6076,14 +6076,14 @@
         <v>100</v>
       </c>
       <c r="H71" t="n">
+        <v>21</v>
+      </c>
+      <c r="I71" t="n">
         <v>42</v>
       </c>
-      <c r="I71" t="n">
+      <c r="J71" t="n">
         <v>26</v>
       </c>
-      <c r="J71" t="n">
-        <v>21</v>
-      </c>
       <c r="K71" t="n">
         <v>0</v>
       </c>
@@ -6094,7 +6094,7 @@
         <v>0</v>
       </c>
       <c r="N71" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -6109,7 +6109,7 @@
         <v>0</v>
       </c>
       <c r="S71" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="T71" t="n">
         <v>0</v>
@@ -6155,14 +6155,14 @@
         <v>100</v>
       </c>
       <c r="H72" s="5" t="n">
+        <v>21</v>
+      </c>
+      <c r="I72" s="5" t="n">
         <v>42</v>
       </c>
-      <c r="I72" s="5" t="n">
+      <c r="J72" s="5" t="n">
         <v>26</v>
       </c>
-      <c r="J72" s="5" t="n">
-        <v>21</v>
-      </c>
       <c r="K72" s="5" t="n">
         <v>0</v>
       </c>
@@ -6173,7 +6173,7 @@
         <v>0</v>
       </c>
       <c r="N72" s="5" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="O72" s="5" t="n">
         <v>0</v>
@@ -6188,7 +6188,7 @@
         <v>0</v>
       </c>
       <c r="S72" s="5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="T72" s="5" t="n">
         <v>0</v>
@@ -6234,14 +6234,14 @@
         <v>100</v>
       </c>
       <c r="H73" t="n">
+        <v>19</v>
+      </c>
+      <c r="I73" t="n">
         <v>42</v>
       </c>
-      <c r="I73" t="n">
+      <c r="J73" t="n">
         <v>26</v>
       </c>
-      <c r="J73" t="n">
-        <v>19</v>
-      </c>
       <c r="K73" t="n">
         <v>0</v>
       </c>
@@ -6252,7 +6252,7 @@
         <v>0</v>
       </c>
       <c r="N73" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -6267,7 +6267,7 @@
         <v>0</v>
       </c>
       <c r="S73" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="T73" t="n">
         <v>0</v>
@@ -6313,14 +6313,14 @@
         <v>100</v>
       </c>
       <c r="H74" s="5" t="n">
+        <v>23</v>
+      </c>
+      <c r="I74" s="5" t="n">
         <v>42</v>
       </c>
-      <c r="I74" s="5" t="n">
+      <c r="J74" s="5" t="n">
         <v>26</v>
       </c>
-      <c r="J74" s="5" t="n">
-        <v>23</v>
-      </c>
       <c r="K74" s="5" t="n">
         <v>0</v>
       </c>
@@ -6331,7 +6331,7 @@
         <v>0</v>
       </c>
       <c r="N74" s="5" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="O74" s="5" t="n">
         <v>0</v>
@@ -6346,7 +6346,7 @@
         <v>0</v>
       </c>
       <c r="S74" s="5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="T74" s="5" t="n">
         <v>0</v>
@@ -6392,14 +6392,14 @@
         <v>100</v>
       </c>
       <c r="H75" t="n">
+        <v>23</v>
+      </c>
+      <c r="I75" t="n">
         <v>42</v>
       </c>
-      <c r="I75" t="n">
+      <c r="J75" t="n">
         <v>26</v>
       </c>
-      <c r="J75" t="n">
-        <v>23</v>
-      </c>
       <c r="K75" t="n">
         <v>0</v>
       </c>
@@ -6410,7 +6410,7 @@
         <v>0</v>
       </c>
       <c r="N75" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -6425,7 +6425,7 @@
         <v>0</v>
       </c>
       <c r="S75" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="T75" t="n">
         <v>0</v>
@@ -6471,14 +6471,14 @@
         <v>100</v>
       </c>
       <c r="H76" s="5" t="n">
+        <v>23</v>
+      </c>
+      <c r="I76" s="5" t="n">
         <v>42</v>
       </c>
-      <c r="I76" s="5" t="n">
+      <c r="J76" s="5" t="n">
         <v>26</v>
       </c>
-      <c r="J76" s="5" t="n">
-        <v>23</v>
-      </c>
       <c r="K76" s="5" t="n">
         <v>0</v>
       </c>
@@ -6488,7 +6488,9 @@
       <c r="M76" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="N76" s="5" t="n"/>
+      <c r="N76" s="5" t="n">
+        <v>24</v>
+      </c>
       <c r="O76" s="5" t="n">
         <v>0</v>
       </c>
@@ -6498,11 +6500,9 @@
       <c r="Q76" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="R76" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="R76" s="5" t="n"/>
       <c r="S76" s="5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="T76" s="5" t="n">
         <v>0</v>
@@ -6546,14 +6546,14 @@
         <v>100</v>
       </c>
       <c r="H77" t="n">
+        <v>23</v>
+      </c>
+      <c r="I77" t="n">
         <v>42</v>
       </c>
-      <c r="I77" t="n">
+      <c r="J77" t="n">
         <v>26</v>
       </c>
-      <c r="J77" t="n">
-        <v>23</v>
-      </c>
       <c r="K77" t="n">
         <v>0</v>
       </c>
@@ -6563,9 +6563,6 @@
       <c r="M77" t="n">
         <v>0</v>
       </c>
-      <c r="N77" t="n">
-        <v>0</v>
-      </c>
       <c r="O77" t="n">
         <v>0</v>
       </c>
@@ -6576,6 +6573,9 @@
         <v>0</v>
       </c>
       <c r="R77" t="n">
+        <v>0</v>
+      </c>
+      <c r="S77" t="n">
         <v>0</v>
       </c>
       <c r="T77" t="n">
@@ -6622,14 +6622,14 @@
         <v>100</v>
       </c>
       <c r="H78" s="5" t="n">
+        <v>23</v>
+      </c>
+      <c r="I78" s="5" t="n">
         <v>42</v>
       </c>
-      <c r="I78" s="5" t="n">
+      <c r="J78" s="5" t="n">
         <v>26</v>
       </c>
-      <c r="J78" s="5" t="n">
-        <v>23</v>
-      </c>
       <c r="K78" s="5" t="n">
         <v>0</v>
       </c>
@@ -6640,7 +6640,7 @@
         <v>0</v>
       </c>
       <c r="N78" s="5" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="O78" s="5" t="n">
         <v>0</v>
@@ -6655,7 +6655,7 @@
         <v>0</v>
       </c>
       <c r="S78" s="5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="T78" s="5" t="n">
         <v>0</v>
@@ -6701,14 +6701,14 @@
         <v>100</v>
       </c>
       <c r="H79" t="n">
+        <v>23</v>
+      </c>
+      <c r="I79" t="n">
         <v>42</v>
       </c>
-      <c r="I79" t="n">
+      <c r="J79" t="n">
         <v>26</v>
       </c>
-      <c r="J79" t="n">
-        <v>23</v>
-      </c>
       <c r="K79" t="n">
         <v>0</v>
       </c>
@@ -6718,9 +6718,6 @@
       <c r="M79" t="n">
         <v>0</v>
       </c>
-      <c r="N79" t="n">
-        <v>0</v>
-      </c>
       <c r="O79" t="n">
         <v>0</v>
       </c>
@@ -6731,6 +6728,9 @@
         <v>0</v>
       </c>
       <c r="R79" t="n">
+        <v>0</v>
+      </c>
+      <c r="S79" t="n">
         <v>0</v>
       </c>
       <c r="T79" t="n">
@@ -6777,14 +6777,14 @@
         <v>90</v>
       </c>
       <c r="H80" s="5" t="n">
+        <v>23</v>
+      </c>
+      <c r="I80" s="5" t="n">
         <v>42</v>
       </c>
-      <c r="I80" s="5" t="n">
+      <c r="J80" s="5" t="n">
         <v>26</v>
       </c>
-      <c r="J80" s="5" t="n">
-        <v>23</v>
-      </c>
       <c r="K80" s="5" t="n">
         <v>0</v>
       </c>
@@ -6794,9 +6794,7 @@
       <c r="M80" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="N80" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="N80" s="5" t="n"/>
       <c r="O80" s="5" t="n">
         <v>0</v>
       </c>
@@ -6809,7 +6807,9 @@
       <c r="R80" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="S80" s="5" t="n"/>
+      <c r="S80" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="T80" s="5" t="n">
         <v>0</v>
       </c>
@@ -6854,14 +6854,14 @@
         <v>90</v>
       </c>
       <c r="H81" t="n">
+        <v>23</v>
+      </c>
+      <c r="I81" t="n">
         <v>42</v>
       </c>
-      <c r="I81" t="n">
+      <c r="J81" t="n">
         <v>26</v>
       </c>
-      <c r="J81" t="n">
-        <v>23</v>
-      </c>
       <c r="K81" t="n">
         <v>0</v>
       </c>
@@ -6872,7 +6872,7 @@
         <v>0</v>
       </c>
       <c r="N81" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="O81" t="n">
         <v>0</v>
@@ -6887,7 +6887,7 @@
         <v>0</v>
       </c>
       <c r="S81" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="T81" t="n">
         <v>0</v>
@@ -6933,14 +6933,14 @@
         <v>96</v>
       </c>
       <c r="H82" s="5" t="n">
+        <v>23</v>
+      </c>
+      <c r="I82" s="5" t="n">
         <v>42</v>
       </c>
-      <c r="I82" s="5" t="n">
+      <c r="J82" s="5" t="n">
         <v>26</v>
       </c>
-      <c r="J82" s="5" t="n">
-        <v>23</v>
-      </c>
       <c r="K82" s="5" t="n">
         <v>0</v>
       </c>
@@ -6950,9 +6950,7 @@
       <c r="M82" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="N82" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="N82" s="5" t="n"/>
       <c r="O82" s="5" t="n">
         <v>0</v>
       </c>
@@ -6965,7 +6963,9 @@
       <c r="R82" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="S82" s="5" t="n"/>
+      <c r="S82" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="T82" s="5" t="n">
         <v>0</v>
       </c>
@@ -7007,14 +7007,14 @@
         <v>96</v>
       </c>
       <c r="H83" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="I83" t="n">
+        <v>0</v>
+      </c>
+      <c r="J83" t="n">
         <v>26</v>
       </c>
-      <c r="J83" t="n">
-        <v>23</v>
-      </c>
       <c r="K83" t="n">
         <v>0</v>
       </c>
@@ -7025,7 +7025,7 @@
         <v>0</v>
       </c>
       <c r="N83" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="O83" t="n">
         <v>0</v>
@@ -7040,7 +7040,7 @@
         <v>0</v>
       </c>
       <c r="S83" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="T83" t="n">
         <v>0</v>
@@ -7086,14 +7086,14 @@
         <v>96</v>
       </c>
       <c r="H84" s="5" t="n">
+        <v>23</v>
+      </c>
+      <c r="I84" s="5" t="n">
         <v>42</v>
       </c>
-      <c r="I84" s="5" t="n">
+      <c r="J84" s="5" t="n">
         <v>26</v>
       </c>
-      <c r="J84" s="5" t="n">
-        <v>23</v>
-      </c>
       <c r="K84" s="5" t="n">
         <v>0</v>
       </c>
@@ -7104,7 +7104,7 @@
         <v>0</v>
       </c>
       <c r="N84" s="5" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="O84" s="5" t="n">
         <v>0</v>
@@ -7119,7 +7119,7 @@
         <v>0</v>
       </c>
       <c r="S84" s="5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="T84" s="5" t="n">
         <v>0</v>
@@ -7165,14 +7165,14 @@
         <v>94</v>
       </c>
       <c r="H85" t="n">
+        <v>23</v>
+      </c>
+      <c r="I85" t="n">
         <v>42</v>
       </c>
-      <c r="I85" t="n">
+      <c r="J85" t="n">
         <v>15</v>
       </c>
-      <c r="J85" t="n">
-        <v>23</v>
-      </c>
       <c r="K85" t="n">
         <v>0</v>
       </c>
@@ -7182,9 +7182,6 @@
       <c r="M85" t="n">
         <v>0</v>
       </c>
-      <c r="N85" t="n">
-        <v>0</v>
-      </c>
       <c r="O85" t="n">
         <v>0</v>
       </c>
@@ -7195,6 +7192,9 @@
         <v>0</v>
       </c>
       <c r="R85" t="n">
+        <v>0</v>
+      </c>
+      <c r="S85" t="n">
         <v>0</v>
       </c>
       <c r="T85" t="n">
@@ -7241,14 +7241,14 @@
         <v>94</v>
       </c>
       <c r="H86" s="5" t="n">
+        <v>23</v>
+      </c>
+      <c r="I86" s="5" t="n">
         <v>42</v>
       </c>
-      <c r="I86" s="5" t="n">
+      <c r="J86" s="5" t="n">
         <v>12</v>
       </c>
-      <c r="J86" s="5" t="n">
-        <v>23</v>
-      </c>
       <c r="K86" s="5" t="n">
         <v>0</v>
       </c>
@@ -7258,9 +7258,7 @@
       <c r="M86" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="N86" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="N86" s="5" t="n"/>
       <c r="O86" s="5" t="n">
         <v>0</v>
       </c>
@@ -7273,7 +7271,9 @@
       <c r="R86" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="S86" s="5" t="n"/>
+      <c r="S86" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="T86" s="5" t="n">
         <v>0</v>
       </c>
@@ -7318,14 +7318,14 @@
         <v>94</v>
       </c>
       <c r="H87" t="n">
+        <v>23</v>
+      </c>
+      <c r="I87" t="n">
         <v>42</v>
       </c>
-      <c r="I87" t="n">
+      <c r="J87" t="n">
         <v>12</v>
       </c>
-      <c r="J87" t="n">
-        <v>23</v>
-      </c>
       <c r="K87" t="n">
         <v>0</v>
       </c>
@@ -7335,9 +7335,6 @@
       <c r="M87" t="n">
         <v>0</v>
       </c>
-      <c r="N87" t="n">
-        <v>0</v>
-      </c>
       <c r="O87" t="n">
         <v>0</v>
       </c>
@@ -7348,6 +7345,9 @@
         <v>0</v>
       </c>
       <c r="R87" t="n">
+        <v>0</v>
+      </c>
+      <c r="S87" t="n">
         <v>0</v>
       </c>
       <c r="T87" t="n">
@@ -7394,14 +7394,14 @@
         <v>93</v>
       </c>
       <c r="H88" s="5" t="n">
+        <v>23</v>
+      </c>
+      <c r="I88" s="5" t="n">
         <v>42</v>
       </c>
-      <c r="I88" s="5" t="n">
+      <c r="J88" s="5" t="n">
         <v>14</v>
       </c>
-      <c r="J88" s="5" t="n">
-        <v>23</v>
-      </c>
       <c r="K88" s="5" t="n">
         <v>0</v>
       </c>
@@ -7411,9 +7411,7 @@
       <c r="M88" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="N88" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="N88" s="5" t="n"/>
       <c r="O88" s="5" t="n">
         <v>0</v>
       </c>
@@ -7426,7 +7424,9 @@
       <c r="R88" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="S88" s="5" t="n"/>
+      <c r="S88" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="T88" s="5" t="n">
         <v>0</v>
       </c>
@@ -7471,14 +7471,14 @@
         <v>93</v>
       </c>
       <c r="H89" t="n">
+        <v>18</v>
+      </c>
+      <c r="I89" t="n">
         <v>42</v>
       </c>
-      <c r="I89" t="n">
+      <c r="J89" t="n">
         <v>19</v>
       </c>
-      <c r="J89" t="n">
-        <v>18</v>
-      </c>
       <c r="K89" t="n">
         <v>0</v>
       </c>
@@ -7488,9 +7488,6 @@
       <c r="M89" t="n">
         <v>0</v>
       </c>
-      <c r="N89" t="n">
-        <v>0</v>
-      </c>
       <c r="O89" t="n">
         <v>0</v>
       </c>
@@ -7501,6 +7498,9 @@
         <v>0</v>
       </c>
       <c r="R89" t="n">
+        <v>0</v>
+      </c>
+      <c r="S89" t="n">
         <v>0</v>
       </c>
       <c r="T89" t="n">
@@ -7547,12 +7547,12 @@
         <v>93</v>
       </c>
       <c r="H90" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I90" s="5" t="n"/>
-      <c r="J90" s="5" t="n">
         <v>18</v>
       </c>
+      <c r="I90" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J90" s="5" t="n"/>
       <c r="K90" s="5" t="n">
         <v>0</v>
       </c>
@@ -7563,7 +7563,7 @@
         <v>0</v>
       </c>
       <c r="N90" s="5" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="O90" s="5" t="n">
         <v>0</v>
@@ -7578,7 +7578,7 @@
         <v>0</v>
       </c>
       <c r="S90" s="5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="T90" s="5" t="n">
         <v>0</v>
@@ -7624,14 +7624,14 @@
         <v>93</v>
       </c>
       <c r="H91" t="n">
+        <v>18</v>
+      </c>
+      <c r="I91" t="n">
         <v>42</v>
       </c>
-      <c r="I91" t="n">
+      <c r="J91" t="n">
         <v>19</v>
       </c>
-      <c r="J91" t="n">
-        <v>18</v>
-      </c>
       <c r="K91" t="n">
         <v>0</v>
       </c>
@@ -7641,9 +7641,6 @@
       <c r="M91" t="n">
         <v>0</v>
       </c>
-      <c r="N91" t="n">
-        <v>0</v>
-      </c>
       <c r="O91" t="n">
         <v>0</v>
       </c>
@@ -7654,6 +7651,9 @@
         <v>0</v>
       </c>
       <c r="R91" t="n">
+        <v>0</v>
+      </c>
+      <c r="S91" t="n">
         <v>0</v>
       </c>
       <c r="T91" t="n">
@@ -7700,14 +7700,14 @@
         <v>93</v>
       </c>
       <c r="H92" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="I92" s="5" t="n">
         <v>42</v>
       </c>
-      <c r="I92" s="5" t="n">
+      <c r="J92" s="5" t="n">
         <v>19</v>
       </c>
-      <c r="J92" s="5" t="n">
-        <v>18</v>
-      </c>
       <c r="K92" s="5" t="n">
         <v>0</v>
       </c>
@@ -7717,9 +7717,7 @@
       <c r="M92" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="N92" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="N92" s="5" t="n"/>
       <c r="O92" s="5" t="n">
         <v>0</v>
       </c>
@@ -7732,7 +7730,9 @@
       <c r="R92" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="S92" s="5" t="n"/>
+      <c r="S92" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="T92" s="5" t="n">
         <v>0</v>
       </c>
@@ -7777,14 +7777,14 @@
         <v>101</v>
       </c>
       <c r="H93" t="n">
+        <v>18</v>
+      </c>
+      <c r="I93" t="n">
         <v>42</v>
       </c>
-      <c r="I93" t="n">
+      <c r="J93" t="n">
         <v>23</v>
       </c>
-      <c r="J93" t="n">
-        <v>18</v>
-      </c>
       <c r="K93" t="n">
         <v>0</v>
       </c>
@@ -7794,9 +7794,6 @@
       <c r="M93" t="n">
         <v>0</v>
       </c>
-      <c r="N93" t="n">
-        <v>0</v>
-      </c>
       <c r="O93" t="n">
         <v>0</v>
       </c>
@@ -7807,6 +7804,9 @@
         <v>0</v>
       </c>
       <c r="R93" t="n">
+        <v>0</v>
+      </c>
+      <c r="S93" t="n">
         <v>0</v>
       </c>
       <c r="T93" t="n">
@@ -7853,14 +7853,14 @@
         <v>101</v>
       </c>
       <c r="H94" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="I94" s="5" t="n">
         <v>42</v>
       </c>
-      <c r="I94" s="5" t="n">
+      <c r="J94" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="J94" s="5" t="n">
-        <v>18</v>
-      </c>
       <c r="K94" s="5" t="n">
         <v>0</v>
       </c>
@@ -7870,9 +7870,7 @@
       <c r="M94" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="N94" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="N94" s="5" t="n"/>
       <c r="O94" s="5" t="n">
         <v>0</v>
       </c>
@@ -7885,7 +7883,9 @@
       <c r="R94" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="S94" s="5" t="n"/>
+      <c r="S94" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="T94" s="5" t="n">
         <v>0</v>
       </c>
@@ -7930,14 +7930,14 @@
         <v>101</v>
       </c>
       <c r="H95" t="n">
+        <v>18</v>
+      </c>
+      <c r="I95" t="n">
         <v>42</v>
       </c>
-      <c r="I95" t="n">
+      <c r="J95" t="n">
         <v>40</v>
       </c>
-      <c r="J95" t="n">
-        <v>18</v>
-      </c>
       <c r="K95" t="n">
         <v>0</v>
       </c>
@@ -7947,9 +7947,6 @@
       <c r="M95" t="n">
         <v>0</v>
       </c>
-      <c r="N95" t="n">
-        <v>0</v>
-      </c>
       <c r="O95" t="n">
         <v>0</v>
       </c>
@@ -7962,6 +7959,9 @@
       <c r="R95" t="n">
         <v>0</v>
       </c>
+      <c r="S95" t="n">
+        <v>0</v>
+      </c>
       <c r="T95" t="n">
         <v>0</v>
       </c>
@@ -7978,6 +7978,83 @@
         <v>0</v>
       </c>
       <c r="Y95" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B96" s="5" t="n">
+        <v>885</v>
+      </c>
+      <c r="C96" s="5" t="n">
+        <v>518</v>
+      </c>
+      <c r="D96" s="5" t="n">
+        <v>387</v>
+      </c>
+      <c r="E96" s="5" t="n">
+        <v>303</v>
+      </c>
+      <c r="F96" s="5" t="n">
+        <v>226</v>
+      </c>
+      <c r="G96" s="5" t="n">
+        <v>101</v>
+      </c>
+      <c r="H96" s="5" t="n">
+        <v>62</v>
+      </c>
+      <c r="I96" s="5" t="n">
+        <v>42</v>
+      </c>
+      <c r="J96" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="K96" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L96" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M96" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N96" s="5" t="n"/>
+      <c r="O96" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P96" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q96" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R96" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S96" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T96" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U96" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V96" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W96" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X96" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y96" s="5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8019,7 +8096,7 @@
       </c>
       <c r="D1" s="3" t="inlineStr">
         <is>
-          <t>Lager (2026-10-09)</t>
+          <t>Lager (2026-10-10)</t>
         </is>
       </c>
     </row>
@@ -8040,7 +8117,7 @@
         </is>
       </c>
       <c r="D2" s="4" t="n">
-        <v>522</v>
+        <v>518</v>
       </c>
     </row>
     <row r="3">
@@ -16200,7 +16277,7 @@
         </is>
       </c>
       <c r="D410" s="4" t="n">
-        <v>32</v>
+        <v>12</v>
       </c>
     </row>
     <row r="411">
@@ -16660,7 +16737,7 @@
         </is>
       </c>
       <c r="D433" s="6" t="n">
-        <v>175</v>
+        <v>186</v>
       </c>
     </row>
     <row r="434">
@@ -18360,7 +18437,7 @@
         </is>
       </c>
       <c r="D518" s="4" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
     </row>
     <row r="519">
@@ -25620,7 +25697,7 @@
         </is>
       </c>
       <c r="D881" s="6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="882">
@@ -25740,7 +25817,7 @@
         </is>
       </c>
       <c r="D887" s="6" t="n">
-        <v>241</v>
+        <v>239</v>
       </c>
     </row>
     <row r="888">
@@ -26180,7 +26257,7 @@
         </is>
       </c>
       <c r="D909" s="6" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="910">
@@ -30740,7 +30817,7 @@
         </is>
       </c>
       <c r="D1137" s="6" t="n">
-        <v>472</v>
+        <v>475</v>
       </c>
     </row>
     <row r="1138">

--- a/data/ahlsell_led_panel_inventory.xlsx
+++ b/data/ahlsell_led_panel_inventory.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y98"/>
+  <dimension ref="A1:Y99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -538,77 +538,77 @@
       </c>
       <c r="K1" s="3" t="inlineStr">
         <is>
+          <t>Legrand</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="inlineStr">
+        <is>
+          <t>THORN</t>
+        </is>
+      </c>
+      <c r="M1" s="3" t="inlineStr">
+        <is>
+          <t>Black Box</t>
+        </is>
+      </c>
+      <c r="N1" s="3" t="inlineStr">
+        <is>
+          <t>Esylux</t>
+        </is>
+      </c>
+      <c r="O1" s="3" t="inlineStr">
+        <is>
+          <t>Philips</t>
+        </is>
+      </c>
+      <c r="P1" s="3" t="inlineStr">
+        <is>
+          <t>ZG Lighting</t>
+        </is>
+      </c>
+      <c r="Q1" s="3" t="inlineStr">
+        <is>
+          <t>Norwesco</t>
+        </is>
+      </c>
+      <c r="R1" s="3" t="inlineStr">
+        <is>
+          <t>ANETA LIGHTING</t>
+        </is>
+      </c>
+      <c r="S1" s="3" t="inlineStr">
+        <is>
+          <t>Ensto</t>
+        </is>
+      </c>
+      <c r="T1" s="3" t="inlineStr">
+        <is>
+          <t>Bergdahls</t>
+        </is>
+      </c>
+      <c r="U1" s="3" t="inlineStr">
+        <is>
+          <t>Siteco</t>
+        </is>
+      </c>
+      <c r="V1" s="3" t="inlineStr">
+        <is>
           <t>Easyform</t>
         </is>
       </c>
-      <c r="L1" s="3" t="inlineStr">
-        <is>
-          <t>Legrand</t>
-        </is>
-      </c>
-      <c r="M1" s="3" t="inlineStr">
-        <is>
-          <t>Ensto</t>
-        </is>
-      </c>
-      <c r="N1" s="3" t="inlineStr">
-        <is>
-          <t>Black Box</t>
-        </is>
-      </c>
-      <c r="O1" s="3" t="inlineStr">
-        <is>
-          <t>ANETA LIGHTING</t>
-        </is>
-      </c>
-      <c r="P1" s="3" t="inlineStr">
-        <is>
-          <t>Philips</t>
-        </is>
-      </c>
-      <c r="Q1" s="3" t="inlineStr">
-        <is>
-          <t>THORN</t>
-        </is>
-      </c>
-      <c r="R1" s="3" t="inlineStr">
+      <c r="W1" s="3" t="inlineStr">
+        <is>
+          <t>Westal</t>
+        </is>
+      </c>
+      <c r="X1" s="3" t="inlineStr">
         <is>
           <t>Airam</t>
         </is>
       </c>
-      <c r="S1" s="3" t="inlineStr">
-        <is>
-          <t>Norwesco</t>
-        </is>
-      </c>
-      <c r="T1" s="3" t="inlineStr">
-        <is>
-          <t>ZG Lighting</t>
-        </is>
-      </c>
-      <c r="U1" s="3" t="inlineStr">
+      <c r="Y1" s="3" t="inlineStr">
         <is>
           <t>Nokalux</t>
-        </is>
-      </c>
-      <c r="V1" s="3" t="inlineStr">
-        <is>
-          <t>Siteco</t>
-        </is>
-      </c>
-      <c r="W1" s="3" t="inlineStr">
-        <is>
-          <t>Esylux</t>
-        </is>
-      </c>
-      <c r="X1" s="3" t="inlineStr">
-        <is>
-          <t>Bergdahls</t>
-        </is>
-      </c>
-      <c r="Y1" s="3" t="inlineStr">
-        <is>
-          <t>Westal</t>
         </is>
       </c>
     </row>
@@ -655,7 +655,7 @@
         <v>0</v>
       </c>
       <c r="N2" s="5" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="O2" s="5" t="n">
         <v>0</v>
@@ -682,7 +682,7 @@
         <v>0</v>
       </c>
       <c r="W2" s="5" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="X2" s="5" t="n">
         <v>0</v>
@@ -734,7 +734,7 @@
         <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -761,7 +761,7 @@
         <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
@@ -813,7 +813,7 @@
         <v>0</v>
       </c>
       <c r="N4" s="5" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="O4" s="5" t="n">
         <v>0</v>
@@ -840,7 +840,7 @@
         <v>0</v>
       </c>
       <c r="W4" s="5" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="X4" s="5" t="n">
         <v>0</v>
@@ -892,7 +892,7 @@
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -919,7 +919,7 @@
         <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
@@ -971,7 +971,7 @@
         <v>0</v>
       </c>
       <c r="N6" s="5" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="O6" s="5" t="n">
         <v>0</v>
@@ -998,7 +998,7 @@
         <v>0</v>
       </c>
       <c r="W6" s="5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="X6" s="5" t="n">
         <v>0</v>
@@ -1047,7 +1047,7 @@
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1074,7 +1074,7 @@
         <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
@@ -1126,7 +1126,7 @@
         <v>0</v>
       </c>
       <c r="N8" s="5" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="O8" s="5" t="n">
         <v>0</v>
@@ -1153,7 +1153,7 @@
         <v>0</v>
       </c>
       <c r="W8" s="5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="X8" s="5" t="n">
         <v>0</v>
@@ -1205,7 +1205,7 @@
         <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1232,7 +1232,7 @@
         <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
         <v>0</v>
@@ -1284,7 +1284,7 @@
         <v>0</v>
       </c>
       <c r="N10" s="5" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="O10" s="5" t="n">
         <v>0</v>
@@ -1311,7 +1311,7 @@
         <v>0</v>
       </c>
       <c r="W10" s="5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="X10" s="5" t="n">
         <v>0</v>
@@ -1363,7 +1363,7 @@
         <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1390,7 +1390,7 @@
         <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
         <v>0</v>
@@ -1442,7 +1442,7 @@
         <v>0</v>
       </c>
       <c r="N12" s="5" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="O12" s="5" t="n">
         <v>0</v>
@@ -1469,7 +1469,7 @@
         <v>0</v>
       </c>
       <c r="W12" s="5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="X12" s="5" t="n">
         <v>0</v>
@@ -1521,7 +1521,7 @@
         <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -1548,7 +1548,7 @@
         <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
         <v>0</v>
@@ -1600,7 +1600,7 @@
         <v>0</v>
       </c>
       <c r="N14" s="5" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="O14" s="5" t="n">
         <v>0</v>
@@ -1627,7 +1627,7 @@
         <v>0</v>
       </c>
       <c r="W14" s="5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="X14" s="5" t="n">
         <v>0</v>
@@ -1679,7 +1679,7 @@
         <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -1706,7 +1706,7 @@
         <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
         <v>0</v>
@@ -1758,7 +1758,7 @@
         <v>0</v>
       </c>
       <c r="N16" s="5" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="O16" s="5" t="n">
         <v>0</v>
@@ -1785,7 +1785,7 @@
         <v>0</v>
       </c>
       <c r="W16" s="5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="X16" s="5" t="n">
         <v>0</v>
@@ -1837,7 +1837,7 @@
         <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -1864,7 +1864,7 @@
         <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
         <v>0</v>
@@ -1916,7 +1916,7 @@
         <v>0</v>
       </c>
       <c r="N18" s="5" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="O18" s="5" t="n">
         <v>0</v>
@@ -1943,7 +1943,7 @@
         <v>0</v>
       </c>
       <c r="W18" s="5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="X18" s="5" t="n">
         <v>0</v>
@@ -1995,7 +1995,7 @@
         <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2022,7 +2022,7 @@
         <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
         <v>0</v>
@@ -2074,7 +2074,7 @@
         <v>0</v>
       </c>
       <c r="N20" s="5" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="O20" s="5" t="n">
         <v>0</v>
@@ -2101,7 +2101,7 @@
         <v>0</v>
       </c>
       <c r="W20" s="5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="X20" s="5" t="n">
         <v>0</v>
@@ -2153,7 +2153,7 @@
         <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2180,7 +2180,7 @@
         <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
         <v>0</v>
@@ -2232,7 +2232,7 @@
         <v>0</v>
       </c>
       <c r="N22" s="5" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="O22" s="5" t="n">
         <v>0</v>
@@ -2259,7 +2259,7 @@
         <v>0</v>
       </c>
       <c r="W22" s="5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="X22" s="5" t="n">
         <v>0</v>
@@ -2311,7 +2311,7 @@
         <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -2338,7 +2338,7 @@
         <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
         <v>0</v>
@@ -2390,7 +2390,7 @@
         <v>0</v>
       </c>
       <c r="N24" s="5" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="O24" s="5" t="n">
         <v>0</v>
@@ -2417,7 +2417,7 @@
         <v>0</v>
       </c>
       <c r="W24" s="5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="X24" s="5" t="n">
         <v>0</v>
@@ -2469,7 +2469,7 @@
         <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -2496,7 +2496,7 @@
         <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
         <v>0</v>
@@ -2548,7 +2548,7 @@
         <v>0</v>
       </c>
       <c r="N26" s="5" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="O26" s="5" t="n">
         <v>0</v>
@@ -2575,7 +2575,7 @@
         <v>0</v>
       </c>
       <c r="W26" s="5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="X26" s="5" t="n">
         <v>0</v>
@@ -2627,7 +2627,7 @@
         <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -2654,7 +2654,7 @@
         <v>0</v>
       </c>
       <c r="W27" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="X27" t="n">
         <v>0</v>
@@ -2785,7 +2785,7 @@
         <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -2812,7 +2812,7 @@
         <v>0</v>
       </c>
       <c r="W29" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="X29" t="n">
         <v>0</v>
@@ -2864,7 +2864,7 @@
         <v>0</v>
       </c>
       <c r="N30" s="5" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="O30" s="5" t="n">
         <v>0</v>
@@ -2891,7 +2891,7 @@
         <v>0</v>
       </c>
       <c r="W30" s="5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="X30" s="5" t="n">
         <v>0</v>
@@ -2943,7 +2943,7 @@
         <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -2970,7 +2970,7 @@
         <v>0</v>
       </c>
       <c r="W31" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="X31" t="n">
         <v>0</v>
@@ -3022,7 +3022,7 @@
         <v>0</v>
       </c>
       <c r="N32" s="5" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="O32" s="5" t="n">
         <v>0</v>
@@ -3049,7 +3049,7 @@
         <v>0</v>
       </c>
       <c r="W32" s="5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="X32" s="5" t="n">
         <v>0</v>
@@ -3101,7 +3101,7 @@
         <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -3128,7 +3128,7 @@
         <v>0</v>
       </c>
       <c r="W33" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="X33" t="n">
         <v>0</v>
@@ -3180,7 +3180,7 @@
         <v>0</v>
       </c>
       <c r="N34" s="5" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="O34" s="5" t="n">
         <v>0</v>
@@ -3207,7 +3207,7 @@
         <v>0</v>
       </c>
       <c r="W34" s="5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="X34" s="5" t="n">
         <v>0</v>
@@ -3259,7 +3259,7 @@
         <v>0</v>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -3286,7 +3286,7 @@
         <v>0</v>
       </c>
       <c r="W35" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="X35" t="n">
         <v>0</v>
@@ -3338,7 +3338,7 @@
         <v>0</v>
       </c>
       <c r="N36" s="5" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="O36" s="5" t="n">
         <v>0</v>
@@ -3365,7 +3365,7 @@
         <v>0</v>
       </c>
       <c r="W36" s="5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="X36" s="5" t="n">
         <v>0</v>
@@ -3417,7 +3417,7 @@
         <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -3444,7 +3444,7 @@
         <v>0</v>
       </c>
       <c r="W37" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="X37" t="n">
         <v>0</v>
@@ -3496,7 +3496,7 @@
         <v>0</v>
       </c>
       <c r="N38" s="5" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="O38" s="5" t="n">
         <v>0</v>
@@ -3523,7 +3523,7 @@
         <v>0</v>
       </c>
       <c r="W38" s="5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="X38" s="5" t="n">
         <v>0</v>
@@ -3575,7 +3575,7 @@
         <v>0</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -3602,7 +3602,7 @@
         <v>0</v>
       </c>
       <c r="W39" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="X39" t="n">
         <v>0</v>
@@ -3654,7 +3654,7 @@
         <v>0</v>
       </c>
       <c r="N40" s="5" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="O40" s="5" t="n">
         <v>0</v>
@@ -3681,7 +3681,7 @@
         <v>0</v>
       </c>
       <c r="W40" s="5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="X40" s="5" t="n">
         <v>0</v>
@@ -3733,7 +3733,7 @@
         <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -3760,7 +3760,7 @@
         <v>0</v>
       </c>
       <c r="W41" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="X41" t="n">
         <v>0</v>
@@ -3812,7 +3812,7 @@
         <v>0</v>
       </c>
       <c r="N42" s="5" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="O42" s="5" t="n">
         <v>0</v>
@@ -3839,7 +3839,7 @@
         <v>0</v>
       </c>
       <c r="W42" s="5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="X42" s="5" t="n">
         <v>0</v>
@@ -3891,7 +3891,7 @@
         <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -3918,7 +3918,7 @@
         <v>0</v>
       </c>
       <c r="W43" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="X43" t="n">
         <v>0</v>
@@ -3970,7 +3970,7 @@
         <v>0</v>
       </c>
       <c r="N44" s="5" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="O44" s="5" t="n">
         <v>0</v>
@@ -3997,7 +3997,7 @@
         <v>0</v>
       </c>
       <c r="W44" s="5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="X44" s="5" t="n">
         <v>0</v>
@@ -4049,7 +4049,7 @@
         <v>0</v>
       </c>
       <c r="N45" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -4076,7 +4076,7 @@
         <v>0</v>
       </c>
       <c r="W45" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="X45" t="n">
         <v>0</v>
@@ -4128,7 +4128,7 @@
         <v>0</v>
       </c>
       <c r="N46" s="5" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="O46" s="5" t="n">
         <v>0</v>
@@ -4155,7 +4155,7 @@
         <v>0</v>
       </c>
       <c r="W46" s="5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="X46" s="5" t="n">
         <v>0</v>
@@ -4207,7 +4207,7 @@
         <v>0</v>
       </c>
       <c r="N47" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -4234,7 +4234,7 @@
         <v>0</v>
       </c>
       <c r="W47" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="X47" t="n">
         <v>0</v>
@@ -4286,7 +4286,7 @@
         <v>0</v>
       </c>
       <c r="N48" s="5" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="O48" s="5" t="n">
         <v>0</v>
@@ -4313,7 +4313,7 @@
         <v>0</v>
       </c>
       <c r="W48" s="5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="X48" s="5" t="n">
         <v>0</v>
@@ -4365,7 +4365,7 @@
         <v>0</v>
       </c>
       <c r="N49" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -4392,7 +4392,7 @@
         <v>0</v>
       </c>
       <c r="W49" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="X49" t="n">
         <v>0</v>
@@ -4444,7 +4444,7 @@
         <v>0</v>
       </c>
       <c r="N50" s="5" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="O50" s="5" t="n">
         <v>0</v>
@@ -4471,7 +4471,7 @@
         <v>0</v>
       </c>
       <c r="W50" s="5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="X50" s="5" t="n">
         <v>0</v>
@@ -4523,7 +4523,7 @@
         <v>0</v>
       </c>
       <c r="N51" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -4550,7 +4550,7 @@
         <v>0</v>
       </c>
       <c r="W51" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="X51" t="n">
         <v>0</v>
@@ -4602,7 +4602,7 @@
         <v>0</v>
       </c>
       <c r="N52" s="5" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="O52" s="5" t="n">
         <v>0</v>
@@ -4629,7 +4629,7 @@
         <v>0</v>
       </c>
       <c r="W52" s="5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="X52" s="5" t="n">
         <v>0</v>
@@ -4681,7 +4681,7 @@
         <v>0</v>
       </c>
       <c r="N53" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -4708,7 +4708,7 @@
         <v>0</v>
       </c>
       <c r="W53" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="X53" t="n">
         <v>0</v>
@@ -4760,7 +4760,7 @@
         <v>0</v>
       </c>
       <c r="N54" s="5" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="O54" s="5" t="n">
         <v>0</v>
@@ -4787,7 +4787,7 @@
         <v>0</v>
       </c>
       <c r="W54" s="5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="X54" s="5" t="n">
         <v>0</v>
@@ -4839,7 +4839,7 @@
         <v>0</v>
       </c>
       <c r="N55" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
@@ -4866,7 +4866,7 @@
         <v>0</v>
       </c>
       <c r="W55" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="X55" t="n">
         <v>0</v>
@@ -4918,7 +4918,7 @@
         <v>0</v>
       </c>
       <c r="N56" s="5" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="O56" s="5" t="n">
         <v>0</v>
@@ -4945,7 +4945,7 @@
         <v>0</v>
       </c>
       <c r="W56" s="5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="X56" s="5" t="n">
         <v>0</v>
@@ -4997,7 +4997,7 @@
         <v>0</v>
       </c>
       <c r="N57" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -5024,7 +5024,7 @@
         <v>0</v>
       </c>
       <c r="W57" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="X57" t="n">
         <v>0</v>
@@ -5076,7 +5076,7 @@
         <v>0</v>
       </c>
       <c r="N58" s="5" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="O58" s="5" t="n">
         <v>0</v>
@@ -5103,7 +5103,7 @@
         <v>0</v>
       </c>
       <c r="W58" s="5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="X58" s="5" t="n">
         <v>0</v>
@@ -5155,7 +5155,7 @@
         <v>0</v>
       </c>
       <c r="N59" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -5182,7 +5182,7 @@
         <v>0</v>
       </c>
       <c r="W59" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="X59" t="n">
         <v>0</v>
@@ -5234,7 +5234,7 @@
         <v>0</v>
       </c>
       <c r="N60" s="5" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="O60" s="5" t="n">
         <v>0</v>
@@ -5261,7 +5261,7 @@
         <v>0</v>
       </c>
       <c r="W60" s="5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="X60" s="5" t="n">
         <v>0</v>
@@ -5313,7 +5313,7 @@
         <v>0</v>
       </c>
       <c r="N61" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -5340,7 +5340,7 @@
         <v>0</v>
       </c>
       <c r="W61" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="X61" t="n">
         <v>0</v>
@@ -5392,7 +5392,7 @@
         <v>0</v>
       </c>
       <c r="N62" s="5" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="O62" s="5" t="n">
         <v>0</v>
@@ -5419,7 +5419,7 @@
         <v>0</v>
       </c>
       <c r="W62" s="5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="X62" s="5" t="n">
         <v>0</v>
@@ -5471,7 +5471,7 @@
         <v>0</v>
       </c>
       <c r="N63" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -5498,7 +5498,7 @@
         <v>0</v>
       </c>
       <c r="W63" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="X63" t="n">
         <v>0</v>
@@ -5550,7 +5550,7 @@
         <v>0</v>
       </c>
       <c r="N64" s="5" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="O64" s="5" t="n">
         <v>0</v>
@@ -5577,7 +5577,7 @@
         <v>0</v>
       </c>
       <c r="W64" s="5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="X64" s="5" t="n">
         <v>0</v>
@@ -5629,7 +5629,7 @@
         <v>0</v>
       </c>
       <c r="N65" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -5656,7 +5656,7 @@
         <v>0</v>
       </c>
       <c r="W65" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="X65" t="n">
         <v>0</v>
@@ -5708,7 +5708,7 @@
         <v>0</v>
       </c>
       <c r="N66" s="5" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="O66" s="5" t="n">
         <v>0</v>
@@ -5735,7 +5735,7 @@
         <v>0</v>
       </c>
       <c r="W66" s="5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="X66" s="5" t="n">
         <v>0</v>
@@ -5786,9 +5786,6 @@
       <c r="M67" t="n">
         <v>0</v>
       </c>
-      <c r="N67" t="n">
-        <v>0</v>
-      </c>
       <c r="O67" t="n">
         <v>0</v>
       </c>
@@ -5811,6 +5808,9 @@
         <v>0</v>
       </c>
       <c r="V67" t="n">
+        <v>0</v>
+      </c>
+      <c r="W67" t="n">
         <v>0</v>
       </c>
       <c r="X67" t="n">
@@ -5863,7 +5863,7 @@
         <v>0</v>
       </c>
       <c r="N68" s="5" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="O68" s="5" t="n">
         <v>0</v>
@@ -5890,7 +5890,7 @@
         <v>0</v>
       </c>
       <c r="W68" s="5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="X68" s="5" t="n">
         <v>0</v>
@@ -5938,9 +5938,6 @@
       <c r="M69" t="n">
         <v>0</v>
       </c>
-      <c r="N69" t="n">
-        <v>0</v>
-      </c>
       <c r="O69" t="n">
         <v>0</v>
       </c>
@@ -5963,6 +5960,9 @@
         <v>0</v>
       </c>
       <c r="V69" t="n">
+        <v>0</v>
+      </c>
+      <c r="W69" t="n">
         <v>0</v>
       </c>
       <c r="X69" t="n">
@@ -6015,7 +6015,7 @@
         <v>0</v>
       </c>
       <c r="N70" s="5" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="O70" s="5" t="n">
         <v>0</v>
@@ -6042,7 +6042,7 @@
         <v>0</v>
       </c>
       <c r="W70" s="5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="X70" s="5" t="n">
         <v>0</v>
@@ -6094,7 +6094,7 @@
         <v>0</v>
       </c>
       <c r="N71" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -6121,7 +6121,7 @@
         <v>0</v>
       </c>
       <c r="W71" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="X71" t="n">
         <v>0</v>
@@ -6173,7 +6173,7 @@
         <v>0</v>
       </c>
       <c r="N72" s="5" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="O72" s="5" t="n">
         <v>0</v>
@@ -6200,7 +6200,7 @@
         <v>0</v>
       </c>
       <c r="W72" s="5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="X72" s="5" t="n">
         <v>0</v>
@@ -6252,7 +6252,7 @@
         <v>0</v>
       </c>
       <c r="N73" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -6279,7 +6279,7 @@
         <v>0</v>
       </c>
       <c r="W73" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="X73" t="n">
         <v>0</v>
@@ -6331,7 +6331,7 @@
         <v>0</v>
       </c>
       <c r="N74" s="5" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="O74" s="5" t="n">
         <v>0</v>
@@ -6358,7 +6358,7 @@
         <v>0</v>
       </c>
       <c r="W74" s="5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="X74" s="5" t="n">
         <v>0</v>
@@ -6410,7 +6410,7 @@
         <v>0</v>
       </c>
       <c r="N75" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -6437,7 +6437,7 @@
         <v>0</v>
       </c>
       <c r="W75" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="X75" t="n">
         <v>0</v>
@@ -6479,14 +6479,14 @@
       <c r="J76" s="5" t="n">
         <v>26</v>
       </c>
-      <c r="K76" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L76" s="5" t="n"/>
-      <c r="M76" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N76" s="5" t="n"/>
+      <c r="K76" s="5" t="n"/>
+      <c r="L76" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M76" s="5" t="n"/>
+      <c r="N76" s="5" t="n">
+        <v>24</v>
+      </c>
       <c r="O76" s="5" t="n">
         <v>0</v>
       </c>
@@ -6512,7 +6512,7 @@
         <v>0</v>
       </c>
       <c r="W76" s="5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="X76" s="5" t="n">
         <v>0</v>
@@ -6563,9 +6563,6 @@
       <c r="M77" t="n">
         <v>0</v>
       </c>
-      <c r="N77" t="n">
-        <v>0</v>
-      </c>
       <c r="O77" t="n">
         <v>0</v>
       </c>
@@ -6588,6 +6585,9 @@
         <v>0</v>
       </c>
       <c r="V77" t="n">
+        <v>0</v>
+      </c>
+      <c r="W77" t="n">
         <v>0</v>
       </c>
       <c r="X77" t="n">
@@ -6640,7 +6640,7 @@
         <v>0</v>
       </c>
       <c r="N78" s="5" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="O78" s="5" t="n">
         <v>0</v>
@@ -6667,7 +6667,7 @@
         <v>0</v>
       </c>
       <c r="W78" s="5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="X78" s="5" t="n">
         <v>0</v>
@@ -6718,9 +6718,6 @@
       <c r="M79" t="n">
         <v>0</v>
       </c>
-      <c r="N79" t="n">
-        <v>0</v>
-      </c>
       <c r="O79" t="n">
         <v>0</v>
       </c>
@@ -6743,6 +6740,9 @@
         <v>0</v>
       </c>
       <c r="V79" t="n">
+        <v>0</v>
+      </c>
+      <c r="W79" t="n">
         <v>0</v>
       </c>
       <c r="X79" t="n">
@@ -6794,9 +6794,7 @@
       <c r="M80" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="N80" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="N80" s="5" t="n"/>
       <c r="O80" s="5" t="n">
         <v>0</v>
       </c>
@@ -6821,7 +6819,9 @@
       <c r="V80" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="W80" s="5" t="n"/>
+      <c r="W80" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="X80" s="5" t="n">
         <v>0</v>
       </c>
@@ -6872,7 +6872,7 @@
         <v>0</v>
       </c>
       <c r="N81" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="O81" t="n">
         <v>0</v>
@@ -6899,7 +6899,7 @@
         <v>0</v>
       </c>
       <c r="W81" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="X81" t="n">
         <v>0</v>
@@ -6950,9 +6950,7 @@
       <c r="M82" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="N82" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="N82" s="5" t="n"/>
       <c r="O82" s="5" t="n">
         <v>0</v>
       </c>
@@ -6977,7 +6975,9 @@
       <c r="V82" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="W82" s="5" t="n"/>
+      <c r="W82" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="X82" s="5" t="n">
         <v>0</v>
       </c>
@@ -7025,7 +7025,7 @@
         <v>0</v>
       </c>
       <c r="N83" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="O83" t="n">
         <v>0</v>
@@ -7052,7 +7052,7 @@
         <v>0</v>
       </c>
       <c r="W83" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="X83" t="n">
         <v>0</v>
@@ -7104,7 +7104,7 @@
         <v>0</v>
       </c>
       <c r="N84" s="5" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="O84" s="5" t="n">
         <v>0</v>
@@ -7131,7 +7131,7 @@
         <v>0</v>
       </c>
       <c r="W84" s="5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="X84" s="5" t="n">
         <v>0</v>
@@ -7182,9 +7182,6 @@
       <c r="M85" t="n">
         <v>0</v>
       </c>
-      <c r="N85" t="n">
-        <v>0</v>
-      </c>
       <c r="O85" t="n">
         <v>0</v>
       </c>
@@ -7207,6 +7204,9 @@
         <v>0</v>
       </c>
       <c r="V85" t="n">
+        <v>0</v>
+      </c>
+      <c r="W85" t="n">
         <v>0</v>
       </c>
       <c r="X85" t="n">
@@ -7258,9 +7258,7 @@
       <c r="M86" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="N86" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="N86" s="5" t="n"/>
       <c r="O86" s="5" t="n">
         <v>0</v>
       </c>
@@ -7285,7 +7283,9 @@
       <c r="V86" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="W86" s="5" t="n"/>
+      <c r="W86" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="X86" s="5" t="n">
         <v>0</v>
       </c>
@@ -7335,9 +7335,6 @@
       <c r="M87" t="n">
         <v>0</v>
       </c>
-      <c r="N87" t="n">
-        <v>0</v>
-      </c>
       <c r="O87" t="n">
         <v>0</v>
       </c>
@@ -7360,6 +7357,9 @@
         <v>0</v>
       </c>
       <c r="V87" t="n">
+        <v>0</v>
+      </c>
+      <c r="W87" t="n">
         <v>0</v>
       </c>
       <c r="X87" t="n">
@@ -7411,9 +7411,7 @@
       <c r="M88" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="N88" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="N88" s="5" t="n"/>
       <c r="O88" s="5" t="n">
         <v>0</v>
       </c>
@@ -7438,7 +7436,9 @@
       <c r="V88" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="W88" s="5" t="n"/>
+      <c r="W88" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="X88" s="5" t="n">
         <v>0</v>
       </c>
@@ -7488,9 +7488,6 @@
       <c r="M89" t="n">
         <v>0</v>
       </c>
-      <c r="N89" t="n">
-        <v>0</v>
-      </c>
       <c r="O89" t="n">
         <v>0</v>
       </c>
@@ -7513,6 +7510,9 @@
         <v>0</v>
       </c>
       <c r="V89" t="n">
+        <v>0</v>
+      </c>
+      <c r="W89" t="n">
         <v>0</v>
       </c>
       <c r="X89" t="n">
@@ -7563,7 +7563,7 @@
         <v>0</v>
       </c>
       <c r="N90" s="5" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="O90" s="5" t="n">
         <v>0</v>
@@ -7590,7 +7590,7 @@
         <v>0</v>
       </c>
       <c r="W90" s="5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="X90" s="5" t="n">
         <v>0</v>
@@ -7641,9 +7641,6 @@
       <c r="M91" t="n">
         <v>0</v>
       </c>
-      <c r="N91" t="n">
-        <v>0</v>
-      </c>
       <c r="O91" t="n">
         <v>0</v>
       </c>
@@ -7666,6 +7663,9 @@
         <v>0</v>
       </c>
       <c r="V91" t="n">
+        <v>0</v>
+      </c>
+      <c r="W91" t="n">
         <v>0</v>
       </c>
       <c r="X91" t="n">
@@ -7717,9 +7717,7 @@
       <c r="M92" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="N92" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="N92" s="5" t="n"/>
       <c r="O92" s="5" t="n">
         <v>0</v>
       </c>
@@ -7744,7 +7742,9 @@
       <c r="V92" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="W92" s="5" t="n"/>
+      <c r="W92" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="X92" s="5" t="n">
         <v>0</v>
       </c>
@@ -7794,9 +7794,6 @@
       <c r="M93" t="n">
         <v>0</v>
       </c>
-      <c r="N93" t="n">
-        <v>0</v>
-      </c>
       <c r="O93" t="n">
         <v>0</v>
       </c>
@@ -7819,6 +7816,9 @@
         <v>0</v>
       </c>
       <c r="V93" t="n">
+        <v>0</v>
+      </c>
+      <c r="W93" t="n">
         <v>0</v>
       </c>
       <c r="X93" t="n">
@@ -7870,9 +7870,7 @@
       <c r="M94" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="N94" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="N94" s="5" t="n"/>
       <c r="O94" s="5" t="n">
         <v>0</v>
       </c>
@@ -7897,7 +7895,9 @@
       <c r="V94" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="W94" s="5" t="n"/>
+      <c r="W94" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="X94" s="5" t="n">
         <v>0</v>
       </c>
@@ -7947,9 +7947,6 @@
       <c r="M95" t="n">
         <v>0</v>
       </c>
-      <c r="N95" t="n">
-        <v>0</v>
-      </c>
       <c r="O95" t="n">
         <v>0</v>
       </c>
@@ -7972,6 +7969,9 @@
         <v>0</v>
       </c>
       <c r="V95" t="n">
+        <v>0</v>
+      </c>
+      <c r="W95" t="n">
         <v>0</v>
       </c>
       <c r="X95" t="n">
@@ -8023,9 +8023,7 @@
       <c r="M96" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="N96" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="N96" s="5" t="n"/>
       <c r="O96" s="5" t="n">
         <v>0</v>
       </c>
@@ -8050,7 +8048,9 @@
       <c r="V96" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="W96" s="5" t="n"/>
+      <c r="W96" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="X96" s="5" t="n">
         <v>0</v>
       </c>
@@ -8097,9 +8097,6 @@
       <c r="M97" t="n">
         <v>0</v>
       </c>
-      <c r="N97" t="n">
-        <v>0</v>
-      </c>
       <c r="O97" t="n">
         <v>0</v>
       </c>
@@ -8122,6 +8119,9 @@
         <v>0</v>
       </c>
       <c r="V97" t="n">
+        <v>0</v>
+      </c>
+      <c r="W97" t="n">
         <v>0</v>
       </c>
       <c r="X97" t="n">
@@ -8173,9 +8173,7 @@
       <c r="M98" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="N98" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="N98" s="5" t="n"/>
       <c r="O98" s="5" t="n">
         <v>0</v>
       </c>
@@ -8200,11 +8198,89 @@
       <c r="V98" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="W98" s="5" t="n"/>
+      <c r="W98" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="X98" s="5" t="n">
         <v>0</v>
       </c>
       <c r="Y98" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B99" t="n">
+        <v>906</v>
+      </c>
+      <c r="C99" t="n">
+        <v>491</v>
+      </c>
+      <c r="D99" t="n">
+        <v>398</v>
+      </c>
+      <c r="E99" t="n">
+        <v>302</v>
+      </c>
+      <c r="F99" t="n">
+        <v>224</v>
+      </c>
+      <c r="G99" t="n">
+        <v>174</v>
+      </c>
+      <c r="H99" t="n">
+        <v>101</v>
+      </c>
+      <c r="I99" t="n">
+        <v>42</v>
+      </c>
+      <c r="J99" t="n">
+        <v>20</v>
+      </c>
+      <c r="K99" t="n">
+        <v>0</v>
+      </c>
+      <c r="L99" t="n">
+        <v>0</v>
+      </c>
+      <c r="M99" t="n">
+        <v>0</v>
+      </c>
+      <c r="O99" t="n">
+        <v>0</v>
+      </c>
+      <c r="P99" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q99" t="n">
+        <v>0</v>
+      </c>
+      <c r="R99" t="n">
+        <v>0</v>
+      </c>
+      <c r="S99" t="n">
+        <v>0</v>
+      </c>
+      <c r="T99" t="n">
+        <v>0</v>
+      </c>
+      <c r="U99" t="n">
+        <v>0</v>
+      </c>
+      <c r="V99" t="n">
+        <v>0</v>
+      </c>
+      <c r="W99" t="n">
+        <v>0</v>
+      </c>
+      <c r="X99" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y99" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8246,7 +8322,7 @@
       </c>
       <c r="D1" s="3" t="inlineStr">
         <is>
-          <t>Lager (2026-10-12)</t>
+          <t>Lager (2026-10-13)</t>
         </is>
       </c>
     </row>
@@ -8267,7 +8343,7 @@
         </is>
       </c>
       <c r="D2" s="4" t="n">
-        <v>522</v>
+        <v>491</v>
       </c>
     </row>
     <row r="3">
@@ -16887,7 +16963,7 @@
         </is>
       </c>
       <c r="D433" s="6" t="n">
-        <v>189</v>
+        <v>184</v>
       </c>
     </row>
     <row r="434">
@@ -18587,7 +18663,7 @@
         </is>
       </c>
       <c r="D518" s="4" t="n">
-        <v>100</v>
+        <v>156</v>
       </c>
     </row>
     <row r="519">
@@ -26407,7 +26483,7 @@
         </is>
       </c>
       <c r="D909" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="910">
@@ -27647,7 +27723,7 @@
         </is>
       </c>
       <c r="D971" s="6" t="n">
-        <v>74</v>
+        <v>78</v>
       </c>
     </row>
     <row r="972">
@@ -27667,7 +27743,7 @@
         </is>
       </c>
       <c r="D972" s="4" t="n">
-        <v>118</v>
+        <v>115</v>
       </c>
     </row>
     <row r="973">
@@ -27687,7 +27763,7 @@
         </is>
       </c>
       <c r="D973" s="6" t="n">
-        <v>183</v>
+        <v>193</v>
       </c>
     </row>
     <row r="974">
@@ -30887,7 +30963,7 @@
         </is>
       </c>
       <c r="D1133" s="6" t="n">
-        <v>48</v>
+        <v>54</v>
       </c>
     </row>
     <row r="1134">
@@ -30967,7 +31043,7 @@
         </is>
       </c>
       <c r="D1137" s="6" t="n">
-        <v>459</v>
+        <v>463</v>
       </c>
     </row>
     <row r="1138">
@@ -30987,7 +31063,7 @@
         </is>
       </c>
       <c r="D1138" s="4" t="n">
-        <v>327</v>
+        <v>344</v>
       </c>
     </row>
   </sheetData>

--- a/data/ahlsell_led_panel_inventory.xlsx
+++ b/data/ahlsell_led_panel_inventory.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y102"/>
+  <dimension ref="A1:Y103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -538,77 +538,77 @@
       </c>
       <c r="K1" s="3" t="inlineStr">
         <is>
+          <t>ANETA LIGHTING</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="inlineStr">
+        <is>
+          <t>Easyform</t>
+        </is>
+      </c>
+      <c r="M1" s="3" t="inlineStr">
+        <is>
           <t>Philips</t>
         </is>
       </c>
-      <c r="L1" s="3" t="inlineStr">
+      <c r="N1" s="3" t="inlineStr">
+        <is>
+          <t>Nokalux</t>
+        </is>
+      </c>
+      <c r="O1" s="3" t="inlineStr">
+        <is>
+          <t>Norwesco</t>
+        </is>
+      </c>
+      <c r="P1" s="3" t="inlineStr">
+        <is>
+          <t>Ensto</t>
+        </is>
+      </c>
+      <c r="Q1" s="3" t="inlineStr">
+        <is>
+          <t>ZG Lighting</t>
+        </is>
+      </c>
+      <c r="R1" s="3" t="inlineStr">
+        <is>
+          <t>Black Box</t>
+        </is>
+      </c>
+      <c r="S1" s="3" t="inlineStr">
+        <is>
+          <t>Westal</t>
+        </is>
+      </c>
+      <c r="T1" s="3" t="inlineStr">
+        <is>
+          <t>THORN</t>
+        </is>
+      </c>
+      <c r="U1" s="3" t="inlineStr">
+        <is>
+          <t>Esylux</t>
+        </is>
+      </c>
+      <c r="V1" s="3" t="inlineStr">
         <is>
           <t>Bergdahls</t>
         </is>
       </c>
-      <c r="M1" s="3" t="inlineStr">
-        <is>
-          <t>Black Box</t>
-        </is>
-      </c>
-      <c r="N1" s="3" t="inlineStr">
+      <c r="W1" s="3" t="inlineStr">
+        <is>
+          <t>Airam</t>
+        </is>
+      </c>
+      <c r="X1" s="3" t="inlineStr">
+        <is>
+          <t>Siteco</t>
+        </is>
+      </c>
+      <c r="Y1" s="3" t="inlineStr">
         <is>
           <t>Legrand</t>
-        </is>
-      </c>
-      <c r="O1" s="3" t="inlineStr">
-        <is>
-          <t>Airam</t>
-        </is>
-      </c>
-      <c r="P1" s="3" t="inlineStr">
-        <is>
-          <t>Esylux</t>
-        </is>
-      </c>
-      <c r="Q1" s="3" t="inlineStr">
-        <is>
-          <t>Siteco</t>
-        </is>
-      </c>
-      <c r="R1" s="3" t="inlineStr">
-        <is>
-          <t>Westal</t>
-        </is>
-      </c>
-      <c r="S1" s="3" t="inlineStr">
-        <is>
-          <t>Easyform</t>
-        </is>
-      </c>
-      <c r="T1" s="3" t="inlineStr">
-        <is>
-          <t>Nokalux</t>
-        </is>
-      </c>
-      <c r="U1" s="3" t="inlineStr">
-        <is>
-          <t>Norwesco</t>
-        </is>
-      </c>
-      <c r="V1" s="3" t="inlineStr">
-        <is>
-          <t>ANETA LIGHTING</t>
-        </is>
-      </c>
-      <c r="W1" s="3" t="inlineStr">
-        <is>
-          <t>THORN</t>
-        </is>
-      </c>
-      <c r="X1" s="3" t="inlineStr">
-        <is>
-          <t>ZG Lighting</t>
-        </is>
-      </c>
-      <c r="Y1" s="3" t="inlineStr">
-        <is>
-          <t>Ensto</t>
         </is>
       </c>
     </row>
@@ -661,22 +661,22 @@
         <v>0</v>
       </c>
       <c r="P2" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q2" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R2" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S2" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T2" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U2" s="5" t="n">
         <v>25</v>
-      </c>
-      <c r="Q2" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R2" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S2" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T2" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U2" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="V2" s="5" t="n">
         <v>0</v>
@@ -740,22 +740,22 @@
         <v>0</v>
       </c>
       <c r="P3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U3" t="n">
         <v>25</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S3" t="n">
-        <v>0</v>
-      </c>
-      <c r="T3" t="n">
-        <v>0</v>
-      </c>
-      <c r="U3" t="n">
-        <v>0</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -819,22 +819,22 @@
         <v>0</v>
       </c>
       <c r="P4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U4" s="5" t="n">
         <v>25</v>
-      </c>
-      <c r="Q4" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R4" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S4" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T4" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U4" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="V4" s="5" t="n">
         <v>0</v>
@@ -898,22 +898,22 @@
         <v>0</v>
       </c>
       <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U5" t="n">
         <v>24</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U5" t="n">
-        <v>0</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -977,22 +977,22 @@
         <v>0</v>
       </c>
       <c r="P6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U6" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="Q6" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R6" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S6" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T6" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U6" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="V6" s="5" t="n">
         <v>0</v>
@@ -1053,22 +1053,22 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0</v>
+      </c>
+      <c r="U7" t="n">
         <v>24</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>0</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="n">
-        <v>0</v>
-      </c>
-      <c r="T7" t="n">
-        <v>0</v>
-      </c>
-      <c r="U7" t="n">
-        <v>0</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1132,22 +1132,22 @@
         <v>0</v>
       </c>
       <c r="P8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U8" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="Q8" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R8" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T8" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U8" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="V8" s="5" t="n">
         <v>0</v>
@@ -1211,22 +1211,22 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U9" t="n">
         <v>24</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>0</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U9" t="n">
-        <v>0</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1290,22 +1290,22 @@
         <v>0</v>
       </c>
       <c r="P10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U10" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="Q10" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R10" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T10" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U10" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="V10" s="5" t="n">
         <v>0</v>
@@ -1369,22 +1369,22 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" t="n">
+        <v>0</v>
+      </c>
+      <c r="U11" t="n">
         <v>24</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>0</v>
-      </c>
-      <c r="R11" t="n">
-        <v>0</v>
-      </c>
-      <c r="S11" t="n">
-        <v>0</v>
-      </c>
-      <c r="T11" t="n">
-        <v>0</v>
-      </c>
-      <c r="U11" t="n">
-        <v>0</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1448,22 +1448,22 @@
         <v>0</v>
       </c>
       <c r="P12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U12" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="Q12" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R12" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T12" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U12" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="V12" s="5" t="n">
         <v>0</v>
@@ -1527,22 +1527,22 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0</v>
+      </c>
+      <c r="T13" t="n">
+        <v>0</v>
+      </c>
+      <c r="U13" t="n">
         <v>24</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>0</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" t="n">
-        <v>0</v>
-      </c>
-      <c r="T13" t="n">
-        <v>0</v>
-      </c>
-      <c r="U13" t="n">
-        <v>0</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -1606,22 +1606,22 @@
         <v>0</v>
       </c>
       <c r="P14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U14" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="Q14" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R14" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S14" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T14" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U14" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="V14" s="5" t="n">
         <v>0</v>
@@ -1685,22 +1685,22 @@
         <v>0</v>
       </c>
       <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" t="n">
+        <v>0</v>
+      </c>
+      <c r="U15" t="n">
         <v>24</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>0</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" t="n">
-        <v>0</v>
-      </c>
-      <c r="T15" t="n">
-        <v>0</v>
-      </c>
-      <c r="U15" t="n">
-        <v>0</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1764,22 +1764,22 @@
         <v>0</v>
       </c>
       <c r="P16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U16" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="Q16" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R16" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S16" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T16" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U16" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="V16" s="5" t="n">
         <v>0</v>
@@ -1843,22 +1843,22 @@
         <v>0</v>
       </c>
       <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0</v>
+      </c>
+      <c r="T17" t="n">
+        <v>0</v>
+      </c>
+      <c r="U17" t="n">
         <v>24</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>0</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" t="n">
-        <v>0</v>
-      </c>
-      <c r="T17" t="n">
-        <v>0</v>
-      </c>
-      <c r="U17" t="n">
-        <v>0</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1922,22 +1922,22 @@
         <v>0</v>
       </c>
       <c r="P18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U18" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="Q18" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R18" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S18" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T18" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U18" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="V18" s="5" t="n">
         <v>0</v>
@@ -2001,22 +2001,22 @@
         <v>0</v>
       </c>
       <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0</v>
+      </c>
+      <c r="T19" t="n">
+        <v>0</v>
+      </c>
+      <c r="U19" t="n">
         <v>24</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>0</v>
-      </c>
-      <c r="R19" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" t="n">
-        <v>0</v>
-      </c>
-      <c r="T19" t="n">
-        <v>0</v>
-      </c>
-      <c r="U19" t="n">
-        <v>0</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -2080,22 +2080,22 @@
         <v>0</v>
       </c>
       <c r="P20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U20" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="Q20" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R20" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S20" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T20" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U20" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="V20" s="5" t="n">
         <v>0</v>
@@ -2159,22 +2159,22 @@
         <v>0</v>
       </c>
       <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>0</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" t="n">
+        <v>0</v>
+      </c>
+      <c r="T21" t="n">
+        <v>0</v>
+      </c>
+      <c r="U21" t="n">
         <v>24</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>0</v>
-      </c>
-      <c r="R21" t="n">
-        <v>0</v>
-      </c>
-      <c r="S21" t="n">
-        <v>0</v>
-      </c>
-      <c r="T21" t="n">
-        <v>0</v>
-      </c>
-      <c r="U21" t="n">
-        <v>0</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2238,22 +2238,22 @@
         <v>0</v>
       </c>
       <c r="P22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U22" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="Q22" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R22" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S22" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T22" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U22" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="V22" s="5" t="n">
         <v>0</v>
@@ -2317,22 +2317,22 @@
         <v>0</v>
       </c>
       <c r="P23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>0</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0</v>
+      </c>
+      <c r="S23" t="n">
+        <v>0</v>
+      </c>
+      <c r="T23" t="n">
+        <v>0</v>
+      </c>
+      <c r="U23" t="n">
         <v>24</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>0</v>
-      </c>
-      <c r="R23" t="n">
-        <v>0</v>
-      </c>
-      <c r="S23" t="n">
-        <v>0</v>
-      </c>
-      <c r="T23" t="n">
-        <v>0</v>
-      </c>
-      <c r="U23" t="n">
-        <v>0</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2396,22 +2396,22 @@
         <v>0</v>
       </c>
       <c r="P24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U24" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="Q24" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R24" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S24" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T24" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U24" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="V24" s="5" t="n">
         <v>0</v>
@@ -2475,22 +2475,22 @@
         <v>0</v>
       </c>
       <c r="P25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>0</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0</v>
+      </c>
+      <c r="S25" t="n">
+        <v>0</v>
+      </c>
+      <c r="T25" t="n">
+        <v>0</v>
+      </c>
+      <c r="U25" t="n">
         <v>24</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>0</v>
-      </c>
-      <c r="R25" t="n">
-        <v>0</v>
-      </c>
-      <c r="S25" t="n">
-        <v>0</v>
-      </c>
-      <c r="T25" t="n">
-        <v>0</v>
-      </c>
-      <c r="U25" t="n">
-        <v>0</v>
       </c>
       <c r="V25" t="n">
         <v>0</v>
@@ -2554,22 +2554,22 @@
         <v>0</v>
       </c>
       <c r="P26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U26" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="Q26" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R26" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S26" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T26" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U26" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="V26" s="5" t="n">
         <v>0</v>
@@ -2633,22 +2633,22 @@
         <v>0</v>
       </c>
       <c r="P27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>0</v>
+      </c>
+      <c r="R27" t="n">
+        <v>0</v>
+      </c>
+      <c r="S27" t="n">
+        <v>0</v>
+      </c>
+      <c r="T27" t="n">
+        <v>0</v>
+      </c>
+      <c r="U27" t="n">
         <v>24</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>0</v>
-      </c>
-      <c r="R27" t="n">
-        <v>0</v>
-      </c>
-      <c r="S27" t="n">
-        <v>0</v>
-      </c>
-      <c r="T27" t="n">
-        <v>0</v>
-      </c>
-      <c r="U27" t="n">
-        <v>0</v>
       </c>
       <c r="V27" t="n">
         <v>0</v>
@@ -2791,22 +2791,22 @@
         <v>0</v>
       </c>
       <c r="P29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>0</v>
+      </c>
+      <c r="R29" t="n">
+        <v>0</v>
+      </c>
+      <c r="S29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T29" t="n">
+        <v>0</v>
+      </c>
+      <c r="U29" t="n">
         <v>24</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>0</v>
-      </c>
-      <c r="R29" t="n">
-        <v>0</v>
-      </c>
-      <c r="S29" t="n">
-        <v>0</v>
-      </c>
-      <c r="T29" t="n">
-        <v>0</v>
-      </c>
-      <c r="U29" t="n">
-        <v>0</v>
       </c>
       <c r="V29" t="n">
         <v>0</v>
@@ -2870,22 +2870,22 @@
         <v>0</v>
       </c>
       <c r="P30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U30" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="Q30" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R30" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S30" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T30" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U30" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="V30" s="5" t="n">
         <v>0</v>
@@ -2949,22 +2949,22 @@
         <v>0</v>
       </c>
       <c r="P31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>0</v>
+      </c>
+      <c r="R31" t="n">
+        <v>0</v>
+      </c>
+      <c r="S31" t="n">
+        <v>0</v>
+      </c>
+      <c r="T31" t="n">
+        <v>0</v>
+      </c>
+      <c r="U31" t="n">
         <v>24</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>0</v>
-      </c>
-      <c r="R31" t="n">
-        <v>0</v>
-      </c>
-      <c r="S31" t="n">
-        <v>0</v>
-      </c>
-      <c r="T31" t="n">
-        <v>0</v>
-      </c>
-      <c r="U31" t="n">
-        <v>0</v>
       </c>
       <c r="V31" t="n">
         <v>0</v>
@@ -3028,22 +3028,22 @@
         <v>0</v>
       </c>
       <c r="P32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U32" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="Q32" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R32" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S32" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T32" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U32" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="V32" s="5" t="n">
         <v>0</v>
@@ -3107,22 +3107,22 @@
         <v>0</v>
       </c>
       <c r="P33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>0</v>
+      </c>
+      <c r="R33" t="n">
+        <v>0</v>
+      </c>
+      <c r="S33" t="n">
+        <v>0</v>
+      </c>
+      <c r="T33" t="n">
+        <v>0</v>
+      </c>
+      <c r="U33" t="n">
         <v>24</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>0</v>
-      </c>
-      <c r="R33" t="n">
-        <v>0</v>
-      </c>
-      <c r="S33" t="n">
-        <v>0</v>
-      </c>
-      <c r="T33" t="n">
-        <v>0</v>
-      </c>
-      <c r="U33" t="n">
-        <v>0</v>
       </c>
       <c r="V33" t="n">
         <v>0</v>
@@ -3186,22 +3186,22 @@
         <v>0</v>
       </c>
       <c r="P34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U34" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="Q34" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R34" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S34" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T34" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U34" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="V34" s="5" t="n">
         <v>0</v>
@@ -3265,22 +3265,22 @@
         <v>0</v>
       </c>
       <c r="P35" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>0</v>
+      </c>
+      <c r="R35" t="n">
+        <v>0</v>
+      </c>
+      <c r="S35" t="n">
+        <v>0</v>
+      </c>
+      <c r="T35" t="n">
+        <v>0</v>
+      </c>
+      <c r="U35" t="n">
         <v>24</v>
-      </c>
-      <c r="Q35" t="n">
-        <v>0</v>
-      </c>
-      <c r="R35" t="n">
-        <v>0</v>
-      </c>
-      <c r="S35" t="n">
-        <v>0</v>
-      </c>
-      <c r="T35" t="n">
-        <v>0</v>
-      </c>
-      <c r="U35" t="n">
-        <v>0</v>
       </c>
       <c r="V35" t="n">
         <v>0</v>
@@ -3344,22 +3344,22 @@
         <v>0</v>
       </c>
       <c r="P36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U36" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="Q36" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R36" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S36" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T36" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U36" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="V36" s="5" t="n">
         <v>0</v>
@@ -3423,22 +3423,22 @@
         <v>0</v>
       </c>
       <c r="P37" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>0</v>
+      </c>
+      <c r="R37" t="n">
+        <v>0</v>
+      </c>
+      <c r="S37" t="n">
+        <v>0</v>
+      </c>
+      <c r="T37" t="n">
+        <v>0</v>
+      </c>
+      <c r="U37" t="n">
         <v>24</v>
-      </c>
-      <c r="Q37" t="n">
-        <v>0</v>
-      </c>
-      <c r="R37" t="n">
-        <v>0</v>
-      </c>
-      <c r="S37" t="n">
-        <v>0</v>
-      </c>
-      <c r="T37" t="n">
-        <v>0</v>
-      </c>
-      <c r="U37" t="n">
-        <v>0</v>
       </c>
       <c r="V37" t="n">
         <v>0</v>
@@ -3502,22 +3502,22 @@
         <v>0</v>
       </c>
       <c r="P38" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q38" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R38" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S38" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T38" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U38" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="Q38" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R38" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S38" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T38" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U38" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="V38" s="5" t="n">
         <v>0</v>
@@ -3581,22 +3581,22 @@
         <v>0</v>
       </c>
       <c r="P39" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>0</v>
+      </c>
+      <c r="R39" t="n">
+        <v>0</v>
+      </c>
+      <c r="S39" t="n">
+        <v>0</v>
+      </c>
+      <c r="T39" t="n">
+        <v>0</v>
+      </c>
+      <c r="U39" t="n">
         <v>24</v>
-      </c>
-      <c r="Q39" t="n">
-        <v>0</v>
-      </c>
-      <c r="R39" t="n">
-        <v>0</v>
-      </c>
-      <c r="S39" t="n">
-        <v>0</v>
-      </c>
-      <c r="T39" t="n">
-        <v>0</v>
-      </c>
-      <c r="U39" t="n">
-        <v>0</v>
       </c>
       <c r="V39" t="n">
         <v>0</v>
@@ -3660,22 +3660,22 @@
         <v>0</v>
       </c>
       <c r="P40" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q40" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R40" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S40" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T40" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U40" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="Q40" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R40" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S40" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T40" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U40" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="V40" s="5" t="n">
         <v>0</v>
@@ -3739,22 +3739,22 @@
         <v>0</v>
       </c>
       <c r="P41" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>0</v>
+      </c>
+      <c r="R41" t="n">
+        <v>0</v>
+      </c>
+      <c r="S41" t="n">
+        <v>0</v>
+      </c>
+      <c r="T41" t="n">
+        <v>0</v>
+      </c>
+      <c r="U41" t="n">
         <v>24</v>
-      </c>
-      <c r="Q41" t="n">
-        <v>0</v>
-      </c>
-      <c r="R41" t="n">
-        <v>0</v>
-      </c>
-      <c r="S41" t="n">
-        <v>0</v>
-      </c>
-      <c r="T41" t="n">
-        <v>0</v>
-      </c>
-      <c r="U41" t="n">
-        <v>0</v>
       </c>
       <c r="V41" t="n">
         <v>0</v>
@@ -3818,22 +3818,22 @@
         <v>0</v>
       </c>
       <c r="P42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U42" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="Q42" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R42" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S42" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T42" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U42" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="V42" s="5" t="n">
         <v>0</v>
@@ -3897,22 +3897,22 @@
         <v>0</v>
       </c>
       <c r="P43" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>0</v>
+      </c>
+      <c r="R43" t="n">
+        <v>0</v>
+      </c>
+      <c r="S43" t="n">
+        <v>0</v>
+      </c>
+      <c r="T43" t="n">
+        <v>0</v>
+      </c>
+      <c r="U43" t="n">
         <v>24</v>
-      </c>
-      <c r="Q43" t="n">
-        <v>0</v>
-      </c>
-      <c r="R43" t="n">
-        <v>0</v>
-      </c>
-      <c r="S43" t="n">
-        <v>0</v>
-      </c>
-      <c r="T43" t="n">
-        <v>0</v>
-      </c>
-      <c r="U43" t="n">
-        <v>0</v>
       </c>
       <c r="V43" t="n">
         <v>0</v>
@@ -3976,22 +3976,22 @@
         <v>0</v>
       </c>
       <c r="P44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U44" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="Q44" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R44" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S44" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T44" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U44" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="V44" s="5" t="n">
         <v>0</v>
@@ -4055,22 +4055,22 @@
         <v>0</v>
       </c>
       <c r="P45" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>0</v>
+      </c>
+      <c r="R45" t="n">
+        <v>0</v>
+      </c>
+      <c r="S45" t="n">
+        <v>0</v>
+      </c>
+      <c r="T45" t="n">
+        <v>0</v>
+      </c>
+      <c r="U45" t="n">
         <v>24</v>
-      </c>
-      <c r="Q45" t="n">
-        <v>0</v>
-      </c>
-      <c r="R45" t="n">
-        <v>0</v>
-      </c>
-      <c r="S45" t="n">
-        <v>0</v>
-      </c>
-      <c r="T45" t="n">
-        <v>0</v>
-      </c>
-      <c r="U45" t="n">
-        <v>0</v>
       </c>
       <c r="V45" t="n">
         <v>0</v>
@@ -4134,22 +4134,22 @@
         <v>0</v>
       </c>
       <c r="P46" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q46" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R46" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S46" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T46" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U46" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="Q46" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R46" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S46" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T46" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U46" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="V46" s="5" t="n">
         <v>0</v>
@@ -4213,22 +4213,22 @@
         <v>0</v>
       </c>
       <c r="P47" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>0</v>
+      </c>
+      <c r="R47" t="n">
+        <v>0</v>
+      </c>
+      <c r="S47" t="n">
+        <v>0</v>
+      </c>
+      <c r="T47" t="n">
+        <v>0</v>
+      </c>
+      <c r="U47" t="n">
         <v>24</v>
-      </c>
-      <c r="Q47" t="n">
-        <v>0</v>
-      </c>
-      <c r="R47" t="n">
-        <v>0</v>
-      </c>
-      <c r="S47" t="n">
-        <v>0</v>
-      </c>
-      <c r="T47" t="n">
-        <v>0</v>
-      </c>
-      <c r="U47" t="n">
-        <v>0</v>
       </c>
       <c r="V47" t="n">
         <v>0</v>
@@ -4292,22 +4292,22 @@
         <v>0</v>
       </c>
       <c r="P48" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q48" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R48" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S48" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T48" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U48" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="Q48" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R48" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S48" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T48" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U48" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="V48" s="5" t="n">
         <v>0</v>
@@ -4371,22 +4371,22 @@
         <v>0</v>
       </c>
       <c r="P49" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>0</v>
+      </c>
+      <c r="R49" t="n">
+        <v>0</v>
+      </c>
+      <c r="S49" t="n">
+        <v>0</v>
+      </c>
+      <c r="T49" t="n">
+        <v>0</v>
+      </c>
+      <c r="U49" t="n">
         <v>24</v>
-      </c>
-      <c r="Q49" t="n">
-        <v>0</v>
-      </c>
-      <c r="R49" t="n">
-        <v>0</v>
-      </c>
-      <c r="S49" t="n">
-        <v>0</v>
-      </c>
-      <c r="T49" t="n">
-        <v>0</v>
-      </c>
-      <c r="U49" t="n">
-        <v>0</v>
       </c>
       <c r="V49" t="n">
         <v>0</v>
@@ -4450,22 +4450,22 @@
         <v>0</v>
       </c>
       <c r="P50" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q50" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R50" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S50" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T50" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U50" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="Q50" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R50" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S50" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T50" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U50" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="V50" s="5" t="n">
         <v>0</v>
@@ -4529,22 +4529,22 @@
         <v>0</v>
       </c>
       <c r="P51" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>0</v>
+      </c>
+      <c r="R51" t="n">
+        <v>0</v>
+      </c>
+      <c r="S51" t="n">
+        <v>0</v>
+      </c>
+      <c r="T51" t="n">
+        <v>0</v>
+      </c>
+      <c r="U51" t="n">
         <v>24</v>
-      </c>
-      <c r="Q51" t="n">
-        <v>0</v>
-      </c>
-      <c r="R51" t="n">
-        <v>0</v>
-      </c>
-      <c r="S51" t="n">
-        <v>0</v>
-      </c>
-      <c r="T51" t="n">
-        <v>0</v>
-      </c>
-      <c r="U51" t="n">
-        <v>0</v>
       </c>
       <c r="V51" t="n">
         <v>0</v>
@@ -4608,22 +4608,22 @@
         <v>0</v>
       </c>
       <c r="P52" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q52" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R52" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S52" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T52" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U52" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="Q52" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R52" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S52" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T52" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U52" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="V52" s="5" t="n">
         <v>0</v>
@@ -4687,22 +4687,22 @@
         <v>0</v>
       </c>
       <c r="P53" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>0</v>
+      </c>
+      <c r="R53" t="n">
+        <v>0</v>
+      </c>
+      <c r="S53" t="n">
+        <v>0</v>
+      </c>
+      <c r="T53" t="n">
+        <v>0</v>
+      </c>
+      <c r="U53" t="n">
         <v>24</v>
-      </c>
-      <c r="Q53" t="n">
-        <v>0</v>
-      </c>
-      <c r="R53" t="n">
-        <v>0</v>
-      </c>
-      <c r="S53" t="n">
-        <v>0</v>
-      </c>
-      <c r="T53" t="n">
-        <v>0</v>
-      </c>
-      <c r="U53" t="n">
-        <v>0</v>
       </c>
       <c r="V53" t="n">
         <v>0</v>
@@ -4766,22 +4766,22 @@
         <v>0</v>
       </c>
       <c r="P54" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q54" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R54" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S54" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T54" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U54" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="Q54" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R54" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S54" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T54" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U54" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="V54" s="5" t="n">
         <v>0</v>
@@ -4845,22 +4845,22 @@
         <v>0</v>
       </c>
       <c r="P55" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>0</v>
+      </c>
+      <c r="R55" t="n">
+        <v>0</v>
+      </c>
+      <c r="S55" t="n">
+        <v>0</v>
+      </c>
+      <c r="T55" t="n">
+        <v>0</v>
+      </c>
+      <c r="U55" t="n">
         <v>24</v>
-      </c>
-      <c r="Q55" t="n">
-        <v>0</v>
-      </c>
-      <c r="R55" t="n">
-        <v>0</v>
-      </c>
-      <c r="S55" t="n">
-        <v>0</v>
-      </c>
-      <c r="T55" t="n">
-        <v>0</v>
-      </c>
-      <c r="U55" t="n">
-        <v>0</v>
       </c>
       <c r="V55" t="n">
         <v>0</v>
@@ -4924,22 +4924,22 @@
         <v>0</v>
       </c>
       <c r="P56" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q56" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R56" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S56" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T56" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U56" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="Q56" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R56" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S56" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T56" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U56" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="V56" s="5" t="n">
         <v>0</v>
@@ -5003,22 +5003,22 @@
         <v>0</v>
       </c>
       <c r="P57" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>0</v>
+      </c>
+      <c r="R57" t="n">
+        <v>0</v>
+      </c>
+      <c r="S57" t="n">
+        <v>0</v>
+      </c>
+      <c r="T57" t="n">
+        <v>0</v>
+      </c>
+      <c r="U57" t="n">
         <v>24</v>
-      </c>
-      <c r="Q57" t="n">
-        <v>0</v>
-      </c>
-      <c r="R57" t="n">
-        <v>0</v>
-      </c>
-      <c r="S57" t="n">
-        <v>0</v>
-      </c>
-      <c r="T57" t="n">
-        <v>0</v>
-      </c>
-      <c r="U57" t="n">
-        <v>0</v>
       </c>
       <c r="V57" t="n">
         <v>0</v>
@@ -5082,22 +5082,22 @@
         <v>0</v>
       </c>
       <c r="P58" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q58" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R58" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S58" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T58" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U58" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="Q58" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R58" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S58" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T58" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U58" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="V58" s="5" t="n">
         <v>0</v>
@@ -5161,22 +5161,22 @@
         <v>0</v>
       </c>
       <c r="P59" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>0</v>
+      </c>
+      <c r="R59" t="n">
+        <v>0</v>
+      </c>
+      <c r="S59" t="n">
+        <v>0</v>
+      </c>
+      <c r="T59" t="n">
+        <v>0</v>
+      </c>
+      <c r="U59" t="n">
         <v>24</v>
-      </c>
-      <c r="Q59" t="n">
-        <v>0</v>
-      </c>
-      <c r="R59" t="n">
-        <v>0</v>
-      </c>
-      <c r="S59" t="n">
-        <v>0</v>
-      </c>
-      <c r="T59" t="n">
-        <v>0</v>
-      </c>
-      <c r="U59" t="n">
-        <v>0</v>
       </c>
       <c r="V59" t="n">
         <v>0</v>
@@ -5240,22 +5240,22 @@
         <v>0</v>
       </c>
       <c r="P60" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q60" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R60" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S60" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T60" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U60" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="Q60" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R60" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S60" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T60" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U60" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="V60" s="5" t="n">
         <v>0</v>
@@ -5319,22 +5319,22 @@
         <v>0</v>
       </c>
       <c r="P61" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q61" t="n">
+        <v>0</v>
+      </c>
+      <c r="R61" t="n">
+        <v>0</v>
+      </c>
+      <c r="S61" t="n">
+        <v>0</v>
+      </c>
+      <c r="T61" t="n">
+        <v>0</v>
+      </c>
+      <c r="U61" t="n">
         <v>24</v>
-      </c>
-      <c r="Q61" t="n">
-        <v>0</v>
-      </c>
-      <c r="R61" t="n">
-        <v>0</v>
-      </c>
-      <c r="S61" t="n">
-        <v>0</v>
-      </c>
-      <c r="T61" t="n">
-        <v>0</v>
-      </c>
-      <c r="U61" t="n">
-        <v>0</v>
       </c>
       <c r="V61" t="n">
         <v>0</v>
@@ -5398,22 +5398,22 @@
         <v>0</v>
       </c>
       <c r="P62" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q62" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R62" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S62" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T62" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U62" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="Q62" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R62" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S62" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T62" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U62" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="V62" s="5" t="n">
         <v>0</v>
@@ -5477,22 +5477,22 @@
         <v>0</v>
       </c>
       <c r="P63" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q63" t="n">
+        <v>0</v>
+      </c>
+      <c r="R63" t="n">
+        <v>0</v>
+      </c>
+      <c r="S63" t="n">
+        <v>0</v>
+      </c>
+      <c r="T63" t="n">
+        <v>0</v>
+      </c>
+      <c r="U63" t="n">
         <v>24</v>
-      </c>
-      <c r="Q63" t="n">
-        <v>0</v>
-      </c>
-      <c r="R63" t="n">
-        <v>0</v>
-      </c>
-      <c r="S63" t="n">
-        <v>0</v>
-      </c>
-      <c r="T63" t="n">
-        <v>0</v>
-      </c>
-      <c r="U63" t="n">
-        <v>0</v>
       </c>
       <c r="V63" t="n">
         <v>0</v>
@@ -5556,22 +5556,22 @@
         <v>0</v>
       </c>
       <c r="P64" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q64" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R64" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S64" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T64" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U64" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="Q64" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R64" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S64" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T64" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U64" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="V64" s="5" t="n">
         <v>0</v>
@@ -5635,22 +5635,22 @@
         <v>0</v>
       </c>
       <c r="P65" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q65" t="n">
+        <v>0</v>
+      </c>
+      <c r="R65" t="n">
+        <v>0</v>
+      </c>
+      <c r="S65" t="n">
+        <v>0</v>
+      </c>
+      <c r="T65" t="n">
+        <v>0</v>
+      </c>
+      <c r="U65" t="n">
         <v>24</v>
-      </c>
-      <c r="Q65" t="n">
-        <v>0</v>
-      </c>
-      <c r="R65" t="n">
-        <v>0</v>
-      </c>
-      <c r="S65" t="n">
-        <v>0</v>
-      </c>
-      <c r="T65" t="n">
-        <v>0</v>
-      </c>
-      <c r="U65" t="n">
-        <v>0</v>
       </c>
       <c r="V65" t="n">
         <v>0</v>
@@ -5714,22 +5714,22 @@
         <v>0</v>
       </c>
       <c r="P66" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q66" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R66" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S66" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T66" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U66" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="Q66" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R66" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S66" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T66" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U66" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="V66" s="5" t="n">
         <v>0</v>
@@ -5792,6 +5792,9 @@
       <c r="O67" t="n">
         <v>0</v>
       </c>
+      <c r="P67" t="n">
+        <v>0</v>
+      </c>
       <c r="Q67" t="n">
         <v>0</v>
       </c>
@@ -5802,9 +5805,6 @@
         <v>0</v>
       </c>
       <c r="T67" t="n">
-        <v>0</v>
-      </c>
-      <c r="U67" t="n">
         <v>0</v>
       </c>
       <c r="V67" t="n">
@@ -5869,22 +5869,22 @@
         <v>0</v>
       </c>
       <c r="P68" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q68" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R68" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S68" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T68" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U68" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="Q68" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R68" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S68" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T68" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U68" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="V68" s="5" t="n">
         <v>0</v>
@@ -5944,6 +5944,9 @@
       <c r="O69" t="n">
         <v>0</v>
       </c>
+      <c r="P69" t="n">
+        <v>0</v>
+      </c>
       <c r="Q69" t="n">
         <v>0</v>
       </c>
@@ -5954,9 +5957,6 @@
         <v>0</v>
       </c>
       <c r="T69" t="n">
-        <v>0</v>
-      </c>
-      <c r="U69" t="n">
         <v>0</v>
       </c>
       <c r="V69" t="n">
@@ -6021,22 +6021,22 @@
         <v>0</v>
       </c>
       <c r="P70" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q70" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R70" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S70" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T70" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U70" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="Q70" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R70" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S70" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T70" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U70" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="V70" s="5" t="n">
         <v>0</v>
@@ -6100,22 +6100,22 @@
         <v>0</v>
       </c>
       <c r="P71" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q71" t="n">
+        <v>0</v>
+      </c>
+      <c r="R71" t="n">
+        <v>0</v>
+      </c>
+      <c r="S71" t="n">
+        <v>0</v>
+      </c>
+      <c r="T71" t="n">
+        <v>0</v>
+      </c>
+      <c r="U71" t="n">
         <v>24</v>
-      </c>
-      <c r="Q71" t="n">
-        <v>0</v>
-      </c>
-      <c r="R71" t="n">
-        <v>0</v>
-      </c>
-      <c r="S71" t="n">
-        <v>0</v>
-      </c>
-      <c r="T71" t="n">
-        <v>0</v>
-      </c>
-      <c r="U71" t="n">
-        <v>0</v>
       </c>
       <c r="V71" t="n">
         <v>0</v>
@@ -6179,22 +6179,22 @@
         <v>0</v>
       </c>
       <c r="P72" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q72" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R72" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S72" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T72" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U72" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="Q72" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R72" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S72" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T72" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U72" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="V72" s="5" t="n">
         <v>0</v>
@@ -6258,22 +6258,22 @@
         <v>0</v>
       </c>
       <c r="P73" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q73" t="n">
+        <v>0</v>
+      </c>
+      <c r="R73" t="n">
+        <v>0</v>
+      </c>
+      <c r="S73" t="n">
+        <v>0</v>
+      </c>
+      <c r="T73" t="n">
+        <v>0</v>
+      </c>
+      <c r="U73" t="n">
         <v>24</v>
-      </c>
-      <c r="Q73" t="n">
-        <v>0</v>
-      </c>
-      <c r="R73" t="n">
-        <v>0</v>
-      </c>
-      <c r="S73" t="n">
-        <v>0</v>
-      </c>
-      <c r="T73" t="n">
-        <v>0</v>
-      </c>
-      <c r="U73" t="n">
-        <v>0</v>
       </c>
       <c r="V73" t="n">
         <v>0</v>
@@ -6337,22 +6337,22 @@
         <v>0</v>
       </c>
       <c r="P74" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q74" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R74" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S74" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T74" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U74" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="Q74" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R74" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S74" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T74" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U74" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="V74" s="5" t="n">
         <v>0</v>
@@ -6416,22 +6416,22 @@
         <v>0</v>
       </c>
       <c r="P75" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
         <v>24</v>
-      </c>
-      <c r="Q75" t="n">
-        <v>0</v>
-      </c>
-      <c r="R75" t="n">
-        <v>0</v>
-      </c>
-      <c r="S75" t="n">
-        <v>0</v>
-      </c>
-      <c r="T75" t="n">
-        <v>0</v>
-      </c>
-      <c r="U75" t="n">
-        <v>0</v>
       </c>
       <c r="V75" t="n">
         <v>0</v>
@@ -6485,29 +6485,31 @@
       <c r="L76" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="M76" s="5" t="n"/>
-      <c r="N76" s="5" t="n"/>
+      <c r="M76" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N76" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="O76" s="5" t="n">
         <v>0</v>
       </c>
       <c r="P76" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q76" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R76" s="5" t="n"/>
+      <c r="S76" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T76" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U76" s="5" t="n">
         <v>24</v>
       </c>
-      <c r="Q76" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R76" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S76" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T76" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U76" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="V76" s="5" t="n">
         <v>0</v>
       </c>
@@ -6517,9 +6519,7 @@
       <c r="X76" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="Y76" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="Y76" s="5" t="n"/>
     </row>
     <row r="77">
       <c r="A77" s="6" t="inlineStr">
@@ -6569,6 +6569,9 @@
       <c r="O77" t="n">
         <v>0</v>
       </c>
+      <c r="P77" t="n">
+        <v>0</v>
+      </c>
       <c r="Q77" t="n">
         <v>0</v>
       </c>
@@ -6579,9 +6582,6 @@
         <v>0</v>
       </c>
       <c r="T77" t="n">
-        <v>0</v>
-      </c>
-      <c r="U77" t="n">
         <v>0</v>
       </c>
       <c r="V77" t="n">
@@ -6646,22 +6646,22 @@
         <v>0</v>
       </c>
       <c r="P78" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q78" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R78" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S78" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T78" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U78" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="Q78" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R78" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S78" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T78" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U78" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="V78" s="5" t="n">
         <v>0</v>
@@ -6724,6 +6724,9 @@
       <c r="O79" t="n">
         <v>0</v>
       </c>
+      <c r="P79" t="n">
+        <v>0</v>
+      </c>
       <c r="Q79" t="n">
         <v>0</v>
       </c>
@@ -6734,9 +6737,6 @@
         <v>0</v>
       </c>
       <c r="T79" t="n">
-        <v>0</v>
-      </c>
-      <c r="U79" t="n">
         <v>0</v>
       </c>
       <c r="V79" t="n">
@@ -6800,7 +6800,9 @@
       <c r="O80" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="P80" s="5" t="n"/>
+      <c r="P80" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="Q80" s="5" t="n">
         <v>0</v>
       </c>
@@ -6813,9 +6815,7 @@
       <c r="T80" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="U80" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="U80" s="5" t="n"/>
       <c r="V80" s="5" t="n">
         <v>0</v>
       </c>
@@ -6878,22 +6878,22 @@
         <v>0</v>
       </c>
       <c r="P81" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q81" t="n">
+        <v>0</v>
+      </c>
+      <c r="R81" t="n">
+        <v>0</v>
+      </c>
+      <c r="S81" t="n">
+        <v>0</v>
+      </c>
+      <c r="T81" t="n">
+        <v>0</v>
+      </c>
+      <c r="U81" t="n">
         <v>24</v>
-      </c>
-      <c r="Q81" t="n">
-        <v>0</v>
-      </c>
-      <c r="R81" t="n">
-        <v>0</v>
-      </c>
-      <c r="S81" t="n">
-        <v>0</v>
-      </c>
-      <c r="T81" t="n">
-        <v>0</v>
-      </c>
-      <c r="U81" t="n">
-        <v>0</v>
       </c>
       <c r="V81" t="n">
         <v>0</v>
@@ -6956,7 +6956,9 @@
       <c r="O82" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="P82" s="5" t="n"/>
+      <c r="P82" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="Q82" s="5" t="n">
         <v>0</v>
       </c>
@@ -6969,9 +6971,7 @@
       <c r="T82" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="U82" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="U82" s="5" t="n"/>
       <c r="V82" s="5" t="n">
         <v>0</v>
       </c>
@@ -7031,22 +7031,22 @@
         <v>0</v>
       </c>
       <c r="P83" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q83" t="n">
+        <v>0</v>
+      </c>
+      <c r="R83" t="n">
+        <v>0</v>
+      </c>
+      <c r="S83" t="n">
+        <v>0</v>
+      </c>
+      <c r="T83" t="n">
+        <v>0</v>
+      </c>
+      <c r="U83" t="n">
         <v>24</v>
-      </c>
-      <c r="Q83" t="n">
-        <v>0</v>
-      </c>
-      <c r="R83" t="n">
-        <v>0</v>
-      </c>
-      <c r="S83" t="n">
-        <v>0</v>
-      </c>
-      <c r="T83" t="n">
-        <v>0</v>
-      </c>
-      <c r="U83" t="n">
-        <v>0</v>
       </c>
       <c r="V83" t="n">
         <v>0</v>
@@ -7110,22 +7110,22 @@
         <v>0</v>
       </c>
       <c r="P84" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q84" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R84" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S84" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T84" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U84" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="Q84" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R84" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S84" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T84" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U84" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="V84" s="5" t="n">
         <v>0</v>
@@ -7188,6 +7188,9 @@
       <c r="O85" t="n">
         <v>0</v>
       </c>
+      <c r="P85" t="n">
+        <v>0</v>
+      </c>
       <c r="Q85" t="n">
         <v>0</v>
       </c>
@@ -7198,9 +7201,6 @@
         <v>0</v>
       </c>
       <c r="T85" t="n">
-        <v>0</v>
-      </c>
-      <c r="U85" t="n">
         <v>0</v>
       </c>
       <c r="V85" t="n">
@@ -7264,7 +7264,9 @@
       <c r="O86" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="P86" s="5" t="n"/>
+      <c r="P86" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="Q86" s="5" t="n">
         <v>0</v>
       </c>
@@ -7277,9 +7279,7 @@
       <c r="T86" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="U86" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="U86" s="5" t="n"/>
       <c r="V86" s="5" t="n">
         <v>0</v>
       </c>
@@ -7341,6 +7341,9 @@
       <c r="O87" t="n">
         <v>0</v>
       </c>
+      <c r="P87" t="n">
+        <v>0</v>
+      </c>
       <c r="Q87" t="n">
         <v>0</v>
       </c>
@@ -7351,9 +7354,6 @@
         <v>0</v>
       </c>
       <c r="T87" t="n">
-        <v>0</v>
-      </c>
-      <c r="U87" t="n">
         <v>0</v>
       </c>
       <c r="V87" t="n">
@@ -7417,7 +7417,9 @@
       <c r="O88" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="P88" s="5" t="n"/>
+      <c r="P88" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="Q88" s="5" t="n">
         <v>0</v>
       </c>
@@ -7430,9 +7432,7 @@
       <c r="T88" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="U88" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="U88" s="5" t="n"/>
       <c r="V88" s="5" t="n">
         <v>0</v>
       </c>
@@ -7494,6 +7494,9 @@
       <c r="O89" t="n">
         <v>0</v>
       </c>
+      <c r="P89" t="n">
+        <v>0</v>
+      </c>
       <c r="Q89" t="n">
         <v>0</v>
       </c>
@@ -7504,9 +7507,6 @@
         <v>0</v>
       </c>
       <c r="T89" t="n">
-        <v>0</v>
-      </c>
-      <c r="U89" t="n">
         <v>0</v>
       </c>
       <c r="V89" t="n">
@@ -7569,22 +7569,22 @@
         <v>0</v>
       </c>
       <c r="P90" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q90" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R90" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S90" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T90" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U90" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="Q90" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R90" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S90" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T90" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U90" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="V90" s="5" t="n">
         <v>0</v>
@@ -7647,6 +7647,9 @@
       <c r="O91" t="n">
         <v>0</v>
       </c>
+      <c r="P91" t="n">
+        <v>0</v>
+      </c>
       <c r="Q91" t="n">
         <v>0</v>
       </c>
@@ -7657,9 +7660,6 @@
         <v>0</v>
       </c>
       <c r="T91" t="n">
-        <v>0</v>
-      </c>
-      <c r="U91" t="n">
         <v>0</v>
       </c>
       <c r="V91" t="n">
@@ -7723,7 +7723,9 @@
       <c r="O92" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="P92" s="5" t="n"/>
+      <c r="P92" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="Q92" s="5" t="n">
         <v>0</v>
       </c>
@@ -7736,9 +7738,7 @@
       <c r="T92" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="U92" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="U92" s="5" t="n"/>
       <c r="V92" s="5" t="n">
         <v>0</v>
       </c>
@@ -7800,6 +7800,9 @@
       <c r="O93" t="n">
         <v>0</v>
       </c>
+      <c r="P93" t="n">
+        <v>0</v>
+      </c>
       <c r="Q93" t="n">
         <v>0</v>
       </c>
@@ -7810,9 +7813,6 @@
         <v>0</v>
       </c>
       <c r="T93" t="n">
-        <v>0</v>
-      </c>
-      <c r="U93" t="n">
         <v>0</v>
       </c>
       <c r="V93" t="n">
@@ -7876,7 +7876,9 @@
       <c r="O94" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="P94" s="5" t="n"/>
+      <c r="P94" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="Q94" s="5" t="n">
         <v>0</v>
       </c>
@@ -7889,9 +7891,7 @@
       <c r="T94" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="U94" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="U94" s="5" t="n"/>
       <c r="V94" s="5" t="n">
         <v>0</v>
       </c>
@@ -7953,6 +7953,9 @@
       <c r="O95" t="n">
         <v>0</v>
       </c>
+      <c r="P95" t="n">
+        <v>0</v>
+      </c>
       <c r="Q95" t="n">
         <v>0</v>
       </c>
@@ -7963,9 +7966,6 @@
         <v>0</v>
       </c>
       <c r="T95" t="n">
-        <v>0</v>
-      </c>
-      <c r="U95" t="n">
         <v>0</v>
       </c>
       <c r="V95" t="n">
@@ -8029,7 +8029,9 @@
       <c r="O96" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="P96" s="5" t="n"/>
+      <c r="P96" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="Q96" s="5" t="n">
         <v>0</v>
       </c>
@@ -8042,9 +8044,7 @@
       <c r="T96" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="U96" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="U96" s="5" t="n"/>
       <c r="V96" s="5" t="n">
         <v>0</v>
       </c>
@@ -8103,6 +8103,9 @@
       <c r="O97" t="n">
         <v>0</v>
       </c>
+      <c r="P97" t="n">
+        <v>0</v>
+      </c>
       <c r="Q97" t="n">
         <v>0</v>
       </c>
@@ -8113,9 +8116,6 @@
         <v>0</v>
       </c>
       <c r="T97" t="n">
-        <v>0</v>
-      </c>
-      <c r="U97" t="n">
         <v>0</v>
       </c>
       <c r="V97" t="n">
@@ -8179,7 +8179,9 @@
       <c r="O98" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="P98" s="5" t="n"/>
+      <c r="P98" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="Q98" s="5" t="n">
         <v>0</v>
       </c>
@@ -8192,9 +8194,7 @@
       <c r="T98" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="U98" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="U98" s="5" t="n"/>
       <c r="V98" s="5" t="n">
         <v>0</v>
       </c>
@@ -8256,6 +8256,9 @@
       <c r="O99" t="n">
         <v>0</v>
       </c>
+      <c r="P99" t="n">
+        <v>0</v>
+      </c>
       <c r="Q99" t="n">
         <v>0</v>
       </c>
@@ -8266,9 +8269,6 @@
         <v>0</v>
       </c>
       <c r="T99" t="n">
-        <v>0</v>
-      </c>
-      <c r="U99" t="n">
         <v>0</v>
       </c>
       <c r="V99" t="n">
@@ -8332,7 +8332,9 @@
       <c r="O100" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="P100" s="5" t="n"/>
+      <c r="P100" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="Q100" s="5" t="n">
         <v>0</v>
       </c>
@@ -8345,9 +8347,7 @@
       <c r="T100" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="U100" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="U100" s="5" t="n"/>
       <c r="V100" s="5" t="n">
         <v>0</v>
       </c>
@@ -8409,6 +8409,9 @@
       <c r="O101" t="n">
         <v>0</v>
       </c>
+      <c r="P101" t="n">
+        <v>0</v>
+      </c>
       <c r="Q101" t="n">
         <v>0</v>
       </c>
@@ -8419,9 +8422,6 @@
         <v>0</v>
       </c>
       <c r="T101" t="n">
-        <v>0</v>
-      </c>
-      <c r="U101" t="n">
         <v>0</v>
       </c>
       <c r="V101" t="n">
@@ -8485,7 +8485,9 @@
       <c r="O102" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="P102" s="5" t="n"/>
+      <c r="P102" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="Q102" s="5" t="n">
         <v>0</v>
       </c>
@@ -8498,9 +8500,7 @@
       <c r="T102" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="U102" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="U102" s="5" t="n"/>
       <c r="V102" s="5" t="n">
         <v>0</v>
       </c>
@@ -8511,6 +8511,82 @@
         <v>0</v>
       </c>
       <c r="Y102" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="B103" t="n">
+        <v>899</v>
+      </c>
+      <c r="C103" t="n">
+        <v>485</v>
+      </c>
+      <c r="D103" t="n">
+        <v>411</v>
+      </c>
+      <c r="E103" t="n">
+        <v>274</v>
+      </c>
+      <c r="F103" t="n">
+        <v>220</v>
+      </c>
+      <c r="G103" t="n">
+        <v>123</v>
+      </c>
+      <c r="H103" t="n">
+        <v>101</v>
+      </c>
+      <c r="I103" t="n">
+        <v>42</v>
+      </c>
+      <c r="J103" t="n">
+        <v>26</v>
+      </c>
+      <c r="K103" t="n">
+        <v>0</v>
+      </c>
+      <c r="L103" t="n">
+        <v>0</v>
+      </c>
+      <c r="M103" t="n">
+        <v>0</v>
+      </c>
+      <c r="N103" t="n">
+        <v>0</v>
+      </c>
+      <c r="O103" t="n">
+        <v>0</v>
+      </c>
+      <c r="P103" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q103" t="n">
+        <v>0</v>
+      </c>
+      <c r="R103" t="n">
+        <v>0</v>
+      </c>
+      <c r="S103" t="n">
+        <v>0</v>
+      </c>
+      <c r="T103" t="n">
+        <v>0</v>
+      </c>
+      <c r="V103" t="n">
+        <v>0</v>
+      </c>
+      <c r="W103" t="n">
+        <v>0</v>
+      </c>
+      <c r="X103" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y103" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8552,7 +8628,7 @@
       </c>
       <c r="D1" s="3" t="inlineStr">
         <is>
-          <t>Lager (2026-10-16)</t>
+          <t>Lager (2026-10-17)</t>
         </is>
       </c>
     </row>
@@ -8573,7 +8649,7 @@
         </is>
       </c>
       <c r="D2" s="4" t="n">
-        <v>488</v>
+        <v>485</v>
       </c>
     </row>
     <row r="3">
@@ -16453,7 +16529,7 @@
         </is>
       </c>
       <c r="D396" s="4" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
     </row>
     <row r="397">
@@ -16913,7 +16989,7 @@
         </is>
       </c>
       <c r="D419" s="6" t="n">
-        <v>182</v>
+        <v>180</v>
       </c>
     </row>
     <row r="420">
@@ -17573,7 +17649,7 @@
         </is>
       </c>
       <c r="D452" s="4" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="453">
@@ -18033,7 +18109,7 @@
         </is>
       </c>
       <c r="D475" s="6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="476">
@@ -18613,7 +18689,7 @@
         </is>
       </c>
       <c r="D504" s="4" t="n">
-        <v>155</v>
+        <v>113</v>
       </c>
     </row>
     <row r="505">
@@ -25853,7 +25929,7 @@
         </is>
       </c>
       <c r="D866" s="4" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
     </row>
     <row r="867">
@@ -25993,7 +26069,7 @@
         </is>
       </c>
       <c r="D873" s="6" t="n">
-        <v>223</v>
+        <v>216</v>
       </c>
     </row>
     <row r="874">
@@ -27833,7 +27909,7 @@
         </is>
       </c>
       <c r="D965" s="6" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="966">
@@ -27853,7 +27929,7 @@
         </is>
       </c>
       <c r="D966" s="4" t="n">
-        <v>143</v>
+        <v>146</v>
       </c>
     </row>
     <row r="967">
@@ -27873,7 +27949,7 @@
         </is>
       </c>
       <c r="D967" s="6" t="n">
-        <v>193</v>
+        <v>188</v>
       </c>
     </row>
     <row r="968">
@@ -31873,7 +31949,7 @@
         </is>
       </c>
       <c r="D1167" s="6" t="n">
-        <v>464</v>
+        <v>460</v>
       </c>
     </row>
     <row r="1168">
@@ -31893,7 +31969,7 @@
         </is>
       </c>
       <c r="D1168" s="4" t="n">
-        <v>344</v>
+        <v>340</v>
       </c>
     </row>
   </sheetData>

--- a/data/ahlsell_led_panel_inventory.xlsx
+++ b/data/ahlsell_led_panel_inventory.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y105"/>
+  <dimension ref="A1:Y106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -538,77 +538,77 @@
       </c>
       <c r="K1" s="3" t="inlineStr">
         <is>
+          <t>ZG Lighting</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="inlineStr">
+        <is>
+          <t>Norwesco</t>
+        </is>
+      </c>
+      <c r="M1" s="3" t="inlineStr">
+        <is>
+          <t>Philips</t>
+        </is>
+      </c>
+      <c r="N1" s="3" t="inlineStr">
+        <is>
+          <t>ANETA LIGHTING</t>
+        </is>
+      </c>
+      <c r="O1" s="3" t="inlineStr">
+        <is>
           <t>Ensto</t>
         </is>
       </c>
-      <c r="L1" s="3" t="inlineStr">
-        <is>
-          <t>ZG Lighting</t>
-        </is>
-      </c>
-      <c r="M1" s="3" t="inlineStr">
+      <c r="P1" s="3" t="inlineStr">
+        <is>
+          <t>Black Box</t>
+        </is>
+      </c>
+      <c r="Q1" s="3" t="inlineStr">
+        <is>
+          <t>THORN</t>
+        </is>
+      </c>
+      <c r="R1" s="3" t="inlineStr">
+        <is>
+          <t>Legrand</t>
+        </is>
+      </c>
+      <c r="S1" s="3" t="inlineStr">
+        <is>
+          <t>Easyform</t>
+        </is>
+      </c>
+      <c r="T1" s="3" t="inlineStr">
+        <is>
+          <t>Siteco</t>
+        </is>
+      </c>
+      <c r="U1" s="3" t="inlineStr">
         <is>
           <t>Bergdahls</t>
         </is>
       </c>
-      <c r="N1" s="3" t="inlineStr">
+      <c r="V1" s="3" t="inlineStr">
+        <is>
+          <t>Airam</t>
+        </is>
+      </c>
+      <c r="W1" s="3" t="inlineStr">
         <is>
           <t>Westal</t>
         </is>
       </c>
-      <c r="O1" s="3" t="inlineStr">
-        <is>
-          <t>ANETA LIGHTING</t>
-        </is>
-      </c>
-      <c r="P1" s="3" t="inlineStr">
-        <is>
-          <t>Black Box</t>
-        </is>
-      </c>
-      <c r="Q1" s="3" t="inlineStr">
+      <c r="X1" s="3" t="inlineStr">
+        <is>
+          <t>Esylux</t>
+        </is>
+      </c>
+      <c r="Y1" s="3" t="inlineStr">
         <is>
           <t>Nokalux</t>
-        </is>
-      </c>
-      <c r="R1" s="3" t="inlineStr">
-        <is>
-          <t>Philips</t>
-        </is>
-      </c>
-      <c r="S1" s="3" t="inlineStr">
-        <is>
-          <t>Easyform</t>
-        </is>
-      </c>
-      <c r="T1" s="3" t="inlineStr">
-        <is>
-          <t>Airam</t>
-        </is>
-      </c>
-      <c r="U1" s="3" t="inlineStr">
-        <is>
-          <t>Norwesco</t>
-        </is>
-      </c>
-      <c r="V1" s="3" t="inlineStr">
-        <is>
-          <t>Esylux</t>
-        </is>
-      </c>
-      <c r="W1" s="3" t="inlineStr">
-        <is>
-          <t>Siteco</t>
-        </is>
-      </c>
-      <c r="X1" s="3" t="inlineStr">
-        <is>
-          <t>Legrand</t>
-        </is>
-      </c>
-      <c r="Y1" s="3" t="inlineStr">
-        <is>
-          <t>THORN</t>
         </is>
       </c>
     </row>
@@ -679,13 +679,13 @@
         <v>0</v>
       </c>
       <c r="V2" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W2" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X2" s="5" t="n">
         <v>25</v>
-      </c>
-      <c r="W2" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="X2" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="Y2" s="5" t="n">
         <v>0</v>
@@ -758,13 +758,13 @@
         <v>0</v>
       </c>
       <c r="V3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X3" t="n">
         <v>25</v>
-      </c>
-      <c r="W3" t="n">
-        <v>0</v>
-      </c>
-      <c r="X3" t="n">
-        <v>0</v>
       </c>
       <c r="Y3" t="n">
         <v>0</v>
@@ -837,13 +837,13 @@
         <v>0</v>
       </c>
       <c r="V4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X4" s="5" t="n">
         <v>25</v>
-      </c>
-      <c r="W4" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="X4" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="Y4" s="5" t="n">
         <v>0</v>
@@ -916,13 +916,13 @@
         <v>0</v>
       </c>
       <c r="V5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X5" t="n">
         <v>24</v>
-      </c>
-      <c r="W5" t="n">
-        <v>0</v>
-      </c>
-      <c r="X5" t="n">
-        <v>0</v>
       </c>
       <c r="Y5" t="n">
         <v>0</v>
@@ -995,13 +995,13 @@
         <v>0</v>
       </c>
       <c r="V6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="W6" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="X6" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="Y6" s="5" t="n">
         <v>0</v>
@@ -1071,13 +1071,13 @@
         <v>0</v>
       </c>
       <c r="V7" t="n">
+        <v>0</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" t="n">
         <v>24</v>
-      </c>
-      <c r="W7" t="n">
-        <v>0</v>
-      </c>
-      <c r="X7" t="n">
-        <v>0</v>
       </c>
       <c r="Y7" t="n">
         <v>0</v>
@@ -1150,13 +1150,13 @@
         <v>0</v>
       </c>
       <c r="V8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X8" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="W8" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="X8" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="Y8" s="5" t="n">
         <v>0</v>
@@ -1229,13 +1229,13 @@
         <v>0</v>
       </c>
       <c r="V9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X9" t="n">
         <v>24</v>
-      </c>
-      <c r="W9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X9" t="n">
-        <v>0</v>
       </c>
       <c r="Y9" t="n">
         <v>0</v>
@@ -1308,13 +1308,13 @@
         <v>0</v>
       </c>
       <c r="V10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X10" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="W10" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="X10" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="Y10" s="5" t="n">
         <v>0</v>
@@ -1387,13 +1387,13 @@
         <v>0</v>
       </c>
       <c r="V11" t="n">
+        <v>0</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0</v>
+      </c>
+      <c r="X11" t="n">
         <v>24</v>
-      </c>
-      <c r="W11" t="n">
-        <v>0</v>
-      </c>
-      <c r="X11" t="n">
-        <v>0</v>
       </c>
       <c r="Y11" t="n">
         <v>0</v>
@@ -1466,13 +1466,13 @@
         <v>0</v>
       </c>
       <c r="V12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X12" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="W12" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="X12" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="Y12" s="5" t="n">
         <v>0</v>
@@ -1545,13 +1545,13 @@
         <v>0</v>
       </c>
       <c r="V13" t="n">
+        <v>0</v>
+      </c>
+      <c r="W13" t="n">
+        <v>0</v>
+      </c>
+      <c r="X13" t="n">
         <v>24</v>
-      </c>
-      <c r="W13" t="n">
-        <v>0</v>
-      </c>
-      <c r="X13" t="n">
-        <v>0</v>
       </c>
       <c r="Y13" t="n">
         <v>0</v>
@@ -1624,13 +1624,13 @@
         <v>0</v>
       </c>
       <c r="V14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X14" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="W14" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="X14" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="Y14" s="5" t="n">
         <v>0</v>
@@ -1703,13 +1703,13 @@
         <v>0</v>
       </c>
       <c r="V15" t="n">
+        <v>0</v>
+      </c>
+      <c r="W15" t="n">
+        <v>0</v>
+      </c>
+      <c r="X15" t="n">
         <v>24</v>
-      </c>
-      <c r="W15" t="n">
-        <v>0</v>
-      </c>
-      <c r="X15" t="n">
-        <v>0</v>
       </c>
       <c r="Y15" t="n">
         <v>0</v>
@@ -1782,13 +1782,13 @@
         <v>0</v>
       </c>
       <c r="V16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X16" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="W16" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="X16" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="Y16" s="5" t="n">
         <v>0</v>
@@ -1861,13 +1861,13 @@
         <v>0</v>
       </c>
       <c r="V17" t="n">
+        <v>0</v>
+      </c>
+      <c r="W17" t="n">
+        <v>0</v>
+      </c>
+      <c r="X17" t="n">
         <v>24</v>
-      </c>
-      <c r="W17" t="n">
-        <v>0</v>
-      </c>
-      <c r="X17" t="n">
-        <v>0</v>
       </c>
       <c r="Y17" t="n">
         <v>0</v>
@@ -1940,13 +1940,13 @@
         <v>0</v>
       </c>
       <c r="V18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X18" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="W18" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="X18" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="Y18" s="5" t="n">
         <v>0</v>
@@ -2019,13 +2019,13 @@
         <v>0</v>
       </c>
       <c r="V19" t="n">
+        <v>0</v>
+      </c>
+      <c r="W19" t="n">
+        <v>0</v>
+      </c>
+      <c r="X19" t="n">
         <v>24</v>
-      </c>
-      <c r="W19" t="n">
-        <v>0</v>
-      </c>
-      <c r="X19" t="n">
-        <v>0</v>
       </c>
       <c r="Y19" t="n">
         <v>0</v>
@@ -2098,13 +2098,13 @@
         <v>0</v>
       </c>
       <c r="V20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X20" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="W20" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="X20" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="Y20" s="5" t="n">
         <v>0</v>
@@ -2177,13 +2177,13 @@
         <v>0</v>
       </c>
       <c r="V21" t="n">
+        <v>0</v>
+      </c>
+      <c r="W21" t="n">
+        <v>0</v>
+      </c>
+      <c r="X21" t="n">
         <v>24</v>
-      </c>
-      <c r="W21" t="n">
-        <v>0</v>
-      </c>
-      <c r="X21" t="n">
-        <v>0</v>
       </c>
       <c r="Y21" t="n">
         <v>0</v>
@@ -2256,13 +2256,13 @@
         <v>0</v>
       </c>
       <c r="V22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X22" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="W22" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="X22" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="Y22" s="5" t="n">
         <v>0</v>
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="V23" t="n">
+        <v>0</v>
+      </c>
+      <c r="W23" t="n">
+        <v>0</v>
+      </c>
+      <c r="X23" t="n">
         <v>24</v>
-      </c>
-      <c r="W23" t="n">
-        <v>0</v>
-      </c>
-      <c r="X23" t="n">
-        <v>0</v>
       </c>
       <c r="Y23" t="n">
         <v>0</v>
@@ -2414,13 +2414,13 @@
         <v>0</v>
       </c>
       <c r="V24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X24" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="W24" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="X24" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="Y24" s="5" t="n">
         <v>0</v>
@@ -2493,13 +2493,13 @@
         <v>0</v>
       </c>
       <c r="V25" t="n">
+        <v>0</v>
+      </c>
+      <c r="W25" t="n">
+        <v>0</v>
+      </c>
+      <c r="X25" t="n">
         <v>24</v>
-      </c>
-      <c r="W25" t="n">
-        <v>0</v>
-      </c>
-      <c r="X25" t="n">
-        <v>0</v>
       </c>
       <c r="Y25" t="n">
         <v>0</v>
@@ -2572,13 +2572,13 @@
         <v>0</v>
       </c>
       <c r="V26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X26" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="W26" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="X26" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="Y26" s="5" t="n">
         <v>0</v>
@@ -2651,13 +2651,13 @@
         <v>0</v>
       </c>
       <c r="V27" t="n">
+        <v>0</v>
+      </c>
+      <c r="W27" t="n">
+        <v>0</v>
+      </c>
+      <c r="X27" t="n">
         <v>24</v>
-      </c>
-      <c r="W27" t="n">
-        <v>0</v>
-      </c>
-      <c r="X27" t="n">
-        <v>0</v>
       </c>
       <c r="Y27" t="n">
         <v>0</v>
@@ -2809,13 +2809,13 @@
         <v>0</v>
       </c>
       <c r="V29" t="n">
+        <v>0</v>
+      </c>
+      <c r="W29" t="n">
+        <v>0</v>
+      </c>
+      <c r="X29" t="n">
         <v>24</v>
-      </c>
-      <c r="W29" t="n">
-        <v>0</v>
-      </c>
-      <c r="X29" t="n">
-        <v>0</v>
       </c>
       <c r="Y29" t="n">
         <v>0</v>
@@ -2888,13 +2888,13 @@
         <v>0</v>
       </c>
       <c r="V30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X30" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="W30" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="X30" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="Y30" s="5" t="n">
         <v>0</v>
@@ -2967,13 +2967,13 @@
         <v>0</v>
       </c>
       <c r="V31" t="n">
+        <v>0</v>
+      </c>
+      <c r="W31" t="n">
+        <v>0</v>
+      </c>
+      <c r="X31" t="n">
         <v>24</v>
-      </c>
-      <c r="W31" t="n">
-        <v>0</v>
-      </c>
-      <c r="X31" t="n">
-        <v>0</v>
       </c>
       <c r="Y31" t="n">
         <v>0</v>
@@ -3046,13 +3046,13 @@
         <v>0</v>
       </c>
       <c r="V32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X32" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="W32" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="X32" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="Y32" s="5" t="n">
         <v>0</v>
@@ -3125,13 +3125,13 @@
         <v>0</v>
       </c>
       <c r="V33" t="n">
+        <v>0</v>
+      </c>
+      <c r="W33" t="n">
+        <v>0</v>
+      </c>
+      <c r="X33" t="n">
         <v>24</v>
-      </c>
-      <c r="W33" t="n">
-        <v>0</v>
-      </c>
-      <c r="X33" t="n">
-        <v>0</v>
       </c>
       <c r="Y33" t="n">
         <v>0</v>
@@ -3204,13 +3204,13 @@
         <v>0</v>
       </c>
       <c r="V34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X34" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="W34" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="X34" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="Y34" s="5" t="n">
         <v>0</v>
@@ -3283,13 +3283,13 @@
         <v>0</v>
       </c>
       <c r="V35" t="n">
+        <v>0</v>
+      </c>
+      <c r="W35" t="n">
+        <v>0</v>
+      </c>
+      <c r="X35" t="n">
         <v>24</v>
-      </c>
-      <c r="W35" t="n">
-        <v>0</v>
-      </c>
-      <c r="X35" t="n">
-        <v>0</v>
       </c>
       <c r="Y35" t="n">
         <v>0</v>
@@ -3362,13 +3362,13 @@
         <v>0</v>
       </c>
       <c r="V36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X36" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="W36" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="X36" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="Y36" s="5" t="n">
         <v>0</v>
@@ -3441,13 +3441,13 @@
         <v>0</v>
       </c>
       <c r="V37" t="n">
+        <v>0</v>
+      </c>
+      <c r="W37" t="n">
+        <v>0</v>
+      </c>
+      <c r="X37" t="n">
         <v>24</v>
-      </c>
-      <c r="W37" t="n">
-        <v>0</v>
-      </c>
-      <c r="X37" t="n">
-        <v>0</v>
       </c>
       <c r="Y37" t="n">
         <v>0</v>
@@ -3520,13 +3520,13 @@
         <v>0</v>
       </c>
       <c r="V38" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W38" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X38" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="W38" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="X38" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="Y38" s="5" t="n">
         <v>0</v>
@@ -3599,13 +3599,13 @@
         <v>0</v>
       </c>
       <c r="V39" t="n">
+        <v>0</v>
+      </c>
+      <c r="W39" t="n">
+        <v>0</v>
+      </c>
+      <c r="X39" t="n">
         <v>24</v>
-      </c>
-      <c r="W39" t="n">
-        <v>0</v>
-      </c>
-      <c r="X39" t="n">
-        <v>0</v>
       </c>
       <c r="Y39" t="n">
         <v>0</v>
@@ -3678,13 +3678,13 @@
         <v>0</v>
       </c>
       <c r="V40" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W40" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X40" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="W40" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="X40" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="Y40" s="5" t="n">
         <v>0</v>
@@ -3757,13 +3757,13 @@
         <v>0</v>
       </c>
       <c r="V41" t="n">
+        <v>0</v>
+      </c>
+      <c r="W41" t="n">
+        <v>0</v>
+      </c>
+      <c r="X41" t="n">
         <v>24</v>
-      </c>
-      <c r="W41" t="n">
-        <v>0</v>
-      </c>
-      <c r="X41" t="n">
-        <v>0</v>
       </c>
       <c r="Y41" t="n">
         <v>0</v>
@@ -3836,13 +3836,13 @@
         <v>0</v>
       </c>
       <c r="V42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X42" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="W42" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="X42" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="Y42" s="5" t="n">
         <v>0</v>
@@ -3915,13 +3915,13 @@
         <v>0</v>
       </c>
       <c r="V43" t="n">
+        <v>0</v>
+      </c>
+      <c r="W43" t="n">
+        <v>0</v>
+      </c>
+      <c r="X43" t="n">
         <v>24</v>
-      </c>
-      <c r="W43" t="n">
-        <v>0</v>
-      </c>
-      <c r="X43" t="n">
-        <v>0</v>
       </c>
       <c r="Y43" t="n">
         <v>0</v>
@@ -3994,13 +3994,13 @@
         <v>0</v>
       </c>
       <c r="V44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X44" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="W44" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="X44" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="Y44" s="5" t="n">
         <v>0</v>
@@ -4073,13 +4073,13 @@
         <v>0</v>
       </c>
       <c r="V45" t="n">
+        <v>0</v>
+      </c>
+      <c r="W45" t="n">
+        <v>0</v>
+      </c>
+      <c r="X45" t="n">
         <v>24</v>
-      </c>
-      <c r="W45" t="n">
-        <v>0</v>
-      </c>
-      <c r="X45" t="n">
-        <v>0</v>
       </c>
       <c r="Y45" t="n">
         <v>0</v>
@@ -4152,13 +4152,13 @@
         <v>0</v>
       </c>
       <c r="V46" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W46" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X46" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="W46" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="X46" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="Y46" s="5" t="n">
         <v>0</v>
@@ -4231,13 +4231,13 @@
         <v>0</v>
       </c>
       <c r="V47" t="n">
+        <v>0</v>
+      </c>
+      <c r="W47" t="n">
+        <v>0</v>
+      </c>
+      <c r="X47" t="n">
         <v>24</v>
-      </c>
-      <c r="W47" t="n">
-        <v>0</v>
-      </c>
-      <c r="X47" t="n">
-        <v>0</v>
       </c>
       <c r="Y47" t="n">
         <v>0</v>
@@ -4310,13 +4310,13 @@
         <v>0</v>
       </c>
       <c r="V48" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W48" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X48" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="W48" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="X48" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="Y48" s="5" t="n">
         <v>0</v>
@@ -4389,13 +4389,13 @@
         <v>0</v>
       </c>
       <c r="V49" t="n">
+        <v>0</v>
+      </c>
+      <c r="W49" t="n">
+        <v>0</v>
+      </c>
+      <c r="X49" t="n">
         <v>24</v>
-      </c>
-      <c r="W49" t="n">
-        <v>0</v>
-      </c>
-      <c r="X49" t="n">
-        <v>0</v>
       </c>
       <c r="Y49" t="n">
         <v>0</v>
@@ -4468,13 +4468,13 @@
         <v>0</v>
       </c>
       <c r="V50" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W50" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X50" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="W50" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="X50" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="Y50" s="5" t="n">
         <v>0</v>
@@ -4547,13 +4547,13 @@
         <v>0</v>
       </c>
       <c r="V51" t="n">
+        <v>0</v>
+      </c>
+      <c r="W51" t="n">
+        <v>0</v>
+      </c>
+      <c r="X51" t="n">
         <v>24</v>
-      </c>
-      <c r="W51" t="n">
-        <v>0</v>
-      </c>
-      <c r="X51" t="n">
-        <v>0</v>
       </c>
       <c r="Y51" t="n">
         <v>0</v>
@@ -4626,13 +4626,13 @@
         <v>0</v>
       </c>
       <c r="V52" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W52" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X52" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="W52" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="X52" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="Y52" s="5" t="n">
         <v>0</v>
@@ -4705,13 +4705,13 @@
         <v>0</v>
       </c>
       <c r="V53" t="n">
+        <v>0</v>
+      </c>
+      <c r="W53" t="n">
+        <v>0</v>
+      </c>
+      <c r="X53" t="n">
         <v>24</v>
-      </c>
-      <c r="W53" t="n">
-        <v>0</v>
-      </c>
-      <c r="X53" t="n">
-        <v>0</v>
       </c>
       <c r="Y53" t="n">
         <v>0</v>
@@ -4784,13 +4784,13 @@
         <v>0</v>
       </c>
       <c r="V54" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W54" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X54" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="W54" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="X54" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="Y54" s="5" t="n">
         <v>0</v>
@@ -4863,13 +4863,13 @@
         <v>0</v>
       </c>
       <c r="V55" t="n">
+        <v>0</v>
+      </c>
+      <c r="W55" t="n">
+        <v>0</v>
+      </c>
+      <c r="X55" t="n">
         <v>24</v>
-      </c>
-      <c r="W55" t="n">
-        <v>0</v>
-      </c>
-      <c r="X55" t="n">
-        <v>0</v>
       </c>
       <c r="Y55" t="n">
         <v>0</v>
@@ -4942,13 +4942,13 @@
         <v>0</v>
       </c>
       <c r="V56" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W56" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X56" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="W56" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="X56" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="Y56" s="5" t="n">
         <v>0</v>
@@ -5021,13 +5021,13 @@
         <v>0</v>
       </c>
       <c r="V57" t="n">
+        <v>0</v>
+      </c>
+      <c r="W57" t="n">
+        <v>0</v>
+      </c>
+      <c r="X57" t="n">
         <v>24</v>
-      </c>
-      <c r="W57" t="n">
-        <v>0</v>
-      </c>
-      <c r="X57" t="n">
-        <v>0</v>
       </c>
       <c r="Y57" t="n">
         <v>0</v>
@@ -5100,13 +5100,13 @@
         <v>0</v>
       </c>
       <c r="V58" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W58" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X58" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="W58" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="X58" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="Y58" s="5" t="n">
         <v>0</v>
@@ -5179,13 +5179,13 @@
         <v>0</v>
       </c>
       <c r="V59" t="n">
+        <v>0</v>
+      </c>
+      <c r="W59" t="n">
+        <v>0</v>
+      </c>
+      <c r="X59" t="n">
         <v>24</v>
-      </c>
-      <c r="W59" t="n">
-        <v>0</v>
-      </c>
-      <c r="X59" t="n">
-        <v>0</v>
       </c>
       <c r="Y59" t="n">
         <v>0</v>
@@ -5258,13 +5258,13 @@
         <v>0</v>
       </c>
       <c r="V60" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W60" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X60" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="W60" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="X60" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="Y60" s="5" t="n">
         <v>0</v>
@@ -5337,13 +5337,13 @@
         <v>0</v>
       </c>
       <c r="V61" t="n">
+        <v>0</v>
+      </c>
+      <c r="W61" t="n">
+        <v>0</v>
+      </c>
+      <c r="X61" t="n">
         <v>24</v>
-      </c>
-      <c r="W61" t="n">
-        <v>0</v>
-      </c>
-      <c r="X61" t="n">
-        <v>0</v>
       </c>
       <c r="Y61" t="n">
         <v>0</v>
@@ -5416,13 +5416,13 @@
         <v>0</v>
       </c>
       <c r="V62" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W62" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X62" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="W62" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="X62" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="Y62" s="5" t="n">
         <v>0</v>
@@ -5495,13 +5495,13 @@
         <v>0</v>
       </c>
       <c r="V63" t="n">
+        <v>0</v>
+      </c>
+      <c r="W63" t="n">
+        <v>0</v>
+      </c>
+      <c r="X63" t="n">
         <v>24</v>
-      </c>
-      <c r="W63" t="n">
-        <v>0</v>
-      </c>
-      <c r="X63" t="n">
-        <v>0</v>
       </c>
       <c r="Y63" t="n">
         <v>0</v>
@@ -5574,13 +5574,13 @@
         <v>0</v>
       </c>
       <c r="V64" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W64" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X64" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="W64" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="X64" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="Y64" s="5" t="n">
         <v>0</v>
@@ -5653,13 +5653,13 @@
         <v>0</v>
       </c>
       <c r="V65" t="n">
+        <v>0</v>
+      </c>
+      <c r="W65" t="n">
+        <v>0</v>
+      </c>
+      <c r="X65" t="n">
         <v>24</v>
-      </c>
-      <c r="W65" t="n">
-        <v>0</v>
-      </c>
-      <c r="X65" t="n">
-        <v>0</v>
       </c>
       <c r="Y65" t="n">
         <v>0</v>
@@ -5732,13 +5732,13 @@
         <v>0</v>
       </c>
       <c r="V66" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W66" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X66" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="W66" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="X66" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="Y66" s="5" t="n">
         <v>0</v>
@@ -5810,10 +5810,10 @@
       <c r="U67" t="n">
         <v>0</v>
       </c>
+      <c r="V67" t="n">
+        <v>0</v>
+      </c>
       <c r="W67" t="n">
-        <v>0</v>
-      </c>
-      <c r="X67" t="n">
         <v>0</v>
       </c>
       <c r="Y67" t="n">
@@ -5887,13 +5887,13 @@
         <v>0</v>
       </c>
       <c r="V68" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W68" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X68" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="W68" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="X68" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="Y68" s="5" t="n">
         <v>0</v>
@@ -5962,10 +5962,10 @@
       <c r="U69" t="n">
         <v>0</v>
       </c>
+      <c r="V69" t="n">
+        <v>0</v>
+      </c>
       <c r="W69" t="n">
-        <v>0</v>
-      </c>
-      <c r="X69" t="n">
         <v>0</v>
       </c>
       <c r="Y69" t="n">
@@ -6039,13 +6039,13 @@
         <v>0</v>
       </c>
       <c r="V70" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W70" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X70" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="W70" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="X70" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="Y70" s="5" t="n">
         <v>0</v>
@@ -6118,13 +6118,13 @@
         <v>0</v>
       </c>
       <c r="V71" t="n">
+        <v>0</v>
+      </c>
+      <c r="W71" t="n">
+        <v>0</v>
+      </c>
+      <c r="X71" t="n">
         <v>24</v>
-      </c>
-      <c r="W71" t="n">
-        <v>0</v>
-      </c>
-      <c r="X71" t="n">
-        <v>0</v>
       </c>
       <c r="Y71" t="n">
         <v>0</v>
@@ -6197,13 +6197,13 @@
         <v>0</v>
       </c>
       <c r="V72" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W72" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X72" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="W72" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="X72" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="Y72" s="5" t="n">
         <v>0</v>
@@ -6276,13 +6276,13 @@
         <v>0</v>
       </c>
       <c r="V73" t="n">
+        <v>0</v>
+      </c>
+      <c r="W73" t="n">
+        <v>0</v>
+      </c>
+      <c r="X73" t="n">
         <v>24</v>
-      </c>
-      <c r="W73" t="n">
-        <v>0</v>
-      </c>
-      <c r="X73" t="n">
-        <v>0</v>
       </c>
       <c r="Y73" t="n">
         <v>0</v>
@@ -6355,13 +6355,13 @@
         <v>0</v>
       </c>
       <c r="V74" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W74" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X74" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="W74" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="X74" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="Y74" s="5" t="n">
         <v>0</v>
@@ -6434,13 +6434,13 @@
         <v>0</v>
       </c>
       <c r="V75" t="n">
+        <v>0</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0</v>
+      </c>
+      <c r="X75" t="n">
         <v>24</v>
-      </c>
-      <c r="W75" t="n">
-        <v>0</v>
-      </c>
-      <c r="X75" t="n">
-        <v>0</v>
       </c>
       <c r="Y75" t="n">
         <v>0</v>
@@ -6498,9 +6498,7 @@
       <c r="Q76" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="R76" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="R76" s="5" t="n"/>
       <c r="S76" s="5" t="n">
         <v>0</v>
       </c>
@@ -6511,12 +6509,14 @@
         <v>0</v>
       </c>
       <c r="V76" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W76" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X76" s="5" t="n">
         <v>24</v>
       </c>
-      <c r="W76" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="X76" s="5" t="n"/>
       <c r="Y76" s="5" t="n">
         <v>0</v>
       </c>
@@ -6587,10 +6587,10 @@
       <c r="U77" t="n">
         <v>0</v>
       </c>
+      <c r="V77" t="n">
+        <v>0</v>
+      </c>
       <c r="W77" t="n">
-        <v>0</v>
-      </c>
-      <c r="X77" t="n">
         <v>0</v>
       </c>
       <c r="Y77" t="n">
@@ -6664,13 +6664,13 @@
         <v>0</v>
       </c>
       <c r="V78" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W78" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X78" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="W78" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="X78" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="Y78" s="5" t="n">
         <v>0</v>
@@ -6742,10 +6742,10 @@
       <c r="U79" t="n">
         <v>0</v>
       </c>
+      <c r="V79" t="n">
+        <v>0</v>
+      </c>
       <c r="W79" t="n">
-        <v>0</v>
-      </c>
-      <c r="X79" t="n">
         <v>0</v>
       </c>
       <c r="Y79" t="n">
@@ -6818,13 +6818,13 @@
       <c r="U80" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="V80" s="5" t="n"/>
+      <c r="V80" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="W80" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="X80" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="X80" s="5" t="n"/>
       <c r="Y80" s="5" t="n">
         <v>0</v>
       </c>
@@ -6896,13 +6896,13 @@
         <v>0</v>
       </c>
       <c r="V81" t="n">
+        <v>0</v>
+      </c>
+      <c r="W81" t="n">
+        <v>0</v>
+      </c>
+      <c r="X81" t="n">
         <v>24</v>
-      </c>
-      <c r="W81" t="n">
-        <v>0</v>
-      </c>
-      <c r="X81" t="n">
-        <v>0</v>
       </c>
       <c r="Y81" t="n">
         <v>0</v>
@@ -6974,13 +6974,13 @@
       <c r="U82" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="V82" s="5" t="n"/>
+      <c r="V82" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="W82" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="X82" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="X82" s="5" t="n"/>
       <c r="Y82" s="5" t="n">
         <v>0</v>
       </c>
@@ -7049,13 +7049,13 @@
         <v>0</v>
       </c>
       <c r="V83" t="n">
+        <v>0</v>
+      </c>
+      <c r="W83" t="n">
+        <v>0</v>
+      </c>
+      <c r="X83" t="n">
         <v>24</v>
-      </c>
-      <c r="W83" t="n">
-        <v>0</v>
-      </c>
-      <c r="X83" t="n">
-        <v>0</v>
       </c>
       <c r="Y83" t="n">
         <v>0</v>
@@ -7128,13 +7128,13 @@
         <v>0</v>
       </c>
       <c r="V84" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W84" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X84" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="W84" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="X84" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="Y84" s="5" t="n">
         <v>0</v>
@@ -7206,10 +7206,10 @@
       <c r="U85" t="n">
         <v>0</v>
       </c>
+      <c r="V85" t="n">
+        <v>0</v>
+      </c>
       <c r="W85" t="n">
-        <v>0</v>
-      </c>
-      <c r="X85" t="n">
         <v>0</v>
       </c>
       <c r="Y85" t="n">
@@ -7282,13 +7282,13 @@
       <c r="U86" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="V86" s="5" t="n"/>
+      <c r="V86" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="W86" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="X86" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="X86" s="5" t="n"/>
       <c r="Y86" s="5" t="n">
         <v>0</v>
       </c>
@@ -7359,10 +7359,10 @@
       <c r="U87" t="n">
         <v>0</v>
       </c>
+      <c r="V87" t="n">
+        <v>0</v>
+      </c>
       <c r="W87" t="n">
-        <v>0</v>
-      </c>
-      <c r="X87" t="n">
         <v>0</v>
       </c>
       <c r="Y87" t="n">
@@ -7435,13 +7435,13 @@
       <c r="U88" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="V88" s="5" t="n"/>
+      <c r="V88" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="W88" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="X88" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="X88" s="5" t="n"/>
       <c r="Y88" s="5" t="n">
         <v>0</v>
       </c>
@@ -7512,10 +7512,10 @@
       <c r="U89" t="n">
         <v>0</v>
       </c>
+      <c r="V89" t="n">
+        <v>0</v>
+      </c>
       <c r="W89" t="n">
-        <v>0</v>
-      </c>
-      <c r="X89" t="n">
         <v>0</v>
       </c>
       <c r="Y89" t="n">
@@ -7587,13 +7587,13 @@
         <v>0</v>
       </c>
       <c r="V90" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W90" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X90" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="W90" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="X90" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="Y90" s="5" t="n">
         <v>0</v>
@@ -7665,10 +7665,10 @@
       <c r="U91" t="n">
         <v>0</v>
       </c>
+      <c r="V91" t="n">
+        <v>0</v>
+      </c>
       <c r="W91" t="n">
-        <v>0</v>
-      </c>
-      <c r="X91" t="n">
         <v>0</v>
       </c>
       <c r="Y91" t="n">
@@ -7741,13 +7741,13 @@
       <c r="U92" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="V92" s="5" t="n"/>
+      <c r="V92" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="W92" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="X92" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="X92" s="5" t="n"/>
       <c r="Y92" s="5" t="n">
         <v>0</v>
       </c>
@@ -7818,10 +7818,10 @@
       <c r="U93" t="n">
         <v>0</v>
       </c>
+      <c r="V93" t="n">
+        <v>0</v>
+      </c>
       <c r="W93" t="n">
-        <v>0</v>
-      </c>
-      <c r="X93" t="n">
         <v>0</v>
       </c>
       <c r="Y93" t="n">
@@ -7894,13 +7894,13 @@
       <c r="U94" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="V94" s="5" t="n"/>
+      <c r="V94" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="W94" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="X94" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="X94" s="5" t="n"/>
       <c r="Y94" s="5" t="n">
         <v>0</v>
       </c>
@@ -7971,10 +7971,10 @@
       <c r="U95" t="n">
         <v>0</v>
       </c>
+      <c r="V95" t="n">
+        <v>0</v>
+      </c>
       <c r="W95" t="n">
-        <v>0</v>
-      </c>
-      <c r="X95" t="n">
         <v>0</v>
       </c>
       <c r="Y95" t="n">
@@ -8047,13 +8047,13 @@
       <c r="U96" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="V96" s="5" t="n"/>
+      <c r="V96" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="W96" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="X96" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="X96" s="5" t="n"/>
       <c r="Y96" s="5" t="n">
         <v>0</v>
       </c>
@@ -8121,10 +8121,10 @@
       <c r="U97" t="n">
         <v>0</v>
       </c>
+      <c r="V97" t="n">
+        <v>0</v>
+      </c>
       <c r="W97" t="n">
-        <v>0</v>
-      </c>
-      <c r="X97" t="n">
         <v>0</v>
       </c>
       <c r="Y97" t="n">
@@ -8197,13 +8197,13 @@
       <c r="U98" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="V98" s="5" t="n"/>
+      <c r="V98" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="W98" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="X98" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="X98" s="5" t="n"/>
       <c r="Y98" s="5" t="n">
         <v>0</v>
       </c>
@@ -8274,10 +8274,10 @@
       <c r="U99" t="n">
         <v>0</v>
       </c>
+      <c r="V99" t="n">
+        <v>0</v>
+      </c>
       <c r="W99" t="n">
-        <v>0</v>
-      </c>
-      <c r="X99" t="n">
         <v>0</v>
       </c>
       <c r="Y99" t="n">
@@ -8350,13 +8350,13 @@
       <c r="U100" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="V100" s="5" t="n"/>
+      <c r="V100" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="W100" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="X100" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="X100" s="5" t="n"/>
       <c r="Y100" s="5" t="n">
         <v>0</v>
       </c>
@@ -8427,10 +8427,10 @@
       <c r="U101" t="n">
         <v>0</v>
       </c>
+      <c r="V101" t="n">
+        <v>0</v>
+      </c>
       <c r="W101" t="n">
-        <v>0</v>
-      </c>
-      <c r="X101" t="n">
         <v>0</v>
       </c>
       <c r="Y101" t="n">
@@ -8503,13 +8503,13 @@
       <c r="U102" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="V102" s="5" t="n"/>
+      <c r="V102" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="W102" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="X102" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="X102" s="5" t="n"/>
       <c r="Y102" s="5" t="n">
         <v>0</v>
       </c>
@@ -8580,10 +8580,10 @@
       <c r="U103" t="n">
         <v>0</v>
       </c>
+      <c r="V103" t="n">
+        <v>0</v>
+      </c>
       <c r="W103" t="n">
-        <v>0</v>
-      </c>
-      <c r="X103" t="n">
         <v>0</v>
       </c>
       <c r="Y103" t="n">
@@ -8656,13 +8656,13 @@
       <c r="U104" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="V104" s="5" t="n"/>
+      <c r="V104" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="W104" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="X104" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="X104" s="5" t="n"/>
       <c r="Y104" s="5" t="n">
         <v>0</v>
       </c>
@@ -8733,13 +8733,90 @@
       <c r="U105" t="n">
         <v>0</v>
       </c>
+      <c r="V105" t="n">
+        <v>0</v>
+      </c>
       <c r="W105" t="n">
         <v>0</v>
       </c>
-      <c r="X105" t="n">
-        <v>0</v>
-      </c>
       <c r="Y105" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B106" s="5" t="n">
+        <v>920</v>
+      </c>
+      <c r="C106" s="5" t="n">
+        <v>480</v>
+      </c>
+      <c r="D106" s="5" t="n">
+        <v>399</v>
+      </c>
+      <c r="E106" s="5" t="n">
+        <v>284</v>
+      </c>
+      <c r="F106" s="5" t="n">
+        <v>217</v>
+      </c>
+      <c r="G106" s="5" t="n">
+        <v>123</v>
+      </c>
+      <c r="H106" s="5" t="n">
+        <v>101</v>
+      </c>
+      <c r="I106" s="5" t="n">
+        <v>42</v>
+      </c>
+      <c r="J106" s="5" t="n">
+        <v>26</v>
+      </c>
+      <c r="K106" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L106" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M106" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N106" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O106" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P106" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q106" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R106" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S106" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T106" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U106" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V106" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W106" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X106" s="5" t="n"/>
+      <c r="Y106" s="5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8781,7 +8858,7 @@
       </c>
       <c r="D1" s="3" t="inlineStr">
         <is>
-          <t>Lager (2026-10-19)</t>
+          <t>Lager (2026-10-20)</t>
         </is>
       </c>
     </row>
@@ -8802,7 +8879,7 @@
         </is>
       </c>
       <c r="D2" s="4" t="n">
-        <v>493</v>
+        <v>480</v>
       </c>
     </row>
     <row r="3">
@@ -17142,7 +17219,7 @@
         </is>
       </c>
       <c r="D419" s="6" t="n">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="420">
@@ -17222,7 +17299,7 @@
         </is>
       </c>
       <c r="D423" s="6" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="424">
@@ -26302,7 +26379,7 @@
         </is>
       </c>
       <c r="D877" s="6" t="n">
-        <v>216</v>
+        <v>210</v>
       </c>
     </row>
     <row r="878">
@@ -26742,7 +26819,7 @@
         </is>
       </c>
       <c r="D899" s="6" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
     </row>
     <row r="900">
@@ -28162,7 +28239,7 @@
         </is>
       </c>
       <c r="D970" s="4" t="n">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="971">
@@ -28182,7 +28259,7 @@
         </is>
       </c>
       <c r="D971" s="6" t="n">
-        <v>188</v>
+        <v>177</v>
       </c>
     </row>
     <row r="972">
@@ -32122,7 +32199,7 @@
         </is>
       </c>
       <c r="D1168" s="4" t="n">
-        <v>39</v>
+        <v>33</v>
       </c>
     </row>
     <row r="1169">
@@ -32182,7 +32259,7 @@
         </is>
       </c>
       <c r="D1171" s="6" t="n">
-        <v>463</v>
+        <v>492</v>
       </c>
     </row>
     <row r="1172">
@@ -32202,7 +32279,7 @@
         </is>
       </c>
       <c r="D1172" s="4" t="n">
-        <v>340</v>
+        <v>335</v>
       </c>
     </row>
   </sheetData>

--- a/data/ahlsell_led_panel_inventory.xlsx
+++ b/data/ahlsell_led_panel_inventory.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y107"/>
+  <dimension ref="A1:Y108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -538,77 +538,77 @@
       </c>
       <c r="K1" s="3" t="inlineStr">
         <is>
+          <t>Philips</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="inlineStr">
+        <is>
+          <t>Bergdahls</t>
+        </is>
+      </c>
+      <c r="M1" s="3" t="inlineStr">
+        <is>
+          <t>THORN</t>
+        </is>
+      </c>
+      <c r="N1" s="3" t="inlineStr">
+        <is>
+          <t>Westal</t>
+        </is>
+      </c>
+      <c r="O1" s="3" t="inlineStr">
+        <is>
+          <t>Ensto</t>
+        </is>
+      </c>
+      <c r="P1" s="3" t="inlineStr">
+        <is>
+          <t>Norwesco</t>
+        </is>
+      </c>
+      <c r="Q1" s="3" t="inlineStr">
+        <is>
+          <t>ANETA LIGHTING</t>
+        </is>
+      </c>
+      <c r="R1" s="3" t="inlineStr">
+        <is>
+          <t>Nokalux</t>
+        </is>
+      </c>
+      <c r="S1" s="3" t="inlineStr">
+        <is>
+          <t>Airam</t>
+        </is>
+      </c>
+      <c r="T1" s="3" t="inlineStr">
+        <is>
+          <t>ZG Lighting</t>
+        </is>
+      </c>
+      <c r="U1" s="3" t="inlineStr">
+        <is>
+          <t>Siteco</t>
+        </is>
+      </c>
+      <c r="V1" s="3" t="inlineStr">
+        <is>
+          <t>Legrand</t>
+        </is>
+      </c>
+      <c r="W1" s="3" t="inlineStr">
+        <is>
           <t>Esylux</t>
         </is>
       </c>
-      <c r="L1" s="3" t="inlineStr">
-        <is>
-          <t>Ensto</t>
-        </is>
-      </c>
-      <c r="M1" s="3" t="inlineStr">
-        <is>
-          <t>ANETA LIGHTING</t>
-        </is>
-      </c>
-      <c r="N1" s="3" t="inlineStr">
+      <c r="X1" s="3" t="inlineStr">
         <is>
           <t>Easyform</t>
         </is>
       </c>
-      <c r="O1" s="3" t="inlineStr">
+      <c r="Y1" s="3" t="inlineStr">
         <is>
           <t>Black Box</t>
-        </is>
-      </c>
-      <c r="P1" s="3" t="inlineStr">
-        <is>
-          <t>ZG Lighting</t>
-        </is>
-      </c>
-      <c r="Q1" s="3" t="inlineStr">
-        <is>
-          <t>Airam</t>
-        </is>
-      </c>
-      <c r="R1" s="3" t="inlineStr">
-        <is>
-          <t>THORN</t>
-        </is>
-      </c>
-      <c r="S1" s="3" t="inlineStr">
-        <is>
-          <t>Nokalux</t>
-        </is>
-      </c>
-      <c r="T1" s="3" t="inlineStr">
-        <is>
-          <t>Bergdahls</t>
-        </is>
-      </c>
-      <c r="U1" s="3" t="inlineStr">
-        <is>
-          <t>Philips</t>
-        </is>
-      </c>
-      <c r="V1" s="3" t="inlineStr">
-        <is>
-          <t>Norwesco</t>
-        </is>
-      </c>
-      <c r="W1" s="3" t="inlineStr">
-        <is>
-          <t>Westal</t>
-        </is>
-      </c>
-      <c r="X1" s="3" t="inlineStr">
-        <is>
-          <t>Legrand</t>
-        </is>
-      </c>
-      <c r="Y1" s="3" t="inlineStr">
-        <is>
-          <t>Siteco</t>
         </is>
       </c>
     </row>
@@ -646,43 +646,43 @@
         <v>33</v>
       </c>
       <c r="K2" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q2" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R2" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S2" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T2" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U2" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V2" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W2" s="5" t="n">
         <v>25</v>
-      </c>
-      <c r="L2" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M2" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N2" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O2" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P2" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q2" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R2" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S2" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T2" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U2" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V2" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W2" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="X2" s="5" t="n">
         <v>0</v>
@@ -725,43 +725,43 @@
         <v>33</v>
       </c>
       <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W3" t="n">
         <v>25</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S3" t="n">
-        <v>0</v>
-      </c>
-      <c r="T3" t="n">
-        <v>0</v>
-      </c>
-      <c r="U3" t="n">
-        <v>0</v>
-      </c>
-      <c r="V3" t="n">
-        <v>0</v>
-      </c>
-      <c r="W3" t="n">
-        <v>0</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
@@ -804,43 +804,43 @@
         <v>33</v>
       </c>
       <c r="K4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W4" s="5" t="n">
         <v>25</v>
-      </c>
-      <c r="L4" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M4" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O4" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q4" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R4" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S4" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T4" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U4" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V4" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W4" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="X4" s="5" t="n">
         <v>0</v>
@@ -883,43 +883,43 @@
         <v>33</v>
       </c>
       <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W5" t="n">
         <v>24</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W5" t="n">
-        <v>0</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
@@ -962,43 +962,43 @@
         <v>33</v>
       </c>
       <c r="K6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W6" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="L6" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R6" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S6" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T6" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U6" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V6" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W6" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="X6" s="5" t="n">
         <v>0</v>
@@ -1038,43 +1038,43 @@
         <v>33</v>
       </c>
       <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0</v>
+      </c>
+      <c r="W7" t="n">
         <v>24</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>0</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="n">
-        <v>0</v>
-      </c>
-      <c r="T7" t="n">
-        <v>0</v>
-      </c>
-      <c r="U7" t="n">
-        <v>0</v>
-      </c>
-      <c r="V7" t="n">
-        <v>0</v>
-      </c>
-      <c r="W7" t="n">
-        <v>0</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
@@ -1117,43 +1117,43 @@
         <v>33</v>
       </c>
       <c r="K8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W8" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="L8" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R8" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T8" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U8" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V8" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W8" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="X8" s="5" t="n">
         <v>0</v>
@@ -1196,43 +1196,43 @@
         <v>33</v>
       </c>
       <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W9" t="n">
         <v>24</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>0</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W9" t="n">
-        <v>0</v>
       </c>
       <c r="X9" t="n">
         <v>0</v>
@@ -1275,43 +1275,43 @@
         <v>33</v>
       </c>
       <c r="K10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W10" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="L10" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R10" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T10" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U10" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V10" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W10" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="X10" s="5" t="n">
         <v>0</v>
@@ -1354,43 +1354,43 @@
         <v>33</v>
       </c>
       <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" t="n">
+        <v>0</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" t="n">
+        <v>0</v>
+      </c>
+      <c r="W11" t="n">
         <v>24</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>0</v>
-      </c>
-      <c r="R11" t="n">
-        <v>0</v>
-      </c>
-      <c r="S11" t="n">
-        <v>0</v>
-      </c>
-      <c r="T11" t="n">
-        <v>0</v>
-      </c>
-      <c r="U11" t="n">
-        <v>0</v>
-      </c>
-      <c r="V11" t="n">
-        <v>0</v>
-      </c>
-      <c r="W11" t="n">
-        <v>0</v>
       </c>
       <c r="X11" t="n">
         <v>0</v>
@@ -1433,43 +1433,43 @@
         <v>33</v>
       </c>
       <c r="K12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W12" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="L12" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R12" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T12" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U12" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V12" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W12" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="X12" s="5" t="n">
         <v>0</v>
@@ -1512,43 +1512,43 @@
         <v>33</v>
       </c>
       <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0</v>
+      </c>
+      <c r="T13" t="n">
+        <v>0</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" t="n">
+        <v>0</v>
+      </c>
+      <c r="W13" t="n">
         <v>24</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>0</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" t="n">
-        <v>0</v>
-      </c>
-      <c r="T13" t="n">
-        <v>0</v>
-      </c>
-      <c r="U13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V13" t="n">
-        <v>0</v>
-      </c>
-      <c r="W13" t="n">
-        <v>0</v>
       </c>
       <c r="X13" t="n">
         <v>0</v>
@@ -1591,43 +1591,43 @@
         <v>33</v>
       </c>
       <c r="K14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W14" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="L14" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R14" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S14" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T14" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U14" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V14" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W14" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="X14" s="5" t="n">
         <v>0</v>
@@ -1670,43 +1670,43 @@
         <v>33</v>
       </c>
       <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" t="n">
+        <v>0</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0</v>
+      </c>
+      <c r="W15" t="n">
         <v>24</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>0</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" t="n">
-        <v>0</v>
-      </c>
-      <c r="T15" t="n">
-        <v>0</v>
-      </c>
-      <c r="U15" t="n">
-        <v>0</v>
-      </c>
-      <c r="V15" t="n">
-        <v>0</v>
-      </c>
-      <c r="W15" t="n">
-        <v>0</v>
       </c>
       <c r="X15" t="n">
         <v>0</v>
@@ -1749,43 +1749,43 @@
         <v>33</v>
       </c>
       <c r="K16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W16" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="L16" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R16" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S16" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T16" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U16" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V16" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W16" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="X16" s="5" t="n">
         <v>0</v>
@@ -1828,43 +1828,43 @@
         <v>33</v>
       </c>
       <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0</v>
+      </c>
+      <c r="T17" t="n">
+        <v>0</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" t="n">
+        <v>0</v>
+      </c>
+      <c r="W17" t="n">
         <v>24</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>0</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" t="n">
-        <v>0</v>
-      </c>
-      <c r="T17" t="n">
-        <v>0</v>
-      </c>
-      <c r="U17" t="n">
-        <v>0</v>
-      </c>
-      <c r="V17" t="n">
-        <v>0</v>
-      </c>
-      <c r="W17" t="n">
-        <v>0</v>
       </c>
       <c r="X17" t="n">
         <v>0</v>
@@ -1907,43 +1907,43 @@
         <v>33</v>
       </c>
       <c r="K18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W18" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="L18" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R18" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S18" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T18" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U18" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V18" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W18" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="X18" s="5" t="n">
         <v>0</v>
@@ -1986,43 +1986,43 @@
         <v>33</v>
       </c>
       <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0</v>
+      </c>
+      <c r="T19" t="n">
+        <v>0</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" t="n">
+        <v>0</v>
+      </c>
+      <c r="W19" t="n">
         <v>24</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>0</v>
-      </c>
-      <c r="R19" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" t="n">
-        <v>0</v>
-      </c>
-      <c r="T19" t="n">
-        <v>0</v>
-      </c>
-      <c r="U19" t="n">
-        <v>0</v>
-      </c>
-      <c r="V19" t="n">
-        <v>0</v>
-      </c>
-      <c r="W19" t="n">
-        <v>0</v>
       </c>
       <c r="X19" t="n">
         <v>0</v>
@@ -2065,43 +2065,43 @@
         <v>33</v>
       </c>
       <c r="K20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W20" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="L20" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M20" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O20" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q20" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R20" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S20" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T20" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U20" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V20" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W20" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="X20" s="5" t="n">
         <v>0</v>
@@ -2144,43 +2144,43 @@
         <v>33</v>
       </c>
       <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>0</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" t="n">
+        <v>0</v>
+      </c>
+      <c r="T21" t="n">
+        <v>0</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0</v>
+      </c>
+      <c r="V21" t="n">
+        <v>0</v>
+      </c>
+      <c r="W21" t="n">
         <v>24</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" t="n">
-        <v>0</v>
-      </c>
-      <c r="O21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>0</v>
-      </c>
-      <c r="R21" t="n">
-        <v>0</v>
-      </c>
-      <c r="S21" t="n">
-        <v>0</v>
-      </c>
-      <c r="T21" t="n">
-        <v>0</v>
-      </c>
-      <c r="U21" t="n">
-        <v>0</v>
-      </c>
-      <c r="V21" t="n">
-        <v>0</v>
-      </c>
-      <c r="W21" t="n">
-        <v>0</v>
       </c>
       <c r="X21" t="n">
         <v>0</v>
@@ -2223,43 +2223,43 @@
         <v>33</v>
       </c>
       <c r="K22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W22" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="L22" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M22" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N22" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O22" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q22" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R22" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S22" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T22" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U22" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V22" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W22" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="X22" s="5" t="n">
         <v>0</v>
@@ -2302,43 +2302,43 @@
         <v>33</v>
       </c>
       <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>0</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0</v>
+      </c>
+      <c r="S23" t="n">
+        <v>0</v>
+      </c>
+      <c r="T23" t="n">
+        <v>0</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0</v>
+      </c>
+      <c r="V23" t="n">
+        <v>0</v>
+      </c>
+      <c r="W23" t="n">
         <v>24</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
-      <c r="M23" t="n">
-        <v>0</v>
-      </c>
-      <c r="N23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>0</v>
-      </c>
-      <c r="R23" t="n">
-        <v>0</v>
-      </c>
-      <c r="S23" t="n">
-        <v>0</v>
-      </c>
-      <c r="T23" t="n">
-        <v>0</v>
-      </c>
-      <c r="U23" t="n">
-        <v>0</v>
-      </c>
-      <c r="V23" t="n">
-        <v>0</v>
-      </c>
-      <c r="W23" t="n">
-        <v>0</v>
       </c>
       <c r="X23" t="n">
         <v>0</v>
@@ -2381,43 +2381,43 @@
         <v>33</v>
       </c>
       <c r="K24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W24" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="L24" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M24" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N24" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O24" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P24" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q24" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R24" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S24" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T24" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U24" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V24" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W24" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="X24" s="5" t="n">
         <v>0</v>
@@ -2460,43 +2460,43 @@
         <v>33</v>
       </c>
       <c r="K25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>0</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0</v>
+      </c>
+      <c r="S25" t="n">
+        <v>0</v>
+      </c>
+      <c r="T25" t="n">
+        <v>0</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0</v>
+      </c>
+      <c r="V25" t="n">
+        <v>0</v>
+      </c>
+      <c r="W25" t="n">
         <v>24</v>
-      </c>
-      <c r="L25" t="n">
-        <v>0</v>
-      </c>
-      <c r="M25" t="n">
-        <v>0</v>
-      </c>
-      <c r="N25" t="n">
-        <v>0</v>
-      </c>
-      <c r="O25" t="n">
-        <v>0</v>
-      </c>
-      <c r="P25" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>0</v>
-      </c>
-      <c r="R25" t="n">
-        <v>0</v>
-      </c>
-      <c r="S25" t="n">
-        <v>0</v>
-      </c>
-      <c r="T25" t="n">
-        <v>0</v>
-      </c>
-      <c r="U25" t="n">
-        <v>0</v>
-      </c>
-      <c r="V25" t="n">
-        <v>0</v>
-      </c>
-      <c r="W25" t="n">
-        <v>0</v>
       </c>
       <c r="X25" t="n">
         <v>0</v>
@@ -2539,43 +2539,43 @@
         <v>33</v>
       </c>
       <c r="K26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W26" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="L26" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M26" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N26" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O26" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P26" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q26" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R26" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S26" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T26" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U26" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V26" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W26" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="X26" s="5" t="n">
         <v>0</v>
@@ -2618,43 +2618,43 @@
         <v>33</v>
       </c>
       <c r="K27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>0</v>
+      </c>
+      <c r="R27" t="n">
+        <v>0</v>
+      </c>
+      <c r="S27" t="n">
+        <v>0</v>
+      </c>
+      <c r="T27" t="n">
+        <v>0</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0</v>
+      </c>
+      <c r="V27" t="n">
+        <v>0</v>
+      </c>
+      <c r="W27" t="n">
         <v>24</v>
-      </c>
-      <c r="L27" t="n">
-        <v>0</v>
-      </c>
-      <c r="M27" t="n">
-        <v>0</v>
-      </c>
-      <c r="N27" t="n">
-        <v>0</v>
-      </c>
-      <c r="O27" t="n">
-        <v>0</v>
-      </c>
-      <c r="P27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>0</v>
-      </c>
-      <c r="R27" t="n">
-        <v>0</v>
-      </c>
-      <c r="S27" t="n">
-        <v>0</v>
-      </c>
-      <c r="T27" t="n">
-        <v>0</v>
-      </c>
-      <c r="U27" t="n">
-        <v>0</v>
-      </c>
-      <c r="V27" t="n">
-        <v>0</v>
-      </c>
-      <c r="W27" t="n">
-        <v>0</v>
       </c>
       <c r="X27" t="n">
         <v>0</v>
@@ -2776,43 +2776,43 @@
         <v>33</v>
       </c>
       <c r="K29" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>0</v>
+      </c>
+      <c r="R29" t="n">
+        <v>0</v>
+      </c>
+      <c r="S29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T29" t="n">
+        <v>0</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0</v>
+      </c>
+      <c r="V29" t="n">
+        <v>0</v>
+      </c>
+      <c r="W29" t="n">
         <v>24</v>
-      </c>
-      <c r="L29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M29" t="n">
-        <v>0</v>
-      </c>
-      <c r="N29" t="n">
-        <v>0</v>
-      </c>
-      <c r="O29" t="n">
-        <v>0</v>
-      </c>
-      <c r="P29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>0</v>
-      </c>
-      <c r="R29" t="n">
-        <v>0</v>
-      </c>
-      <c r="S29" t="n">
-        <v>0</v>
-      </c>
-      <c r="T29" t="n">
-        <v>0</v>
-      </c>
-      <c r="U29" t="n">
-        <v>0</v>
-      </c>
-      <c r="V29" t="n">
-        <v>0</v>
-      </c>
-      <c r="W29" t="n">
-        <v>0</v>
       </c>
       <c r="X29" t="n">
         <v>0</v>
@@ -2855,43 +2855,43 @@
         <v>33</v>
       </c>
       <c r="K30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W30" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="L30" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M30" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N30" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O30" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P30" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q30" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R30" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S30" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T30" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U30" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V30" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W30" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="X30" s="5" t="n">
         <v>0</v>
@@ -2934,43 +2934,43 @@
         <v>33</v>
       </c>
       <c r="K31" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" t="n">
+        <v>0</v>
+      </c>
+      <c r="N31" t="n">
+        <v>0</v>
+      </c>
+      <c r="O31" t="n">
+        <v>0</v>
+      </c>
+      <c r="P31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>0</v>
+      </c>
+      <c r="R31" t="n">
+        <v>0</v>
+      </c>
+      <c r="S31" t="n">
+        <v>0</v>
+      </c>
+      <c r="T31" t="n">
+        <v>0</v>
+      </c>
+      <c r="U31" t="n">
+        <v>0</v>
+      </c>
+      <c r="V31" t="n">
+        <v>0</v>
+      </c>
+      <c r="W31" t="n">
         <v>24</v>
-      </c>
-      <c r="L31" t="n">
-        <v>0</v>
-      </c>
-      <c r="M31" t="n">
-        <v>0</v>
-      </c>
-      <c r="N31" t="n">
-        <v>0</v>
-      </c>
-      <c r="O31" t="n">
-        <v>0</v>
-      </c>
-      <c r="P31" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>0</v>
-      </c>
-      <c r="R31" t="n">
-        <v>0</v>
-      </c>
-      <c r="S31" t="n">
-        <v>0</v>
-      </c>
-      <c r="T31" t="n">
-        <v>0</v>
-      </c>
-      <c r="U31" t="n">
-        <v>0</v>
-      </c>
-      <c r="V31" t="n">
-        <v>0</v>
-      </c>
-      <c r="W31" t="n">
-        <v>0</v>
       </c>
       <c r="X31" t="n">
         <v>0</v>
@@ -3013,43 +3013,43 @@
         <v>33</v>
       </c>
       <c r="K32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W32" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="L32" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M32" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N32" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O32" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P32" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q32" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R32" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S32" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T32" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U32" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V32" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W32" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="X32" s="5" t="n">
         <v>0</v>
@@ -3092,43 +3092,43 @@
         <v>33</v>
       </c>
       <c r="K33" t="n">
+        <v>0</v>
+      </c>
+      <c r="L33" t="n">
+        <v>0</v>
+      </c>
+      <c r="M33" t="n">
+        <v>0</v>
+      </c>
+      <c r="N33" t="n">
+        <v>0</v>
+      </c>
+      <c r="O33" t="n">
+        <v>0</v>
+      </c>
+      <c r="P33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>0</v>
+      </c>
+      <c r="R33" t="n">
+        <v>0</v>
+      </c>
+      <c r="S33" t="n">
+        <v>0</v>
+      </c>
+      <c r="T33" t="n">
+        <v>0</v>
+      </c>
+      <c r="U33" t="n">
+        <v>0</v>
+      </c>
+      <c r="V33" t="n">
+        <v>0</v>
+      </c>
+      <c r="W33" t="n">
         <v>24</v>
-      </c>
-      <c r="L33" t="n">
-        <v>0</v>
-      </c>
-      <c r="M33" t="n">
-        <v>0</v>
-      </c>
-      <c r="N33" t="n">
-        <v>0</v>
-      </c>
-      <c r="O33" t="n">
-        <v>0</v>
-      </c>
-      <c r="P33" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>0</v>
-      </c>
-      <c r="R33" t="n">
-        <v>0</v>
-      </c>
-      <c r="S33" t="n">
-        <v>0</v>
-      </c>
-      <c r="T33" t="n">
-        <v>0</v>
-      </c>
-      <c r="U33" t="n">
-        <v>0</v>
-      </c>
-      <c r="V33" t="n">
-        <v>0</v>
-      </c>
-      <c r="W33" t="n">
-        <v>0</v>
       </c>
       <c r="X33" t="n">
         <v>0</v>
@@ -3171,43 +3171,43 @@
         <v>33</v>
       </c>
       <c r="K34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W34" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="L34" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M34" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N34" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O34" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P34" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q34" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R34" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S34" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T34" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U34" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V34" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W34" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="X34" s="5" t="n">
         <v>0</v>
@@ -3250,43 +3250,43 @@
         <v>33</v>
       </c>
       <c r="K35" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" t="n">
+        <v>0</v>
+      </c>
+      <c r="M35" t="n">
+        <v>0</v>
+      </c>
+      <c r="N35" t="n">
+        <v>0</v>
+      </c>
+      <c r="O35" t="n">
+        <v>0</v>
+      </c>
+      <c r="P35" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>0</v>
+      </c>
+      <c r="R35" t="n">
+        <v>0</v>
+      </c>
+      <c r="S35" t="n">
+        <v>0</v>
+      </c>
+      <c r="T35" t="n">
+        <v>0</v>
+      </c>
+      <c r="U35" t="n">
+        <v>0</v>
+      </c>
+      <c r="V35" t="n">
+        <v>0</v>
+      </c>
+      <c r="W35" t="n">
         <v>24</v>
-      </c>
-      <c r="L35" t="n">
-        <v>0</v>
-      </c>
-      <c r="M35" t="n">
-        <v>0</v>
-      </c>
-      <c r="N35" t="n">
-        <v>0</v>
-      </c>
-      <c r="O35" t="n">
-        <v>0</v>
-      </c>
-      <c r="P35" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q35" t="n">
-        <v>0</v>
-      </c>
-      <c r="R35" t="n">
-        <v>0</v>
-      </c>
-      <c r="S35" t="n">
-        <v>0</v>
-      </c>
-      <c r="T35" t="n">
-        <v>0</v>
-      </c>
-      <c r="U35" t="n">
-        <v>0</v>
-      </c>
-      <c r="V35" t="n">
-        <v>0</v>
-      </c>
-      <c r="W35" t="n">
-        <v>0</v>
       </c>
       <c r="X35" t="n">
         <v>0</v>
@@ -3329,43 +3329,43 @@
         <v>33</v>
       </c>
       <c r="K36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W36" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="L36" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M36" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N36" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O36" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P36" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q36" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R36" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S36" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T36" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U36" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V36" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W36" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="X36" s="5" t="n">
         <v>0</v>
@@ -3408,43 +3408,43 @@
         <v>33</v>
       </c>
       <c r="K37" t="n">
+        <v>0</v>
+      </c>
+      <c r="L37" t="n">
+        <v>0</v>
+      </c>
+      <c r="M37" t="n">
+        <v>0</v>
+      </c>
+      <c r="N37" t="n">
+        <v>0</v>
+      </c>
+      <c r="O37" t="n">
+        <v>0</v>
+      </c>
+      <c r="P37" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>0</v>
+      </c>
+      <c r="R37" t="n">
+        <v>0</v>
+      </c>
+      <c r="S37" t="n">
+        <v>0</v>
+      </c>
+      <c r="T37" t="n">
+        <v>0</v>
+      </c>
+      <c r="U37" t="n">
+        <v>0</v>
+      </c>
+      <c r="V37" t="n">
+        <v>0</v>
+      </c>
+      <c r="W37" t="n">
         <v>24</v>
-      </c>
-      <c r="L37" t="n">
-        <v>0</v>
-      </c>
-      <c r="M37" t="n">
-        <v>0</v>
-      </c>
-      <c r="N37" t="n">
-        <v>0</v>
-      </c>
-      <c r="O37" t="n">
-        <v>0</v>
-      </c>
-      <c r="P37" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q37" t="n">
-        <v>0</v>
-      </c>
-      <c r="R37" t="n">
-        <v>0</v>
-      </c>
-      <c r="S37" t="n">
-        <v>0</v>
-      </c>
-      <c r="T37" t="n">
-        <v>0</v>
-      </c>
-      <c r="U37" t="n">
-        <v>0</v>
-      </c>
-      <c r="V37" t="n">
-        <v>0</v>
-      </c>
-      <c r="W37" t="n">
-        <v>0</v>
       </c>
       <c r="X37" t="n">
         <v>0</v>
@@ -3487,43 +3487,43 @@
         <v>33</v>
       </c>
       <c r="K38" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L38" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M38" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N38" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O38" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P38" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q38" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R38" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S38" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T38" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U38" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V38" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W38" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="L38" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M38" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N38" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O38" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P38" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q38" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R38" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S38" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T38" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U38" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V38" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W38" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="X38" s="5" t="n">
         <v>0</v>
@@ -3566,43 +3566,43 @@
         <v>33</v>
       </c>
       <c r="K39" t="n">
+        <v>0</v>
+      </c>
+      <c r="L39" t="n">
+        <v>0</v>
+      </c>
+      <c r="M39" t="n">
+        <v>0</v>
+      </c>
+      <c r="N39" t="n">
+        <v>0</v>
+      </c>
+      <c r="O39" t="n">
+        <v>0</v>
+      </c>
+      <c r="P39" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>0</v>
+      </c>
+      <c r="R39" t="n">
+        <v>0</v>
+      </c>
+      <c r="S39" t="n">
+        <v>0</v>
+      </c>
+      <c r="T39" t="n">
+        <v>0</v>
+      </c>
+      <c r="U39" t="n">
+        <v>0</v>
+      </c>
+      <c r="V39" t="n">
+        <v>0</v>
+      </c>
+      <c r="W39" t="n">
         <v>24</v>
-      </c>
-      <c r="L39" t="n">
-        <v>0</v>
-      </c>
-      <c r="M39" t="n">
-        <v>0</v>
-      </c>
-      <c r="N39" t="n">
-        <v>0</v>
-      </c>
-      <c r="O39" t="n">
-        <v>0</v>
-      </c>
-      <c r="P39" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q39" t="n">
-        <v>0</v>
-      </c>
-      <c r="R39" t="n">
-        <v>0</v>
-      </c>
-      <c r="S39" t="n">
-        <v>0</v>
-      </c>
-      <c r="T39" t="n">
-        <v>0</v>
-      </c>
-      <c r="U39" t="n">
-        <v>0</v>
-      </c>
-      <c r="V39" t="n">
-        <v>0</v>
-      </c>
-      <c r="W39" t="n">
-        <v>0</v>
       </c>
       <c r="X39" t="n">
         <v>0</v>
@@ -3645,43 +3645,43 @@
         <v>33</v>
       </c>
       <c r="K40" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L40" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M40" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N40" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O40" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P40" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q40" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R40" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S40" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T40" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U40" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V40" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W40" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="L40" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M40" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N40" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O40" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P40" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q40" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R40" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S40" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T40" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U40" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V40" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W40" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="X40" s="5" t="n">
         <v>0</v>
@@ -3724,43 +3724,43 @@
         <v>33</v>
       </c>
       <c r="K41" t="n">
+        <v>0</v>
+      </c>
+      <c r="L41" t="n">
+        <v>0</v>
+      </c>
+      <c r="M41" t="n">
+        <v>0</v>
+      </c>
+      <c r="N41" t="n">
+        <v>0</v>
+      </c>
+      <c r="O41" t="n">
+        <v>0</v>
+      </c>
+      <c r="P41" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>0</v>
+      </c>
+      <c r="R41" t="n">
+        <v>0</v>
+      </c>
+      <c r="S41" t="n">
+        <v>0</v>
+      </c>
+      <c r="T41" t="n">
+        <v>0</v>
+      </c>
+      <c r="U41" t="n">
+        <v>0</v>
+      </c>
+      <c r="V41" t="n">
+        <v>0</v>
+      </c>
+      <c r="W41" t="n">
         <v>24</v>
-      </c>
-      <c r="L41" t="n">
-        <v>0</v>
-      </c>
-      <c r="M41" t="n">
-        <v>0</v>
-      </c>
-      <c r="N41" t="n">
-        <v>0</v>
-      </c>
-      <c r="O41" t="n">
-        <v>0</v>
-      </c>
-      <c r="P41" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q41" t="n">
-        <v>0</v>
-      </c>
-      <c r="R41" t="n">
-        <v>0</v>
-      </c>
-      <c r="S41" t="n">
-        <v>0</v>
-      </c>
-      <c r="T41" t="n">
-        <v>0</v>
-      </c>
-      <c r="U41" t="n">
-        <v>0</v>
-      </c>
-      <c r="V41" t="n">
-        <v>0</v>
-      </c>
-      <c r="W41" t="n">
-        <v>0</v>
       </c>
       <c r="X41" t="n">
         <v>0</v>
@@ -3803,43 +3803,43 @@
         <v>33</v>
       </c>
       <c r="K42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W42" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="L42" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M42" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N42" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O42" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P42" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q42" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R42" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S42" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T42" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U42" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V42" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W42" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="X42" s="5" t="n">
         <v>0</v>
@@ -3882,43 +3882,43 @@
         <v>33</v>
       </c>
       <c r="K43" t="n">
+        <v>0</v>
+      </c>
+      <c r="L43" t="n">
+        <v>0</v>
+      </c>
+      <c r="M43" t="n">
+        <v>0</v>
+      </c>
+      <c r="N43" t="n">
+        <v>0</v>
+      </c>
+      <c r="O43" t="n">
+        <v>0</v>
+      </c>
+      <c r="P43" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>0</v>
+      </c>
+      <c r="R43" t="n">
+        <v>0</v>
+      </c>
+      <c r="S43" t="n">
+        <v>0</v>
+      </c>
+      <c r="T43" t="n">
+        <v>0</v>
+      </c>
+      <c r="U43" t="n">
+        <v>0</v>
+      </c>
+      <c r="V43" t="n">
+        <v>0</v>
+      </c>
+      <c r="W43" t="n">
         <v>24</v>
-      </c>
-      <c r="L43" t="n">
-        <v>0</v>
-      </c>
-      <c r="M43" t="n">
-        <v>0</v>
-      </c>
-      <c r="N43" t="n">
-        <v>0</v>
-      </c>
-      <c r="O43" t="n">
-        <v>0</v>
-      </c>
-      <c r="P43" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q43" t="n">
-        <v>0</v>
-      </c>
-      <c r="R43" t="n">
-        <v>0</v>
-      </c>
-      <c r="S43" t="n">
-        <v>0</v>
-      </c>
-      <c r="T43" t="n">
-        <v>0</v>
-      </c>
-      <c r="U43" t="n">
-        <v>0</v>
-      </c>
-      <c r="V43" t="n">
-        <v>0</v>
-      </c>
-      <c r="W43" t="n">
-        <v>0</v>
       </c>
       <c r="X43" t="n">
         <v>0</v>
@@ -3961,43 +3961,43 @@
         <v>33</v>
       </c>
       <c r="K44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W44" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="L44" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M44" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N44" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O44" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P44" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q44" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R44" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S44" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T44" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U44" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V44" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W44" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="X44" s="5" t="n">
         <v>0</v>
@@ -4040,43 +4040,43 @@
         <v>33</v>
       </c>
       <c r="K45" t="n">
+        <v>0</v>
+      </c>
+      <c r="L45" t="n">
+        <v>0</v>
+      </c>
+      <c r="M45" t="n">
+        <v>0</v>
+      </c>
+      <c r="N45" t="n">
+        <v>0</v>
+      </c>
+      <c r="O45" t="n">
+        <v>0</v>
+      </c>
+      <c r="P45" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>0</v>
+      </c>
+      <c r="R45" t="n">
+        <v>0</v>
+      </c>
+      <c r="S45" t="n">
+        <v>0</v>
+      </c>
+      <c r="T45" t="n">
+        <v>0</v>
+      </c>
+      <c r="U45" t="n">
+        <v>0</v>
+      </c>
+      <c r="V45" t="n">
+        <v>0</v>
+      </c>
+      <c r="W45" t="n">
         <v>24</v>
-      </c>
-      <c r="L45" t="n">
-        <v>0</v>
-      </c>
-      <c r="M45" t="n">
-        <v>0</v>
-      </c>
-      <c r="N45" t="n">
-        <v>0</v>
-      </c>
-      <c r="O45" t="n">
-        <v>0</v>
-      </c>
-      <c r="P45" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q45" t="n">
-        <v>0</v>
-      </c>
-      <c r="R45" t="n">
-        <v>0</v>
-      </c>
-      <c r="S45" t="n">
-        <v>0</v>
-      </c>
-      <c r="T45" t="n">
-        <v>0</v>
-      </c>
-      <c r="U45" t="n">
-        <v>0</v>
-      </c>
-      <c r="V45" t="n">
-        <v>0</v>
-      </c>
-      <c r="W45" t="n">
-        <v>0</v>
       </c>
       <c r="X45" t="n">
         <v>0</v>
@@ -4119,43 +4119,43 @@
         <v>33</v>
       </c>
       <c r="K46" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L46" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M46" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N46" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O46" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P46" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q46" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R46" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S46" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T46" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U46" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V46" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W46" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="L46" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M46" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N46" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O46" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P46" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q46" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R46" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S46" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T46" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U46" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V46" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W46" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="X46" s="5" t="n">
         <v>0</v>
@@ -4198,43 +4198,43 @@
         <v>33</v>
       </c>
       <c r="K47" t="n">
+        <v>0</v>
+      </c>
+      <c r="L47" t="n">
+        <v>0</v>
+      </c>
+      <c r="M47" t="n">
+        <v>0</v>
+      </c>
+      <c r="N47" t="n">
+        <v>0</v>
+      </c>
+      <c r="O47" t="n">
+        <v>0</v>
+      </c>
+      <c r="P47" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>0</v>
+      </c>
+      <c r="R47" t="n">
+        <v>0</v>
+      </c>
+      <c r="S47" t="n">
+        <v>0</v>
+      </c>
+      <c r="T47" t="n">
+        <v>0</v>
+      </c>
+      <c r="U47" t="n">
+        <v>0</v>
+      </c>
+      <c r="V47" t="n">
+        <v>0</v>
+      </c>
+      <c r="W47" t="n">
         <v>24</v>
-      </c>
-      <c r="L47" t="n">
-        <v>0</v>
-      </c>
-      <c r="M47" t="n">
-        <v>0</v>
-      </c>
-      <c r="N47" t="n">
-        <v>0</v>
-      </c>
-      <c r="O47" t="n">
-        <v>0</v>
-      </c>
-      <c r="P47" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q47" t="n">
-        <v>0</v>
-      </c>
-      <c r="R47" t="n">
-        <v>0</v>
-      </c>
-      <c r="S47" t="n">
-        <v>0</v>
-      </c>
-      <c r="T47" t="n">
-        <v>0</v>
-      </c>
-      <c r="U47" t="n">
-        <v>0</v>
-      </c>
-      <c r="V47" t="n">
-        <v>0</v>
-      </c>
-      <c r="W47" t="n">
-        <v>0</v>
       </c>
       <c r="X47" t="n">
         <v>0</v>
@@ -4277,43 +4277,43 @@
         <v>33</v>
       </c>
       <c r="K48" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L48" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M48" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N48" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O48" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P48" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q48" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R48" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S48" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T48" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U48" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V48" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W48" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="L48" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M48" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N48" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O48" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P48" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q48" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R48" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S48" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T48" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U48" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V48" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W48" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="X48" s="5" t="n">
         <v>0</v>
@@ -4356,43 +4356,43 @@
         <v>33</v>
       </c>
       <c r="K49" t="n">
+        <v>0</v>
+      </c>
+      <c r="L49" t="n">
+        <v>0</v>
+      </c>
+      <c r="M49" t="n">
+        <v>0</v>
+      </c>
+      <c r="N49" t="n">
+        <v>0</v>
+      </c>
+      <c r="O49" t="n">
+        <v>0</v>
+      </c>
+      <c r="P49" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>0</v>
+      </c>
+      <c r="R49" t="n">
+        <v>0</v>
+      </c>
+      <c r="S49" t="n">
+        <v>0</v>
+      </c>
+      <c r="T49" t="n">
+        <v>0</v>
+      </c>
+      <c r="U49" t="n">
+        <v>0</v>
+      </c>
+      <c r="V49" t="n">
+        <v>0</v>
+      </c>
+      <c r="W49" t="n">
         <v>24</v>
-      </c>
-      <c r="L49" t="n">
-        <v>0</v>
-      </c>
-      <c r="M49" t="n">
-        <v>0</v>
-      </c>
-      <c r="N49" t="n">
-        <v>0</v>
-      </c>
-      <c r="O49" t="n">
-        <v>0</v>
-      </c>
-      <c r="P49" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q49" t="n">
-        <v>0</v>
-      </c>
-      <c r="R49" t="n">
-        <v>0</v>
-      </c>
-      <c r="S49" t="n">
-        <v>0</v>
-      </c>
-      <c r="T49" t="n">
-        <v>0</v>
-      </c>
-      <c r="U49" t="n">
-        <v>0</v>
-      </c>
-      <c r="V49" t="n">
-        <v>0</v>
-      </c>
-      <c r="W49" t="n">
-        <v>0</v>
       </c>
       <c r="X49" t="n">
         <v>0</v>
@@ -4435,43 +4435,43 @@
         <v>33</v>
       </c>
       <c r="K50" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L50" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M50" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N50" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O50" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P50" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q50" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R50" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S50" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T50" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U50" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V50" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W50" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="L50" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M50" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N50" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O50" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P50" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q50" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R50" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S50" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T50" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U50" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V50" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W50" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="X50" s="5" t="n">
         <v>0</v>
@@ -4514,43 +4514,43 @@
         <v>33</v>
       </c>
       <c r="K51" t="n">
+        <v>0</v>
+      </c>
+      <c r="L51" t="n">
+        <v>0</v>
+      </c>
+      <c r="M51" t="n">
+        <v>0</v>
+      </c>
+      <c r="N51" t="n">
+        <v>0</v>
+      </c>
+      <c r="O51" t="n">
+        <v>0</v>
+      </c>
+      <c r="P51" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>0</v>
+      </c>
+      <c r="R51" t="n">
+        <v>0</v>
+      </c>
+      <c r="S51" t="n">
+        <v>0</v>
+      </c>
+      <c r="T51" t="n">
+        <v>0</v>
+      </c>
+      <c r="U51" t="n">
+        <v>0</v>
+      </c>
+      <c r="V51" t="n">
+        <v>0</v>
+      </c>
+      <c r="W51" t="n">
         <v>24</v>
-      </c>
-      <c r="L51" t="n">
-        <v>0</v>
-      </c>
-      <c r="M51" t="n">
-        <v>0</v>
-      </c>
-      <c r="N51" t="n">
-        <v>0</v>
-      </c>
-      <c r="O51" t="n">
-        <v>0</v>
-      </c>
-      <c r="P51" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q51" t="n">
-        <v>0</v>
-      </c>
-      <c r="R51" t="n">
-        <v>0</v>
-      </c>
-      <c r="S51" t="n">
-        <v>0</v>
-      </c>
-      <c r="T51" t="n">
-        <v>0</v>
-      </c>
-      <c r="U51" t="n">
-        <v>0</v>
-      </c>
-      <c r="V51" t="n">
-        <v>0</v>
-      </c>
-      <c r="W51" t="n">
-        <v>0</v>
       </c>
       <c r="X51" t="n">
         <v>0</v>
@@ -4593,43 +4593,43 @@
         <v>30</v>
       </c>
       <c r="K52" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L52" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M52" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N52" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O52" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P52" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q52" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R52" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S52" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T52" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U52" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V52" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W52" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="L52" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M52" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N52" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O52" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P52" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q52" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R52" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S52" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T52" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U52" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V52" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W52" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="X52" s="5" t="n">
         <v>0</v>
@@ -4672,43 +4672,43 @@
         <v>30</v>
       </c>
       <c r="K53" t="n">
+        <v>0</v>
+      </c>
+      <c r="L53" t="n">
+        <v>0</v>
+      </c>
+      <c r="M53" t="n">
+        <v>0</v>
+      </c>
+      <c r="N53" t="n">
+        <v>0</v>
+      </c>
+      <c r="O53" t="n">
+        <v>0</v>
+      </c>
+      <c r="P53" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>0</v>
+      </c>
+      <c r="R53" t="n">
+        <v>0</v>
+      </c>
+      <c r="S53" t="n">
+        <v>0</v>
+      </c>
+      <c r="T53" t="n">
+        <v>0</v>
+      </c>
+      <c r="U53" t="n">
+        <v>0</v>
+      </c>
+      <c r="V53" t="n">
+        <v>0</v>
+      </c>
+      <c r="W53" t="n">
         <v>24</v>
-      </c>
-      <c r="L53" t="n">
-        <v>0</v>
-      </c>
-      <c r="M53" t="n">
-        <v>0</v>
-      </c>
-      <c r="N53" t="n">
-        <v>0</v>
-      </c>
-      <c r="O53" t="n">
-        <v>0</v>
-      </c>
-      <c r="P53" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q53" t="n">
-        <v>0</v>
-      </c>
-      <c r="R53" t="n">
-        <v>0</v>
-      </c>
-      <c r="S53" t="n">
-        <v>0</v>
-      </c>
-      <c r="T53" t="n">
-        <v>0</v>
-      </c>
-      <c r="U53" t="n">
-        <v>0</v>
-      </c>
-      <c r="V53" t="n">
-        <v>0</v>
-      </c>
-      <c r="W53" t="n">
-        <v>0</v>
       </c>
       <c r="X53" t="n">
         <v>0</v>
@@ -4751,43 +4751,43 @@
         <v>30</v>
       </c>
       <c r="K54" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L54" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M54" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N54" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O54" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P54" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q54" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R54" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S54" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T54" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U54" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V54" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W54" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="L54" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M54" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N54" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O54" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P54" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q54" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R54" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S54" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T54" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U54" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V54" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W54" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="X54" s="5" t="n">
         <v>0</v>
@@ -4830,43 +4830,43 @@
         <v>30</v>
       </c>
       <c r="K55" t="n">
+        <v>0</v>
+      </c>
+      <c r="L55" t="n">
+        <v>0</v>
+      </c>
+      <c r="M55" t="n">
+        <v>0</v>
+      </c>
+      <c r="N55" t="n">
+        <v>0</v>
+      </c>
+      <c r="O55" t="n">
+        <v>0</v>
+      </c>
+      <c r="P55" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>0</v>
+      </c>
+      <c r="R55" t="n">
+        <v>0</v>
+      </c>
+      <c r="S55" t="n">
+        <v>0</v>
+      </c>
+      <c r="T55" t="n">
+        <v>0</v>
+      </c>
+      <c r="U55" t="n">
+        <v>0</v>
+      </c>
+      <c r="V55" t="n">
+        <v>0</v>
+      </c>
+      <c r="W55" t="n">
         <v>24</v>
-      </c>
-      <c r="L55" t="n">
-        <v>0</v>
-      </c>
-      <c r="M55" t="n">
-        <v>0</v>
-      </c>
-      <c r="N55" t="n">
-        <v>0</v>
-      </c>
-      <c r="O55" t="n">
-        <v>0</v>
-      </c>
-      <c r="P55" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q55" t="n">
-        <v>0</v>
-      </c>
-      <c r="R55" t="n">
-        <v>0</v>
-      </c>
-      <c r="S55" t="n">
-        <v>0</v>
-      </c>
-      <c r="T55" t="n">
-        <v>0</v>
-      </c>
-      <c r="U55" t="n">
-        <v>0</v>
-      </c>
-      <c r="V55" t="n">
-        <v>0</v>
-      </c>
-      <c r="W55" t="n">
-        <v>0</v>
       </c>
       <c r="X55" t="n">
         <v>0</v>
@@ -4909,43 +4909,43 @@
         <v>30</v>
       </c>
       <c r="K56" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L56" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M56" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N56" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O56" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P56" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q56" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R56" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S56" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T56" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U56" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V56" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W56" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="L56" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M56" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N56" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O56" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P56" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q56" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R56" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S56" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T56" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U56" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V56" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W56" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="X56" s="5" t="n">
         <v>0</v>
@@ -4988,43 +4988,43 @@
         <v>24</v>
       </c>
       <c r="K57" t="n">
+        <v>0</v>
+      </c>
+      <c r="L57" t="n">
+        <v>0</v>
+      </c>
+      <c r="M57" t="n">
+        <v>0</v>
+      </c>
+      <c r="N57" t="n">
+        <v>0</v>
+      </c>
+      <c r="O57" t="n">
+        <v>0</v>
+      </c>
+      <c r="P57" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>0</v>
+      </c>
+      <c r="R57" t="n">
+        <v>0</v>
+      </c>
+      <c r="S57" t="n">
+        <v>0</v>
+      </c>
+      <c r="T57" t="n">
+        <v>0</v>
+      </c>
+      <c r="U57" t="n">
+        <v>0</v>
+      </c>
+      <c r="V57" t="n">
+        <v>0</v>
+      </c>
+      <c r="W57" t="n">
         <v>24</v>
-      </c>
-      <c r="L57" t="n">
-        <v>0</v>
-      </c>
-      <c r="M57" t="n">
-        <v>0</v>
-      </c>
-      <c r="N57" t="n">
-        <v>0</v>
-      </c>
-      <c r="O57" t="n">
-        <v>0</v>
-      </c>
-      <c r="P57" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q57" t="n">
-        <v>0</v>
-      </c>
-      <c r="R57" t="n">
-        <v>0</v>
-      </c>
-      <c r="S57" t="n">
-        <v>0</v>
-      </c>
-      <c r="T57" t="n">
-        <v>0</v>
-      </c>
-      <c r="U57" t="n">
-        <v>0</v>
-      </c>
-      <c r="V57" t="n">
-        <v>0</v>
-      </c>
-      <c r="W57" t="n">
-        <v>0</v>
       </c>
       <c r="X57" t="n">
         <v>0</v>
@@ -5067,43 +5067,43 @@
         <v>26</v>
       </c>
       <c r="K58" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L58" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M58" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N58" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O58" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P58" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q58" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R58" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S58" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T58" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U58" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V58" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W58" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="L58" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M58" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N58" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O58" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P58" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q58" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R58" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S58" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T58" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U58" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V58" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W58" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="X58" s="5" t="n">
         <v>0</v>
@@ -5146,43 +5146,43 @@
         <v>26</v>
       </c>
       <c r="K59" t="n">
+        <v>0</v>
+      </c>
+      <c r="L59" t="n">
+        <v>0</v>
+      </c>
+      <c r="M59" t="n">
+        <v>0</v>
+      </c>
+      <c r="N59" t="n">
+        <v>0</v>
+      </c>
+      <c r="O59" t="n">
+        <v>0</v>
+      </c>
+      <c r="P59" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>0</v>
+      </c>
+      <c r="R59" t="n">
+        <v>0</v>
+      </c>
+      <c r="S59" t="n">
+        <v>0</v>
+      </c>
+      <c r="T59" t="n">
+        <v>0</v>
+      </c>
+      <c r="U59" t="n">
+        <v>0</v>
+      </c>
+      <c r="V59" t="n">
+        <v>0</v>
+      </c>
+      <c r="W59" t="n">
         <v>24</v>
-      </c>
-      <c r="L59" t="n">
-        <v>0</v>
-      </c>
-      <c r="M59" t="n">
-        <v>0</v>
-      </c>
-      <c r="N59" t="n">
-        <v>0</v>
-      </c>
-      <c r="O59" t="n">
-        <v>0</v>
-      </c>
-      <c r="P59" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q59" t="n">
-        <v>0</v>
-      </c>
-      <c r="R59" t="n">
-        <v>0</v>
-      </c>
-      <c r="S59" t="n">
-        <v>0</v>
-      </c>
-      <c r="T59" t="n">
-        <v>0</v>
-      </c>
-      <c r="U59" t="n">
-        <v>0</v>
-      </c>
-      <c r="V59" t="n">
-        <v>0</v>
-      </c>
-      <c r="W59" t="n">
-        <v>0</v>
       </c>
       <c r="X59" t="n">
         <v>0</v>
@@ -5225,43 +5225,43 @@
         <v>23</v>
       </c>
       <c r="K60" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L60" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M60" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N60" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O60" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P60" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q60" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R60" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S60" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T60" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U60" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V60" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W60" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="L60" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M60" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N60" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O60" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P60" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q60" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R60" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S60" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T60" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U60" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V60" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W60" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="X60" s="5" t="n">
         <v>0</v>
@@ -5304,43 +5304,43 @@
         <v>29</v>
       </c>
       <c r="K61" t="n">
+        <v>0</v>
+      </c>
+      <c r="L61" t="n">
+        <v>0</v>
+      </c>
+      <c r="M61" t="n">
+        <v>0</v>
+      </c>
+      <c r="N61" t="n">
+        <v>0</v>
+      </c>
+      <c r="O61" t="n">
+        <v>0</v>
+      </c>
+      <c r="P61" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q61" t="n">
+        <v>0</v>
+      </c>
+      <c r="R61" t="n">
+        <v>0</v>
+      </c>
+      <c r="S61" t="n">
+        <v>0</v>
+      </c>
+      <c r="T61" t="n">
+        <v>0</v>
+      </c>
+      <c r="U61" t="n">
+        <v>0</v>
+      </c>
+      <c r="V61" t="n">
+        <v>0</v>
+      </c>
+      <c r="W61" t="n">
         <v>24</v>
-      </c>
-      <c r="L61" t="n">
-        <v>0</v>
-      </c>
-      <c r="M61" t="n">
-        <v>0</v>
-      </c>
-      <c r="N61" t="n">
-        <v>0</v>
-      </c>
-      <c r="O61" t="n">
-        <v>0</v>
-      </c>
-      <c r="P61" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q61" t="n">
-        <v>0</v>
-      </c>
-      <c r="R61" t="n">
-        <v>0</v>
-      </c>
-      <c r="S61" t="n">
-        <v>0</v>
-      </c>
-      <c r="T61" t="n">
-        <v>0</v>
-      </c>
-      <c r="U61" t="n">
-        <v>0</v>
-      </c>
-      <c r="V61" t="n">
-        <v>0</v>
-      </c>
-      <c r="W61" t="n">
-        <v>0</v>
       </c>
       <c r="X61" t="n">
         <v>0</v>
@@ -5383,43 +5383,43 @@
         <v>29</v>
       </c>
       <c r="K62" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L62" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M62" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N62" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O62" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P62" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q62" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R62" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S62" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T62" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U62" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V62" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W62" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="L62" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M62" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N62" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O62" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P62" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q62" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R62" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S62" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T62" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U62" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V62" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W62" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="X62" s="5" t="n">
         <v>0</v>
@@ -5462,43 +5462,43 @@
         <v>29</v>
       </c>
       <c r="K63" t="n">
+        <v>0</v>
+      </c>
+      <c r="L63" t="n">
+        <v>0</v>
+      </c>
+      <c r="M63" t="n">
+        <v>0</v>
+      </c>
+      <c r="N63" t="n">
+        <v>0</v>
+      </c>
+      <c r="O63" t="n">
+        <v>0</v>
+      </c>
+      <c r="P63" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q63" t="n">
+        <v>0</v>
+      </c>
+      <c r="R63" t="n">
+        <v>0</v>
+      </c>
+      <c r="S63" t="n">
+        <v>0</v>
+      </c>
+      <c r="T63" t="n">
+        <v>0</v>
+      </c>
+      <c r="U63" t="n">
+        <v>0</v>
+      </c>
+      <c r="V63" t="n">
+        <v>0</v>
+      </c>
+      <c r="W63" t="n">
         <v>24</v>
-      </c>
-      <c r="L63" t="n">
-        <v>0</v>
-      </c>
-      <c r="M63" t="n">
-        <v>0</v>
-      </c>
-      <c r="N63" t="n">
-        <v>0</v>
-      </c>
-      <c r="O63" t="n">
-        <v>0</v>
-      </c>
-      <c r="P63" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q63" t="n">
-        <v>0</v>
-      </c>
-      <c r="R63" t="n">
-        <v>0</v>
-      </c>
-      <c r="S63" t="n">
-        <v>0</v>
-      </c>
-      <c r="T63" t="n">
-        <v>0</v>
-      </c>
-      <c r="U63" t="n">
-        <v>0</v>
-      </c>
-      <c r="V63" t="n">
-        <v>0</v>
-      </c>
-      <c r="W63" t="n">
-        <v>0</v>
       </c>
       <c r="X63" t="n">
         <v>0</v>
@@ -5541,43 +5541,43 @@
         <v>20</v>
       </c>
       <c r="K64" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L64" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M64" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N64" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O64" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P64" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q64" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R64" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S64" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T64" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U64" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V64" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W64" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="L64" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M64" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N64" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O64" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P64" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q64" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R64" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S64" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T64" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U64" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V64" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W64" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="X64" s="5" t="n">
         <v>0</v>
@@ -5620,43 +5620,43 @@
         <v>20</v>
       </c>
       <c r="K65" t="n">
+        <v>0</v>
+      </c>
+      <c r="L65" t="n">
+        <v>0</v>
+      </c>
+      <c r="M65" t="n">
+        <v>0</v>
+      </c>
+      <c r="N65" t="n">
+        <v>0</v>
+      </c>
+      <c r="O65" t="n">
+        <v>0</v>
+      </c>
+      <c r="P65" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q65" t="n">
+        <v>0</v>
+      </c>
+      <c r="R65" t="n">
+        <v>0</v>
+      </c>
+      <c r="S65" t="n">
+        <v>0</v>
+      </c>
+      <c r="T65" t="n">
+        <v>0</v>
+      </c>
+      <c r="U65" t="n">
+        <v>0</v>
+      </c>
+      <c r="V65" t="n">
+        <v>0</v>
+      </c>
+      <c r="W65" t="n">
         <v>24</v>
-      </c>
-      <c r="L65" t="n">
-        <v>0</v>
-      </c>
-      <c r="M65" t="n">
-        <v>0</v>
-      </c>
-      <c r="N65" t="n">
-        <v>0</v>
-      </c>
-      <c r="O65" t="n">
-        <v>0</v>
-      </c>
-      <c r="P65" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q65" t="n">
-        <v>0</v>
-      </c>
-      <c r="R65" t="n">
-        <v>0</v>
-      </c>
-      <c r="S65" t="n">
-        <v>0</v>
-      </c>
-      <c r="T65" t="n">
-        <v>0</v>
-      </c>
-      <c r="U65" t="n">
-        <v>0</v>
-      </c>
-      <c r="V65" t="n">
-        <v>0</v>
-      </c>
-      <c r="W65" t="n">
-        <v>0</v>
       </c>
       <c r="X65" t="n">
         <v>0</v>
@@ -5699,43 +5699,43 @@
         <v>26</v>
       </c>
       <c r="K66" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L66" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M66" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N66" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O66" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P66" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q66" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R66" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S66" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T66" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U66" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V66" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W66" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="L66" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M66" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N66" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O66" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P66" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q66" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R66" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S66" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T66" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U66" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V66" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W66" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="X66" s="5" t="n">
         <v>0</v>
@@ -5777,6 +5777,9 @@
       <c r="J67" t="n">
         <v>26</v>
       </c>
+      <c r="K67" t="n">
+        <v>0</v>
+      </c>
       <c r="L67" t="n">
         <v>0</v>
       </c>
@@ -5808,9 +5811,6 @@
         <v>0</v>
       </c>
       <c r="V67" t="n">
-        <v>0</v>
-      </c>
-      <c r="W67" t="n">
         <v>0</v>
       </c>
       <c r="X67" t="n">
@@ -5854,43 +5854,43 @@
         <v>26</v>
       </c>
       <c r="K68" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L68" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M68" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N68" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O68" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P68" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q68" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R68" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S68" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T68" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U68" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V68" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W68" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="L68" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M68" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N68" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O68" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P68" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q68" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R68" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S68" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T68" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U68" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V68" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W68" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="X68" s="5" t="n">
         <v>0</v>
@@ -5929,6 +5929,9 @@
       <c r="J69" t="n">
         <v>26</v>
       </c>
+      <c r="K69" t="n">
+        <v>0</v>
+      </c>
       <c r="L69" t="n">
         <v>0</v>
       </c>
@@ -5960,9 +5963,6 @@
         <v>0</v>
       </c>
       <c r="V69" t="n">
-        <v>0</v>
-      </c>
-      <c r="W69" t="n">
         <v>0</v>
       </c>
       <c r="X69" t="n">
@@ -6006,43 +6006,43 @@
         <v>26</v>
       </c>
       <c r="K70" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L70" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M70" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N70" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O70" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P70" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q70" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R70" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S70" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T70" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U70" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V70" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W70" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="L70" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M70" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N70" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O70" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P70" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q70" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R70" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S70" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T70" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U70" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V70" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W70" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="X70" s="5" t="n">
         <v>0</v>
@@ -6085,43 +6085,43 @@
         <v>26</v>
       </c>
       <c r="K71" t="n">
+        <v>0</v>
+      </c>
+      <c r="L71" t="n">
+        <v>0</v>
+      </c>
+      <c r="M71" t="n">
+        <v>0</v>
+      </c>
+      <c r="N71" t="n">
+        <v>0</v>
+      </c>
+      <c r="O71" t="n">
+        <v>0</v>
+      </c>
+      <c r="P71" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q71" t="n">
+        <v>0</v>
+      </c>
+      <c r="R71" t="n">
+        <v>0</v>
+      </c>
+      <c r="S71" t="n">
+        <v>0</v>
+      </c>
+      <c r="T71" t="n">
+        <v>0</v>
+      </c>
+      <c r="U71" t="n">
+        <v>0</v>
+      </c>
+      <c r="V71" t="n">
+        <v>0</v>
+      </c>
+      <c r="W71" t="n">
         <v>24</v>
-      </c>
-      <c r="L71" t="n">
-        <v>0</v>
-      </c>
-      <c r="M71" t="n">
-        <v>0</v>
-      </c>
-      <c r="N71" t="n">
-        <v>0</v>
-      </c>
-      <c r="O71" t="n">
-        <v>0</v>
-      </c>
-      <c r="P71" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q71" t="n">
-        <v>0</v>
-      </c>
-      <c r="R71" t="n">
-        <v>0</v>
-      </c>
-      <c r="S71" t="n">
-        <v>0</v>
-      </c>
-      <c r="T71" t="n">
-        <v>0</v>
-      </c>
-      <c r="U71" t="n">
-        <v>0</v>
-      </c>
-      <c r="V71" t="n">
-        <v>0</v>
-      </c>
-      <c r="W71" t="n">
-        <v>0</v>
       </c>
       <c r="X71" t="n">
         <v>0</v>
@@ -6164,43 +6164,43 @@
         <v>26</v>
       </c>
       <c r="K72" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L72" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M72" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N72" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O72" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P72" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q72" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R72" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S72" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T72" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U72" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V72" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W72" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="L72" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M72" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N72" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O72" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P72" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q72" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R72" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S72" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T72" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U72" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V72" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W72" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="X72" s="5" t="n">
         <v>0</v>
@@ -6243,43 +6243,43 @@
         <v>26</v>
       </c>
       <c r="K73" t="n">
+        <v>0</v>
+      </c>
+      <c r="L73" t="n">
+        <v>0</v>
+      </c>
+      <c r="M73" t="n">
+        <v>0</v>
+      </c>
+      <c r="N73" t="n">
+        <v>0</v>
+      </c>
+      <c r="O73" t="n">
+        <v>0</v>
+      </c>
+      <c r="P73" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q73" t="n">
+        <v>0</v>
+      </c>
+      <c r="R73" t="n">
+        <v>0</v>
+      </c>
+      <c r="S73" t="n">
+        <v>0</v>
+      </c>
+      <c r="T73" t="n">
+        <v>0</v>
+      </c>
+      <c r="U73" t="n">
+        <v>0</v>
+      </c>
+      <c r="V73" t="n">
+        <v>0</v>
+      </c>
+      <c r="W73" t="n">
         <v>24</v>
-      </c>
-      <c r="L73" t="n">
-        <v>0</v>
-      </c>
-      <c r="M73" t="n">
-        <v>0</v>
-      </c>
-      <c r="N73" t="n">
-        <v>0</v>
-      </c>
-      <c r="O73" t="n">
-        <v>0</v>
-      </c>
-      <c r="P73" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q73" t="n">
-        <v>0</v>
-      </c>
-      <c r="R73" t="n">
-        <v>0</v>
-      </c>
-      <c r="S73" t="n">
-        <v>0</v>
-      </c>
-      <c r="T73" t="n">
-        <v>0</v>
-      </c>
-      <c r="U73" t="n">
-        <v>0</v>
-      </c>
-      <c r="V73" t="n">
-        <v>0</v>
-      </c>
-      <c r="W73" t="n">
-        <v>0</v>
       </c>
       <c r="X73" t="n">
         <v>0</v>
@@ -6322,43 +6322,43 @@
         <v>26</v>
       </c>
       <c r="K74" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L74" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M74" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N74" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O74" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P74" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q74" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R74" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S74" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T74" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U74" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V74" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W74" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="L74" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M74" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N74" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O74" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P74" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q74" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R74" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S74" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T74" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U74" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V74" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W74" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="X74" s="5" t="n">
         <v>0</v>
@@ -6401,43 +6401,43 @@
         <v>26</v>
       </c>
       <c r="K75" t="n">
+        <v>0</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0</v>
+      </c>
+      <c r="N75" t="n">
+        <v>0</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>0</v>
+      </c>
+      <c r="W75" t="n">
         <v>24</v>
-      </c>
-      <c r="L75" t="n">
-        <v>0</v>
-      </c>
-      <c r="M75" t="n">
-        <v>0</v>
-      </c>
-      <c r="N75" t="n">
-        <v>0</v>
-      </c>
-      <c r="O75" t="n">
-        <v>0</v>
-      </c>
-      <c r="P75" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q75" t="n">
-        <v>0</v>
-      </c>
-      <c r="R75" t="n">
-        <v>0</v>
-      </c>
-      <c r="S75" t="n">
-        <v>0</v>
-      </c>
-      <c r="T75" t="n">
-        <v>0</v>
-      </c>
-      <c r="U75" t="n">
-        <v>0</v>
-      </c>
-      <c r="V75" t="n">
-        <v>0</v>
-      </c>
-      <c r="W75" t="n">
-        <v>0</v>
       </c>
       <c r="X75" t="n">
         <v>0</v>
@@ -6480,46 +6480,46 @@
         <v>26</v>
       </c>
       <c r="K76" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L76" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M76" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N76" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O76" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P76" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q76" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R76" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S76" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T76" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U76" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V76" s="5" t="n"/>
+      <c r="W76" s="5" t="n">
         <v>24</v>
       </c>
-      <c r="L76" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M76" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N76" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O76" s="5" t="n"/>
-      <c r="P76" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q76" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R76" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S76" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T76" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U76" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V76" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W76" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="X76" s="5" t="n"/>
-      <c r="Y76" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="X76" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y76" s="5" t="n"/>
     </row>
     <row r="77">
       <c r="A77" s="6" t="inlineStr">
@@ -6554,6 +6554,9 @@
       <c r="J77" t="n">
         <v>26</v>
       </c>
+      <c r="K77" t="n">
+        <v>0</v>
+      </c>
       <c r="L77" t="n">
         <v>0</v>
       </c>
@@ -6585,9 +6588,6 @@
         <v>0</v>
       </c>
       <c r="V77" t="n">
-        <v>0</v>
-      </c>
-      <c r="W77" t="n">
         <v>0</v>
       </c>
       <c r="X77" t="n">
@@ -6631,43 +6631,43 @@
         <v>26</v>
       </c>
       <c r="K78" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L78" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M78" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N78" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O78" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P78" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q78" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R78" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S78" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T78" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U78" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V78" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W78" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="L78" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M78" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N78" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O78" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P78" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q78" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R78" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S78" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T78" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U78" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V78" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W78" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="X78" s="5" t="n">
         <v>0</v>
@@ -6709,6 +6709,9 @@
       <c r="J79" t="n">
         <v>26</v>
       </c>
+      <c r="K79" t="n">
+        <v>0</v>
+      </c>
       <c r="L79" t="n">
         <v>0</v>
       </c>
@@ -6740,9 +6743,6 @@
         <v>0</v>
       </c>
       <c r="V79" t="n">
-        <v>0</v>
-      </c>
-      <c r="W79" t="n">
         <v>0</v>
       </c>
       <c r="X79" t="n">
@@ -6785,7 +6785,9 @@
       <c r="J80" s="5" t="n">
         <v>26</v>
       </c>
-      <c r="K80" s="5" t="n"/>
+      <c r="K80" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="L80" s="5" t="n">
         <v>0</v>
       </c>
@@ -6819,9 +6821,7 @@
       <c r="V80" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="W80" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="W80" s="5" t="n"/>
       <c r="X80" s="5" t="n">
         <v>0</v>
       </c>
@@ -6863,43 +6863,43 @@
         <v>26</v>
       </c>
       <c r="K81" t="n">
+        <v>0</v>
+      </c>
+      <c r="L81" t="n">
+        <v>0</v>
+      </c>
+      <c r="M81" t="n">
+        <v>0</v>
+      </c>
+      <c r="N81" t="n">
+        <v>0</v>
+      </c>
+      <c r="O81" t="n">
+        <v>0</v>
+      </c>
+      <c r="P81" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q81" t="n">
+        <v>0</v>
+      </c>
+      <c r="R81" t="n">
+        <v>0</v>
+      </c>
+      <c r="S81" t="n">
+        <v>0</v>
+      </c>
+      <c r="T81" t="n">
+        <v>0</v>
+      </c>
+      <c r="U81" t="n">
+        <v>0</v>
+      </c>
+      <c r="V81" t="n">
+        <v>0</v>
+      </c>
+      <c r="W81" t="n">
         <v>24</v>
-      </c>
-      <c r="L81" t="n">
-        <v>0</v>
-      </c>
-      <c r="M81" t="n">
-        <v>0</v>
-      </c>
-      <c r="N81" t="n">
-        <v>0</v>
-      </c>
-      <c r="O81" t="n">
-        <v>0</v>
-      </c>
-      <c r="P81" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q81" t="n">
-        <v>0</v>
-      </c>
-      <c r="R81" t="n">
-        <v>0</v>
-      </c>
-      <c r="S81" t="n">
-        <v>0</v>
-      </c>
-      <c r="T81" t="n">
-        <v>0</v>
-      </c>
-      <c r="U81" t="n">
-        <v>0</v>
-      </c>
-      <c r="V81" t="n">
-        <v>0</v>
-      </c>
-      <c r="W81" t="n">
-        <v>0</v>
       </c>
       <c r="X81" t="n">
         <v>0</v>
@@ -6941,7 +6941,9 @@
       <c r="J82" s="5" t="n">
         <v>26</v>
       </c>
-      <c r="K82" s="5" t="n"/>
+      <c r="K82" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="L82" s="5" t="n">
         <v>0</v>
       </c>
@@ -6975,9 +6977,7 @@
       <c r="V82" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="W82" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="W82" s="5" t="n"/>
       <c r="X82" s="5" t="n">
         <v>0</v>
       </c>
@@ -7016,43 +7016,43 @@
         <v>26</v>
       </c>
       <c r="K83" t="n">
+        <v>0</v>
+      </c>
+      <c r="L83" t="n">
+        <v>0</v>
+      </c>
+      <c r="M83" t="n">
+        <v>0</v>
+      </c>
+      <c r="N83" t="n">
+        <v>0</v>
+      </c>
+      <c r="O83" t="n">
+        <v>0</v>
+      </c>
+      <c r="P83" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q83" t="n">
+        <v>0</v>
+      </c>
+      <c r="R83" t="n">
+        <v>0</v>
+      </c>
+      <c r="S83" t="n">
+        <v>0</v>
+      </c>
+      <c r="T83" t="n">
+        <v>0</v>
+      </c>
+      <c r="U83" t="n">
+        <v>0</v>
+      </c>
+      <c r="V83" t="n">
+        <v>0</v>
+      </c>
+      <c r="W83" t="n">
         <v>24</v>
-      </c>
-      <c r="L83" t="n">
-        <v>0</v>
-      </c>
-      <c r="M83" t="n">
-        <v>0</v>
-      </c>
-      <c r="N83" t="n">
-        <v>0</v>
-      </c>
-      <c r="O83" t="n">
-        <v>0</v>
-      </c>
-      <c r="P83" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q83" t="n">
-        <v>0</v>
-      </c>
-      <c r="R83" t="n">
-        <v>0</v>
-      </c>
-      <c r="S83" t="n">
-        <v>0</v>
-      </c>
-      <c r="T83" t="n">
-        <v>0</v>
-      </c>
-      <c r="U83" t="n">
-        <v>0</v>
-      </c>
-      <c r="V83" t="n">
-        <v>0</v>
-      </c>
-      <c r="W83" t="n">
-        <v>0</v>
       </c>
       <c r="X83" t="n">
         <v>0</v>
@@ -7095,43 +7095,43 @@
         <v>26</v>
       </c>
       <c r="K84" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L84" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M84" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N84" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O84" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P84" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q84" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R84" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S84" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T84" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U84" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V84" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W84" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="L84" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M84" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N84" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O84" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P84" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q84" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R84" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S84" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T84" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U84" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V84" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W84" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="X84" s="5" t="n">
         <v>0</v>
@@ -7173,6 +7173,9 @@
       <c r="J85" t="n">
         <v>15</v>
       </c>
+      <c r="K85" t="n">
+        <v>0</v>
+      </c>
       <c r="L85" t="n">
         <v>0</v>
       </c>
@@ -7204,9 +7207,6 @@
         <v>0</v>
       </c>
       <c r="V85" t="n">
-        <v>0</v>
-      </c>
-      <c r="W85" t="n">
         <v>0</v>
       </c>
       <c r="X85" t="n">
@@ -7249,7 +7249,9 @@
       <c r="J86" s="5" t="n">
         <v>12</v>
       </c>
-      <c r="K86" s="5" t="n"/>
+      <c r="K86" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="L86" s="5" t="n">
         <v>0</v>
       </c>
@@ -7283,9 +7285,7 @@
       <c r="V86" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="W86" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="W86" s="5" t="n"/>
       <c r="X86" s="5" t="n">
         <v>0</v>
       </c>
@@ -7326,6 +7326,9 @@
       <c r="J87" t="n">
         <v>12</v>
       </c>
+      <c r="K87" t="n">
+        <v>0</v>
+      </c>
       <c r="L87" t="n">
         <v>0</v>
       </c>
@@ -7357,9 +7360,6 @@
         <v>0</v>
       </c>
       <c r="V87" t="n">
-        <v>0</v>
-      </c>
-      <c r="W87" t="n">
         <v>0</v>
       </c>
       <c r="X87" t="n">
@@ -7402,7 +7402,9 @@
       <c r="J88" s="5" t="n">
         <v>14</v>
       </c>
-      <c r="K88" s="5" t="n"/>
+      <c r="K88" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="L88" s="5" t="n">
         <v>0</v>
       </c>
@@ -7436,9 +7438,7 @@
       <c r="V88" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="W88" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="W88" s="5" t="n"/>
       <c r="X88" s="5" t="n">
         <v>0</v>
       </c>
@@ -7479,6 +7479,9 @@
       <c r="J89" t="n">
         <v>19</v>
       </c>
+      <c r="K89" t="n">
+        <v>0</v>
+      </c>
       <c r="L89" t="n">
         <v>0</v>
       </c>
@@ -7510,9 +7513,6 @@
         <v>0</v>
       </c>
       <c r="V89" t="n">
-        <v>0</v>
-      </c>
-      <c r="W89" t="n">
         <v>0</v>
       </c>
       <c r="X89" t="n">
@@ -7554,43 +7554,43 @@
       </c>
       <c r="J90" s="5" t="n"/>
       <c r="K90" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L90" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M90" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N90" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O90" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P90" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q90" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R90" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S90" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T90" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U90" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V90" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W90" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="L90" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M90" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N90" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O90" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P90" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q90" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R90" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S90" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T90" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U90" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V90" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W90" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="X90" s="5" t="n">
         <v>0</v>
@@ -7632,6 +7632,9 @@
       <c r="J91" t="n">
         <v>19</v>
       </c>
+      <c r="K91" t="n">
+        <v>0</v>
+      </c>
       <c r="L91" t="n">
         <v>0</v>
       </c>
@@ -7663,9 +7666,6 @@
         <v>0</v>
       </c>
       <c r="V91" t="n">
-        <v>0</v>
-      </c>
-      <c r="W91" t="n">
         <v>0</v>
       </c>
       <c r="X91" t="n">
@@ -7708,7 +7708,9 @@
       <c r="J92" s="5" t="n">
         <v>19</v>
       </c>
-      <c r="K92" s="5" t="n"/>
+      <c r="K92" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="L92" s="5" t="n">
         <v>0</v>
       </c>
@@ -7742,9 +7744,7 @@
       <c r="V92" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="W92" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="W92" s="5" t="n"/>
       <c r="X92" s="5" t="n">
         <v>0</v>
       </c>
@@ -7785,6 +7785,9 @@
       <c r="J93" t="n">
         <v>23</v>
       </c>
+      <c r="K93" t="n">
+        <v>0</v>
+      </c>
       <c r="L93" t="n">
         <v>0</v>
       </c>
@@ -7816,9 +7819,6 @@
         <v>0</v>
       </c>
       <c r="V93" t="n">
-        <v>0</v>
-      </c>
-      <c r="W93" t="n">
         <v>0</v>
       </c>
       <c r="X93" t="n">
@@ -7861,7 +7861,9 @@
       <c r="J94" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="K94" s="5" t="n"/>
+      <c r="K94" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="L94" s="5" t="n">
         <v>0</v>
       </c>
@@ -7895,9 +7897,7 @@
       <c r="V94" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="W94" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="W94" s="5" t="n"/>
       <c r="X94" s="5" t="n">
         <v>0</v>
       </c>
@@ -7938,6 +7938,9 @@
       <c r="J95" t="n">
         <v>40</v>
       </c>
+      <c r="K95" t="n">
+        <v>0</v>
+      </c>
       <c r="L95" t="n">
         <v>0</v>
       </c>
@@ -7969,9 +7972,6 @@
         <v>0</v>
       </c>
       <c r="V95" t="n">
-        <v>0</v>
-      </c>
-      <c r="W95" t="n">
         <v>0</v>
       </c>
       <c r="X95" t="n">
@@ -8014,7 +8014,9 @@
       <c r="J96" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="K96" s="5" t="n"/>
+      <c r="K96" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="L96" s="5" t="n">
         <v>0</v>
       </c>
@@ -8048,9 +8050,7 @@
       <c r="V96" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="W96" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="W96" s="5" t="n"/>
       <c r="X96" s="5" t="n">
         <v>0</v>
       </c>
@@ -8088,6 +8088,9 @@
       <c r="J97" t="n">
         <v>20</v>
       </c>
+      <c r="K97" t="n">
+        <v>0</v>
+      </c>
       <c r="L97" t="n">
         <v>0</v>
       </c>
@@ -8119,9 +8122,6 @@
         <v>0</v>
       </c>
       <c r="V97" t="n">
-        <v>0</v>
-      </c>
-      <c r="W97" t="n">
         <v>0</v>
       </c>
       <c r="X97" t="n">
@@ -8164,7 +8164,9 @@
       <c r="J98" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="K98" s="5" t="n"/>
+      <c r="K98" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="L98" s="5" t="n">
         <v>0</v>
       </c>
@@ -8198,9 +8200,7 @@
       <c r="V98" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="W98" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="W98" s="5" t="n"/>
       <c r="X98" s="5" t="n">
         <v>0</v>
       </c>
@@ -8241,6 +8241,9 @@
       <c r="J99" t="n">
         <v>20</v>
       </c>
+      <c r="K99" t="n">
+        <v>0</v>
+      </c>
       <c r="L99" t="n">
         <v>0</v>
       </c>
@@ -8272,9 +8275,6 @@
         <v>0</v>
       </c>
       <c r="V99" t="n">
-        <v>0</v>
-      </c>
-      <c r="W99" t="n">
         <v>0</v>
       </c>
       <c r="X99" t="n">
@@ -8317,7 +8317,9 @@
       <c r="J100" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="K100" s="5" t="n"/>
+      <c r="K100" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="L100" s="5" t="n">
         <v>0</v>
       </c>
@@ -8351,9 +8353,7 @@
       <c r="V100" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="W100" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="W100" s="5" t="n"/>
       <c r="X100" s="5" t="n">
         <v>0</v>
       </c>
@@ -8394,6 +8394,9 @@
       <c r="J101" t="n">
         <v>20</v>
       </c>
+      <c r="K101" t="n">
+        <v>0</v>
+      </c>
       <c r="L101" t="n">
         <v>0</v>
       </c>
@@ -8425,9 +8428,6 @@
         <v>0</v>
       </c>
       <c r="V101" t="n">
-        <v>0</v>
-      </c>
-      <c r="W101" t="n">
         <v>0</v>
       </c>
       <c r="X101" t="n">
@@ -8470,7 +8470,9 @@
       <c r="J102" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="K102" s="5" t="n"/>
+      <c r="K102" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="L102" s="5" t="n">
         <v>0</v>
       </c>
@@ -8504,9 +8506,7 @@
       <c r="V102" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="W102" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="W102" s="5" t="n"/>
       <c r="X102" s="5" t="n">
         <v>0</v>
       </c>
@@ -8547,6 +8547,9 @@
       <c r="J103" t="n">
         <v>26</v>
       </c>
+      <c r="K103" t="n">
+        <v>0</v>
+      </c>
       <c r="L103" t="n">
         <v>0</v>
       </c>
@@ -8578,9 +8581,6 @@
         <v>0</v>
       </c>
       <c r="V103" t="n">
-        <v>0</v>
-      </c>
-      <c r="W103" t="n">
         <v>0</v>
       </c>
       <c r="X103" t="n">
@@ -8623,7 +8623,9 @@
       <c r="J104" s="5" t="n">
         <v>26</v>
       </c>
-      <c r="K104" s="5" t="n"/>
+      <c r="K104" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="L104" s="5" t="n">
         <v>0</v>
       </c>
@@ -8657,9 +8659,7 @@
       <c r="V104" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="W104" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="W104" s="5" t="n"/>
       <c r="X104" s="5" t="n">
         <v>0</v>
       </c>
@@ -8700,6 +8700,9 @@
       <c r="J105" t="n">
         <v>26</v>
       </c>
+      <c r="K105" t="n">
+        <v>0</v>
+      </c>
       <c r="L105" t="n">
         <v>0</v>
       </c>
@@ -8731,9 +8734,6 @@
         <v>0</v>
       </c>
       <c r="V105" t="n">
-        <v>0</v>
-      </c>
-      <c r="W105" t="n">
         <v>0</v>
       </c>
       <c r="X105" t="n">
@@ -8776,7 +8776,9 @@
       <c r="J106" s="5" t="n">
         <v>26</v>
       </c>
-      <c r="K106" s="5" t="n"/>
+      <c r="K106" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="L106" s="5" t="n">
         <v>0</v>
       </c>
@@ -8810,9 +8812,7 @@
       <c r="V106" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="W106" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="W106" s="5" t="n"/>
       <c r="X106" s="5" t="n">
         <v>0</v>
       </c>
@@ -8853,6 +8853,9 @@
       <c r="J107" t="n">
         <v>26</v>
       </c>
+      <c r="K107" t="n">
+        <v>0</v>
+      </c>
       <c r="L107" t="n">
         <v>0</v>
       </c>
@@ -8886,13 +8889,87 @@
       <c r="V107" t="n">
         <v>0</v>
       </c>
-      <c r="W107" t="n">
-        <v>0</v>
-      </c>
       <c r="X107" t="n">
         <v>0</v>
       </c>
       <c r="Y107" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B108" s="5" t="n">
+        <v>884</v>
+      </c>
+      <c r="C108" s="5" t="n">
+        <v>469</v>
+      </c>
+      <c r="D108" s="5" t="n">
+        <v>327</v>
+      </c>
+      <c r="E108" s="5" t="n">
+        <v>284</v>
+      </c>
+      <c r="F108" s="5" t="n">
+        <v>217</v>
+      </c>
+      <c r="G108" s="5" t="n">
+        <v>123</v>
+      </c>
+      <c r="H108" s="5" t="n">
+        <v>101</v>
+      </c>
+      <c r="I108" s="5" t="n">
+        <v>42</v>
+      </c>
+      <c r="J108" s="5" t="n">
+        <v>26</v>
+      </c>
+      <c r="K108" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L108" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M108" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N108" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O108" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P108" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q108" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R108" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S108" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T108" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U108" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V108" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W108" s="5" t="n"/>
+      <c r="X108" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y108" s="5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8934,7 +9011,7 @@
       </c>
       <c r="D1" s="3" t="inlineStr">
         <is>
-          <t>Lager (2026-10-21)</t>
+          <t>Lager (2026-10-22)</t>
         </is>
       </c>
     </row>
@@ -8955,7 +9032,7 @@
         </is>
       </c>
       <c r="D2" s="4" t="n">
-        <v>475</v>
+        <v>469</v>
       </c>
     </row>
     <row r="3">
@@ -27481,12 +27558,12 @@
     <row r="929">
       <c r="A929" s="6" t="inlineStr">
         <is>
-          <t>7018057</t>
+          <t>7016803</t>
         </is>
       </c>
       <c r="B929" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense TW</t>
+          <t>Interiörarmatur Sense TW rund</t>
         </is>
       </c>
       <c r="C929" t="inlineStr">
@@ -27501,12 +27578,12 @@
     <row r="930">
       <c r="A930" s="4" t="inlineStr">
         <is>
-          <t>7018056</t>
+          <t>7016818</t>
         </is>
       </c>
       <c r="B930" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense TW</t>
+          <t>Interiörarmatur Sense TW rund</t>
         </is>
       </c>
       <c r="C930" s="5" t="inlineStr">
@@ -27521,7 +27598,7 @@
     <row r="931">
       <c r="A931" s="6" t="inlineStr">
         <is>
-          <t>7016803</t>
+          <t>7016819</t>
         </is>
       </c>
       <c r="B931" t="inlineStr">
@@ -27541,7 +27618,7 @@
     <row r="932">
       <c r="A932" s="4" t="inlineStr">
         <is>
-          <t>7016818</t>
+          <t>7016820</t>
         </is>
       </c>
       <c r="B932" s="5" t="inlineStr">
@@ -27561,7 +27638,7 @@
     <row r="933">
       <c r="A933" s="6" t="inlineStr">
         <is>
-          <t>7016819</t>
+          <t>7016822</t>
         </is>
       </c>
       <c r="B933" t="inlineStr">
@@ -27581,12 +27658,12 @@
     <row r="934">
       <c r="A934" s="4" t="inlineStr">
         <is>
-          <t>7016820</t>
+          <t>7018056</t>
         </is>
       </c>
       <c r="B934" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense TW rund</t>
+          <t>Interiörarmatur Sense TW, Kvadratisk</t>
         </is>
       </c>
       <c r="C934" s="5" t="inlineStr">
@@ -27601,12 +27678,12 @@
     <row r="935">
       <c r="A935" s="6" t="inlineStr">
         <is>
-          <t>7016822</t>
+          <t>7018057</t>
         </is>
       </c>
       <c r="B935" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense TW rund</t>
+          <t>Interiörarmatur Sense TW, Rektangulär</t>
         </is>
       </c>
       <c r="C935" t="inlineStr">
@@ -27626,7 +27703,7 @@
       </c>
       <c r="B936" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense TW rund</t>
+          <t>Interiörarmatur Sense TW, Rund</t>
         </is>
       </c>
       <c r="C936" s="5" t="inlineStr">
@@ -28435,7 +28512,7 @@
         </is>
       </c>
       <c r="D976" s="4" t="n">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="977">
@@ -32455,7 +32532,7 @@
         </is>
       </c>
       <c r="D1177" s="6" t="n">
-        <v>481</v>
+        <v>455</v>
       </c>
     </row>
     <row r="1178">

--- a/data/ahlsell_led_panel_inventory.xlsx
+++ b/data/ahlsell_led_panel_inventory.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y109"/>
+  <dimension ref="A1:Y112"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -538,77 +538,77 @@
       </c>
       <c r="K1" s="3" t="inlineStr">
         <is>
+          <t>Airam</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="inlineStr">
+        <is>
+          <t>Siteco</t>
+        </is>
+      </c>
+      <c r="M1" s="3" t="inlineStr">
+        <is>
+          <t>Ensto</t>
+        </is>
+      </c>
+      <c r="N1" s="3" t="inlineStr">
+        <is>
+          <t>Norwesco</t>
+        </is>
+      </c>
+      <c r="O1" s="3" t="inlineStr">
+        <is>
+          <t>ANETA LIGHTING</t>
+        </is>
+      </c>
+      <c r="P1" s="3" t="inlineStr">
+        <is>
           <t>ZG Lighting</t>
         </is>
       </c>
-      <c r="L1" s="3" t="inlineStr">
+      <c r="Q1" s="3" t="inlineStr">
+        <is>
+          <t>Westal</t>
+        </is>
+      </c>
+      <c r="R1" s="3" t="inlineStr">
+        <is>
+          <t>Nokalux</t>
+        </is>
+      </c>
+      <c r="S1" s="3" t="inlineStr">
         <is>
           <t>Esylux</t>
         </is>
       </c>
-      <c r="M1" s="3" t="inlineStr">
+      <c r="T1" s="3" t="inlineStr">
+        <is>
+          <t>Black Box</t>
+        </is>
+      </c>
+      <c r="U1" s="3" t="inlineStr">
+        <is>
+          <t>Legrand</t>
+        </is>
+      </c>
+      <c r="V1" s="3" t="inlineStr">
+        <is>
+          <t>Bergdahls</t>
+        </is>
+      </c>
+      <c r="W1" s="3" t="inlineStr">
+        <is>
+          <t>Philips</t>
+        </is>
+      </c>
+      <c r="X1" s="3" t="inlineStr">
+        <is>
+          <t>THORN</t>
+        </is>
+      </c>
+      <c r="Y1" s="3" t="inlineStr">
         <is>
           <t>Easyform</t>
-        </is>
-      </c>
-      <c r="N1" s="3" t="inlineStr">
-        <is>
-          <t>Ensto</t>
-        </is>
-      </c>
-      <c r="O1" s="3" t="inlineStr">
-        <is>
-          <t>Airam</t>
-        </is>
-      </c>
-      <c r="P1" s="3" t="inlineStr">
-        <is>
-          <t>Siteco</t>
-        </is>
-      </c>
-      <c r="Q1" s="3" t="inlineStr">
-        <is>
-          <t>Legrand</t>
-        </is>
-      </c>
-      <c r="R1" s="3" t="inlineStr">
-        <is>
-          <t>Philips</t>
-        </is>
-      </c>
-      <c r="S1" s="3" t="inlineStr">
-        <is>
-          <t>Bergdahls</t>
-        </is>
-      </c>
-      <c r="T1" s="3" t="inlineStr">
-        <is>
-          <t>Westal</t>
-        </is>
-      </c>
-      <c r="U1" s="3" t="inlineStr">
-        <is>
-          <t>Black Box</t>
-        </is>
-      </c>
-      <c r="V1" s="3" t="inlineStr">
-        <is>
-          <t>THORN</t>
-        </is>
-      </c>
-      <c r="W1" s="3" t="inlineStr">
-        <is>
-          <t>Nokalux</t>
-        </is>
-      </c>
-      <c r="X1" s="3" t="inlineStr">
-        <is>
-          <t>ANETA LIGHTING</t>
-        </is>
-      </c>
-      <c r="Y1" s="3" t="inlineStr">
-        <is>
-          <t>Norwesco</t>
         </is>
       </c>
     </row>
@@ -649,28 +649,28 @@
         <v>0</v>
       </c>
       <c r="L2" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q2" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R2" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S2" s="5" t="n">
         <v>25</v>
-      </c>
-      <c r="M2" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N2" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O2" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P2" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q2" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R2" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S2" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="T2" s="5" t="n">
         <v>0</v>
@@ -728,28 +728,28 @@
         <v>0</v>
       </c>
       <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" t="n">
         <v>25</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S3" t="n">
-        <v>0</v>
       </c>
       <c r="T3" t="n">
         <v>0</v>
@@ -807,28 +807,28 @@
         <v>0</v>
       </c>
       <c r="L4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" s="5" t="n">
         <v>25</v>
-      </c>
-      <c r="M4" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O4" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q4" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R4" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S4" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="T4" s="5" t="n">
         <v>0</v>
@@ -886,28 +886,28 @@
         <v>0</v>
       </c>
       <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
         <v>24</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" t="n">
-        <v>0</v>
       </c>
       <c r="T5" t="n">
         <v>0</v>
@@ -965,28 +965,28 @@
         <v>0</v>
       </c>
       <c r="L6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="M6" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R6" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S6" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="T6" s="5" t="n">
         <v>0</v>
@@ -1041,28 +1041,28 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
         <v>24</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>0</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="n">
-        <v>0</v>
       </c>
       <c r="T7" t="n">
         <v>0</v>
@@ -1120,28 +1120,28 @@
         <v>0</v>
       </c>
       <c r="L8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="M8" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R8" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="T8" s="5" t="n">
         <v>0</v>
@@ -1199,28 +1199,28 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
         <v>24</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>0</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" t="n">
-        <v>0</v>
       </c>
       <c r="T9" t="n">
         <v>0</v>
@@ -1278,28 +1278,28 @@
         <v>0</v>
       </c>
       <c r="L10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="M10" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R10" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="T10" s="5" t="n">
         <v>0</v>
@@ -1357,28 +1357,28 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
         <v>24</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>0</v>
-      </c>
-      <c r="R11" t="n">
-        <v>0</v>
-      </c>
-      <c r="S11" t="n">
-        <v>0</v>
       </c>
       <c r="T11" t="n">
         <v>0</v>
@@ -1436,28 +1436,28 @@
         <v>0</v>
       </c>
       <c r="L12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="M12" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R12" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="T12" s="5" t="n">
         <v>0</v>
@@ -1515,28 +1515,28 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
         <v>24</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>0</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" t="n">
-        <v>0</v>
       </c>
       <c r="T13" t="n">
         <v>0</v>
@@ -1594,28 +1594,28 @@
         <v>0</v>
       </c>
       <c r="L14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="M14" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R14" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S14" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="T14" s="5" t="n">
         <v>0</v>
@@ -1673,28 +1673,28 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
         <v>24</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>0</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" t="n">
-        <v>0</v>
       </c>
       <c r="T15" t="n">
         <v>0</v>
@@ -1752,28 +1752,28 @@
         <v>0</v>
       </c>
       <c r="L16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="M16" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R16" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S16" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="T16" s="5" t="n">
         <v>0</v>
@@ -1831,28 +1831,28 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
         <v>24</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>0</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" t="n">
-        <v>0</v>
       </c>
       <c r="T17" t="n">
         <v>0</v>
@@ -1910,28 +1910,28 @@
         <v>0</v>
       </c>
       <c r="L18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="M18" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R18" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S18" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="T18" s="5" t="n">
         <v>0</v>
@@ -1989,28 +1989,28 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
         <v>24</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>0</v>
-      </c>
-      <c r="R19" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" t="n">
-        <v>0</v>
       </c>
       <c r="T19" t="n">
         <v>0</v>
@@ -2068,28 +2068,28 @@
         <v>0</v>
       </c>
       <c r="L20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="M20" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O20" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q20" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R20" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S20" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="T20" s="5" t="n">
         <v>0</v>
@@ -2147,28 +2147,28 @@
         <v>0</v>
       </c>
       <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>0</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" t="n">
         <v>24</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" t="n">
-        <v>0</v>
-      </c>
-      <c r="O21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>0</v>
-      </c>
-      <c r="R21" t="n">
-        <v>0</v>
-      </c>
-      <c r="S21" t="n">
-        <v>0</v>
       </c>
       <c r="T21" t="n">
         <v>0</v>
@@ -2226,28 +2226,28 @@
         <v>0</v>
       </c>
       <c r="L22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="M22" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N22" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O22" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q22" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R22" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S22" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="T22" s="5" t="n">
         <v>0</v>
@@ -2305,28 +2305,28 @@
         <v>0</v>
       </c>
       <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>0</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0</v>
+      </c>
+      <c r="S23" t="n">
         <v>24</v>
-      </c>
-      <c r="M23" t="n">
-        <v>0</v>
-      </c>
-      <c r="N23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>0</v>
-      </c>
-      <c r="R23" t="n">
-        <v>0</v>
-      </c>
-      <c r="S23" t="n">
-        <v>0</v>
       </c>
       <c r="T23" t="n">
         <v>0</v>
@@ -2384,28 +2384,28 @@
         <v>0</v>
       </c>
       <c r="L24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S24" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="M24" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N24" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O24" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P24" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q24" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R24" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S24" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="T24" s="5" t="n">
         <v>0</v>
@@ -2463,28 +2463,28 @@
         <v>0</v>
       </c>
       <c r="L25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>0</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0</v>
+      </c>
+      <c r="S25" t="n">
         <v>24</v>
-      </c>
-      <c r="M25" t="n">
-        <v>0</v>
-      </c>
-      <c r="N25" t="n">
-        <v>0</v>
-      </c>
-      <c r="O25" t="n">
-        <v>0</v>
-      </c>
-      <c r="P25" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>0</v>
-      </c>
-      <c r="R25" t="n">
-        <v>0</v>
-      </c>
-      <c r="S25" t="n">
-        <v>0</v>
       </c>
       <c r="T25" t="n">
         <v>0</v>
@@ -2542,28 +2542,28 @@
         <v>0</v>
       </c>
       <c r="L26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S26" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="M26" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N26" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O26" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P26" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q26" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R26" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S26" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="T26" s="5" t="n">
         <v>0</v>
@@ -2621,28 +2621,28 @@
         <v>0</v>
       </c>
       <c r="L27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>0</v>
+      </c>
+      <c r="R27" t="n">
+        <v>0</v>
+      </c>
+      <c r="S27" t="n">
         <v>24</v>
-      </c>
-      <c r="M27" t="n">
-        <v>0</v>
-      </c>
-      <c r="N27" t="n">
-        <v>0</v>
-      </c>
-      <c r="O27" t="n">
-        <v>0</v>
-      </c>
-      <c r="P27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>0</v>
-      </c>
-      <c r="R27" t="n">
-        <v>0</v>
-      </c>
-      <c r="S27" t="n">
-        <v>0</v>
       </c>
       <c r="T27" t="n">
         <v>0</v>
@@ -2779,28 +2779,28 @@
         <v>0</v>
       </c>
       <c r="L29" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>0</v>
+      </c>
+      <c r="R29" t="n">
+        <v>0</v>
+      </c>
+      <c r="S29" t="n">
         <v>24</v>
-      </c>
-      <c r="M29" t="n">
-        <v>0</v>
-      </c>
-      <c r="N29" t="n">
-        <v>0</v>
-      </c>
-      <c r="O29" t="n">
-        <v>0</v>
-      </c>
-      <c r="P29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>0</v>
-      </c>
-      <c r="R29" t="n">
-        <v>0</v>
-      </c>
-      <c r="S29" t="n">
-        <v>0</v>
       </c>
       <c r="T29" t="n">
         <v>0</v>
@@ -2858,28 +2858,28 @@
         <v>0</v>
       </c>
       <c r="L30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S30" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="M30" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N30" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O30" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P30" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q30" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R30" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S30" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="T30" s="5" t="n">
         <v>0</v>
@@ -2937,28 +2937,28 @@
         <v>0</v>
       </c>
       <c r="L31" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" t="n">
+        <v>0</v>
+      </c>
+      <c r="N31" t="n">
+        <v>0</v>
+      </c>
+      <c r="O31" t="n">
+        <v>0</v>
+      </c>
+      <c r="P31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>0</v>
+      </c>
+      <c r="R31" t="n">
+        <v>0</v>
+      </c>
+      <c r="S31" t="n">
         <v>24</v>
-      </c>
-      <c r="M31" t="n">
-        <v>0</v>
-      </c>
-      <c r="N31" t="n">
-        <v>0</v>
-      </c>
-      <c r="O31" t="n">
-        <v>0</v>
-      </c>
-      <c r="P31" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>0</v>
-      </c>
-      <c r="R31" t="n">
-        <v>0</v>
-      </c>
-      <c r="S31" t="n">
-        <v>0</v>
       </c>
       <c r="T31" t="n">
         <v>0</v>
@@ -3016,28 +3016,28 @@
         <v>0</v>
       </c>
       <c r="L32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S32" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="M32" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N32" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O32" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P32" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q32" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R32" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S32" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="T32" s="5" t="n">
         <v>0</v>
@@ -3095,28 +3095,28 @@
         <v>0</v>
       </c>
       <c r="L33" t="n">
+        <v>0</v>
+      </c>
+      <c r="M33" t="n">
+        <v>0</v>
+      </c>
+      <c r="N33" t="n">
+        <v>0</v>
+      </c>
+      <c r="O33" t="n">
+        <v>0</v>
+      </c>
+      <c r="P33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>0</v>
+      </c>
+      <c r="R33" t="n">
+        <v>0</v>
+      </c>
+      <c r="S33" t="n">
         <v>24</v>
-      </c>
-      <c r="M33" t="n">
-        <v>0</v>
-      </c>
-      <c r="N33" t="n">
-        <v>0</v>
-      </c>
-      <c r="O33" t="n">
-        <v>0</v>
-      </c>
-      <c r="P33" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>0</v>
-      </c>
-      <c r="R33" t="n">
-        <v>0</v>
-      </c>
-      <c r="S33" t="n">
-        <v>0</v>
       </c>
       <c r="T33" t="n">
         <v>0</v>
@@ -3174,28 +3174,28 @@
         <v>0</v>
       </c>
       <c r="L34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S34" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="M34" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N34" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O34" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P34" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q34" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R34" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S34" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="T34" s="5" t="n">
         <v>0</v>
@@ -3253,28 +3253,28 @@
         <v>0</v>
       </c>
       <c r="L35" t="n">
+        <v>0</v>
+      </c>
+      <c r="M35" t="n">
+        <v>0</v>
+      </c>
+      <c r="N35" t="n">
+        <v>0</v>
+      </c>
+      <c r="O35" t="n">
+        <v>0</v>
+      </c>
+      <c r="P35" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>0</v>
+      </c>
+      <c r="R35" t="n">
+        <v>0</v>
+      </c>
+      <c r="S35" t="n">
         <v>24</v>
-      </c>
-      <c r="M35" t="n">
-        <v>0</v>
-      </c>
-      <c r="N35" t="n">
-        <v>0</v>
-      </c>
-      <c r="O35" t="n">
-        <v>0</v>
-      </c>
-      <c r="P35" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q35" t="n">
-        <v>0</v>
-      </c>
-      <c r="R35" t="n">
-        <v>0</v>
-      </c>
-      <c r="S35" t="n">
-        <v>0</v>
       </c>
       <c r="T35" t="n">
         <v>0</v>
@@ -3332,28 +3332,28 @@
         <v>0</v>
       </c>
       <c r="L36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S36" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="M36" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N36" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O36" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P36" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q36" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R36" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S36" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="T36" s="5" t="n">
         <v>0</v>
@@ -3411,28 +3411,28 @@
         <v>0</v>
       </c>
       <c r="L37" t="n">
+        <v>0</v>
+      </c>
+      <c r="M37" t="n">
+        <v>0</v>
+      </c>
+      <c r="N37" t="n">
+        <v>0</v>
+      </c>
+      <c r="O37" t="n">
+        <v>0</v>
+      </c>
+      <c r="P37" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>0</v>
+      </c>
+      <c r="R37" t="n">
+        <v>0</v>
+      </c>
+      <c r="S37" t="n">
         <v>24</v>
-      </c>
-      <c r="M37" t="n">
-        <v>0</v>
-      </c>
-      <c r="N37" t="n">
-        <v>0</v>
-      </c>
-      <c r="O37" t="n">
-        <v>0</v>
-      </c>
-      <c r="P37" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q37" t="n">
-        <v>0</v>
-      </c>
-      <c r="R37" t="n">
-        <v>0</v>
-      </c>
-      <c r="S37" t="n">
-        <v>0</v>
       </c>
       <c r="T37" t="n">
         <v>0</v>
@@ -3490,28 +3490,28 @@
         <v>0</v>
       </c>
       <c r="L38" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M38" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N38" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O38" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P38" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q38" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R38" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S38" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="M38" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N38" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O38" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P38" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q38" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R38" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S38" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="T38" s="5" t="n">
         <v>0</v>
@@ -3569,28 +3569,28 @@
         <v>0</v>
       </c>
       <c r="L39" t="n">
+        <v>0</v>
+      </c>
+      <c r="M39" t="n">
+        <v>0</v>
+      </c>
+      <c r="N39" t="n">
+        <v>0</v>
+      </c>
+      <c r="O39" t="n">
+        <v>0</v>
+      </c>
+      <c r="P39" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>0</v>
+      </c>
+      <c r="R39" t="n">
+        <v>0</v>
+      </c>
+      <c r="S39" t="n">
         <v>24</v>
-      </c>
-      <c r="M39" t="n">
-        <v>0</v>
-      </c>
-      <c r="N39" t="n">
-        <v>0</v>
-      </c>
-      <c r="O39" t="n">
-        <v>0</v>
-      </c>
-      <c r="P39" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q39" t="n">
-        <v>0</v>
-      </c>
-      <c r="R39" t="n">
-        <v>0</v>
-      </c>
-      <c r="S39" t="n">
-        <v>0</v>
       </c>
       <c r="T39" t="n">
         <v>0</v>
@@ -3648,28 +3648,28 @@
         <v>0</v>
       </c>
       <c r="L40" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M40" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N40" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O40" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P40" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q40" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R40" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S40" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="M40" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N40" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O40" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P40" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q40" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R40" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S40" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="T40" s="5" t="n">
         <v>0</v>
@@ -3727,28 +3727,28 @@
         <v>0</v>
       </c>
       <c r="L41" t="n">
+        <v>0</v>
+      </c>
+      <c r="M41" t="n">
+        <v>0</v>
+      </c>
+      <c r="N41" t="n">
+        <v>0</v>
+      </c>
+      <c r="O41" t="n">
+        <v>0</v>
+      </c>
+      <c r="P41" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>0</v>
+      </c>
+      <c r="R41" t="n">
+        <v>0</v>
+      </c>
+      <c r="S41" t="n">
         <v>24</v>
-      </c>
-      <c r="M41" t="n">
-        <v>0</v>
-      </c>
-      <c r="N41" t="n">
-        <v>0</v>
-      </c>
-      <c r="O41" t="n">
-        <v>0</v>
-      </c>
-      <c r="P41" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q41" t="n">
-        <v>0</v>
-      </c>
-      <c r="R41" t="n">
-        <v>0</v>
-      </c>
-      <c r="S41" t="n">
-        <v>0</v>
       </c>
       <c r="T41" t="n">
         <v>0</v>
@@ -3806,28 +3806,28 @@
         <v>0</v>
       </c>
       <c r="L42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S42" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="M42" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N42" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O42" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P42" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q42" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R42" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S42" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="T42" s="5" t="n">
         <v>0</v>
@@ -3885,28 +3885,28 @@
         <v>0</v>
       </c>
       <c r="L43" t="n">
+        <v>0</v>
+      </c>
+      <c r="M43" t="n">
+        <v>0</v>
+      </c>
+      <c r="N43" t="n">
+        <v>0</v>
+      </c>
+      <c r="O43" t="n">
+        <v>0</v>
+      </c>
+      <c r="P43" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>0</v>
+      </c>
+      <c r="R43" t="n">
+        <v>0</v>
+      </c>
+      <c r="S43" t="n">
         <v>24</v>
-      </c>
-      <c r="M43" t="n">
-        <v>0</v>
-      </c>
-      <c r="N43" t="n">
-        <v>0</v>
-      </c>
-      <c r="O43" t="n">
-        <v>0</v>
-      </c>
-      <c r="P43" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q43" t="n">
-        <v>0</v>
-      </c>
-      <c r="R43" t="n">
-        <v>0</v>
-      </c>
-      <c r="S43" t="n">
-        <v>0</v>
       </c>
       <c r="T43" t="n">
         <v>0</v>
@@ -3964,28 +3964,28 @@
         <v>0</v>
       </c>
       <c r="L44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S44" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="M44" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N44" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O44" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P44" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q44" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R44" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S44" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="T44" s="5" t="n">
         <v>0</v>
@@ -4043,28 +4043,28 @@
         <v>0</v>
       </c>
       <c r="L45" t="n">
+        <v>0</v>
+      </c>
+      <c r="M45" t="n">
+        <v>0</v>
+      </c>
+      <c r="N45" t="n">
+        <v>0</v>
+      </c>
+      <c r="O45" t="n">
+        <v>0</v>
+      </c>
+      <c r="P45" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>0</v>
+      </c>
+      <c r="R45" t="n">
+        <v>0</v>
+      </c>
+      <c r="S45" t="n">
         <v>24</v>
-      </c>
-      <c r="M45" t="n">
-        <v>0</v>
-      </c>
-      <c r="N45" t="n">
-        <v>0</v>
-      </c>
-      <c r="O45" t="n">
-        <v>0</v>
-      </c>
-      <c r="P45" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q45" t="n">
-        <v>0</v>
-      </c>
-      <c r="R45" t="n">
-        <v>0</v>
-      </c>
-      <c r="S45" t="n">
-        <v>0</v>
       </c>
       <c r="T45" t="n">
         <v>0</v>
@@ -4122,28 +4122,28 @@
         <v>0</v>
       </c>
       <c r="L46" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M46" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N46" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O46" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P46" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q46" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R46" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S46" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="M46" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N46" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O46" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P46" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q46" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R46" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S46" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="T46" s="5" t="n">
         <v>0</v>
@@ -4201,28 +4201,28 @@
         <v>0</v>
       </c>
       <c r="L47" t="n">
+        <v>0</v>
+      </c>
+      <c r="M47" t="n">
+        <v>0</v>
+      </c>
+      <c r="N47" t="n">
+        <v>0</v>
+      </c>
+      <c r="O47" t="n">
+        <v>0</v>
+      </c>
+      <c r="P47" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>0</v>
+      </c>
+      <c r="R47" t="n">
+        <v>0</v>
+      </c>
+      <c r="S47" t="n">
         <v>24</v>
-      </c>
-      <c r="M47" t="n">
-        <v>0</v>
-      </c>
-      <c r="N47" t="n">
-        <v>0</v>
-      </c>
-      <c r="O47" t="n">
-        <v>0</v>
-      </c>
-      <c r="P47" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q47" t="n">
-        <v>0</v>
-      </c>
-      <c r="R47" t="n">
-        <v>0</v>
-      </c>
-      <c r="S47" t="n">
-        <v>0</v>
       </c>
       <c r="T47" t="n">
         <v>0</v>
@@ -4280,28 +4280,28 @@
         <v>0</v>
       </c>
       <c r="L48" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M48" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N48" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O48" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P48" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q48" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R48" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S48" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="M48" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N48" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O48" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P48" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q48" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R48" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S48" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="T48" s="5" t="n">
         <v>0</v>
@@ -4359,28 +4359,28 @@
         <v>0</v>
       </c>
       <c r="L49" t="n">
+        <v>0</v>
+      </c>
+      <c r="M49" t="n">
+        <v>0</v>
+      </c>
+      <c r="N49" t="n">
+        <v>0</v>
+      </c>
+      <c r="O49" t="n">
+        <v>0</v>
+      </c>
+      <c r="P49" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>0</v>
+      </c>
+      <c r="R49" t="n">
+        <v>0</v>
+      </c>
+      <c r="S49" t="n">
         <v>24</v>
-      </c>
-      <c r="M49" t="n">
-        <v>0</v>
-      </c>
-      <c r="N49" t="n">
-        <v>0</v>
-      </c>
-      <c r="O49" t="n">
-        <v>0</v>
-      </c>
-      <c r="P49" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q49" t="n">
-        <v>0</v>
-      </c>
-      <c r="R49" t="n">
-        <v>0</v>
-      </c>
-      <c r="S49" t="n">
-        <v>0</v>
       </c>
       <c r="T49" t="n">
         <v>0</v>
@@ -4438,28 +4438,28 @@
         <v>0</v>
       </c>
       <c r="L50" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M50" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N50" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O50" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P50" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q50" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R50" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S50" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="M50" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N50" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O50" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P50" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q50" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R50" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S50" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="T50" s="5" t="n">
         <v>0</v>
@@ -4517,28 +4517,28 @@
         <v>0</v>
       </c>
       <c r="L51" t="n">
+        <v>0</v>
+      </c>
+      <c r="M51" t="n">
+        <v>0</v>
+      </c>
+      <c r="N51" t="n">
+        <v>0</v>
+      </c>
+      <c r="O51" t="n">
+        <v>0</v>
+      </c>
+      <c r="P51" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>0</v>
+      </c>
+      <c r="R51" t="n">
+        <v>0</v>
+      </c>
+      <c r="S51" t="n">
         <v>24</v>
-      </c>
-      <c r="M51" t="n">
-        <v>0</v>
-      </c>
-      <c r="N51" t="n">
-        <v>0</v>
-      </c>
-      <c r="O51" t="n">
-        <v>0</v>
-      </c>
-      <c r="P51" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q51" t="n">
-        <v>0</v>
-      </c>
-      <c r="R51" t="n">
-        <v>0</v>
-      </c>
-      <c r="S51" t="n">
-        <v>0</v>
       </c>
       <c r="T51" t="n">
         <v>0</v>
@@ -4596,28 +4596,28 @@
         <v>0</v>
       </c>
       <c r="L52" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M52" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N52" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O52" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P52" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q52" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R52" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S52" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="M52" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N52" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O52" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P52" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q52" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R52" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S52" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="T52" s="5" t="n">
         <v>0</v>
@@ -4675,28 +4675,28 @@
         <v>0</v>
       </c>
       <c r="L53" t="n">
+        <v>0</v>
+      </c>
+      <c r="M53" t="n">
+        <v>0</v>
+      </c>
+      <c r="N53" t="n">
+        <v>0</v>
+      </c>
+      <c r="O53" t="n">
+        <v>0</v>
+      </c>
+      <c r="P53" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>0</v>
+      </c>
+      <c r="R53" t="n">
+        <v>0</v>
+      </c>
+      <c r="S53" t="n">
         <v>24</v>
-      </c>
-      <c r="M53" t="n">
-        <v>0</v>
-      </c>
-      <c r="N53" t="n">
-        <v>0</v>
-      </c>
-      <c r="O53" t="n">
-        <v>0</v>
-      </c>
-      <c r="P53" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q53" t="n">
-        <v>0</v>
-      </c>
-      <c r="R53" t="n">
-        <v>0</v>
-      </c>
-      <c r="S53" t="n">
-        <v>0</v>
       </c>
       <c r="T53" t="n">
         <v>0</v>
@@ -4754,28 +4754,28 @@
         <v>0</v>
       </c>
       <c r="L54" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M54" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N54" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O54" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P54" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q54" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R54" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S54" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="M54" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N54" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O54" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P54" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q54" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R54" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S54" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="T54" s="5" t="n">
         <v>0</v>
@@ -4833,28 +4833,28 @@
         <v>0</v>
       </c>
       <c r="L55" t="n">
+        <v>0</v>
+      </c>
+      <c r="M55" t="n">
+        <v>0</v>
+      </c>
+      <c r="N55" t="n">
+        <v>0</v>
+      </c>
+      <c r="O55" t="n">
+        <v>0</v>
+      </c>
+      <c r="P55" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>0</v>
+      </c>
+      <c r="R55" t="n">
+        <v>0</v>
+      </c>
+      <c r="S55" t="n">
         <v>24</v>
-      </c>
-      <c r="M55" t="n">
-        <v>0</v>
-      </c>
-      <c r="N55" t="n">
-        <v>0</v>
-      </c>
-      <c r="O55" t="n">
-        <v>0</v>
-      </c>
-      <c r="P55" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q55" t="n">
-        <v>0</v>
-      </c>
-      <c r="R55" t="n">
-        <v>0</v>
-      </c>
-      <c r="S55" t="n">
-        <v>0</v>
       </c>
       <c r="T55" t="n">
         <v>0</v>
@@ -4912,28 +4912,28 @@
         <v>0</v>
       </c>
       <c r="L56" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M56" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N56" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O56" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P56" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q56" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R56" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S56" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="M56" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N56" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O56" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P56" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q56" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R56" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S56" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="T56" s="5" t="n">
         <v>0</v>
@@ -4991,28 +4991,28 @@
         <v>0</v>
       </c>
       <c r="L57" t="n">
+        <v>0</v>
+      </c>
+      <c r="M57" t="n">
+        <v>0</v>
+      </c>
+      <c r="N57" t="n">
+        <v>0</v>
+      </c>
+      <c r="O57" t="n">
+        <v>0</v>
+      </c>
+      <c r="P57" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>0</v>
+      </c>
+      <c r="R57" t="n">
+        <v>0</v>
+      </c>
+      <c r="S57" t="n">
         <v>24</v>
-      </c>
-      <c r="M57" t="n">
-        <v>0</v>
-      </c>
-      <c r="N57" t="n">
-        <v>0</v>
-      </c>
-      <c r="O57" t="n">
-        <v>0</v>
-      </c>
-      <c r="P57" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q57" t="n">
-        <v>0</v>
-      </c>
-      <c r="R57" t="n">
-        <v>0</v>
-      </c>
-      <c r="S57" t="n">
-        <v>0</v>
       </c>
       <c r="T57" t="n">
         <v>0</v>
@@ -5070,28 +5070,28 @@
         <v>0</v>
       </c>
       <c r="L58" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M58" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N58" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O58" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P58" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q58" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R58" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S58" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="M58" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N58" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O58" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P58" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q58" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R58" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S58" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="T58" s="5" t="n">
         <v>0</v>
@@ -5149,28 +5149,28 @@
         <v>0</v>
       </c>
       <c r="L59" t="n">
+        <v>0</v>
+      </c>
+      <c r="M59" t="n">
+        <v>0</v>
+      </c>
+      <c r="N59" t="n">
+        <v>0</v>
+      </c>
+      <c r="O59" t="n">
+        <v>0</v>
+      </c>
+      <c r="P59" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>0</v>
+      </c>
+      <c r="R59" t="n">
+        <v>0</v>
+      </c>
+      <c r="S59" t="n">
         <v>24</v>
-      </c>
-      <c r="M59" t="n">
-        <v>0</v>
-      </c>
-      <c r="N59" t="n">
-        <v>0</v>
-      </c>
-      <c r="O59" t="n">
-        <v>0</v>
-      </c>
-      <c r="P59" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q59" t="n">
-        <v>0</v>
-      </c>
-      <c r="R59" t="n">
-        <v>0</v>
-      </c>
-      <c r="S59" t="n">
-        <v>0</v>
       </c>
       <c r="T59" t="n">
         <v>0</v>
@@ -5228,28 +5228,28 @@
         <v>0</v>
       </c>
       <c r="L60" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M60" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N60" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O60" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P60" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q60" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R60" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S60" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="M60" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N60" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O60" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P60" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q60" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R60" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S60" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="T60" s="5" t="n">
         <v>0</v>
@@ -5307,28 +5307,28 @@
         <v>0</v>
       </c>
       <c r="L61" t="n">
+        <v>0</v>
+      </c>
+      <c r="M61" t="n">
+        <v>0</v>
+      </c>
+      <c r="N61" t="n">
+        <v>0</v>
+      </c>
+      <c r="O61" t="n">
+        <v>0</v>
+      </c>
+      <c r="P61" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q61" t="n">
+        <v>0</v>
+      </c>
+      <c r="R61" t="n">
+        <v>0</v>
+      </c>
+      <c r="S61" t="n">
         <v>24</v>
-      </c>
-      <c r="M61" t="n">
-        <v>0</v>
-      </c>
-      <c r="N61" t="n">
-        <v>0</v>
-      </c>
-      <c r="O61" t="n">
-        <v>0</v>
-      </c>
-      <c r="P61" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q61" t="n">
-        <v>0</v>
-      </c>
-      <c r="R61" t="n">
-        <v>0</v>
-      </c>
-      <c r="S61" t="n">
-        <v>0</v>
       </c>
       <c r="T61" t="n">
         <v>0</v>
@@ -5386,28 +5386,28 @@
         <v>0</v>
       </c>
       <c r="L62" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M62" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N62" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O62" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P62" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q62" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R62" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S62" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="M62" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N62" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O62" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P62" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q62" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R62" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S62" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="T62" s="5" t="n">
         <v>0</v>
@@ -5465,28 +5465,28 @@
         <v>0</v>
       </c>
       <c r="L63" t="n">
+        <v>0</v>
+      </c>
+      <c r="M63" t="n">
+        <v>0</v>
+      </c>
+      <c r="N63" t="n">
+        <v>0</v>
+      </c>
+      <c r="O63" t="n">
+        <v>0</v>
+      </c>
+      <c r="P63" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q63" t="n">
+        <v>0</v>
+      </c>
+      <c r="R63" t="n">
+        <v>0</v>
+      </c>
+      <c r="S63" t="n">
         <v>24</v>
-      </c>
-      <c r="M63" t="n">
-        <v>0</v>
-      </c>
-      <c r="N63" t="n">
-        <v>0</v>
-      </c>
-      <c r="O63" t="n">
-        <v>0</v>
-      </c>
-      <c r="P63" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q63" t="n">
-        <v>0</v>
-      </c>
-      <c r="R63" t="n">
-        <v>0</v>
-      </c>
-      <c r="S63" t="n">
-        <v>0</v>
       </c>
       <c r="T63" t="n">
         <v>0</v>
@@ -5544,28 +5544,28 @@
         <v>0</v>
       </c>
       <c r="L64" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M64" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N64" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O64" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P64" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q64" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R64" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S64" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="M64" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N64" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O64" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P64" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q64" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R64" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S64" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="T64" s="5" t="n">
         <v>0</v>
@@ -5623,28 +5623,28 @@
         <v>0</v>
       </c>
       <c r="L65" t="n">
+        <v>0</v>
+      </c>
+      <c r="M65" t="n">
+        <v>0</v>
+      </c>
+      <c r="N65" t="n">
+        <v>0</v>
+      </c>
+      <c r="O65" t="n">
+        <v>0</v>
+      </c>
+      <c r="P65" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q65" t="n">
+        <v>0</v>
+      </c>
+      <c r="R65" t="n">
+        <v>0</v>
+      </c>
+      <c r="S65" t="n">
         <v>24</v>
-      </c>
-      <c r="M65" t="n">
-        <v>0</v>
-      </c>
-      <c r="N65" t="n">
-        <v>0</v>
-      </c>
-      <c r="O65" t="n">
-        <v>0</v>
-      </c>
-      <c r="P65" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q65" t="n">
-        <v>0</v>
-      </c>
-      <c r="R65" t="n">
-        <v>0</v>
-      </c>
-      <c r="S65" t="n">
-        <v>0</v>
       </c>
       <c r="T65" t="n">
         <v>0</v>
@@ -5702,28 +5702,28 @@
         <v>0</v>
       </c>
       <c r="L66" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M66" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N66" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O66" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P66" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q66" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R66" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S66" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="M66" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N66" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O66" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P66" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q66" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R66" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S66" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="T66" s="5" t="n">
         <v>0</v>
@@ -5780,6 +5780,9 @@
       <c r="K67" t="n">
         <v>0</v>
       </c>
+      <c r="L67" t="n">
+        <v>0</v>
+      </c>
       <c r="M67" t="n">
         <v>0</v>
       </c>
@@ -5796,9 +5799,6 @@
         <v>0</v>
       </c>
       <c r="R67" t="n">
-        <v>0</v>
-      </c>
-      <c r="S67" t="n">
         <v>0</v>
       </c>
       <c r="T67" t="n">
@@ -5857,28 +5857,28 @@
         <v>0</v>
       </c>
       <c r="L68" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M68" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N68" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O68" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P68" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q68" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R68" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S68" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="M68" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N68" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O68" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P68" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q68" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R68" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S68" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="T68" s="5" t="n">
         <v>0</v>
@@ -5932,6 +5932,9 @@
       <c r="K69" t="n">
         <v>0</v>
       </c>
+      <c r="L69" t="n">
+        <v>0</v>
+      </c>
       <c r="M69" t="n">
         <v>0</v>
       </c>
@@ -5948,9 +5951,6 @@
         <v>0</v>
       </c>
       <c r="R69" t="n">
-        <v>0</v>
-      </c>
-      <c r="S69" t="n">
         <v>0</v>
       </c>
       <c r="T69" t="n">
@@ -6009,28 +6009,28 @@
         <v>0</v>
       </c>
       <c r="L70" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M70" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N70" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O70" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P70" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q70" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R70" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S70" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="M70" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N70" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O70" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P70" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q70" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R70" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S70" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="T70" s="5" t="n">
         <v>0</v>
@@ -6088,28 +6088,28 @@
         <v>0</v>
       </c>
       <c r="L71" t="n">
+        <v>0</v>
+      </c>
+      <c r="M71" t="n">
+        <v>0</v>
+      </c>
+      <c r="N71" t="n">
+        <v>0</v>
+      </c>
+      <c r="O71" t="n">
+        <v>0</v>
+      </c>
+      <c r="P71" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q71" t="n">
+        <v>0</v>
+      </c>
+      <c r="R71" t="n">
+        <v>0</v>
+      </c>
+      <c r="S71" t="n">
         <v>24</v>
-      </c>
-      <c r="M71" t="n">
-        <v>0</v>
-      </c>
-      <c r="N71" t="n">
-        <v>0</v>
-      </c>
-      <c r="O71" t="n">
-        <v>0</v>
-      </c>
-      <c r="P71" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q71" t="n">
-        <v>0</v>
-      </c>
-      <c r="R71" t="n">
-        <v>0</v>
-      </c>
-      <c r="S71" t="n">
-        <v>0</v>
       </c>
       <c r="T71" t="n">
         <v>0</v>
@@ -6167,28 +6167,28 @@
         <v>0</v>
       </c>
       <c r="L72" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M72" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N72" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O72" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P72" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q72" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R72" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S72" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="M72" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N72" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O72" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P72" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q72" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R72" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S72" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="T72" s="5" t="n">
         <v>0</v>
@@ -6246,28 +6246,28 @@
         <v>0</v>
       </c>
       <c r="L73" t="n">
+        <v>0</v>
+      </c>
+      <c r="M73" t="n">
+        <v>0</v>
+      </c>
+      <c r="N73" t="n">
+        <v>0</v>
+      </c>
+      <c r="O73" t="n">
+        <v>0</v>
+      </c>
+      <c r="P73" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q73" t="n">
+        <v>0</v>
+      </c>
+      <c r="R73" t="n">
+        <v>0</v>
+      </c>
+      <c r="S73" t="n">
         <v>24</v>
-      </c>
-      <c r="M73" t="n">
-        <v>0</v>
-      </c>
-      <c r="N73" t="n">
-        <v>0</v>
-      </c>
-      <c r="O73" t="n">
-        <v>0</v>
-      </c>
-      <c r="P73" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q73" t="n">
-        <v>0</v>
-      </c>
-      <c r="R73" t="n">
-        <v>0</v>
-      </c>
-      <c r="S73" t="n">
-        <v>0</v>
       </c>
       <c r="T73" t="n">
         <v>0</v>
@@ -6325,28 +6325,28 @@
         <v>0</v>
       </c>
       <c r="L74" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M74" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N74" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O74" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P74" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q74" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R74" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S74" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="M74" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N74" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O74" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P74" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q74" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R74" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S74" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="T74" s="5" t="n">
         <v>0</v>
@@ -6404,28 +6404,28 @@
         <v>0</v>
       </c>
       <c r="L75" t="n">
+        <v>0</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0</v>
+      </c>
+      <c r="N75" t="n">
+        <v>0</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
         <v>24</v>
-      </c>
-      <c r="M75" t="n">
-        <v>0</v>
-      </c>
-      <c r="N75" t="n">
-        <v>0</v>
-      </c>
-      <c r="O75" t="n">
-        <v>0</v>
-      </c>
-      <c r="P75" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q75" t="n">
-        <v>0</v>
-      </c>
-      <c r="R75" t="n">
-        <v>0</v>
-      </c>
-      <c r="S75" t="n">
-        <v>0</v>
       </c>
       <c r="T75" t="n">
         <v>0</v>
@@ -6483,30 +6483,30 @@
         <v>0</v>
       </c>
       <c r="L76" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M76" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N76" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O76" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P76" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q76" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R76" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S76" s="5" t="n">
         <v>24</v>
       </c>
-      <c r="M76" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N76" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O76" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P76" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q76" s="5" t="n"/>
-      <c r="R76" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S76" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T76" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="T76" s="5" t="n"/>
       <c r="U76" s="5" t="n"/>
       <c r="V76" s="5" t="n">
         <v>0</v>
@@ -6557,6 +6557,9 @@
       <c r="K77" t="n">
         <v>0</v>
       </c>
+      <c r="L77" t="n">
+        <v>0</v>
+      </c>
       <c r="M77" t="n">
         <v>0</v>
       </c>
@@ -6573,9 +6576,6 @@
         <v>0</v>
       </c>
       <c r="R77" t="n">
-        <v>0</v>
-      </c>
-      <c r="S77" t="n">
         <v>0</v>
       </c>
       <c r="T77" t="n">
@@ -6634,28 +6634,28 @@
         <v>0</v>
       </c>
       <c r="L78" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M78" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N78" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O78" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P78" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q78" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R78" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S78" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="M78" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N78" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O78" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P78" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q78" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R78" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S78" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="T78" s="5" t="n">
         <v>0</v>
@@ -6712,6 +6712,9 @@
       <c r="K79" t="n">
         <v>0</v>
       </c>
+      <c r="L79" t="n">
+        <v>0</v>
+      </c>
       <c r="M79" t="n">
         <v>0</v>
       </c>
@@ -6728,9 +6731,6 @@
         <v>0</v>
       </c>
       <c r="R79" t="n">
-        <v>0</v>
-      </c>
-      <c r="S79" t="n">
         <v>0</v>
       </c>
       <c r="T79" t="n">
@@ -6788,7 +6788,9 @@
       <c r="K80" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="L80" s="5" t="n"/>
+      <c r="L80" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="M80" s="5" t="n">
         <v>0</v>
       </c>
@@ -6807,9 +6809,7 @@
       <c r="R80" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="S80" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="S80" s="5" t="n"/>
       <c r="T80" s="5" t="n">
         <v>0</v>
       </c>
@@ -6866,28 +6866,28 @@
         <v>0</v>
       </c>
       <c r="L81" t="n">
+        <v>0</v>
+      </c>
+      <c r="M81" t="n">
+        <v>0</v>
+      </c>
+      <c r="N81" t="n">
+        <v>0</v>
+      </c>
+      <c r="O81" t="n">
+        <v>0</v>
+      </c>
+      <c r="P81" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q81" t="n">
+        <v>0</v>
+      </c>
+      <c r="R81" t="n">
+        <v>0</v>
+      </c>
+      <c r="S81" t="n">
         <v>24</v>
-      </c>
-      <c r="M81" t="n">
-        <v>0</v>
-      </c>
-      <c r="N81" t="n">
-        <v>0</v>
-      </c>
-      <c r="O81" t="n">
-        <v>0</v>
-      </c>
-      <c r="P81" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q81" t="n">
-        <v>0</v>
-      </c>
-      <c r="R81" t="n">
-        <v>0</v>
-      </c>
-      <c r="S81" t="n">
-        <v>0</v>
       </c>
       <c r="T81" t="n">
         <v>0</v>
@@ -6944,7 +6944,9 @@
       <c r="K82" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="L82" s="5" t="n"/>
+      <c r="L82" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="M82" s="5" t="n">
         <v>0</v>
       </c>
@@ -6963,9 +6965,7 @@
       <c r="R82" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="S82" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="S82" s="5" t="n"/>
       <c r="T82" s="5" t="n">
         <v>0</v>
       </c>
@@ -7019,28 +7019,28 @@
         <v>0</v>
       </c>
       <c r="L83" t="n">
+        <v>0</v>
+      </c>
+      <c r="M83" t="n">
+        <v>0</v>
+      </c>
+      <c r="N83" t="n">
+        <v>0</v>
+      </c>
+      <c r="O83" t="n">
+        <v>0</v>
+      </c>
+      <c r="P83" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q83" t="n">
+        <v>0</v>
+      </c>
+      <c r="R83" t="n">
+        <v>0</v>
+      </c>
+      <c r="S83" t="n">
         <v>24</v>
-      </c>
-      <c r="M83" t="n">
-        <v>0</v>
-      </c>
-      <c r="N83" t="n">
-        <v>0</v>
-      </c>
-      <c r="O83" t="n">
-        <v>0</v>
-      </c>
-      <c r="P83" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q83" t="n">
-        <v>0</v>
-      </c>
-      <c r="R83" t="n">
-        <v>0</v>
-      </c>
-      <c r="S83" t="n">
-        <v>0</v>
       </c>
       <c r="T83" t="n">
         <v>0</v>
@@ -7098,28 +7098,28 @@
         <v>0</v>
       </c>
       <c r="L84" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M84" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N84" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O84" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P84" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q84" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R84" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S84" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="M84" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N84" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O84" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P84" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q84" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R84" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S84" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="T84" s="5" t="n">
         <v>0</v>
@@ -7176,6 +7176,9 @@
       <c r="K85" t="n">
         <v>0</v>
       </c>
+      <c r="L85" t="n">
+        <v>0</v>
+      </c>
       <c r="M85" t="n">
         <v>0</v>
       </c>
@@ -7192,9 +7195,6 @@
         <v>0</v>
       </c>
       <c r="R85" t="n">
-        <v>0</v>
-      </c>
-      <c r="S85" t="n">
         <v>0</v>
       </c>
       <c r="T85" t="n">
@@ -7252,7 +7252,9 @@
       <c r="K86" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="L86" s="5" t="n"/>
+      <c r="L86" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="M86" s="5" t="n">
         <v>0</v>
       </c>
@@ -7271,9 +7273,7 @@
       <c r="R86" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="S86" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="S86" s="5" t="n"/>
       <c r="T86" s="5" t="n">
         <v>0</v>
       </c>
@@ -7329,6 +7329,9 @@
       <c r="K87" t="n">
         <v>0</v>
       </c>
+      <c r="L87" t="n">
+        <v>0</v>
+      </c>
       <c r="M87" t="n">
         <v>0</v>
       </c>
@@ -7345,9 +7348,6 @@
         <v>0</v>
       </c>
       <c r="R87" t="n">
-        <v>0</v>
-      </c>
-      <c r="S87" t="n">
         <v>0</v>
       </c>
       <c r="T87" t="n">
@@ -7405,7 +7405,9 @@
       <c r="K88" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="L88" s="5" t="n"/>
+      <c r="L88" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="M88" s="5" t="n">
         <v>0</v>
       </c>
@@ -7424,9 +7426,7 @@
       <c r="R88" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="S88" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="S88" s="5" t="n"/>
       <c r="T88" s="5" t="n">
         <v>0</v>
       </c>
@@ -7482,6 +7482,9 @@
       <c r="K89" t="n">
         <v>0</v>
       </c>
+      <c r="L89" t="n">
+        <v>0</v>
+      </c>
       <c r="M89" t="n">
         <v>0</v>
       </c>
@@ -7498,9 +7501,6 @@
         <v>0</v>
       </c>
       <c r="R89" t="n">
-        <v>0</v>
-      </c>
-      <c r="S89" t="n">
         <v>0</v>
       </c>
       <c r="T89" t="n">
@@ -7557,28 +7557,28 @@
         <v>0</v>
       </c>
       <c r="L90" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M90" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N90" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O90" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P90" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q90" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R90" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S90" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="M90" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N90" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O90" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P90" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q90" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R90" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S90" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="T90" s="5" t="n">
         <v>0</v>
@@ -7635,6 +7635,9 @@
       <c r="K91" t="n">
         <v>0</v>
       </c>
+      <c r="L91" t="n">
+        <v>0</v>
+      </c>
       <c r="M91" t="n">
         <v>0</v>
       </c>
@@ -7651,9 +7654,6 @@
         <v>0</v>
       </c>
       <c r="R91" t="n">
-        <v>0</v>
-      </c>
-      <c r="S91" t="n">
         <v>0</v>
       </c>
       <c r="T91" t="n">
@@ -7711,7 +7711,9 @@
       <c r="K92" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="L92" s="5" t="n"/>
+      <c r="L92" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="M92" s="5" t="n">
         <v>0</v>
       </c>
@@ -7730,9 +7732,7 @@
       <c r="R92" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="S92" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="S92" s="5" t="n"/>
       <c r="T92" s="5" t="n">
         <v>0</v>
       </c>
@@ -7788,6 +7788,9 @@
       <c r="K93" t="n">
         <v>0</v>
       </c>
+      <c r="L93" t="n">
+        <v>0</v>
+      </c>
       <c r="M93" t="n">
         <v>0</v>
       </c>
@@ -7804,9 +7807,6 @@
         <v>0</v>
       </c>
       <c r="R93" t="n">
-        <v>0</v>
-      </c>
-      <c r="S93" t="n">
         <v>0</v>
       </c>
       <c r="T93" t="n">
@@ -7864,7 +7864,9 @@
       <c r="K94" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="L94" s="5" t="n"/>
+      <c r="L94" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="M94" s="5" t="n">
         <v>0</v>
       </c>
@@ -7883,9 +7885,7 @@
       <c r="R94" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="S94" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="S94" s="5" t="n"/>
       <c r="T94" s="5" t="n">
         <v>0</v>
       </c>
@@ -7941,6 +7941,9 @@
       <c r="K95" t="n">
         <v>0</v>
       </c>
+      <c r="L95" t="n">
+        <v>0</v>
+      </c>
       <c r="M95" t="n">
         <v>0</v>
       </c>
@@ -7957,9 +7960,6 @@
         <v>0</v>
       </c>
       <c r="R95" t="n">
-        <v>0</v>
-      </c>
-      <c r="S95" t="n">
         <v>0</v>
       </c>
       <c r="T95" t="n">
@@ -8017,7 +8017,9 @@
       <c r="K96" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="L96" s="5" t="n"/>
+      <c r="L96" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="M96" s="5" t="n">
         <v>0</v>
       </c>
@@ -8036,9 +8038,7 @@
       <c r="R96" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="S96" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="S96" s="5" t="n"/>
       <c r="T96" s="5" t="n">
         <v>0</v>
       </c>
@@ -8091,6 +8091,9 @@
       <c r="K97" t="n">
         <v>0</v>
       </c>
+      <c r="L97" t="n">
+        <v>0</v>
+      </c>
       <c r="M97" t="n">
         <v>0</v>
       </c>
@@ -8107,9 +8110,6 @@
         <v>0</v>
       </c>
       <c r="R97" t="n">
-        <v>0</v>
-      </c>
-      <c r="S97" t="n">
         <v>0</v>
       </c>
       <c r="T97" t="n">
@@ -8167,7 +8167,9 @@
       <c r="K98" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="L98" s="5" t="n"/>
+      <c r="L98" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="M98" s="5" t="n">
         <v>0</v>
       </c>
@@ -8186,9 +8188,7 @@
       <c r="R98" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="S98" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="S98" s="5" t="n"/>
       <c r="T98" s="5" t="n">
         <v>0</v>
       </c>
@@ -8244,6 +8244,9 @@
       <c r="K99" t="n">
         <v>0</v>
       </c>
+      <c r="L99" t="n">
+        <v>0</v>
+      </c>
       <c r="M99" t="n">
         <v>0</v>
       </c>
@@ -8260,9 +8263,6 @@
         <v>0</v>
       </c>
       <c r="R99" t="n">
-        <v>0</v>
-      </c>
-      <c r="S99" t="n">
         <v>0</v>
       </c>
       <c r="T99" t="n">
@@ -8320,7 +8320,9 @@
       <c r="K100" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="L100" s="5" t="n"/>
+      <c r="L100" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="M100" s="5" t="n">
         <v>0</v>
       </c>
@@ -8339,9 +8341,7 @@
       <c r="R100" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="S100" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="S100" s="5" t="n"/>
       <c r="T100" s="5" t="n">
         <v>0</v>
       </c>
@@ -8397,6 +8397,9 @@
       <c r="K101" t="n">
         <v>0</v>
       </c>
+      <c r="L101" t="n">
+        <v>0</v>
+      </c>
       <c r="M101" t="n">
         <v>0</v>
       </c>
@@ -8413,9 +8416,6 @@
         <v>0</v>
       </c>
       <c r="R101" t="n">
-        <v>0</v>
-      </c>
-      <c r="S101" t="n">
         <v>0</v>
       </c>
       <c r="T101" t="n">
@@ -8473,7 +8473,9 @@
       <c r="K102" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="L102" s="5" t="n"/>
+      <c r="L102" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="M102" s="5" t="n">
         <v>0</v>
       </c>
@@ -8492,9 +8494,7 @@
       <c r="R102" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="S102" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="S102" s="5" t="n"/>
       <c r="T102" s="5" t="n">
         <v>0</v>
       </c>
@@ -8550,6 +8550,9 @@
       <c r="K103" t="n">
         <v>0</v>
       </c>
+      <c r="L103" t="n">
+        <v>0</v>
+      </c>
       <c r="M103" t="n">
         <v>0</v>
       </c>
@@ -8566,9 +8569,6 @@
         <v>0</v>
       </c>
       <c r="R103" t="n">
-        <v>0</v>
-      </c>
-      <c r="S103" t="n">
         <v>0</v>
       </c>
       <c r="T103" t="n">
@@ -8626,7 +8626,9 @@
       <c r="K104" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="L104" s="5" t="n"/>
+      <c r="L104" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="M104" s="5" t="n">
         <v>0</v>
       </c>
@@ -8645,9 +8647,7 @@
       <c r="R104" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="S104" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="S104" s="5" t="n"/>
       <c r="T104" s="5" t="n">
         <v>0</v>
       </c>
@@ -8703,6 +8703,9 @@
       <c r="K105" t="n">
         <v>0</v>
       </c>
+      <c r="L105" t="n">
+        <v>0</v>
+      </c>
       <c r="M105" t="n">
         <v>0</v>
       </c>
@@ -8719,9 +8722,6 @@
         <v>0</v>
       </c>
       <c r="R105" t="n">
-        <v>0</v>
-      </c>
-      <c r="S105" t="n">
         <v>0</v>
       </c>
       <c r="T105" t="n">
@@ -8779,7 +8779,9 @@
       <c r="K106" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="L106" s="5" t="n"/>
+      <c r="L106" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="M106" s="5" t="n">
         <v>0</v>
       </c>
@@ -8798,9 +8800,7 @@
       <c r="R106" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="S106" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="S106" s="5" t="n"/>
       <c r="T106" s="5" t="n">
         <v>0</v>
       </c>
@@ -8856,6 +8856,9 @@
       <c r="K107" t="n">
         <v>0</v>
       </c>
+      <c r="L107" t="n">
+        <v>0</v>
+      </c>
       <c r="M107" t="n">
         <v>0</v>
       </c>
@@ -8872,9 +8875,6 @@
         <v>0</v>
       </c>
       <c r="R107" t="n">
-        <v>0</v>
-      </c>
-      <c r="S107" t="n">
         <v>0</v>
       </c>
       <c r="T107" t="n">
@@ -8932,7 +8932,9 @@
       <c r="K108" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="L108" s="5" t="n"/>
+      <c r="L108" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="M108" s="5" t="n">
         <v>0</v>
       </c>
@@ -8951,9 +8953,7 @@
       <c r="R108" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="S108" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="S108" s="5" t="n"/>
       <c r="T108" s="5" t="n">
         <v>0</v>
       </c>
@@ -9009,6 +9009,9 @@
       <c r="K109" t="n">
         <v>0</v>
       </c>
+      <c r="L109" t="n">
+        <v>0</v>
+      </c>
       <c r="M109" t="n">
         <v>0</v>
       </c>
@@ -9027,9 +9030,6 @@
       <c r="R109" t="n">
         <v>0</v>
       </c>
-      <c r="S109" t="n">
-        <v>0</v>
-      </c>
       <c r="T109" t="n">
         <v>0</v>
       </c>
@@ -9046,6 +9046,233 @@
         <v>0</v>
       </c>
       <c r="Y109" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B110" s="5" t="n">
+        <v>876</v>
+      </c>
+      <c r="C110" s="5" t="n">
+        <v>459</v>
+      </c>
+      <c r="D110" s="5" t="n">
+        <v>321</v>
+      </c>
+      <c r="E110" s="5" t="n">
+        <v>289</v>
+      </c>
+      <c r="F110" s="5" t="n">
+        <v>212</v>
+      </c>
+      <c r="G110" s="5" t="n">
+        <v>123</v>
+      </c>
+      <c r="H110" s="5" t="n">
+        <v>101</v>
+      </c>
+      <c r="I110" s="5" t="n">
+        <v>42</v>
+      </c>
+      <c r="J110" s="5" t="n">
+        <v>22</v>
+      </c>
+      <c r="K110" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L110" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M110" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N110" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O110" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P110" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q110" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R110" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S110" s="5" t="n"/>
+      <c r="T110" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U110" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V110" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W110" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X110" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y110" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="B111" t="n">
+        <v>876</v>
+      </c>
+      <c r="D111" t="n">
+        <v>321</v>
+      </c>
+      <c r="E111" t="n">
+        <v>268</v>
+      </c>
+      <c r="F111" t="n">
+        <v>212</v>
+      </c>
+      <c r="G111" t="n">
+        <v>123</v>
+      </c>
+      <c r="H111" t="n">
+        <v>101</v>
+      </c>
+      <c r="I111" t="n">
+        <v>0</v>
+      </c>
+      <c r="J111" t="n">
+        <v>22</v>
+      </c>
+      <c r="K111" t="n">
+        <v>0</v>
+      </c>
+      <c r="L111" t="n">
+        <v>0</v>
+      </c>
+      <c r="M111" t="n">
+        <v>0</v>
+      </c>
+      <c r="N111" t="n">
+        <v>0</v>
+      </c>
+      <c r="O111" t="n">
+        <v>0</v>
+      </c>
+      <c r="P111" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q111" t="n">
+        <v>0</v>
+      </c>
+      <c r="R111" t="n">
+        <v>0</v>
+      </c>
+      <c r="T111" t="n">
+        <v>0</v>
+      </c>
+      <c r="U111" t="n">
+        <v>0</v>
+      </c>
+      <c r="V111" t="n">
+        <v>0</v>
+      </c>
+      <c r="W111" t="n">
+        <v>0</v>
+      </c>
+      <c r="X111" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y111" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B112" s="5" t="n">
+        <v>876</v>
+      </c>
+      <c r="C112" s="5" t="n">
+        <v>459</v>
+      </c>
+      <c r="D112" s="5" t="n">
+        <v>321</v>
+      </c>
+      <c r="E112" s="5" t="n">
+        <v>289</v>
+      </c>
+      <c r="F112" s="5" t="n">
+        <v>212</v>
+      </c>
+      <c r="G112" s="5" t="n">
+        <v>123</v>
+      </c>
+      <c r="H112" s="5" t="n">
+        <v>101</v>
+      </c>
+      <c r="I112" s="5" t="n">
+        <v>42</v>
+      </c>
+      <c r="J112" s="5" t="n">
+        <v>22</v>
+      </c>
+      <c r="K112" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L112" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M112" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N112" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O112" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P112" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q112" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R112" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S112" s="5" t="n"/>
+      <c r="T112" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U112" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V112" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W112" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X112" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y112" s="5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9087,7 +9314,7 @@
       </c>
       <c r="D1" s="3" t="inlineStr">
         <is>
-          <t>Lager (2026-10-23)</t>
+          <t>Lager (2026-10-26)</t>
         </is>
       </c>
     </row>
@@ -9108,7 +9335,7 @@
         </is>
       </c>
       <c r="D2" s="4" t="n">
-        <v>457</v>
+        <v>459</v>
       </c>
     </row>
     <row r="3">
@@ -17668,7 +17895,7 @@
         </is>
       </c>
       <c r="D430" s="4" t="n">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="431">
@@ -30388,7 +30615,7 @@
         </is>
       </c>
       <c r="D1066" s="4" t="n">
-        <v>448</v>
+        <v>445</v>
       </c>
     </row>
     <row r="1067">

--- a/data/ahlsell_led_panel_inventory.xlsx
+++ b/data/ahlsell_led_panel_inventory.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y112"/>
+  <dimension ref="A1:Y113"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -538,77 +538,77 @@
       </c>
       <c r="K1" s="3" t="inlineStr">
         <is>
+          <t>Legrand</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="inlineStr">
+        <is>
+          <t>Norwesco</t>
+        </is>
+      </c>
+      <c r="M1" s="3" t="inlineStr">
+        <is>
+          <t>ZG Lighting</t>
+        </is>
+      </c>
+      <c r="N1" s="3" t="inlineStr">
+        <is>
+          <t>Bergdahls</t>
+        </is>
+      </c>
+      <c r="O1" s="3" t="inlineStr">
+        <is>
+          <t>Nokalux</t>
+        </is>
+      </c>
+      <c r="P1" s="3" t="inlineStr">
+        <is>
+          <t>Black Box</t>
+        </is>
+      </c>
+      <c r="Q1" s="3" t="inlineStr">
+        <is>
+          <t>ANETA LIGHTING</t>
+        </is>
+      </c>
+      <c r="R1" s="3" t="inlineStr">
+        <is>
+          <t>Siteco</t>
+        </is>
+      </c>
+      <c r="S1" s="3" t="inlineStr">
+        <is>
+          <t>Philips</t>
+        </is>
+      </c>
+      <c r="T1" s="3" t="inlineStr">
+        <is>
+          <t>THORN</t>
+        </is>
+      </c>
+      <c r="U1" s="3" t="inlineStr">
+        <is>
+          <t>Ensto</t>
+        </is>
+      </c>
+      <c r="V1" s="3" t="inlineStr">
+        <is>
+          <t>Easyform</t>
+        </is>
+      </c>
+      <c r="W1" s="3" t="inlineStr">
+        <is>
+          <t>Westal</t>
+        </is>
+      </c>
+      <c r="X1" s="3" t="inlineStr">
+        <is>
           <t>Airam</t>
         </is>
       </c>
-      <c r="L1" s="3" t="inlineStr">
-        <is>
-          <t>Siteco</t>
-        </is>
-      </c>
-      <c r="M1" s="3" t="inlineStr">
-        <is>
-          <t>Ensto</t>
-        </is>
-      </c>
-      <c r="N1" s="3" t="inlineStr">
-        <is>
-          <t>Norwesco</t>
-        </is>
-      </c>
-      <c r="O1" s="3" t="inlineStr">
-        <is>
-          <t>ANETA LIGHTING</t>
-        </is>
-      </c>
-      <c r="P1" s="3" t="inlineStr">
-        <is>
-          <t>ZG Lighting</t>
-        </is>
-      </c>
-      <c r="Q1" s="3" t="inlineStr">
-        <is>
-          <t>Westal</t>
-        </is>
-      </c>
-      <c r="R1" s="3" t="inlineStr">
-        <is>
-          <t>Nokalux</t>
-        </is>
-      </c>
-      <c r="S1" s="3" t="inlineStr">
+      <c r="Y1" s="3" t="inlineStr">
         <is>
           <t>Esylux</t>
-        </is>
-      </c>
-      <c r="T1" s="3" t="inlineStr">
-        <is>
-          <t>Black Box</t>
-        </is>
-      </c>
-      <c r="U1" s="3" t="inlineStr">
-        <is>
-          <t>Legrand</t>
-        </is>
-      </c>
-      <c r="V1" s="3" t="inlineStr">
-        <is>
-          <t>Bergdahls</t>
-        </is>
-      </c>
-      <c r="W1" s="3" t="inlineStr">
-        <is>
-          <t>Philips</t>
-        </is>
-      </c>
-      <c r="X1" s="3" t="inlineStr">
-        <is>
-          <t>THORN</t>
-        </is>
-      </c>
-      <c r="Y1" s="3" t="inlineStr">
-        <is>
-          <t>Easyform</t>
         </is>
       </c>
     </row>
@@ -670,25 +670,25 @@
         <v>0</v>
       </c>
       <c r="S2" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T2" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U2" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V2" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W2" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X2" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y2" s="5" t="n">
         <v>25</v>
-      </c>
-      <c r="T2" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U2" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V2" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W2" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="X2" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y2" s="5" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -749,25 +749,25 @@
         <v>0</v>
       </c>
       <c r="S3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y3" t="n">
         <v>25</v>
-      </c>
-      <c r="T3" t="n">
-        <v>0</v>
-      </c>
-      <c r="U3" t="n">
-        <v>0</v>
-      </c>
-      <c r="V3" t="n">
-        <v>0</v>
-      </c>
-      <c r="W3" t="n">
-        <v>0</v>
-      </c>
-      <c r="X3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -828,25 +828,25 @@
         <v>0</v>
       </c>
       <c r="S4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y4" s="5" t="n">
         <v>25</v>
-      </c>
-      <c r="T4" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U4" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V4" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W4" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="X4" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y4" s="5" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -907,25 +907,25 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y5" t="n">
         <v>24</v>
-      </c>
-      <c r="T5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W5" t="n">
-        <v>0</v>
-      </c>
-      <c r="X5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -986,25 +986,25 @@
         <v>0</v>
       </c>
       <c r="S6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y6" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="T6" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U6" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V6" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W6" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="X6" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y6" s="5" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -1062,25 +1062,25 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y7" t="n">
         <v>24</v>
-      </c>
-      <c r="T7" t="n">
-        <v>0</v>
-      </c>
-      <c r="U7" t="n">
-        <v>0</v>
-      </c>
-      <c r="V7" t="n">
-        <v>0</v>
-      </c>
-      <c r="W7" t="n">
-        <v>0</v>
-      </c>
-      <c r="X7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -1141,25 +1141,25 @@
         <v>0</v>
       </c>
       <c r="S8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y8" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="T8" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U8" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V8" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W8" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="X8" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y8" s="5" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -1220,25 +1220,25 @@
         <v>0</v>
       </c>
       <c r="S9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y9" t="n">
         <v>24</v>
-      </c>
-      <c r="T9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -1299,25 +1299,25 @@
         <v>0</v>
       </c>
       <c r="S10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y10" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="T10" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U10" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V10" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W10" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="X10" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y10" s="5" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1378,25 +1378,25 @@
         <v>0</v>
       </c>
       <c r="S11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" t="n">
+        <v>0</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" t="n">
+        <v>0</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0</v>
+      </c>
+      <c r="X11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y11" t="n">
         <v>24</v>
-      </c>
-      <c r="T11" t="n">
-        <v>0</v>
-      </c>
-      <c r="U11" t="n">
-        <v>0</v>
-      </c>
-      <c r="V11" t="n">
-        <v>0</v>
-      </c>
-      <c r="W11" t="n">
-        <v>0</v>
-      </c>
-      <c r="X11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1457,25 +1457,25 @@
         <v>0</v>
       </c>
       <c r="S12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y12" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="T12" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U12" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V12" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W12" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="X12" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y12" s="5" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1536,25 +1536,25 @@
         <v>0</v>
       </c>
       <c r="S13" t="n">
+        <v>0</v>
+      </c>
+      <c r="T13" t="n">
+        <v>0</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" t="n">
+        <v>0</v>
+      </c>
+      <c r="W13" t="n">
+        <v>0</v>
+      </c>
+      <c r="X13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y13" t="n">
         <v>24</v>
-      </c>
-      <c r="T13" t="n">
-        <v>0</v>
-      </c>
-      <c r="U13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V13" t="n">
-        <v>0</v>
-      </c>
-      <c r="W13" t="n">
-        <v>0</v>
-      </c>
-      <c r="X13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -1615,25 +1615,25 @@
         <v>0</v>
       </c>
       <c r="S14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y14" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="T14" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U14" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V14" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W14" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="X14" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y14" s="5" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -1694,25 +1694,25 @@
         <v>0</v>
       </c>
       <c r="S15" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" t="n">
+        <v>0</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0</v>
+      </c>
+      <c r="W15" t="n">
+        <v>0</v>
+      </c>
+      <c r="X15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y15" t="n">
         <v>24</v>
-      </c>
-      <c r="T15" t="n">
-        <v>0</v>
-      </c>
-      <c r="U15" t="n">
-        <v>0</v>
-      </c>
-      <c r="V15" t="n">
-        <v>0</v>
-      </c>
-      <c r="W15" t="n">
-        <v>0</v>
-      </c>
-      <c r="X15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -1773,25 +1773,25 @@
         <v>0</v>
       </c>
       <c r="S16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y16" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="T16" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U16" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V16" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W16" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="X16" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y16" s="5" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1852,25 +1852,25 @@
         <v>0</v>
       </c>
       <c r="S17" t="n">
+        <v>0</v>
+      </c>
+      <c r="T17" t="n">
+        <v>0</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" t="n">
+        <v>0</v>
+      </c>
+      <c r="W17" t="n">
+        <v>0</v>
+      </c>
+      <c r="X17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y17" t="n">
         <v>24</v>
-      </c>
-      <c r="T17" t="n">
-        <v>0</v>
-      </c>
-      <c r="U17" t="n">
-        <v>0</v>
-      </c>
-      <c r="V17" t="n">
-        <v>0</v>
-      </c>
-      <c r="W17" t="n">
-        <v>0</v>
-      </c>
-      <c r="X17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -1931,25 +1931,25 @@
         <v>0</v>
       </c>
       <c r="S18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y18" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="T18" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U18" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V18" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W18" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="X18" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y18" s="5" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2010,25 +2010,25 @@
         <v>0</v>
       </c>
       <c r="S19" t="n">
+        <v>0</v>
+      </c>
+      <c r="T19" t="n">
+        <v>0</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" t="n">
+        <v>0</v>
+      </c>
+      <c r="W19" t="n">
+        <v>0</v>
+      </c>
+      <c r="X19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y19" t="n">
         <v>24</v>
-      </c>
-      <c r="T19" t="n">
-        <v>0</v>
-      </c>
-      <c r="U19" t="n">
-        <v>0</v>
-      </c>
-      <c r="V19" t="n">
-        <v>0</v>
-      </c>
-      <c r="W19" t="n">
-        <v>0</v>
-      </c>
-      <c r="X19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2089,25 +2089,25 @@
         <v>0</v>
       </c>
       <c r="S20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y20" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="T20" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U20" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V20" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W20" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="X20" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y20" s="5" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2168,25 +2168,25 @@
         <v>0</v>
       </c>
       <c r="S21" t="n">
+        <v>0</v>
+      </c>
+      <c r="T21" t="n">
+        <v>0</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0</v>
+      </c>
+      <c r="V21" t="n">
+        <v>0</v>
+      </c>
+      <c r="W21" t="n">
+        <v>0</v>
+      </c>
+      <c r="X21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y21" t="n">
         <v>24</v>
-      </c>
-      <c r="T21" t="n">
-        <v>0</v>
-      </c>
-      <c r="U21" t="n">
-        <v>0</v>
-      </c>
-      <c r="V21" t="n">
-        <v>0</v>
-      </c>
-      <c r="W21" t="n">
-        <v>0</v>
-      </c>
-      <c r="X21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -2247,25 +2247,25 @@
         <v>0</v>
       </c>
       <c r="S22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y22" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="T22" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U22" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V22" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W22" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="X22" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y22" s="5" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -2326,25 +2326,25 @@
         <v>0</v>
       </c>
       <c r="S23" t="n">
+        <v>0</v>
+      </c>
+      <c r="T23" t="n">
+        <v>0</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0</v>
+      </c>
+      <c r="V23" t="n">
+        <v>0</v>
+      </c>
+      <c r="W23" t="n">
+        <v>0</v>
+      </c>
+      <c r="X23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y23" t="n">
         <v>24</v>
-      </c>
-      <c r="T23" t="n">
-        <v>0</v>
-      </c>
-      <c r="U23" t="n">
-        <v>0</v>
-      </c>
-      <c r="V23" t="n">
-        <v>0</v>
-      </c>
-      <c r="W23" t="n">
-        <v>0</v>
-      </c>
-      <c r="X23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -2405,25 +2405,25 @@
         <v>0</v>
       </c>
       <c r="S24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y24" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="T24" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U24" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V24" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W24" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="X24" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y24" s="5" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -2484,25 +2484,25 @@
         <v>0</v>
       </c>
       <c r="S25" t="n">
+        <v>0</v>
+      </c>
+      <c r="T25" t="n">
+        <v>0</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0</v>
+      </c>
+      <c r="V25" t="n">
+        <v>0</v>
+      </c>
+      <c r="W25" t="n">
+        <v>0</v>
+      </c>
+      <c r="X25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y25" t="n">
         <v>24</v>
-      </c>
-      <c r="T25" t="n">
-        <v>0</v>
-      </c>
-      <c r="U25" t="n">
-        <v>0</v>
-      </c>
-      <c r="V25" t="n">
-        <v>0</v>
-      </c>
-      <c r="W25" t="n">
-        <v>0</v>
-      </c>
-      <c r="X25" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -2563,25 +2563,25 @@
         <v>0</v>
       </c>
       <c r="S26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y26" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="T26" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U26" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V26" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W26" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="X26" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y26" s="5" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -2642,25 +2642,25 @@
         <v>0</v>
       </c>
       <c r="S27" t="n">
+        <v>0</v>
+      </c>
+      <c r="T27" t="n">
+        <v>0</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0</v>
+      </c>
+      <c r="V27" t="n">
+        <v>0</v>
+      </c>
+      <c r="W27" t="n">
+        <v>0</v>
+      </c>
+      <c r="X27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y27" t="n">
         <v>24</v>
-      </c>
-      <c r="T27" t="n">
-        <v>0</v>
-      </c>
-      <c r="U27" t="n">
-        <v>0</v>
-      </c>
-      <c r="V27" t="n">
-        <v>0</v>
-      </c>
-      <c r="W27" t="n">
-        <v>0</v>
-      </c>
-      <c r="X27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -2800,25 +2800,25 @@
         <v>0</v>
       </c>
       <c r="S29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T29" t="n">
+        <v>0</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0</v>
+      </c>
+      <c r="V29" t="n">
+        <v>0</v>
+      </c>
+      <c r="W29" t="n">
+        <v>0</v>
+      </c>
+      <c r="X29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y29" t="n">
         <v>24</v>
-      </c>
-      <c r="T29" t="n">
-        <v>0</v>
-      </c>
-      <c r="U29" t="n">
-        <v>0</v>
-      </c>
-      <c r="V29" t="n">
-        <v>0</v>
-      </c>
-      <c r="W29" t="n">
-        <v>0</v>
-      </c>
-      <c r="X29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -2879,25 +2879,25 @@
         <v>0</v>
       </c>
       <c r="S30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y30" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="T30" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U30" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V30" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W30" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="X30" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y30" s="5" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -2958,25 +2958,25 @@
         <v>0</v>
       </c>
       <c r="S31" t="n">
+        <v>0</v>
+      </c>
+      <c r="T31" t="n">
+        <v>0</v>
+      </c>
+      <c r="U31" t="n">
+        <v>0</v>
+      </c>
+      <c r="V31" t="n">
+        <v>0</v>
+      </c>
+      <c r="W31" t="n">
+        <v>0</v>
+      </c>
+      <c r="X31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y31" t="n">
         <v>24</v>
-      </c>
-      <c r="T31" t="n">
-        <v>0</v>
-      </c>
-      <c r="U31" t="n">
-        <v>0</v>
-      </c>
-      <c r="V31" t="n">
-        <v>0</v>
-      </c>
-      <c r="W31" t="n">
-        <v>0</v>
-      </c>
-      <c r="X31" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -3037,25 +3037,25 @@
         <v>0</v>
       </c>
       <c r="S32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y32" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="T32" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U32" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V32" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W32" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="X32" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y32" s="5" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="33">
@@ -3116,25 +3116,25 @@
         <v>0</v>
       </c>
       <c r="S33" t="n">
+        <v>0</v>
+      </c>
+      <c r="T33" t="n">
+        <v>0</v>
+      </c>
+      <c r="U33" t="n">
+        <v>0</v>
+      </c>
+      <c r="V33" t="n">
+        <v>0</v>
+      </c>
+      <c r="W33" t="n">
+        <v>0</v>
+      </c>
+      <c r="X33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y33" t="n">
         <v>24</v>
-      </c>
-      <c r="T33" t="n">
-        <v>0</v>
-      </c>
-      <c r="U33" t="n">
-        <v>0</v>
-      </c>
-      <c r="V33" t="n">
-        <v>0</v>
-      </c>
-      <c r="W33" t="n">
-        <v>0</v>
-      </c>
-      <c r="X33" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y33" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -3195,25 +3195,25 @@
         <v>0</v>
       </c>
       <c r="S34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y34" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="T34" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U34" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V34" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W34" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="X34" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y34" s="5" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="35">
@@ -3274,25 +3274,25 @@
         <v>0</v>
       </c>
       <c r="S35" t="n">
+        <v>0</v>
+      </c>
+      <c r="T35" t="n">
+        <v>0</v>
+      </c>
+      <c r="U35" t="n">
+        <v>0</v>
+      </c>
+      <c r="V35" t="n">
+        <v>0</v>
+      </c>
+      <c r="W35" t="n">
+        <v>0</v>
+      </c>
+      <c r="X35" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y35" t="n">
         <v>24</v>
-      </c>
-      <c r="T35" t="n">
-        <v>0</v>
-      </c>
-      <c r="U35" t="n">
-        <v>0</v>
-      </c>
-      <c r="V35" t="n">
-        <v>0</v>
-      </c>
-      <c r="W35" t="n">
-        <v>0</v>
-      </c>
-      <c r="X35" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y35" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -3353,25 +3353,25 @@
         <v>0</v>
       </c>
       <c r="S36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y36" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="T36" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U36" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V36" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W36" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="X36" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y36" s="5" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -3432,25 +3432,25 @@
         <v>0</v>
       </c>
       <c r="S37" t="n">
+        <v>0</v>
+      </c>
+      <c r="T37" t="n">
+        <v>0</v>
+      </c>
+      <c r="U37" t="n">
+        <v>0</v>
+      </c>
+      <c r="V37" t="n">
+        <v>0</v>
+      </c>
+      <c r="W37" t="n">
+        <v>0</v>
+      </c>
+      <c r="X37" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y37" t="n">
         <v>24</v>
-      </c>
-      <c r="T37" t="n">
-        <v>0</v>
-      </c>
-      <c r="U37" t="n">
-        <v>0</v>
-      </c>
-      <c r="V37" t="n">
-        <v>0</v>
-      </c>
-      <c r="W37" t="n">
-        <v>0</v>
-      </c>
-      <c r="X37" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y37" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -3511,25 +3511,25 @@
         <v>0</v>
       </c>
       <c r="S38" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T38" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U38" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V38" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W38" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X38" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y38" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="T38" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U38" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V38" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W38" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="X38" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y38" s="5" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -3590,25 +3590,25 @@
         <v>0</v>
       </c>
       <c r="S39" t="n">
+        <v>0</v>
+      </c>
+      <c r="T39" t="n">
+        <v>0</v>
+      </c>
+      <c r="U39" t="n">
+        <v>0</v>
+      </c>
+      <c r="V39" t="n">
+        <v>0</v>
+      </c>
+      <c r="W39" t="n">
+        <v>0</v>
+      </c>
+      <c r="X39" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y39" t="n">
         <v>24</v>
-      </c>
-      <c r="T39" t="n">
-        <v>0</v>
-      </c>
-      <c r="U39" t="n">
-        <v>0</v>
-      </c>
-      <c r="V39" t="n">
-        <v>0</v>
-      </c>
-      <c r="W39" t="n">
-        <v>0</v>
-      </c>
-      <c r="X39" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y39" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -3669,25 +3669,25 @@
         <v>0</v>
       </c>
       <c r="S40" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T40" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U40" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V40" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W40" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X40" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y40" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="T40" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U40" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V40" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W40" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="X40" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y40" s="5" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -3748,25 +3748,25 @@
         <v>0</v>
       </c>
       <c r="S41" t="n">
+        <v>0</v>
+      </c>
+      <c r="T41" t="n">
+        <v>0</v>
+      </c>
+      <c r="U41" t="n">
+        <v>0</v>
+      </c>
+      <c r="V41" t="n">
+        <v>0</v>
+      </c>
+      <c r="W41" t="n">
+        <v>0</v>
+      </c>
+      <c r="X41" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y41" t="n">
         <v>24</v>
-      </c>
-      <c r="T41" t="n">
-        <v>0</v>
-      </c>
-      <c r="U41" t="n">
-        <v>0</v>
-      </c>
-      <c r="V41" t="n">
-        <v>0</v>
-      </c>
-      <c r="W41" t="n">
-        <v>0</v>
-      </c>
-      <c r="X41" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y41" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -3827,25 +3827,25 @@
         <v>0</v>
       </c>
       <c r="S42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y42" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="T42" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U42" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V42" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W42" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="X42" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y42" s="5" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -3906,25 +3906,25 @@
         <v>0</v>
       </c>
       <c r="S43" t="n">
+        <v>0</v>
+      </c>
+      <c r="T43" t="n">
+        <v>0</v>
+      </c>
+      <c r="U43" t="n">
+        <v>0</v>
+      </c>
+      <c r="V43" t="n">
+        <v>0</v>
+      </c>
+      <c r="W43" t="n">
+        <v>0</v>
+      </c>
+      <c r="X43" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y43" t="n">
         <v>24</v>
-      </c>
-      <c r="T43" t="n">
-        <v>0</v>
-      </c>
-      <c r="U43" t="n">
-        <v>0</v>
-      </c>
-      <c r="V43" t="n">
-        <v>0</v>
-      </c>
-      <c r="W43" t="n">
-        <v>0</v>
-      </c>
-      <c r="X43" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y43" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -3985,25 +3985,25 @@
         <v>0</v>
       </c>
       <c r="S44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y44" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="T44" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U44" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V44" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W44" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="X44" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y44" s="5" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -4064,25 +4064,25 @@
         <v>0</v>
       </c>
       <c r="S45" t="n">
+        <v>0</v>
+      </c>
+      <c r="T45" t="n">
+        <v>0</v>
+      </c>
+      <c r="U45" t="n">
+        <v>0</v>
+      </c>
+      <c r="V45" t="n">
+        <v>0</v>
+      </c>
+      <c r="W45" t="n">
+        <v>0</v>
+      </c>
+      <c r="X45" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y45" t="n">
         <v>24</v>
-      </c>
-      <c r="T45" t="n">
-        <v>0</v>
-      </c>
-      <c r="U45" t="n">
-        <v>0</v>
-      </c>
-      <c r="V45" t="n">
-        <v>0</v>
-      </c>
-      <c r="W45" t="n">
-        <v>0</v>
-      </c>
-      <c r="X45" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y45" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -4143,25 +4143,25 @@
         <v>0</v>
       </c>
       <c r="S46" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T46" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U46" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V46" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W46" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X46" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y46" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="T46" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U46" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V46" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W46" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="X46" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y46" s="5" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -4222,25 +4222,25 @@
         <v>0</v>
       </c>
       <c r="S47" t="n">
+        <v>0</v>
+      </c>
+      <c r="T47" t="n">
+        <v>0</v>
+      </c>
+      <c r="U47" t="n">
+        <v>0</v>
+      </c>
+      <c r="V47" t="n">
+        <v>0</v>
+      </c>
+      <c r="W47" t="n">
+        <v>0</v>
+      </c>
+      <c r="X47" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y47" t="n">
         <v>24</v>
-      </c>
-      <c r="T47" t="n">
-        <v>0</v>
-      </c>
-      <c r="U47" t="n">
-        <v>0</v>
-      </c>
-      <c r="V47" t="n">
-        <v>0</v>
-      </c>
-      <c r="W47" t="n">
-        <v>0</v>
-      </c>
-      <c r="X47" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y47" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -4301,25 +4301,25 @@
         <v>0</v>
       </c>
       <c r="S48" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T48" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U48" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V48" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W48" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X48" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y48" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="T48" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U48" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V48" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W48" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="X48" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y48" s="5" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -4380,25 +4380,25 @@
         <v>0</v>
       </c>
       <c r="S49" t="n">
+        <v>0</v>
+      </c>
+      <c r="T49" t="n">
+        <v>0</v>
+      </c>
+      <c r="U49" t="n">
+        <v>0</v>
+      </c>
+      <c r="V49" t="n">
+        <v>0</v>
+      </c>
+      <c r="W49" t="n">
+        <v>0</v>
+      </c>
+      <c r="X49" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y49" t="n">
         <v>24</v>
-      </c>
-      <c r="T49" t="n">
-        <v>0</v>
-      </c>
-      <c r="U49" t="n">
-        <v>0</v>
-      </c>
-      <c r="V49" t="n">
-        <v>0</v>
-      </c>
-      <c r="W49" t="n">
-        <v>0</v>
-      </c>
-      <c r="X49" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y49" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="50">
@@ -4459,25 +4459,25 @@
         <v>0</v>
       </c>
       <c r="S50" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T50" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U50" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V50" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W50" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X50" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y50" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="T50" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U50" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V50" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W50" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="X50" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y50" s="5" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -4538,25 +4538,25 @@
         <v>0</v>
       </c>
       <c r="S51" t="n">
+        <v>0</v>
+      </c>
+      <c r="T51" t="n">
+        <v>0</v>
+      </c>
+      <c r="U51" t="n">
+        <v>0</v>
+      </c>
+      <c r="V51" t="n">
+        <v>0</v>
+      </c>
+      <c r="W51" t="n">
+        <v>0</v>
+      </c>
+      <c r="X51" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y51" t="n">
         <v>24</v>
-      </c>
-      <c r="T51" t="n">
-        <v>0</v>
-      </c>
-      <c r="U51" t="n">
-        <v>0</v>
-      </c>
-      <c r="V51" t="n">
-        <v>0</v>
-      </c>
-      <c r="W51" t="n">
-        <v>0</v>
-      </c>
-      <c r="X51" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y51" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -4617,25 +4617,25 @@
         <v>0</v>
       </c>
       <c r="S52" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T52" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U52" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V52" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W52" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X52" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y52" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="T52" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U52" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V52" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W52" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="X52" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y52" s="5" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -4696,25 +4696,25 @@
         <v>0</v>
       </c>
       <c r="S53" t="n">
+        <v>0</v>
+      </c>
+      <c r="T53" t="n">
+        <v>0</v>
+      </c>
+      <c r="U53" t="n">
+        <v>0</v>
+      </c>
+      <c r="V53" t="n">
+        <v>0</v>
+      </c>
+      <c r="W53" t="n">
+        <v>0</v>
+      </c>
+      <c r="X53" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y53" t="n">
         <v>24</v>
-      </c>
-      <c r="T53" t="n">
-        <v>0</v>
-      </c>
-      <c r="U53" t="n">
-        <v>0</v>
-      </c>
-      <c r="V53" t="n">
-        <v>0</v>
-      </c>
-      <c r="W53" t="n">
-        <v>0</v>
-      </c>
-      <c r="X53" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y53" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -4775,25 +4775,25 @@
         <v>0</v>
       </c>
       <c r="S54" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T54" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U54" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V54" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W54" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X54" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y54" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="T54" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U54" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V54" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W54" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="X54" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y54" s="5" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -4854,25 +4854,25 @@
         <v>0</v>
       </c>
       <c r="S55" t="n">
+        <v>0</v>
+      </c>
+      <c r="T55" t="n">
+        <v>0</v>
+      </c>
+      <c r="U55" t="n">
+        <v>0</v>
+      </c>
+      <c r="V55" t="n">
+        <v>0</v>
+      </c>
+      <c r="W55" t="n">
+        <v>0</v>
+      </c>
+      <c r="X55" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y55" t="n">
         <v>24</v>
-      </c>
-      <c r="T55" t="n">
-        <v>0</v>
-      </c>
-      <c r="U55" t="n">
-        <v>0</v>
-      </c>
-      <c r="V55" t="n">
-        <v>0</v>
-      </c>
-      <c r="W55" t="n">
-        <v>0</v>
-      </c>
-      <c r="X55" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y55" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="56">
@@ -4933,25 +4933,25 @@
         <v>0</v>
       </c>
       <c r="S56" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T56" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U56" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V56" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W56" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X56" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y56" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="T56" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U56" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V56" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W56" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="X56" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y56" s="5" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -5012,25 +5012,25 @@
         <v>0</v>
       </c>
       <c r="S57" t="n">
+        <v>0</v>
+      </c>
+      <c r="T57" t="n">
+        <v>0</v>
+      </c>
+      <c r="U57" t="n">
+        <v>0</v>
+      </c>
+      <c r="V57" t="n">
+        <v>0</v>
+      </c>
+      <c r="W57" t="n">
+        <v>0</v>
+      </c>
+      <c r="X57" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y57" t="n">
         <v>24</v>
-      </c>
-      <c r="T57" t="n">
-        <v>0</v>
-      </c>
-      <c r="U57" t="n">
-        <v>0</v>
-      </c>
-      <c r="V57" t="n">
-        <v>0</v>
-      </c>
-      <c r="W57" t="n">
-        <v>0</v>
-      </c>
-      <c r="X57" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y57" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="58">
@@ -5091,25 +5091,25 @@
         <v>0</v>
       </c>
       <c r="S58" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T58" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U58" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V58" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W58" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X58" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y58" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="T58" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U58" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V58" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W58" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="X58" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y58" s="5" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="59">
@@ -5170,25 +5170,25 @@
         <v>0</v>
       </c>
       <c r="S59" t="n">
+        <v>0</v>
+      </c>
+      <c r="T59" t="n">
+        <v>0</v>
+      </c>
+      <c r="U59" t="n">
+        <v>0</v>
+      </c>
+      <c r="V59" t="n">
+        <v>0</v>
+      </c>
+      <c r="W59" t="n">
+        <v>0</v>
+      </c>
+      <c r="X59" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y59" t="n">
         <v>24</v>
-      </c>
-      <c r="T59" t="n">
-        <v>0</v>
-      </c>
-      <c r="U59" t="n">
-        <v>0</v>
-      </c>
-      <c r="V59" t="n">
-        <v>0</v>
-      </c>
-      <c r="W59" t="n">
-        <v>0</v>
-      </c>
-      <c r="X59" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y59" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="60">
@@ -5249,25 +5249,25 @@
         <v>0</v>
       </c>
       <c r="S60" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T60" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U60" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V60" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W60" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X60" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y60" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="T60" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U60" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V60" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W60" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="X60" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y60" s="5" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="61">
@@ -5328,25 +5328,25 @@
         <v>0</v>
       </c>
       <c r="S61" t="n">
+        <v>0</v>
+      </c>
+      <c r="T61" t="n">
+        <v>0</v>
+      </c>
+      <c r="U61" t="n">
+        <v>0</v>
+      </c>
+      <c r="V61" t="n">
+        <v>0</v>
+      </c>
+      <c r="W61" t="n">
+        <v>0</v>
+      </c>
+      <c r="X61" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y61" t="n">
         <v>24</v>
-      </c>
-      <c r="T61" t="n">
-        <v>0</v>
-      </c>
-      <c r="U61" t="n">
-        <v>0</v>
-      </c>
-      <c r="V61" t="n">
-        <v>0</v>
-      </c>
-      <c r="W61" t="n">
-        <v>0</v>
-      </c>
-      <c r="X61" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y61" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="62">
@@ -5407,25 +5407,25 @@
         <v>0</v>
       </c>
       <c r="S62" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T62" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U62" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V62" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W62" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X62" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y62" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="T62" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U62" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V62" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W62" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="X62" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y62" s="5" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="63">
@@ -5486,25 +5486,25 @@
         <v>0</v>
       </c>
       <c r="S63" t="n">
+        <v>0</v>
+      </c>
+      <c r="T63" t="n">
+        <v>0</v>
+      </c>
+      <c r="U63" t="n">
+        <v>0</v>
+      </c>
+      <c r="V63" t="n">
+        <v>0</v>
+      </c>
+      <c r="W63" t="n">
+        <v>0</v>
+      </c>
+      <c r="X63" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y63" t="n">
         <v>24</v>
-      </c>
-      <c r="T63" t="n">
-        <v>0</v>
-      </c>
-      <c r="U63" t="n">
-        <v>0</v>
-      </c>
-      <c r="V63" t="n">
-        <v>0</v>
-      </c>
-      <c r="W63" t="n">
-        <v>0</v>
-      </c>
-      <c r="X63" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y63" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="64">
@@ -5565,25 +5565,25 @@
         <v>0</v>
       </c>
       <c r="S64" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T64" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U64" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V64" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W64" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X64" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y64" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="T64" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U64" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V64" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W64" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="X64" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y64" s="5" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="65">
@@ -5644,25 +5644,25 @@
         <v>0</v>
       </c>
       <c r="S65" t="n">
+        <v>0</v>
+      </c>
+      <c r="T65" t="n">
+        <v>0</v>
+      </c>
+      <c r="U65" t="n">
+        <v>0</v>
+      </c>
+      <c r="V65" t="n">
+        <v>0</v>
+      </c>
+      <c r="W65" t="n">
+        <v>0</v>
+      </c>
+      <c r="X65" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y65" t="n">
         <v>24</v>
-      </c>
-      <c r="T65" t="n">
-        <v>0</v>
-      </c>
-      <c r="U65" t="n">
-        <v>0</v>
-      </c>
-      <c r="V65" t="n">
-        <v>0</v>
-      </c>
-      <c r="W65" t="n">
-        <v>0</v>
-      </c>
-      <c r="X65" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y65" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="66">
@@ -5723,25 +5723,25 @@
         <v>0</v>
       </c>
       <c r="S66" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T66" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U66" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V66" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W66" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X66" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y66" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="T66" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U66" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V66" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W66" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="X66" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y66" s="5" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="67">
@@ -5801,6 +5801,9 @@
       <c r="R67" t="n">
         <v>0</v>
       </c>
+      <c r="S67" t="n">
+        <v>0</v>
+      </c>
       <c r="T67" t="n">
         <v>0</v>
       </c>
@@ -5814,9 +5817,6 @@
         <v>0</v>
       </c>
       <c r="X67" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y67" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5878,25 +5878,25 @@
         <v>0</v>
       </c>
       <c r="S68" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T68" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U68" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V68" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W68" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X68" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y68" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="T68" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U68" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V68" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W68" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="X68" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y68" s="5" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="69">
@@ -5953,6 +5953,9 @@
       <c r="R69" t="n">
         <v>0</v>
       </c>
+      <c r="S69" t="n">
+        <v>0</v>
+      </c>
       <c r="T69" t="n">
         <v>0</v>
       </c>
@@ -5966,9 +5969,6 @@
         <v>0</v>
       </c>
       <c r="X69" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y69" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6030,25 +6030,25 @@
         <v>0</v>
       </c>
       <c r="S70" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T70" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U70" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V70" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W70" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X70" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y70" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="T70" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U70" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V70" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W70" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="X70" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y70" s="5" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="71">
@@ -6109,25 +6109,25 @@
         <v>0</v>
       </c>
       <c r="S71" t="n">
+        <v>0</v>
+      </c>
+      <c r="T71" t="n">
+        <v>0</v>
+      </c>
+      <c r="U71" t="n">
+        <v>0</v>
+      </c>
+      <c r="V71" t="n">
+        <v>0</v>
+      </c>
+      <c r="W71" t="n">
+        <v>0</v>
+      </c>
+      <c r="X71" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y71" t="n">
         <v>24</v>
-      </c>
-      <c r="T71" t="n">
-        <v>0</v>
-      </c>
-      <c r="U71" t="n">
-        <v>0</v>
-      </c>
-      <c r="V71" t="n">
-        <v>0</v>
-      </c>
-      <c r="W71" t="n">
-        <v>0</v>
-      </c>
-      <c r="X71" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y71" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="72">
@@ -6188,25 +6188,25 @@
         <v>0</v>
       </c>
       <c r="S72" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T72" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U72" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V72" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W72" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X72" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y72" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="T72" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U72" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V72" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W72" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="X72" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y72" s="5" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="73">
@@ -6267,25 +6267,25 @@
         <v>0</v>
       </c>
       <c r="S73" t="n">
+        <v>0</v>
+      </c>
+      <c r="T73" t="n">
+        <v>0</v>
+      </c>
+      <c r="U73" t="n">
+        <v>0</v>
+      </c>
+      <c r="V73" t="n">
+        <v>0</v>
+      </c>
+      <c r="W73" t="n">
+        <v>0</v>
+      </c>
+      <c r="X73" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y73" t="n">
         <v>24</v>
-      </c>
-      <c r="T73" t="n">
-        <v>0</v>
-      </c>
-      <c r="U73" t="n">
-        <v>0</v>
-      </c>
-      <c r="V73" t="n">
-        <v>0</v>
-      </c>
-      <c r="W73" t="n">
-        <v>0</v>
-      </c>
-      <c r="X73" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y73" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="74">
@@ -6346,25 +6346,25 @@
         <v>0</v>
       </c>
       <c r="S74" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T74" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U74" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V74" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W74" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X74" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y74" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="T74" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U74" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V74" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W74" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="X74" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y74" s="5" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="75">
@@ -6425,25 +6425,25 @@
         <v>0</v>
       </c>
       <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>0</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y75" t="n">
         <v>24</v>
-      </c>
-      <c r="T75" t="n">
-        <v>0</v>
-      </c>
-      <c r="U75" t="n">
-        <v>0</v>
-      </c>
-      <c r="V75" t="n">
-        <v>0</v>
-      </c>
-      <c r="W75" t="n">
-        <v>0</v>
-      </c>
-      <c r="X75" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y75" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="76">
@@ -6479,9 +6479,7 @@
       <c r="J76" s="5" t="n">
         <v>26</v>
       </c>
-      <c r="K76" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="K76" s="5" t="n"/>
       <c r="L76" s="5" t="n">
         <v>0</v>
       </c>
@@ -6494,9 +6492,7 @@
       <c r="O76" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="P76" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="P76" s="5" t="n"/>
       <c r="Q76" s="5" t="n">
         <v>0</v>
       </c>
@@ -6504,21 +6500,25 @@
         <v>0</v>
       </c>
       <c r="S76" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T76" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U76" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V76" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W76" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X76" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y76" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="T76" s="5" t="n"/>
-      <c r="U76" s="5" t="n"/>
-      <c r="V76" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W76" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="X76" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y76" s="5" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="77">
@@ -6578,6 +6578,9 @@
       <c r="R77" t="n">
         <v>0</v>
       </c>
+      <c r="S77" t="n">
+        <v>0</v>
+      </c>
       <c r="T77" t="n">
         <v>0</v>
       </c>
@@ -6591,9 +6594,6 @@
         <v>0</v>
       </c>
       <c r="X77" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y77" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6655,25 +6655,25 @@
         <v>0</v>
       </c>
       <c r="S78" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T78" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U78" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V78" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W78" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X78" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y78" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="T78" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U78" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V78" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W78" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="X78" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y78" s="5" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="79">
@@ -6733,6 +6733,9 @@
       <c r="R79" t="n">
         <v>0</v>
       </c>
+      <c r="S79" t="n">
+        <v>0</v>
+      </c>
       <c r="T79" t="n">
         <v>0</v>
       </c>
@@ -6746,9 +6749,6 @@
         <v>0</v>
       </c>
       <c r="X79" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y79" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6809,7 +6809,9 @@
       <c r="R80" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="S80" s="5" t="n"/>
+      <c r="S80" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="T80" s="5" t="n">
         <v>0</v>
       </c>
@@ -6825,9 +6827,7 @@
       <c r="X80" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="Y80" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="Y80" s="5" t="n"/>
     </row>
     <row r="81">
       <c r="A81" s="6" t="inlineStr">
@@ -6887,25 +6887,25 @@
         <v>0</v>
       </c>
       <c r="S81" t="n">
+        <v>0</v>
+      </c>
+      <c r="T81" t="n">
+        <v>0</v>
+      </c>
+      <c r="U81" t="n">
+        <v>0</v>
+      </c>
+      <c r="V81" t="n">
+        <v>0</v>
+      </c>
+      <c r="W81" t="n">
+        <v>0</v>
+      </c>
+      <c r="X81" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y81" t="n">
         <v>24</v>
-      </c>
-      <c r="T81" t="n">
-        <v>0</v>
-      </c>
-      <c r="U81" t="n">
-        <v>0</v>
-      </c>
-      <c r="V81" t="n">
-        <v>0</v>
-      </c>
-      <c r="W81" t="n">
-        <v>0</v>
-      </c>
-      <c r="X81" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y81" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="82">
@@ -6965,7 +6965,9 @@
       <c r="R82" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="S82" s="5" t="n"/>
+      <c r="S82" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="T82" s="5" t="n">
         <v>0</v>
       </c>
@@ -6981,9 +6983,7 @@
       <c r="X82" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="Y82" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="Y82" s="5" t="n"/>
     </row>
     <row r="83">
       <c r="A83" s="6" t="inlineStr">
@@ -7040,25 +7040,25 @@
         <v>0</v>
       </c>
       <c r="S83" t="n">
+        <v>0</v>
+      </c>
+      <c r="T83" t="n">
+        <v>0</v>
+      </c>
+      <c r="U83" t="n">
+        <v>0</v>
+      </c>
+      <c r="V83" t="n">
+        <v>0</v>
+      </c>
+      <c r="W83" t="n">
+        <v>0</v>
+      </c>
+      <c r="X83" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y83" t="n">
         <v>24</v>
-      </c>
-      <c r="T83" t="n">
-        <v>0</v>
-      </c>
-      <c r="U83" t="n">
-        <v>0</v>
-      </c>
-      <c r="V83" t="n">
-        <v>0</v>
-      </c>
-      <c r="W83" t="n">
-        <v>0</v>
-      </c>
-      <c r="X83" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y83" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="84">
@@ -7119,25 +7119,25 @@
         <v>0</v>
       </c>
       <c r="S84" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T84" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U84" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V84" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W84" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X84" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y84" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="T84" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U84" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V84" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W84" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="X84" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y84" s="5" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="85">
@@ -7197,6 +7197,9 @@
       <c r="R85" t="n">
         <v>0</v>
       </c>
+      <c r="S85" t="n">
+        <v>0</v>
+      </c>
       <c r="T85" t="n">
         <v>0</v>
       </c>
@@ -7210,9 +7213,6 @@
         <v>0</v>
       </c>
       <c r="X85" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y85" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7273,7 +7273,9 @@
       <c r="R86" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="S86" s="5" t="n"/>
+      <c r="S86" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="T86" s="5" t="n">
         <v>0</v>
       </c>
@@ -7289,9 +7291,7 @@
       <c r="X86" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="Y86" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="Y86" s="5" t="n"/>
     </row>
     <row r="87">
       <c r="A87" s="6" t="inlineStr">
@@ -7350,6 +7350,9 @@
       <c r="R87" t="n">
         <v>0</v>
       </c>
+      <c r="S87" t="n">
+        <v>0</v>
+      </c>
       <c r="T87" t="n">
         <v>0</v>
       </c>
@@ -7363,9 +7366,6 @@
         <v>0</v>
       </c>
       <c r="X87" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y87" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7426,7 +7426,9 @@
       <c r="R88" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="S88" s="5" t="n"/>
+      <c r="S88" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="T88" s="5" t="n">
         <v>0</v>
       </c>
@@ -7442,9 +7444,7 @@
       <c r="X88" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="Y88" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="Y88" s="5" t="n"/>
     </row>
     <row r="89">
       <c r="A89" s="6" t="inlineStr">
@@ -7503,6 +7503,9 @@
       <c r="R89" t="n">
         <v>0</v>
       </c>
+      <c r="S89" t="n">
+        <v>0</v>
+      </c>
       <c r="T89" t="n">
         <v>0</v>
       </c>
@@ -7516,9 +7519,6 @@
         <v>0</v>
       </c>
       <c r="X89" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y89" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7578,25 +7578,25 @@
         <v>0</v>
       </c>
       <c r="S90" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T90" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U90" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V90" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W90" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X90" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y90" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="T90" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U90" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V90" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W90" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="X90" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y90" s="5" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="91">
@@ -7656,6 +7656,9 @@
       <c r="R91" t="n">
         <v>0</v>
       </c>
+      <c r="S91" t="n">
+        <v>0</v>
+      </c>
       <c r="T91" t="n">
         <v>0</v>
       </c>
@@ -7669,9 +7672,6 @@
         <v>0</v>
       </c>
       <c r="X91" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y91" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7732,7 +7732,9 @@
       <c r="R92" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="S92" s="5" t="n"/>
+      <c r="S92" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="T92" s="5" t="n">
         <v>0</v>
       </c>
@@ -7748,9 +7750,7 @@
       <c r="X92" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="Y92" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="Y92" s="5" t="n"/>
     </row>
     <row r="93">
       <c r="A93" s="6" t="inlineStr">
@@ -7809,6 +7809,9 @@
       <c r="R93" t="n">
         <v>0</v>
       </c>
+      <c r="S93" t="n">
+        <v>0</v>
+      </c>
       <c r="T93" t="n">
         <v>0</v>
       </c>
@@ -7822,9 +7825,6 @@
         <v>0</v>
       </c>
       <c r="X93" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y93" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7885,7 +7885,9 @@
       <c r="R94" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="S94" s="5" t="n"/>
+      <c r="S94" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="T94" s="5" t="n">
         <v>0</v>
       </c>
@@ -7901,9 +7903,7 @@
       <c r="X94" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="Y94" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="Y94" s="5" t="n"/>
     </row>
     <row r="95">
       <c r="A95" s="6" t="inlineStr">
@@ -7962,6 +7962,9 @@
       <c r="R95" t="n">
         <v>0</v>
       </c>
+      <c r="S95" t="n">
+        <v>0</v>
+      </c>
       <c r="T95" t="n">
         <v>0</v>
       </c>
@@ -7975,9 +7978,6 @@
         <v>0</v>
       </c>
       <c r="X95" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y95" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8038,7 +8038,9 @@
       <c r="R96" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="S96" s="5" t="n"/>
+      <c r="S96" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="T96" s="5" t="n">
         <v>0</v>
       </c>
@@ -8054,9 +8056,7 @@
       <c r="X96" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="Y96" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="Y96" s="5" t="n"/>
     </row>
     <row r="97">
       <c r="A97" s="6" t="inlineStr">
@@ -8112,6 +8112,9 @@
       <c r="R97" t="n">
         <v>0</v>
       </c>
+      <c r="S97" t="n">
+        <v>0</v>
+      </c>
       <c r="T97" t="n">
         <v>0</v>
       </c>
@@ -8125,9 +8128,6 @@
         <v>0</v>
       </c>
       <c r="X97" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y97" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8188,7 +8188,9 @@
       <c r="R98" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="S98" s="5" t="n"/>
+      <c r="S98" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="T98" s="5" t="n">
         <v>0</v>
       </c>
@@ -8204,9 +8206,7 @@
       <c r="X98" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="Y98" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="Y98" s="5" t="n"/>
     </row>
     <row r="99">
       <c r="A99" s="6" t="inlineStr">
@@ -8265,6 +8265,9 @@
       <c r="R99" t="n">
         <v>0</v>
       </c>
+      <c r="S99" t="n">
+        <v>0</v>
+      </c>
       <c r="T99" t="n">
         <v>0</v>
       </c>
@@ -8278,9 +8281,6 @@
         <v>0</v>
       </c>
       <c r="X99" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y99" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8341,7 +8341,9 @@
       <c r="R100" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="S100" s="5" t="n"/>
+      <c r="S100" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="T100" s="5" t="n">
         <v>0</v>
       </c>
@@ -8357,9 +8359,7 @@
       <c r="X100" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="Y100" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="Y100" s="5" t="n"/>
     </row>
     <row r="101">
       <c r="A101" s="6" t="inlineStr">
@@ -8418,6 +8418,9 @@
       <c r="R101" t="n">
         <v>0</v>
       </c>
+      <c r="S101" t="n">
+        <v>0</v>
+      </c>
       <c r="T101" t="n">
         <v>0</v>
       </c>
@@ -8431,9 +8434,6 @@
         <v>0</v>
       </c>
       <c r="X101" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y101" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8494,7 +8494,9 @@
       <c r="R102" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="S102" s="5" t="n"/>
+      <c r="S102" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="T102" s="5" t="n">
         <v>0</v>
       </c>
@@ -8510,9 +8512,7 @@
       <c r="X102" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="Y102" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="Y102" s="5" t="n"/>
     </row>
     <row r="103">
       <c r="A103" s="6" t="inlineStr">
@@ -8571,6 +8571,9 @@
       <c r="R103" t="n">
         <v>0</v>
       </c>
+      <c r="S103" t="n">
+        <v>0</v>
+      </c>
       <c r="T103" t="n">
         <v>0</v>
       </c>
@@ -8584,9 +8587,6 @@
         <v>0</v>
       </c>
       <c r="X103" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y103" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8647,7 +8647,9 @@
       <c r="R104" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="S104" s="5" t="n"/>
+      <c r="S104" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="T104" s="5" t="n">
         <v>0</v>
       </c>
@@ -8663,9 +8665,7 @@
       <c r="X104" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="Y104" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="Y104" s="5" t="n"/>
     </row>
     <row r="105">
       <c r="A105" s="6" t="inlineStr">
@@ -8724,6 +8724,9 @@
       <c r="R105" t="n">
         <v>0</v>
       </c>
+      <c r="S105" t="n">
+        <v>0</v>
+      </c>
       <c r="T105" t="n">
         <v>0</v>
       </c>
@@ -8737,9 +8740,6 @@
         <v>0</v>
       </c>
       <c r="X105" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y105" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8800,7 +8800,9 @@
       <c r="R106" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="S106" s="5" t="n"/>
+      <c r="S106" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="T106" s="5" t="n">
         <v>0</v>
       </c>
@@ -8816,9 +8818,7 @@
       <c r="X106" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="Y106" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="Y106" s="5" t="n"/>
     </row>
     <row r="107">
       <c r="A107" s="6" t="inlineStr">
@@ -8877,6 +8877,9 @@
       <c r="R107" t="n">
         <v>0</v>
       </c>
+      <c r="S107" t="n">
+        <v>0</v>
+      </c>
       <c r="T107" t="n">
         <v>0</v>
       </c>
@@ -8890,9 +8893,6 @@
         <v>0</v>
       </c>
       <c r="X107" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y107" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8953,7 +8953,9 @@
       <c r="R108" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="S108" s="5" t="n"/>
+      <c r="S108" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="T108" s="5" t="n">
         <v>0</v>
       </c>
@@ -8969,9 +8971,7 @@
       <c r="X108" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="Y108" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="Y108" s="5" t="n"/>
     </row>
     <row r="109">
       <c r="A109" s="6" t="inlineStr">
@@ -9030,6 +9030,9 @@
       <c r="R109" t="n">
         <v>0</v>
       </c>
+      <c r="S109" t="n">
+        <v>0</v>
+      </c>
       <c r="T109" t="n">
         <v>0</v>
       </c>
@@ -9043,9 +9046,6 @@
         <v>0</v>
       </c>
       <c r="X109" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y109" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9106,7 +9106,9 @@
       <c r="R110" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="S110" s="5" t="n"/>
+      <c r="S110" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="T110" s="5" t="n">
         <v>0</v>
       </c>
@@ -9122,9 +9124,7 @@
       <c r="X110" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="Y110" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="Y110" s="5" t="n"/>
     </row>
     <row r="111">
       <c r="A111" s="6" t="inlineStr">
@@ -9180,6 +9180,9 @@
       <c r="R111" t="n">
         <v>0</v>
       </c>
+      <c r="S111" t="n">
+        <v>0</v>
+      </c>
       <c r="T111" t="n">
         <v>0</v>
       </c>
@@ -9193,9 +9196,6 @@
         <v>0</v>
       </c>
       <c r="X111" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y111" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9256,7 +9256,9 @@
       <c r="R112" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="S112" s="5" t="n"/>
+      <c r="S112" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="T112" s="5" t="n">
         <v>0</v>
       </c>
@@ -9272,7 +9274,81 @@
       <c r="X112" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="Y112" s="5" t="n">
+      <c r="Y112" s="5" t="n"/>
+    </row>
+    <row r="113">
+      <c r="A113" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B113" t="n">
+        <v>899</v>
+      </c>
+      <c r="C113" t="n">
+        <v>468</v>
+      </c>
+      <c r="D113" t="n">
+        <v>315</v>
+      </c>
+      <c r="E113" t="n">
+        <v>274</v>
+      </c>
+      <c r="F113" t="n">
+        <v>205</v>
+      </c>
+      <c r="G113" t="n">
+        <v>117</v>
+      </c>
+      <c r="H113" t="n">
+        <v>101</v>
+      </c>
+      <c r="I113" t="n">
+        <v>34</v>
+      </c>
+      <c r="J113" t="n">
+        <v>22</v>
+      </c>
+      <c r="K113" t="n">
+        <v>0</v>
+      </c>
+      <c r="L113" t="n">
+        <v>0</v>
+      </c>
+      <c r="M113" t="n">
+        <v>0</v>
+      </c>
+      <c r="N113" t="n">
+        <v>0</v>
+      </c>
+      <c r="O113" t="n">
+        <v>0</v>
+      </c>
+      <c r="P113" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q113" t="n">
+        <v>0</v>
+      </c>
+      <c r="R113" t="n">
+        <v>0</v>
+      </c>
+      <c r="S113" t="n">
+        <v>0</v>
+      </c>
+      <c r="T113" t="n">
+        <v>0</v>
+      </c>
+      <c r="U113" t="n">
+        <v>0</v>
+      </c>
+      <c r="V113" t="n">
+        <v>0</v>
+      </c>
+      <c r="W113" t="n">
+        <v>0</v>
+      </c>
+      <c r="X113" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9314,7 +9390,7 @@
       </c>
       <c r="D1" s="3" t="inlineStr">
         <is>
-          <t>Lager (2026-10-26)</t>
+          <t>Lager (2026-10-27)</t>
         </is>
       </c>
     </row>
@@ -9335,7 +9411,7 @@
         </is>
       </c>
       <c r="D2" s="4" t="n">
-        <v>459</v>
+        <v>468</v>
       </c>
     </row>
     <row r="3">
@@ -13215,7 +13291,7 @@
         </is>
       </c>
       <c r="D196" s="4" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
     </row>
     <row r="197">
@@ -17895,7 +17971,7 @@
         </is>
       </c>
       <c r="D430" s="4" t="n">
-        <v>175</v>
+        <v>168</v>
       </c>
     </row>
     <row r="431">
@@ -19615,7 +19691,7 @@
         </is>
       </c>
       <c r="D516" s="4" t="n">
-        <v>113</v>
+        <v>107</v>
       </c>
     </row>
     <row r="517">
@@ -27555,7 +27631,7 @@
         </is>
       </c>
       <c r="D913" s="6" t="n">
-        <v>215</v>
+        <v>200</v>
       </c>
     </row>
     <row r="914">
@@ -29355,7 +29431,7 @@
         </is>
       </c>
       <c r="D1003" s="6" t="n">
-        <v>138</v>
+        <v>132</v>
       </c>
     </row>
     <row r="1004">
@@ -30615,7 +30691,7 @@
         </is>
       </c>
       <c r="D1066" s="4" t="n">
-        <v>445</v>
+        <v>471</v>
       </c>
     </row>
     <row r="1067">
@@ -30635,7 +30711,7 @@
         </is>
       </c>
       <c r="D1067" s="6" t="n">
-        <v>339</v>
+        <v>336</v>
       </c>
     </row>
   </sheetData>

--- a/data/ahlsell_led_panel_inventory.xlsx
+++ b/data/ahlsell_led_panel_inventory.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y114"/>
+  <dimension ref="A1:Y115"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -538,77 +538,77 @@
       </c>
       <c r="K1" s="3" t="inlineStr">
         <is>
+          <t>Black Box</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="inlineStr">
+        <is>
+          <t>ZG Lighting</t>
+        </is>
+      </c>
+      <c r="M1" s="3" t="inlineStr">
+        <is>
+          <t>Easyform</t>
+        </is>
+      </c>
+      <c r="N1" s="3" t="inlineStr">
+        <is>
+          <t>Philips</t>
+        </is>
+      </c>
+      <c r="O1" s="3" t="inlineStr">
+        <is>
+          <t>Westal</t>
+        </is>
+      </c>
+      <c r="P1" s="3" t="inlineStr">
+        <is>
+          <t>Nokalux</t>
+        </is>
+      </c>
+      <c r="Q1" s="3" t="inlineStr">
+        <is>
+          <t>Norwesco</t>
+        </is>
+      </c>
+      <c r="R1" s="3" t="inlineStr">
+        <is>
+          <t>Airam</t>
+        </is>
+      </c>
+      <c r="S1" s="3" t="inlineStr">
+        <is>
+          <t>Legrand</t>
+        </is>
+      </c>
+      <c r="T1" s="3" t="inlineStr">
+        <is>
+          <t>ANETA LIGHTING</t>
+        </is>
+      </c>
+      <c r="U1" s="3" t="inlineStr">
+        <is>
+          <t>Bergdahls</t>
+        </is>
+      </c>
+      <c r="V1" s="3" t="inlineStr">
+        <is>
+          <t>THORN</t>
+        </is>
+      </c>
+      <c r="W1" s="3" t="inlineStr">
+        <is>
+          <t>Esylux</t>
+        </is>
+      </c>
+      <c r="X1" s="3" t="inlineStr">
+        <is>
+          <t>Ensto</t>
+        </is>
+      </c>
+      <c r="Y1" s="3" t="inlineStr">
+        <is>
           <t>Siteco</t>
-        </is>
-      </c>
-      <c r="L1" s="3" t="inlineStr">
-        <is>
-          <t>Bergdahls</t>
-        </is>
-      </c>
-      <c r="M1" s="3" t="inlineStr">
-        <is>
-          <t>ZG Lighting</t>
-        </is>
-      </c>
-      <c r="N1" s="3" t="inlineStr">
-        <is>
-          <t>Esylux</t>
-        </is>
-      </c>
-      <c r="O1" s="3" t="inlineStr">
-        <is>
-          <t>THORN</t>
-        </is>
-      </c>
-      <c r="P1" s="3" t="inlineStr">
-        <is>
-          <t>Ensto</t>
-        </is>
-      </c>
-      <c r="Q1" s="3" t="inlineStr">
-        <is>
-          <t>Westal</t>
-        </is>
-      </c>
-      <c r="R1" s="3" t="inlineStr">
-        <is>
-          <t>ANETA LIGHTING</t>
-        </is>
-      </c>
-      <c r="S1" s="3" t="inlineStr">
-        <is>
-          <t>Easyform</t>
-        </is>
-      </c>
-      <c r="T1" s="3" t="inlineStr">
-        <is>
-          <t>Black Box</t>
-        </is>
-      </c>
-      <c r="U1" s="3" t="inlineStr">
-        <is>
-          <t>Legrand</t>
-        </is>
-      </c>
-      <c r="V1" s="3" t="inlineStr">
-        <is>
-          <t>Airam</t>
-        </is>
-      </c>
-      <c r="W1" s="3" t="inlineStr">
-        <is>
-          <t>Norwesco</t>
-        </is>
-      </c>
-      <c r="X1" s="3" t="inlineStr">
-        <is>
-          <t>Philips</t>
-        </is>
-      </c>
-      <c r="Y1" s="3" t="inlineStr">
-        <is>
-          <t>Nokalux</t>
         </is>
       </c>
     </row>
@@ -655,34 +655,34 @@
         <v>0</v>
       </c>
       <c r="N2" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q2" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R2" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S2" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T2" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U2" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V2" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W2" s="5" t="n">
         <v>25</v>
-      </c>
-      <c r="O2" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P2" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q2" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R2" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S2" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T2" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U2" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V2" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W2" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="X2" s="5" t="n">
         <v>0</v>
@@ -734,34 +734,34 @@
         <v>0</v>
       </c>
       <c r="N3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W3" t="n">
         <v>25</v>
-      </c>
-      <c r="O3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S3" t="n">
-        <v>0</v>
-      </c>
-      <c r="T3" t="n">
-        <v>0</v>
-      </c>
-      <c r="U3" t="n">
-        <v>0</v>
-      </c>
-      <c r="V3" t="n">
-        <v>0</v>
-      </c>
-      <c r="W3" t="n">
-        <v>0</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
@@ -813,34 +813,34 @@
         <v>0</v>
       </c>
       <c r="N4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W4" s="5" t="n">
         <v>25</v>
-      </c>
-      <c r="O4" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q4" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R4" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S4" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T4" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U4" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V4" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W4" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="X4" s="5" t="n">
         <v>0</v>
@@ -892,34 +892,34 @@
         <v>0</v>
       </c>
       <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W5" t="n">
         <v>24</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W5" t="n">
-        <v>0</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
@@ -971,34 +971,34 @@
         <v>0</v>
       </c>
       <c r="N6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W6" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="O6" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R6" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S6" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T6" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U6" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V6" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W6" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="X6" s="5" t="n">
         <v>0</v>
@@ -1047,34 +1047,34 @@
         <v>0</v>
       </c>
       <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0</v>
+      </c>
+      <c r="W7" t="n">
         <v>24</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>0</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="n">
-        <v>0</v>
-      </c>
-      <c r="T7" t="n">
-        <v>0</v>
-      </c>
-      <c r="U7" t="n">
-        <v>0</v>
-      </c>
-      <c r="V7" t="n">
-        <v>0</v>
-      </c>
-      <c r="W7" t="n">
-        <v>0</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
@@ -1126,34 +1126,34 @@
         <v>0</v>
       </c>
       <c r="N8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W8" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="O8" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R8" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T8" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U8" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V8" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W8" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="X8" s="5" t="n">
         <v>0</v>
@@ -1205,34 +1205,34 @@
         <v>0</v>
       </c>
       <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W9" t="n">
         <v>24</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>0</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W9" t="n">
-        <v>0</v>
       </c>
       <c r="X9" t="n">
         <v>0</v>
@@ -1284,34 +1284,34 @@
         <v>0</v>
       </c>
       <c r="N10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W10" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="O10" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R10" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T10" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U10" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V10" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W10" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="X10" s="5" t="n">
         <v>0</v>
@@ -1363,34 +1363,34 @@
         <v>0</v>
       </c>
       <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" t="n">
+        <v>0</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" t="n">
+        <v>0</v>
+      </c>
+      <c r="W11" t="n">
         <v>24</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>0</v>
-      </c>
-      <c r="R11" t="n">
-        <v>0</v>
-      </c>
-      <c r="S11" t="n">
-        <v>0</v>
-      </c>
-      <c r="T11" t="n">
-        <v>0</v>
-      </c>
-      <c r="U11" t="n">
-        <v>0</v>
-      </c>
-      <c r="V11" t="n">
-        <v>0</v>
-      </c>
-      <c r="W11" t="n">
-        <v>0</v>
       </c>
       <c r="X11" t="n">
         <v>0</v>
@@ -1442,34 +1442,34 @@
         <v>0</v>
       </c>
       <c r="N12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W12" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="O12" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R12" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T12" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U12" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V12" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W12" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="X12" s="5" t="n">
         <v>0</v>
@@ -1521,34 +1521,34 @@
         <v>0</v>
       </c>
       <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0</v>
+      </c>
+      <c r="T13" t="n">
+        <v>0</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" t="n">
+        <v>0</v>
+      </c>
+      <c r="W13" t="n">
         <v>24</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>0</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" t="n">
-        <v>0</v>
-      </c>
-      <c r="T13" t="n">
-        <v>0</v>
-      </c>
-      <c r="U13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V13" t="n">
-        <v>0</v>
-      </c>
-      <c r="W13" t="n">
-        <v>0</v>
       </c>
       <c r="X13" t="n">
         <v>0</v>
@@ -1600,34 +1600,34 @@
         <v>0</v>
       </c>
       <c r="N14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W14" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="O14" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R14" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S14" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T14" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U14" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V14" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W14" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="X14" s="5" t="n">
         <v>0</v>
@@ -1679,34 +1679,34 @@
         <v>0</v>
       </c>
       <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" t="n">
+        <v>0</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0</v>
+      </c>
+      <c r="W15" t="n">
         <v>24</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>0</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" t="n">
-        <v>0</v>
-      </c>
-      <c r="T15" t="n">
-        <v>0</v>
-      </c>
-      <c r="U15" t="n">
-        <v>0</v>
-      </c>
-      <c r="V15" t="n">
-        <v>0</v>
-      </c>
-      <c r="W15" t="n">
-        <v>0</v>
       </c>
       <c r="X15" t="n">
         <v>0</v>
@@ -1758,34 +1758,34 @@
         <v>0</v>
       </c>
       <c r="N16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W16" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="O16" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R16" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S16" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T16" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U16" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V16" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W16" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="X16" s="5" t="n">
         <v>0</v>
@@ -1837,34 +1837,34 @@
         <v>0</v>
       </c>
       <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0</v>
+      </c>
+      <c r="T17" t="n">
+        <v>0</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" t="n">
+        <v>0</v>
+      </c>
+      <c r="W17" t="n">
         <v>24</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>0</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" t="n">
-        <v>0</v>
-      </c>
-      <c r="T17" t="n">
-        <v>0</v>
-      </c>
-      <c r="U17" t="n">
-        <v>0</v>
-      </c>
-      <c r="V17" t="n">
-        <v>0</v>
-      </c>
-      <c r="W17" t="n">
-        <v>0</v>
       </c>
       <c r="X17" t="n">
         <v>0</v>
@@ -1916,34 +1916,34 @@
         <v>0</v>
       </c>
       <c r="N18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W18" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="O18" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R18" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S18" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T18" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U18" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V18" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W18" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="X18" s="5" t="n">
         <v>0</v>
@@ -1995,34 +1995,34 @@
         <v>0</v>
       </c>
       <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0</v>
+      </c>
+      <c r="T19" t="n">
+        <v>0</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" t="n">
+        <v>0</v>
+      </c>
+      <c r="W19" t="n">
         <v>24</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>0</v>
-      </c>
-      <c r="R19" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" t="n">
-        <v>0</v>
-      </c>
-      <c r="T19" t="n">
-        <v>0</v>
-      </c>
-      <c r="U19" t="n">
-        <v>0</v>
-      </c>
-      <c r="V19" t="n">
-        <v>0</v>
-      </c>
-      <c r="W19" t="n">
-        <v>0</v>
       </c>
       <c r="X19" t="n">
         <v>0</v>
@@ -2074,34 +2074,34 @@
         <v>0</v>
       </c>
       <c r="N20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W20" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="O20" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q20" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R20" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S20" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T20" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U20" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V20" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W20" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="X20" s="5" t="n">
         <v>0</v>
@@ -2153,34 +2153,34 @@
         <v>0</v>
       </c>
       <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>0</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" t="n">
+        <v>0</v>
+      </c>
+      <c r="T21" t="n">
+        <v>0</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0</v>
+      </c>
+      <c r="V21" t="n">
+        <v>0</v>
+      </c>
+      <c r="W21" t="n">
         <v>24</v>
-      </c>
-      <c r="O21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>0</v>
-      </c>
-      <c r="R21" t="n">
-        <v>0</v>
-      </c>
-      <c r="S21" t="n">
-        <v>0</v>
-      </c>
-      <c r="T21" t="n">
-        <v>0</v>
-      </c>
-      <c r="U21" t="n">
-        <v>0</v>
-      </c>
-      <c r="V21" t="n">
-        <v>0</v>
-      </c>
-      <c r="W21" t="n">
-        <v>0</v>
       </c>
       <c r="X21" t="n">
         <v>0</v>
@@ -2232,34 +2232,34 @@
         <v>0</v>
       </c>
       <c r="N22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W22" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="O22" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q22" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R22" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S22" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T22" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U22" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V22" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W22" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="X22" s="5" t="n">
         <v>0</v>
@@ -2311,34 +2311,34 @@
         <v>0</v>
       </c>
       <c r="N23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>0</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0</v>
+      </c>
+      <c r="S23" t="n">
+        <v>0</v>
+      </c>
+      <c r="T23" t="n">
+        <v>0</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0</v>
+      </c>
+      <c r="V23" t="n">
+        <v>0</v>
+      </c>
+      <c r="W23" t="n">
         <v>24</v>
-      </c>
-      <c r="O23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>0</v>
-      </c>
-      <c r="R23" t="n">
-        <v>0</v>
-      </c>
-      <c r="S23" t="n">
-        <v>0</v>
-      </c>
-      <c r="T23" t="n">
-        <v>0</v>
-      </c>
-      <c r="U23" t="n">
-        <v>0</v>
-      </c>
-      <c r="V23" t="n">
-        <v>0</v>
-      </c>
-      <c r="W23" t="n">
-        <v>0</v>
       </c>
       <c r="X23" t="n">
         <v>0</v>
@@ -2390,34 +2390,34 @@
         <v>0</v>
       </c>
       <c r="N24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W24" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="O24" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P24" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q24" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R24" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S24" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T24" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U24" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V24" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W24" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="X24" s="5" t="n">
         <v>0</v>
@@ -2469,34 +2469,34 @@
         <v>0</v>
       </c>
       <c r="N25" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>0</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0</v>
+      </c>
+      <c r="S25" t="n">
+        <v>0</v>
+      </c>
+      <c r="T25" t="n">
+        <v>0</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0</v>
+      </c>
+      <c r="V25" t="n">
+        <v>0</v>
+      </c>
+      <c r="W25" t="n">
         <v>24</v>
-      </c>
-      <c r="O25" t="n">
-        <v>0</v>
-      </c>
-      <c r="P25" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>0</v>
-      </c>
-      <c r="R25" t="n">
-        <v>0</v>
-      </c>
-      <c r="S25" t="n">
-        <v>0</v>
-      </c>
-      <c r="T25" t="n">
-        <v>0</v>
-      </c>
-      <c r="U25" t="n">
-        <v>0</v>
-      </c>
-      <c r="V25" t="n">
-        <v>0</v>
-      </c>
-      <c r="W25" t="n">
-        <v>0</v>
       </c>
       <c r="X25" t="n">
         <v>0</v>
@@ -2548,34 +2548,34 @@
         <v>0</v>
       </c>
       <c r="N26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W26" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="O26" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P26" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q26" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R26" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S26" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T26" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U26" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V26" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W26" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="X26" s="5" t="n">
         <v>0</v>
@@ -2627,34 +2627,34 @@
         <v>0</v>
       </c>
       <c r="N27" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>0</v>
+      </c>
+      <c r="R27" t="n">
+        <v>0</v>
+      </c>
+      <c r="S27" t="n">
+        <v>0</v>
+      </c>
+      <c r="T27" t="n">
+        <v>0</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0</v>
+      </c>
+      <c r="V27" t="n">
+        <v>0</v>
+      </c>
+      <c r="W27" t="n">
         <v>24</v>
-      </c>
-      <c r="O27" t="n">
-        <v>0</v>
-      </c>
-      <c r="P27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>0</v>
-      </c>
-      <c r="R27" t="n">
-        <v>0</v>
-      </c>
-      <c r="S27" t="n">
-        <v>0</v>
-      </c>
-      <c r="T27" t="n">
-        <v>0</v>
-      </c>
-      <c r="U27" t="n">
-        <v>0</v>
-      </c>
-      <c r="V27" t="n">
-        <v>0</v>
-      </c>
-      <c r="W27" t="n">
-        <v>0</v>
       </c>
       <c r="X27" t="n">
         <v>0</v>
@@ -2785,34 +2785,34 @@
         <v>0</v>
       </c>
       <c r="N29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>0</v>
+      </c>
+      <c r="R29" t="n">
+        <v>0</v>
+      </c>
+      <c r="S29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T29" t="n">
+        <v>0</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0</v>
+      </c>
+      <c r="V29" t="n">
+        <v>0</v>
+      </c>
+      <c r="W29" t="n">
         <v>24</v>
-      </c>
-      <c r="O29" t="n">
-        <v>0</v>
-      </c>
-      <c r="P29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>0</v>
-      </c>
-      <c r="R29" t="n">
-        <v>0</v>
-      </c>
-      <c r="S29" t="n">
-        <v>0</v>
-      </c>
-      <c r="T29" t="n">
-        <v>0</v>
-      </c>
-      <c r="U29" t="n">
-        <v>0</v>
-      </c>
-      <c r="V29" t="n">
-        <v>0</v>
-      </c>
-      <c r="W29" t="n">
-        <v>0</v>
       </c>
       <c r="X29" t="n">
         <v>0</v>
@@ -2864,34 +2864,34 @@
         <v>0</v>
       </c>
       <c r="N30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W30" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="O30" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P30" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q30" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R30" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S30" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T30" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U30" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V30" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W30" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="X30" s="5" t="n">
         <v>0</v>
@@ -2943,34 +2943,34 @@
         <v>0</v>
       </c>
       <c r="N31" t="n">
+        <v>0</v>
+      </c>
+      <c r="O31" t="n">
+        <v>0</v>
+      </c>
+      <c r="P31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>0</v>
+      </c>
+      <c r="R31" t="n">
+        <v>0</v>
+      </c>
+      <c r="S31" t="n">
+        <v>0</v>
+      </c>
+      <c r="T31" t="n">
+        <v>0</v>
+      </c>
+      <c r="U31" t="n">
+        <v>0</v>
+      </c>
+      <c r="V31" t="n">
+        <v>0</v>
+      </c>
+      <c r="W31" t="n">
         <v>24</v>
-      </c>
-      <c r="O31" t="n">
-        <v>0</v>
-      </c>
-      <c r="P31" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>0</v>
-      </c>
-      <c r="R31" t="n">
-        <v>0</v>
-      </c>
-      <c r="S31" t="n">
-        <v>0</v>
-      </c>
-      <c r="T31" t="n">
-        <v>0</v>
-      </c>
-      <c r="U31" t="n">
-        <v>0</v>
-      </c>
-      <c r="V31" t="n">
-        <v>0</v>
-      </c>
-      <c r="W31" t="n">
-        <v>0</v>
       </c>
       <c r="X31" t="n">
         <v>0</v>
@@ -3022,34 +3022,34 @@
         <v>0</v>
       </c>
       <c r="N32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W32" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="O32" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P32" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q32" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R32" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S32" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T32" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U32" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V32" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W32" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="X32" s="5" t="n">
         <v>0</v>
@@ -3101,34 +3101,34 @@
         <v>0</v>
       </c>
       <c r="N33" t="n">
+        <v>0</v>
+      </c>
+      <c r="O33" t="n">
+        <v>0</v>
+      </c>
+      <c r="P33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>0</v>
+      </c>
+      <c r="R33" t="n">
+        <v>0</v>
+      </c>
+      <c r="S33" t="n">
+        <v>0</v>
+      </c>
+      <c r="T33" t="n">
+        <v>0</v>
+      </c>
+      <c r="U33" t="n">
+        <v>0</v>
+      </c>
+      <c r="V33" t="n">
+        <v>0</v>
+      </c>
+      <c r="W33" t="n">
         <v>24</v>
-      </c>
-      <c r="O33" t="n">
-        <v>0</v>
-      </c>
-      <c r="P33" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>0</v>
-      </c>
-      <c r="R33" t="n">
-        <v>0</v>
-      </c>
-      <c r="S33" t="n">
-        <v>0</v>
-      </c>
-      <c r="T33" t="n">
-        <v>0</v>
-      </c>
-      <c r="U33" t="n">
-        <v>0</v>
-      </c>
-      <c r="V33" t="n">
-        <v>0</v>
-      </c>
-      <c r="W33" t="n">
-        <v>0</v>
       </c>
       <c r="X33" t="n">
         <v>0</v>
@@ -3180,34 +3180,34 @@
         <v>0</v>
       </c>
       <c r="N34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W34" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="O34" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P34" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q34" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R34" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S34" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T34" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U34" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V34" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W34" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="X34" s="5" t="n">
         <v>0</v>
@@ -3259,34 +3259,34 @@
         <v>0</v>
       </c>
       <c r="N35" t="n">
+        <v>0</v>
+      </c>
+      <c r="O35" t="n">
+        <v>0</v>
+      </c>
+      <c r="P35" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>0</v>
+      </c>
+      <c r="R35" t="n">
+        <v>0</v>
+      </c>
+      <c r="S35" t="n">
+        <v>0</v>
+      </c>
+      <c r="T35" t="n">
+        <v>0</v>
+      </c>
+      <c r="U35" t="n">
+        <v>0</v>
+      </c>
+      <c r="V35" t="n">
+        <v>0</v>
+      </c>
+      <c r="W35" t="n">
         <v>24</v>
-      </c>
-      <c r="O35" t="n">
-        <v>0</v>
-      </c>
-      <c r="P35" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q35" t="n">
-        <v>0</v>
-      </c>
-      <c r="R35" t="n">
-        <v>0</v>
-      </c>
-      <c r="S35" t="n">
-        <v>0</v>
-      </c>
-      <c r="T35" t="n">
-        <v>0</v>
-      </c>
-      <c r="U35" t="n">
-        <v>0</v>
-      </c>
-      <c r="V35" t="n">
-        <v>0</v>
-      </c>
-      <c r="W35" t="n">
-        <v>0</v>
       </c>
       <c r="X35" t="n">
         <v>0</v>
@@ -3338,34 +3338,34 @@
         <v>0</v>
       </c>
       <c r="N36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W36" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="O36" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P36" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q36" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R36" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S36" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T36" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U36" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V36" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W36" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="X36" s="5" t="n">
         <v>0</v>
@@ -3417,34 +3417,34 @@
         <v>0</v>
       </c>
       <c r="N37" t="n">
+        <v>0</v>
+      </c>
+      <c r="O37" t="n">
+        <v>0</v>
+      </c>
+      <c r="P37" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>0</v>
+      </c>
+      <c r="R37" t="n">
+        <v>0</v>
+      </c>
+      <c r="S37" t="n">
+        <v>0</v>
+      </c>
+      <c r="T37" t="n">
+        <v>0</v>
+      </c>
+      <c r="U37" t="n">
+        <v>0</v>
+      </c>
+      <c r="V37" t="n">
+        <v>0</v>
+      </c>
+      <c r="W37" t="n">
         <v>24</v>
-      </c>
-      <c r="O37" t="n">
-        <v>0</v>
-      </c>
-      <c r="P37" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q37" t="n">
-        <v>0</v>
-      </c>
-      <c r="R37" t="n">
-        <v>0</v>
-      </c>
-      <c r="S37" t="n">
-        <v>0</v>
-      </c>
-      <c r="T37" t="n">
-        <v>0</v>
-      </c>
-      <c r="U37" t="n">
-        <v>0</v>
-      </c>
-      <c r="V37" t="n">
-        <v>0</v>
-      </c>
-      <c r="W37" t="n">
-        <v>0</v>
       </c>
       <c r="X37" t="n">
         <v>0</v>
@@ -3496,34 +3496,34 @@
         <v>0</v>
       </c>
       <c r="N38" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O38" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P38" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q38" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R38" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S38" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T38" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U38" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V38" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W38" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="O38" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P38" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q38" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R38" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S38" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T38" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U38" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V38" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W38" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="X38" s="5" t="n">
         <v>0</v>
@@ -3575,34 +3575,34 @@
         <v>0</v>
       </c>
       <c r="N39" t="n">
+        <v>0</v>
+      </c>
+      <c r="O39" t="n">
+        <v>0</v>
+      </c>
+      <c r="P39" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>0</v>
+      </c>
+      <c r="R39" t="n">
+        <v>0</v>
+      </c>
+      <c r="S39" t="n">
+        <v>0</v>
+      </c>
+      <c r="T39" t="n">
+        <v>0</v>
+      </c>
+      <c r="U39" t="n">
+        <v>0</v>
+      </c>
+      <c r="V39" t="n">
+        <v>0</v>
+      </c>
+      <c r="W39" t="n">
         <v>24</v>
-      </c>
-      <c r="O39" t="n">
-        <v>0</v>
-      </c>
-      <c r="P39" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q39" t="n">
-        <v>0</v>
-      </c>
-      <c r="R39" t="n">
-        <v>0</v>
-      </c>
-      <c r="S39" t="n">
-        <v>0</v>
-      </c>
-      <c r="T39" t="n">
-        <v>0</v>
-      </c>
-      <c r="U39" t="n">
-        <v>0</v>
-      </c>
-      <c r="V39" t="n">
-        <v>0</v>
-      </c>
-      <c r="W39" t="n">
-        <v>0</v>
       </c>
       <c r="X39" t="n">
         <v>0</v>
@@ -3654,34 +3654,34 @@
         <v>0</v>
       </c>
       <c r="N40" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O40" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P40" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q40" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R40" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S40" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T40" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U40" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V40" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W40" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="O40" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P40" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q40" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R40" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S40" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T40" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U40" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V40" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W40" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="X40" s="5" t="n">
         <v>0</v>
@@ -3733,34 +3733,34 @@
         <v>0</v>
       </c>
       <c r="N41" t="n">
+        <v>0</v>
+      </c>
+      <c r="O41" t="n">
+        <v>0</v>
+      </c>
+      <c r="P41" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>0</v>
+      </c>
+      <c r="R41" t="n">
+        <v>0</v>
+      </c>
+      <c r="S41" t="n">
+        <v>0</v>
+      </c>
+      <c r="T41" t="n">
+        <v>0</v>
+      </c>
+      <c r="U41" t="n">
+        <v>0</v>
+      </c>
+      <c r="V41" t="n">
+        <v>0</v>
+      </c>
+      <c r="W41" t="n">
         <v>24</v>
-      </c>
-      <c r="O41" t="n">
-        <v>0</v>
-      </c>
-      <c r="P41" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q41" t="n">
-        <v>0</v>
-      </c>
-      <c r="R41" t="n">
-        <v>0</v>
-      </c>
-      <c r="S41" t="n">
-        <v>0</v>
-      </c>
-      <c r="T41" t="n">
-        <v>0</v>
-      </c>
-      <c r="U41" t="n">
-        <v>0</v>
-      </c>
-      <c r="V41" t="n">
-        <v>0</v>
-      </c>
-      <c r="W41" t="n">
-        <v>0</v>
       </c>
       <c r="X41" t="n">
         <v>0</v>
@@ -3812,34 +3812,34 @@
         <v>0</v>
       </c>
       <c r="N42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W42" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="O42" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P42" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q42" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R42" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S42" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T42" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U42" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V42" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W42" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="X42" s="5" t="n">
         <v>0</v>
@@ -3891,34 +3891,34 @@
         <v>0</v>
       </c>
       <c r="N43" t="n">
+        <v>0</v>
+      </c>
+      <c r="O43" t="n">
+        <v>0</v>
+      </c>
+      <c r="P43" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>0</v>
+      </c>
+      <c r="R43" t="n">
+        <v>0</v>
+      </c>
+      <c r="S43" t="n">
+        <v>0</v>
+      </c>
+      <c r="T43" t="n">
+        <v>0</v>
+      </c>
+      <c r="U43" t="n">
+        <v>0</v>
+      </c>
+      <c r="V43" t="n">
+        <v>0</v>
+      </c>
+      <c r="W43" t="n">
         <v>24</v>
-      </c>
-      <c r="O43" t="n">
-        <v>0</v>
-      </c>
-      <c r="P43" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q43" t="n">
-        <v>0</v>
-      </c>
-      <c r="R43" t="n">
-        <v>0</v>
-      </c>
-      <c r="S43" t="n">
-        <v>0</v>
-      </c>
-      <c r="T43" t="n">
-        <v>0</v>
-      </c>
-      <c r="U43" t="n">
-        <v>0</v>
-      </c>
-      <c r="V43" t="n">
-        <v>0</v>
-      </c>
-      <c r="W43" t="n">
-        <v>0</v>
       </c>
       <c r="X43" t="n">
         <v>0</v>
@@ -3970,34 +3970,34 @@
         <v>0</v>
       </c>
       <c r="N44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W44" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="O44" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P44" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q44" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R44" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S44" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T44" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U44" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V44" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W44" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="X44" s="5" t="n">
         <v>0</v>
@@ -4049,34 +4049,34 @@
         <v>0</v>
       </c>
       <c r="N45" t="n">
+        <v>0</v>
+      </c>
+      <c r="O45" t="n">
+        <v>0</v>
+      </c>
+      <c r="P45" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>0</v>
+      </c>
+      <c r="R45" t="n">
+        <v>0</v>
+      </c>
+      <c r="S45" t="n">
+        <v>0</v>
+      </c>
+      <c r="T45" t="n">
+        <v>0</v>
+      </c>
+      <c r="U45" t="n">
+        <v>0</v>
+      </c>
+      <c r="V45" t="n">
+        <v>0</v>
+      </c>
+      <c r="W45" t="n">
         <v>24</v>
-      </c>
-      <c r="O45" t="n">
-        <v>0</v>
-      </c>
-      <c r="P45" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q45" t="n">
-        <v>0</v>
-      </c>
-      <c r="R45" t="n">
-        <v>0</v>
-      </c>
-      <c r="S45" t="n">
-        <v>0</v>
-      </c>
-      <c r="T45" t="n">
-        <v>0</v>
-      </c>
-      <c r="U45" t="n">
-        <v>0</v>
-      </c>
-      <c r="V45" t="n">
-        <v>0</v>
-      </c>
-      <c r="W45" t="n">
-        <v>0</v>
       </c>
       <c r="X45" t="n">
         <v>0</v>
@@ -4128,34 +4128,34 @@
         <v>0</v>
       </c>
       <c r="N46" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O46" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P46" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q46" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R46" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S46" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T46" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U46" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V46" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W46" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="O46" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P46" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q46" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R46" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S46" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T46" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U46" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V46" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W46" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="X46" s="5" t="n">
         <v>0</v>
@@ -4207,34 +4207,34 @@
         <v>0</v>
       </c>
       <c r="N47" t="n">
+        <v>0</v>
+      </c>
+      <c r="O47" t="n">
+        <v>0</v>
+      </c>
+      <c r="P47" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>0</v>
+      </c>
+      <c r="R47" t="n">
+        <v>0</v>
+      </c>
+      <c r="S47" t="n">
+        <v>0</v>
+      </c>
+      <c r="T47" t="n">
+        <v>0</v>
+      </c>
+      <c r="U47" t="n">
+        <v>0</v>
+      </c>
+      <c r="V47" t="n">
+        <v>0</v>
+      </c>
+      <c r="W47" t="n">
         <v>24</v>
-      </c>
-      <c r="O47" t="n">
-        <v>0</v>
-      </c>
-      <c r="P47" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q47" t="n">
-        <v>0</v>
-      </c>
-      <c r="R47" t="n">
-        <v>0</v>
-      </c>
-      <c r="S47" t="n">
-        <v>0</v>
-      </c>
-      <c r="T47" t="n">
-        <v>0</v>
-      </c>
-      <c r="U47" t="n">
-        <v>0</v>
-      </c>
-      <c r="V47" t="n">
-        <v>0</v>
-      </c>
-      <c r="W47" t="n">
-        <v>0</v>
       </c>
       <c r="X47" t="n">
         <v>0</v>
@@ -4286,34 +4286,34 @@
         <v>0</v>
       </c>
       <c r="N48" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O48" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P48" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q48" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R48" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S48" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T48" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U48" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V48" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W48" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="O48" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P48" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q48" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R48" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S48" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T48" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U48" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V48" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W48" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="X48" s="5" t="n">
         <v>0</v>
@@ -4365,34 +4365,34 @@
         <v>0</v>
       </c>
       <c r="N49" t="n">
+        <v>0</v>
+      </c>
+      <c r="O49" t="n">
+        <v>0</v>
+      </c>
+      <c r="P49" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>0</v>
+      </c>
+      <c r="R49" t="n">
+        <v>0</v>
+      </c>
+      <c r="S49" t="n">
+        <v>0</v>
+      </c>
+      <c r="T49" t="n">
+        <v>0</v>
+      </c>
+      <c r="U49" t="n">
+        <v>0</v>
+      </c>
+      <c r="V49" t="n">
+        <v>0</v>
+      </c>
+      <c r="W49" t="n">
         <v>24</v>
-      </c>
-      <c r="O49" t="n">
-        <v>0</v>
-      </c>
-      <c r="P49" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q49" t="n">
-        <v>0</v>
-      </c>
-      <c r="R49" t="n">
-        <v>0</v>
-      </c>
-      <c r="S49" t="n">
-        <v>0</v>
-      </c>
-      <c r="T49" t="n">
-        <v>0</v>
-      </c>
-      <c r="U49" t="n">
-        <v>0</v>
-      </c>
-      <c r="V49" t="n">
-        <v>0</v>
-      </c>
-      <c r="W49" t="n">
-        <v>0</v>
       </c>
       <c r="X49" t="n">
         <v>0</v>
@@ -4444,34 +4444,34 @@
         <v>0</v>
       </c>
       <c r="N50" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O50" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P50" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q50" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R50" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S50" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T50" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U50" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V50" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W50" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="O50" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P50" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q50" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R50" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S50" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T50" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U50" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V50" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W50" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="X50" s="5" t="n">
         <v>0</v>
@@ -4523,34 +4523,34 @@
         <v>0</v>
       </c>
       <c r="N51" t="n">
+        <v>0</v>
+      </c>
+      <c r="O51" t="n">
+        <v>0</v>
+      </c>
+      <c r="P51" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>0</v>
+      </c>
+      <c r="R51" t="n">
+        <v>0</v>
+      </c>
+      <c r="S51" t="n">
+        <v>0</v>
+      </c>
+      <c r="T51" t="n">
+        <v>0</v>
+      </c>
+      <c r="U51" t="n">
+        <v>0</v>
+      </c>
+      <c r="V51" t="n">
+        <v>0</v>
+      </c>
+      <c r="W51" t="n">
         <v>24</v>
-      </c>
-      <c r="O51" t="n">
-        <v>0</v>
-      </c>
-      <c r="P51" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q51" t="n">
-        <v>0</v>
-      </c>
-      <c r="R51" t="n">
-        <v>0</v>
-      </c>
-      <c r="S51" t="n">
-        <v>0</v>
-      </c>
-      <c r="T51" t="n">
-        <v>0</v>
-      </c>
-      <c r="U51" t="n">
-        <v>0</v>
-      </c>
-      <c r="V51" t="n">
-        <v>0</v>
-      </c>
-      <c r="W51" t="n">
-        <v>0</v>
       </c>
       <c r="X51" t="n">
         <v>0</v>
@@ -4602,34 +4602,34 @@
         <v>0</v>
       </c>
       <c r="N52" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O52" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P52" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q52" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R52" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S52" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T52" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U52" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V52" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W52" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="O52" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P52" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q52" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R52" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S52" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T52" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U52" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V52" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W52" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="X52" s="5" t="n">
         <v>0</v>
@@ -4681,34 +4681,34 @@
         <v>0</v>
       </c>
       <c r="N53" t="n">
+        <v>0</v>
+      </c>
+      <c r="O53" t="n">
+        <v>0</v>
+      </c>
+      <c r="P53" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>0</v>
+      </c>
+      <c r="R53" t="n">
+        <v>0</v>
+      </c>
+      <c r="S53" t="n">
+        <v>0</v>
+      </c>
+      <c r="T53" t="n">
+        <v>0</v>
+      </c>
+      <c r="U53" t="n">
+        <v>0</v>
+      </c>
+      <c r="V53" t="n">
+        <v>0</v>
+      </c>
+      <c r="W53" t="n">
         <v>24</v>
-      </c>
-      <c r="O53" t="n">
-        <v>0</v>
-      </c>
-      <c r="P53" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q53" t="n">
-        <v>0</v>
-      </c>
-      <c r="R53" t="n">
-        <v>0</v>
-      </c>
-      <c r="S53" t="n">
-        <v>0</v>
-      </c>
-      <c r="T53" t="n">
-        <v>0</v>
-      </c>
-      <c r="U53" t="n">
-        <v>0</v>
-      </c>
-      <c r="V53" t="n">
-        <v>0</v>
-      </c>
-      <c r="W53" t="n">
-        <v>0</v>
       </c>
       <c r="X53" t="n">
         <v>0</v>
@@ -4760,34 +4760,34 @@
         <v>0</v>
       </c>
       <c r="N54" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O54" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P54" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q54" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R54" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S54" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T54" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U54" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V54" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W54" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="O54" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P54" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q54" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R54" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S54" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T54" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U54" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V54" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W54" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="X54" s="5" t="n">
         <v>0</v>
@@ -4839,34 +4839,34 @@
         <v>0</v>
       </c>
       <c r="N55" t="n">
+        <v>0</v>
+      </c>
+      <c r="O55" t="n">
+        <v>0</v>
+      </c>
+      <c r="P55" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>0</v>
+      </c>
+      <c r="R55" t="n">
+        <v>0</v>
+      </c>
+      <c r="S55" t="n">
+        <v>0</v>
+      </c>
+      <c r="T55" t="n">
+        <v>0</v>
+      </c>
+      <c r="U55" t="n">
+        <v>0</v>
+      </c>
+      <c r="V55" t="n">
+        <v>0</v>
+      </c>
+      <c r="W55" t="n">
         <v>24</v>
-      </c>
-      <c r="O55" t="n">
-        <v>0</v>
-      </c>
-      <c r="P55" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q55" t="n">
-        <v>0</v>
-      </c>
-      <c r="R55" t="n">
-        <v>0</v>
-      </c>
-      <c r="S55" t="n">
-        <v>0</v>
-      </c>
-      <c r="T55" t="n">
-        <v>0</v>
-      </c>
-      <c r="U55" t="n">
-        <v>0</v>
-      </c>
-      <c r="V55" t="n">
-        <v>0</v>
-      </c>
-      <c r="W55" t="n">
-        <v>0</v>
       </c>
       <c r="X55" t="n">
         <v>0</v>
@@ -4918,34 +4918,34 @@
         <v>0</v>
       </c>
       <c r="N56" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O56" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P56" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q56" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R56" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S56" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T56" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U56" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V56" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W56" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="O56" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P56" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q56" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R56" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S56" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T56" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U56" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V56" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W56" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="X56" s="5" t="n">
         <v>0</v>
@@ -4997,34 +4997,34 @@
         <v>0</v>
       </c>
       <c r="N57" t="n">
+        <v>0</v>
+      </c>
+      <c r="O57" t="n">
+        <v>0</v>
+      </c>
+      <c r="P57" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>0</v>
+      </c>
+      <c r="R57" t="n">
+        <v>0</v>
+      </c>
+      <c r="S57" t="n">
+        <v>0</v>
+      </c>
+      <c r="T57" t="n">
+        <v>0</v>
+      </c>
+      <c r="U57" t="n">
+        <v>0</v>
+      </c>
+      <c r="V57" t="n">
+        <v>0</v>
+      </c>
+      <c r="W57" t="n">
         <v>24</v>
-      </c>
-      <c r="O57" t="n">
-        <v>0</v>
-      </c>
-      <c r="P57" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q57" t="n">
-        <v>0</v>
-      </c>
-      <c r="R57" t="n">
-        <v>0</v>
-      </c>
-      <c r="S57" t="n">
-        <v>0</v>
-      </c>
-      <c r="T57" t="n">
-        <v>0</v>
-      </c>
-      <c r="U57" t="n">
-        <v>0</v>
-      </c>
-      <c r="V57" t="n">
-        <v>0</v>
-      </c>
-      <c r="W57" t="n">
-        <v>0</v>
       </c>
       <c r="X57" t="n">
         <v>0</v>
@@ -5076,34 +5076,34 @@
         <v>0</v>
       </c>
       <c r="N58" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O58" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P58" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q58" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R58" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S58" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T58" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U58" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V58" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W58" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="O58" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P58" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q58" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R58" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S58" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T58" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U58" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V58" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W58" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="X58" s="5" t="n">
         <v>0</v>
@@ -5155,34 +5155,34 @@
         <v>0</v>
       </c>
       <c r="N59" t="n">
+        <v>0</v>
+      </c>
+      <c r="O59" t="n">
+        <v>0</v>
+      </c>
+      <c r="P59" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>0</v>
+      </c>
+      <c r="R59" t="n">
+        <v>0</v>
+      </c>
+      <c r="S59" t="n">
+        <v>0</v>
+      </c>
+      <c r="T59" t="n">
+        <v>0</v>
+      </c>
+      <c r="U59" t="n">
+        <v>0</v>
+      </c>
+      <c r="V59" t="n">
+        <v>0</v>
+      </c>
+      <c r="W59" t="n">
         <v>24</v>
-      </c>
-      <c r="O59" t="n">
-        <v>0</v>
-      </c>
-      <c r="P59" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q59" t="n">
-        <v>0</v>
-      </c>
-      <c r="R59" t="n">
-        <v>0</v>
-      </c>
-      <c r="S59" t="n">
-        <v>0</v>
-      </c>
-      <c r="T59" t="n">
-        <v>0</v>
-      </c>
-      <c r="U59" t="n">
-        <v>0</v>
-      </c>
-      <c r="V59" t="n">
-        <v>0</v>
-      </c>
-      <c r="W59" t="n">
-        <v>0</v>
       </c>
       <c r="X59" t="n">
         <v>0</v>
@@ -5234,34 +5234,34 @@
         <v>0</v>
       </c>
       <c r="N60" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O60" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P60" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q60" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R60" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S60" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T60" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U60" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V60" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W60" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="O60" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P60" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q60" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R60" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S60" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T60" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U60" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V60" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W60" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="X60" s="5" t="n">
         <v>0</v>
@@ -5313,34 +5313,34 @@
         <v>0</v>
       </c>
       <c r="N61" t="n">
+        <v>0</v>
+      </c>
+      <c r="O61" t="n">
+        <v>0</v>
+      </c>
+      <c r="P61" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q61" t="n">
+        <v>0</v>
+      </c>
+      <c r="R61" t="n">
+        <v>0</v>
+      </c>
+      <c r="S61" t="n">
+        <v>0</v>
+      </c>
+      <c r="T61" t="n">
+        <v>0</v>
+      </c>
+      <c r="U61" t="n">
+        <v>0</v>
+      </c>
+      <c r="V61" t="n">
+        <v>0</v>
+      </c>
+      <c r="W61" t="n">
         <v>24</v>
-      </c>
-      <c r="O61" t="n">
-        <v>0</v>
-      </c>
-      <c r="P61" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q61" t="n">
-        <v>0</v>
-      </c>
-      <c r="R61" t="n">
-        <v>0</v>
-      </c>
-      <c r="S61" t="n">
-        <v>0</v>
-      </c>
-      <c r="T61" t="n">
-        <v>0</v>
-      </c>
-      <c r="U61" t="n">
-        <v>0</v>
-      </c>
-      <c r="V61" t="n">
-        <v>0</v>
-      </c>
-      <c r="W61" t="n">
-        <v>0</v>
       </c>
       <c r="X61" t="n">
         <v>0</v>
@@ -5392,34 +5392,34 @@
         <v>0</v>
       </c>
       <c r="N62" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O62" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P62" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q62" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R62" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S62" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T62" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U62" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V62" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W62" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="O62" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P62" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q62" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R62" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S62" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T62" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U62" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V62" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W62" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="X62" s="5" t="n">
         <v>0</v>
@@ -5471,34 +5471,34 @@
         <v>0</v>
       </c>
       <c r="N63" t="n">
+        <v>0</v>
+      </c>
+      <c r="O63" t="n">
+        <v>0</v>
+      </c>
+      <c r="P63" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q63" t="n">
+        <v>0</v>
+      </c>
+      <c r="R63" t="n">
+        <v>0</v>
+      </c>
+      <c r="S63" t="n">
+        <v>0</v>
+      </c>
+      <c r="T63" t="n">
+        <v>0</v>
+      </c>
+      <c r="U63" t="n">
+        <v>0</v>
+      </c>
+      <c r="V63" t="n">
+        <v>0</v>
+      </c>
+      <c r="W63" t="n">
         <v>24</v>
-      </c>
-      <c r="O63" t="n">
-        <v>0</v>
-      </c>
-      <c r="P63" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q63" t="n">
-        <v>0</v>
-      </c>
-      <c r="R63" t="n">
-        <v>0</v>
-      </c>
-      <c r="S63" t="n">
-        <v>0</v>
-      </c>
-      <c r="T63" t="n">
-        <v>0</v>
-      </c>
-      <c r="U63" t="n">
-        <v>0</v>
-      </c>
-      <c r="V63" t="n">
-        <v>0</v>
-      </c>
-      <c r="W63" t="n">
-        <v>0</v>
       </c>
       <c r="X63" t="n">
         <v>0</v>
@@ -5550,34 +5550,34 @@
         <v>0</v>
       </c>
       <c r="N64" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O64" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P64" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q64" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R64" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S64" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T64" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U64" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V64" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W64" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="O64" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P64" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q64" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R64" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S64" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T64" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U64" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V64" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W64" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="X64" s="5" t="n">
         <v>0</v>
@@ -5629,34 +5629,34 @@
         <v>0</v>
       </c>
       <c r="N65" t="n">
+        <v>0</v>
+      </c>
+      <c r="O65" t="n">
+        <v>0</v>
+      </c>
+      <c r="P65" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q65" t="n">
+        <v>0</v>
+      </c>
+      <c r="R65" t="n">
+        <v>0</v>
+      </c>
+      <c r="S65" t="n">
+        <v>0</v>
+      </c>
+      <c r="T65" t="n">
+        <v>0</v>
+      </c>
+      <c r="U65" t="n">
+        <v>0</v>
+      </c>
+      <c r="V65" t="n">
+        <v>0</v>
+      </c>
+      <c r="W65" t="n">
         <v>24</v>
-      </c>
-      <c r="O65" t="n">
-        <v>0</v>
-      </c>
-      <c r="P65" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q65" t="n">
-        <v>0</v>
-      </c>
-      <c r="R65" t="n">
-        <v>0</v>
-      </c>
-      <c r="S65" t="n">
-        <v>0</v>
-      </c>
-      <c r="T65" t="n">
-        <v>0</v>
-      </c>
-      <c r="U65" t="n">
-        <v>0</v>
-      </c>
-      <c r="V65" t="n">
-        <v>0</v>
-      </c>
-      <c r="W65" t="n">
-        <v>0</v>
       </c>
       <c r="X65" t="n">
         <v>0</v>
@@ -5708,34 +5708,34 @@
         <v>0</v>
       </c>
       <c r="N66" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O66" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P66" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q66" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R66" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S66" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T66" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U66" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V66" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W66" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="O66" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P66" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q66" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R66" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S66" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T66" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U66" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V66" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W66" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="X66" s="5" t="n">
         <v>0</v>
@@ -5786,6 +5786,9 @@
       <c r="M67" t="n">
         <v>0</v>
       </c>
+      <c r="N67" t="n">
+        <v>0</v>
+      </c>
       <c r="O67" t="n">
         <v>0</v>
       </c>
@@ -5808,9 +5811,6 @@
         <v>0</v>
       </c>
       <c r="V67" t="n">
-        <v>0</v>
-      </c>
-      <c r="W67" t="n">
         <v>0</v>
       </c>
       <c r="X67" t="n">
@@ -5863,34 +5863,34 @@
         <v>0</v>
       </c>
       <c r="N68" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O68" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P68" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q68" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R68" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S68" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T68" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U68" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V68" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W68" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="O68" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P68" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q68" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R68" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S68" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T68" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U68" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V68" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W68" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="X68" s="5" t="n">
         <v>0</v>
@@ -5938,6 +5938,9 @@
       <c r="M69" t="n">
         <v>0</v>
       </c>
+      <c r="N69" t="n">
+        <v>0</v>
+      </c>
       <c r="O69" t="n">
         <v>0</v>
       </c>
@@ -5960,9 +5963,6 @@
         <v>0</v>
       </c>
       <c r="V69" t="n">
-        <v>0</v>
-      </c>
-      <c r="W69" t="n">
         <v>0</v>
       </c>
       <c r="X69" t="n">
@@ -6015,34 +6015,34 @@
         <v>0</v>
       </c>
       <c r="N70" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O70" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P70" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q70" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R70" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S70" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T70" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U70" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V70" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W70" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="O70" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P70" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q70" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R70" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S70" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T70" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U70" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V70" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W70" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="X70" s="5" t="n">
         <v>0</v>
@@ -6094,34 +6094,34 @@
         <v>0</v>
       </c>
       <c r="N71" t="n">
+        <v>0</v>
+      </c>
+      <c r="O71" t="n">
+        <v>0</v>
+      </c>
+      <c r="P71" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q71" t="n">
+        <v>0</v>
+      </c>
+      <c r="R71" t="n">
+        <v>0</v>
+      </c>
+      <c r="S71" t="n">
+        <v>0</v>
+      </c>
+      <c r="T71" t="n">
+        <v>0</v>
+      </c>
+      <c r="U71" t="n">
+        <v>0</v>
+      </c>
+      <c r="V71" t="n">
+        <v>0</v>
+      </c>
+      <c r="W71" t="n">
         <v>24</v>
-      </c>
-      <c r="O71" t="n">
-        <v>0</v>
-      </c>
-      <c r="P71" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q71" t="n">
-        <v>0</v>
-      </c>
-      <c r="R71" t="n">
-        <v>0</v>
-      </c>
-      <c r="S71" t="n">
-        <v>0</v>
-      </c>
-      <c r="T71" t="n">
-        <v>0</v>
-      </c>
-      <c r="U71" t="n">
-        <v>0</v>
-      </c>
-      <c r="V71" t="n">
-        <v>0</v>
-      </c>
-      <c r="W71" t="n">
-        <v>0</v>
       </c>
       <c r="X71" t="n">
         <v>0</v>
@@ -6173,34 +6173,34 @@
         <v>0</v>
       </c>
       <c r="N72" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O72" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P72" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q72" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R72" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S72" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T72" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U72" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V72" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W72" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="O72" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P72" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q72" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R72" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S72" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T72" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U72" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V72" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W72" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="X72" s="5" t="n">
         <v>0</v>
@@ -6252,34 +6252,34 @@
         <v>0</v>
       </c>
       <c r="N73" t="n">
+        <v>0</v>
+      </c>
+      <c r="O73" t="n">
+        <v>0</v>
+      </c>
+      <c r="P73" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q73" t="n">
+        <v>0</v>
+      </c>
+      <c r="R73" t="n">
+        <v>0</v>
+      </c>
+      <c r="S73" t="n">
+        <v>0</v>
+      </c>
+      <c r="T73" t="n">
+        <v>0</v>
+      </c>
+      <c r="U73" t="n">
+        <v>0</v>
+      </c>
+      <c r="V73" t="n">
+        <v>0</v>
+      </c>
+      <c r="W73" t="n">
         <v>24</v>
-      </c>
-      <c r="O73" t="n">
-        <v>0</v>
-      </c>
-      <c r="P73" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q73" t="n">
-        <v>0</v>
-      </c>
-      <c r="R73" t="n">
-        <v>0</v>
-      </c>
-      <c r="S73" t="n">
-        <v>0</v>
-      </c>
-      <c r="T73" t="n">
-        <v>0</v>
-      </c>
-      <c r="U73" t="n">
-        <v>0</v>
-      </c>
-      <c r="V73" t="n">
-        <v>0</v>
-      </c>
-      <c r="W73" t="n">
-        <v>0</v>
       </c>
       <c r="X73" t="n">
         <v>0</v>
@@ -6331,34 +6331,34 @@
         <v>0</v>
       </c>
       <c r="N74" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O74" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P74" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q74" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R74" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S74" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T74" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U74" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V74" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W74" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="O74" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P74" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q74" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R74" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S74" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T74" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U74" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V74" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W74" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="X74" s="5" t="n">
         <v>0</v>
@@ -6410,34 +6410,34 @@
         <v>0</v>
       </c>
       <c r="N75" t="n">
+        <v>0</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>0</v>
+      </c>
+      <c r="W75" t="n">
         <v>24</v>
-      </c>
-      <c r="O75" t="n">
-        <v>0</v>
-      </c>
-      <c r="P75" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q75" t="n">
-        <v>0</v>
-      </c>
-      <c r="R75" t="n">
-        <v>0</v>
-      </c>
-      <c r="S75" t="n">
-        <v>0</v>
-      </c>
-      <c r="T75" t="n">
-        <v>0</v>
-      </c>
-      <c r="U75" t="n">
-        <v>0</v>
-      </c>
-      <c r="V75" t="n">
-        <v>0</v>
-      </c>
-      <c r="W75" t="n">
-        <v>0</v>
       </c>
       <c r="X75" t="n">
         <v>0</v>
@@ -6479,9 +6479,7 @@
       <c r="J76" s="5" t="n">
         <v>26</v>
       </c>
-      <c r="K76" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="K76" s="5" t="n"/>
       <c r="L76" s="5" t="n">
         <v>0</v>
       </c>
@@ -6489,30 +6487,32 @@
         <v>0</v>
       </c>
       <c r="N76" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O76" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P76" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q76" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R76" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S76" s="5" t="n"/>
+      <c r="T76" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U76" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V76" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W76" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="O76" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P76" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q76" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R76" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S76" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T76" s="5" t="n"/>
-      <c r="U76" s="5" t="n"/>
-      <c r="V76" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W76" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="X76" s="5" t="n">
         <v>0</v>
@@ -6563,6 +6563,9 @@
       <c r="M77" t="n">
         <v>0</v>
       </c>
+      <c r="N77" t="n">
+        <v>0</v>
+      </c>
       <c r="O77" t="n">
         <v>0</v>
       </c>
@@ -6585,9 +6588,6 @@
         <v>0</v>
       </c>
       <c r="V77" t="n">
-        <v>0</v>
-      </c>
-      <c r="W77" t="n">
         <v>0</v>
       </c>
       <c r="X77" t="n">
@@ -6640,34 +6640,34 @@
         <v>0</v>
       </c>
       <c r="N78" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O78" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P78" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q78" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R78" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S78" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T78" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U78" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V78" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W78" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="O78" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P78" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q78" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R78" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S78" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T78" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U78" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V78" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W78" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="X78" s="5" t="n">
         <v>0</v>
@@ -6718,6 +6718,9 @@
       <c r="M79" t="n">
         <v>0</v>
       </c>
+      <c r="N79" t="n">
+        <v>0</v>
+      </c>
       <c r="O79" t="n">
         <v>0</v>
       </c>
@@ -6740,9 +6743,6 @@
         <v>0</v>
       </c>
       <c r="V79" t="n">
-        <v>0</v>
-      </c>
-      <c r="W79" t="n">
         <v>0</v>
       </c>
       <c r="X79" t="n">
@@ -6794,7 +6794,9 @@
       <c r="M80" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="N80" s="5" t="n"/>
+      <c r="N80" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="O80" s="5" t="n">
         <v>0</v>
       </c>
@@ -6819,9 +6821,7 @@
       <c r="V80" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="W80" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="W80" s="5" t="n"/>
       <c r="X80" s="5" t="n">
         <v>0</v>
       </c>
@@ -6872,34 +6872,34 @@
         <v>0</v>
       </c>
       <c r="N81" t="n">
+        <v>0</v>
+      </c>
+      <c r="O81" t="n">
+        <v>0</v>
+      </c>
+      <c r="P81" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q81" t="n">
+        <v>0</v>
+      </c>
+      <c r="R81" t="n">
+        <v>0</v>
+      </c>
+      <c r="S81" t="n">
+        <v>0</v>
+      </c>
+      <c r="T81" t="n">
+        <v>0</v>
+      </c>
+      <c r="U81" t="n">
+        <v>0</v>
+      </c>
+      <c r="V81" t="n">
+        <v>0</v>
+      </c>
+      <c r="W81" t="n">
         <v>24</v>
-      </c>
-      <c r="O81" t="n">
-        <v>0</v>
-      </c>
-      <c r="P81" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q81" t="n">
-        <v>0</v>
-      </c>
-      <c r="R81" t="n">
-        <v>0</v>
-      </c>
-      <c r="S81" t="n">
-        <v>0</v>
-      </c>
-      <c r="T81" t="n">
-        <v>0</v>
-      </c>
-      <c r="U81" t="n">
-        <v>0</v>
-      </c>
-      <c r="V81" t="n">
-        <v>0</v>
-      </c>
-      <c r="W81" t="n">
-        <v>0</v>
       </c>
       <c r="X81" t="n">
         <v>0</v>
@@ -6950,7 +6950,9 @@
       <c r="M82" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="N82" s="5" t="n"/>
+      <c r="N82" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="O82" s="5" t="n">
         <v>0</v>
       </c>
@@ -6975,9 +6977,7 @@
       <c r="V82" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="W82" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="W82" s="5" t="n"/>
       <c r="X82" s="5" t="n">
         <v>0</v>
       </c>
@@ -7025,34 +7025,34 @@
         <v>0</v>
       </c>
       <c r="N83" t="n">
+        <v>0</v>
+      </c>
+      <c r="O83" t="n">
+        <v>0</v>
+      </c>
+      <c r="P83" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q83" t="n">
+        <v>0</v>
+      </c>
+      <c r="R83" t="n">
+        <v>0</v>
+      </c>
+      <c r="S83" t="n">
+        <v>0</v>
+      </c>
+      <c r="T83" t="n">
+        <v>0</v>
+      </c>
+      <c r="U83" t="n">
+        <v>0</v>
+      </c>
+      <c r="V83" t="n">
+        <v>0</v>
+      </c>
+      <c r="W83" t="n">
         <v>24</v>
-      </c>
-      <c r="O83" t="n">
-        <v>0</v>
-      </c>
-      <c r="P83" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q83" t="n">
-        <v>0</v>
-      </c>
-      <c r="R83" t="n">
-        <v>0</v>
-      </c>
-      <c r="S83" t="n">
-        <v>0</v>
-      </c>
-      <c r="T83" t="n">
-        <v>0</v>
-      </c>
-      <c r="U83" t="n">
-        <v>0</v>
-      </c>
-      <c r="V83" t="n">
-        <v>0</v>
-      </c>
-      <c r="W83" t="n">
-        <v>0</v>
       </c>
       <c r="X83" t="n">
         <v>0</v>
@@ -7104,34 +7104,34 @@
         <v>0</v>
       </c>
       <c r="N84" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O84" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P84" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q84" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R84" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S84" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T84" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U84" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V84" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W84" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="O84" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P84" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q84" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R84" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S84" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T84" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U84" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V84" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W84" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="X84" s="5" t="n">
         <v>0</v>
@@ -7182,6 +7182,9 @@
       <c r="M85" t="n">
         <v>0</v>
       </c>
+      <c r="N85" t="n">
+        <v>0</v>
+      </c>
       <c r="O85" t="n">
         <v>0</v>
       </c>
@@ -7204,9 +7207,6 @@
         <v>0</v>
       </c>
       <c r="V85" t="n">
-        <v>0</v>
-      </c>
-      <c r="W85" t="n">
         <v>0</v>
       </c>
       <c r="X85" t="n">
@@ -7258,7 +7258,9 @@
       <c r="M86" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="N86" s="5" t="n"/>
+      <c r="N86" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="O86" s="5" t="n">
         <v>0</v>
       </c>
@@ -7283,9 +7285,7 @@
       <c r="V86" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="W86" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="W86" s="5" t="n"/>
       <c r="X86" s="5" t="n">
         <v>0</v>
       </c>
@@ -7335,6 +7335,9 @@
       <c r="M87" t="n">
         <v>0</v>
       </c>
+      <c r="N87" t="n">
+        <v>0</v>
+      </c>
       <c r="O87" t="n">
         <v>0</v>
       </c>
@@ -7357,9 +7360,6 @@
         <v>0</v>
       </c>
       <c r="V87" t="n">
-        <v>0</v>
-      </c>
-      <c r="W87" t="n">
         <v>0</v>
       </c>
       <c r="X87" t="n">
@@ -7411,7 +7411,9 @@
       <c r="M88" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="N88" s="5" t="n"/>
+      <c r="N88" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="O88" s="5" t="n">
         <v>0</v>
       </c>
@@ -7436,9 +7438,7 @@
       <c r="V88" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="W88" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="W88" s="5" t="n"/>
       <c r="X88" s="5" t="n">
         <v>0</v>
       </c>
@@ -7488,6 +7488,9 @@
       <c r="M89" t="n">
         <v>0</v>
       </c>
+      <c r="N89" t="n">
+        <v>0</v>
+      </c>
       <c r="O89" t="n">
         <v>0</v>
       </c>
@@ -7510,9 +7513,6 @@
         <v>0</v>
       </c>
       <c r="V89" t="n">
-        <v>0</v>
-      </c>
-      <c r="W89" t="n">
         <v>0</v>
       </c>
       <c r="X89" t="n">
@@ -7563,34 +7563,34 @@
         <v>0</v>
       </c>
       <c r="N90" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O90" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P90" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q90" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R90" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S90" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T90" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U90" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V90" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W90" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="O90" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P90" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q90" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R90" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S90" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T90" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U90" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V90" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W90" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="X90" s="5" t="n">
         <v>0</v>
@@ -7641,6 +7641,9 @@
       <c r="M91" t="n">
         <v>0</v>
       </c>
+      <c r="N91" t="n">
+        <v>0</v>
+      </c>
       <c r="O91" t="n">
         <v>0</v>
       </c>
@@ -7663,9 +7666,6 @@
         <v>0</v>
       </c>
       <c r="V91" t="n">
-        <v>0</v>
-      </c>
-      <c r="W91" t="n">
         <v>0</v>
       </c>
       <c r="X91" t="n">
@@ -7717,7 +7717,9 @@
       <c r="M92" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="N92" s="5" t="n"/>
+      <c r="N92" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="O92" s="5" t="n">
         <v>0</v>
       </c>
@@ -7742,9 +7744,7 @@
       <c r="V92" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="W92" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="W92" s="5" t="n"/>
       <c r="X92" s="5" t="n">
         <v>0</v>
       </c>
@@ -7794,6 +7794,9 @@
       <c r="M93" t="n">
         <v>0</v>
       </c>
+      <c r="N93" t="n">
+        <v>0</v>
+      </c>
       <c r="O93" t="n">
         <v>0</v>
       </c>
@@ -7816,9 +7819,6 @@
         <v>0</v>
       </c>
       <c r="V93" t="n">
-        <v>0</v>
-      </c>
-      <c r="W93" t="n">
         <v>0</v>
       </c>
       <c r="X93" t="n">
@@ -7870,7 +7870,9 @@
       <c r="M94" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="N94" s="5" t="n"/>
+      <c r="N94" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="O94" s="5" t="n">
         <v>0</v>
       </c>
@@ -7895,9 +7897,7 @@
       <c r="V94" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="W94" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="W94" s="5" t="n"/>
       <c r="X94" s="5" t="n">
         <v>0</v>
       </c>
@@ -7947,6 +7947,9 @@
       <c r="M95" t="n">
         <v>0</v>
       </c>
+      <c r="N95" t="n">
+        <v>0</v>
+      </c>
       <c r="O95" t="n">
         <v>0</v>
       </c>
@@ -7969,9 +7972,6 @@
         <v>0</v>
       </c>
       <c r="V95" t="n">
-        <v>0</v>
-      </c>
-      <c r="W95" t="n">
         <v>0</v>
       </c>
       <c r="X95" t="n">
@@ -8023,7 +8023,9 @@
       <c r="M96" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="N96" s="5" t="n"/>
+      <c r="N96" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="O96" s="5" t="n">
         <v>0</v>
       </c>
@@ -8048,9 +8050,7 @@
       <c r="V96" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="W96" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="W96" s="5" t="n"/>
       <c r="X96" s="5" t="n">
         <v>0</v>
       </c>
@@ -8097,6 +8097,9 @@
       <c r="M97" t="n">
         <v>0</v>
       </c>
+      <c r="N97" t="n">
+        <v>0</v>
+      </c>
       <c r="O97" t="n">
         <v>0</v>
       </c>
@@ -8119,9 +8122,6 @@
         <v>0</v>
       </c>
       <c r="V97" t="n">
-        <v>0</v>
-      </c>
-      <c r="W97" t="n">
         <v>0</v>
       </c>
       <c r="X97" t="n">
@@ -8173,7 +8173,9 @@
       <c r="M98" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="N98" s="5" t="n"/>
+      <c r="N98" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="O98" s="5" t="n">
         <v>0</v>
       </c>
@@ -8198,9 +8200,7 @@
       <c r="V98" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="W98" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="W98" s="5" t="n"/>
       <c r="X98" s="5" t="n">
         <v>0</v>
       </c>
@@ -8250,6 +8250,9 @@
       <c r="M99" t="n">
         <v>0</v>
       </c>
+      <c r="N99" t="n">
+        <v>0</v>
+      </c>
       <c r="O99" t="n">
         <v>0</v>
       </c>
@@ -8272,9 +8275,6 @@
         <v>0</v>
       </c>
       <c r="V99" t="n">
-        <v>0</v>
-      </c>
-      <c r="W99" t="n">
         <v>0</v>
       </c>
       <c r="X99" t="n">
@@ -8326,7 +8326,9 @@
       <c r="M100" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="N100" s="5" t="n"/>
+      <c r="N100" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="O100" s="5" t="n">
         <v>0</v>
       </c>
@@ -8351,9 +8353,7 @@
       <c r="V100" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="W100" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="W100" s="5" t="n"/>
       <c r="X100" s="5" t="n">
         <v>0</v>
       </c>
@@ -8403,6 +8403,9 @@
       <c r="M101" t="n">
         <v>0</v>
       </c>
+      <c r="N101" t="n">
+        <v>0</v>
+      </c>
       <c r="O101" t="n">
         <v>0</v>
       </c>
@@ -8425,9 +8428,6 @@
         <v>0</v>
       </c>
       <c r="V101" t="n">
-        <v>0</v>
-      </c>
-      <c r="W101" t="n">
         <v>0</v>
       </c>
       <c r="X101" t="n">
@@ -8479,7 +8479,9 @@
       <c r="M102" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="N102" s="5" t="n"/>
+      <c r="N102" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="O102" s="5" t="n">
         <v>0</v>
       </c>
@@ -8504,9 +8506,7 @@
       <c r="V102" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="W102" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="W102" s="5" t="n"/>
       <c r="X102" s="5" t="n">
         <v>0</v>
       </c>
@@ -8556,6 +8556,9 @@
       <c r="M103" t="n">
         <v>0</v>
       </c>
+      <c r="N103" t="n">
+        <v>0</v>
+      </c>
       <c r="O103" t="n">
         <v>0</v>
       </c>
@@ -8578,9 +8581,6 @@
         <v>0</v>
       </c>
       <c r="V103" t="n">
-        <v>0</v>
-      </c>
-      <c r="W103" t="n">
         <v>0</v>
       </c>
       <c r="X103" t="n">
@@ -8632,7 +8632,9 @@
       <c r="M104" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="N104" s="5" t="n"/>
+      <c r="N104" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="O104" s="5" t="n">
         <v>0</v>
       </c>
@@ -8657,9 +8659,7 @@
       <c r="V104" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="W104" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="W104" s="5" t="n"/>
       <c r="X104" s="5" t="n">
         <v>0</v>
       </c>
@@ -8709,6 +8709,9 @@
       <c r="M105" t="n">
         <v>0</v>
       </c>
+      <c r="N105" t="n">
+        <v>0</v>
+      </c>
       <c r="O105" t="n">
         <v>0</v>
       </c>
@@ -8731,9 +8734,6 @@
         <v>0</v>
       </c>
       <c r="V105" t="n">
-        <v>0</v>
-      </c>
-      <c r="W105" t="n">
         <v>0</v>
       </c>
       <c r="X105" t="n">
@@ -8785,7 +8785,9 @@
       <c r="M106" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="N106" s="5" t="n"/>
+      <c r="N106" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="O106" s="5" t="n">
         <v>0</v>
       </c>
@@ -8810,9 +8812,7 @@
       <c r="V106" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="W106" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="W106" s="5" t="n"/>
       <c r="X106" s="5" t="n">
         <v>0</v>
       </c>
@@ -8862,6 +8862,9 @@
       <c r="M107" t="n">
         <v>0</v>
       </c>
+      <c r="N107" t="n">
+        <v>0</v>
+      </c>
       <c r="O107" t="n">
         <v>0</v>
       </c>
@@ -8884,9 +8887,6 @@
         <v>0</v>
       </c>
       <c r="V107" t="n">
-        <v>0</v>
-      </c>
-      <c r="W107" t="n">
         <v>0</v>
       </c>
       <c r="X107" t="n">
@@ -8938,7 +8938,9 @@
       <c r="M108" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="N108" s="5" t="n"/>
+      <c r="N108" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="O108" s="5" t="n">
         <v>0</v>
       </c>
@@ -8963,9 +8965,7 @@
       <c r="V108" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="W108" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="W108" s="5" t="n"/>
       <c r="X108" s="5" t="n">
         <v>0</v>
       </c>
@@ -9015,6 +9015,9 @@
       <c r="M109" t="n">
         <v>0</v>
       </c>
+      <c r="N109" t="n">
+        <v>0</v>
+      </c>
       <c r="O109" t="n">
         <v>0</v>
       </c>
@@ -9037,9 +9040,6 @@
         <v>0</v>
       </c>
       <c r="V109" t="n">
-        <v>0</v>
-      </c>
-      <c r="W109" t="n">
         <v>0</v>
       </c>
       <c r="X109" t="n">
@@ -9091,7 +9091,9 @@
       <c r="M110" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="N110" s="5" t="n"/>
+      <c r="N110" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="O110" s="5" t="n">
         <v>0</v>
       </c>
@@ -9116,9 +9118,7 @@
       <c r="V110" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="W110" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="W110" s="5" t="n"/>
       <c r="X110" s="5" t="n">
         <v>0</v>
       </c>
@@ -9165,6 +9165,9 @@
       <c r="M111" t="n">
         <v>0</v>
       </c>
+      <c r="N111" t="n">
+        <v>0</v>
+      </c>
       <c r="O111" t="n">
         <v>0</v>
       </c>
@@ -9187,9 +9190,6 @@
         <v>0</v>
       </c>
       <c r="V111" t="n">
-        <v>0</v>
-      </c>
-      <c r="W111" t="n">
         <v>0</v>
       </c>
       <c r="X111" t="n">
@@ -9241,7 +9241,9 @@
       <c r="M112" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="N112" s="5" t="n"/>
+      <c r="N112" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="O112" s="5" t="n">
         <v>0</v>
       </c>
@@ -9266,9 +9268,7 @@
       <c r="V112" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="W112" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="W112" s="5" t="n"/>
       <c r="X112" s="5" t="n">
         <v>0</v>
       </c>
@@ -9318,6 +9318,9 @@
       <c r="M113" t="n">
         <v>0</v>
       </c>
+      <c r="N113" t="n">
+        <v>0</v>
+      </c>
       <c r="O113" t="n">
         <v>0</v>
       </c>
@@ -9340,9 +9343,6 @@
         <v>0</v>
       </c>
       <c r="V113" t="n">
-        <v>0</v>
-      </c>
-      <c r="W113" t="n">
         <v>0</v>
       </c>
       <c r="X113" t="n">
@@ -9394,7 +9394,9 @@
       <c r="M114" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="N114" s="5" t="n"/>
+      <c r="N114" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="O114" s="5" t="n">
         <v>0</v>
       </c>
@@ -9419,13 +9421,87 @@
       <c r="V114" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="W114" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="W114" s="5" t="n"/>
       <c r="X114" s="5" t="n">
         <v>0</v>
       </c>
       <c r="Y114" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B115" t="n">
+        <v>892</v>
+      </c>
+      <c r="C115" t="n">
+        <v>454</v>
+      </c>
+      <c r="D115" t="n">
+        <v>389</v>
+      </c>
+      <c r="E115" t="n">
+        <v>291</v>
+      </c>
+      <c r="F115" t="n">
+        <v>266</v>
+      </c>
+      <c r="G115" t="n">
+        <v>206</v>
+      </c>
+      <c r="H115" t="n">
+        <v>101</v>
+      </c>
+      <c r="I115" t="n">
+        <v>34</v>
+      </c>
+      <c r="J115" t="n">
+        <v>22</v>
+      </c>
+      <c r="K115" t="n">
+        <v>0</v>
+      </c>
+      <c r="L115" t="n">
+        <v>0</v>
+      </c>
+      <c r="M115" t="n">
+        <v>0</v>
+      </c>
+      <c r="N115" t="n">
+        <v>0</v>
+      </c>
+      <c r="O115" t="n">
+        <v>0</v>
+      </c>
+      <c r="P115" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q115" t="n">
+        <v>0</v>
+      </c>
+      <c r="R115" t="n">
+        <v>0</v>
+      </c>
+      <c r="S115" t="n">
+        <v>0</v>
+      </c>
+      <c r="T115" t="n">
+        <v>0</v>
+      </c>
+      <c r="U115" t="n">
+        <v>0</v>
+      </c>
+      <c r="V115" t="n">
+        <v>0</v>
+      </c>
+      <c r="X115" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y115" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9440,7 +9516,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D1053"/>
+  <dimension ref="A1:D1049"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -9467,7 +9543,7 @@
       </c>
       <c r="D1" s="3" t="inlineStr">
         <is>
-          <t>Lager (2026-10-28)</t>
+          <t>Lager (2026-10-29)</t>
         </is>
       </c>
     </row>
@@ -9488,7 +9564,7 @@
         </is>
       </c>
       <c r="D2" s="4" t="n">
-        <v>467</v>
+        <v>454</v>
       </c>
     </row>
     <row r="3">
@@ -19848,7 +19924,7 @@
         </is>
       </c>
       <c r="D520" s="4" t="n">
-        <v>399</v>
+        <v>379</v>
       </c>
     </row>
     <row r="521">
@@ -27388,7 +27464,7 @@
         </is>
       </c>
       <c r="D897" s="6" t="n">
-        <v>190</v>
+        <v>176</v>
       </c>
     </row>
     <row r="898">
@@ -27828,7 +27904,7 @@
         </is>
       </c>
       <c r="D919" s="6" t="n">
-        <v>20</v>
+        <v>36</v>
       </c>
     </row>
     <row r="920">
@@ -29188,7 +29264,7 @@
         </is>
       </c>
       <c r="D987" s="6" t="n">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="988">
@@ -29208,7 +29284,7 @@
         </is>
       </c>
       <c r="D988" s="4" t="n">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="989">
@@ -30034,12 +30110,12 @@
     <row r="1030">
       <c r="A1030" s="4" t="inlineStr">
         <is>
-          <t>7021294</t>
+          <t>7028545</t>
         </is>
       </c>
       <c r="B1030" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur WLP Backlit</t>
+          <t>Interiörarmatur WLP Backlit PIR</t>
         </is>
       </c>
       <c r="C1030" s="5" t="inlineStr">
@@ -30054,12 +30130,12 @@
     <row r="1031">
       <c r="A1031" s="6" t="inlineStr">
         <is>
-          <t>7021295</t>
+          <t>7024616</t>
         </is>
       </c>
       <c r="B1031" t="inlineStr">
         <is>
-          <t>Interiörarmatur WLP Backlit</t>
+          <t>Interiörarmatur WLP Backlit, ActiveAhead</t>
         </is>
       </c>
       <c r="C1031" t="inlineStr">
@@ -30074,12 +30150,12 @@
     <row r="1032">
       <c r="A1032" s="4" t="inlineStr">
         <is>
-          <t>7024767</t>
+          <t>7024617</t>
         </is>
       </c>
       <c r="B1032" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur WLP Backlit</t>
+          <t>Interiörarmatur WLP Backlit, ActiveAhead</t>
         </is>
       </c>
       <c r="C1032" s="5" t="inlineStr">
@@ -30094,12 +30170,12 @@
     <row r="1033">
       <c r="A1033" s="6" t="inlineStr">
         <is>
-          <t>7024768</t>
+          <t>7024816</t>
         </is>
       </c>
       <c r="B1033" t="inlineStr">
         <is>
-          <t>Interiörarmatur WLP Backlit</t>
+          <t>Interiörarmatur WLP Backlit, ActiveAhead</t>
         </is>
       </c>
       <c r="C1033" t="inlineStr">
@@ -30114,12 +30190,12 @@
     <row r="1034">
       <c r="A1034" s="4" t="inlineStr">
         <is>
-          <t>7028545</t>
+          <t>7024817</t>
         </is>
       </c>
       <c r="B1034" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur WLP Backlit PIR</t>
+          <t>Interiörarmatur WLP Backlit, ActiveAhead</t>
         </is>
       </c>
       <c r="C1034" s="5" t="inlineStr">
@@ -30134,12 +30210,12 @@
     <row r="1035">
       <c r="A1035" s="6" t="inlineStr">
         <is>
-          <t>7024616</t>
+          <t>7026166</t>
         </is>
       </c>
       <c r="B1035" t="inlineStr">
         <is>
-          <t>Interiörarmatur WLP Backlit, ActiveAhead</t>
+          <t>Interiörarmatur WLP Cleanroom</t>
         </is>
       </c>
       <c r="C1035" t="inlineStr">
@@ -30154,12 +30230,12 @@
     <row r="1036">
       <c r="A1036" s="4" t="inlineStr">
         <is>
-          <t>7024617</t>
+          <t>7024618</t>
         </is>
       </c>
       <c r="B1036" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur WLP Backlit, ActiveAhead</t>
+          <t>Interiörarmatur WLP Dor ActiveAhead</t>
         </is>
       </c>
       <c r="C1036" s="5" t="inlineStr">
@@ -30174,12 +30250,12 @@
     <row r="1037">
       <c r="A1037" s="6" t="inlineStr">
         <is>
-          <t>7024816</t>
+          <t>7024779</t>
         </is>
       </c>
       <c r="B1037" t="inlineStr">
         <is>
-          <t>Interiörarmatur WLP Backlit, ActiveAhead</t>
+          <t>Interiörarmatur WLP Dor ActiveAhead</t>
         </is>
       </c>
       <c r="C1037" t="inlineStr">
@@ -30194,12 +30270,12 @@
     <row r="1038">
       <c r="A1038" s="4" t="inlineStr">
         <is>
-          <t>7024817</t>
+          <t>7027313</t>
         </is>
       </c>
       <c r="B1038" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur WLP Backlit, ActiveAhead</t>
+          <t>Interiörarmatur WLP-B</t>
         </is>
       </c>
       <c r="C1038" s="5" t="inlineStr">
@@ -30214,17 +30290,17 @@
     <row r="1039">
       <c r="A1039" s="6" t="inlineStr">
         <is>
-          <t>7026166</t>
+          <t>7028323</t>
         </is>
       </c>
       <c r="B1039" t="inlineStr">
         <is>
-          <t>Interiörarmatur WLP Cleanroom</t>
+          <t>Interiörarmatur Beta Force</t>
         </is>
       </c>
       <c r="C1039" t="inlineStr">
         <is>
-          <t>Westal</t>
+          <t>ZG Lighting</t>
         </is>
       </c>
       <c r="D1039" s="6" t="n">
@@ -30234,17 +30310,17 @@
     <row r="1040">
       <c r="A1040" s="4" t="inlineStr">
         <is>
-          <t>7024618</t>
+          <t>7028324</t>
         </is>
       </c>
       <c r="B1040" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur WLP Dor ActiveAhead</t>
+          <t>Interiörarmatur Beta Force</t>
         </is>
       </c>
       <c r="C1040" s="5" t="inlineStr">
         <is>
-          <t>Westal</t>
+          <t>ZG Lighting</t>
         </is>
       </c>
       <c r="D1040" s="4" t="n">
@@ -30254,17 +30330,17 @@
     <row r="1041">
       <c r="A1041" s="6" t="inlineStr">
         <is>
-          <t>7024779</t>
+          <t>7028311</t>
         </is>
       </c>
       <c r="B1041" t="inlineStr">
         <is>
-          <t>Interiörarmatur WLP Dor ActiveAhead</t>
+          <t>Interiörarmatur Maya</t>
         </is>
       </c>
       <c r="C1041" t="inlineStr">
         <is>
-          <t>Westal</t>
+          <t>ZG Lighting</t>
         </is>
       </c>
       <c r="D1041" s="6" t="n">
@@ -30274,37 +30350,37 @@
     <row r="1042">
       <c r="A1042" s="4" t="inlineStr">
         <is>
-          <t>7027313</t>
+          <t>7013475</t>
         </is>
       </c>
       <c r="B1042" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur WLP-B</t>
+          <t>Infälld interiörarmatur aLight Office LED</t>
         </is>
       </c>
       <c r="C1042" s="5" t="inlineStr">
         <is>
-          <t>Westal</t>
+          <t>a-collection</t>
         </is>
       </c>
       <c r="D1042" s="4" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1043">
       <c r="A1043" s="6" t="inlineStr">
         <is>
-          <t>7028323</t>
+          <t>7018286</t>
         </is>
       </c>
       <c r="B1043" t="inlineStr">
         <is>
-          <t>Interiörarmatur Beta Force</t>
+          <t>Infälld interiörarmatur aLight Office aPerture</t>
         </is>
       </c>
       <c r="C1043" t="inlineStr">
         <is>
-          <t>ZG Lighting</t>
+          <t>a-collection</t>
         </is>
       </c>
       <c r="D1043" s="6" t="n">
@@ -30314,52 +30390,52 @@
     <row r="1044">
       <c r="A1044" s="4" t="inlineStr">
         <is>
-          <t>7028324</t>
+          <t>7028368</t>
         </is>
       </c>
       <c r="B1044" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Beta Force</t>
+          <t>LED-Panel Flex</t>
         </is>
       </c>
       <c r="C1044" s="5" t="inlineStr">
         <is>
-          <t>ZG Lighting</t>
+          <t>a-collection</t>
         </is>
       </c>
       <c r="D1044" s="4" t="n">
-        <v>0</v>
+        <v>54</v>
       </c>
     </row>
     <row r="1045">
       <c r="A1045" s="6" t="inlineStr">
         <is>
-          <t>7028311</t>
+          <t>7028369</t>
         </is>
       </c>
       <c r="B1045" t="inlineStr">
         <is>
-          <t>Interiörarmatur Maya</t>
+          <t>LED-Panel Flex</t>
         </is>
       </c>
       <c r="C1045" t="inlineStr">
         <is>
-          <t>ZG Lighting</t>
+          <t>a-collection</t>
         </is>
       </c>
       <c r="D1045" s="6" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
     </row>
     <row r="1046">
       <c r="A1046" s="4" t="inlineStr">
         <is>
-          <t>7013475</t>
+          <t>7028001</t>
         </is>
       </c>
       <c r="B1046" s="5" t="inlineStr">
         <is>
-          <t>Infälld interiörarmatur aLight Office LED</t>
+          <t>LED-Panel aLight Office Rektangulär</t>
         </is>
       </c>
       <c r="C1046" s="5" t="inlineStr">
@@ -30368,18 +30444,18 @@
         </is>
       </c>
       <c r="D1046" s="4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1047">
       <c r="A1047" s="6" t="inlineStr">
         <is>
-          <t>7018286</t>
+          <t>7028002</t>
         </is>
       </c>
       <c r="B1047" t="inlineStr">
         <is>
-          <t>Infälld interiörarmatur aLight Office aPerture</t>
+          <t>LED-Panel aLight Office Rektangulär</t>
         </is>
       </c>
       <c r="C1047" t="inlineStr">
@@ -30394,12 +30470,12 @@
     <row r="1048">
       <c r="A1048" s="4" t="inlineStr">
         <is>
-          <t>7028368</t>
+          <t>7027999</t>
         </is>
       </c>
       <c r="B1048" s="5" t="inlineStr">
         <is>
-          <t>LED-Panel Flex</t>
+          <t>LED-panel aLight Office</t>
         </is>
       </c>
       <c r="C1048" s="5" t="inlineStr">
@@ -30408,18 +30484,18 @@
         </is>
       </c>
       <c r="D1048" s="4" t="n">
-        <v>54</v>
+        <v>469</v>
       </c>
     </row>
     <row r="1049">
       <c r="A1049" s="6" t="inlineStr">
         <is>
-          <t>7028369</t>
+          <t>7028000</t>
         </is>
       </c>
       <c r="B1049" t="inlineStr">
         <is>
-          <t>LED-Panel Flex</t>
+          <t>LED-panel aLight Office</t>
         </is>
       </c>
       <c r="C1049" t="inlineStr">
@@ -30428,87 +30504,7 @@
         </is>
       </c>
       <c r="D1049" s="6" t="n">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="1050">
-      <c r="A1050" s="4" t="inlineStr">
-        <is>
-          <t>7028001</t>
-        </is>
-      </c>
-      <c r="B1050" s="5" t="inlineStr">
-        <is>
-          <t>LED-Panel aLight Office Rektangulär</t>
-        </is>
-      </c>
-      <c r="C1050" s="5" t="inlineStr">
-        <is>
-          <t>a-collection</t>
-        </is>
-      </c>
-      <c r="D1050" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1051">
-      <c r="A1051" s="6" t="inlineStr">
-        <is>
-          <t>7028002</t>
-        </is>
-      </c>
-      <c r="B1051" t="inlineStr">
-        <is>
-          <t>LED-Panel aLight Office Rektangulär</t>
-        </is>
-      </c>
-      <c r="C1051" t="inlineStr">
-        <is>
-          <t>a-collection</t>
-        </is>
-      </c>
-      <c r="D1051" s="6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1052">
-      <c r="A1052" s="4" t="inlineStr">
-        <is>
-          <t>7027999</t>
-        </is>
-      </c>
-      <c r="B1052" s="5" t="inlineStr">
-        <is>
-          <t>LED-panel aLight Office</t>
-        </is>
-      </c>
-      <c r="C1052" s="5" t="inlineStr">
-        <is>
-          <t>a-collection</t>
-        </is>
-      </c>
-      <c r="D1052" s="4" t="n">
-        <v>487</v>
-      </c>
-    </row>
-    <row r="1053">
-      <c r="A1053" s="6" t="inlineStr">
-        <is>
-          <t>7028000</t>
-        </is>
-      </c>
-      <c r="B1053" t="inlineStr">
-        <is>
-          <t>LED-panel aLight Office</t>
-        </is>
-      </c>
-      <c r="C1053" t="inlineStr">
-        <is>
-          <t>a-collection</t>
-        </is>
-      </c>
-      <c r="D1053" s="6" t="n">
-        <v>334</v>
+        <v>332</v>
       </c>
     </row>
   </sheetData>
